--- a/output/delivered/Demand_baseline_workshop_2026_10_08_history.xlsx
+++ b/output/delivered/Demand_baseline_workshop_2026_10_08_history.xlsx
@@ -30,12 +30,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="168" formatCode="#,##0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -186,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -654,20 +655,23 @@
     <xf numFmtId="164" fontId="1" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="168" fontId="1" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="4" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -36891,7 +36895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V70"/>
+  <dimension ref="A1:V110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -41255,6 +41259,2060 @@
       <c r="T70" s="155" t="inlineStr"/>
       <c r="U70" s="155" t="inlineStr"/>
       <c r="V70" s="155" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="151" t="inlineStr">
+        <is>
+          <t>6. Estimated sales by province, 2023-2025: petrol (estimates, not observations)</t>
+        </is>
+      </c>
+      <c r="B72" s="151" t="n"/>
+      <c r="C72" s="151" t="n"/>
+      <c r="D72" s="151" t="n"/>
+      <c r="E72" s="151" t="n"/>
+      <c r="F72" s="151" t="n"/>
+      <c r="G72" s="151" t="n"/>
+      <c r="H72" s="151" t="n"/>
+      <c r="I72" s="151" t="n"/>
+      <c r="J72" s="151" t="n"/>
+      <c r="K72" s="151" t="n"/>
+      <c r="L72" s="151" t="n"/>
+      <c r="M72" s="151" t="n"/>
+      <c r="N72" s="151" t="n"/>
+      <c r="O72" s="151" t="n"/>
+      <c r="P72" s="151" t="n"/>
+      <c r="Q72" s="151" t="n"/>
+      <c r="R72" s="151" t="n"/>
+      <c r="S72" s="151" t="n"/>
+      <c r="T72" s="151" t="n"/>
+      <c r="U72" s="151" t="n"/>
+      <c r="V72" s="151" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="161" t="inlineStr">
+        <is>
+          <t>Gauteng share of petrol</t>
+        </is>
+      </c>
+      <c r="B73" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C73" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D73" s="163" t="n"/>
+      <c r="E73" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F73" s="163" t="n"/>
+      <c r="G73" s="163" t="n"/>
+      <c r="H73" s="163" t="n"/>
+      <c r="I73" s="163" t="n"/>
+      <c r="J73" s="163" t="n"/>
+      <c r="K73" s="163" t="n"/>
+      <c r="L73" s="163" t="n"/>
+      <c r="M73" s="163" t="n"/>
+      <c r="N73" s="163" t="n"/>
+      <c r="O73" s="163" t="n"/>
+      <c r="P73" s="163" t="n"/>
+      <c r="Q73" s="163" t="n">
+        <v>38.29082808102595</v>
+      </c>
+      <c r="R73" s="163" t="n">
+        <v>38.377262681276</v>
+      </c>
+      <c r="S73" s="163" t="n">
+        <v>38.377262681276</v>
+      </c>
+      <c r="T73" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U73" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V73" s="161" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="161" t="inlineStr">
+        <is>
+          <t>KwaZulu-Natal share of petrol</t>
+        </is>
+      </c>
+      <c r="B74" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C74" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D74" s="163" t="n"/>
+      <c r="E74" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F74" s="163" t="n"/>
+      <c r="G74" s="163" t="n"/>
+      <c r="H74" s="163" t="n"/>
+      <c r="I74" s="163" t="n"/>
+      <c r="J74" s="163" t="n"/>
+      <c r="K74" s="163" t="n"/>
+      <c r="L74" s="163" t="n"/>
+      <c r="M74" s="163" t="n"/>
+      <c r="N74" s="163" t="n"/>
+      <c r="O74" s="163" t="n"/>
+      <c r="P74" s="163" t="n"/>
+      <c r="Q74" s="163" t="n">
+        <v>16.13082894316334</v>
+      </c>
+      <c r="R74" s="163" t="n">
+        <v>16.11326672611471</v>
+      </c>
+      <c r="S74" s="163" t="n">
+        <v>16.11326672611471</v>
+      </c>
+      <c r="T74" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U74" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V74" s="161" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="161" t="inlineStr">
+        <is>
+          <t>Western Cape share of petrol</t>
+        </is>
+      </c>
+      <c r="B75" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C75" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D75" s="163" t="n"/>
+      <c r="E75" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F75" s="163" t="n"/>
+      <c r="G75" s="163" t="n"/>
+      <c r="H75" s="163" t="n"/>
+      <c r="I75" s="163" t="n"/>
+      <c r="J75" s="163" t="n"/>
+      <c r="K75" s="163" t="n"/>
+      <c r="L75" s="163" t="n"/>
+      <c r="M75" s="163" t="n"/>
+      <c r="N75" s="163" t="n"/>
+      <c r="O75" s="163" t="n"/>
+      <c r="P75" s="163" t="n"/>
+      <c r="Q75" s="163" t="n">
+        <v>16.21627470314407</v>
+      </c>
+      <c r="R75" s="163" t="n">
+        <v>16.24783009372781</v>
+      </c>
+      <c r="S75" s="163" t="n">
+        <v>16.24783009372781</v>
+      </c>
+      <c r="T75" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U75" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V75" s="161" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="161" t="inlineStr">
+        <is>
+          <t>Eastern Cape share of petrol</t>
+        </is>
+      </c>
+      <c r="B76" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C76" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D76" s="163" t="n"/>
+      <c r="E76" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F76" s="163" t="n"/>
+      <c r="G76" s="163" t="n"/>
+      <c r="H76" s="163" t="n"/>
+      <c r="I76" s="163" t="n"/>
+      <c r="J76" s="163" t="n"/>
+      <c r="K76" s="163" t="n"/>
+      <c r="L76" s="163" t="n"/>
+      <c r="M76" s="163" t="n"/>
+      <c r="N76" s="163" t="n"/>
+      <c r="O76" s="163" t="n"/>
+      <c r="P76" s="163" t="n"/>
+      <c r="Q76" s="163" t="n">
+        <v>7.511233012378306</v>
+      </c>
+      <c r="R76" s="163" t="n">
+        <v>7.458565493679201</v>
+      </c>
+      <c r="S76" s="163" t="n">
+        <v>7.458565493679201</v>
+      </c>
+      <c r="T76" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U76" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V76" s="161" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="161" t="inlineStr">
+        <is>
+          <t>Mpumalanga share of petrol</t>
+        </is>
+      </c>
+      <c r="B77" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C77" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D77" s="163" t="n"/>
+      <c r="E77" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F77" s="163" t="n"/>
+      <c r="G77" s="163" t="n"/>
+      <c r="H77" s="163" t="n"/>
+      <c r="I77" s="163" t="n"/>
+      <c r="J77" s="163" t="n"/>
+      <c r="K77" s="163" t="n"/>
+      <c r="L77" s="163" t="n"/>
+      <c r="M77" s="163" t="n"/>
+      <c r="N77" s="163" t="n"/>
+      <c r="O77" s="163" t="n"/>
+      <c r="P77" s="163" t="n"/>
+      <c r="Q77" s="163" t="n">
+        <v>7.055371979667532</v>
+      </c>
+      <c r="R77" s="163" t="n">
+        <v>7.040255181823918</v>
+      </c>
+      <c r="S77" s="163" t="n">
+        <v>7.040255181823918</v>
+      </c>
+      <c r="T77" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U77" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V77" s="161" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="161" t="inlineStr">
+        <is>
+          <t>Free State share of petrol</t>
+        </is>
+      </c>
+      <c r="B78" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C78" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D78" s="163" t="n"/>
+      <c r="E78" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F78" s="163" t="n"/>
+      <c r="G78" s="163" t="n"/>
+      <c r="H78" s="163" t="n"/>
+      <c r="I78" s="163" t="n"/>
+      <c r="J78" s="163" t="n"/>
+      <c r="K78" s="163" t="n"/>
+      <c r="L78" s="163" t="n"/>
+      <c r="M78" s="163" t="n"/>
+      <c r="N78" s="163" t="n"/>
+      <c r="O78" s="163" t="n"/>
+      <c r="P78" s="163" t="n"/>
+      <c r="Q78" s="163" t="n">
+        <v>5.932159079461925</v>
+      </c>
+      <c r="R78" s="163" t="n">
+        <v>5.927995171497546</v>
+      </c>
+      <c r="S78" s="163" t="n">
+        <v>5.927995171497546</v>
+      </c>
+      <c r="T78" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U78" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V78" s="161" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="161" t="inlineStr">
+        <is>
+          <t>North West share of petrol</t>
+        </is>
+      </c>
+      <c r="B79" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C79" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D79" s="163" t="n"/>
+      <c r="E79" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F79" s="163" t="n"/>
+      <c r="G79" s="163" t="n"/>
+      <c r="H79" s="163" t="n"/>
+      <c r="I79" s="163" t="n"/>
+      <c r="J79" s="163" t="n"/>
+      <c r="K79" s="163" t="n"/>
+      <c r="L79" s="163" t="n"/>
+      <c r="M79" s="163" t="n"/>
+      <c r="N79" s="163" t="n"/>
+      <c r="O79" s="163" t="n"/>
+      <c r="P79" s="163" t="n"/>
+      <c r="Q79" s="163" t="n">
+        <v>4.766687274392559</v>
+      </c>
+      <c r="R79" s="163" t="n">
+        <v>4.734315144837777</v>
+      </c>
+      <c r="S79" s="163" t="n">
+        <v>4.734315144837777</v>
+      </c>
+      <c r="T79" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U79" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V79" s="161" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="161" t="inlineStr">
+        <is>
+          <t>Limpopo share of petrol</t>
+        </is>
+      </c>
+      <c r="B80" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C80" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D80" s="163" t="n"/>
+      <c r="E80" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F80" s="163" t="n"/>
+      <c r="G80" s="163" t="n"/>
+      <c r="H80" s="163" t="n"/>
+      <c r="I80" s="163" t="n"/>
+      <c r="J80" s="163" t="n"/>
+      <c r="K80" s="163" t="n"/>
+      <c r="L80" s="163" t="n"/>
+      <c r="M80" s="163" t="n"/>
+      <c r="N80" s="163" t="n"/>
+      <c r="O80" s="163" t="n"/>
+      <c r="P80" s="163" t="n"/>
+      <c r="Q80" s="163" t="n">
+        <v>3.008852500759491</v>
+      </c>
+      <c r="R80" s="163" t="n">
+        <v>3.01928993993442</v>
+      </c>
+      <c r="S80" s="163" t="n">
+        <v>3.01928993993442</v>
+      </c>
+      <c r="T80" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U80" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V80" s="161" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="161" t="inlineStr">
+        <is>
+          <t>Northern Cape share of petrol</t>
+        </is>
+      </c>
+      <c r="B81" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C81" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D81" s="163" t="n"/>
+      <c r="E81" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F81" s="163" t="n"/>
+      <c r="G81" s="163" t="n"/>
+      <c r="H81" s="163" t="n"/>
+      <c r="I81" s="163" t="n"/>
+      <c r="J81" s="163" t="n"/>
+      <c r="K81" s="163" t="n"/>
+      <c r="L81" s="163" t="n"/>
+      <c r="M81" s="163" t="n"/>
+      <c r="N81" s="163" t="n"/>
+      <c r="O81" s="163" t="n"/>
+      <c r="P81" s="163" t="n"/>
+      <c r="Q81" s="163" t="n">
+        <v>1.087764426006824</v>
+      </c>
+      <c r="R81" s="163" t="n">
+        <v>1.081219567108614</v>
+      </c>
+      <c r="S81" s="163" t="n">
+        <v>1.081219567108614</v>
+      </c>
+      <c r="T81" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U81" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V81" s="161" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="161" t="inlineStr">
+        <is>
+          <t>Gauteng petrol, estimated</t>
+        </is>
+      </c>
+      <c r="B82" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C82" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D82" s="164" t="n"/>
+      <c r="E82" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F82" s="164" t="n"/>
+      <c r="G82" s="164" t="n"/>
+      <c r="H82" s="164" t="n"/>
+      <c r="I82" s="164" t="n"/>
+      <c r="J82" s="164" t="n"/>
+      <c r="K82" s="164" t="n"/>
+      <c r="L82" s="164" t="n"/>
+      <c r="M82" s="164" t="n"/>
+      <c r="N82" s="164" t="n"/>
+      <c r="O82" s="164" t="n"/>
+      <c r="P82" s="164" t="n"/>
+      <c r="Q82" s="164">
+        <f>IF(COUNT(Q73,Q57)&lt;2,"",Q73/100*Q57)</f>
+        <v/>
+      </c>
+      <c r="R82" s="164">
+        <f>IF(COUNT(R73,R57)&lt;2,"",R73/100*R57)</f>
+        <v/>
+      </c>
+      <c r="S82" s="164">
+        <f>IF(COUNT(S73,S57)&lt;2,"",S73/100*S57)</f>
+        <v/>
+      </c>
+      <c r="T82" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U82" s="161" t="inlineStr"/>
+      <c r="V82" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="161" t="inlineStr">
+        <is>
+          <t>KwaZulu-Natal petrol, estimated</t>
+        </is>
+      </c>
+      <c r="B83" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C83" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D83" s="164" t="n"/>
+      <c r="E83" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F83" s="164" t="n"/>
+      <c r="G83" s="164" t="n"/>
+      <c r="H83" s="164" t="n"/>
+      <c r="I83" s="164" t="n"/>
+      <c r="J83" s="164" t="n"/>
+      <c r="K83" s="164" t="n"/>
+      <c r="L83" s="164" t="n"/>
+      <c r="M83" s="164" t="n"/>
+      <c r="N83" s="164" t="n"/>
+      <c r="O83" s="164" t="n"/>
+      <c r="P83" s="164" t="n"/>
+      <c r="Q83" s="164">
+        <f>IF(COUNT(Q74,Q57)&lt;2,"",Q74/100*Q57)</f>
+        <v/>
+      </c>
+      <c r="R83" s="164">
+        <f>IF(COUNT(R74,R57)&lt;2,"",R74/100*R57)</f>
+        <v/>
+      </c>
+      <c r="S83" s="164">
+        <f>IF(COUNT(S74,S57)&lt;2,"",S74/100*S57)</f>
+        <v/>
+      </c>
+      <c r="T83" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U83" s="161" t="inlineStr"/>
+      <c r="V83" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="161" t="inlineStr">
+        <is>
+          <t>Western Cape petrol, estimated</t>
+        </is>
+      </c>
+      <c r="B84" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C84" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D84" s="164" t="n"/>
+      <c r="E84" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F84" s="164" t="n"/>
+      <c r="G84" s="164" t="n"/>
+      <c r="H84" s="164" t="n"/>
+      <c r="I84" s="164" t="n"/>
+      <c r="J84" s="164" t="n"/>
+      <c r="K84" s="164" t="n"/>
+      <c r="L84" s="164" t="n"/>
+      <c r="M84" s="164" t="n"/>
+      <c r="N84" s="164" t="n"/>
+      <c r="O84" s="164" t="n"/>
+      <c r="P84" s="164" t="n"/>
+      <c r="Q84" s="164">
+        <f>IF(COUNT(Q75,Q57)&lt;2,"",Q75/100*Q57)</f>
+        <v/>
+      </c>
+      <c r="R84" s="164">
+        <f>IF(COUNT(R75,R57)&lt;2,"",R75/100*R57)</f>
+        <v/>
+      </c>
+      <c r="S84" s="164">
+        <f>IF(COUNT(S75,S57)&lt;2,"",S75/100*S57)</f>
+        <v/>
+      </c>
+      <c r="T84" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U84" s="161" t="inlineStr"/>
+      <c r="V84" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="161" t="inlineStr">
+        <is>
+          <t>Eastern Cape petrol, estimated</t>
+        </is>
+      </c>
+      <c r="B85" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C85" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D85" s="164" t="n"/>
+      <c r="E85" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F85" s="164" t="n"/>
+      <c r="G85" s="164" t="n"/>
+      <c r="H85" s="164" t="n"/>
+      <c r="I85" s="164" t="n"/>
+      <c r="J85" s="164" t="n"/>
+      <c r="K85" s="164" t="n"/>
+      <c r="L85" s="164" t="n"/>
+      <c r="M85" s="164" t="n"/>
+      <c r="N85" s="164" t="n"/>
+      <c r="O85" s="164" t="n"/>
+      <c r="P85" s="164" t="n"/>
+      <c r="Q85" s="164">
+        <f>IF(COUNT(Q76,Q57)&lt;2,"",Q76/100*Q57)</f>
+        <v/>
+      </c>
+      <c r="R85" s="164">
+        <f>IF(COUNT(R76,R57)&lt;2,"",R76/100*R57)</f>
+        <v/>
+      </c>
+      <c r="S85" s="164">
+        <f>IF(COUNT(S76,S57)&lt;2,"",S76/100*S57)</f>
+        <v/>
+      </c>
+      <c r="T85" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U85" s="161" t="inlineStr"/>
+      <c r="V85" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="161" t="inlineStr">
+        <is>
+          <t>Mpumalanga petrol, estimated</t>
+        </is>
+      </c>
+      <c r="B86" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C86" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D86" s="164" t="n"/>
+      <c r="E86" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F86" s="164" t="n"/>
+      <c r="G86" s="164" t="n"/>
+      <c r="H86" s="164" t="n"/>
+      <c r="I86" s="164" t="n"/>
+      <c r="J86" s="164" t="n"/>
+      <c r="K86" s="164" t="n"/>
+      <c r="L86" s="164" t="n"/>
+      <c r="M86" s="164" t="n"/>
+      <c r="N86" s="164" t="n"/>
+      <c r="O86" s="164" t="n"/>
+      <c r="P86" s="164" t="n"/>
+      <c r="Q86" s="164">
+        <f>IF(COUNT(Q77,Q57)&lt;2,"",Q77/100*Q57)</f>
+        <v/>
+      </c>
+      <c r="R86" s="164">
+        <f>IF(COUNT(R77,R57)&lt;2,"",R77/100*R57)</f>
+        <v/>
+      </c>
+      <c r="S86" s="164">
+        <f>IF(COUNT(S77,S57)&lt;2,"",S77/100*S57)</f>
+        <v/>
+      </c>
+      <c r="T86" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U86" s="161" t="inlineStr"/>
+      <c r="V86" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="161" t="inlineStr">
+        <is>
+          <t>Free State petrol, estimated</t>
+        </is>
+      </c>
+      <c r="B87" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C87" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D87" s="164" t="n"/>
+      <c r="E87" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F87" s="164" t="n"/>
+      <c r="G87" s="164" t="n"/>
+      <c r="H87" s="164" t="n"/>
+      <c r="I87" s="164" t="n"/>
+      <c r="J87" s="164" t="n"/>
+      <c r="K87" s="164" t="n"/>
+      <c r="L87" s="164" t="n"/>
+      <c r="M87" s="164" t="n"/>
+      <c r="N87" s="164" t="n"/>
+      <c r="O87" s="164" t="n"/>
+      <c r="P87" s="164" t="n"/>
+      <c r="Q87" s="164">
+        <f>IF(COUNT(Q78,Q57)&lt;2,"",Q78/100*Q57)</f>
+        <v/>
+      </c>
+      <c r="R87" s="164">
+        <f>IF(COUNT(R78,R57)&lt;2,"",R78/100*R57)</f>
+        <v/>
+      </c>
+      <c r="S87" s="164">
+        <f>IF(COUNT(S78,S57)&lt;2,"",S78/100*S57)</f>
+        <v/>
+      </c>
+      <c r="T87" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U87" s="161" t="inlineStr"/>
+      <c r="V87" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="161" t="inlineStr">
+        <is>
+          <t>North West petrol, estimated</t>
+        </is>
+      </c>
+      <c r="B88" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C88" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D88" s="164" t="n"/>
+      <c r="E88" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F88" s="164" t="n"/>
+      <c r="G88" s="164" t="n"/>
+      <c r="H88" s="164" t="n"/>
+      <c r="I88" s="164" t="n"/>
+      <c r="J88" s="164" t="n"/>
+      <c r="K88" s="164" t="n"/>
+      <c r="L88" s="164" t="n"/>
+      <c r="M88" s="164" t="n"/>
+      <c r="N88" s="164" t="n"/>
+      <c r="O88" s="164" t="n"/>
+      <c r="P88" s="164" t="n"/>
+      <c r="Q88" s="164">
+        <f>IF(COUNT(Q79,Q57)&lt;2,"",Q79/100*Q57)</f>
+        <v/>
+      </c>
+      <c r="R88" s="164">
+        <f>IF(COUNT(R79,R57)&lt;2,"",R79/100*R57)</f>
+        <v/>
+      </c>
+      <c r="S88" s="164">
+        <f>IF(COUNT(S79,S57)&lt;2,"",S79/100*S57)</f>
+        <v/>
+      </c>
+      <c r="T88" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U88" s="161" t="inlineStr"/>
+      <c r="V88" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="161" t="inlineStr">
+        <is>
+          <t>Limpopo petrol, estimated</t>
+        </is>
+      </c>
+      <c r="B89" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C89" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D89" s="164" t="n"/>
+      <c r="E89" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F89" s="164" t="n"/>
+      <c r="G89" s="164" t="n"/>
+      <c r="H89" s="164" t="n"/>
+      <c r="I89" s="164" t="n"/>
+      <c r="J89" s="164" t="n"/>
+      <c r="K89" s="164" t="n"/>
+      <c r="L89" s="164" t="n"/>
+      <c r="M89" s="164" t="n"/>
+      <c r="N89" s="164" t="n"/>
+      <c r="O89" s="164" t="n"/>
+      <c r="P89" s="164" t="n"/>
+      <c r="Q89" s="164">
+        <f>IF(COUNT(Q80,Q57)&lt;2,"",Q80/100*Q57)</f>
+        <v/>
+      </c>
+      <c r="R89" s="164">
+        <f>IF(COUNT(R80,R57)&lt;2,"",R80/100*R57)</f>
+        <v/>
+      </c>
+      <c r="S89" s="164">
+        <f>IF(COUNT(S80,S57)&lt;2,"",S80/100*S57)</f>
+        <v/>
+      </c>
+      <c r="T89" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U89" s="161" t="inlineStr"/>
+      <c r="V89" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="161" t="inlineStr">
+        <is>
+          <t>Northern Cape petrol, estimated</t>
+        </is>
+      </c>
+      <c r="B90" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C90" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D90" s="164" t="n"/>
+      <c r="E90" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F90" s="164" t="n"/>
+      <c r="G90" s="164" t="n"/>
+      <c r="H90" s="164" t="n"/>
+      <c r="I90" s="164" t="n"/>
+      <c r="J90" s="164" t="n"/>
+      <c r="K90" s="164" t="n"/>
+      <c r="L90" s="164" t="n"/>
+      <c r="M90" s="164" t="n"/>
+      <c r="N90" s="164" t="n"/>
+      <c r="O90" s="164" t="n"/>
+      <c r="P90" s="164" t="n"/>
+      <c r="Q90" s="164">
+        <f>IF(COUNT(Q81,Q57)&lt;2,"",Q81/100*Q57)</f>
+        <v/>
+      </c>
+      <c r="R90" s="164">
+        <f>IF(COUNT(R81,R57)&lt;2,"",R81/100*R57)</f>
+        <v/>
+      </c>
+      <c r="S90" s="164">
+        <f>IF(COUNT(S81,S57)&lt;2,"",S81/100*S57)</f>
+        <v/>
+      </c>
+      <c r="T90" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U90" s="161" t="inlineStr"/>
+      <c r="V90" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="151" t="inlineStr">
+        <is>
+          <t>6. Estimated sales by province, 2023-2025: diesel (estimates, not observations)</t>
+        </is>
+      </c>
+      <c r="B92" s="151" t="n"/>
+      <c r="C92" s="151" t="n"/>
+      <c r="D92" s="151" t="n"/>
+      <c r="E92" s="151" t="n"/>
+      <c r="F92" s="151" t="n"/>
+      <c r="G92" s="151" t="n"/>
+      <c r="H92" s="151" t="n"/>
+      <c r="I92" s="151" t="n"/>
+      <c r="J92" s="151" t="n"/>
+      <c r="K92" s="151" t="n"/>
+      <c r="L92" s="151" t="n"/>
+      <c r="M92" s="151" t="n"/>
+      <c r="N92" s="151" t="n"/>
+      <c r="O92" s="151" t="n"/>
+      <c r="P92" s="151" t="n"/>
+      <c r="Q92" s="151" t="n"/>
+      <c r="R92" s="151" t="n"/>
+      <c r="S92" s="151" t="n"/>
+      <c r="T92" s="151" t="n"/>
+      <c r="U92" s="151" t="n"/>
+      <c r="V92" s="151" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="161" t="inlineStr">
+        <is>
+          <t>Gauteng share of diesel</t>
+        </is>
+      </c>
+      <c r="B93" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C93" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D93" s="163" t="n"/>
+      <c r="E93" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F93" s="163" t="n"/>
+      <c r="G93" s="163" t="n"/>
+      <c r="H93" s="163" t="n"/>
+      <c r="I93" s="163" t="n"/>
+      <c r="J93" s="163" t="n"/>
+      <c r="K93" s="163" t="n"/>
+      <c r="L93" s="163" t="n"/>
+      <c r="M93" s="163" t="n"/>
+      <c r="N93" s="163" t="n"/>
+      <c r="O93" s="163" t="n"/>
+      <c r="P93" s="163" t="n"/>
+      <c r="Q93" s="163" t="n">
+        <v>25.95571268012436</v>
+      </c>
+      <c r="R93" s="163" t="n">
+        <v>26.02351192632266</v>
+      </c>
+      <c r="S93" s="163" t="n">
+        <v>26.02351192632266</v>
+      </c>
+      <c r="T93" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U93" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V93" s="161" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="161" t="inlineStr">
+        <is>
+          <t>KwaZulu-Natal share of diesel</t>
+        </is>
+      </c>
+      <c r="B94" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C94" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D94" s="163" t="n"/>
+      <c r="E94" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F94" s="163" t="n"/>
+      <c r="G94" s="163" t="n"/>
+      <c r="H94" s="163" t="n"/>
+      <c r="I94" s="163" t="n"/>
+      <c r="J94" s="163" t="n"/>
+      <c r="K94" s="163" t="n"/>
+      <c r="L94" s="163" t="n"/>
+      <c r="M94" s="163" t="n"/>
+      <c r="N94" s="163" t="n"/>
+      <c r="O94" s="163" t="n"/>
+      <c r="P94" s="163" t="n"/>
+      <c r="Q94" s="163" t="n">
+        <v>18.98574601235529</v>
+      </c>
+      <c r="R94" s="163" t="n">
+        <v>18.97178908483028</v>
+      </c>
+      <c r="S94" s="163" t="n">
+        <v>18.97178908483028</v>
+      </c>
+      <c r="T94" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U94" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V94" s="161" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="161" t="inlineStr">
+        <is>
+          <t>Western Cape share of diesel</t>
+        </is>
+      </c>
+      <c r="B95" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C95" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D95" s="163" t="n"/>
+      <c r="E95" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F95" s="163" t="n"/>
+      <c r="G95" s="163" t="n"/>
+      <c r="H95" s="163" t="n"/>
+      <c r="I95" s="163" t="n"/>
+      <c r="J95" s="163" t="n"/>
+      <c r="K95" s="163" t="n"/>
+      <c r="L95" s="163" t="n"/>
+      <c r="M95" s="163" t="n"/>
+      <c r="N95" s="163" t="n"/>
+      <c r="O95" s="163" t="n"/>
+      <c r="P95" s="163" t="n"/>
+      <c r="Q95" s="163" t="n">
+        <v>23.48567896125875</v>
+      </c>
+      <c r="R95" s="163" t="n">
+        <v>23.53970993881584</v>
+      </c>
+      <c r="S95" s="163" t="n">
+        <v>23.53970993881584</v>
+      </c>
+      <c r="T95" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U95" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V95" s="161" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="161" t="inlineStr">
+        <is>
+          <t>Eastern Cape share of diesel</t>
+        </is>
+      </c>
+      <c r="B96" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C96" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D96" s="163" t="n"/>
+      <c r="E96" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F96" s="163" t="n"/>
+      <c r="G96" s="163" t="n"/>
+      <c r="H96" s="163" t="n"/>
+      <c r="I96" s="163" t="n"/>
+      <c r="J96" s="163" t="n"/>
+      <c r="K96" s="163" t="n"/>
+      <c r="L96" s="163" t="n"/>
+      <c r="M96" s="163" t="n"/>
+      <c r="N96" s="163" t="n"/>
+      <c r="O96" s="163" t="n"/>
+      <c r="P96" s="163" t="n"/>
+      <c r="Q96" s="163" t="n">
+        <v>7.89067723132441</v>
+      </c>
+      <c r="R96" s="163" t="n">
+        <v>7.83812278680507</v>
+      </c>
+      <c r="S96" s="163" t="n">
+        <v>7.83812278680507</v>
+      </c>
+      <c r="T96" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U96" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V96" s="161" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="161" t="inlineStr">
+        <is>
+          <t>Mpumalanga share of diesel</t>
+        </is>
+      </c>
+      <c r="B97" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C97" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D97" s="163" t="n"/>
+      <c r="E97" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F97" s="163" t="n"/>
+      <c r="G97" s="163" t="n"/>
+      <c r="H97" s="163" t="n"/>
+      <c r="I97" s="163" t="n"/>
+      <c r="J97" s="163" t="n"/>
+      <c r="K97" s="163" t="n"/>
+      <c r="L97" s="163" t="n"/>
+      <c r="M97" s="163" t="n"/>
+      <c r="N97" s="163" t="n"/>
+      <c r="O97" s="163" t="n"/>
+      <c r="P97" s="163" t="n"/>
+      <c r="Q97" s="163" t="n">
+        <v>9.154016030764375</v>
+      </c>
+      <c r="R97" s="163" t="n">
+        <v>9.137636223166661</v>
+      </c>
+      <c r="S97" s="163" t="n">
+        <v>9.137636223166661</v>
+      </c>
+      <c r="T97" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U97" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V97" s="161" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="161" t="inlineStr">
+        <is>
+          <t>Free State share of diesel</t>
+        </is>
+      </c>
+      <c r="B98" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C98" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D98" s="163" t="n"/>
+      <c r="E98" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F98" s="163" t="n"/>
+      <c r="G98" s="163" t="n"/>
+      <c r="H98" s="163" t="n"/>
+      <c r="I98" s="163" t="n"/>
+      <c r="J98" s="163" t="n"/>
+      <c r="K98" s="163" t="n"/>
+      <c r="L98" s="163" t="n"/>
+      <c r="M98" s="163" t="n"/>
+      <c r="N98" s="163" t="n"/>
+      <c r="O98" s="163" t="n"/>
+      <c r="P98" s="163" t="n"/>
+      <c r="Q98" s="163" t="n">
+        <v>5.426397730797064</v>
+      </c>
+      <c r="R98" s="163" t="n">
+        <v>5.42450839649958</v>
+      </c>
+      <c r="S98" s="163" t="n">
+        <v>5.42450839649958</v>
+      </c>
+      <c r="T98" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U98" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V98" s="161" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="161" t="inlineStr">
+        <is>
+          <t>North West share of diesel</t>
+        </is>
+      </c>
+      <c r="B99" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C99" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D99" s="163" t="n"/>
+      <c r="E99" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F99" s="163" t="n"/>
+      <c r="G99" s="163" t="n"/>
+      <c r="H99" s="163" t="n"/>
+      <c r="I99" s="163" t="n"/>
+      <c r="J99" s="163" t="n"/>
+      <c r="K99" s="163" t="n"/>
+      <c r="L99" s="163" t="n"/>
+      <c r="M99" s="163" t="n"/>
+      <c r="N99" s="163" t="n"/>
+      <c r="O99" s="163" t="n"/>
+      <c r="P99" s="163" t="n"/>
+      <c r="Q99" s="163" t="n">
+        <v>4.4050379640929</v>
+      </c>
+      <c r="R99" s="163" t="n">
+        <v>4.376670684154155</v>
+      </c>
+      <c r="S99" s="163" t="n">
+        <v>4.376670684154155</v>
+      </c>
+      <c r="T99" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U99" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V99" s="161" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="161" t="inlineStr">
+        <is>
+          <t>Limpopo share of diesel</t>
+        </is>
+      </c>
+      <c r="B100" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C100" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D100" s="163" t="n"/>
+      <c r="E100" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F100" s="163" t="n"/>
+      <c r="G100" s="163" t="n"/>
+      <c r="H100" s="163" t="n"/>
+      <c r="I100" s="163" t="n"/>
+      <c r="J100" s="163" t="n"/>
+      <c r="K100" s="163" t="n"/>
+      <c r="L100" s="163" t="n"/>
+      <c r="M100" s="163" t="n"/>
+      <c r="N100" s="163" t="n"/>
+      <c r="O100" s="163" t="n"/>
+      <c r="P100" s="163" t="n"/>
+      <c r="Q100" s="163" t="n">
+        <v>1.888937215844854</v>
+      </c>
+      <c r="R100" s="163" t="n">
+        <v>1.896160763259574</v>
+      </c>
+      <c r="S100" s="163" t="n">
+        <v>1.896160763259574</v>
+      </c>
+      <c r="T100" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U100" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V100" s="161" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="161" t="inlineStr">
+        <is>
+          <t>Northern Cape share of diesel</t>
+        </is>
+      </c>
+      <c r="B101" s="162" t="inlineStr">
+        <is>
+          <t>% of national</t>
+        </is>
+      </c>
+      <c r="C101" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D101" s="163" t="n"/>
+      <c r="E101" s="161" t="inlineStr">
+        <is>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F101" s="163" t="n"/>
+      <c r="G101" s="163" t="n"/>
+      <c r="H101" s="163" t="n"/>
+      <c r="I101" s="163" t="n"/>
+      <c r="J101" s="163" t="n"/>
+      <c r="K101" s="163" t="n"/>
+      <c r="L101" s="163" t="n"/>
+      <c r="M101" s="163" t="n"/>
+      <c r="N101" s="163" t="n"/>
+      <c r="O101" s="163" t="n"/>
+      <c r="P101" s="163" t="n"/>
+      <c r="Q101" s="163" t="n">
+        <v>2.807796173437997</v>
+      </c>
+      <c r="R101" s="163" t="n">
+        <v>2.791890196146183</v>
+      </c>
+      <c r="S101" s="163" t="n">
+        <v>2.791890196146183</v>
+      </c>
+      <c r="T101" s="161" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U101" s="161" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V101" s="161" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="161" t="inlineStr">
+        <is>
+          <t>Gauteng diesel, estimated</t>
+        </is>
+      </c>
+      <c r="B102" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C102" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D102" s="164" t="n"/>
+      <c r="E102" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F102" s="164" t="n"/>
+      <c r="G102" s="164" t="n"/>
+      <c r="H102" s="164" t="n"/>
+      <c r="I102" s="164" t="n"/>
+      <c r="J102" s="164" t="n"/>
+      <c r="K102" s="164" t="n"/>
+      <c r="L102" s="164" t="n"/>
+      <c r="M102" s="164" t="n"/>
+      <c r="N102" s="164" t="n"/>
+      <c r="O102" s="164" t="n"/>
+      <c r="P102" s="164" t="n"/>
+      <c r="Q102" s="164">
+        <f>IF(COUNT(Q93,Q62)&lt;2,"",Q93/100*Q62)</f>
+        <v/>
+      </c>
+      <c r="R102" s="164">
+        <f>IF(COUNT(R93,R62)&lt;2,"",R93/100*R62)</f>
+        <v/>
+      </c>
+      <c r="S102" s="164">
+        <f>IF(COUNT(S93,S62)&lt;2,"",S93/100*S62)</f>
+        <v/>
+      </c>
+      <c r="T102" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U102" s="161" t="inlineStr"/>
+      <c r="V102" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="161" t="inlineStr">
+        <is>
+          <t>KwaZulu-Natal diesel, estimated</t>
+        </is>
+      </c>
+      <c r="B103" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C103" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D103" s="164" t="n"/>
+      <c r="E103" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F103" s="164" t="n"/>
+      <c r="G103" s="164" t="n"/>
+      <c r="H103" s="164" t="n"/>
+      <c r="I103" s="164" t="n"/>
+      <c r="J103" s="164" t="n"/>
+      <c r="K103" s="164" t="n"/>
+      <c r="L103" s="164" t="n"/>
+      <c r="M103" s="164" t="n"/>
+      <c r="N103" s="164" t="n"/>
+      <c r="O103" s="164" t="n"/>
+      <c r="P103" s="164" t="n"/>
+      <c r="Q103" s="164">
+        <f>IF(COUNT(Q94,Q62)&lt;2,"",Q94/100*Q62)</f>
+        <v/>
+      </c>
+      <c r="R103" s="164">
+        <f>IF(COUNT(R94,R62)&lt;2,"",R94/100*R62)</f>
+        <v/>
+      </c>
+      <c r="S103" s="164">
+        <f>IF(COUNT(S94,S62)&lt;2,"",S94/100*S62)</f>
+        <v/>
+      </c>
+      <c r="T103" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U103" s="161" t="inlineStr"/>
+      <c r="V103" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="161" t="inlineStr">
+        <is>
+          <t>Western Cape diesel, estimated</t>
+        </is>
+      </c>
+      <c r="B104" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C104" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D104" s="164" t="n"/>
+      <c r="E104" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F104" s="164" t="n"/>
+      <c r="G104" s="164" t="n"/>
+      <c r="H104" s="164" t="n"/>
+      <c r="I104" s="164" t="n"/>
+      <c r="J104" s="164" t="n"/>
+      <c r="K104" s="164" t="n"/>
+      <c r="L104" s="164" t="n"/>
+      <c r="M104" s="164" t="n"/>
+      <c r="N104" s="164" t="n"/>
+      <c r="O104" s="164" t="n"/>
+      <c r="P104" s="164" t="n"/>
+      <c r="Q104" s="164">
+        <f>IF(COUNT(Q95,Q62)&lt;2,"",Q95/100*Q62)</f>
+        <v/>
+      </c>
+      <c r="R104" s="164">
+        <f>IF(COUNT(R95,R62)&lt;2,"",R95/100*R62)</f>
+        <v/>
+      </c>
+      <c r="S104" s="164">
+        <f>IF(COUNT(S95,S62)&lt;2,"",S95/100*S62)</f>
+        <v/>
+      </c>
+      <c r="T104" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U104" s="161" t="inlineStr"/>
+      <c r="V104" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="161" t="inlineStr">
+        <is>
+          <t>Eastern Cape diesel, estimated</t>
+        </is>
+      </c>
+      <c r="B105" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C105" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D105" s="164" t="n"/>
+      <c r="E105" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F105" s="164" t="n"/>
+      <c r="G105" s="164" t="n"/>
+      <c r="H105" s="164" t="n"/>
+      <c r="I105" s="164" t="n"/>
+      <c r="J105" s="164" t="n"/>
+      <c r="K105" s="164" t="n"/>
+      <c r="L105" s="164" t="n"/>
+      <c r="M105" s="164" t="n"/>
+      <c r="N105" s="164" t="n"/>
+      <c r="O105" s="164" t="n"/>
+      <c r="P105" s="164" t="n"/>
+      <c r="Q105" s="164">
+        <f>IF(COUNT(Q96,Q62)&lt;2,"",Q96/100*Q62)</f>
+        <v/>
+      </c>
+      <c r="R105" s="164">
+        <f>IF(COUNT(R96,R62)&lt;2,"",R96/100*R62)</f>
+        <v/>
+      </c>
+      <c r="S105" s="164">
+        <f>IF(COUNT(S96,S62)&lt;2,"",S96/100*S62)</f>
+        <v/>
+      </c>
+      <c r="T105" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U105" s="161" t="inlineStr"/>
+      <c r="V105" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="161" t="inlineStr">
+        <is>
+          <t>Mpumalanga diesel, estimated</t>
+        </is>
+      </c>
+      <c r="B106" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C106" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D106" s="164" t="n"/>
+      <c r="E106" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F106" s="164" t="n"/>
+      <c r="G106" s="164" t="n"/>
+      <c r="H106" s="164" t="n"/>
+      <c r="I106" s="164" t="n"/>
+      <c r="J106" s="164" t="n"/>
+      <c r="K106" s="164" t="n"/>
+      <c r="L106" s="164" t="n"/>
+      <c r="M106" s="164" t="n"/>
+      <c r="N106" s="164" t="n"/>
+      <c r="O106" s="164" t="n"/>
+      <c r="P106" s="164" t="n"/>
+      <c r="Q106" s="164">
+        <f>IF(COUNT(Q97,Q62)&lt;2,"",Q97/100*Q62)</f>
+        <v/>
+      </c>
+      <c r="R106" s="164">
+        <f>IF(COUNT(R97,R62)&lt;2,"",R97/100*R62)</f>
+        <v/>
+      </c>
+      <c r="S106" s="164">
+        <f>IF(COUNT(S97,S62)&lt;2,"",S97/100*S62)</f>
+        <v/>
+      </c>
+      <c r="T106" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U106" s="161" t="inlineStr"/>
+      <c r="V106" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="161" t="inlineStr">
+        <is>
+          <t>Free State diesel, estimated</t>
+        </is>
+      </c>
+      <c r="B107" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C107" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D107" s="164" t="n"/>
+      <c r="E107" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F107" s="164" t="n"/>
+      <c r="G107" s="164" t="n"/>
+      <c r="H107" s="164" t="n"/>
+      <c r="I107" s="164" t="n"/>
+      <c r="J107" s="164" t="n"/>
+      <c r="K107" s="164" t="n"/>
+      <c r="L107" s="164" t="n"/>
+      <c r="M107" s="164" t="n"/>
+      <c r="N107" s="164" t="n"/>
+      <c r="O107" s="164" t="n"/>
+      <c r="P107" s="164" t="n"/>
+      <c r="Q107" s="164">
+        <f>IF(COUNT(Q98,Q62)&lt;2,"",Q98/100*Q62)</f>
+        <v/>
+      </c>
+      <c r="R107" s="164">
+        <f>IF(COUNT(R98,R62)&lt;2,"",R98/100*R62)</f>
+        <v/>
+      </c>
+      <c r="S107" s="164">
+        <f>IF(COUNT(S98,S62)&lt;2,"",S98/100*S62)</f>
+        <v/>
+      </c>
+      <c r="T107" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U107" s="161" t="inlineStr"/>
+      <c r="V107" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="161" t="inlineStr">
+        <is>
+          <t>North West diesel, estimated</t>
+        </is>
+      </c>
+      <c r="B108" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C108" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D108" s="164" t="n"/>
+      <c r="E108" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F108" s="164" t="n"/>
+      <c r="G108" s="164" t="n"/>
+      <c r="H108" s="164" t="n"/>
+      <c r="I108" s="164" t="n"/>
+      <c r="J108" s="164" t="n"/>
+      <c r="K108" s="164" t="n"/>
+      <c r="L108" s="164" t="n"/>
+      <c r="M108" s="164" t="n"/>
+      <c r="N108" s="164" t="n"/>
+      <c r="O108" s="164" t="n"/>
+      <c r="P108" s="164" t="n"/>
+      <c r="Q108" s="164">
+        <f>IF(COUNT(Q99,Q62)&lt;2,"",Q99/100*Q62)</f>
+        <v/>
+      </c>
+      <c r="R108" s="164">
+        <f>IF(COUNT(R99,R62)&lt;2,"",R99/100*R62)</f>
+        <v/>
+      </c>
+      <c r="S108" s="164">
+        <f>IF(COUNT(S99,S62)&lt;2,"",S99/100*S62)</f>
+        <v/>
+      </c>
+      <c r="T108" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U108" s="161" t="inlineStr"/>
+      <c r="V108" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="161" t="inlineStr">
+        <is>
+          <t>Limpopo diesel, estimated</t>
+        </is>
+      </c>
+      <c r="B109" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C109" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D109" s="164" t="n"/>
+      <c r="E109" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F109" s="164" t="n"/>
+      <c r="G109" s="164" t="n"/>
+      <c r="H109" s="164" t="n"/>
+      <c r="I109" s="164" t="n"/>
+      <c r="J109" s="164" t="n"/>
+      <c r="K109" s="164" t="n"/>
+      <c r="L109" s="164" t="n"/>
+      <c r="M109" s="164" t="n"/>
+      <c r="N109" s="164" t="n"/>
+      <c r="O109" s="164" t="n"/>
+      <c r="P109" s="164" t="n"/>
+      <c r="Q109" s="164">
+        <f>IF(COUNT(Q100,Q62)&lt;2,"",Q100/100*Q62)</f>
+        <v/>
+      </c>
+      <c r="R109" s="164">
+        <f>IF(COUNT(R100,R62)&lt;2,"",R100/100*R62)</f>
+        <v/>
+      </c>
+      <c r="S109" s="164">
+        <f>IF(COUNT(S100,S62)&lt;2,"",S100/100*S62)</f>
+        <v/>
+      </c>
+      <c r="T109" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U109" s="161" t="inlineStr"/>
+      <c r="V109" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="161" t="inlineStr">
+        <is>
+          <t>Northern Cape diesel, estimated</t>
+        </is>
+      </c>
+      <c r="B110" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C110" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D110" s="164" t="n"/>
+      <c r="E110" s="161" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F110" s="164" t="n"/>
+      <c r="G110" s="164" t="n"/>
+      <c r="H110" s="164" t="n"/>
+      <c r="I110" s="164" t="n"/>
+      <c r="J110" s="164" t="n"/>
+      <c r="K110" s="164" t="n"/>
+      <c r="L110" s="164" t="n"/>
+      <c r="M110" s="164" t="n"/>
+      <c r="N110" s="164" t="n"/>
+      <c r="O110" s="164" t="n"/>
+      <c r="P110" s="164" t="n"/>
+      <c r="Q110" s="164">
+        <f>IF(COUNT(Q101,Q62)&lt;2,"",Q101/100*Q62)</f>
+        <v/>
+      </c>
+      <c r="R110" s="164">
+        <f>IF(COUNT(R101,R62)&lt;2,"",R101/100*R62)</f>
+        <v/>
+      </c>
+      <c r="S110" s="164">
+        <f>IF(COUNT(S101,S62)&lt;2,"",S101/100*S62)</f>
+        <v/>
+      </c>
+      <c r="T110" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U110" s="161" t="inlineStr"/>
+      <c r="V110" s="161" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -41580,65 +43638,65 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D8" s="161" t="n"/>
+      <c r="D8" s="165" t="n"/>
       <c r="E8" s="155" t="inlineStr">
         <is>
           <t>Diesel divided by the activity measure, each year both exist.</t>
         </is>
       </c>
-      <c r="F8" s="161">
+      <c r="F8" s="165">
         <f>IF(COUNT(F6,F7)&lt;2,"",F6/F7)</f>
         <v/>
       </c>
-      <c r="G8" s="161">
+      <c r="G8" s="165">
         <f>IF(COUNT(G6,G7)&lt;2,"",G6/G7)</f>
         <v/>
       </c>
-      <c r="H8" s="161">
+      <c r="H8" s="165">
         <f>IF(COUNT(H6,H7)&lt;2,"",H6/H7)</f>
         <v/>
       </c>
-      <c r="I8" s="161">
+      <c r="I8" s="165">
         <f>IF(COUNT(I6,I7)&lt;2,"",I6/I7)</f>
         <v/>
       </c>
-      <c r="J8" s="161">
+      <c r="J8" s="165">
         <f>IF(COUNT(J6,J7)&lt;2,"",J6/J7)</f>
         <v/>
       </c>
-      <c r="K8" s="161">
+      <c r="K8" s="165">
         <f>IF(COUNT(K6,K7)&lt;2,"",K6/K7)</f>
         <v/>
       </c>
-      <c r="L8" s="161">
+      <c r="L8" s="165">
         <f>IF(COUNT(L6,L7)&lt;2,"",L6/L7)</f>
         <v/>
       </c>
-      <c r="M8" s="161">
+      <c r="M8" s="165">
         <f>IF(COUNT(M6,M7)&lt;2,"",M6/M7)</f>
         <v/>
       </c>
-      <c r="N8" s="161">
+      <c r="N8" s="165">
         <f>IF(COUNT(N6,N7)&lt;2,"",N6/N7)</f>
         <v/>
       </c>
-      <c r="O8" s="161">
+      <c r="O8" s="165">
         <f>IF(COUNT(O6,O7)&lt;2,"",O6/O7)</f>
         <v/>
       </c>
-      <c r="P8" s="161">
+      <c r="P8" s="165">
         <f>IF(COUNT(P6,P7)&lt;2,"",P6/P7)</f>
         <v/>
       </c>
-      <c r="Q8" s="161">
+      <c r="Q8" s="165">
         <f>IF(COUNT(Q6,Q7)&lt;2,"",Q6/Q7)</f>
         <v/>
       </c>
-      <c r="R8" s="161">
+      <c r="R8" s="165">
         <f>IF(COUNT(R6,R7)&lt;2,"",R6/R7)</f>
         <v/>
       </c>
-      <c r="S8" s="161">
+      <c r="S8" s="165">
         <f>IF(COUNT(S6,S7)&lt;2,"",S6/S7)</f>
         <v/>
       </c>
@@ -41647,17 +43705,17 @@
       <c r="V8" s="155" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="162" t="inlineStr">
+      <c r="A9" s="161" t="inlineStr">
         <is>
           <t>Indicative diesel at observed activity (mining and quarrying diesel)</t>
         </is>
       </c>
-      <c r="B9" s="163" t="inlineStr">
+      <c r="B9" s="162" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C9" s="163" t="inlineStr">
+      <c r="C9" s="162" t="inlineStr">
         <is>
           <t>Proposed estimate</t>
         </is>
@@ -41666,7 +43724,7 @@
         <f>AVERAGE(L8:O8)</f>
         <v/>
       </c>
-      <c r="E9" s="162" t="inlineStr">
+      <c r="E9" s="161" t="inlineStr">
         <is>
           <t>Average 2018-2021 intensity (column D) times the activity measure. An indication for years without a balance; not an observation and not an accepted input.</t>
         </is>
@@ -41727,13 +43785,13 @@
         <f>IF(ISNUMBER(S7),$D$9*S7,"")</f>
         <v/>
       </c>
-      <c r="T9" s="162" t="inlineStr">
+      <c r="T9" s="161" t="inlineStr">
         <is>
           <t>Estimate for discussion</t>
         </is>
       </c>
-      <c r="U9" s="162" t="inlineStr"/>
-      <c r="V9" s="162" t="inlineStr">
+      <c r="U9" s="161" t="inlineStr"/>
+      <c r="V9" s="161" t="inlineStr">
         <is>
           <t>Agree base year, driver and whether intensity is held constant (Nigel)</t>
         </is>
@@ -42103,65 +44161,65 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D18" s="161" t="n"/>
+      <c r="D18" s="165" t="n"/>
       <c r="E18" s="155" t="inlineStr">
         <is>
           <t>Diesel divided by the activity measure, each year both exist.</t>
         </is>
       </c>
-      <c r="F18" s="161">
+      <c r="F18" s="165">
         <f>IF(COUNT(F16,F17)&lt;2,"",F16/F17)</f>
         <v/>
       </c>
-      <c r="G18" s="161">
+      <c r="G18" s="165">
         <f>IF(COUNT(G16,G17)&lt;2,"",G16/G17)</f>
         <v/>
       </c>
-      <c r="H18" s="161">
+      <c r="H18" s="165">
         <f>IF(COUNT(H16,H17)&lt;2,"",H16/H17)</f>
         <v/>
       </c>
-      <c r="I18" s="161">
+      <c r="I18" s="165">
         <f>IF(COUNT(I16,I17)&lt;2,"",I16/I17)</f>
         <v/>
       </c>
-      <c r="J18" s="161">
+      <c r="J18" s="165">
         <f>IF(COUNT(J16,J17)&lt;2,"",J16/J17)</f>
         <v/>
       </c>
-      <c r="K18" s="161">
+      <c r="K18" s="165">
         <f>IF(COUNT(K16,K17)&lt;2,"",K16/K17)</f>
         <v/>
       </c>
-      <c r="L18" s="161">
+      <c r="L18" s="165">
         <f>IF(COUNT(L16,L17)&lt;2,"",L16/L17)</f>
         <v/>
       </c>
-      <c r="M18" s="161">
+      <c r="M18" s="165">
         <f>IF(COUNT(M16,M17)&lt;2,"",M16/M17)</f>
         <v/>
       </c>
-      <c r="N18" s="161">
+      <c r="N18" s="165">
         <f>IF(COUNT(N16,N17)&lt;2,"",N16/N17)</f>
         <v/>
       </c>
-      <c r="O18" s="161">
+      <c r="O18" s="165">
         <f>IF(COUNT(O16,O17)&lt;2,"",O16/O17)</f>
         <v/>
       </c>
-      <c r="P18" s="161">
+      <c r="P18" s="165">
         <f>IF(COUNT(P16,P17)&lt;2,"",P16/P17)</f>
         <v/>
       </c>
-      <c r="Q18" s="161">
+      <c r="Q18" s="165">
         <f>IF(COUNT(Q16,Q17)&lt;2,"",Q16/Q17)</f>
         <v/>
       </c>
-      <c r="R18" s="161">
+      <c r="R18" s="165">
         <f>IF(COUNT(R16,R17)&lt;2,"",R16/R17)</f>
         <v/>
       </c>
-      <c r="S18" s="161">
+      <c r="S18" s="165">
         <f>IF(COUNT(S16,S17)&lt;2,"",S16/S17)</f>
         <v/>
       </c>
@@ -42170,17 +44228,17 @@
       <c r="V18" s="155" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="162" t="inlineStr">
+      <c r="A19" s="161" t="inlineStr">
         <is>
           <t>Indicative diesel at observed activity (manufacturing and other industry diesel)</t>
         </is>
       </c>
-      <c r="B19" s="163" t="inlineStr">
+      <c r="B19" s="162" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C19" s="163" t="inlineStr">
+      <c r="C19" s="162" t="inlineStr">
         <is>
           <t>Proposed estimate</t>
         </is>
@@ -42189,7 +44247,7 @@
         <f>AVERAGE(L18:O18)</f>
         <v/>
       </c>
-      <c r="E19" s="162" t="inlineStr">
+      <c r="E19" s="161" t="inlineStr">
         <is>
           <t>Average 2018-2021 intensity (column D) times the activity measure. An indication for years without a balance; not an observation and not an accepted input.</t>
         </is>
@@ -42250,13 +44308,13 @@
         <f>IF(ISNUMBER(S17),$D$19*S17,"")</f>
         <v/>
       </c>
-      <c r="T19" s="162" t="inlineStr">
+      <c r="T19" s="161" t="inlineStr">
         <is>
           <t>Estimate for discussion</t>
         </is>
       </c>
-      <c r="U19" s="162" t="inlineStr"/>
-      <c r="V19" s="162" t="inlineStr">
+      <c r="U19" s="161" t="inlineStr"/>
+      <c r="V19" s="161" t="inlineStr">
         <is>
           <t>Agree base year, driver and whether intensity is held constant (Nigel)</t>
         </is>
@@ -42450,65 +44508,65 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D24" s="161" t="n"/>
+      <c r="D24" s="165" t="n"/>
       <c r="E24" s="155" t="inlineStr">
         <is>
           <t>Diesel divided by the activity measure, each year both exist.</t>
         </is>
       </c>
-      <c r="F24" s="161">
+      <c r="F24" s="165">
         <f>IF(COUNT(F22,F23)&lt;2,"",F22/F23)</f>
         <v/>
       </c>
-      <c r="G24" s="161">
+      <c r="G24" s="165">
         <f>IF(COUNT(G22,G23)&lt;2,"",G22/G23)</f>
         <v/>
       </c>
-      <c r="H24" s="161">
+      <c r="H24" s="165">
         <f>IF(COUNT(H22,H23)&lt;2,"",H22/H23)</f>
         <v/>
       </c>
-      <c r="I24" s="161">
+      <c r="I24" s="165">
         <f>IF(COUNT(I22,I23)&lt;2,"",I22/I23)</f>
         <v/>
       </c>
-      <c r="J24" s="161">
+      <c r="J24" s="165">
         <f>IF(COUNT(J22,J23)&lt;2,"",J22/J23)</f>
         <v/>
       </c>
-      <c r="K24" s="161">
+      <c r="K24" s="165">
         <f>IF(COUNT(K22,K23)&lt;2,"",K22/K23)</f>
         <v/>
       </c>
-      <c r="L24" s="161">
+      <c r="L24" s="165">
         <f>IF(COUNT(L22,L23)&lt;2,"",L22/L23)</f>
         <v/>
       </c>
-      <c r="M24" s="161">
+      <c r="M24" s="165">
         <f>IF(COUNT(M22,M23)&lt;2,"",M22/M23)</f>
         <v/>
       </c>
-      <c r="N24" s="161">
+      <c r="N24" s="165">
         <f>IF(COUNT(N22,N23)&lt;2,"",N22/N23)</f>
         <v/>
       </c>
-      <c r="O24" s="161">
+      <c r="O24" s="165">
         <f>IF(COUNT(O22,O23)&lt;2,"",O22/O23)</f>
         <v/>
       </c>
-      <c r="P24" s="161">
+      <c r="P24" s="165">
         <f>IF(COUNT(P22,P23)&lt;2,"",P22/P23)</f>
         <v/>
       </c>
-      <c r="Q24" s="161">
+      <c r="Q24" s="165">
         <f>IF(COUNT(Q22,Q23)&lt;2,"",Q22/Q23)</f>
         <v/>
       </c>
-      <c r="R24" s="161">
+      <c r="R24" s="165">
         <f>IF(COUNT(R22,R23)&lt;2,"",R22/R23)</f>
         <v/>
       </c>
-      <c r="S24" s="161">
+      <c r="S24" s="165">
         <f>IF(COUNT(S22,S23)&lt;2,"",S22/S23)</f>
         <v/>
       </c>
@@ -42517,17 +44575,17 @@
       <c r="V24" s="155" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="162" t="inlineStr">
+      <c r="A25" s="161" t="inlineStr">
         <is>
           <t>Indicative diesel at observed activity (agriculture and forestry diesel)</t>
         </is>
       </c>
-      <c r="B25" s="163" t="inlineStr">
+      <c r="B25" s="162" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C25" s="163" t="inlineStr">
+      <c r="C25" s="162" t="inlineStr">
         <is>
           <t>Proposed estimate</t>
         </is>
@@ -42536,7 +44594,7 @@
         <f>AVERAGE(L24:O24)</f>
         <v/>
       </c>
-      <c r="E25" s="162" t="inlineStr">
+      <c r="E25" s="161" t="inlineStr">
         <is>
           <t>Average 2018-2021 intensity (column D) times the activity measure. An indication for years without a balance; not an observation and not an accepted input.</t>
         </is>
@@ -42597,13 +44655,13 @@
         <f>IF(ISNUMBER(S23),$D$25*S23,"")</f>
         <v/>
       </c>
-      <c r="T25" s="162" t="inlineStr">
+      <c r="T25" s="161" t="inlineStr">
         <is>
           <t>Estimate for discussion</t>
         </is>
       </c>
-      <c r="U25" s="162" t="inlineStr"/>
-      <c r="V25" s="162" t="inlineStr">
+      <c r="U25" s="161" t="inlineStr"/>
+      <c r="V25" s="161" t="inlineStr">
         <is>
           <t>Agree base year, driver and whether intensity is held constant (Nigel)</t>
         </is>
@@ -42647,37 +44705,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="165" t="inlineStr">
+      <c r="A4" s="166" t="inlineStr">
         <is>
           <t>Evidence row</t>
         </is>
       </c>
-      <c r="B4" s="165" t="inlineStr">
+      <c r="B4" s="166" t="inlineStr">
         <is>
           <t>Series</t>
         </is>
       </c>
-      <c r="C4" s="165" t="inlineStr">
+      <c r="C4" s="166" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D4" s="165" t="inlineStr">
+      <c r="D4" s="166" t="inlineStr">
         <is>
           <t>Workbook value</t>
         </is>
       </c>
-      <c r="E4" s="165" t="inlineStr">
+      <c r="E4" s="166" t="inlineStr">
         <is>
           <t>Recomputed from inputs</t>
         </is>
       </c>
-      <c r="F4" s="165" t="inlineStr">
+      <c r="F4" s="166" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="G4" s="165" t="inlineStr">
+      <c r="G4" s="166" t="inlineStr">
         <is>
           <t>Input file</t>
         </is>
@@ -42697,10 +44755,10 @@
       <c r="C5" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D5" s="166" t="n">
+      <c r="D5" s="167" t="n">
         <v>9185</v>
       </c>
-      <c r="E5" s="166" t="n">
+      <c r="E5" s="167" t="n">
         <v>9185</v>
       </c>
       <c r="F5" s="1" t="inlineStr">
@@ -42728,10 +44786,10 @@
       <c r="C6" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D6" s="166" t="n">
+      <c r="D6" s="167" t="n">
         <v>9037</v>
       </c>
-      <c r="E6" s="166" t="n">
+      <c r="E6" s="167" t="n">
         <v>9037</v>
       </c>
       <c r="F6" s="1" t="inlineStr">
@@ -42759,10 +44817,10 @@
       <c r="C7" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D7" s="166" t="n">
+      <c r="D7" s="167" t="n">
         <v>9029</v>
       </c>
-      <c r="E7" s="166" t="n">
+      <c r="E7" s="167" t="n">
         <v>9029</v>
       </c>
       <c r="F7" s="1" t="inlineStr">
@@ -42790,10 +44848,10 @@
       <c r="C8" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D8" s="166" t="n">
+      <c r="D8" s="167" t="n">
         <v>9184.869915572999</v>
       </c>
-      <c r="E8" s="166" t="n">
+      <c r="E8" s="167" t="n">
         <v>9184.869915572999</v>
       </c>
       <c r="F8" s="1" t="inlineStr">
@@ -42821,10 +44879,10 @@
       <c r="C9" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D9" s="166" t="n">
+      <c r="D9" s="167" t="n">
         <v>9036.950113492001</v>
       </c>
-      <c r="E9" s="166" t="n">
+      <c r="E9" s="167" t="n">
         <v>9036.950113492001</v>
       </c>
       <c r="F9" s="1" t="inlineStr">
@@ -42852,10 +44910,10 @@
       <c r="C10" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D10" s="166" t="n">
+      <c r="D10" s="167" t="n">
         <v>12717</v>
       </c>
-      <c r="E10" s="166" t="n">
+      <c r="E10" s="167" t="n">
         <v>12717</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
@@ -42883,10 +44941,10 @@
       <c r="C11" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D11" s="166" t="n">
+      <c r="D11" s="167" t="n">
         <v>12907</v>
       </c>
-      <c r="E11" s="166" t="n">
+      <c r="E11" s="167" t="n">
         <v>12907</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
@@ -42914,10 +44972,10 @@
       <c r="C12" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D12" s="166" t="n">
+      <c r="D12" s="167" t="n">
         <v>11734</v>
       </c>
-      <c r="E12" s="166" t="n">
+      <c r="E12" s="167" t="n">
         <v>11734</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
@@ -42945,10 +45003,10 @@
       <c r="C13" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D13" s="166" t="n">
+      <c r="D13" s="167" t="n">
         <v>12717.326319019</v>
       </c>
-      <c r="E13" s="166" t="n">
+      <c r="E13" s="167" t="n">
         <v>12717.326319019</v>
       </c>
       <c r="F13" s="1" t="inlineStr">
@@ -42976,10 +45034,10 @@
       <c r="C14" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D14" s="166" t="n">
+      <c r="D14" s="167" t="n">
         <v>12907.499965808</v>
       </c>
-      <c r="E14" s="166" t="n">
+      <c r="E14" s="167" t="n">
         <v>12907.499965808</v>
       </c>
       <c r="F14" s="1" t="inlineStr">
@@ -43007,10 +45065,10 @@
       <c r="C15" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D15" s="166" t="n">
+      <c r="D15" s="167" t="n">
         <v>1478</v>
       </c>
-      <c r="E15" s="166" t="n">
+      <c r="E15" s="167" t="n">
         <v>1478</v>
       </c>
       <c r="F15" s="1" t="inlineStr">
@@ -43038,10 +45096,10 @@
       <c r="C16" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D16" s="166" t="n">
+      <c r="D16" s="167" t="n">
         <v>1844</v>
       </c>
-      <c r="E16" s="166" t="n">
+      <c r="E16" s="167" t="n">
         <v>1844</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
@@ -43069,10 +45127,10 @@
       <c r="C17" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D17" s="166" t="n">
+      <c r="D17" s="167" t="n">
         <v>1955</v>
       </c>
-      <c r="E17" s="166" t="n">
+      <c r="E17" s="167" t="n">
         <v>1955</v>
       </c>
       <c r="F17" s="1" t="inlineStr">
@@ -43100,10 +45158,10 @@
       <c r="C18" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D18" s="166" t="n">
+      <c r="D18" s="167" t="n">
         <v>1478.149852603</v>
       </c>
-      <c r="E18" s="166" t="n">
+      <c r="E18" s="167" t="n">
         <v>1478.149852603</v>
       </c>
       <c r="F18" s="1" t="inlineStr">
@@ -43131,10 +45189,10 @@
       <c r="C19" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D19" s="166" t="n">
+      <c r="D19" s="167" t="n">
         <v>1843.971762465</v>
       </c>
-      <c r="E19" s="166" t="n">
+      <c r="E19" s="167" t="n">
         <v>1843.971762465</v>
       </c>
       <c r="F19" s="1" t="inlineStr">
@@ -43162,10 +45220,10 @@
       <c r="C20" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D20" s="166" t="n">
+      <c r="D20" s="167" t="n">
         <v>594</v>
       </c>
-      <c r="E20" s="166" t="n">
+      <c r="E20" s="167" t="n">
         <v>594</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
@@ -43193,10 +45251,10 @@
       <c r="C21" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D21" s="166" t="n">
+      <c r="D21" s="167" t="n">
         <v>658</v>
       </c>
-      <c r="E21" s="166" t="n">
+      <c r="E21" s="167" t="n">
         <v>658</v>
       </c>
       <c r="F21" s="1" t="inlineStr">
@@ -43224,10 +45282,10 @@
       <c r="C22" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D22" s="166" t="n">
+      <c r="D22" s="167" t="n">
         <v>441</v>
       </c>
-      <c r="E22" s="166" t="n">
+      <c r="E22" s="167" t="n">
         <v>441</v>
       </c>
       <c r="F22" s="1" t="inlineStr">
@@ -43255,10 +45313,10 @@
       <c r="C23" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D23" s="166" t="n">
+      <c r="D23" s="167" t="n">
         <v>594.0401649620001</v>
       </c>
-      <c r="E23" s="166" t="n">
+      <c r="E23" s="167" t="n">
         <v>594.0401649620001</v>
       </c>
       <c r="F23" s="1" t="inlineStr">
@@ -43286,10 +45344,10 @@
       <c r="C24" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D24" s="166" t="n">
+      <c r="D24" s="167" t="n">
         <v>658.0930416160001</v>
       </c>
-      <c r="E24" s="166" t="n">
+      <c r="E24" s="167" t="n">
         <v>658.0930416160001</v>
       </c>
       <c r="F24" s="1" t="inlineStr">
@@ -43317,10 +45375,10 @@
       <c r="C25" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D25" s="166" t="n">
+      <c r="D25" s="167" t="n">
         <v>76055.06748983047</v>
       </c>
-      <c r="E25" s="166" t="n">
+      <c r="E25" s="167" t="n">
         <v>76055.06748983047</v>
       </c>
       <c r="F25" s="1" t="inlineStr">
@@ -43348,10 +45406,10 @@
       <c r="C26" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D26" s="166" t="n">
+      <c r="D26" s="167" t="n">
         <v>75781.52071231291</v>
       </c>
-      <c r="E26" s="166" t="n">
+      <c r="E26" s="167" t="n">
         <v>75781.52071231291</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
@@ -43379,10 +45437,10 @@
       <c r="C27" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D27" s="166" t="n">
+      <c r="D27" s="167" t="n">
         <v>75255.62912098455</v>
       </c>
-      <c r="E27" s="166" t="n">
+      <c r="E27" s="167" t="n">
         <v>75255.62912098455</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
@@ -43410,10 +45468,10 @@
       <c r="C28" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D28" s="166" t="n">
+      <c r="D28" s="167" t="n">
         <v>75149.98563223911</v>
       </c>
-      <c r="E28" s="166" t="n">
+      <c r="E28" s="167" t="n">
         <v>75149.98563223911</v>
       </c>
       <c r="F28" s="1" t="inlineStr">
@@ -43441,10 +45499,10 @@
       <c r="C29" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D29" s="166" t="n">
+      <c r="D29" s="167" t="n">
         <v>131.7706421450265</v>
       </c>
-      <c r="E29" s="166" t="n">
+      <c r="E29" s="167" t="n">
         <v>131.7706421450265</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
@@ -43472,10 +45530,10 @@
       <c r="C30" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D30" s="166" t="n">
+      <c r="D30" s="167" t="n">
         <v>125.7466421450265</v>
       </c>
-      <c r="E30" s="166" t="n">
+      <c r="E30" s="167" t="n">
         <v>125.7466421450265</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
@@ -43503,10 +45561,10 @@
       <c r="C31" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D31" s="166" t="n">
+      <c r="D31" s="167" t="n">
         <v>114.7916421450265</v>
       </c>
-      <c r="E31" s="166" t="n">
+      <c r="E31" s="167" t="n">
         <v>114.7916421450265</v>
       </c>
       <c r="F31" s="1" t="inlineStr">
@@ -43534,10 +45592,10 @@
       <c r="C32" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D32" s="166" t="n">
+      <c r="D32" s="167" t="n">
         <v>134.7967469817132</v>
       </c>
-      <c r="E32" s="166" t="n">
+      <c r="E32" s="167" t="n">
         <v>134.7967469817132</v>
       </c>
       <c r="F32" s="1" t="inlineStr">
@@ -43565,10 +45623,10 @@
       <c r="C33" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D33" s="166" t="n">
+      <c r="D33" s="167" t="n">
         <v>523.0907540648606</v>
       </c>
-      <c r="E33" s="166" t="n">
+      <c r="E33" s="167" t="n">
         <v>523.0907540648606</v>
       </c>
       <c r="F33" s="1" t="inlineStr">
@@ -43596,10 +45654,10 @@
       <c r="C34" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D34" s="166" t="n">
+      <c r="D34" s="167" t="n">
         <v>524.9937540648609</v>
       </c>
-      <c r="E34" s="166" t="n">
+      <c r="E34" s="167" t="n">
         <v>524.9937540648609</v>
       </c>
       <c r="F34" s="1" t="inlineStr">
@@ -43627,10 +45685,10 @@
       <c r="C35" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D35" s="166" t="n">
+      <c r="D35" s="167" t="n">
         <v>523.150754064861</v>
       </c>
-      <c r="E35" s="166" t="n">
+      <c r="E35" s="167" t="n">
         <v>523.150754064861</v>
       </c>
       <c r="F35" s="1" t="inlineStr">
@@ -43658,10 +45716,10 @@
       <c r="C36" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D36" s="166" t="n">
+      <c r="D36" s="167" t="n">
         <v>516.9856529750193</v>
       </c>
-      <c r="E36" s="166" t="n">
+      <c r="E36" s="167" t="n">
         <v>516.9856529750193</v>
       </c>
       <c r="F36" s="1" t="inlineStr">
@@ -43689,10 +45747,10 @@
       <c r="C37" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D37" s="166" t="n">
+      <c r="D37" s="167" t="n">
         <v>204.4529227196744</v>
       </c>
-      <c r="E37" s="166" t="n">
+      <c r="E37" s="167" t="n">
         <v>204.4529227196744</v>
       </c>
       <c r="F37" s="1" t="inlineStr">
@@ -43720,10 +45778,10 @@
       <c r="C38" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D38" s="166" t="n">
+      <c r="D38" s="167" t="n">
         <v>204.2286999662737</v>
       </c>
-      <c r="E38" s="166" t="n">
+      <c r="E38" s="167" t="n">
         <v>204.2286999662738</v>
       </c>
       <c r="F38" s="1" t="inlineStr">
@@ -43751,10 +45809,10 @@
       <c r="C39" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D39" s="166" t="n">
+      <c r="D39" s="167" t="n">
         <v>205.1258295918731</v>
       </c>
-      <c r="E39" s="166" t="n">
+      <c r="E39" s="167" t="n">
         <v>205.1258295918731</v>
       </c>
       <c r="F39" s="1" t="inlineStr">
@@ -43782,10 +45840,10 @@
       <c r="C40" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D40" s="166" t="n">
+      <c r="D40" s="167" t="n">
         <v>205.4648860142573</v>
       </c>
-      <c r="E40" s="166" t="n">
+      <c r="E40" s="167" t="n">
         <v>205.4648860142574</v>
       </c>
       <c r="F40" s="1" t="inlineStr">
@@ -43813,10 +45871,10 @@
       <c r="C41" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D41" s="166" t="n">
+      <c r="D41" s="167" t="n">
         <v>110.0650907489087</v>
       </c>
-      <c r="E41" s="166" t="n">
+      <c r="E41" s="167" t="n">
         <v>110.0650907489087</v>
       </c>
       <c r="F41" s="1" t="inlineStr">
@@ -43844,10 +45902,10 @@
       <c r="C42" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D42" s="166" t="n">
+      <c r="D42" s="167" t="n">
         <v>109.5650907489087</v>
       </c>
-      <c r="E42" s="166" t="n">
+      <c r="E42" s="167" t="n">
         <v>109.5650907489087</v>
       </c>
       <c r="F42" s="1" t="inlineStr">
@@ -43875,10 +45933,10 @@
       <c r="C43" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D43" s="166" t="n">
+      <c r="D43" s="167" t="n">
         <v>103.6250907489087</v>
       </c>
-      <c r="E43" s="166" t="n">
+      <c r="E43" s="167" t="n">
         <v>103.6250907489087</v>
       </c>
       <c r="F43" s="1" t="inlineStr">
@@ -43906,10 +45964,10 @@
       <c r="C44" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D44" s="166" t="n">
+      <c r="D44" s="167" t="n">
         <v>99.09852067977131</v>
       </c>
-      <c r="E44" s="166" t="n">
+      <c r="E44" s="167" t="n">
         <v>99.09852067977131</v>
       </c>
       <c r="F44" s="1" t="inlineStr">
@@ -43937,10 +45995,10 @@
       <c r="C45" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D45" s="166" t="n">
+      <c r="D45" s="167" t="n">
         <v>93.14166666666667</v>
       </c>
-      <c r="E45" s="166" t="n">
+      <c r="E45" s="167" t="n">
         <v>93.14166666666667</v>
       </c>
       <c r="F45" s="1" t="inlineStr">
@@ -43968,10 +46026,10 @@
       <c r="C46" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D46" s="166" t="n">
+      <c r="D46" s="167" t="n">
         <v>93.71666666666665</v>
       </c>
-      <c r="E46" s="166" t="n">
+      <c r="E46" s="167" t="n">
         <v>93.71666666666665</v>
       </c>
       <c r="F46" s="1" t="inlineStr">
@@ -43999,10 +46057,10 @@
       <c r="C47" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D47" s="166" t="n">
+      <c r="D47" s="167" t="n">
         <v>93.33333333333333</v>
       </c>
-      <c r="E47" s="166" t="n">
+      <c r="E47" s="167" t="n">
         <v>93.33333333333333</v>
       </c>
       <c r="F47" s="1" t="inlineStr">
@@ -44030,10 +46088,10 @@
       <c r="C48" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D48" s="166" t="n">
+      <c r="D48" s="167" t="n">
         <v>92.14166666666665</v>
       </c>
-      <c r="E48" s="166" t="n">
+      <c r="E48" s="167" t="n">
         <v>92.14166666666667</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
@@ -44061,10 +46119,10 @@
       <c r="C49" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D49" s="166" t="n">
+      <c r="D49" s="167" t="n">
         <v>93.00833333333334</v>
       </c>
-      <c r="E49" s="166" t="n">
+      <c r="E49" s="167" t="n">
         <v>93.00833333333333</v>
       </c>
       <c r="F49" s="1" t="inlineStr">
@@ -44092,10 +46150,10 @@
       <c r="C50" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D50" s="166" t="n">
+      <c r="D50" s="167" t="n">
         <v>93.01666666666667</v>
       </c>
-      <c r="E50" s="166" t="n">
+      <c r="E50" s="167" t="n">
         <v>93.01666666666667</v>
       </c>
       <c r="F50" s="1" t="inlineStr">
@@ -44123,10 +46181,10 @@
       <c r="C51" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D51" s="166" t="n">
+      <c r="D51" s="167" t="n">
         <v>93.53333333333332</v>
       </c>
-      <c r="E51" s="166" t="n">
+      <c r="E51" s="167" t="n">
         <v>93.53333333333335</v>
       </c>
       <c r="F51" s="1" t="inlineStr">
@@ -44154,10 +46212,10 @@
       <c r="C52" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D52" s="166" t="n">
+      <c r="D52" s="167" t="n">
         <v>93.70833333333333</v>
       </c>
-      <c r="E52" s="166" t="n">
+      <c r="E52" s="167" t="n">
         <v>93.70833333333333</v>
       </c>
       <c r="F52" s="1" t="inlineStr">
@@ -44185,10 +46243,10 @@
       <c r="C53" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D53" s="166" t="n">
+      <c r="D53" s="167" t="n">
         <v>703.1324447169991</v>
       </c>
-      <c r="E53" s="166" t="n">
+      <c r="E53" s="167" t="n">
         <v>703.132444716999</v>
       </c>
       <c r="F53" s="1" t="inlineStr">
@@ -44216,10 +46274,10 @@
       <c r="C54" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D54" s="166" t="n">
+      <c r="D54" s="167" t="n">
         <v>587.4580081820001</v>
       </c>
-      <c r="E54" s="166" t="n">
+      <c r="E54" s="167" t="n">
         <v>587.4580081820001</v>
       </c>
       <c r="F54" s="1" t="inlineStr">
@@ -44247,10 +46305,10 @@
       <c r="C55" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D55" s="166" t="n">
+      <c r="D55" s="167" t="n">
         <v>3530.440256933996</v>
       </c>
-      <c r="E55" s="166" t="n">
+      <c r="E55" s="167" t="n">
         <v>3530.440256933996</v>
       </c>
       <c r="F55" s="1" t="inlineStr">
@@ -44278,10 +46336,10 @@
       <c r="C56" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D56" s="166" t="n">
+      <c r="D56" s="167" t="n">
         <v>1498.937893394999</v>
       </c>
-      <c r="E56" s="166" t="n">
+      <c r="E56" s="167" t="n">
         <v>1498.937893394999</v>
       </c>
       <c r="F56" s="1" t="inlineStr">
@@ -44309,10 +46367,10 @@
       <c r="C57" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D57" s="166" t="n">
+      <c r="D57" s="167" t="n">
         <v>273.644045045999</v>
       </c>
-      <c r="E57" s="166" t="n">
+      <c r="E57" s="167" t="n">
         <v>273.644045045999</v>
       </c>
       <c r="F57" s="1" t="inlineStr">
@@ -44340,10 +46398,10 @@
       <c r="C58" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D58" s="166" t="n">
+      <c r="D58" s="167" t="n">
         <v>612.2656460789989</v>
       </c>
-      <c r="E58" s="166" t="n">
+      <c r="E58" s="167" t="n">
         <v>612.2656460789989</v>
       </c>
       <c r="F58" s="1" t="inlineStr">
@@ -44371,10 +46429,10 @@
       <c r="C59" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D59" s="166" t="n">
+      <c r="D59" s="167" t="n">
         <v>99.82992901300001</v>
       </c>
-      <c r="E59" s="166" t="n">
+      <c r="E59" s="167" t="n">
         <v>99.829929013</v>
       </c>
       <c r="F59" s="1" t="inlineStr">
@@ -44402,10 +46460,10 @@
       <c r="C60" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D60" s="166" t="n">
+      <c r="D60" s="167" t="n">
         <v>448.1562321239999</v>
       </c>
-      <c r="E60" s="166" t="n">
+      <c r="E60" s="167" t="n">
         <v>448.1562321239999</v>
       </c>
       <c r="F60" s="1" t="inlineStr">
@@ -44433,10 +46491,10 @@
       <c r="C61" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D61" s="166" t="n">
+      <c r="D61" s="167" t="n">
         <v>1431.005460082997</v>
       </c>
-      <c r="E61" s="166" t="n">
+      <c r="E61" s="167" t="n">
         <v>1431.005460082997</v>
       </c>
       <c r="F61" s="1" t="inlineStr">
@@ -44464,10 +46522,10 @@
       <c r="C62" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D62" s="166" t="n">
+      <c r="D62" s="167" t="n">
         <v>1032.35218272</v>
       </c>
-      <c r="E62" s="166" t="n">
+      <c r="E62" s="167" t="n">
         <v>1032.35218272</v>
       </c>
       <c r="F62" s="1" t="inlineStr">
@@ -44495,10 +46553,10 @@
       <c r="C63" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D63" s="166" t="n">
+      <c r="D63" s="167" t="n">
         <v>781.8611598310002</v>
       </c>
-      <c r="E63" s="166" t="n">
+      <c r="E63" s="167" t="n">
         <v>781.8611598310002</v>
       </c>
       <c r="F63" s="1" t="inlineStr">
@@ -44526,10 +46584,10 @@
       <c r="C64" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D64" s="166" t="n">
+      <c r="D64" s="167" t="n">
         <v>3278.990501961999</v>
       </c>
-      <c r="E64" s="166" t="n">
+      <c r="E64" s="167" t="n">
         <v>3278.990501961999</v>
       </c>
       <c r="F64" s="1" t="inlineStr">
@@ -44557,10 +46615,10 @@
       <c r="C65" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D65" s="166" t="n">
+      <c r="D65" s="167" t="n">
         <v>2785.554802503</v>
       </c>
-      <c r="E65" s="166" t="n">
+      <c r="E65" s="167" t="n">
         <v>2785.554802503</v>
       </c>
       <c r="F65" s="1" t="inlineStr">
@@ -44588,10 +46646,10 @@
       <c r="C66" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D66" s="166" t="n">
+      <c r="D66" s="167" t="n">
         <v>221.987440248</v>
       </c>
-      <c r="E66" s="166" t="n">
+      <c r="E66" s="167" t="n">
         <v>221.987440248</v>
       </c>
       <c r="F66" s="1" t="inlineStr">
@@ -44619,10 +46677,10 @@
       <c r="C67" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D67" s="166" t="n">
+      <c r="D67" s="167" t="n">
         <v>1144.924075864997</v>
       </c>
-      <c r="E67" s="166" t="n">
+      <c r="E67" s="167" t="n">
         <v>1144.924075864997</v>
       </c>
       <c r="F67" s="1" t="inlineStr">
@@ -44650,10 +46708,10 @@
       <c r="C68" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D68" s="166" t="n">
+      <c r="D68" s="167" t="n">
         <v>351.9801199100001</v>
       </c>
-      <c r="E68" s="166" t="n">
+      <c r="E68" s="167" t="n">
         <v>351.9801199100001</v>
       </c>
       <c r="F68" s="1" t="inlineStr">
@@ -44681,10 +46739,10 @@
       <c r="C69" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D69" s="166" t="n">
+      <c r="D69" s="167" t="n">
         <v>619.906488913</v>
       </c>
-      <c r="E69" s="166" t="n">
+      <c r="E69" s="167" t="n">
         <v>619.906488913</v>
       </c>
       <c r="F69" s="1" t="inlineStr">
@@ -44712,10 +46770,10 @@
       <c r="C70" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D70" s="166" t="n">
+      <c r="D70" s="167" t="n">
         <v>2499.769547067</v>
       </c>
-      <c r="E70" s="166" t="n">
+      <c r="E70" s="167" t="n">
         <v>2499.769547067</v>
       </c>
       <c r="F70" s="1" t="inlineStr">
@@ -47394,517 +49452,517 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="165" t="inlineStr">
+      <c r="A4" s="166" t="inlineStr">
         <is>
           <t>Used for</t>
         </is>
       </c>
-      <c r="B4" s="165" t="inlineStr">
+      <c r="B4" s="166" t="inlineStr">
         <is>
           <t>Publisher</t>
         </is>
       </c>
-      <c r="C4" s="165" t="inlineStr">
+      <c r="C4" s="166" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="D4" s="165" t="inlineStr">
+      <c r="D4" s="166" t="inlineStr">
         <is>
           <t>Original file</t>
         </is>
       </c>
-      <c r="E4" s="165" t="inlineStr">
+      <c r="E4" s="166" t="inlineStr">
         <is>
           <t>Where the original is kept</t>
         </is>
       </c>
-      <c r="F4" s="165" t="inlineStr">
+      <c r="F4" s="166" t="inlineStr">
         <is>
           <t>Extract in the repository</t>
         </is>
       </c>
-      <c r="G4" s="165" t="inlineStr">
+      <c r="G4" s="166" t="inlineStr">
         <is>
           <t>Refresh command</t>
         </is>
       </c>
-      <c r="H4" s="165" t="inlineStr">
+      <c r="H4" s="166" t="inlineStr">
         <is>
           <t>Periods</t>
         </is>
       </c>
-      <c r="I4" s="165" t="inlineStr">
+      <c r="I4" s="166" t="inlineStr">
         <is>
           <t>Limits</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="167" t="inlineStr">
+      <c r="A5" s="168" t="inlineStr">
         <is>
           <t>History sections 1 and 4: national sales</t>
         </is>
       </c>
-      <c r="B5" s="167" t="inlineStr">
+      <c r="B5" s="168" t="inlineStr">
         <is>
           <t>Department of Mineral and Petroleum Resources (energy department)</t>
         </is>
       </c>
-      <c r="C5" s="167" t="inlineStr">
+      <c r="C5" s="168" t="inlineStr">
         <is>
           <t>https://www.dmpr.gov.za/Portals/0/Energy_Website/files/media/SA FUEL SALES VOLUME/</t>
         </is>
       </c>
-      <c r="D5" s="167" t="inlineStr">
+      <c r="D5" s="168" t="inlineStr">
         <is>
           <t>&lt;year&gt;-...-FSV....xls(x), national annual workbooks 2005-2023</t>
         </is>
       </c>
-      <c r="E5" s="167" t="inlineStr">
+      <c r="E5" s="168" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main</t>
         </is>
       </c>
-      <c r="F5" s="167" t="inlineStr">
+      <c r="F5" s="168" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_sales_department.csv</t>
         </is>
       </c>
-      <c r="G5" s="167" t="inlineStr">
+      <c r="G5" s="168" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_energy_dept --vintage 2026</t>
         </is>
       </c>
-      <c r="H5" s="167" t="inlineStr">
+      <c r="H5" s="168" t="inlineStr">
         <is>
           <t>2005-2023</t>
         </is>
       </c>
-      <c r="I5" s="167" t="inlineStr">
+      <c r="I5" s="168" t="inlineStr">
         <is>
           <t>2013 corrected on manish-branch (published sheet). Series ends 2023.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="167" t="inlineStr">
+      <c r="A6" s="168" t="inlineStr">
         <is>
           <t>History section 1: sales by province</t>
         </is>
       </c>
-      <c r="B6" s="167" t="inlineStr">
+      <c r="B6" s="168" t="inlineStr">
         <is>
           <t>Department of Mineral and Petroleum Resources (energy department)</t>
         </is>
       </c>
-      <c r="C6" s="167" t="inlineStr">
+      <c r="C6" s="168" t="inlineStr">
         <is>
           <t>https://www.dmpr.gov.za/Portals/0/Energy_Website/files/media/SA FUEL SALES VOLUME/</t>
         </is>
       </c>
-      <c r="D6" s="167" t="inlineStr">
+      <c r="D6" s="168" t="inlineStr">
         <is>
           <t>&lt;year&gt;-...-Magisterial-Districts-data.xlsx, quarterly sheets</t>
         </is>
       </c>
-      <c r="E6" s="167" t="inlineStr">
+      <c r="E6" s="168" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main (2013 annual workbook on manish-branch)</t>
         </is>
       </c>
-      <c r="F6" s="167" t="inlineStr">
+      <c r="F6" s="168" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_sales_department_by_province.csv</t>
         </is>
       </c>
-      <c r="G6" s="167" t="inlineStr">
+      <c r="G6" s="168" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_energy_dept --vintage 2026</t>
         </is>
       </c>
-      <c r="H6" s="167" t="inlineStr">
+      <c r="H6" s="168" t="inlineStr">
         <is>
           <t>2013-2022</t>
         </is>
       </c>
-      <c r="I6" s="167" t="inlineStr">
+      <c r="I6" s="168" t="inlineStr">
         <is>
           <t>Ends 2022. 2018 understated about 1.8% (district Q1 sheet incomplete). 2014-Q3 differs from national file.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="167" t="inlineStr">
+      <c r="A7" s="168" t="inlineStr">
         <is>
           <t>History section 2: imports and exports</t>
         </is>
       </c>
-      <c r="B7" s="167" t="inlineStr">
+      <c r="B7" s="168" t="inlineStr">
         <is>
           <t>South African Revenue Service, trade statistics</t>
         </is>
       </c>
-      <c r="C7" s="167" t="inlineStr">
+      <c r="C7" s="168" t="inlineStr">
         <is>
           <t>https://tools.sars.gov.za/tradestatsportal/data_download.aspx</t>
         </is>
       </c>
-      <c r="D7" s="167" t="inlineStr">
+      <c r="D7" s="168" t="inlineStr">
         <is>
           <t>sars-&lt;imports|exports&gt;-chapter27-fuels-&lt;year&gt;.xlsx, 2010-2026</t>
         </is>
       </c>
-      <c r="E7" s="167" t="inlineStr">
+      <c r="E7" s="168" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/sars/)</t>
         </is>
       </c>
-      <c r="F7" s="167" t="inlineStr">
+      <c r="F7" s="168" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_trade_sars.csv</t>
         </is>
       </c>
-      <c r="G7" s="167" t="inlineStr">
+      <c r="G7" s="168" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_sars --vintage 2026</t>
         </is>
       </c>
-      <c r="H7" s="167" t="inlineStr">
+      <c r="H7" s="168" t="inlineStr">
         <is>
           <t>2010-2026</t>
         </is>
       </c>
-      <c r="I7" s="167" t="inlineStr">
+      <c r="I7" s="168" t="inlineStr">
         <is>
           <t>Primary record of imports and exports from 2014. Kilograms to 2012, litres from 2014, both in 2013.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="167" t="inlineStr">
+      <c r="A8" s="168" t="inlineStr">
         <is>
           <t>History section 2: FIASA comparison rows</t>
         </is>
       </c>
-      <c r="B8" s="167" t="inlineStr">
+      <c r="B8" s="168" t="inlineStr">
         <is>
           <t>Fuels Industry Association of South Africa (from customs data)</t>
         </is>
       </c>
-      <c r="C8" s="167" t="inlineStr">
+      <c r="C8" s="168" t="inlineStr">
         <is>
           <t>https://fuelsindustry.org.za/publications/annual-reports/</t>
         </is>
       </c>
-      <c r="D8" s="167" t="inlineStr">
+      <c r="D8" s="168" t="inlineStr">
         <is>
           <t>annual-report-&lt;year&gt;.pdf; 2025 edition pp.47-49</t>
         </is>
       </c>
-      <c r="E8" s="167" t="inlineStr">
+      <c r="E8" s="168" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main; 2025 edition on main</t>
         </is>
       </c>
-      <c r="F8" s="167" t="inlineStr">
+      <c r="F8" s="168" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_trade_fiasa.csv</t>
         </is>
       </c>
-      <c r="G8" s="167" t="inlineStr">
+      <c r="G8" s="168" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_fuel_sales --vintage 2026</t>
         </is>
       </c>
-      <c r="H8" s="167" t="inlineStr">
+      <c r="H8" s="168" t="inlineStr">
         <is>
           <t>2009-2025</t>
         </is>
       </c>
-      <c r="I8" s="167" t="inlineStr">
+      <c r="I8" s="168" t="inlineStr">
         <is>
           <t>Cross-check, and the record before 2014; SARS is primary from 2014. 'Kerosene' is jet plus paraffin. Its 2024 diesel import figure is 4.000 bn L above customs.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="167" t="inlineStr">
+      <c r="A9" s="168" t="inlineStr">
         <is>
           <t>History section 4: FIASA comparison row</t>
         </is>
       </c>
-      <c r="B9" s="167" t="inlineStr">
+      <c r="B9" s="168" t="inlineStr">
         <is>
           <t>Fuels Industry Association of South Africa</t>
         </is>
       </c>
-      <c r="C9" s="167" t="inlineStr">
+      <c r="C9" s="168" t="inlineStr">
         <is>
           <t>https://fuelsindustry.org.za/publications/annual-reports/</t>
         </is>
       </c>
-      <c r="D9" s="167" t="inlineStr">
+      <c r="D9" s="168" t="inlineStr">
         <is>
           <t>annual-report-&lt;year&gt;.pdf, 2021-2025 editions</t>
         </is>
       </c>
-      <c r="E9" s="167" t="inlineStr">
+      <c r="E9" s="168" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main; 2025 edition on main</t>
         </is>
       </c>
-      <c r="F9" s="167" t="inlineStr">
+      <c r="F9" s="168" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_sales_fiasa.csv</t>
         </is>
       </c>
-      <c r="G9" s="167" t="inlineStr">
+      <c r="G9" s="168" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_fuel_sales --vintage 2026</t>
         </is>
       </c>
-      <c r="H9" s="167" t="inlineStr">
+      <c r="H9" s="168" t="inlineStr">
         <is>
           <t>2009-2024</t>
         </is>
       </c>
-      <c r="I9" s="167" t="inlineStr">
+      <c r="I9" s="168" t="inlineStr">
         <is>
           <t>Used for 2024 only. Its 2013 figures equal the department's superseded sheet.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="167" t="inlineStr">
+      <c r="A10" s="168" t="inlineStr">
         <is>
           <t>History section 3 and Sector history: production and diesel by sector</t>
         </is>
       </c>
-      <c r="B10" s="167" t="inlineStr">
+      <c r="B10" s="168" t="inlineStr">
         <is>
           <t>Department of Mineral and Petroleum Resources (energy department)</t>
         </is>
       </c>
-      <c r="C10" s="167" t="inlineStr">
+      <c r="C10" s="168" t="inlineStr">
         <is>
           <t>https://www.dmpr.gov.za/Portals/0/Energy_Website/files/media/Energy_Balances.html</t>
         </is>
       </c>
-      <c r="D10" s="167" t="inlineStr">
+      <c r="D10" s="168" t="inlineStr">
         <is>
           <t>&lt;year&gt;-Commodity-Flow-and-Energy-Balance.xlsx, 2007-2021</t>
         </is>
       </c>
-      <c r="E10" s="167" t="inlineStr">
+      <c r="E10" s="168" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main</t>
         </is>
       </c>
-      <c r="F10" s="167" t="inlineStr">
+      <c r="F10" s="168" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/energy_balance_department.csv</t>
         </is>
       </c>
-      <c r="G10" s="167" t="inlineStr">
+      <c r="G10" s="168" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_energy_dept --vintage 2026</t>
         </is>
       </c>
-      <c r="H10" s="167" t="inlineStr">
+      <c r="H10" s="168" t="inlineStr">
         <is>
           <t>2007-2021</t>
         </is>
       </c>
-      <c r="I10" s="167" t="inlineStr">
+      <c r="I10" s="168" t="inlineStr">
         <is>
           <t>Ends 2021. Sector definitions shift in 2016. Fuel oil not extracted.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="167" t="inlineStr">
+      <c r="A11" s="168" t="inlineStr">
         <is>
           <t>History section 3: operators' reported output</t>
         </is>
       </c>
-      <c r="B11" s="167" t="inlineStr">
+      <c r="B11" s="168" t="inlineStr">
         <is>
           <t>Sasol (production and sales metrics); Glencore (annual reports)</t>
         </is>
       </c>
-      <c r="C11" s="167" t="inlineStr">
+      <c r="C11" s="168" t="inlineStr">
         <is>
           <t>https://www.sasol.com/</t>
         </is>
       </c>
-      <c r="D11" s="167" t="inlineStr">
+      <c r="D11" s="168" t="inlineStr">
         <is>
           <t>sasol-metrics-fy2022/2025/2026.pdf, p.4; GLEN-2023/2024/2025-Annual-Report.pdf</t>
         </is>
       </c>
-      <c r="E11" s="167" t="inlineStr">
+      <c r="E11" s="168" t="inlineStr">
         <is>
           <t>Sasol files on manish-branch (external/data/raw/sasol/); Glencore reports by link only</t>
         </is>
       </c>
-      <c r="F11" s="167" t="inlineStr">
+      <c r="F11" s="168" t="inlineStr">
         <is>
           <t>assumptions/2026/reference/refinery_output_operators.csv</t>
         </is>
       </c>
-      <c r="G11" s="167" t="inlineStr">
+      <c r="G11" s="168" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="H11" s="167" t="inlineStr">
+      <c r="H11" s="168" t="inlineStr">
         <is>
           <t>2020-2026</t>
         </is>
       </c>
-      <c r="I11" s="167" t="inlineStr">
+      <c r="I11" s="168" t="inlineStr">
         <is>
           <t>All refined products, no product split; fiscal and calendar years; Astron as energy content.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="167" t="inlineStr">
+      <c r="A12" s="168" t="inlineStr">
         <is>
           <t>History section 5: litres levied</t>
         </is>
       </c>
-      <c r="B12" s="167" t="inlineStr">
+      <c r="B12" s="168" t="inlineStr">
         <is>
           <t>Road Accident Fund</t>
         </is>
       </c>
-      <c r="C12" s="167" t="inlineStr">
+      <c r="C12" s="168" t="inlineStr">
         <is>
           <t>https://static.pmg.org.za/RAF_Annual_Report_2025.pdf</t>
         </is>
       </c>
-      <c r="D12" s="167" t="inlineStr">
+      <c r="D12" s="168" t="inlineStr">
         <is>
           <t>raf-annual-report-2024-25.pdf, note 16 (p.183)</t>
         </is>
       </c>
-      <c r="E12" s="167" t="inlineStr">
+      <c r="E12" s="168" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/raf/)</t>
         </is>
       </c>
-      <c r="F12" s="167" t="inlineStr">
+      <c r="F12" s="168" t="inlineStr">
         <is>
           <t>assumptions/2026/reference/fuel_levy_revenue_raf.csv</t>
         </is>
       </c>
-      <c r="G12" s="167" t="inlineStr">
+      <c r="G12" s="168" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="H12" s="167" t="inlineStr">
+      <c r="H12" s="168" t="inlineStr">
         <is>
           <t>2024-2025</t>
         </is>
       </c>
-      <c r="I12" s="167" t="inlineStr">
+      <c r="I12" s="168" t="inlineStr">
         <is>
           <t>Gross levies and diesel rebate in rand; litres derived in the balance note. Fiscal years; petrol and diesel together.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="167" t="inlineStr">
+      <c r="A13" s="168" t="inlineStr">
         <is>
           <t>Sector history: mining and manufacturing volume indices</t>
         </is>
       </c>
-      <c r="B13" s="167" t="inlineStr">
+      <c r="B13" s="168" t="inlineStr">
         <is>
           <t>Statistics South Africa (P2041 mining, P3041.2 manufacturing, P7162 land transport, P0141 CPI)</t>
         </is>
       </c>
-      <c r="C13" s="167" t="inlineStr">
+      <c r="C13" s="168" t="inlineStr">
         <is>
           <t>https://www.statssa.gov.za/?page_id=1847</t>
         </is>
       </c>
-      <c r="D13" s="167" t="inlineStr">
+      <c r="D13" s="168" t="inlineStr">
         <is>
           <t>release zips, July and August 2026</t>
         </is>
       </c>
-      <c r="E13" s="167" t="inlineStr">
+      <c r="E13" s="168" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/statssa/)</t>
         </is>
       </c>
-      <c r="F13" s="167" t="inlineStr">
+      <c r="F13" s="168" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/activity_statssa_monthly.csv</t>
         </is>
       </c>
-      <c r="G13" s="167" t="inlineStr">
+      <c r="G13" s="168" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_statssa_monthly --vintage 2026</t>
         </is>
       </c>
-      <c r="H13" s="167" t="inlineStr">
+      <c r="H13" s="168" t="inlineStr">
         <is>
           <t>1998-01-2026-08</t>
         </is>
       </c>
-      <c r="I13" s="167" t="inlineStr">
+      <c r="I13" s="168" t="inlineStr">
         <is>
           <t>Activity measures, not fuel volumes. Not seasonally adjusted. Tonnes, not tonne-kilometres.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="167" t="inlineStr">
+      <c r="A14" s="168" t="inlineStr">
         <is>
           <t>Sector history: agriculture real value added</t>
         </is>
       </c>
-      <c r="B14" s="167" t="inlineStr">
+      <c r="B14" s="168" t="inlineStr">
         <is>
           <t>Statistics South Africa (P0441 GDP; P0302 mid-year population)</t>
         </is>
       </c>
-      <c r="C14" s="167" t="inlineStr">
+      <c r="C14" s="168" t="inlineStr">
         <is>
           <t>https://www.statssa.gov.za/?page_id=1854&amp;PPN=P0441</t>
         </is>
       </c>
-      <c r="D14" s="167" t="inlineStr">
+      <c r="D14" s="168" t="inlineStr">
         <is>
           <t>GDP P0441 - GDP Time series Q2 2026.xlsx (Annual sheet); Country projection ... (2002-2026).xlsx</t>
         </is>
       </c>
-      <c r="E14" s="167" t="inlineStr">
+      <c r="E14" s="168" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/statssa/)</t>
         </is>
       </c>
-      <c r="F14" s="167" t="inlineStr">
+      <c r="F14" s="168" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/macro_statssa.csv</t>
         </is>
       </c>
-      <c r="G14" s="167" t="inlineStr">
+      <c r="G14" s="168" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_economy --vintage 2026</t>
         </is>
       </c>
-      <c r="H14" s="167" t="inlineStr">
+      <c r="H14" s="168" t="inlineStr">
         <is>
           <t>1993-2050</t>
         </is>
       </c>
-      <c r="I14" s="167" t="inlineStr">
+      <c r="I14" s="168" t="inlineStr">
         <is>
           <t>Manual placement each release. Years after 2026 are projections, not observations.</t>
         </is>

--- a/output/delivered/Demand_baseline_workshop_2026_10_08_history.xlsx
+++ b/output/delivered/Demand_baseline_workshop_2026_10_08_history.xlsx
@@ -21,8 +21,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HML" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector history" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History sources" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vehicle history" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History sources" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -187,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -670,6 +671,18 @@
     <xf numFmtId="4" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -44678,2210 +44691,3232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:V60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="11.5" customWidth="1" min="6" max="6"/>
+    <col width="11.5" customWidth="1" min="7" max="7"/>
+    <col width="11.5" customWidth="1" min="8" max="8"/>
+    <col width="11.5" customWidth="1" min="9" max="9"/>
+    <col width="11.5" customWidth="1" min="10" max="10"/>
+    <col width="11.5" customWidth="1" min="11" max="11"/>
+    <col width="11.5" customWidth="1" min="12" max="12"/>
+    <col width="11.5" customWidth="1" min="13" max="13"/>
+    <col width="11.5" customWidth="1" min="14" max="14"/>
+    <col width="11.5" customWidth="1" min="15" max="15"/>
+    <col width="11.5" customWidth="1" min="16" max="16"/>
+    <col width="11.5" customWidth="1" min="17" max="17"/>
+    <col width="11.5" customWidth="1" min="18" max="18"/>
+    <col width="11.5" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="44" customWidth="1" min="21" max="21"/>
+    <col width="44" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="149" t="inlineStr">
         <is>
-          <t>Checks on the workshop workbook, 7 October 2026</t>
+          <t>Vehicle block: what is observed beside what the model assumes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Each Evidence row that can be traced to a registered input is recomputed from that input. Differences above 0.05% are listed as 'differs'.</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Stock, new sales, scrapping, drivetrain, fuel split and use. Observations are values from the registered inputs; the model's settings are in column D; shares, retirements and cross-checks are formulas.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="166" t="inlineStr">
-        <is>
-          <t>Evidence row</t>
-        </is>
-      </c>
-      <c r="B4" s="166" t="inlineStr">
-        <is>
-          <t>Series</t>
-        </is>
-      </c>
-      <c r="C4" s="166" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="D4" s="166" t="inlineStr">
-        <is>
-          <t>Workbook value</t>
-        </is>
-      </c>
-      <c r="E4" s="166" t="inlineStr">
-        <is>
-          <t>Recomputed from inputs</t>
-        </is>
-      </c>
-      <c r="F4" s="166" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="G4" s="166" t="inlineStr">
-        <is>
-          <t>Input file</t>
+      <c r="A4" s="150" t="inlineStr">
+        <is>
+          <t>Driver / output</t>
+        </is>
+      </c>
+      <c r="B4" s="150" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C4" s="150" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D4" s="150" t="inlineStr">
+        <is>
+          <t>Scalar / latest value</t>
+        </is>
+      </c>
+      <c r="E4" s="150" t="inlineStr">
+        <is>
+          <t>Definition / period</t>
+        </is>
+      </c>
+      <c r="F4" s="150" t="n">
+        <v>2012</v>
+      </c>
+      <c r="G4" s="150" t="n">
+        <v>2013</v>
+      </c>
+      <c r="H4" s="150" t="n">
+        <v>2014</v>
+      </c>
+      <c r="I4" s="150" t="n">
+        <v>2015</v>
+      </c>
+      <c r="J4" s="150" t="n">
+        <v>2016</v>
+      </c>
+      <c r="K4" s="150" t="n">
+        <v>2017</v>
+      </c>
+      <c r="L4" s="150" t="n">
+        <v>2018</v>
+      </c>
+      <c r="M4" s="150" t="n">
+        <v>2019</v>
+      </c>
+      <c r="N4" s="150" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O4" s="150" t="n">
+        <v>2021</v>
+      </c>
+      <c r="P4" s="150" t="n">
+        <v>2022</v>
+      </c>
+      <c r="Q4" s="150" t="n">
+        <v>2023</v>
+      </c>
+      <c r="R4" s="150" t="n">
+        <v>2024</v>
+      </c>
+      <c r="S4" s="150" t="n">
+        <v>2025</v>
+      </c>
+      <c r="T4" s="150" t="inlineStr">
+        <is>
+          <t>Coverage / status</t>
+        </is>
+      </c>
+      <c r="U4" s="150" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="V4" s="150" t="inlineStr">
+        <is>
+          <t>Missing evidence / next action</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>sales_petrol</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D5" s="167" t="n">
-        <v>9185</v>
-      </c>
-      <c r="E5" s="167" t="n">
-        <v>9185</v>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_fiasa.csv</t>
-        </is>
-      </c>
+      <c r="A5" s="151" t="inlineStr">
+        <is>
+          <t>1. Registered vehicles at December</t>
+        </is>
+      </c>
+      <c r="B5" s="151" t="n"/>
+      <c r="C5" s="151" t="n"/>
+      <c r="D5" s="151" t="n"/>
+      <c r="E5" s="151" t="n"/>
+      <c r="F5" s="151" t="n"/>
+      <c r="G5" s="151" t="n"/>
+      <c r="H5" s="151" t="n"/>
+      <c r="I5" s="151" t="n"/>
+      <c r="J5" s="151" t="n"/>
+      <c r="K5" s="151" t="n"/>
+      <c r="L5" s="151" t="n"/>
+      <c r="M5" s="151" t="n"/>
+      <c r="N5" s="151" t="n"/>
+      <c r="O5" s="151" t="n"/>
+      <c r="P5" s="151" t="n"/>
+      <c r="Q5" s="151" t="n"/>
+      <c r="R5" s="151" t="n"/>
+      <c r="S5" s="151" t="n"/>
+      <c r="T5" s="151" t="n"/>
+      <c r="U5" s="151" t="n"/>
+      <c r="V5" s="151" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>G5</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>sales_petrol</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D6" s="167" t="n">
-        <v>9037</v>
-      </c>
-      <c r="E6" s="167" t="n">
-        <v>9037</v>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_fiasa.csv</t>
+      <c r="A6" s="152" t="inlineStr">
+        <is>
+          <t>Cars</t>
+        </is>
+      </c>
+      <c r="B6" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C6" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D6" s="166" t="n"/>
+      <c r="E6" s="152" t="inlineStr">
+        <is>
+          <t>Live (licensed) vehicles, all fuels together.</t>
+        </is>
+      </c>
+      <c r="F6" s="166" t="n"/>
+      <c r="G6" s="166" t="n"/>
+      <c r="H6" s="166" t="n"/>
+      <c r="I6" s="166" t="n"/>
+      <c r="J6" s="166" t="n"/>
+      <c r="K6" s="166" t="n"/>
+      <c r="L6" s="166" t="n"/>
+      <c r="M6" s="166" t="n"/>
+      <c r="N6" s="166" t="n"/>
+      <c r="O6" s="166" t="n">
+        <v>7652077</v>
+      </c>
+      <c r="P6" s="166" t="n">
+        <v>7685153</v>
+      </c>
+      <c r="Q6" s="166" t="n">
+        <v>7794164</v>
+      </c>
+      <c r="R6" s="166" t="n">
+        <v>7949275</v>
+      </c>
+      <c r="S6" s="166" t="n">
+        <v>8184111</v>
+      </c>
+      <c r="T6" s="152" t="inlineStr">
+        <is>
+          <t>2021-2025</t>
+        </is>
+      </c>
+      <c r="U6" s="152" t="inlineStr">
+        <is>
+          <t>NaTIS live vehicle population, December</t>
+        </is>
+      </c>
+      <c r="V6" s="152" t="inlineStr">
+        <is>
+          <t>No split by fuel or by age in this source</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>sales_petrol</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D7" s="167" t="n">
-        <v>9029</v>
-      </c>
-      <c r="E7" s="167" t="n">
-        <v>9029</v>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_fiasa.csv</t>
+      <c r="A7" s="152" t="inlineStr">
+        <is>
+          <t>Light commercial vehicles</t>
+        </is>
+      </c>
+      <c r="B7" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C7" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D7" s="166" t="n"/>
+      <c r="E7" s="152" t="inlineStr">
+        <is>
+          <t>Live (licensed) vehicles, all fuels together.</t>
+        </is>
+      </c>
+      <c r="F7" s="166" t="n"/>
+      <c r="G7" s="166" t="n"/>
+      <c r="H7" s="166" t="n"/>
+      <c r="I7" s="166" t="n"/>
+      <c r="J7" s="166" t="n"/>
+      <c r="K7" s="166" t="n"/>
+      <c r="L7" s="166" t="n"/>
+      <c r="M7" s="166" t="n"/>
+      <c r="N7" s="166" t="n"/>
+      <c r="O7" s="166" t="n">
+        <v>2671314</v>
+      </c>
+      <c r="P7" s="166" t="n">
+        <v>2658416</v>
+      </c>
+      <c r="Q7" s="166" t="n">
+        <v>2689310</v>
+      </c>
+      <c r="R7" s="166" t="n">
+        <v>2725606</v>
+      </c>
+      <c r="S7" s="166" t="n">
+        <v>2776258</v>
+      </c>
+      <c r="T7" s="152" t="inlineStr">
+        <is>
+          <t>2021-2025</t>
+        </is>
+      </c>
+      <c r="U7" s="152" t="inlineStr">
+        <is>
+          <t>NaTIS live vehicle population, December</t>
+        </is>
+      </c>
+      <c r="V7" s="152" t="inlineStr">
+        <is>
+          <t>No split by fuel or by age in this source</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>F6</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>dept_petrol</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D8" s="167" t="n">
-        <v>9184.869915572999</v>
-      </c>
-      <c r="E8" s="167" t="n">
-        <v>9184.869915572999</v>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department.csv</t>
+      <c r="A8" s="152" t="inlineStr">
+        <is>
+          <t>Trucks</t>
+        </is>
+      </c>
+      <c r="B8" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C8" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D8" s="166" t="n"/>
+      <c r="E8" s="152" t="inlineStr">
+        <is>
+          <t>Live (licensed) vehicles, all fuels together.</t>
+        </is>
+      </c>
+      <c r="F8" s="166" t="n"/>
+      <c r="G8" s="166" t="n"/>
+      <c r="H8" s="166" t="n"/>
+      <c r="I8" s="166" t="n"/>
+      <c r="J8" s="166" t="n"/>
+      <c r="K8" s="166" t="n"/>
+      <c r="L8" s="166" t="n"/>
+      <c r="M8" s="166" t="n"/>
+      <c r="N8" s="166" t="n"/>
+      <c r="O8" s="166" t="n">
+        <v>389112</v>
+      </c>
+      <c r="P8" s="166" t="n">
+        <v>385845</v>
+      </c>
+      <c r="Q8" s="166" t="n">
+        <v>392349</v>
+      </c>
+      <c r="R8" s="166" t="n">
+        <v>398542</v>
+      </c>
+      <c r="S8" s="166" t="n">
+        <v>404752</v>
+      </c>
+      <c r="T8" s="152" t="inlineStr">
+        <is>
+          <t>2021-2025</t>
+        </is>
+      </c>
+      <c r="U8" s="152" t="inlineStr">
+        <is>
+          <t>NaTIS live vehicle population, December</t>
+        </is>
+      </c>
+      <c r="V8" s="152" t="inlineStr">
+        <is>
+          <t>No split by fuel or by age in this source</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>G6</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>dept_petrol</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D9" s="167" t="n">
-        <v>9036.950113492001</v>
-      </c>
-      <c r="E9" s="167" t="n">
-        <v>9036.950113492001</v>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department.csv</t>
+      <c r="A9" s="152" t="inlineStr">
+        <is>
+          <t>Buses</t>
+        </is>
+      </c>
+      <c r="B9" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C9" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D9" s="166" t="n"/>
+      <c r="E9" s="152" t="inlineStr">
+        <is>
+          <t>Live (licensed) vehicles, all fuels together.</t>
+        </is>
+      </c>
+      <c r="F9" s="166" t="n"/>
+      <c r="G9" s="166" t="n"/>
+      <c r="H9" s="166" t="n"/>
+      <c r="I9" s="166" t="n"/>
+      <c r="J9" s="166" t="n"/>
+      <c r="K9" s="166" t="n"/>
+      <c r="L9" s="166" t="n"/>
+      <c r="M9" s="166" t="n"/>
+      <c r="N9" s="166" t="n"/>
+      <c r="O9" s="166" t="n">
+        <v>64340</v>
+      </c>
+      <c r="P9" s="166" t="n">
+        <v>64170</v>
+      </c>
+      <c r="Q9" s="166" t="n">
+        <v>64982</v>
+      </c>
+      <c r="R9" s="166" t="n">
+        <v>65792</v>
+      </c>
+      <c r="S9" s="166" t="n">
+        <v>66249</v>
+      </c>
+      <c r="T9" s="152" t="inlineStr">
+        <is>
+          <t>2021-2025</t>
+        </is>
+      </c>
+      <c r="U9" s="152" t="inlineStr">
+        <is>
+          <t>NaTIS live vehicle population, December</t>
+        </is>
+      </c>
+      <c r="V9" s="152" t="inlineStr">
+        <is>
+          <t>No split by fuel or by age in this source</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>F7</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>sales_diesel</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D10" s="167" t="n">
-        <v>12717</v>
-      </c>
-      <c r="E10" s="167" t="n">
-        <v>12717</v>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_fiasa.csv</t>
+      <c r="A10" s="152" t="inlineStr">
+        <is>
+          <t>Minibuses</t>
+        </is>
+      </c>
+      <c r="B10" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C10" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D10" s="166" t="n"/>
+      <c r="E10" s="152" t="inlineStr">
+        <is>
+          <t>Live (licensed) vehicles, all fuels together.</t>
+        </is>
+      </c>
+      <c r="F10" s="166" t="n"/>
+      <c r="G10" s="166" t="n"/>
+      <c r="H10" s="166" t="n"/>
+      <c r="I10" s="166" t="n"/>
+      <c r="J10" s="166" t="n"/>
+      <c r="K10" s="166" t="n"/>
+      <c r="L10" s="166" t="n"/>
+      <c r="M10" s="166" t="n"/>
+      <c r="N10" s="166" t="n"/>
+      <c r="O10" s="166" t="n">
+        <v>349671</v>
+      </c>
+      <c r="P10" s="166" t="n">
+        <v>349335</v>
+      </c>
+      <c r="Q10" s="166" t="n">
+        <v>355235</v>
+      </c>
+      <c r="R10" s="166" t="n">
+        <v>355139</v>
+      </c>
+      <c r="S10" s="166" t="n">
+        <v>355145</v>
+      </c>
+      <c r="T10" s="152" t="inlineStr">
+        <is>
+          <t>2021-2025</t>
+        </is>
+      </c>
+      <c r="U10" s="152" t="inlineStr">
+        <is>
+          <t>NaTIS live vehicle population, December</t>
+        </is>
+      </c>
+      <c r="V10" s="152" t="inlineStr">
+        <is>
+          <t>No split by fuel or by age in this source</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>G7</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>sales_diesel</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D11" s="167" t="n">
-        <v>12907</v>
-      </c>
-      <c r="E11" s="167" t="n">
-        <v>12907</v>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_fiasa.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>sales_diesel</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D12" s="167" t="n">
-        <v>11734</v>
-      </c>
-      <c r="E12" s="167" t="n">
-        <v>11734</v>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_fiasa.csv</t>
+      <c r="A11" s="152" t="inlineStr">
+        <is>
+          <t>Motorcycles</t>
+        </is>
+      </c>
+      <c r="B11" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C11" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D11" s="166" t="n"/>
+      <c r="E11" s="152" t="inlineStr">
+        <is>
+          <t>Live (licensed) vehicles, all fuels together.</t>
+        </is>
+      </c>
+      <c r="F11" s="166" t="n"/>
+      <c r="G11" s="166" t="n"/>
+      <c r="H11" s="166" t="n"/>
+      <c r="I11" s="166" t="n"/>
+      <c r="J11" s="166" t="n"/>
+      <c r="K11" s="166" t="n"/>
+      <c r="L11" s="166" t="n"/>
+      <c r="M11" s="166" t="n"/>
+      <c r="N11" s="166" t="n"/>
+      <c r="O11" s="166" t="n">
+        <v>347631</v>
+      </c>
+      <c r="P11" s="166" t="n">
+        <v>346153</v>
+      </c>
+      <c r="Q11" s="166" t="n">
+        <v>349215</v>
+      </c>
+      <c r="R11" s="166" t="n">
+        <v>358817</v>
+      </c>
+      <c r="S11" s="166" t="n">
+        <v>372137</v>
+      </c>
+      <c r="T11" s="152" t="inlineStr">
+        <is>
+          <t>2021-2025</t>
+        </is>
+      </c>
+      <c r="U11" s="152" t="inlineStr">
+        <is>
+          <t>NaTIS live vehicle population, December</t>
+        </is>
+      </c>
+      <c r="V11" s="152" t="inlineStr">
+        <is>
+          <t>No split by fuel or by age in this source</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>F8</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>dept_diesel</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D13" s="167" t="n">
-        <v>12717.326319019</v>
-      </c>
-      <c r="E13" s="167" t="n">
-        <v>12717.326319019</v>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department.csv</t>
-        </is>
-      </c>
+      <c r="A13" s="151" t="inlineStr">
+        <is>
+          <t>2. New vehicle sales</t>
+        </is>
+      </c>
+      <c r="B13" s="151" t="n"/>
+      <c r="C13" s="151" t="n"/>
+      <c r="D13" s="151" t="n"/>
+      <c r="E13" s="151" t="n"/>
+      <c r="F13" s="151" t="n"/>
+      <c r="G13" s="151" t="n"/>
+      <c r="H13" s="151" t="n"/>
+      <c r="I13" s="151" t="n"/>
+      <c r="J13" s="151" t="n"/>
+      <c r="K13" s="151" t="n"/>
+      <c r="L13" s="151" t="n"/>
+      <c r="M13" s="151" t="n"/>
+      <c r="N13" s="151" t="n"/>
+      <c r="O13" s="151" t="n"/>
+      <c r="P13" s="151" t="n"/>
+      <c r="Q13" s="151" t="n"/>
+      <c r="R13" s="151" t="n"/>
+      <c r="S13" s="151" t="n"/>
+      <c r="T13" s="151" t="n"/>
+      <c r="U13" s="151" t="n"/>
+      <c r="V13" s="151" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>G8</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>dept_diesel</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D14" s="167" t="n">
-        <v>12907.499965808</v>
-      </c>
-      <c r="E14" s="167" t="n">
-        <v>12907.499965808</v>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department.csv</t>
-        </is>
-      </c>
+      <c r="A14" s="152" t="inlineStr">
+        <is>
+          <t>Cars, new sales</t>
+        </is>
+      </c>
+      <c r="B14" s="153" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C14" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D14" s="166" t="n"/>
+      <c r="E14" s="152" t="inlineStr">
+        <is>
+          <t>Actual new sales, all drivetrains.</t>
+        </is>
+      </c>
+      <c r="F14" s="166" t="n"/>
+      <c r="G14" s="166" t="n"/>
+      <c r="H14" s="166" t="n"/>
+      <c r="I14" s="166" t="n">
+        <v>412397</v>
+      </c>
+      <c r="J14" s="166" t="n">
+        <v>361265</v>
+      </c>
+      <c r="K14" s="166" t="n">
+        <v>368114</v>
+      </c>
+      <c r="L14" s="166" t="n">
+        <v>365247</v>
+      </c>
+      <c r="M14" s="166" t="n">
+        <v>355379</v>
+      </c>
+      <c r="N14" s="166" t="n">
+        <v>246541</v>
+      </c>
+      <c r="O14" s="166" t="n">
+        <v>304338</v>
+      </c>
+      <c r="P14" s="166" t="n">
+        <v>363681</v>
+      </c>
+      <c r="Q14" s="166" t="n">
+        <v>347377</v>
+      </c>
+      <c r="R14" s="166" t="n">
+        <v>351553</v>
+      </c>
+      <c r="S14" s="166" t="n">
+        <v>422463</v>
+      </c>
+      <c r="T14" s="152" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+      <c r="U14" s="152" t="inlineStr">
+        <is>
+          <t>naamsa industry vehicle sales</t>
+        </is>
+      </c>
+      <c r="V14" s="152" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>F9</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>sales_jet</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D15" s="167" t="n">
-        <v>1478</v>
-      </c>
-      <c r="E15" s="167" t="n">
-        <v>1478</v>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_fiasa.csv</t>
-        </is>
-      </c>
+      <c r="A15" s="152" t="inlineStr">
+        <is>
+          <t>Light commercial vehicles, new sales</t>
+        </is>
+      </c>
+      <c r="B15" s="153" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C15" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D15" s="166" t="n"/>
+      <c r="E15" s="152" t="inlineStr">
+        <is>
+          <t>Actual new sales, all drivetrains.</t>
+        </is>
+      </c>
+      <c r="F15" s="166" t="n"/>
+      <c r="G15" s="166" t="n"/>
+      <c r="H15" s="166" t="n"/>
+      <c r="I15" s="166" t="n">
+        <v>174812</v>
+      </c>
+      <c r="J15" s="166" t="n">
+        <v>159316</v>
+      </c>
+      <c r="K15" s="166" t="n">
+        <v>163317</v>
+      </c>
+      <c r="L15" s="166" t="n">
+        <v>159525</v>
+      </c>
+      <c r="M15" s="166" t="n">
+        <v>153221</v>
+      </c>
+      <c r="N15" s="166" t="n">
+        <v>110912</v>
+      </c>
+      <c r="O15" s="166" t="n">
+        <v>133078</v>
+      </c>
+      <c r="P15" s="166" t="n">
+        <v>135711</v>
+      </c>
+      <c r="Q15" s="166" t="n">
+        <v>151490</v>
+      </c>
+      <c r="R15" s="166" t="n">
+        <v>133375</v>
+      </c>
+      <c r="S15" s="166" t="n">
+        <v>143964</v>
+      </c>
+      <c r="T15" s="152" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+      <c r="U15" s="152" t="inlineStr">
+        <is>
+          <t>naamsa industry vehicle sales</t>
+        </is>
+      </c>
+      <c r="V15" s="152" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>G9</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>sales_jet</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D16" s="167" t="n">
-        <v>1844</v>
-      </c>
-      <c r="E16" s="167" t="n">
-        <v>1844</v>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_fiasa.csv</t>
-        </is>
-      </c>
+      <c r="A16" s="152" t="inlineStr">
+        <is>
+          <t>Medium and heavy commercial vehicles, new sales</t>
+        </is>
+      </c>
+      <c r="B16" s="153" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C16" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D16" s="166" t="n"/>
+      <c r="E16" s="152" t="inlineStr">
+        <is>
+          <t>Actual new sales, all drivetrains.</t>
+        </is>
+      </c>
+      <c r="F16" s="166" t="n"/>
+      <c r="G16" s="166" t="n"/>
+      <c r="H16" s="166" t="n"/>
+      <c r="I16" s="166" t="n">
+        <v>30441</v>
+      </c>
+      <c r="J16" s="166" t="n">
+        <v>26972</v>
+      </c>
+      <c r="K16" s="166" t="n">
+        <v>26272</v>
+      </c>
+      <c r="L16" s="166" t="n">
+        <v>27449</v>
+      </c>
+      <c r="M16" s="166" t="n">
+        <v>27891</v>
+      </c>
+      <c r="N16" s="166" t="n">
+        <v>22614</v>
+      </c>
+      <c r="O16" s="166" t="n">
+        <v>26906</v>
+      </c>
+      <c r="P16" s="166" t="n">
+        <v>29942</v>
+      </c>
+      <c r="Q16" s="166" t="n">
+        <v>32690</v>
+      </c>
+      <c r="R16" s="166" t="n">
+        <v>31175</v>
+      </c>
+      <c r="S16" s="166" t="n">
+        <v>30911</v>
+      </c>
+      <c r="T16" s="152" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+      <c r="U16" s="152" t="inlineStr">
+        <is>
+          <t>naamsa industry vehicle sales</t>
+        </is>
+      </c>
+      <c r="V16" s="152" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>H9</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>sales_jet</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D17" s="167" t="n">
-        <v>1955</v>
-      </c>
-      <c r="E17" s="167" t="n">
-        <v>1955</v>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_fiasa.csv</t>
-        </is>
-      </c>
+      <c r="A17" s="152" t="inlineStr">
+        <is>
+          <t>All segments, new sales</t>
+        </is>
+      </c>
+      <c r="B17" s="153" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C17" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D17" s="166" t="n"/>
+      <c r="E17" s="152" t="inlineStr">
+        <is>
+          <t>Total market as reported.</t>
+        </is>
+      </c>
+      <c r="F17" s="166" t="n"/>
+      <c r="G17" s="166" t="n"/>
+      <c r="H17" s="166" t="n"/>
+      <c r="I17" s="166" t="n">
+        <v>617650</v>
+      </c>
+      <c r="J17" s="166" t="n">
+        <v>547552</v>
+      </c>
+      <c r="K17" s="166" t="n">
+        <v>557719</v>
+      </c>
+      <c r="L17" s="166" t="n">
+        <v>552221</v>
+      </c>
+      <c r="M17" s="166" t="n">
+        <v>536486</v>
+      </c>
+      <c r="N17" s="166" t="n">
+        <v>380065</v>
+      </c>
+      <c r="O17" s="166" t="n">
+        <v>464322</v>
+      </c>
+      <c r="P17" s="166" t="n">
+        <v>529335</v>
+      </c>
+      <c r="Q17" s="166" t="n">
+        <v>531557</v>
+      </c>
+      <c r="R17" s="166" t="n">
+        <v>516103</v>
+      </c>
+      <c r="S17" s="166" t="n">
+        <v>597338</v>
+      </c>
+      <c r="T17" s="152" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+      <c r="U17" s="152" t="inlineStr">
+        <is>
+          <t>naamsa industry vehicle sales</t>
+        </is>
+      </c>
+      <c r="V17" s="152" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>F10</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>dept_jet</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>2022</v>
+      <c r="A18" s="155" t="inlineStr">
+        <is>
+          <t>Cars share of new sales</t>
+        </is>
+      </c>
+      <c r="B18" s="156" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C18" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
       </c>
       <c r="D18" s="167" t="n">
-        <v>1478.149852603</v>
-      </c>
-      <c r="E18" s="167" t="n">
-        <v>1478.149852603</v>
-      </c>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department.csv</t>
-        </is>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="E18" s="155" t="inlineStr">
+        <is>
+          <t>Observed share. Column D is the model's fixed split of new vehicles.</t>
+        </is>
+      </c>
+      <c r="F18" s="167">
+        <f>IF(COUNT(F14,F17)&lt;2,"",F14/F17*100)</f>
+        <v/>
+      </c>
+      <c r="G18" s="167">
+        <f>IF(COUNT(G14,G17)&lt;2,"",G14/G17*100)</f>
+        <v/>
+      </c>
+      <c r="H18" s="167">
+        <f>IF(COUNT(H14,H17)&lt;2,"",H14/H17*100)</f>
+        <v/>
+      </c>
+      <c r="I18" s="167">
+        <f>IF(COUNT(I14,I17)&lt;2,"",I14/I17*100)</f>
+        <v/>
+      </c>
+      <c r="J18" s="167">
+        <f>IF(COUNT(J14,J17)&lt;2,"",J14/J17*100)</f>
+        <v/>
+      </c>
+      <c r="K18" s="167">
+        <f>IF(COUNT(K14,K17)&lt;2,"",K14/K17*100)</f>
+        <v/>
+      </c>
+      <c r="L18" s="167">
+        <f>IF(COUNT(L14,L17)&lt;2,"",L14/L17*100)</f>
+        <v/>
+      </c>
+      <c r="M18" s="167">
+        <f>IF(COUNT(M14,M17)&lt;2,"",M14/M17*100)</f>
+        <v/>
+      </c>
+      <c r="N18" s="167">
+        <f>IF(COUNT(N14,N17)&lt;2,"",N14/N17*100)</f>
+        <v/>
+      </c>
+      <c r="O18" s="167">
+        <f>IF(COUNT(O14,O17)&lt;2,"",O14/O17*100)</f>
+        <v/>
+      </c>
+      <c r="P18" s="167">
+        <f>IF(COUNT(P14,P17)&lt;2,"",P14/P17*100)</f>
+        <v/>
+      </c>
+      <c r="Q18" s="167">
+        <f>IF(COUNT(Q14,Q17)&lt;2,"",Q14/Q17*100)</f>
+        <v/>
+      </c>
+      <c r="R18" s="167">
+        <f>IF(COUNT(R14,R17)&lt;2,"",R14/R17*100)</f>
+        <v/>
+      </c>
+      <c r="S18" s="167">
+        <f>IF(COUNT(S14,S17)&lt;2,"",S14/S17*100)</f>
+        <v/>
+      </c>
+      <c r="T18" s="155" t="inlineStr">
+        <is>
+          <t>Model setting in column D</t>
+        </is>
+      </c>
+      <c r="U18" s="155" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml: new_vehicle_segment_split</t>
+        </is>
+      </c>
+      <c r="V18" s="155" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>G10</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>dept_jet</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>2023</v>
+      <c r="A19" s="155" t="inlineStr">
+        <is>
+          <t>Light commercial share of new sales</t>
+        </is>
+      </c>
+      <c r="B19" s="156" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C19" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
       </c>
       <c r="D19" s="167" t="n">
-        <v>1843.971762465</v>
-      </c>
-      <c r="E19" s="167" t="n">
-        <v>1843.971762465</v>
-      </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department.csv</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E19" s="155" t="inlineStr">
+        <is>
+          <t>Observed share. Column D is the model's fixed split of new vehicles.</t>
+        </is>
+      </c>
+      <c r="F19" s="167">
+        <f>IF(COUNT(F15,F17)&lt;2,"",F15/F17*100)</f>
+        <v/>
+      </c>
+      <c r="G19" s="167">
+        <f>IF(COUNT(G15,G17)&lt;2,"",G15/G17*100)</f>
+        <v/>
+      </c>
+      <c r="H19" s="167">
+        <f>IF(COUNT(H15,H17)&lt;2,"",H15/H17*100)</f>
+        <v/>
+      </c>
+      <c r="I19" s="167">
+        <f>IF(COUNT(I15,I17)&lt;2,"",I15/I17*100)</f>
+        <v/>
+      </c>
+      <c r="J19" s="167">
+        <f>IF(COUNT(J15,J17)&lt;2,"",J15/J17*100)</f>
+        <v/>
+      </c>
+      <c r="K19" s="167">
+        <f>IF(COUNT(K15,K17)&lt;2,"",K15/K17*100)</f>
+        <v/>
+      </c>
+      <c r="L19" s="167">
+        <f>IF(COUNT(L15,L17)&lt;2,"",L15/L17*100)</f>
+        <v/>
+      </c>
+      <c r="M19" s="167">
+        <f>IF(COUNT(M15,M17)&lt;2,"",M15/M17*100)</f>
+        <v/>
+      </c>
+      <c r="N19" s="167">
+        <f>IF(COUNT(N15,N17)&lt;2,"",N15/N17*100)</f>
+        <v/>
+      </c>
+      <c r="O19" s="167">
+        <f>IF(COUNT(O15,O17)&lt;2,"",O15/O17*100)</f>
+        <v/>
+      </c>
+      <c r="P19" s="167">
+        <f>IF(COUNT(P15,P17)&lt;2,"",P15/P17*100)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="167">
+        <f>IF(COUNT(Q15,Q17)&lt;2,"",Q15/Q17*100)</f>
+        <v/>
+      </c>
+      <c r="R19" s="167">
+        <f>IF(COUNT(R15,R17)&lt;2,"",R15/R17*100)</f>
+        <v/>
+      </c>
+      <c r="S19" s="167">
+        <f>IF(COUNT(S15,S17)&lt;2,"",S15/S17*100)</f>
+        <v/>
+      </c>
+      <c r="T19" s="155" t="inlineStr">
+        <is>
+          <t>Model setting in column D</t>
+        </is>
+      </c>
+      <c r="U19" s="155" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml: new_vehicle_segment_split</t>
+        </is>
+      </c>
+      <c r="V19" s="155" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>F11</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>sales_fuel_oil</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>2022</v>
+      <c r="A20" s="155" t="inlineStr">
+        <is>
+          <t>Medium and heavy commercial share of new sales</t>
+        </is>
+      </c>
+      <c r="B20" s="156" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C20" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
       </c>
       <c r="D20" s="167" t="n">
-        <v>594</v>
-      </c>
-      <c r="E20" s="167" t="n">
-        <v>594</v>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_fiasa.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>sales_fuel_oil</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D21" s="167" t="n">
-        <v>658</v>
-      </c>
-      <c r="E21" s="167" t="n">
-        <v>658</v>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_fiasa.csv</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E20" s="155" t="inlineStr">
+        <is>
+          <t>Observed share. Column D is the model's fixed split of new vehicles.</t>
+        </is>
+      </c>
+      <c r="F20" s="167">
+        <f>IF(COUNT(F16,F17)&lt;2,"",F16/F17*100)</f>
+        <v/>
+      </c>
+      <c r="G20" s="167">
+        <f>IF(COUNT(G16,G17)&lt;2,"",G16/G17*100)</f>
+        <v/>
+      </c>
+      <c r="H20" s="167">
+        <f>IF(COUNT(H16,H17)&lt;2,"",H16/H17*100)</f>
+        <v/>
+      </c>
+      <c r="I20" s="167">
+        <f>IF(COUNT(I16,I17)&lt;2,"",I16/I17*100)</f>
+        <v/>
+      </c>
+      <c r="J20" s="167">
+        <f>IF(COUNT(J16,J17)&lt;2,"",J16/J17*100)</f>
+        <v/>
+      </c>
+      <c r="K20" s="167">
+        <f>IF(COUNT(K16,K17)&lt;2,"",K16/K17*100)</f>
+        <v/>
+      </c>
+      <c r="L20" s="167">
+        <f>IF(COUNT(L16,L17)&lt;2,"",L16/L17*100)</f>
+        <v/>
+      </c>
+      <c r="M20" s="167">
+        <f>IF(COUNT(M16,M17)&lt;2,"",M16/M17*100)</f>
+        <v/>
+      </c>
+      <c r="N20" s="167">
+        <f>IF(COUNT(N16,N17)&lt;2,"",N16/N17*100)</f>
+        <v/>
+      </c>
+      <c r="O20" s="167">
+        <f>IF(COUNT(O16,O17)&lt;2,"",O16/O17*100)</f>
+        <v/>
+      </c>
+      <c r="P20" s="167">
+        <f>IF(COUNT(P16,P17)&lt;2,"",P16/P17*100)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="167">
+        <f>IF(COUNT(Q16,Q17)&lt;2,"",Q16/Q17*100)</f>
+        <v/>
+      </c>
+      <c r="R20" s="167">
+        <f>IF(COUNT(R16,R17)&lt;2,"",R16/R17*100)</f>
+        <v/>
+      </c>
+      <c r="S20" s="167">
+        <f>IF(COUNT(S16,S17)&lt;2,"",S16/S17*100)</f>
+        <v/>
+      </c>
+      <c r="T20" s="155" t="inlineStr">
+        <is>
+          <t>Model setting in column D</t>
+        </is>
+      </c>
+      <c r="U20" s="155" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml: new_vehicle_segment_split</t>
+        </is>
+      </c>
+      <c r="V20" s="155" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>H11</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>sales_fuel_oil</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D22" s="167" t="n">
-        <v>441</v>
-      </c>
-      <c r="E22" s="167" t="n">
-        <v>441</v>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_fiasa.csv</t>
-        </is>
-      </c>
+      <c r="A22" s="151" t="inlineStr">
+        <is>
+          <t>3. Apparent retirements: last December's stock plus this year's sales less this December's stock</t>
+        </is>
+      </c>
+      <c r="B22" s="151" t="n"/>
+      <c r="C22" s="151" t="n"/>
+      <c r="D22" s="151" t="n"/>
+      <c r="E22" s="151" t="n"/>
+      <c r="F22" s="151" t="n"/>
+      <c r="G22" s="151" t="n"/>
+      <c r="H22" s="151" t="n"/>
+      <c r="I22" s="151" t="n"/>
+      <c r="J22" s="151" t="n"/>
+      <c r="K22" s="151" t="n"/>
+      <c r="L22" s="151" t="n"/>
+      <c r="M22" s="151" t="n"/>
+      <c r="N22" s="151" t="n"/>
+      <c r="O22" s="151" t="n"/>
+      <c r="P22" s="151" t="n"/>
+      <c r="Q22" s="151" t="n"/>
+      <c r="R22" s="151" t="n"/>
+      <c r="S22" s="151" t="n"/>
+      <c r="T22" s="151" t="n"/>
+      <c r="U22" s="151" t="n"/>
+      <c r="V22" s="151" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>F12</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>dept_fuel_oil</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D23" s="167" t="n">
-        <v>594.0401649620001</v>
-      </c>
-      <c r="E23" s="167" t="n">
-        <v>594.0401649620001</v>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department.csv</t>
-        </is>
-      </c>
+      <c r="A23" s="155" t="inlineStr">
+        <is>
+          <t>Cars retired</t>
+        </is>
+      </c>
+      <c r="B23" s="156" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C23" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D23" s="168" t="n"/>
+      <c r="E23" s="155" t="inlineStr">
+        <is>
+          <t>Includes deregistration, export and write-off; used imports and re-registration would lower it.</t>
+        </is>
+      </c>
+      <c r="F23" s="168" t="n"/>
+      <c r="G23" s="168">
+        <f>IF(COUNT(F6,G6,G14)&lt;3,"",F6+G14-G6)</f>
+        <v/>
+      </c>
+      <c r="H23" s="168">
+        <f>IF(COUNT(G6,H6,H14)&lt;3,"",G6+H14-H6)</f>
+        <v/>
+      </c>
+      <c r="I23" s="168">
+        <f>IF(COUNT(H6,I6,I14)&lt;3,"",H6+I14-I6)</f>
+        <v/>
+      </c>
+      <c r="J23" s="168">
+        <f>IF(COUNT(I6,J6,J14)&lt;3,"",I6+J14-J6)</f>
+        <v/>
+      </c>
+      <c r="K23" s="168">
+        <f>IF(COUNT(J6,K6,K14)&lt;3,"",J6+K14-K6)</f>
+        <v/>
+      </c>
+      <c r="L23" s="168">
+        <f>IF(COUNT(K6,L6,L14)&lt;3,"",K6+L14-L6)</f>
+        <v/>
+      </c>
+      <c r="M23" s="168">
+        <f>IF(COUNT(L6,M6,M14)&lt;3,"",L6+M14-M6)</f>
+        <v/>
+      </c>
+      <c r="N23" s="168">
+        <f>IF(COUNT(M6,N6,N14)&lt;3,"",M6+N14-N6)</f>
+        <v/>
+      </c>
+      <c r="O23" s="168">
+        <f>IF(COUNT(N6,O6,O14)&lt;3,"",N6+O14-O6)</f>
+        <v/>
+      </c>
+      <c r="P23" s="168">
+        <f>IF(COUNT(O6,P6,P14)&lt;3,"",O6+P14-P6)</f>
+        <v/>
+      </c>
+      <c r="Q23" s="168">
+        <f>IF(COUNT(P6,Q6,Q14)&lt;3,"",P6+Q14-Q6)</f>
+        <v/>
+      </c>
+      <c r="R23" s="168">
+        <f>IF(COUNT(Q6,R6,R14)&lt;3,"",Q6+R14-R6)</f>
+        <v/>
+      </c>
+      <c r="S23" s="168">
+        <f>IF(COUNT(R6,S6,S14)&lt;3,"",R6+S14-S6)</f>
+        <v/>
+      </c>
+      <c r="T23" s="155" t="inlineStr"/>
+      <c r="U23" s="155" t="inlineStr"/>
+      <c r="V23" s="155" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>dept_fuel_oil</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>2023</v>
+      <c r="A24" s="155" t="inlineStr">
+        <is>
+          <t>Cars retirement rate</t>
+        </is>
+      </c>
+      <c r="B24" s="156" t="inlineStr">
+        <is>
+          <t>% of last December's stock</t>
+        </is>
+      </c>
+      <c r="C24" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
       </c>
       <c r="D24" s="167" t="n">
-        <v>658.0930416160001</v>
-      </c>
-      <c r="E24" s="167" t="n">
-        <v>658.0930416160001</v>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department.csv</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E24" s="155" t="inlineStr">
+        <is>
+          <t>Retired divided by last December's stock. Column D is the model's scrappage rate.</t>
+        </is>
+      </c>
+      <c r="F24" s="167" t="n"/>
+      <c r="G24" s="167">
+        <f>IF(ISNUMBER(G23),G23/F6*100,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="167">
+        <f>IF(ISNUMBER(H23),H23/G6*100,"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="167">
+        <f>IF(ISNUMBER(I23),I23/H6*100,"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="167">
+        <f>IF(ISNUMBER(J23),J23/I6*100,"")</f>
+        <v/>
+      </c>
+      <c r="K24" s="167">
+        <f>IF(ISNUMBER(K23),K23/J6*100,"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="167">
+        <f>IF(ISNUMBER(L23),L23/K6*100,"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="167">
+        <f>IF(ISNUMBER(M23),M23/L6*100,"")</f>
+        <v/>
+      </c>
+      <c r="N24" s="167">
+        <f>IF(ISNUMBER(N23),N23/M6*100,"")</f>
+        <v/>
+      </c>
+      <c r="O24" s="167">
+        <f>IF(ISNUMBER(O23),O23/N6*100,"")</f>
+        <v/>
+      </c>
+      <c r="P24" s="167">
+        <f>IF(ISNUMBER(P23),P23/O6*100,"")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="167">
+        <f>IF(ISNUMBER(Q23),Q23/P6*100,"")</f>
+        <v/>
+      </c>
+      <c r="R24" s="167">
+        <f>IF(ISNUMBER(R23),R23/Q6*100,"")</f>
+        <v/>
+      </c>
+      <c r="S24" s="167">
+        <f>IF(ISNUMBER(S23),S23/R6*100,"")</f>
+        <v/>
+      </c>
+      <c r="T24" s="155" t="inlineStr">
+        <is>
+          <t>Model setting in column D</t>
+        </is>
+      </c>
+      <c r="U24" s="155" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml: scrappage_rate</t>
+        </is>
+      </c>
+      <c r="V24" s="155" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>F25</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>macro_gdp_per_capita</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D25" s="167" t="n">
-        <v>76055.06748983047</v>
-      </c>
-      <c r="E25" s="167" t="n">
-        <v>76055.06748983047</v>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
+      <c r="A25" s="155" t="inlineStr">
+        <is>
+          <t>Light commercial vehicles retired</t>
+        </is>
+      </c>
+      <c r="B25" s="156" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C25" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D25" s="168" t="n"/>
+      <c r="E25" s="155" t="inlineStr">
+        <is>
+          <t>Includes deregistration, export and write-off; used imports and re-registration would lower it.</t>
+        </is>
+      </c>
+      <c r="F25" s="168" t="n"/>
+      <c r="G25" s="168">
+        <f>IF(COUNT(F7,G7,G15)&lt;3,"",F7+G15-G7)</f>
+        <v/>
+      </c>
+      <c r="H25" s="168">
+        <f>IF(COUNT(G7,H7,H15)&lt;3,"",G7+H15-H7)</f>
+        <v/>
+      </c>
+      <c r="I25" s="168">
+        <f>IF(COUNT(H7,I7,I15)&lt;3,"",H7+I15-I7)</f>
+        <v/>
+      </c>
+      <c r="J25" s="168">
+        <f>IF(COUNT(I7,J7,J15)&lt;3,"",I7+J15-J7)</f>
+        <v/>
+      </c>
+      <c r="K25" s="168">
+        <f>IF(COUNT(J7,K7,K15)&lt;3,"",J7+K15-K7)</f>
+        <v/>
+      </c>
+      <c r="L25" s="168">
+        <f>IF(COUNT(K7,L7,L15)&lt;3,"",K7+L15-L7)</f>
+        <v/>
+      </c>
+      <c r="M25" s="168">
+        <f>IF(COUNT(L7,M7,M15)&lt;3,"",L7+M15-M7)</f>
+        <v/>
+      </c>
+      <c r="N25" s="168">
+        <f>IF(COUNT(M7,N7,N15)&lt;3,"",M7+N15-N7)</f>
+        <v/>
+      </c>
+      <c r="O25" s="168">
+        <f>IF(COUNT(N7,O7,O15)&lt;3,"",N7+O15-O7)</f>
+        <v/>
+      </c>
+      <c r="P25" s="168">
+        <f>IF(COUNT(O7,P7,P15)&lt;3,"",O7+P15-P7)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="168">
+        <f>IF(COUNT(P7,Q7,Q15)&lt;3,"",P7+Q15-Q7)</f>
+        <v/>
+      </c>
+      <c r="R25" s="168">
+        <f>IF(COUNT(Q7,R7,R15)&lt;3,"",Q7+R15-R7)</f>
+        <v/>
+      </c>
+      <c r="S25" s="168">
+        <f>IF(COUNT(R7,S7,S15)&lt;3,"",R7+S15-S7)</f>
+        <v/>
+      </c>
+      <c r="T25" s="155" t="inlineStr"/>
+      <c r="U25" s="155" t="inlineStr"/>
+      <c r="V25" s="155" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>G25</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>macro_gdp_per_capita</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>2023</v>
+      <c r="A26" s="155" t="inlineStr">
+        <is>
+          <t>Light commercial vehicles retirement rate</t>
+        </is>
+      </c>
+      <c r="B26" s="156" t="inlineStr">
+        <is>
+          <t>% of last December's stock</t>
+        </is>
+      </c>
+      <c r="C26" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
       </c>
       <c r="D26" s="167" t="n">
-        <v>75781.52071231291</v>
-      </c>
-      <c r="E26" s="167" t="n">
-        <v>75781.52071231291</v>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E26" s="155" t="inlineStr">
+        <is>
+          <t>Retired divided by last December's stock. Column D is the model's scrappage rate.</t>
+        </is>
+      </c>
+      <c r="F26" s="167" t="n"/>
+      <c r="G26" s="167">
+        <f>IF(ISNUMBER(G25),G25/F7*100,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="167">
+        <f>IF(ISNUMBER(H25),H25/G7*100,"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="167">
+        <f>IF(ISNUMBER(I25),I25/H7*100,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="167">
+        <f>IF(ISNUMBER(J25),J25/I7*100,"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="167">
+        <f>IF(ISNUMBER(K25),K25/J7*100,"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="167">
+        <f>IF(ISNUMBER(L25),L25/K7*100,"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="167">
+        <f>IF(ISNUMBER(M25),M25/L7*100,"")</f>
+        <v/>
+      </c>
+      <c r="N26" s="167">
+        <f>IF(ISNUMBER(N25),N25/M7*100,"")</f>
+        <v/>
+      </c>
+      <c r="O26" s="167">
+        <f>IF(ISNUMBER(O25),O25/N7*100,"")</f>
+        <v/>
+      </c>
+      <c r="P26" s="167">
+        <f>IF(ISNUMBER(P25),P25/O7*100,"")</f>
+        <v/>
+      </c>
+      <c r="Q26" s="167">
+        <f>IF(ISNUMBER(Q25),Q25/P7*100,"")</f>
+        <v/>
+      </c>
+      <c r="R26" s="167">
+        <f>IF(ISNUMBER(R25),R25/Q7*100,"")</f>
+        <v/>
+      </c>
+      <c r="S26" s="167">
+        <f>IF(ISNUMBER(S25),S25/R7*100,"")</f>
+        <v/>
+      </c>
+      <c r="T26" s="155" t="inlineStr">
+        <is>
+          <t>Model setting in column D</t>
+        </is>
+      </c>
+      <c r="U26" s="155" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml: scrappage_rate</t>
+        </is>
+      </c>
+      <c r="V26" s="155" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>H25</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>macro_gdp_per_capita</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D27" s="167" t="n">
-        <v>75255.62912098455</v>
-      </c>
-      <c r="E27" s="167" t="n">
-        <v>75255.62912098455</v>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
+      <c r="A27" s="155" t="inlineStr">
+        <is>
+          <t>Trucks retired</t>
+        </is>
+      </c>
+      <c r="B27" s="156" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C27" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D27" s="168" t="n"/>
+      <c r="E27" s="155" t="inlineStr">
+        <is>
+          <t>Includes deregistration, export and write-off; used imports and re-registration would lower it.</t>
+        </is>
+      </c>
+      <c r="F27" s="168" t="n"/>
+      <c r="G27" s="168">
+        <f>IF(COUNT(F8,G8,G16)&lt;3,"",F8+G16-G8)</f>
+        <v/>
+      </c>
+      <c r="H27" s="168">
+        <f>IF(COUNT(G8,H8,H16)&lt;3,"",G8+H16-H8)</f>
+        <v/>
+      </c>
+      <c r="I27" s="168">
+        <f>IF(COUNT(H8,I8,I16)&lt;3,"",H8+I16-I8)</f>
+        <v/>
+      </c>
+      <c r="J27" s="168">
+        <f>IF(COUNT(I8,J8,J16)&lt;3,"",I8+J16-J8)</f>
+        <v/>
+      </c>
+      <c r="K27" s="168">
+        <f>IF(COUNT(J8,K8,K16)&lt;3,"",J8+K16-K8)</f>
+        <v/>
+      </c>
+      <c r="L27" s="168">
+        <f>IF(COUNT(K8,L8,L16)&lt;3,"",K8+L16-L8)</f>
+        <v/>
+      </c>
+      <c r="M27" s="168">
+        <f>IF(COUNT(L8,M8,M16)&lt;3,"",L8+M16-M8)</f>
+        <v/>
+      </c>
+      <c r="N27" s="168">
+        <f>IF(COUNT(M8,N8,N16)&lt;3,"",M8+N16-N8)</f>
+        <v/>
+      </c>
+      <c r="O27" s="168">
+        <f>IF(COUNT(N8,O8,O16)&lt;3,"",N8+O16-O8)</f>
+        <v/>
+      </c>
+      <c r="P27" s="168">
+        <f>IF(COUNT(O8,P8,P16)&lt;3,"",O8+P16-P8)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="168">
+        <f>IF(COUNT(P8,Q8,Q16)&lt;3,"",P8+Q16-Q8)</f>
+        <v/>
+      </c>
+      <c r="R27" s="168">
+        <f>IF(COUNT(Q8,R8,R16)&lt;3,"",Q8+R16-R8)</f>
+        <v/>
+      </c>
+      <c r="S27" s="168">
+        <f>IF(COUNT(R8,S8,S16)&lt;3,"",R8+S16-S8)</f>
+        <v/>
+      </c>
+      <c r="T27" s="155" t="inlineStr"/>
+      <c r="U27" s="155" t="inlineStr"/>
+      <c r="V27" s="155" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>I25</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>macro_gdp_per_capita</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>2025</v>
+      <c r="A28" s="155" t="inlineStr">
+        <is>
+          <t>Trucks retirement rate</t>
+        </is>
+      </c>
+      <c r="B28" s="156" t="inlineStr">
+        <is>
+          <t>% of last December's stock</t>
+        </is>
+      </c>
+      <c r="C28" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
       </c>
       <c r="D28" s="167" t="n">
-        <v>75149.98563223911</v>
-      </c>
-      <c r="E28" s="167" t="n">
-        <v>75149.98563223911</v>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>F26</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>macro_agriculture_forestry_and_fishing</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D29" s="167" t="n">
-        <v>131.7706421450265</v>
-      </c>
-      <c r="E29" s="167" t="n">
-        <v>131.7706421450265</v>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="E28" s="155" t="inlineStr">
+        <is>
+          <t>Retired divided by last December's stock. Column D is the model's scrappage rate.</t>
+        </is>
+      </c>
+      <c r="F28" s="167" t="n"/>
+      <c r="G28" s="167">
+        <f>IF(ISNUMBER(G27),G27/F8*100,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="167">
+        <f>IF(ISNUMBER(H27),H27/G8*100,"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="167">
+        <f>IF(ISNUMBER(I27),I27/H8*100,"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="167">
+        <f>IF(ISNUMBER(J27),J27/I8*100,"")</f>
+        <v/>
+      </c>
+      <c r="K28" s="167">
+        <f>IF(ISNUMBER(K27),K27/J8*100,"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="167">
+        <f>IF(ISNUMBER(L27),L27/K8*100,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="167">
+        <f>IF(ISNUMBER(M27),M27/L8*100,"")</f>
+        <v/>
+      </c>
+      <c r="N28" s="167">
+        <f>IF(ISNUMBER(N27),N27/M8*100,"")</f>
+        <v/>
+      </c>
+      <c r="O28" s="167">
+        <f>IF(ISNUMBER(O27),O27/N8*100,"")</f>
+        <v/>
+      </c>
+      <c r="P28" s="167">
+        <f>IF(ISNUMBER(P27),P27/O8*100,"")</f>
+        <v/>
+      </c>
+      <c r="Q28" s="167">
+        <f>IF(ISNUMBER(Q27),Q27/P8*100,"")</f>
+        <v/>
+      </c>
+      <c r="R28" s="167">
+        <f>IF(ISNUMBER(R27),R27/Q8*100,"")</f>
+        <v/>
+      </c>
+      <c r="S28" s="167">
+        <f>IF(ISNUMBER(S27),S27/R8*100,"")</f>
+        <v/>
+      </c>
+      <c r="T28" s="155" t="inlineStr">
+        <is>
+          <t>Model setting in column D</t>
+        </is>
+      </c>
+      <c r="U28" s="155" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml: scrappage_rate</t>
+        </is>
+      </c>
+      <c r="V28" s="155" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>G26</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>macro_agriculture_forestry_and_fishing</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D30" s="167" t="n">
-        <v>125.7466421450265</v>
-      </c>
-      <c r="E30" s="167" t="n">
-        <v>125.7466421450265</v>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
+      <c r="A30" s="151" t="inlineStr">
+        <is>
+          <t>4. Electrified new sales (all segments)</t>
+        </is>
+      </c>
+      <c r="B30" s="151" t="n"/>
+      <c r="C30" s="151" t="n"/>
+      <c r="D30" s="151" t="n"/>
+      <c r="E30" s="151" t="n"/>
+      <c r="F30" s="151" t="n"/>
+      <c r="G30" s="151" t="n"/>
+      <c r="H30" s="151" t="n"/>
+      <c r="I30" s="151" t="n"/>
+      <c r="J30" s="151" t="n"/>
+      <c r="K30" s="151" t="n"/>
+      <c r="L30" s="151" t="n"/>
+      <c r="M30" s="151" t="n"/>
+      <c r="N30" s="151" t="n"/>
+      <c r="O30" s="151" t="n"/>
+      <c r="P30" s="151" t="n"/>
+      <c r="Q30" s="151" t="n"/>
+      <c r="R30" s="151" t="n"/>
+      <c r="S30" s="151" t="n"/>
+      <c r="T30" s="151" t="n"/>
+      <c r="U30" s="151" t="n"/>
+      <c r="V30" s="151" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>H26</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>macro_agriculture_forestry_and_fishing</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D31" s="167" t="n">
-        <v>114.7916421450265</v>
-      </c>
-      <c r="E31" s="167" t="n">
-        <v>114.7916421450265</v>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
+      <c r="A31" s="152" t="inlineStr">
+        <is>
+          <t>Battery electric, new sales</t>
+        </is>
+      </c>
+      <c r="B31" s="153" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C31" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D31" s="166" t="n"/>
+      <c r="E31" s="152" t="inlineStr">
+        <is>
+          <t>Total market, not passenger cars only.</t>
+        </is>
+      </c>
+      <c r="F31" s="166" t="n"/>
+      <c r="G31" s="166" t="n"/>
+      <c r="H31" s="166" t="n"/>
+      <c r="I31" s="166" t="n"/>
+      <c r="J31" s="166" t="n"/>
+      <c r="K31" s="166" t="n"/>
+      <c r="L31" s="166" t="n"/>
+      <c r="M31" s="166" t="n">
+        <v>154</v>
+      </c>
+      <c r="N31" s="166" t="n">
+        <v>92</v>
+      </c>
+      <c r="O31" s="166" t="n">
+        <v>218</v>
+      </c>
+      <c r="P31" s="166" t="n">
+        <v>502</v>
+      </c>
+      <c r="Q31" s="166" t="n">
+        <v>929</v>
+      </c>
+      <c r="R31" s="166" t="n">
+        <v>1257</v>
+      </c>
+      <c r="S31" s="166" t="n">
+        <v>1088</v>
+      </c>
+      <c r="T31" s="152" t="inlineStr">
+        <is>
+          <t>2019-2025</t>
+        </is>
+      </c>
+      <c r="U31" s="152" t="inlineStr">
+        <is>
+          <t>naamsa new-energy vehicle sales</t>
+        </is>
+      </c>
+      <c r="V31" s="152" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>I26</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>macro_agriculture_forestry_and_fishing</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D32" s="167" t="n">
-        <v>134.7967469817132</v>
-      </c>
-      <c r="E32" s="167" t="n">
-        <v>134.7967469817132</v>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
+      <c r="A32" s="155" t="inlineStr">
+        <is>
+          <t>Battery electric share of new sales</t>
+        </is>
+      </c>
+      <c r="B32" s="156" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C32" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D32" s="169" t="n"/>
+      <c r="E32" s="155" t="inlineStr">
+        <is>
+          <t>Share of all new vehicles sold in the year.</t>
+        </is>
+      </c>
+      <c r="F32" s="169">
+        <f>IF(COUNT(F31,F17)&lt;2,"",F31/F17*100)</f>
+        <v/>
+      </c>
+      <c r="G32" s="169">
+        <f>IF(COUNT(G31,G17)&lt;2,"",G31/G17*100)</f>
+        <v/>
+      </c>
+      <c r="H32" s="169">
+        <f>IF(COUNT(H31,H17)&lt;2,"",H31/H17*100)</f>
+        <v/>
+      </c>
+      <c r="I32" s="169">
+        <f>IF(COUNT(I31,I17)&lt;2,"",I31/I17*100)</f>
+        <v/>
+      </c>
+      <c r="J32" s="169">
+        <f>IF(COUNT(J31,J17)&lt;2,"",J31/J17*100)</f>
+        <v/>
+      </c>
+      <c r="K32" s="169">
+        <f>IF(COUNT(K31,K17)&lt;2,"",K31/K17*100)</f>
+        <v/>
+      </c>
+      <c r="L32" s="169">
+        <f>IF(COUNT(L31,L17)&lt;2,"",L31/L17*100)</f>
+        <v/>
+      </c>
+      <c r="M32" s="169">
+        <f>IF(COUNT(M31,M17)&lt;2,"",M31/M17*100)</f>
+        <v/>
+      </c>
+      <c r="N32" s="169">
+        <f>IF(COUNT(N31,N17)&lt;2,"",N31/N17*100)</f>
+        <v/>
+      </c>
+      <c r="O32" s="169">
+        <f>IF(COUNT(O31,O17)&lt;2,"",O31/O17*100)</f>
+        <v/>
+      </c>
+      <c r="P32" s="169">
+        <f>IF(COUNT(P31,P17)&lt;2,"",P31/P17*100)</f>
+        <v/>
+      </c>
+      <c r="Q32" s="169">
+        <f>IF(COUNT(Q31,Q17)&lt;2,"",Q31/Q17*100)</f>
+        <v/>
+      </c>
+      <c r="R32" s="169">
+        <f>IF(COUNT(R31,R17)&lt;2,"",R31/R17*100)</f>
+        <v/>
+      </c>
+      <c r="S32" s="169">
+        <f>IF(COUNT(S31,S17)&lt;2,"",S31/S17*100)</f>
+        <v/>
+      </c>
+      <c r="T32" s="155" t="inlineStr"/>
+      <c r="U32" s="155" t="inlineStr"/>
+      <c r="V32" s="155" t="inlineStr">
+        <is>
+          <t>Share of the fleet is not observed after December 2023</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>F27</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t>macro_manufacturing</t>
-        </is>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D33" s="167" t="n">
-        <v>523.0907540648606</v>
-      </c>
-      <c r="E33" s="167" t="n">
-        <v>523.0907540648606</v>
-      </c>
-      <c r="F33" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
+      <c r="A33" s="152" t="inlineStr">
+        <is>
+          <t>Plug-in hybrid, new sales</t>
+        </is>
+      </c>
+      <c r="B33" s="153" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C33" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D33" s="166" t="n"/>
+      <c r="E33" s="152" t="inlineStr">
+        <is>
+          <t>Total market, not passenger cars only.</t>
+        </is>
+      </c>
+      <c r="F33" s="166" t="n"/>
+      <c r="G33" s="166" t="n"/>
+      <c r="H33" s="166" t="n"/>
+      <c r="I33" s="166" t="n"/>
+      <c r="J33" s="166" t="n"/>
+      <c r="K33" s="166" t="n"/>
+      <c r="L33" s="166" t="n"/>
+      <c r="M33" s="166" t="n">
+        <v>72</v>
+      </c>
+      <c r="N33" s="166" t="n">
+        <v>77</v>
+      </c>
+      <c r="O33" s="166" t="n">
+        <v>51</v>
+      </c>
+      <c r="P33" s="166" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q33" s="166" t="n">
+        <v>368</v>
+      </c>
+      <c r="R33" s="166" t="n">
+        <v>738</v>
+      </c>
+      <c r="S33" s="166" t="n">
+        <v>2810</v>
+      </c>
+      <c r="T33" s="152" t="inlineStr">
+        <is>
+          <t>2019-2025</t>
+        </is>
+      </c>
+      <c r="U33" s="152" t="inlineStr">
+        <is>
+          <t>naamsa new-energy vehicle sales</t>
+        </is>
+      </c>
+      <c r="V33" s="152" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>G27</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>macro_manufacturing</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D34" s="167" t="n">
-        <v>524.9937540648609</v>
-      </c>
-      <c r="E34" s="167" t="n">
-        <v>524.9937540648609</v>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
+      <c r="A34" s="155" t="inlineStr">
+        <is>
+          <t>Plug-in hybrid share of new sales</t>
+        </is>
+      </c>
+      <c r="B34" s="156" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C34" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D34" s="169" t="n"/>
+      <c r="E34" s="155" t="inlineStr">
+        <is>
+          <t>Share of all new vehicles sold in the year.</t>
+        </is>
+      </c>
+      <c r="F34" s="169">
+        <f>IF(COUNT(F33,F17)&lt;2,"",F33/F17*100)</f>
+        <v/>
+      </c>
+      <c r="G34" s="169">
+        <f>IF(COUNT(G33,G17)&lt;2,"",G33/G17*100)</f>
+        <v/>
+      </c>
+      <c r="H34" s="169">
+        <f>IF(COUNT(H33,H17)&lt;2,"",H33/H17*100)</f>
+        <v/>
+      </c>
+      <c r="I34" s="169">
+        <f>IF(COUNT(I33,I17)&lt;2,"",I33/I17*100)</f>
+        <v/>
+      </c>
+      <c r="J34" s="169">
+        <f>IF(COUNT(J33,J17)&lt;2,"",J33/J17*100)</f>
+        <v/>
+      </c>
+      <c r="K34" s="169">
+        <f>IF(COUNT(K33,K17)&lt;2,"",K33/K17*100)</f>
+        <v/>
+      </c>
+      <c r="L34" s="169">
+        <f>IF(COUNT(L33,L17)&lt;2,"",L33/L17*100)</f>
+        <v/>
+      </c>
+      <c r="M34" s="169">
+        <f>IF(COUNT(M33,M17)&lt;2,"",M33/M17*100)</f>
+        <v/>
+      </c>
+      <c r="N34" s="169">
+        <f>IF(COUNT(N33,N17)&lt;2,"",N33/N17*100)</f>
+        <v/>
+      </c>
+      <c r="O34" s="169">
+        <f>IF(COUNT(O33,O17)&lt;2,"",O33/O17*100)</f>
+        <v/>
+      </c>
+      <c r="P34" s="169">
+        <f>IF(COUNT(P33,P17)&lt;2,"",P33/P17*100)</f>
+        <v/>
+      </c>
+      <c r="Q34" s="169">
+        <f>IF(COUNT(Q33,Q17)&lt;2,"",Q33/Q17*100)</f>
+        <v/>
+      </c>
+      <c r="R34" s="169">
+        <f>IF(COUNT(R33,R17)&lt;2,"",R33/R17*100)</f>
+        <v/>
+      </c>
+      <c r="S34" s="169">
+        <f>IF(COUNT(S33,S17)&lt;2,"",S33/S17*100)</f>
+        <v/>
+      </c>
+      <c r="T34" s="155" t="inlineStr"/>
+      <c r="U34" s="155" t="inlineStr"/>
+      <c r="V34" s="155" t="inlineStr">
+        <is>
+          <t>Share of the fleet is not observed after December 2023</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>H27</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>macro_manufacturing</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D35" s="167" t="n">
-        <v>523.150754064861</v>
-      </c>
-      <c r="E35" s="167" t="n">
-        <v>523.150754064861</v>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
+      <c r="A35" s="152" t="inlineStr">
+        <is>
+          <t>Conventional hybrid, new sales</t>
+        </is>
+      </c>
+      <c r="B35" s="153" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C35" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D35" s="166" t="n"/>
+      <c r="E35" s="152" t="inlineStr">
+        <is>
+          <t>Total market, not passenger cars only.</t>
+        </is>
+      </c>
+      <c r="F35" s="166" t="n"/>
+      <c r="G35" s="166" t="n"/>
+      <c r="H35" s="166" t="n"/>
+      <c r="I35" s="166" t="n"/>
+      <c r="J35" s="166" t="n"/>
+      <c r="K35" s="166" t="n"/>
+      <c r="L35" s="166" t="n"/>
+      <c r="M35" s="166" t="n">
+        <v>181</v>
+      </c>
+      <c r="N35" s="166" t="n">
+        <v>155</v>
+      </c>
+      <c r="O35" s="166" t="n">
+        <v>627</v>
+      </c>
+      <c r="P35" s="166" t="n">
+        <v>4070</v>
+      </c>
+      <c r="Q35" s="166" t="n">
+        <v>6485</v>
+      </c>
+      <c r="R35" s="166" t="n">
+        <v>13616</v>
+      </c>
+      <c r="S35" s="166" t="n">
+        <v>12818</v>
+      </c>
+      <c r="T35" s="152" t="inlineStr">
+        <is>
+          <t>2019-2025</t>
+        </is>
+      </c>
+      <c r="U35" s="152" t="inlineStr">
+        <is>
+          <t>naamsa new-energy vehicle sales</t>
+        </is>
+      </c>
+      <c r="V35" s="152" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>I27</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>macro_manufacturing</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D36" s="167" t="n">
-        <v>516.9856529750193</v>
-      </c>
-      <c r="E36" s="167" t="n">
-        <v>516.9856529750193</v>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>F28</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>macro_mining_and_quarrying</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D37" s="167" t="n">
-        <v>204.4529227196744</v>
-      </c>
-      <c r="E37" s="167" t="n">
-        <v>204.4529227196744</v>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
+      <c r="A36" s="155" t="inlineStr">
+        <is>
+          <t>Conventional hybrid share of new sales</t>
+        </is>
+      </c>
+      <c r="B36" s="156" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C36" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D36" s="169" t="n"/>
+      <c r="E36" s="155" t="inlineStr">
+        <is>
+          <t>Share of all new vehicles sold in the year.</t>
+        </is>
+      </c>
+      <c r="F36" s="169">
+        <f>IF(COUNT(F35,F17)&lt;2,"",F35/F17*100)</f>
+        <v/>
+      </c>
+      <c r="G36" s="169">
+        <f>IF(COUNT(G35,G17)&lt;2,"",G35/G17*100)</f>
+        <v/>
+      </c>
+      <c r="H36" s="169">
+        <f>IF(COUNT(H35,H17)&lt;2,"",H35/H17*100)</f>
+        <v/>
+      </c>
+      <c r="I36" s="169">
+        <f>IF(COUNT(I35,I17)&lt;2,"",I35/I17*100)</f>
+        <v/>
+      </c>
+      <c r="J36" s="169">
+        <f>IF(COUNT(J35,J17)&lt;2,"",J35/J17*100)</f>
+        <v/>
+      </c>
+      <c r="K36" s="169">
+        <f>IF(COUNT(K35,K17)&lt;2,"",K35/K17*100)</f>
+        <v/>
+      </c>
+      <c r="L36" s="169">
+        <f>IF(COUNT(L35,L17)&lt;2,"",L35/L17*100)</f>
+        <v/>
+      </c>
+      <c r="M36" s="169">
+        <f>IF(COUNT(M35,M17)&lt;2,"",M35/M17*100)</f>
+        <v/>
+      </c>
+      <c r="N36" s="169">
+        <f>IF(COUNT(N35,N17)&lt;2,"",N35/N17*100)</f>
+        <v/>
+      </c>
+      <c r="O36" s="169">
+        <f>IF(COUNT(O35,O17)&lt;2,"",O35/O17*100)</f>
+        <v/>
+      </c>
+      <c r="P36" s="169">
+        <f>IF(COUNT(P35,P17)&lt;2,"",P35/P17*100)</f>
+        <v/>
+      </c>
+      <c r="Q36" s="169">
+        <f>IF(COUNT(Q35,Q17)&lt;2,"",Q35/Q17*100)</f>
+        <v/>
+      </c>
+      <c r="R36" s="169">
+        <f>IF(COUNT(R35,R17)&lt;2,"",R35/R17*100)</f>
+        <v/>
+      </c>
+      <c r="S36" s="169">
+        <f>IF(COUNT(S35,S17)&lt;2,"",S35/S17*100)</f>
+        <v/>
+      </c>
+      <c r="T36" s="155" t="inlineStr"/>
+      <c r="U36" s="155" t="inlineStr"/>
+      <c r="V36" s="155" t="inlineStr">
+        <is>
+          <t>Share of the fleet is not observed after December 2023</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>G28</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>macro_mining_and_quarrying</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D38" s="167" t="n">
-        <v>204.2286999662737</v>
-      </c>
-      <c r="E38" s="167" t="n">
-        <v>204.2286999662738</v>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
+      <c r="A38" s="151" t="inlineStr">
+        <is>
+          <t>5. Fuel split of the registered fleet</t>
+        </is>
+      </c>
+      <c r="B38" s="151" t="n"/>
+      <c r="C38" s="151" t="n"/>
+      <c r="D38" s="151" t="n"/>
+      <c r="E38" s="151" t="n"/>
+      <c r="F38" s="151" t="n"/>
+      <c r="G38" s="151" t="n"/>
+      <c r="H38" s="151" t="n"/>
+      <c r="I38" s="151" t="n"/>
+      <c r="J38" s="151" t="n"/>
+      <c r="K38" s="151" t="n"/>
+      <c r="L38" s="151" t="n"/>
+      <c r="M38" s="151" t="n"/>
+      <c r="N38" s="151" t="n"/>
+      <c r="O38" s="151" t="n"/>
+      <c r="P38" s="151" t="n"/>
+      <c r="Q38" s="151" t="n"/>
+      <c r="R38" s="151" t="n"/>
+      <c r="S38" s="151" t="n"/>
+      <c r="T38" s="151" t="n"/>
+      <c r="U38" s="151" t="n"/>
+      <c r="V38" s="151" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>H28</t>
-        </is>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>macro_mining_and_quarrying</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D39" s="167" t="n">
-        <v>205.1258295918731</v>
-      </c>
-      <c r="E39" s="167" t="n">
-        <v>205.1258295918731</v>
-      </c>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
+      <c r="A39" s="152" t="inlineStr">
+        <is>
+          <t>Petrol vehicles registered</t>
+        </is>
+      </c>
+      <c r="B39" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C39" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D39" s="166" t="n"/>
+      <c r="E39" s="152" t="inlineStr">
+        <is>
+          <t>All classes, December 2023.</t>
+        </is>
+      </c>
+      <c r="F39" s="166" t="n"/>
+      <c r="G39" s="166" t="n"/>
+      <c r="H39" s="166" t="n"/>
+      <c r="I39" s="166" t="n"/>
+      <c r="J39" s="166" t="n"/>
+      <c r="K39" s="166" t="n"/>
+      <c r="L39" s="166" t="n"/>
+      <c r="M39" s="166" t="n"/>
+      <c r="N39" s="166" t="n"/>
+      <c r="O39" s="166" t="n"/>
+      <c r="P39" s="166" t="n"/>
+      <c r="Q39" s="166" t="n">
+        <v>8555772</v>
+      </c>
+      <c r="R39" s="166" t="n"/>
+      <c r="S39" s="166" t="n"/>
+      <c r="T39" s="152" t="inlineStr">
+        <is>
+          <t>One date only</t>
+        </is>
+      </c>
+      <c r="U39" s="152" t="inlineStr">
+        <is>
+          <t>Department of Transport, 2023</t>
+        </is>
+      </c>
+      <c r="V39" s="152" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>I28</t>
-        </is>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>macro_mining_and_quarrying</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D40" s="167" t="n">
-        <v>205.4648860142573</v>
-      </c>
-      <c r="E40" s="167" t="n">
-        <v>205.4648860142574</v>
-      </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
+      <c r="A40" s="152" t="inlineStr">
+        <is>
+          <t>Diesel vehicles registered</t>
+        </is>
+      </c>
+      <c r="B40" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C40" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D40" s="166" t="n"/>
+      <c r="E40" s="152" t="inlineStr">
+        <is>
+          <t>All classes, December 2023.</t>
+        </is>
+      </c>
+      <c r="F40" s="166" t="n"/>
+      <c r="G40" s="166" t="n"/>
+      <c r="H40" s="166" t="n"/>
+      <c r="I40" s="166" t="n"/>
+      <c r="J40" s="166" t="n"/>
+      <c r="K40" s="166" t="n"/>
+      <c r="L40" s="166" t="n"/>
+      <c r="M40" s="166" t="n"/>
+      <c r="N40" s="166" t="n"/>
+      <c r="O40" s="166" t="n"/>
+      <c r="P40" s="166" t="n"/>
+      <c r="Q40" s="166" t="n">
+        <v>3335546</v>
+      </c>
+      <c r="R40" s="166" t="n"/>
+      <c r="S40" s="166" t="n"/>
+      <c r="T40" s="152" t="inlineStr">
+        <is>
+          <t>One date only</t>
+        </is>
+      </c>
+      <c r="U40" s="152" t="inlineStr">
+        <is>
+          <t>Department of Transport, 2023</t>
+        </is>
+      </c>
+      <c r="V40" s="152" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>F29</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>macro_construction</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D41" s="167" t="n">
-        <v>110.0650907489087</v>
-      </c>
-      <c r="E41" s="167" t="n">
-        <v>110.0650907489087</v>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
+      <c r="A41" s="152" t="inlineStr">
+        <is>
+          <t>Electric vehicles registered</t>
+        </is>
+      </c>
+      <c r="B41" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C41" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D41" s="166" t="n"/>
+      <c r="E41" s="152" t="inlineStr">
+        <is>
+          <t>All classes, December 2023.</t>
+        </is>
+      </c>
+      <c r="F41" s="166" t="n"/>
+      <c r="G41" s="166" t="n"/>
+      <c r="H41" s="166" t="n"/>
+      <c r="I41" s="166" t="n"/>
+      <c r="J41" s="166" t="n"/>
+      <c r="K41" s="166" t="n"/>
+      <c r="L41" s="166" t="n"/>
+      <c r="M41" s="166" t="n"/>
+      <c r="N41" s="166" t="n"/>
+      <c r="O41" s="166" t="n"/>
+      <c r="P41" s="166" t="n"/>
+      <c r="Q41" s="166" t="n">
+        <v>4090</v>
+      </c>
+      <c r="R41" s="166" t="n"/>
+      <c r="S41" s="166" t="n"/>
+      <c r="T41" s="152" t="inlineStr">
+        <is>
+          <t>One date only</t>
+        </is>
+      </c>
+      <c r="U41" s="152" t="inlineStr">
+        <is>
+          <t>Department of Transport, 2023</t>
+        </is>
+      </c>
+      <c r="V41" s="152" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>G29</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>macro_construction</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D42" s="167" t="n">
-        <v>109.5650907489087</v>
-      </c>
-      <c r="E42" s="167" t="n">
-        <v>109.5650907489087</v>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
+      <c r="A42" s="155" t="inlineStr">
+        <is>
+          <t>Diesel vehicles implied by the model's split</t>
+        </is>
+      </c>
+      <c r="B42" s="156" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C42" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D42" s="168" t="n"/>
+      <c r="E42" s="155" t="inlineStr">
+        <is>
+          <t>Cars x 17% plus light commercial x 70% plus trucks and buses. The model's split is for new sales; applied here to stock as a test.</t>
+        </is>
+      </c>
+      <c r="F42" s="168">
+        <f>IF(COUNT(F6,F7)&lt;2,"",F6*0.17+F7*0.7+F8+F9)</f>
+        <v/>
+      </c>
+      <c r="G42" s="168">
+        <f>IF(COUNT(G6,G7)&lt;2,"",G6*0.17+G7*0.7+G8+G9)</f>
+        <v/>
+      </c>
+      <c r="H42" s="168">
+        <f>IF(COUNT(H6,H7)&lt;2,"",H6*0.17+H7*0.7+H8+H9)</f>
+        <v/>
+      </c>
+      <c r="I42" s="168">
+        <f>IF(COUNT(I6,I7)&lt;2,"",I6*0.17+I7*0.7+I8+I9)</f>
+        <v/>
+      </c>
+      <c r="J42" s="168">
+        <f>IF(COUNT(J6,J7)&lt;2,"",J6*0.17+J7*0.7+J8+J9)</f>
+        <v/>
+      </c>
+      <c r="K42" s="168">
+        <f>IF(COUNT(K6,K7)&lt;2,"",K6*0.17+K7*0.7+K8+K9)</f>
+        <v/>
+      </c>
+      <c r="L42" s="168">
+        <f>IF(COUNT(L6,L7)&lt;2,"",L6*0.17+L7*0.7+L8+L9)</f>
+        <v/>
+      </c>
+      <c r="M42" s="168">
+        <f>IF(COUNT(M6,M7)&lt;2,"",M6*0.17+M7*0.7+M8+M9)</f>
+        <v/>
+      </c>
+      <c r="N42" s="168">
+        <f>IF(COUNT(N6,N7)&lt;2,"",N6*0.17+N7*0.7+N8+N9)</f>
+        <v/>
+      </c>
+      <c r="O42" s="168">
+        <f>IF(COUNT(O6,O7)&lt;2,"",O6*0.17+O7*0.7+O8+O9)</f>
+        <v/>
+      </c>
+      <c r="P42" s="168">
+        <f>IF(COUNT(P6,P7)&lt;2,"",P6*0.17+P7*0.7+P8+P9)</f>
+        <v/>
+      </c>
+      <c r="Q42" s="168">
+        <f>IF(COUNT(Q6,Q7)&lt;2,"",Q6*0.17+Q7*0.7+Q8+Q9)</f>
+        <v/>
+      </c>
+      <c r="R42" s="168">
+        <f>IF(COUNT(R6,R7)&lt;2,"",R6*0.17+R7*0.7+R8+R9)</f>
+        <v/>
+      </c>
+      <c r="S42" s="168">
+        <f>IF(COUNT(S6,S7)&lt;2,"",S6*0.17+S7*0.7+S8+S9)</f>
+        <v/>
+      </c>
+      <c r="T42" s="155" t="inlineStr"/>
+      <c r="U42" s="155" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml: petrol_diesel_split</t>
+        </is>
+      </c>
+      <c r="V42" s="155" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>H29</t>
-        </is>
-      </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>macro_construction</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D43" s="167" t="n">
-        <v>103.6250907489087</v>
-      </c>
-      <c r="E43" s="167" t="n">
-        <v>103.6250907489087</v>
-      </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>I29</t>
-        </is>
-      </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>macro_construction</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D44" s="167" t="n">
-        <v>99.09852067977131</v>
-      </c>
-      <c r="E44" s="167" t="n">
-        <v>99.09852067977131</v>
-      </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>macro_statssa.csv</t>
-        </is>
-      </c>
+      <c r="A43" s="155" t="inlineStr">
+        <is>
+          <t>Implied less registered diesel vehicles</t>
+        </is>
+      </c>
+      <c r="B43" s="156" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C43" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D43" s="168" t="n"/>
+      <c r="E43" s="155" t="inlineStr">
+        <is>
+          <t>Positive means the model's split puts more diesel vehicles on the road than are registered. Minibuses and motorcycles are left out of the implied figure.</t>
+        </is>
+      </c>
+      <c r="F43" s="168">
+        <f>IF(COUNT(F42,F40)&lt;2,"",F42-F40)</f>
+        <v/>
+      </c>
+      <c r="G43" s="168">
+        <f>IF(COUNT(G42,G40)&lt;2,"",G42-G40)</f>
+        <v/>
+      </c>
+      <c r="H43" s="168">
+        <f>IF(COUNT(H42,H40)&lt;2,"",H42-H40)</f>
+        <v/>
+      </c>
+      <c r="I43" s="168">
+        <f>IF(COUNT(I42,I40)&lt;2,"",I42-I40)</f>
+        <v/>
+      </c>
+      <c r="J43" s="168">
+        <f>IF(COUNT(J42,J40)&lt;2,"",J42-J40)</f>
+        <v/>
+      </c>
+      <c r="K43" s="168">
+        <f>IF(COUNT(K42,K40)&lt;2,"",K42-K40)</f>
+        <v/>
+      </c>
+      <c r="L43" s="168">
+        <f>IF(COUNT(L42,L40)&lt;2,"",L42-L40)</f>
+        <v/>
+      </c>
+      <c r="M43" s="168">
+        <f>IF(COUNT(M42,M40)&lt;2,"",M42-M40)</f>
+        <v/>
+      </c>
+      <c r="N43" s="168">
+        <f>IF(COUNT(N42,N40)&lt;2,"",N42-N40)</f>
+        <v/>
+      </c>
+      <c r="O43" s="168">
+        <f>IF(COUNT(O42,O40)&lt;2,"",O42-O40)</f>
+        <v/>
+      </c>
+      <c r="P43" s="168">
+        <f>IF(COUNT(P42,P40)&lt;2,"",P42-P40)</f>
+        <v/>
+      </c>
+      <c r="Q43" s="168">
+        <f>IF(COUNT(Q42,Q40)&lt;2,"",Q42-Q40)</f>
+        <v/>
+      </c>
+      <c r="R43" s="168">
+        <f>IF(COUNT(R42,R40)&lt;2,"",R42-R40)</f>
+        <v/>
+      </c>
+      <c r="S43" s="168">
+        <f>IF(COUNT(S42,S40)&lt;2,"",S42-S40)</f>
+        <v/>
+      </c>
+      <c r="T43" s="155" t="inlineStr"/>
+      <c r="U43" s="155" t="inlineStr"/>
+      <c r="V43" s="155" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>F30</t>
-        </is>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>manufacturing_volume_total</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D45" s="167" t="n">
-        <v>93.14166666666667</v>
-      </c>
-      <c r="E45" s="167" t="n">
-        <v>93.14166666666667</v>
-      </c>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>activity_statssa_monthly.csv</t>
-        </is>
-      </c>
+      <c r="A45" s="151" t="inlineStr">
+        <is>
+          <t>6. Distance and fuel use: model settings beside the published study</t>
+        </is>
+      </c>
+      <c r="B45" s="151" t="n"/>
+      <c r="C45" s="151" t="n"/>
+      <c r="D45" s="151" t="n"/>
+      <c r="E45" s="151" t="n"/>
+      <c r="F45" s="151" t="n"/>
+      <c r="G45" s="151" t="n"/>
+      <c r="H45" s="151" t="n"/>
+      <c r="I45" s="151" t="n"/>
+      <c r="J45" s="151" t="n"/>
+      <c r="K45" s="151" t="n"/>
+      <c r="L45" s="151" t="n"/>
+      <c r="M45" s="151" t="n"/>
+      <c r="N45" s="151" t="n"/>
+      <c r="O45" s="151" t="n"/>
+      <c r="P45" s="151" t="n"/>
+      <c r="Q45" s="151" t="n"/>
+      <c r="R45" s="151" t="n"/>
+      <c r="S45" s="151" t="n"/>
+      <c r="T45" s="151" t="n"/>
+      <c r="U45" s="151" t="n"/>
+      <c r="V45" s="151" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>G30</t>
-        </is>
-      </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>manufacturing_volume_total</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D46" s="167" t="n">
-        <v>93.71666666666665</v>
-      </c>
-      <c r="E46" s="167" t="n">
-        <v>93.71666666666665</v>
-      </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>activity_statssa_monthly.csv</t>
+      <c r="A46" s="158" t="inlineStr">
+        <is>
+          <t>Passenger cars, distance</t>
+        </is>
+      </c>
+      <c r="B46" s="159" t="inlineStr">
+        <is>
+          <t>km/vehicle/year</t>
+        </is>
+      </c>
+      <c r="C46" s="159" t="inlineStr">
+        <is>
+          <t>Model setting</t>
+        </is>
+      </c>
+      <c r="D46" s="160" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E46" s="158" t="inlineStr">
+        <is>
+          <t>Column D is the model's value. The study gives 14,457.0 for CarGasoline (fleet average, 2014 base).</t>
+        </is>
+      </c>
+      <c r="F46" s="160" t="n"/>
+      <c r="G46" s="160" t="n"/>
+      <c r="H46" s="160" t="n"/>
+      <c r="I46" s="160" t="n"/>
+      <c r="J46" s="160" t="n"/>
+      <c r="K46" s="160" t="n"/>
+      <c r="L46" s="160" t="n"/>
+      <c r="M46" s="160" t="n"/>
+      <c r="N46" s="160" t="n"/>
+      <c r="O46" s="160" t="n"/>
+      <c r="P46" s="160" t="n"/>
+      <c r="Q46" s="160" t="n"/>
+      <c r="R46" s="160" t="n"/>
+      <c r="S46" s="160" t="n"/>
+      <c r="T46" s="158" t="inlineStr">
+        <is>
+          <t>Model value is a placeholder with no source</t>
+        </is>
+      </c>
+      <c r="U46" s="158" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
+        </is>
+      </c>
+      <c r="V46" s="158" t="inlineStr">
+        <is>
+          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>H30</t>
-        </is>
-      </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>manufacturing_volume_total</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D47" s="167" t="n">
-        <v>93.33333333333333</v>
-      </c>
-      <c r="E47" s="167" t="n">
-        <v>93.33333333333333</v>
-      </c>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>activity_statssa_monthly.csv</t>
+      <c r="A47" s="158" t="inlineStr">
+        <is>
+          <t>Light commercial, distance</t>
+        </is>
+      </c>
+      <c r="B47" s="159" t="inlineStr">
+        <is>
+          <t>km/vehicle/year</t>
+        </is>
+      </c>
+      <c r="C47" s="159" t="inlineStr">
+        <is>
+          <t>Model setting</t>
+        </is>
+      </c>
+      <c r="D47" s="160" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E47" s="158" t="inlineStr">
+        <is>
+          <t>Column D is the model's value. The study gives 20,397.0 for LCVDiesel (fleet average, 2014 base).</t>
+        </is>
+      </c>
+      <c r="F47" s="160" t="n"/>
+      <c r="G47" s="160" t="n"/>
+      <c r="H47" s="160" t="n"/>
+      <c r="I47" s="160" t="n"/>
+      <c r="J47" s="160" t="n"/>
+      <c r="K47" s="160" t="n"/>
+      <c r="L47" s="160" t="n"/>
+      <c r="M47" s="160" t="n"/>
+      <c r="N47" s="160" t="n"/>
+      <c r="O47" s="160" t="n"/>
+      <c r="P47" s="160" t="n"/>
+      <c r="Q47" s="160" t="n"/>
+      <c r="R47" s="160" t="n"/>
+      <c r="S47" s="160" t="n"/>
+      <c r="T47" s="158" t="inlineStr">
+        <is>
+          <t>Model value is a placeholder with no source</t>
+        </is>
+      </c>
+      <c r="U47" s="158" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
+        </is>
+      </c>
+      <c r="V47" s="158" t="inlineStr">
+        <is>
+          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>I30</t>
-        </is>
-      </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>manufacturing_volume_total</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D48" s="167" t="n">
-        <v>92.14166666666665</v>
-      </c>
-      <c r="E48" s="167" t="n">
-        <v>92.14166666666667</v>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>activity_statssa_monthly.csv</t>
+      <c r="A48" s="158" t="inlineStr">
+        <is>
+          <t>Heavy commercial, distance</t>
+        </is>
+      </c>
+      <c r="B48" s="159" t="inlineStr">
+        <is>
+          <t>km/vehicle/year</t>
+        </is>
+      </c>
+      <c r="C48" s="159" t="inlineStr">
+        <is>
+          <t>Model setting</t>
+        </is>
+      </c>
+      <c r="D48" s="160" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E48" s="158" t="inlineStr">
+        <is>
+          <t>Column D is the model's value. The study gives 62,461.0 for HCV5Diesel (fleet average, 2014 base).</t>
+        </is>
+      </c>
+      <c r="F48" s="160" t="n"/>
+      <c r="G48" s="160" t="n"/>
+      <c r="H48" s="160" t="n"/>
+      <c r="I48" s="160" t="n"/>
+      <c r="J48" s="160" t="n"/>
+      <c r="K48" s="160" t="n"/>
+      <c r="L48" s="160" t="n"/>
+      <c r="M48" s="160" t="n"/>
+      <c r="N48" s="160" t="n"/>
+      <c r="O48" s="160" t="n"/>
+      <c r="P48" s="160" t="n"/>
+      <c r="Q48" s="160" t="n"/>
+      <c r="R48" s="160" t="n"/>
+      <c r="S48" s="160" t="n"/>
+      <c r="T48" s="158" t="inlineStr">
+        <is>
+          <t>Model value is a placeholder with no source</t>
+        </is>
+      </c>
+      <c r="U48" s="158" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
+        </is>
+      </c>
+      <c r="V48" s="158" t="inlineStr">
+        <is>
+          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>F31</t>
-        </is>
-      </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>mining_volume_total</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D49" s="167" t="n">
-        <v>93.00833333333334</v>
-      </c>
-      <c r="E49" s="167" t="n">
-        <v>93.00833333333333</v>
-      </c>
-      <c r="F49" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>activity_statssa_monthly.csv</t>
+      <c r="A49" s="158" t="inlineStr">
+        <is>
+          <t>Petrol cars, fuel use</t>
+        </is>
+      </c>
+      <c r="B49" s="159" t="inlineStr">
+        <is>
+          <t>L/100 km</t>
+        </is>
+      </c>
+      <c r="C49" s="159" t="inlineStr">
+        <is>
+          <t>Model setting</t>
+        </is>
+      </c>
+      <c r="D49" s="160" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E49" s="158" t="inlineStr">
+        <is>
+          <t>Column D is the model's value. The study gives 8.2 for CarGasoline (fleet average, 2014 base).</t>
+        </is>
+      </c>
+      <c r="F49" s="160" t="n"/>
+      <c r="G49" s="160" t="n"/>
+      <c r="H49" s="160" t="n"/>
+      <c r="I49" s="160" t="n"/>
+      <c r="J49" s="160" t="n"/>
+      <c r="K49" s="160" t="n"/>
+      <c r="L49" s="160" t="n"/>
+      <c r="M49" s="160" t="n"/>
+      <c r="N49" s="160" t="n"/>
+      <c r="O49" s="160" t="n"/>
+      <c r="P49" s="160" t="n"/>
+      <c r="Q49" s="160" t="n"/>
+      <c r="R49" s="160" t="n"/>
+      <c r="S49" s="160" t="n"/>
+      <c r="T49" s="158" t="inlineStr">
+        <is>
+          <t>Model value is a placeholder with no source</t>
+        </is>
+      </c>
+      <c r="U49" s="158" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
+        </is>
+      </c>
+      <c r="V49" s="158" t="inlineStr">
+        <is>
+          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>G31</t>
-        </is>
-      </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>mining_volume_total</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D50" s="167" t="n">
-        <v>93.01666666666667</v>
-      </c>
-      <c r="E50" s="167" t="n">
-        <v>93.01666666666667</v>
-      </c>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>activity_statssa_monthly.csv</t>
+      <c r="A50" s="158" t="inlineStr">
+        <is>
+          <t>Diesel light commercial, fuel use</t>
+        </is>
+      </c>
+      <c r="B50" s="159" t="inlineStr">
+        <is>
+          <t>L/100 km</t>
+        </is>
+      </c>
+      <c r="C50" s="159" t="inlineStr">
+        <is>
+          <t>Model setting</t>
+        </is>
+      </c>
+      <c r="D50" s="160" t="n">
+        <v>9</v>
+      </c>
+      <c r="E50" s="158" t="inlineStr">
+        <is>
+          <t>Column D is the model's value. The study gives 12.4 for LCVDiesel (fleet average, 2014 base).</t>
+        </is>
+      </c>
+      <c r="F50" s="160" t="n"/>
+      <c r="G50" s="160" t="n"/>
+      <c r="H50" s="160" t="n"/>
+      <c r="I50" s="160" t="n"/>
+      <c r="J50" s="160" t="n"/>
+      <c r="K50" s="160" t="n"/>
+      <c r="L50" s="160" t="n"/>
+      <c r="M50" s="160" t="n"/>
+      <c r="N50" s="160" t="n"/>
+      <c r="O50" s="160" t="n"/>
+      <c r="P50" s="160" t="n"/>
+      <c r="Q50" s="160" t="n"/>
+      <c r="R50" s="160" t="n"/>
+      <c r="S50" s="160" t="n"/>
+      <c r="T50" s="158" t="inlineStr">
+        <is>
+          <t>Model value is a placeholder with no source</t>
+        </is>
+      </c>
+      <c r="U50" s="158" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
+        </is>
+      </c>
+      <c r="V50" s="158" t="inlineStr">
+        <is>
+          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>H31</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>mining_volume_total</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D51" s="167" t="n">
-        <v>93.53333333333332</v>
-      </c>
-      <c r="E51" s="167" t="n">
-        <v>93.53333333333335</v>
-      </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>activity_statssa_monthly.csv</t>
+      <c r="A51" s="158" t="inlineStr">
+        <is>
+          <t>Heavy commercial, fuel use</t>
+        </is>
+      </c>
+      <c r="B51" s="159" t="inlineStr">
+        <is>
+          <t>L/100 km</t>
+        </is>
+      </c>
+      <c r="C51" s="159" t="inlineStr">
+        <is>
+          <t>Model setting</t>
+        </is>
+      </c>
+      <c r="D51" s="160" t="n">
+        <v>35</v>
+      </c>
+      <c r="E51" s="158" t="inlineStr">
+        <is>
+          <t>Column D is the model's value. The study gives 31.2 for HCV5Diesel (fleet average, 2014 base).</t>
+        </is>
+      </c>
+      <c r="F51" s="160" t="n"/>
+      <c r="G51" s="160" t="n"/>
+      <c r="H51" s="160" t="n"/>
+      <c r="I51" s="160" t="n"/>
+      <c r="J51" s="160" t="n"/>
+      <c r="K51" s="160" t="n"/>
+      <c r="L51" s="160" t="n"/>
+      <c r="M51" s="160" t="n"/>
+      <c r="N51" s="160" t="n"/>
+      <c r="O51" s="160" t="n"/>
+      <c r="P51" s="160" t="n"/>
+      <c r="Q51" s="160" t="n"/>
+      <c r="R51" s="160" t="n"/>
+      <c r="S51" s="160" t="n"/>
+      <c r="T51" s="158" t="inlineStr">
+        <is>
+          <t>Model value is a placeholder with no source</t>
+        </is>
+      </c>
+      <c r="U51" s="158" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
+        </is>
+      </c>
+      <c r="V51" s="158" t="inlineStr">
+        <is>
+          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>I31</t>
-        </is>
-      </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>mining_volume_total</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D52" s="167" t="n">
-        <v>93.70833333333333</v>
-      </c>
-      <c r="E52" s="167" t="n">
-        <v>93.70833333333333</v>
-      </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>activity_statssa_monthly.csv</t>
-        </is>
-      </c>
+      <c r="A52" s="155" t="inlineStr">
+        <is>
+          <t>Petrol sold per registered petrol vehicle</t>
+        </is>
+      </c>
+      <c r="B52" s="156" t="inlineStr">
+        <is>
+          <t>litres/vehicle/year</t>
+        </is>
+      </c>
+      <c r="C52" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D52" s="168" t="n"/>
+      <c r="E52" s="155" t="inlineStr">
+        <is>
+          <t>National petrol sales used (History) divided by registered petrol vehicles.</t>
+        </is>
+      </c>
+      <c r="F52" s="168">
+        <f>IF(COUNT(History!F57,F39)&lt;2,"",History!F57*1000000/F39)</f>
+        <v/>
+      </c>
+      <c r="G52" s="168">
+        <f>IF(COUNT(History!G57,G39)&lt;2,"",History!G57*1000000/G39)</f>
+        <v/>
+      </c>
+      <c r="H52" s="168">
+        <f>IF(COUNT(History!H57,H39)&lt;2,"",History!H57*1000000/H39)</f>
+        <v/>
+      </c>
+      <c r="I52" s="168">
+        <f>IF(COUNT(History!I57,I39)&lt;2,"",History!I57*1000000/I39)</f>
+        <v/>
+      </c>
+      <c r="J52" s="168">
+        <f>IF(COUNT(History!J57,J39)&lt;2,"",History!J57*1000000/J39)</f>
+        <v/>
+      </c>
+      <c r="K52" s="168">
+        <f>IF(COUNT(History!K57,K39)&lt;2,"",History!K57*1000000/K39)</f>
+        <v/>
+      </c>
+      <c r="L52" s="168">
+        <f>IF(COUNT(History!L57,L39)&lt;2,"",History!L57*1000000/L39)</f>
+        <v/>
+      </c>
+      <c r="M52" s="168">
+        <f>IF(COUNT(History!M57,M39)&lt;2,"",History!M57*1000000/M39)</f>
+        <v/>
+      </c>
+      <c r="N52" s="168">
+        <f>IF(COUNT(History!N57,N39)&lt;2,"",History!N57*1000000/N39)</f>
+        <v/>
+      </c>
+      <c r="O52" s="168">
+        <f>IF(COUNT(History!O57,O39)&lt;2,"",History!O57*1000000/O39)</f>
+        <v/>
+      </c>
+      <c r="P52" s="168">
+        <f>IF(COUNT(History!P57,P39)&lt;2,"",History!P57*1000000/P39)</f>
+        <v/>
+      </c>
+      <c r="Q52" s="168">
+        <f>IF(COUNT(History!Q57,Q39)&lt;2,"",History!Q57*1000000/Q39)</f>
+        <v/>
+      </c>
+      <c r="R52" s="168">
+        <f>IF(COUNT(History!R57,R39)&lt;2,"",History!R57*1000000/R39)</f>
+        <v/>
+      </c>
+      <c r="S52" s="168">
+        <f>IF(COUNT(History!S57,S39)&lt;2,"",History!S57*1000000/S39)</f>
+        <v/>
+      </c>
+      <c r="T52" s="155" t="inlineStr"/>
+      <c r="U52" s="155" t="inlineStr"/>
+      <c r="V52" s="155" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>F43</t>
-        </is>
-      </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: EC petrol / million L/year</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D53" s="167" t="n">
-        <v>703.1324447169991</v>
-      </c>
-      <c r="E53" s="167" t="n">
-        <v>703.132444716999</v>
-      </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>F44</t>
-        </is>
-      </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: FS petrol / million L/year</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D54" s="167" t="n">
-        <v>587.4580081820001</v>
-      </c>
-      <c r="E54" s="167" t="n">
-        <v>587.4580081820001</v>
-      </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
+      <c r="A53" s="155" t="inlineStr">
+        <is>
+          <t>Distance implied by petrol sales</t>
+        </is>
+      </c>
+      <c r="B53" s="156" t="inlineStr">
+        <is>
+          <t>km/vehicle/year</t>
+        </is>
+      </c>
+      <c r="C53" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D53" s="168" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E53" s="155" t="inlineStr">
+        <is>
+          <t>Litres per vehicle divided by 8.2 L/100 km (the study's petrol car average). Column D is the model's passenger distance.</t>
+        </is>
+      </c>
+      <c r="F53" s="168">
+        <f>IF(ISNUMBER(F52),F52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="168">
+        <f>IF(ISNUMBER(G52),G52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="168">
+        <f>IF(ISNUMBER(H52),H52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="I53" s="168">
+        <f>IF(ISNUMBER(I52),I52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="J53" s="168">
+        <f>IF(ISNUMBER(J52),J52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="K53" s="168">
+        <f>IF(ISNUMBER(K52),K52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="L53" s="168">
+        <f>IF(ISNUMBER(L52),L52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="M53" s="168">
+        <f>IF(ISNUMBER(M52),M52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="N53" s="168">
+        <f>IF(ISNUMBER(N52),N52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="O53" s="168">
+        <f>IF(ISNUMBER(O52),O52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="P53" s="168">
+        <f>IF(ISNUMBER(P52),P52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="Q53" s="168">
+        <f>IF(ISNUMBER(Q52),Q52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="R53" s="168">
+        <f>IF(ISNUMBER(R52),R52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="S53" s="168">
+        <f>IF(ISNUMBER(S52),S52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="T53" s="155" t="inlineStr"/>
+      <c r="U53" s="155" t="inlineStr"/>
+      <c r="V53" s="155" t="inlineStr">
+        <is>
+          <t>If the model's distance and fuel use both held, petrol sales would be far above what is recorded</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>F45</t>
-        </is>
-      </c>
-      <c r="B55" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: GP petrol / million L/year</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D55" s="167" t="n">
-        <v>3530.440256933996</v>
-      </c>
-      <c r="E55" s="167" t="n">
-        <v>3530.440256933996</v>
-      </c>
-      <c r="F55" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G55" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
-        </is>
-      </c>
+      <c r="A55" s="151" t="inlineStr">
+        <is>
+          <t>7. Not available from any source held</t>
+        </is>
+      </c>
+      <c r="B55" s="151" t="n"/>
+      <c r="C55" s="151" t="n"/>
+      <c r="D55" s="151" t="n"/>
+      <c r="E55" s="151" t="n"/>
+      <c r="F55" s="151" t="n"/>
+      <c r="G55" s="151" t="n"/>
+      <c r="H55" s="151" t="n"/>
+      <c r="I55" s="151" t="n"/>
+      <c r="J55" s="151" t="n"/>
+      <c r="K55" s="151" t="n"/>
+      <c r="L55" s="151" t="n"/>
+      <c r="M55" s="151" t="n"/>
+      <c r="N55" s="151" t="n"/>
+      <c r="O55" s="151" t="n"/>
+      <c r="P55" s="151" t="n"/>
+      <c r="Q55" s="151" t="n"/>
+      <c r="R55" s="151" t="n"/>
+      <c r="S55" s="151" t="n"/>
+      <c r="T55" s="151" t="n"/>
+      <c r="U55" s="151" t="n"/>
+      <c r="V55" s="151" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>F46</t>
-        </is>
-      </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: KZN petrol / million L/year</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D56" s="167" t="n">
-        <v>1498.937893394999</v>
-      </c>
-      <c r="E56" s="167" t="n">
-        <v>1498.937893394999</v>
-      </c>
-      <c r="F56" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G56" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
+      <c r="A56" s="161" t="inlineStr">
+        <is>
+          <t>Stock by age (year of first registration)</t>
+        </is>
+      </c>
+      <c r="B56" s="162" t="inlineStr"/>
+      <c r="C56" s="162" t="inlineStr">
+        <is>
+          <t>Missing input</t>
+        </is>
+      </c>
+      <c r="D56" s="164" t="n"/>
+      <c r="E56" s="161" t="inlineStr">
+        <is>
+          <t>Needed for the cohort calculation; NaTIS publishes totals by class only.</t>
+        </is>
+      </c>
+      <c r="F56" s="164" t="n"/>
+      <c r="G56" s="164" t="n"/>
+      <c r="H56" s="164" t="n"/>
+      <c r="I56" s="164" t="n"/>
+      <c r="J56" s="164" t="n"/>
+      <c r="K56" s="164" t="n"/>
+      <c r="L56" s="164" t="n"/>
+      <c r="M56" s="164" t="n"/>
+      <c r="N56" s="164" t="n"/>
+      <c r="O56" s="164" t="n"/>
+      <c r="P56" s="164" t="n"/>
+      <c r="Q56" s="164" t="n"/>
+      <c r="R56" s="164" t="n"/>
+      <c r="S56" s="164" t="n"/>
+      <c r="T56" s="161" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="U56" s="161" t="inlineStr"/>
+      <c r="V56" s="161" t="inlineStr">
+        <is>
+          <t>Source to be found or assumption agreed</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>F47</t>
-        </is>
-      </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: LP petrol / million L/year</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D57" s="167" t="n">
-        <v>273.644045045999</v>
-      </c>
-      <c r="E57" s="167" t="n">
-        <v>273.644045045999</v>
-      </c>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
+      <c r="A57" s="161" t="inlineStr">
+        <is>
+          <t>Stock by fuel within each class</t>
+        </is>
+      </c>
+      <c r="B57" s="162" t="inlineStr"/>
+      <c r="C57" s="162" t="inlineStr">
+        <is>
+          <t>Missing input</t>
+        </is>
+      </c>
+      <c r="D57" s="164" t="n"/>
+      <c r="E57" s="161" t="inlineStr">
+        <is>
+          <t>Only an all-class fuel count exists, for December 2023.</t>
+        </is>
+      </c>
+      <c r="F57" s="164" t="n"/>
+      <c r="G57" s="164" t="n"/>
+      <c r="H57" s="164" t="n"/>
+      <c r="I57" s="164" t="n"/>
+      <c r="J57" s="164" t="n"/>
+      <c r="K57" s="164" t="n"/>
+      <c r="L57" s="164" t="n"/>
+      <c r="M57" s="164" t="n"/>
+      <c r="N57" s="164" t="n"/>
+      <c r="O57" s="164" t="n"/>
+      <c r="P57" s="164" t="n"/>
+      <c r="Q57" s="164" t="n"/>
+      <c r="R57" s="164" t="n"/>
+      <c r="S57" s="164" t="n"/>
+      <c r="T57" s="161" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="U57" s="161" t="inlineStr"/>
+      <c r="V57" s="161" t="inlineStr">
+        <is>
+          <t>Source to be found or assumption agreed</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>F48</t>
-        </is>
-      </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: MP petrol / million L/year</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D58" s="167" t="n">
-        <v>612.2656460789989</v>
-      </c>
-      <c r="E58" s="167" t="n">
-        <v>612.2656460789989</v>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
+      <c r="A58" s="161" t="inlineStr">
+        <is>
+          <t>Electric and hybrid vehicles in the fleet by year</t>
+        </is>
+      </c>
+      <c r="B58" s="162" t="inlineStr"/>
+      <c r="C58" s="162" t="inlineStr">
+        <is>
+          <t>Missing input</t>
+        </is>
+      </c>
+      <c r="D58" s="164" t="n"/>
+      <c r="E58" s="161" t="inlineStr">
+        <is>
+          <t>Sales are known from 2019; stock only for December 2023.</t>
+        </is>
+      </c>
+      <c r="F58" s="164" t="n"/>
+      <c r="G58" s="164" t="n"/>
+      <c r="H58" s="164" t="n"/>
+      <c r="I58" s="164" t="n"/>
+      <c r="J58" s="164" t="n"/>
+      <c r="K58" s="164" t="n"/>
+      <c r="L58" s="164" t="n"/>
+      <c r="M58" s="164" t="n"/>
+      <c r="N58" s="164" t="n"/>
+      <c r="O58" s="164" t="n"/>
+      <c r="P58" s="164" t="n"/>
+      <c r="Q58" s="164" t="n"/>
+      <c r="R58" s="164" t="n"/>
+      <c r="S58" s="164" t="n"/>
+      <c r="T58" s="161" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="U58" s="161" t="inlineStr"/>
+      <c r="V58" s="161" t="inlineStr">
+        <is>
+          <t>Source to be found or assumption agreed</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>F49</t>
-        </is>
-      </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: NC petrol / million L/year</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D59" s="167" t="n">
-        <v>99.82992901300001</v>
-      </c>
-      <c r="E59" s="167" t="n">
-        <v>99.829929013</v>
-      </c>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
+      <c r="A59" s="161" t="inlineStr">
+        <is>
+          <t>Distance driven after 2014</t>
+        </is>
+      </c>
+      <c r="B59" s="162" t="inlineStr"/>
+      <c r="C59" s="162" t="inlineStr">
+        <is>
+          <t>Missing input</t>
+        </is>
+      </c>
+      <c r="D59" s="164" t="n"/>
+      <c r="E59" s="161" t="inlineStr">
+        <is>
+          <t>The study's figures are a 2014 base; no later survey is held.</t>
+        </is>
+      </c>
+      <c r="F59" s="164" t="n"/>
+      <c r="G59" s="164" t="n"/>
+      <c r="H59" s="164" t="n"/>
+      <c r="I59" s="164" t="n"/>
+      <c r="J59" s="164" t="n"/>
+      <c r="K59" s="164" t="n"/>
+      <c r="L59" s="164" t="n"/>
+      <c r="M59" s="164" t="n"/>
+      <c r="N59" s="164" t="n"/>
+      <c r="O59" s="164" t="n"/>
+      <c r="P59" s="164" t="n"/>
+      <c r="Q59" s="164" t="n"/>
+      <c r="R59" s="164" t="n"/>
+      <c r="S59" s="164" t="n"/>
+      <c r="T59" s="161" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="U59" s="161" t="inlineStr"/>
+      <c r="V59" s="161" t="inlineStr">
+        <is>
+          <t>Source to be found or assumption agreed</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>F50</t>
-        </is>
-      </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: NW petrol / million L/year</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D60" s="167" t="n">
-        <v>448.1562321239999</v>
-      </c>
-      <c r="E60" s="167" t="n">
-        <v>448.1562321239999</v>
-      </c>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>F51</t>
-        </is>
-      </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: WC petrol / million L/year</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D61" s="167" t="n">
-        <v>1431.005460082997</v>
-      </c>
-      <c r="E61" s="167" t="n">
-        <v>1431.005460082997</v>
-      </c>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>F52</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: EC diesel / million L/year</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D62" s="167" t="n">
-        <v>1032.35218272</v>
-      </c>
-      <c r="E62" s="167" t="n">
-        <v>1032.35218272</v>
-      </c>
-      <c r="F62" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>F53</t>
-        </is>
-      </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: FS diesel / million L/year</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D63" s="167" t="n">
-        <v>781.8611598310002</v>
-      </c>
-      <c r="E63" s="167" t="n">
-        <v>781.8611598310002</v>
-      </c>
-      <c r="F63" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>F54</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: GP diesel / million L/year</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D64" s="167" t="n">
-        <v>3278.990501961999</v>
-      </c>
-      <c r="E64" s="167" t="n">
-        <v>3278.990501961999</v>
-      </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>F55</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: KZN diesel / million L/year</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D65" s="167" t="n">
-        <v>2785.554802503</v>
-      </c>
-      <c r="E65" s="167" t="n">
-        <v>2785.554802503</v>
-      </c>
-      <c r="F65" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G65" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>F56</t>
-        </is>
-      </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: LP diesel / million L/year</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D66" s="167" t="n">
-        <v>221.987440248</v>
-      </c>
-      <c r="E66" s="167" t="n">
-        <v>221.987440248</v>
-      </c>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr">
-        <is>
-          <t>F57</t>
-        </is>
-      </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: MP diesel / million L/year</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D67" s="167" t="n">
-        <v>1144.924075864997</v>
-      </c>
-      <c r="E67" s="167" t="n">
-        <v>1144.924075864997</v>
-      </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>F58</t>
-        </is>
-      </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: NC diesel / million L/year</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D68" s="167" t="n">
-        <v>351.9801199100001</v>
-      </c>
-      <c r="E68" s="167" t="n">
-        <v>351.9801199100001</v>
-      </c>
-      <c r="F68" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr">
-        <is>
-          <t>F59</t>
-        </is>
-      </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: NW diesel / million L/year</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D69" s="167" t="n">
-        <v>619.906488913</v>
-      </c>
-      <c r="E69" s="167" t="n">
-        <v>619.906488913</v>
-      </c>
-      <c r="F69" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G69" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="inlineStr">
-        <is>
-          <t>F60</t>
-        </is>
-      </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>Provincial: WC diesel / million L/year</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D70" s="167" t="n">
-        <v>2499.769547067</v>
-      </c>
-      <c r="E70" s="167" t="n">
-        <v>2499.769547067</v>
-      </c>
-      <c r="F70" s="1" t="inlineStr">
-        <is>
-          <t>matches</t>
-        </is>
-      </c>
-      <c r="G70" s="1" t="inlineStr">
-        <is>
-          <t>fuel_sales_department_by_province.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="inlineStr">
-        <is>
-          <t>66 values recomputed; 0 differ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr">
-        <is>
-          <t>Not recomputed: vehicle sales and stock, electric vehicle sales, freight, power and airport rows (vehicle block is next), and every 'Model run' row, which is a frozen engine run on main.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="inlineStr">
-        <is>
-          <t>The model run in this workbook was made on main, where industry starts at 2.5 bn litres and agriculture at 0.7 (2024). manish-branch proposes 1.50 and 1.06 (2021 energy balance); see sector_baselines_2026-10-07.md.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr">
-        <is>
-          <t>Changes made in this copy:</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>Source selection!E5: petrol 2022 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>Source selection!E6: petrol 2023 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr">
-        <is>
-          <t>Source selection!E10: diesel 2022 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr">
-        <is>
-          <t>Source selection!E11: diesel 2023 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr">
-        <is>
-          <t>Source selection!E15: jet 2022 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="inlineStr">
-        <is>
-          <t>Source selection!E16: jet 2023 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="inlineStr">
-        <is>
-          <t>Source selection!E20: fuel_oil 2022 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="inlineStr">
-        <is>
-          <t>Source selection!E21: fuel_oil 2023 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="inlineStr">
-        <is>
-          <t>Source selection: 2024 left on FIASA, which is unverified; the department has published no 2024 figure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr">
-        <is>
-          <t>Sheets added: History, Sector history, Checks, History sources. No other cell changed.</t>
+      <c r="A60" s="161" t="inlineStr">
+        <is>
+          <t>Petrol and diesel split of new sales by segment</t>
+        </is>
+      </c>
+      <c r="B60" s="162" t="inlineStr"/>
+      <c r="C60" s="162" t="inlineStr">
+        <is>
+          <t>Missing input</t>
+        </is>
+      </c>
+      <c r="D60" s="164" t="n"/>
+      <c r="E60" s="161" t="inlineStr">
+        <is>
+          <t>naamsa reports drivetrain for the total market only.</t>
+        </is>
+      </c>
+      <c r="F60" s="164" t="n"/>
+      <c r="G60" s="164" t="n"/>
+      <c r="H60" s="164" t="n"/>
+      <c r="I60" s="164" t="n"/>
+      <c r="J60" s="164" t="n"/>
+      <c r="K60" s="164" t="n"/>
+      <c r="L60" s="164" t="n"/>
+      <c r="M60" s="164" t="n"/>
+      <c r="N60" s="164" t="n"/>
+      <c r="O60" s="164" t="n"/>
+      <c r="P60" s="164" t="n"/>
+      <c r="Q60" s="164" t="n"/>
+      <c r="R60" s="164" t="n"/>
+      <c r="S60" s="164" t="n"/>
+      <c r="T60" s="161" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="U60" s="161" t="inlineStr"/>
+      <c r="V60" s="161" t="inlineStr">
+        <is>
+          <t>Source to be found or assumption agreed</t>
         </is>
       </c>
     </row>
@@ -49430,6 +50465,2224 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="149" t="inlineStr">
+        <is>
+          <t>Checks on the workshop workbook, 7 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Each Evidence row that can be traced to a registered input is recomputed from that input. Differences above 0.05% are listed as 'differs'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="170" t="inlineStr">
+        <is>
+          <t>Evidence row</t>
+        </is>
+      </c>
+      <c r="B4" s="170" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="C4" s="170" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="D4" s="170" t="inlineStr">
+        <is>
+          <t>Workbook value</t>
+        </is>
+      </c>
+      <c r="E4" s="170" t="inlineStr">
+        <is>
+          <t>Recomputed from inputs</t>
+        </is>
+      </c>
+      <c r="F4" s="170" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="G4" s="170" t="inlineStr">
+        <is>
+          <t>Input file</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>sales_petrol</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D5" s="171" t="n">
+        <v>9185</v>
+      </c>
+      <c r="E5" s="171" t="n">
+        <v>9185</v>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_fiasa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>sales_petrol</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D6" s="171" t="n">
+        <v>9037</v>
+      </c>
+      <c r="E6" s="171" t="n">
+        <v>9037</v>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_fiasa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>sales_petrol</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D7" s="171" t="n">
+        <v>9029</v>
+      </c>
+      <c r="E7" s="171" t="n">
+        <v>9029</v>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_fiasa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>dept_petrol</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D8" s="171" t="n">
+        <v>9184.869915572999</v>
+      </c>
+      <c r="E8" s="171" t="n">
+        <v>9184.869915572999</v>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>dept_petrol</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="171" t="n">
+        <v>9036.950113492001</v>
+      </c>
+      <c r="E9" s="171" t="n">
+        <v>9036.950113492001</v>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>sales_diesel</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D10" s="171" t="n">
+        <v>12717</v>
+      </c>
+      <c r="E10" s="171" t="n">
+        <v>12717</v>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_fiasa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>sales_diesel</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D11" s="171" t="n">
+        <v>12907</v>
+      </c>
+      <c r="E11" s="171" t="n">
+        <v>12907</v>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_fiasa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>sales_diesel</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D12" s="171" t="n">
+        <v>11734</v>
+      </c>
+      <c r="E12" s="171" t="n">
+        <v>11734</v>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_fiasa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>F8</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>dept_diesel</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D13" s="171" t="n">
+        <v>12717.326319019</v>
+      </c>
+      <c r="E13" s="171" t="n">
+        <v>12717.326319019</v>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>dept_diesel</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D14" s="171" t="n">
+        <v>12907.499965808</v>
+      </c>
+      <c r="E14" s="171" t="n">
+        <v>12907.499965808</v>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>F9</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>sales_jet</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D15" s="171" t="n">
+        <v>1478</v>
+      </c>
+      <c r="E15" s="171" t="n">
+        <v>1478</v>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_fiasa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>sales_jet</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D16" s="171" t="n">
+        <v>1844</v>
+      </c>
+      <c r="E16" s="171" t="n">
+        <v>1844</v>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_fiasa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>H9</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>sales_jet</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D17" s="171" t="n">
+        <v>1955</v>
+      </c>
+      <c r="E17" s="171" t="n">
+        <v>1955</v>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_fiasa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>dept_jet</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D18" s="171" t="n">
+        <v>1478.149852603</v>
+      </c>
+      <c r="E18" s="171" t="n">
+        <v>1478.149852603</v>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>dept_jet</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D19" s="171" t="n">
+        <v>1843.971762465</v>
+      </c>
+      <c r="E19" s="171" t="n">
+        <v>1843.971762465</v>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>sales_fuel_oil</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D20" s="171" t="n">
+        <v>594</v>
+      </c>
+      <c r="E20" s="171" t="n">
+        <v>594</v>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_fiasa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>sales_fuel_oil</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D21" s="171" t="n">
+        <v>658</v>
+      </c>
+      <c r="E21" s="171" t="n">
+        <v>658</v>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_fiasa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>H11</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>sales_fuel_oil</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D22" s="171" t="n">
+        <v>441</v>
+      </c>
+      <c r="E22" s="171" t="n">
+        <v>441</v>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_fiasa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>dept_fuel_oil</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D23" s="171" t="n">
+        <v>594.0401649620001</v>
+      </c>
+      <c r="E23" s="171" t="n">
+        <v>594.0401649620001</v>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>dept_fuel_oil</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D24" s="171" t="n">
+        <v>658.0930416160001</v>
+      </c>
+      <c r="E24" s="171" t="n">
+        <v>658.0930416160001</v>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>F25</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>macro_gdp_per_capita</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D25" s="171" t="n">
+        <v>76055.06748983047</v>
+      </c>
+      <c r="E25" s="171" t="n">
+        <v>76055.06748983047</v>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>G25</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>macro_gdp_per_capita</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D26" s="171" t="n">
+        <v>75781.52071231291</v>
+      </c>
+      <c r="E26" s="171" t="n">
+        <v>75781.52071231291</v>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>H25</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>macro_gdp_per_capita</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D27" s="171" t="n">
+        <v>75255.62912098455</v>
+      </c>
+      <c r="E27" s="171" t="n">
+        <v>75255.62912098455</v>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>I25</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>macro_gdp_per_capita</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D28" s="171" t="n">
+        <v>75149.98563223911</v>
+      </c>
+      <c r="E28" s="171" t="n">
+        <v>75149.98563223911</v>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>F26</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>macro_agriculture_forestry_and_fishing</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D29" s="171" t="n">
+        <v>131.7706421450265</v>
+      </c>
+      <c r="E29" s="171" t="n">
+        <v>131.7706421450265</v>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>G26</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>macro_agriculture_forestry_and_fishing</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D30" s="171" t="n">
+        <v>125.7466421450265</v>
+      </c>
+      <c r="E30" s="171" t="n">
+        <v>125.7466421450265</v>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>H26</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>macro_agriculture_forestry_and_fishing</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D31" s="171" t="n">
+        <v>114.7916421450265</v>
+      </c>
+      <c r="E31" s="171" t="n">
+        <v>114.7916421450265</v>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>I26</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>macro_agriculture_forestry_and_fishing</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D32" s="171" t="n">
+        <v>134.7967469817132</v>
+      </c>
+      <c r="E32" s="171" t="n">
+        <v>134.7967469817132</v>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>F27</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>macro_manufacturing</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D33" s="171" t="n">
+        <v>523.0907540648606</v>
+      </c>
+      <c r="E33" s="171" t="n">
+        <v>523.0907540648606</v>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>G27</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>macro_manufacturing</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D34" s="171" t="n">
+        <v>524.9937540648609</v>
+      </c>
+      <c r="E34" s="171" t="n">
+        <v>524.9937540648609</v>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>H27</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>macro_manufacturing</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D35" s="171" t="n">
+        <v>523.150754064861</v>
+      </c>
+      <c r="E35" s="171" t="n">
+        <v>523.150754064861</v>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>I27</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>macro_manufacturing</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D36" s="171" t="n">
+        <v>516.9856529750193</v>
+      </c>
+      <c r="E36" s="171" t="n">
+        <v>516.9856529750193</v>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>F28</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>macro_mining_and_quarrying</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D37" s="171" t="n">
+        <v>204.4529227196744</v>
+      </c>
+      <c r="E37" s="171" t="n">
+        <v>204.4529227196744</v>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>G28</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>macro_mining_and_quarrying</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D38" s="171" t="n">
+        <v>204.2286999662737</v>
+      </c>
+      <c r="E38" s="171" t="n">
+        <v>204.2286999662738</v>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>H28</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>macro_mining_and_quarrying</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D39" s="171" t="n">
+        <v>205.1258295918731</v>
+      </c>
+      <c r="E39" s="171" t="n">
+        <v>205.1258295918731</v>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>I28</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>macro_mining_and_quarrying</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D40" s="171" t="n">
+        <v>205.4648860142573</v>
+      </c>
+      <c r="E40" s="171" t="n">
+        <v>205.4648860142574</v>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>F29</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>macro_construction</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D41" s="171" t="n">
+        <v>110.0650907489087</v>
+      </c>
+      <c r="E41" s="171" t="n">
+        <v>110.0650907489087</v>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>G29</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>macro_construction</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D42" s="171" t="n">
+        <v>109.5650907489087</v>
+      </c>
+      <c r="E42" s="171" t="n">
+        <v>109.5650907489087</v>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>H29</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>macro_construction</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D43" s="171" t="n">
+        <v>103.6250907489087</v>
+      </c>
+      <c r="E43" s="171" t="n">
+        <v>103.6250907489087</v>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>I29</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>macro_construction</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D44" s="171" t="n">
+        <v>99.09852067977131</v>
+      </c>
+      <c r="E44" s="171" t="n">
+        <v>99.09852067977131</v>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>macro_statssa.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>F30</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>manufacturing_volume_total</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D45" s="171" t="n">
+        <v>93.14166666666667</v>
+      </c>
+      <c r="E45" s="171" t="n">
+        <v>93.14166666666667</v>
+      </c>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>activity_statssa_monthly.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>G30</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>manufacturing_volume_total</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D46" s="171" t="n">
+        <v>93.71666666666665</v>
+      </c>
+      <c r="E46" s="171" t="n">
+        <v>93.71666666666665</v>
+      </c>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>activity_statssa_monthly.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>H30</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>manufacturing_volume_total</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D47" s="171" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="E47" s="171" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>activity_statssa_monthly.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>I30</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>manufacturing_volume_total</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D48" s="171" t="n">
+        <v>92.14166666666665</v>
+      </c>
+      <c r="E48" s="171" t="n">
+        <v>92.14166666666667</v>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>activity_statssa_monthly.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>F31</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>mining_volume_total</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D49" s="171" t="n">
+        <v>93.00833333333334</v>
+      </c>
+      <c r="E49" s="171" t="n">
+        <v>93.00833333333333</v>
+      </c>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>activity_statssa_monthly.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>G31</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>mining_volume_total</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D50" s="171" t="n">
+        <v>93.01666666666667</v>
+      </c>
+      <c r="E50" s="171" t="n">
+        <v>93.01666666666667</v>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>activity_statssa_monthly.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>H31</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>mining_volume_total</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D51" s="171" t="n">
+        <v>93.53333333333332</v>
+      </c>
+      <c r="E51" s="171" t="n">
+        <v>93.53333333333335</v>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>activity_statssa_monthly.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>I31</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>mining_volume_total</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D52" s="171" t="n">
+        <v>93.70833333333333</v>
+      </c>
+      <c r="E52" s="171" t="n">
+        <v>93.70833333333333</v>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>activity_statssa_monthly.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>F43</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: EC petrol / million L/year</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D53" s="171" t="n">
+        <v>703.1324447169991</v>
+      </c>
+      <c r="E53" s="171" t="n">
+        <v>703.132444716999</v>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>F44</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: FS petrol / million L/year</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D54" s="171" t="n">
+        <v>587.4580081820001</v>
+      </c>
+      <c r="E54" s="171" t="n">
+        <v>587.4580081820001</v>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>F45</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: GP petrol / million L/year</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D55" s="171" t="n">
+        <v>3530.440256933996</v>
+      </c>
+      <c r="E55" s="171" t="n">
+        <v>3530.440256933996</v>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>F46</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: KZN petrol / million L/year</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D56" s="171" t="n">
+        <v>1498.937893394999</v>
+      </c>
+      <c r="E56" s="171" t="n">
+        <v>1498.937893394999</v>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>F47</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: LP petrol / million L/year</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D57" s="171" t="n">
+        <v>273.644045045999</v>
+      </c>
+      <c r="E57" s="171" t="n">
+        <v>273.644045045999</v>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>F48</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: MP petrol / million L/year</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D58" s="171" t="n">
+        <v>612.2656460789989</v>
+      </c>
+      <c r="E58" s="171" t="n">
+        <v>612.2656460789989</v>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>F49</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: NC petrol / million L/year</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D59" s="171" t="n">
+        <v>99.82992901300001</v>
+      </c>
+      <c r="E59" s="171" t="n">
+        <v>99.829929013</v>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>F50</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: NW petrol / million L/year</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D60" s="171" t="n">
+        <v>448.1562321239999</v>
+      </c>
+      <c r="E60" s="171" t="n">
+        <v>448.1562321239999</v>
+      </c>
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>F51</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: WC petrol / million L/year</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D61" s="171" t="n">
+        <v>1431.005460082997</v>
+      </c>
+      <c r="E61" s="171" t="n">
+        <v>1431.005460082997</v>
+      </c>
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>F52</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: EC diesel / million L/year</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D62" s="171" t="n">
+        <v>1032.35218272</v>
+      </c>
+      <c r="E62" s="171" t="n">
+        <v>1032.35218272</v>
+      </c>
+      <c r="F62" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>F53</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: FS diesel / million L/year</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D63" s="171" t="n">
+        <v>781.8611598310002</v>
+      </c>
+      <c r="E63" s="171" t="n">
+        <v>781.8611598310002</v>
+      </c>
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>F54</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: GP diesel / million L/year</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D64" s="171" t="n">
+        <v>3278.990501961999</v>
+      </c>
+      <c r="E64" s="171" t="n">
+        <v>3278.990501961999</v>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>F55</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: KZN diesel / million L/year</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D65" s="171" t="n">
+        <v>2785.554802503</v>
+      </c>
+      <c r="E65" s="171" t="n">
+        <v>2785.554802503</v>
+      </c>
+      <c r="F65" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G65" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>F56</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: LP diesel / million L/year</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D66" s="171" t="n">
+        <v>221.987440248</v>
+      </c>
+      <c r="E66" s="171" t="n">
+        <v>221.987440248</v>
+      </c>
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>F57</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: MP diesel / million L/year</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D67" s="171" t="n">
+        <v>1144.924075864997</v>
+      </c>
+      <c r="E67" s="171" t="n">
+        <v>1144.924075864997</v>
+      </c>
+      <c r="F67" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>F58</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: NC diesel / million L/year</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D68" s="171" t="n">
+        <v>351.9801199100001</v>
+      </c>
+      <c r="E68" s="171" t="n">
+        <v>351.9801199100001</v>
+      </c>
+      <c r="F68" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>F59</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: NW diesel / million L/year</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D69" s="171" t="n">
+        <v>619.906488913</v>
+      </c>
+      <c r="E69" s="171" t="n">
+        <v>619.906488913</v>
+      </c>
+      <c r="F69" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G69" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>F60</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>Provincial: WC diesel / million L/year</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D70" s="171" t="n">
+        <v>2499.769547067</v>
+      </c>
+      <c r="E70" s="171" t="n">
+        <v>2499.769547067</v>
+      </c>
+      <c r="F70" s="1" t="inlineStr">
+        <is>
+          <t>matches</t>
+        </is>
+      </c>
+      <c r="G70" s="1" t="inlineStr">
+        <is>
+          <t>fuel_sales_department_by_province.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>66 values recomputed; 0 differ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>Not recomputed: vehicle sales and stock, electric vehicle sales, freight, power and airport rows (vehicle block is next), and every 'Model run' row, which is a frozen engine run on main.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>The model run in this workbook was made on main, where industry starts at 2.5 bn litres and agriculture at 0.7 (2024). manish-branch proposes 1.50 and 1.06 (2021 energy balance); see sector_baselines_2026-10-07.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>Changes made in this copy:</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>Source selection!E5: petrol 2022 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Source selection!E6: petrol 2023 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>Source selection!E10: diesel 2022 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>Source selection!E11: diesel 2023 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>Source selection!E15: jet 2022 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>Source selection!E16: jet 2023 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>Source selection!E20: fuel_oil 2022 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>Source selection!E21: fuel_oil 2023 FIASA -&gt; Department (official series; the two agree to within rounding in these years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>Source selection: 2024 left on FIASA, which is unverified; the department has published no 2024 figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>Sheets added: History, Sector history, Vehicle history, Checks, History sources. No other cell changed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -49452,517 +52705,517 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="166" t="inlineStr">
+      <c r="A4" s="170" t="inlineStr">
         <is>
           <t>Used for</t>
         </is>
       </c>
-      <c r="B4" s="166" t="inlineStr">
+      <c r="B4" s="170" t="inlineStr">
         <is>
           <t>Publisher</t>
         </is>
       </c>
-      <c r="C4" s="166" t="inlineStr">
+      <c r="C4" s="170" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="D4" s="166" t="inlineStr">
+      <c r="D4" s="170" t="inlineStr">
         <is>
           <t>Original file</t>
         </is>
       </c>
-      <c r="E4" s="166" t="inlineStr">
+      <c r="E4" s="170" t="inlineStr">
         <is>
           <t>Where the original is kept</t>
         </is>
       </c>
-      <c r="F4" s="166" t="inlineStr">
+      <c r="F4" s="170" t="inlineStr">
         <is>
           <t>Extract in the repository</t>
         </is>
       </c>
-      <c r="G4" s="166" t="inlineStr">
+      <c r="G4" s="170" t="inlineStr">
         <is>
           <t>Refresh command</t>
         </is>
       </c>
-      <c r="H4" s="166" t="inlineStr">
+      <c r="H4" s="170" t="inlineStr">
         <is>
           <t>Periods</t>
         </is>
       </c>
-      <c r="I4" s="166" t="inlineStr">
+      <c r="I4" s="170" t="inlineStr">
         <is>
           <t>Limits</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="168" t="inlineStr">
+      <c r="A5" s="172" t="inlineStr">
         <is>
           <t>History sections 1 and 4: national sales</t>
         </is>
       </c>
-      <c r="B5" s="168" t="inlineStr">
+      <c r="B5" s="172" t="inlineStr">
         <is>
           <t>Department of Mineral and Petroleum Resources (energy department)</t>
         </is>
       </c>
-      <c r="C5" s="168" t="inlineStr">
+      <c r="C5" s="172" t="inlineStr">
         <is>
           <t>https://www.dmpr.gov.za/Portals/0/Energy_Website/files/media/SA FUEL SALES VOLUME/</t>
         </is>
       </c>
-      <c r="D5" s="168" t="inlineStr">
+      <c r="D5" s="172" t="inlineStr">
         <is>
           <t>&lt;year&gt;-...-FSV....xls(x), national annual workbooks 2005-2023</t>
         </is>
       </c>
-      <c r="E5" s="168" t="inlineStr">
+      <c r="E5" s="172" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main</t>
         </is>
       </c>
-      <c r="F5" s="168" t="inlineStr">
+      <c r="F5" s="172" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_sales_department.csv</t>
         </is>
       </c>
-      <c r="G5" s="168" t="inlineStr">
+      <c r="G5" s="172" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_energy_dept --vintage 2026</t>
         </is>
       </c>
-      <c r="H5" s="168" t="inlineStr">
+      <c r="H5" s="172" t="inlineStr">
         <is>
           <t>2005-2023</t>
         </is>
       </c>
-      <c r="I5" s="168" t="inlineStr">
+      <c r="I5" s="172" t="inlineStr">
         <is>
           <t>2013 corrected on manish-branch (published sheet). Series ends 2023.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="168" t="inlineStr">
+      <c r="A6" s="172" t="inlineStr">
         <is>
           <t>History section 1: sales by province</t>
         </is>
       </c>
-      <c r="B6" s="168" t="inlineStr">
+      <c r="B6" s="172" t="inlineStr">
         <is>
           <t>Department of Mineral and Petroleum Resources (energy department)</t>
         </is>
       </c>
-      <c r="C6" s="168" t="inlineStr">
+      <c r="C6" s="172" t="inlineStr">
         <is>
           <t>https://www.dmpr.gov.za/Portals/0/Energy_Website/files/media/SA FUEL SALES VOLUME/</t>
         </is>
       </c>
-      <c r="D6" s="168" t="inlineStr">
+      <c r="D6" s="172" t="inlineStr">
         <is>
           <t>&lt;year&gt;-...-Magisterial-Districts-data.xlsx, quarterly sheets</t>
         </is>
       </c>
-      <c r="E6" s="168" t="inlineStr">
+      <c r="E6" s="172" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main (2013 annual workbook on manish-branch)</t>
         </is>
       </c>
-      <c r="F6" s="168" t="inlineStr">
+      <c r="F6" s="172" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_sales_department_by_province.csv</t>
         </is>
       </c>
-      <c r="G6" s="168" t="inlineStr">
+      <c r="G6" s="172" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_energy_dept --vintage 2026</t>
         </is>
       </c>
-      <c r="H6" s="168" t="inlineStr">
+      <c r="H6" s="172" t="inlineStr">
         <is>
           <t>2013-2022</t>
         </is>
       </c>
-      <c r="I6" s="168" t="inlineStr">
+      <c r="I6" s="172" t="inlineStr">
         <is>
           <t>Ends 2022. 2018 understated about 1.8% (district Q1 sheet incomplete). 2014-Q3 differs from national file.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="168" t="inlineStr">
+      <c r="A7" s="172" t="inlineStr">
         <is>
           <t>History section 2: imports and exports</t>
         </is>
       </c>
-      <c r="B7" s="168" t="inlineStr">
+      <c r="B7" s="172" t="inlineStr">
         <is>
           <t>South African Revenue Service, trade statistics</t>
         </is>
       </c>
-      <c r="C7" s="168" t="inlineStr">
+      <c r="C7" s="172" t="inlineStr">
         <is>
           <t>https://tools.sars.gov.za/tradestatsportal/data_download.aspx</t>
         </is>
       </c>
-      <c r="D7" s="168" t="inlineStr">
+      <c r="D7" s="172" t="inlineStr">
         <is>
           <t>sars-&lt;imports|exports&gt;-chapter27-fuels-&lt;year&gt;.xlsx, 2010-2026</t>
         </is>
       </c>
-      <c r="E7" s="168" t="inlineStr">
+      <c r="E7" s="172" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/sars/)</t>
         </is>
       </c>
-      <c r="F7" s="168" t="inlineStr">
+      <c r="F7" s="172" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_trade_sars.csv</t>
         </is>
       </c>
-      <c r="G7" s="168" t="inlineStr">
+      <c r="G7" s="172" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_sars --vintage 2026</t>
         </is>
       </c>
-      <c r="H7" s="168" t="inlineStr">
+      <c r="H7" s="172" t="inlineStr">
         <is>
           <t>2010-2026</t>
         </is>
       </c>
-      <c r="I7" s="168" t="inlineStr">
+      <c r="I7" s="172" t="inlineStr">
         <is>
           <t>Primary record of imports and exports from 2014. Kilograms to 2012, litres from 2014, both in 2013.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="168" t="inlineStr">
+      <c r="A8" s="172" t="inlineStr">
         <is>
           <t>History section 2: FIASA comparison rows</t>
         </is>
       </c>
-      <c r="B8" s="168" t="inlineStr">
+      <c r="B8" s="172" t="inlineStr">
         <is>
           <t>Fuels Industry Association of South Africa (from customs data)</t>
         </is>
       </c>
-      <c r="C8" s="168" t="inlineStr">
+      <c r="C8" s="172" t="inlineStr">
         <is>
           <t>https://fuelsindustry.org.za/publications/annual-reports/</t>
         </is>
       </c>
-      <c r="D8" s="168" t="inlineStr">
+      <c r="D8" s="172" t="inlineStr">
         <is>
           <t>annual-report-&lt;year&gt;.pdf; 2025 edition pp.47-49</t>
         </is>
       </c>
-      <c r="E8" s="168" t="inlineStr">
+      <c r="E8" s="172" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main; 2025 edition on main</t>
         </is>
       </c>
-      <c r="F8" s="168" t="inlineStr">
+      <c r="F8" s="172" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_trade_fiasa.csv</t>
         </is>
       </c>
-      <c r="G8" s="168" t="inlineStr">
+      <c r="G8" s="172" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_fuel_sales --vintage 2026</t>
         </is>
       </c>
-      <c r="H8" s="168" t="inlineStr">
+      <c r="H8" s="172" t="inlineStr">
         <is>
           <t>2009-2025</t>
         </is>
       </c>
-      <c r="I8" s="168" t="inlineStr">
+      <c r="I8" s="172" t="inlineStr">
         <is>
           <t>Cross-check, and the record before 2014; SARS is primary from 2014. 'Kerosene' is jet plus paraffin. Its 2024 diesel import figure is 4.000 bn L above customs.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="168" t="inlineStr">
+      <c r="A9" s="172" t="inlineStr">
         <is>
           <t>History section 4: FIASA comparison row</t>
         </is>
       </c>
-      <c r="B9" s="168" t="inlineStr">
+      <c r="B9" s="172" t="inlineStr">
         <is>
           <t>Fuels Industry Association of South Africa</t>
         </is>
       </c>
-      <c r="C9" s="168" t="inlineStr">
+      <c r="C9" s="172" t="inlineStr">
         <is>
           <t>https://fuelsindustry.org.za/publications/annual-reports/</t>
         </is>
       </c>
-      <c r="D9" s="168" t="inlineStr">
+      <c r="D9" s="172" t="inlineStr">
         <is>
           <t>annual-report-&lt;year&gt;.pdf, 2021-2025 editions</t>
         </is>
       </c>
-      <c r="E9" s="168" t="inlineStr">
+      <c r="E9" s="172" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main; 2025 edition on main</t>
         </is>
       </c>
-      <c r="F9" s="168" t="inlineStr">
+      <c r="F9" s="172" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_sales_fiasa.csv</t>
         </is>
       </c>
-      <c r="G9" s="168" t="inlineStr">
+      <c r="G9" s="172" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_fuel_sales --vintage 2026</t>
         </is>
       </c>
-      <c r="H9" s="168" t="inlineStr">
+      <c r="H9" s="172" t="inlineStr">
         <is>
           <t>2009-2024</t>
         </is>
       </c>
-      <c r="I9" s="168" t="inlineStr">
+      <c r="I9" s="172" t="inlineStr">
         <is>
           <t>Used for 2024 only. Its 2013 figures equal the department's superseded sheet.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="168" t="inlineStr">
+      <c r="A10" s="172" t="inlineStr">
         <is>
           <t>History section 3 and Sector history: production and diesel by sector</t>
         </is>
       </c>
-      <c r="B10" s="168" t="inlineStr">
+      <c r="B10" s="172" t="inlineStr">
         <is>
           <t>Department of Mineral and Petroleum Resources (energy department)</t>
         </is>
       </c>
-      <c r="C10" s="168" t="inlineStr">
+      <c r="C10" s="172" t="inlineStr">
         <is>
           <t>https://www.dmpr.gov.za/Portals/0/Energy_Website/files/media/Energy_Balances.html</t>
         </is>
       </c>
-      <c r="D10" s="168" t="inlineStr">
+      <c r="D10" s="172" t="inlineStr">
         <is>
           <t>&lt;year&gt;-Commodity-Flow-and-Energy-Balance.xlsx, 2007-2021</t>
         </is>
       </c>
-      <c r="E10" s="168" t="inlineStr">
+      <c r="E10" s="172" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main</t>
         </is>
       </c>
-      <c r="F10" s="168" t="inlineStr">
+      <c r="F10" s="172" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/energy_balance_department.csv</t>
         </is>
       </c>
-      <c r="G10" s="168" t="inlineStr">
+      <c r="G10" s="172" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_energy_dept --vintage 2026</t>
         </is>
       </c>
-      <c r="H10" s="168" t="inlineStr">
+      <c r="H10" s="172" t="inlineStr">
         <is>
           <t>2007-2021</t>
         </is>
       </c>
-      <c r="I10" s="168" t="inlineStr">
+      <c r="I10" s="172" t="inlineStr">
         <is>
           <t>Ends 2021. Sector definitions shift in 2016. Fuel oil not extracted.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="168" t="inlineStr">
+      <c r="A11" s="172" t="inlineStr">
         <is>
           <t>History section 3: operators' reported output</t>
         </is>
       </c>
-      <c r="B11" s="168" t="inlineStr">
+      <c r="B11" s="172" t="inlineStr">
         <is>
           <t>Sasol (production and sales metrics); Glencore (annual reports)</t>
         </is>
       </c>
-      <c r="C11" s="168" t="inlineStr">
+      <c r="C11" s="172" t="inlineStr">
         <is>
           <t>https://www.sasol.com/</t>
         </is>
       </c>
-      <c r="D11" s="168" t="inlineStr">
+      <c r="D11" s="172" t="inlineStr">
         <is>
           <t>sasol-metrics-fy2022/2025/2026.pdf, p.4; GLEN-2023/2024/2025-Annual-Report.pdf</t>
         </is>
       </c>
-      <c r="E11" s="168" t="inlineStr">
+      <c r="E11" s="172" t="inlineStr">
         <is>
           <t>Sasol files on manish-branch (external/data/raw/sasol/); Glencore reports by link only</t>
         </is>
       </c>
-      <c r="F11" s="168" t="inlineStr">
+      <c r="F11" s="172" t="inlineStr">
         <is>
           <t>assumptions/2026/reference/refinery_output_operators.csv</t>
         </is>
       </c>
-      <c r="G11" s="168" t="inlineStr">
+      <c r="G11" s="172" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="H11" s="168" t="inlineStr">
+      <c r="H11" s="172" t="inlineStr">
         <is>
           <t>2020-2026</t>
         </is>
       </c>
-      <c r="I11" s="168" t="inlineStr">
+      <c r="I11" s="172" t="inlineStr">
         <is>
           <t>All refined products, no product split; fiscal and calendar years; Astron as energy content.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="168" t="inlineStr">
+      <c r="A12" s="172" t="inlineStr">
         <is>
           <t>History section 5: litres levied</t>
         </is>
       </c>
-      <c r="B12" s="168" t="inlineStr">
+      <c r="B12" s="172" t="inlineStr">
         <is>
           <t>Road Accident Fund</t>
         </is>
       </c>
-      <c r="C12" s="168" t="inlineStr">
+      <c r="C12" s="172" t="inlineStr">
         <is>
           <t>https://static.pmg.org.za/RAF_Annual_Report_2025.pdf</t>
         </is>
       </c>
-      <c r="D12" s="168" t="inlineStr">
+      <c r="D12" s="172" t="inlineStr">
         <is>
           <t>raf-annual-report-2024-25.pdf, note 16 (p.183)</t>
         </is>
       </c>
-      <c r="E12" s="168" t="inlineStr">
+      <c r="E12" s="172" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/raf/)</t>
         </is>
       </c>
-      <c r="F12" s="168" t="inlineStr">
+      <c r="F12" s="172" t="inlineStr">
         <is>
           <t>assumptions/2026/reference/fuel_levy_revenue_raf.csv</t>
         </is>
       </c>
-      <c r="G12" s="168" t="inlineStr">
+      <c r="G12" s="172" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="H12" s="168" t="inlineStr">
+      <c r="H12" s="172" t="inlineStr">
         <is>
           <t>2024-2025</t>
         </is>
       </c>
-      <c r="I12" s="168" t="inlineStr">
+      <c r="I12" s="172" t="inlineStr">
         <is>
           <t>Gross levies and diesel rebate in rand; litres derived in the balance note. Fiscal years; petrol and diesel together.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="168" t="inlineStr">
+      <c r="A13" s="172" t="inlineStr">
         <is>
           <t>Sector history: mining and manufacturing volume indices</t>
         </is>
       </c>
-      <c r="B13" s="168" t="inlineStr">
+      <c r="B13" s="172" t="inlineStr">
         <is>
           <t>Statistics South Africa (P2041 mining, P3041.2 manufacturing, P7162 land transport, P0141 CPI)</t>
         </is>
       </c>
-      <c r="C13" s="168" t="inlineStr">
+      <c r="C13" s="172" t="inlineStr">
         <is>
           <t>https://www.statssa.gov.za/?page_id=1847</t>
         </is>
       </c>
-      <c r="D13" s="168" t="inlineStr">
+      <c r="D13" s="172" t="inlineStr">
         <is>
           <t>release zips, July and August 2026</t>
         </is>
       </c>
-      <c r="E13" s="168" t="inlineStr">
+      <c r="E13" s="172" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/statssa/)</t>
         </is>
       </c>
-      <c r="F13" s="168" t="inlineStr">
+      <c r="F13" s="172" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/activity_statssa_monthly.csv</t>
         </is>
       </c>
-      <c r="G13" s="168" t="inlineStr">
+      <c r="G13" s="172" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_statssa_monthly --vintage 2026</t>
         </is>
       </c>
-      <c r="H13" s="168" t="inlineStr">
+      <c r="H13" s="172" t="inlineStr">
         <is>
           <t>1998-01-2026-08</t>
         </is>
       </c>
-      <c r="I13" s="168" t="inlineStr">
+      <c r="I13" s="172" t="inlineStr">
         <is>
           <t>Activity measures, not fuel volumes. Not seasonally adjusted. Tonnes, not tonne-kilometres.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="168" t="inlineStr">
+      <c r="A14" s="172" t="inlineStr">
         <is>
           <t>Sector history: agriculture real value added</t>
         </is>
       </c>
-      <c r="B14" s="168" t="inlineStr">
+      <c r="B14" s="172" t="inlineStr">
         <is>
           <t>Statistics South Africa (P0441 GDP; P0302 mid-year population)</t>
         </is>
       </c>
-      <c r="C14" s="168" t="inlineStr">
+      <c r="C14" s="172" t="inlineStr">
         <is>
           <t>https://www.statssa.gov.za/?page_id=1854&amp;PPN=P0441</t>
         </is>
       </c>
-      <c r="D14" s="168" t="inlineStr">
+      <c r="D14" s="172" t="inlineStr">
         <is>
           <t>GDP P0441 - GDP Time series Q2 2026.xlsx (Annual sheet); Country projection ... (2002-2026).xlsx</t>
         </is>
       </c>
-      <c r="E14" s="168" t="inlineStr">
+      <c r="E14" s="172" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/statssa/)</t>
         </is>
       </c>
-      <c r="F14" s="168" t="inlineStr">
+      <c r="F14" s="172" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/macro_statssa.csv</t>
         </is>
       </c>
-      <c r="G14" s="168" t="inlineStr">
+      <c r="G14" s="172" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_economy --vintage 2026</t>
         </is>
       </c>
-      <c r="H14" s="168" t="inlineStr">
+      <c r="H14" s="172" t="inlineStr">
         <is>
           <t>1993-2050</t>
         </is>
       </c>
-      <c r="I14" s="168" t="inlineStr">
+      <c r="I14" s="172" t="inlineStr">
         <is>
           <t>Manual placement each release. Years after 2026 are projections, not observations.</t>
         </is>

--- a/output/delivered/Demand_baseline_workshop_2026_10_08_history.xlsx
+++ b/output/delivered/Demand_baseline_workshop_2026_10_08_history.xlsx
@@ -21,9 +21,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HML" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector history" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vehicle history" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History sources" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diesel by use" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vehicle history" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History sources" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -188,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -674,6 +675,12 @@
     <xf numFmtId="3" fontId="1" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="168" fontId="1" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="168" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -44691,7 +44698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V60"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -44721,14 +44728,14 @@
     <row r="1">
       <c r="A1" s="149" t="inlineStr">
         <is>
-          <t>Vehicle block: what is observed beside what the model assumes</t>
+          <t>Diesel by use: the six branches drawn at the 7 October check-in</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Stock, new sales, scrapping, drivetrain, fuel split and use. Observations are values from the registered inputs; the model's settings are in column D; shares, retirements and cross-checks are formulas.</t>
+          <t>Mining, manufacturing, agriculture and power are taken from sources; road diesel is what remains of recorded sales and is split with the shares of a published vehicle study (approach A). Million litres a year.</t>
         </is>
       </c>
     </row>
@@ -44819,7 +44826,7 @@
     <row r="5">
       <c r="A5" s="151" t="inlineStr">
         <is>
-          <t>1. Registered vehicles at December</t>
+          <t>1. Sales and the uses taken from sources</t>
         </is>
       </c>
       <c r="B5" s="151" t="n"/>
@@ -44845,262 +44852,370 @@
       <c r="V5" s="151" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="152" t="inlineStr">
-        <is>
-          <t>Cars</t>
-        </is>
-      </c>
-      <c r="B6" s="153" t="inlineStr">
-        <is>
-          <t>vehicles</t>
-        </is>
-      </c>
-      <c r="C6" s="153" t="inlineStr">
-        <is>
-          <t>Source observation</t>
-        </is>
-      </c>
-      <c r="D6" s="166" t="n"/>
-      <c r="E6" s="152" t="inlineStr">
-        <is>
-          <t>Live (licensed) vehicles, all fuels together.</t>
-        </is>
-      </c>
-      <c r="F6" s="166" t="n"/>
-      <c r="G6" s="166" t="n"/>
-      <c r="H6" s="166" t="n"/>
-      <c r="I6" s="166" t="n"/>
-      <c r="J6" s="166" t="n"/>
-      <c r="K6" s="166" t="n"/>
-      <c r="L6" s="166" t="n"/>
-      <c r="M6" s="166" t="n"/>
-      <c r="N6" s="166" t="n"/>
-      <c r="O6" s="166" t="n">
-        <v>7652077</v>
-      </c>
-      <c r="P6" s="166" t="n">
-        <v>7685153</v>
-      </c>
-      <c r="Q6" s="166" t="n">
-        <v>7794164</v>
-      </c>
-      <c r="R6" s="166" t="n">
-        <v>7949275</v>
-      </c>
-      <c r="S6" s="166" t="n">
-        <v>8184111</v>
-      </c>
-      <c r="T6" s="152" t="inlineStr">
-        <is>
-          <t>2021-2025</t>
-        </is>
-      </c>
-      <c r="U6" s="152" t="inlineStr">
-        <is>
-          <t>NaTIS live vehicle population, December</t>
-        </is>
-      </c>
-      <c r="V6" s="152" t="inlineStr">
-        <is>
-          <t>No split by fuel or by age in this source</t>
-        </is>
-      </c>
+      <c r="A6" s="155" t="inlineStr">
+        <is>
+          <t>Diesel sales used</t>
+        </is>
+      </c>
+      <c r="B6" s="156" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C6" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D6" s="157" t="n"/>
+      <c r="E6" s="155" t="inlineStr">
+        <is>
+          <t>From History: department national file to 2023, FIASA (unverified) for 2024.</t>
+        </is>
+      </c>
+      <c r="F6" s="157">
+        <f>IF(ISNUMBER(History!F62),History!F62,"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="157">
+        <f>IF(ISNUMBER(History!G62),History!G62,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="157">
+        <f>IF(ISNUMBER(History!H62),History!H62,"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="157">
+        <f>IF(ISNUMBER(History!I62),History!I62,"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="157">
+        <f>IF(ISNUMBER(History!J62),History!J62,"")</f>
+        <v/>
+      </c>
+      <c r="K6" s="157">
+        <f>IF(ISNUMBER(History!K62),History!K62,"")</f>
+        <v/>
+      </c>
+      <c r="L6" s="157">
+        <f>IF(ISNUMBER(History!L62),History!L62,"")</f>
+        <v/>
+      </c>
+      <c r="M6" s="157">
+        <f>IF(ISNUMBER(History!M62),History!M62,"")</f>
+        <v/>
+      </c>
+      <c r="N6" s="157">
+        <f>IF(ISNUMBER(History!N62),History!N62,"")</f>
+        <v/>
+      </c>
+      <c r="O6" s="157">
+        <f>IF(ISNUMBER(History!O62),History!O62,"")</f>
+        <v/>
+      </c>
+      <c r="P6" s="157">
+        <f>IF(ISNUMBER(History!P62),History!P62,"")</f>
+        <v/>
+      </c>
+      <c r="Q6" s="157">
+        <f>IF(ISNUMBER(History!Q62),History!Q62,"")</f>
+        <v/>
+      </c>
+      <c r="R6" s="157">
+        <f>IF(ISNUMBER(History!R62),History!R62,"")</f>
+        <v/>
+      </c>
+      <c r="S6" s="157">
+        <f>IF(ISNUMBER(History!S62),History!S62,"")</f>
+        <v/>
+      </c>
+      <c r="T6" s="155" t="inlineStr">
+        <is>
+          <t>2012-2024</t>
+        </is>
+      </c>
+      <c r="U6" s="155" t="inlineStr"/>
+      <c r="V6" s="155" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="152" t="inlineStr">
-        <is>
-          <t>Light commercial vehicles</t>
-        </is>
-      </c>
-      <c r="B7" s="153" t="inlineStr">
-        <is>
-          <t>vehicles</t>
-        </is>
-      </c>
-      <c r="C7" s="153" t="inlineStr">
-        <is>
-          <t>Source observation</t>
-        </is>
-      </c>
-      <c r="D7" s="166" t="n"/>
-      <c r="E7" s="152" t="inlineStr">
-        <is>
-          <t>Live (licensed) vehicles, all fuels together.</t>
-        </is>
-      </c>
-      <c r="F7" s="166" t="n"/>
-      <c r="G7" s="166" t="n"/>
-      <c r="H7" s="166" t="n"/>
-      <c r="I7" s="166" t="n"/>
-      <c r="J7" s="166" t="n"/>
-      <c r="K7" s="166" t="n"/>
-      <c r="L7" s="166" t="n"/>
-      <c r="M7" s="166" t="n"/>
-      <c r="N7" s="166" t="n"/>
-      <c r="O7" s="166" t="n">
-        <v>2671314</v>
-      </c>
-      <c r="P7" s="166" t="n">
-        <v>2658416</v>
-      </c>
-      <c r="Q7" s="166" t="n">
-        <v>2689310</v>
-      </c>
-      <c r="R7" s="166" t="n">
-        <v>2725606</v>
-      </c>
-      <c r="S7" s="166" t="n">
-        <v>2776258</v>
-      </c>
-      <c r="T7" s="152" t="inlineStr">
-        <is>
-          <t>2021-2025</t>
-        </is>
-      </c>
-      <c r="U7" s="152" t="inlineStr">
-        <is>
-          <t>NaTIS live vehicle population, December</t>
-        </is>
-      </c>
-      <c r="V7" s="152" t="inlineStr">
-        <is>
-          <t>No split by fuel or by age in this source</t>
-        </is>
-      </c>
+      <c r="A7" s="155" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="B7" s="156" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C7" s="156" t="inlineStr">
+        <is>
+          <t>Observation, then estimate</t>
+        </is>
+      </c>
+      <c r="D7" s="157" t="n"/>
+      <c r="E7" s="155" t="inlineStr">
+        <is>
+          <t>Energy balance to 2021; from 2022 the indicative figure on Sector history. Driver: mining production index.</t>
+        </is>
+      </c>
+      <c r="F7" s="157">
+        <f>IF(ISNUMBER('Sector history'!F6),'Sector history'!F6,IF(ISNUMBER('Sector history'!F9),'Sector history'!F9,""))</f>
+        <v/>
+      </c>
+      <c r="G7" s="157">
+        <f>IF(ISNUMBER('Sector history'!G6),'Sector history'!G6,IF(ISNUMBER('Sector history'!G9),'Sector history'!G9,""))</f>
+        <v/>
+      </c>
+      <c r="H7" s="157">
+        <f>IF(ISNUMBER('Sector history'!H6),'Sector history'!H6,IF(ISNUMBER('Sector history'!H9),'Sector history'!H9,""))</f>
+        <v/>
+      </c>
+      <c r="I7" s="157">
+        <f>IF(ISNUMBER('Sector history'!I6),'Sector history'!I6,IF(ISNUMBER('Sector history'!I9),'Sector history'!I9,""))</f>
+        <v/>
+      </c>
+      <c r="J7" s="157">
+        <f>IF(ISNUMBER('Sector history'!J6),'Sector history'!J6,IF(ISNUMBER('Sector history'!J9),'Sector history'!J9,""))</f>
+        <v/>
+      </c>
+      <c r="K7" s="157">
+        <f>IF(ISNUMBER('Sector history'!K6),'Sector history'!K6,IF(ISNUMBER('Sector history'!K9),'Sector history'!K9,""))</f>
+        <v/>
+      </c>
+      <c r="L7" s="157">
+        <f>IF(ISNUMBER('Sector history'!L6),'Sector history'!L6,IF(ISNUMBER('Sector history'!L9),'Sector history'!L9,""))</f>
+        <v/>
+      </c>
+      <c r="M7" s="157">
+        <f>IF(ISNUMBER('Sector history'!M6),'Sector history'!M6,IF(ISNUMBER('Sector history'!M9),'Sector history'!M9,""))</f>
+        <v/>
+      </c>
+      <c r="N7" s="157">
+        <f>IF(ISNUMBER('Sector history'!N6),'Sector history'!N6,IF(ISNUMBER('Sector history'!N9),'Sector history'!N9,""))</f>
+        <v/>
+      </c>
+      <c r="O7" s="157">
+        <f>IF(ISNUMBER('Sector history'!O6),'Sector history'!O6,IF(ISNUMBER('Sector history'!O9),'Sector history'!O9,""))</f>
+        <v/>
+      </c>
+      <c r="P7" s="157">
+        <f>IF(ISNUMBER('Sector history'!P6),'Sector history'!P6,IF(ISNUMBER('Sector history'!P9),'Sector history'!P9,""))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="157">
+        <f>IF(ISNUMBER('Sector history'!Q6),'Sector history'!Q6,IF(ISNUMBER('Sector history'!Q9),'Sector history'!Q9,""))</f>
+        <v/>
+      </c>
+      <c r="R7" s="157">
+        <f>IF(ISNUMBER('Sector history'!R6),'Sector history'!R6,IF(ISNUMBER('Sector history'!R9),'Sector history'!R9,""))</f>
+        <v/>
+      </c>
+      <c r="S7" s="157">
+        <f>IF(ISNUMBER('Sector history'!S6),'Sector history'!S6,IF(ISNUMBER('Sector history'!S9),'Sector history'!S9,""))</f>
+        <v/>
+      </c>
+      <c r="T7" s="155" t="inlineStr">
+        <is>
+          <t>Observed to 2021; estimated after</t>
+        </is>
+      </c>
+      <c r="U7" s="155" t="inlineStr">
+        <is>
+          <t>Department energy balances; Stats SA P2041</t>
+        </is>
+      </c>
+      <c r="V7" s="155" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="152" t="inlineStr">
-        <is>
-          <t>Trucks</t>
-        </is>
-      </c>
-      <c r="B8" s="153" t="inlineStr">
-        <is>
-          <t>vehicles</t>
-        </is>
-      </c>
-      <c r="C8" s="153" t="inlineStr">
-        <is>
-          <t>Source observation</t>
-        </is>
-      </c>
-      <c r="D8" s="166" t="n"/>
-      <c r="E8" s="152" t="inlineStr">
-        <is>
-          <t>Live (licensed) vehicles, all fuels together.</t>
-        </is>
-      </c>
-      <c r="F8" s="166" t="n"/>
-      <c r="G8" s="166" t="n"/>
-      <c r="H8" s="166" t="n"/>
-      <c r="I8" s="166" t="n"/>
-      <c r="J8" s="166" t="n"/>
-      <c r="K8" s="166" t="n"/>
-      <c r="L8" s="166" t="n"/>
-      <c r="M8" s="166" t="n"/>
-      <c r="N8" s="166" t="n"/>
-      <c r="O8" s="166" t="n">
-        <v>389112</v>
-      </c>
-      <c r="P8" s="166" t="n">
-        <v>385845</v>
-      </c>
-      <c r="Q8" s="166" t="n">
-        <v>392349</v>
-      </c>
-      <c r="R8" s="166" t="n">
-        <v>398542</v>
-      </c>
-      <c r="S8" s="166" t="n">
-        <v>404752</v>
-      </c>
-      <c r="T8" s="152" t="inlineStr">
-        <is>
-          <t>2021-2025</t>
-        </is>
-      </c>
-      <c r="U8" s="152" t="inlineStr">
-        <is>
-          <t>NaTIS live vehicle population, December</t>
-        </is>
-      </c>
-      <c r="V8" s="152" t="inlineStr">
-        <is>
-          <t>No split by fuel or by age in this source</t>
-        </is>
-      </c>
+      <c r="A8" s="155" t="inlineStr">
+        <is>
+          <t>Manufacturing and other industry</t>
+        </is>
+      </c>
+      <c r="B8" s="156" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C8" s="156" t="inlineStr">
+        <is>
+          <t>Observation, then estimate</t>
+        </is>
+      </c>
+      <c r="D8" s="157" t="n"/>
+      <c r="E8" s="155" t="inlineStr">
+        <is>
+          <t>Energy balance industry less mining and construction to 2021; indicative after. Driver: manufacturing production index.</t>
+        </is>
+      </c>
+      <c r="F8" s="157">
+        <f>IF(ISNUMBER('Sector history'!F16),'Sector history'!F16,IF(ISNUMBER('Sector history'!F19),'Sector history'!F19,""))</f>
+        <v/>
+      </c>
+      <c r="G8" s="157">
+        <f>IF(ISNUMBER('Sector history'!G16),'Sector history'!G16,IF(ISNUMBER('Sector history'!G19),'Sector history'!G19,""))</f>
+        <v/>
+      </c>
+      <c r="H8" s="157">
+        <f>IF(ISNUMBER('Sector history'!H16),'Sector history'!H16,IF(ISNUMBER('Sector history'!H19),'Sector history'!H19,""))</f>
+        <v/>
+      </c>
+      <c r="I8" s="157">
+        <f>IF(ISNUMBER('Sector history'!I16),'Sector history'!I16,IF(ISNUMBER('Sector history'!I19),'Sector history'!I19,""))</f>
+        <v/>
+      </c>
+      <c r="J8" s="157">
+        <f>IF(ISNUMBER('Sector history'!J16),'Sector history'!J16,IF(ISNUMBER('Sector history'!J19),'Sector history'!J19,""))</f>
+        <v/>
+      </c>
+      <c r="K8" s="157">
+        <f>IF(ISNUMBER('Sector history'!K16),'Sector history'!K16,IF(ISNUMBER('Sector history'!K19),'Sector history'!K19,""))</f>
+        <v/>
+      </c>
+      <c r="L8" s="157">
+        <f>IF(ISNUMBER('Sector history'!L16),'Sector history'!L16,IF(ISNUMBER('Sector history'!L19),'Sector history'!L19,""))</f>
+        <v/>
+      </c>
+      <c r="M8" s="157">
+        <f>IF(ISNUMBER('Sector history'!M16),'Sector history'!M16,IF(ISNUMBER('Sector history'!M19),'Sector history'!M19,""))</f>
+        <v/>
+      </c>
+      <c r="N8" s="157">
+        <f>IF(ISNUMBER('Sector history'!N16),'Sector history'!N16,IF(ISNUMBER('Sector history'!N19),'Sector history'!N19,""))</f>
+        <v/>
+      </c>
+      <c r="O8" s="157">
+        <f>IF(ISNUMBER('Sector history'!O16),'Sector history'!O16,IF(ISNUMBER('Sector history'!O19),'Sector history'!O19,""))</f>
+        <v/>
+      </c>
+      <c r="P8" s="157">
+        <f>IF(ISNUMBER('Sector history'!P16),'Sector history'!P16,IF(ISNUMBER('Sector history'!P19),'Sector history'!P19,""))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="157">
+        <f>IF(ISNUMBER('Sector history'!Q16),'Sector history'!Q16,IF(ISNUMBER('Sector history'!Q19),'Sector history'!Q19,""))</f>
+        <v/>
+      </c>
+      <c r="R8" s="157">
+        <f>IF(ISNUMBER('Sector history'!R16),'Sector history'!R16,IF(ISNUMBER('Sector history'!R19),'Sector history'!R19,""))</f>
+        <v/>
+      </c>
+      <c r="S8" s="157">
+        <f>IF(ISNUMBER('Sector history'!S16),'Sector history'!S16,IF(ISNUMBER('Sector history'!S19),'Sector history'!S19,""))</f>
+        <v/>
+      </c>
+      <c r="T8" s="155" t="inlineStr">
+        <is>
+          <t>Zero before 2016 in the balance</t>
+        </is>
+      </c>
+      <c r="U8" s="155" t="inlineStr">
+        <is>
+          <t>Department energy balances; Stats SA P3041.2</t>
+        </is>
+      </c>
+      <c r="V8" s="155" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="152" t="inlineStr">
-        <is>
-          <t>Buses</t>
-        </is>
-      </c>
-      <c r="B9" s="153" t="inlineStr">
-        <is>
-          <t>vehicles</t>
-        </is>
-      </c>
-      <c r="C9" s="153" t="inlineStr">
-        <is>
-          <t>Source observation</t>
-        </is>
-      </c>
-      <c r="D9" s="166" t="n"/>
-      <c r="E9" s="152" t="inlineStr">
-        <is>
-          <t>Live (licensed) vehicles, all fuels together.</t>
-        </is>
-      </c>
-      <c r="F9" s="166" t="n"/>
-      <c r="G9" s="166" t="n"/>
-      <c r="H9" s="166" t="n"/>
-      <c r="I9" s="166" t="n"/>
-      <c r="J9" s="166" t="n"/>
-      <c r="K9" s="166" t="n"/>
-      <c r="L9" s="166" t="n"/>
-      <c r="M9" s="166" t="n"/>
-      <c r="N9" s="166" t="n"/>
-      <c r="O9" s="166" t="n">
-        <v>64340</v>
-      </c>
-      <c r="P9" s="166" t="n">
-        <v>64170</v>
-      </c>
-      <c r="Q9" s="166" t="n">
-        <v>64982</v>
-      </c>
-      <c r="R9" s="166" t="n">
-        <v>65792</v>
-      </c>
-      <c r="S9" s="166" t="n">
-        <v>66249</v>
-      </c>
-      <c r="T9" s="152" t="inlineStr">
-        <is>
-          <t>2021-2025</t>
-        </is>
-      </c>
-      <c r="U9" s="152" t="inlineStr">
-        <is>
-          <t>NaTIS live vehicle population, December</t>
-        </is>
-      </c>
-      <c r="V9" s="152" t="inlineStr">
-        <is>
-          <t>No split by fuel or by age in this source</t>
-        </is>
-      </c>
+      <c r="A9" s="155" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="B9" s="156" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C9" s="156" t="inlineStr">
+        <is>
+          <t>Observation, then estimate</t>
+        </is>
+      </c>
+      <c r="D9" s="157" t="n"/>
+      <c r="E9" s="155" t="inlineStr">
+        <is>
+          <t>Energy balance to 2021; indicative after. Driver: agricultural real value added.</t>
+        </is>
+      </c>
+      <c r="F9" s="157">
+        <f>IF(ISNUMBER('Sector history'!F22),'Sector history'!F22,IF(ISNUMBER('Sector history'!F25),'Sector history'!F25,""))</f>
+        <v/>
+      </c>
+      <c r="G9" s="157">
+        <f>IF(ISNUMBER('Sector history'!G22),'Sector history'!G22,IF(ISNUMBER('Sector history'!G25),'Sector history'!G25,""))</f>
+        <v/>
+      </c>
+      <c r="H9" s="157">
+        <f>IF(ISNUMBER('Sector history'!H22),'Sector history'!H22,IF(ISNUMBER('Sector history'!H25),'Sector history'!H25,""))</f>
+        <v/>
+      </c>
+      <c r="I9" s="157">
+        <f>IF(ISNUMBER('Sector history'!I22),'Sector history'!I22,IF(ISNUMBER('Sector history'!I25),'Sector history'!I25,""))</f>
+        <v/>
+      </c>
+      <c r="J9" s="157">
+        <f>IF(ISNUMBER('Sector history'!J22),'Sector history'!J22,IF(ISNUMBER('Sector history'!J25),'Sector history'!J25,""))</f>
+        <v/>
+      </c>
+      <c r="K9" s="157">
+        <f>IF(ISNUMBER('Sector history'!K22),'Sector history'!K22,IF(ISNUMBER('Sector history'!K25),'Sector history'!K25,""))</f>
+        <v/>
+      </c>
+      <c r="L9" s="157">
+        <f>IF(ISNUMBER('Sector history'!L22),'Sector history'!L22,IF(ISNUMBER('Sector history'!L25),'Sector history'!L25,""))</f>
+        <v/>
+      </c>
+      <c r="M9" s="157">
+        <f>IF(ISNUMBER('Sector history'!M22),'Sector history'!M22,IF(ISNUMBER('Sector history'!M25),'Sector history'!M25,""))</f>
+        <v/>
+      </c>
+      <c r="N9" s="157">
+        <f>IF(ISNUMBER('Sector history'!N22),'Sector history'!N22,IF(ISNUMBER('Sector history'!N25),'Sector history'!N25,""))</f>
+        <v/>
+      </c>
+      <c r="O9" s="157">
+        <f>IF(ISNUMBER('Sector history'!O22),'Sector history'!O22,IF(ISNUMBER('Sector history'!O25),'Sector history'!O25,""))</f>
+        <v/>
+      </c>
+      <c r="P9" s="157">
+        <f>IF(ISNUMBER('Sector history'!P22),'Sector history'!P22,IF(ISNUMBER('Sector history'!P25),'Sector history'!P25,""))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="157">
+        <f>IF(ISNUMBER('Sector history'!Q22),'Sector history'!Q22,IF(ISNUMBER('Sector history'!Q25),'Sector history'!Q25,""))</f>
+        <v/>
+      </c>
+      <c r="R9" s="157">
+        <f>IF(ISNUMBER('Sector history'!R22),'Sector history'!R22,IF(ISNUMBER('Sector history'!R25),'Sector history'!R25,""))</f>
+        <v/>
+      </c>
+      <c r="S9" s="157">
+        <f>IF(ISNUMBER('Sector history'!S22),'Sector history'!S22,IF(ISNUMBER('Sector history'!S25),'Sector history'!S25,""))</f>
+        <v/>
+      </c>
+      <c r="T9" s="155" t="inlineStr">
+        <is>
+          <t>Observed to 2021; estimated after</t>
+        </is>
+      </c>
+      <c r="U9" s="155" t="inlineStr">
+        <is>
+          <t>Department energy balances; Stats SA P0441</t>
+        </is>
+      </c>
+      <c r="V9" s="155" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="152" t="inlineStr">
         <is>
-          <t>Minibuses</t>
+          <t>Diesel power generation, Eskom and independent plants</t>
         </is>
       </c>
       <c r="B10" s="153" t="inlineStr">
         <is>
-          <t>vehicles</t>
+          <t>GWh</t>
         </is>
       </c>
       <c r="C10" s="153" t="inlineStr">
@@ -45111,7 +45226,7 @@
       <c r="D10" s="166" t="n"/>
       <c r="E10" s="152" t="inlineStr">
         <is>
-          <t>Live (licensed) vehicles, all fuels together.</t>
+          <t>Year to 31 March of the following year, shown under the calendar year it mostly covers.</t>
         </is>
       </c>
       <c r="F10" s="166" t="n"/>
@@ -45123,46 +45238,40 @@
       <c r="L10" s="166" t="n"/>
       <c r="M10" s="166" t="n"/>
       <c r="N10" s="166" t="n"/>
-      <c r="O10" s="166" t="n">
-        <v>349671</v>
-      </c>
+      <c r="O10" s="166" t="n"/>
       <c r="P10" s="166" t="n">
-        <v>349335</v>
+        <v>4116</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>355235</v>
+        <v>5143</v>
       </c>
       <c r="R10" s="166" t="n">
-        <v>355139</v>
+        <v>2838</v>
       </c>
       <c r="S10" s="166" t="n">
-        <v>355145</v>
+        <v>1079</v>
       </c>
       <c r="T10" s="152" t="inlineStr">
         <is>
-          <t>2021-2025</t>
+          <t>2022-2025</t>
         </is>
       </c>
       <c r="U10" s="152" t="inlineStr">
         <is>
-          <t>NaTIS live vehicle population, December</t>
-        </is>
-      </c>
-      <c r="V10" s="152" t="inlineStr">
-        <is>
-          <t>No split by fuel or by age in this source</t>
-        </is>
-      </c>
+          <t>Eskom</t>
+        </is>
+      </c>
+      <c r="V10" s="152" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="152" t="inlineStr">
         <is>
-          <t>Motorcycles</t>
+          <t>Power generation diesel, energy balance</t>
         </is>
       </c>
       <c r="B11" s="153" t="inlineStr">
         <is>
-          <t>vehicles</t>
+          <t>million L/year</t>
         </is>
       </c>
       <c r="C11" s="153" t="inlineStr">
@@ -45170,640 +45279,582 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D11" s="166" t="n"/>
+      <c r="D11" s="154" t="n"/>
       <c r="E11" s="152" t="inlineStr">
         <is>
-          <t>Live (licensed) vehicles, all fuels together.</t>
-        </is>
-      </c>
-      <c r="F11" s="166" t="n"/>
-      <c r="G11" s="166" t="n"/>
-      <c r="H11" s="166" t="n"/>
-      <c r="I11" s="166" t="n"/>
-      <c r="J11" s="166" t="n"/>
-      <c r="K11" s="166" t="n"/>
-      <c r="L11" s="166" t="n"/>
-      <c r="M11" s="166" t="n"/>
-      <c r="N11" s="166" t="n"/>
-      <c r="O11" s="166" t="n">
-        <v>347631</v>
-      </c>
-      <c r="P11" s="166" t="n">
-        <v>346153</v>
-      </c>
-      <c r="Q11" s="166" t="n">
-        <v>349215</v>
-      </c>
-      <c r="R11" s="166" t="n">
-        <v>358817</v>
-      </c>
-      <c r="S11" s="166" t="n">
-        <v>372137</v>
-      </c>
+          <t>Electricity plants line of the energy balance.</t>
+        </is>
+      </c>
+      <c r="F11" s="154" t="n"/>
+      <c r="G11" s="154" t="n">
+        <v>1148.5</v>
+      </c>
+      <c r="H11" s="154" t="n">
+        <v>1178.599875</v>
+      </c>
+      <c r="I11" s="154" t="n">
+        <v>1247.8</v>
+      </c>
+      <c r="J11" s="154" t="n">
+        <v>1247.800125</v>
+      </c>
+      <c r="K11" s="154" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" s="154" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" s="154" t="n">
+        <v>28.72419140625</v>
+      </c>
+      <c r="N11" s="154" t="n"/>
+      <c r="O11" s="154" t="n"/>
+      <c r="P11" s="154" t="n"/>
+      <c r="Q11" s="154" t="n"/>
+      <c r="R11" s="154" t="n"/>
+      <c r="S11" s="154" t="n"/>
       <c r="T11" s="152" t="inlineStr">
         <is>
-          <t>2021-2025</t>
+          <t>2012-2021; near zero from 2017</t>
         </is>
       </c>
       <c r="U11" s="152" t="inlineStr">
         <is>
-          <t>NaTIS live vehicle population, December</t>
-        </is>
-      </c>
-      <c r="V11" s="152" t="inlineStr">
-        <is>
-          <t>No split by fuel or by age in this source</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="151" t="inlineStr">
-        <is>
-          <t>2. New vehicle sales</t>
-        </is>
-      </c>
-      <c r="B13" s="151" t="n"/>
-      <c r="C13" s="151" t="n"/>
-      <c r="D13" s="151" t="n"/>
-      <c r="E13" s="151" t="n"/>
-      <c r="F13" s="151" t="n"/>
-      <c r="G13" s="151" t="n"/>
-      <c r="H13" s="151" t="n"/>
-      <c r="I13" s="151" t="n"/>
-      <c r="J13" s="151" t="n"/>
-      <c r="K13" s="151" t="n"/>
-      <c r="L13" s="151" t="n"/>
-      <c r="M13" s="151" t="n"/>
-      <c r="N13" s="151" t="n"/>
-      <c r="O13" s="151" t="n"/>
-      <c r="P13" s="151" t="n"/>
-      <c r="Q13" s="151" t="n"/>
-      <c r="R13" s="151" t="n"/>
-      <c r="S13" s="151" t="n"/>
-      <c r="T13" s="151" t="n"/>
-      <c r="U13" s="151" t="n"/>
-      <c r="V13" s="151" t="n"/>
+          <t>Department energy balances</t>
+        </is>
+      </c>
+      <c r="V11" s="152" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="155" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="B12" s="156" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C12" s="156" t="inlineStr">
+        <is>
+          <t>Observation, then estimate</t>
+        </is>
+      </c>
+      <c r="D12" s="165" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E12" s="155" t="inlineStr">
+        <is>
+          <t>Energy balance to 2021; from 2022 generation times litres per kWh (column D). Driver: turbine output.</t>
+        </is>
+      </c>
+      <c r="F12" s="165">
+        <f>IF(ISNUMBER(F10),F10*$D$12,IF(ISNUMBER(F11),F11,""))</f>
+        <v/>
+      </c>
+      <c r="G12" s="165">
+        <f>IF(ISNUMBER(G10),G10*$D$12,IF(ISNUMBER(G11),G11,""))</f>
+        <v/>
+      </c>
+      <c r="H12" s="165">
+        <f>IF(ISNUMBER(H10),H10*$D$12,IF(ISNUMBER(H11),H11,""))</f>
+        <v/>
+      </c>
+      <c r="I12" s="165">
+        <f>IF(ISNUMBER(I10),I10*$D$12,IF(ISNUMBER(I11),I11,""))</f>
+        <v/>
+      </c>
+      <c r="J12" s="165">
+        <f>IF(ISNUMBER(J10),J10*$D$12,IF(ISNUMBER(J11),J11,""))</f>
+        <v/>
+      </c>
+      <c r="K12" s="165">
+        <f>IF(ISNUMBER(K10),K10*$D$12,IF(ISNUMBER(K11),K11,""))</f>
+        <v/>
+      </c>
+      <c r="L12" s="165">
+        <f>IF(ISNUMBER(L10),L10*$D$12,IF(ISNUMBER(L11),L11,""))</f>
+        <v/>
+      </c>
+      <c r="M12" s="165">
+        <f>IF(ISNUMBER(M10),M10*$D$12,IF(ISNUMBER(M11),M11,""))</f>
+        <v/>
+      </c>
+      <c r="N12" s="165">
+        <f>IF(ISNUMBER(N10),N10*$D$12,IF(ISNUMBER(N11),N11,""))</f>
+        <v/>
+      </c>
+      <c r="O12" s="165">
+        <f>IF(ISNUMBER(O10),O10*$D$12,IF(ISNUMBER(O11),O11,""))</f>
+        <v/>
+      </c>
+      <c r="P12" s="165">
+        <f>IF(ISNUMBER(P10),P10*$D$12,IF(ISNUMBER(P11),P11,""))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="165">
+        <f>IF(ISNUMBER(Q10),Q10*$D$12,IF(ISNUMBER(Q11),Q11,""))</f>
+        <v/>
+      </c>
+      <c r="R12" s="165">
+        <f>IF(ISNUMBER(R10),R10*$D$12,IF(ISNUMBER(R11),R11,""))</f>
+        <v/>
+      </c>
+      <c r="S12" s="165">
+        <f>IF(ISNUMBER(S10),S10*$D$12,IF(ISNUMBER(S11),S11,""))</f>
+        <v/>
+      </c>
+      <c r="T12" s="155" t="inlineStr">
+        <is>
+          <t>Estimated from 2022 at 0.31 litres per kWh</t>
+        </is>
+      </c>
+      <c r="U12" s="155" t="inlineStr">
+        <is>
+          <t>Eskom; parliamentary replies on diesel burn</t>
+        </is>
+      </c>
+      <c r="V12" s="155" t="inlineStr">
+        <is>
+          <t>The 0.31 factor is a proposal awaiting review</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="152" t="inlineStr">
-        <is>
-          <t>Cars, new sales</t>
-        </is>
-      </c>
-      <c r="B14" s="153" t="inlineStr">
-        <is>
-          <t>vehicles/year</t>
-        </is>
-      </c>
-      <c r="C14" s="153" t="inlineStr">
-        <is>
-          <t>Source observation</t>
-        </is>
-      </c>
-      <c r="D14" s="166" t="n"/>
-      <c r="E14" s="152" t="inlineStr">
-        <is>
-          <t>Actual new sales, all drivetrains.</t>
-        </is>
-      </c>
-      <c r="F14" s="166" t="n"/>
-      <c r="G14" s="166" t="n"/>
-      <c r="H14" s="166" t="n"/>
-      <c r="I14" s="166" t="n">
-        <v>412397</v>
-      </c>
-      <c r="J14" s="166" t="n">
-        <v>361265</v>
-      </c>
-      <c r="K14" s="166" t="n">
-        <v>368114</v>
-      </c>
-      <c r="L14" s="166" t="n">
-        <v>365247</v>
-      </c>
-      <c r="M14" s="166" t="n">
-        <v>355379</v>
-      </c>
-      <c r="N14" s="166" t="n">
-        <v>246541</v>
-      </c>
-      <c r="O14" s="166" t="n">
-        <v>304338</v>
-      </c>
-      <c r="P14" s="166" t="n">
-        <v>363681</v>
-      </c>
-      <c r="Q14" s="166" t="n">
-        <v>347377</v>
-      </c>
-      <c r="R14" s="166" t="n">
-        <v>351553</v>
-      </c>
-      <c r="S14" s="166" t="n">
-        <v>422463</v>
-      </c>
-      <c r="T14" s="152" t="inlineStr">
-        <is>
-          <t>2017-2025</t>
-        </is>
-      </c>
-      <c r="U14" s="152" t="inlineStr">
-        <is>
-          <t>naamsa industry vehicle sales</t>
-        </is>
-      </c>
-      <c r="V14" s="152" t="inlineStr"/>
+      <c r="A14" s="151" t="inlineStr">
+        <is>
+          <t>2. Road diesel, by difference</t>
+        </is>
+      </c>
+      <c r="B14" s="151" t="n"/>
+      <c r="C14" s="151" t="n"/>
+      <c r="D14" s="151" t="n"/>
+      <c r="E14" s="151" t="n"/>
+      <c r="F14" s="151" t="n"/>
+      <c r="G14" s="151" t="n"/>
+      <c r="H14" s="151" t="n"/>
+      <c r="I14" s="151" t="n"/>
+      <c r="J14" s="151" t="n"/>
+      <c r="K14" s="151" t="n"/>
+      <c r="L14" s="151" t="n"/>
+      <c r="M14" s="151" t="n"/>
+      <c r="N14" s="151" t="n"/>
+      <c r="O14" s="151" t="n"/>
+      <c r="P14" s="151" t="n"/>
+      <c r="Q14" s="151" t="n"/>
+      <c r="R14" s="151" t="n"/>
+      <c r="S14" s="151" t="n"/>
+      <c r="T14" s="151" t="n"/>
+      <c r="U14" s="151" t="n"/>
+      <c r="V14" s="151" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="152" t="inlineStr">
-        <is>
-          <t>Light commercial vehicles, new sales</t>
-        </is>
-      </c>
-      <c r="B15" s="153" t="inlineStr">
-        <is>
-          <t>vehicles/year</t>
-        </is>
-      </c>
-      <c r="C15" s="153" t="inlineStr">
-        <is>
-          <t>Source observation</t>
-        </is>
-      </c>
-      <c r="D15" s="166" t="n"/>
-      <c r="E15" s="152" t="inlineStr">
-        <is>
-          <t>Actual new sales, all drivetrains.</t>
-        </is>
-      </c>
-      <c r="F15" s="166" t="n"/>
-      <c r="G15" s="166" t="n"/>
-      <c r="H15" s="166" t="n"/>
-      <c r="I15" s="166" t="n">
-        <v>174812</v>
-      </c>
-      <c r="J15" s="166" t="n">
-        <v>159316</v>
-      </c>
-      <c r="K15" s="166" t="n">
-        <v>163317</v>
-      </c>
-      <c r="L15" s="166" t="n">
-        <v>159525</v>
-      </c>
-      <c r="M15" s="166" t="n">
-        <v>153221</v>
-      </c>
-      <c r="N15" s="166" t="n">
-        <v>110912</v>
-      </c>
-      <c r="O15" s="166" t="n">
-        <v>133078</v>
-      </c>
-      <c r="P15" s="166" t="n">
-        <v>135711</v>
-      </c>
-      <c r="Q15" s="166" t="n">
-        <v>151490</v>
-      </c>
-      <c r="R15" s="166" t="n">
-        <v>133375</v>
-      </c>
-      <c r="S15" s="166" t="n">
-        <v>143964</v>
-      </c>
-      <c r="T15" s="152" t="inlineStr">
-        <is>
-          <t>2017-2025</t>
-        </is>
-      </c>
-      <c r="U15" s="152" t="inlineStr">
-        <is>
-          <t>naamsa industry vehicle sales</t>
-        </is>
-      </c>
-      <c r="V15" s="152" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="152" t="inlineStr">
-        <is>
-          <t>Medium and heavy commercial vehicles, new sales</t>
-        </is>
-      </c>
-      <c r="B16" s="153" t="inlineStr">
-        <is>
-          <t>vehicles/year</t>
-        </is>
-      </c>
-      <c r="C16" s="153" t="inlineStr">
-        <is>
-          <t>Source observation</t>
-        </is>
-      </c>
-      <c r="D16" s="166" t="n"/>
-      <c r="E16" s="152" t="inlineStr">
-        <is>
-          <t>Actual new sales, all drivetrains.</t>
-        </is>
-      </c>
-      <c r="F16" s="166" t="n"/>
-      <c r="G16" s="166" t="n"/>
-      <c r="H16" s="166" t="n"/>
-      <c r="I16" s="166" t="n">
-        <v>30441</v>
-      </c>
-      <c r="J16" s="166" t="n">
-        <v>26972</v>
-      </c>
-      <c r="K16" s="166" t="n">
-        <v>26272</v>
-      </c>
-      <c r="L16" s="166" t="n">
-        <v>27449</v>
-      </c>
-      <c r="M16" s="166" t="n">
-        <v>27891</v>
-      </c>
-      <c r="N16" s="166" t="n">
-        <v>22614</v>
-      </c>
-      <c r="O16" s="166" t="n">
-        <v>26906</v>
-      </c>
-      <c r="P16" s="166" t="n">
-        <v>29942</v>
-      </c>
-      <c r="Q16" s="166" t="n">
-        <v>32690</v>
-      </c>
-      <c r="R16" s="166" t="n">
-        <v>31175</v>
-      </c>
-      <c r="S16" s="166" t="n">
-        <v>30911</v>
-      </c>
-      <c r="T16" s="152" t="inlineStr">
-        <is>
-          <t>2017-2025</t>
-        </is>
-      </c>
-      <c r="U16" s="152" t="inlineStr">
-        <is>
-          <t>naamsa industry vehicle sales</t>
-        </is>
-      </c>
-      <c r="V16" s="152" t="inlineStr"/>
+      <c r="A15" s="155" t="inlineStr">
+        <is>
+          <t>Road vehicles and uses not listed above</t>
+        </is>
+      </c>
+      <c r="B15" s="156" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C15" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D15" s="157" t="n"/>
+      <c r="E15" s="155" t="inlineStr">
+        <is>
+          <t>Sales less mining, manufacturing, agriculture and power. Includes rail, construction plant, private generators and ships' diesel, which no source separates.</t>
+        </is>
+      </c>
+      <c r="F15" s="157">
+        <f>IF(COUNT(F6,F7,F9)&lt;3,"",F6-F7-N(F8)-F9-N(F12))</f>
+        <v/>
+      </c>
+      <c r="G15" s="157">
+        <f>IF(COUNT(G6,G7,G9)&lt;3,"",G6-G7-N(G8)-G9-N(G12))</f>
+        <v/>
+      </c>
+      <c r="H15" s="157">
+        <f>IF(COUNT(H6,H7,H9)&lt;3,"",H6-H7-N(H8)-H9-N(H12))</f>
+        <v/>
+      </c>
+      <c r="I15" s="157">
+        <f>IF(COUNT(I6,I7,I9)&lt;3,"",I6-I7-N(I8)-I9-N(I12))</f>
+        <v/>
+      </c>
+      <c r="J15" s="157">
+        <f>IF(COUNT(J6,J7,J9)&lt;3,"",J6-J7-N(J8)-J9-N(J12))</f>
+        <v/>
+      </c>
+      <c r="K15" s="157">
+        <f>IF(COUNT(K6,K7,K9)&lt;3,"",K6-K7-N(K8)-K9-N(K12))</f>
+        <v/>
+      </c>
+      <c r="L15" s="157">
+        <f>IF(COUNT(L6,L7,L9)&lt;3,"",L6-L7-N(L8)-L9-N(L12))</f>
+        <v/>
+      </c>
+      <c r="M15" s="157">
+        <f>IF(COUNT(M6,M7,M9)&lt;3,"",M6-M7-N(M8)-M9-N(M12))</f>
+        <v/>
+      </c>
+      <c r="N15" s="157">
+        <f>IF(COUNT(N6,N7,N9)&lt;3,"",N6-N7-N(N8)-N9-N(N12))</f>
+        <v/>
+      </c>
+      <c r="O15" s="157">
+        <f>IF(COUNT(O6,O7,O9)&lt;3,"",O6-O7-N(O8)-O9-N(O12))</f>
+        <v/>
+      </c>
+      <c r="P15" s="157">
+        <f>IF(COUNT(P6,P7,P9)&lt;3,"",P6-P7-N(P8)-P9-N(P12))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="157">
+        <f>IF(COUNT(Q6,Q7,Q9)&lt;3,"",Q6-Q7-N(Q8)-Q9-N(Q12))</f>
+        <v/>
+      </c>
+      <c r="R15" s="157">
+        <f>IF(COUNT(R6,R7,R9)&lt;3,"",R6-R7-N(R8)-R9-N(R12))</f>
+        <v/>
+      </c>
+      <c r="S15" s="157">
+        <f>IF(COUNT(S6,S7,S9)&lt;3,"",S6-S7-N(S8)-S9-N(S12))</f>
+        <v/>
+      </c>
+      <c r="T15" s="155" t="inlineStr"/>
+      <c r="U15" s="155" t="inlineStr"/>
+      <c r="V15" s="155" t="inlineStr">
+        <is>
+          <t>The balance counts mining and farm diesel by buyer, so some of it is burned on public roads</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="152" t="inlineStr">
-        <is>
-          <t>All segments, new sales</t>
-        </is>
-      </c>
-      <c r="B17" s="153" t="inlineStr">
-        <is>
-          <t>vehicles/year</t>
-        </is>
-      </c>
-      <c r="C17" s="153" t="inlineStr">
-        <is>
-          <t>Source observation</t>
-        </is>
-      </c>
-      <c r="D17" s="166" t="n"/>
-      <c r="E17" s="152" t="inlineStr">
-        <is>
-          <t>Total market as reported.</t>
-        </is>
-      </c>
-      <c r="F17" s="166" t="n"/>
-      <c r="G17" s="166" t="n"/>
-      <c r="H17" s="166" t="n"/>
-      <c r="I17" s="166" t="n">
-        <v>617650</v>
-      </c>
-      <c r="J17" s="166" t="n">
-        <v>547552</v>
-      </c>
-      <c r="K17" s="166" t="n">
-        <v>557719</v>
-      </c>
-      <c r="L17" s="166" t="n">
-        <v>552221</v>
-      </c>
-      <c r="M17" s="166" t="n">
-        <v>536486</v>
-      </c>
-      <c r="N17" s="166" t="n">
-        <v>380065</v>
-      </c>
-      <c r="O17" s="166" t="n">
-        <v>464322</v>
-      </c>
-      <c r="P17" s="166" t="n">
-        <v>529335</v>
-      </c>
-      <c r="Q17" s="166" t="n">
-        <v>531557</v>
-      </c>
-      <c r="R17" s="166" t="n">
-        <v>516103</v>
-      </c>
-      <c r="S17" s="166" t="n">
-        <v>597338</v>
-      </c>
-      <c r="T17" s="152" t="inlineStr">
-        <is>
-          <t>2017-2025</t>
-        </is>
-      </c>
-      <c r="U17" s="152" t="inlineStr">
-        <is>
-          <t>naamsa industry vehicle sales</t>
-        </is>
-      </c>
-      <c r="V17" s="152" t="inlineStr"/>
+      <c r="A17" s="151" t="inlineStr">
+        <is>
+          <t>3. Road diesel split by vehicle group (approach A: the study's shares held)</t>
+        </is>
+      </c>
+      <c r="B17" s="151" t="n"/>
+      <c r="C17" s="151" t="n"/>
+      <c r="D17" s="151" t="n"/>
+      <c r="E17" s="151" t="n"/>
+      <c r="F17" s="151" t="n"/>
+      <c r="G17" s="151" t="n"/>
+      <c r="H17" s="151" t="n"/>
+      <c r="I17" s="151" t="n"/>
+      <c r="J17" s="151" t="n"/>
+      <c r="K17" s="151" t="n"/>
+      <c r="L17" s="151" t="n"/>
+      <c r="M17" s="151" t="n"/>
+      <c r="N17" s="151" t="n"/>
+      <c r="O17" s="151" t="n"/>
+      <c r="P17" s="151" t="n"/>
+      <c r="Q17" s="151" t="n"/>
+      <c r="R17" s="151" t="n"/>
+      <c r="S17" s="151" t="n"/>
+      <c r="T17" s="151" t="n"/>
+      <c r="U17" s="151" t="n"/>
+      <c r="V17" s="151" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="155" t="inlineStr">
-        <is>
-          <t>Cars share of new sales</t>
-        </is>
-      </c>
-      <c r="B18" s="156" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C18" s="156" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D18" s="167" t="n">
-        <v>78</v>
-      </c>
-      <c r="E18" s="155" t="inlineStr">
-        <is>
-          <t>Observed share. Column D is the model's fixed split of new vehicles.</t>
-        </is>
-      </c>
-      <c r="F18" s="167">
-        <f>IF(COUNT(F14,F17)&lt;2,"",F14/F17*100)</f>
-        <v/>
-      </c>
-      <c r="G18" s="167">
-        <f>IF(COUNT(G14,G17)&lt;2,"",G14/G17*100)</f>
-        <v/>
-      </c>
-      <c r="H18" s="167">
-        <f>IF(COUNT(H14,H17)&lt;2,"",H14/H17*100)</f>
-        <v/>
-      </c>
-      <c r="I18" s="167">
-        <f>IF(COUNT(I14,I17)&lt;2,"",I14/I17*100)</f>
-        <v/>
-      </c>
-      <c r="J18" s="167">
-        <f>IF(COUNT(J14,J17)&lt;2,"",J14/J17*100)</f>
-        <v/>
-      </c>
-      <c r="K18" s="167">
-        <f>IF(COUNT(K14,K17)&lt;2,"",K14/K17*100)</f>
-        <v/>
-      </c>
-      <c r="L18" s="167">
-        <f>IF(COUNT(L14,L17)&lt;2,"",L14/L17*100)</f>
-        <v/>
-      </c>
-      <c r="M18" s="167">
-        <f>IF(COUNT(M14,M17)&lt;2,"",M14/M17*100)</f>
-        <v/>
-      </c>
-      <c r="N18" s="167">
-        <f>IF(COUNT(N14,N17)&lt;2,"",N14/N17*100)</f>
-        <v/>
-      </c>
-      <c r="O18" s="167">
-        <f>IF(COUNT(O14,O17)&lt;2,"",O14/O17*100)</f>
-        <v/>
-      </c>
-      <c r="P18" s="167">
-        <f>IF(COUNT(P14,P17)&lt;2,"",P14/P17*100)</f>
-        <v/>
-      </c>
-      <c r="Q18" s="167">
-        <f>IF(COUNT(Q14,Q17)&lt;2,"",Q14/Q17*100)</f>
-        <v/>
-      </c>
-      <c r="R18" s="167">
-        <f>IF(COUNT(R14,R17)&lt;2,"",R14/R17*100)</f>
-        <v/>
-      </c>
-      <c r="S18" s="167">
-        <f>IF(COUNT(S14,S17)&lt;2,"",S14/S17*100)</f>
-        <v/>
-      </c>
-      <c r="T18" s="155" t="inlineStr">
-        <is>
-          <t>Model setting in column D</t>
-        </is>
-      </c>
-      <c r="U18" s="155" t="inlineStr">
-        <is>
-          <t>assumptions/2026/vehicles.yaml: new_vehicle_segment_split</t>
-        </is>
-      </c>
-      <c r="V18" s="155" t="inlineStr"/>
+      <c r="A18" s="161" t="inlineStr">
+        <is>
+          <t>Heavy vehicles</t>
+        </is>
+      </c>
+      <c r="B18" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C18" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D18" s="164" t="n">
+        <v>60.53064018906874</v>
+      </c>
+      <c r="E18" s="161" t="inlineStr">
+        <is>
+          <t>Road diesel times the group's share in the study (column D, %). Driver: freight activity, road-to-rail shift, electric share of new trucks.</t>
+        </is>
+      </c>
+      <c r="F18" s="164">
+        <f>IF(ISNUMBER(F15),F15*$D$18/100,"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="164">
+        <f>IF(ISNUMBER(G15),G15*$D$18/100,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="164">
+        <f>IF(ISNUMBER(H15),H15*$D$18/100,"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="164">
+        <f>IF(ISNUMBER(I15),I15*$D$18/100,"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="164">
+        <f>IF(ISNUMBER(J15),J15*$D$18/100,"")</f>
+        <v/>
+      </c>
+      <c r="K18" s="164">
+        <f>IF(ISNUMBER(K15),K15*$D$18/100,"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="164">
+        <f>IF(ISNUMBER(L15),L15*$D$18/100,"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="164">
+        <f>IF(ISNUMBER(M15),M15*$D$18/100,"")</f>
+        <v/>
+      </c>
+      <c r="N18" s="164">
+        <f>IF(ISNUMBER(N15),N15*$D$18/100,"")</f>
+        <v/>
+      </c>
+      <c r="O18" s="164">
+        <f>IF(ISNUMBER(O15),O15*$D$18/100,"")</f>
+        <v/>
+      </c>
+      <c r="P18" s="164">
+        <f>IF(ISNUMBER(P15),P15*$D$18/100,"")</f>
+        <v/>
+      </c>
+      <c r="Q18" s="164">
+        <f>IF(ISNUMBER(Q15),Q15*$D$18/100,"")</f>
+        <v/>
+      </c>
+      <c r="R18" s="164">
+        <f>IF(ISNUMBER(R15),R15*$D$18/100,"")</f>
+        <v/>
+      </c>
+      <c r="S18" s="164">
+        <f>IF(ISNUMBER(S15),S15*$D$18/100,"")</f>
+        <v/>
+      </c>
+      <c r="T18" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; shares are for the 2010 fleet</t>
+        </is>
+      </c>
+      <c r="U18" s="161" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018), vehicles x distance x fuel use by class</t>
+        </is>
+      </c>
+      <c r="V18" s="161" t="inlineStr">
+        <is>
+          <t>Diesel vehicles have doubled since 2010 while trucks grew about a quarter, so today's heavy share is probably lower</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="155" t="inlineStr">
-        <is>
-          <t>Light commercial share of new sales</t>
-        </is>
-      </c>
-      <c r="B19" s="156" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C19" s="156" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D19" s="167" t="n">
-        <v>18</v>
-      </c>
-      <c r="E19" s="155" t="inlineStr">
-        <is>
-          <t>Observed share. Column D is the model's fixed split of new vehicles.</t>
-        </is>
-      </c>
-      <c r="F19" s="167">
-        <f>IF(COUNT(F15,F17)&lt;2,"",F15/F17*100)</f>
-        <v/>
-      </c>
-      <c r="G19" s="167">
-        <f>IF(COUNT(G15,G17)&lt;2,"",G15/G17*100)</f>
-        <v/>
-      </c>
-      <c r="H19" s="167">
-        <f>IF(COUNT(H15,H17)&lt;2,"",H15/H17*100)</f>
-        <v/>
-      </c>
-      <c r="I19" s="167">
-        <f>IF(COUNT(I15,I17)&lt;2,"",I15/I17*100)</f>
-        <v/>
-      </c>
-      <c r="J19" s="167">
-        <f>IF(COUNT(J15,J17)&lt;2,"",J15/J17*100)</f>
-        <v/>
-      </c>
-      <c r="K19" s="167">
-        <f>IF(COUNT(K15,K17)&lt;2,"",K15/K17*100)</f>
-        <v/>
-      </c>
-      <c r="L19" s="167">
-        <f>IF(COUNT(L15,L17)&lt;2,"",L15/L17*100)</f>
-        <v/>
-      </c>
-      <c r="M19" s="167">
-        <f>IF(COUNT(M15,M17)&lt;2,"",M15/M17*100)</f>
-        <v/>
-      </c>
-      <c r="N19" s="167">
-        <f>IF(COUNT(N15,N17)&lt;2,"",N15/N17*100)</f>
-        <v/>
-      </c>
-      <c r="O19" s="167">
-        <f>IF(COUNT(O15,O17)&lt;2,"",O15/O17*100)</f>
-        <v/>
-      </c>
-      <c r="P19" s="167">
-        <f>IF(COUNT(P15,P17)&lt;2,"",P15/P17*100)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="167">
-        <f>IF(COUNT(Q15,Q17)&lt;2,"",Q15/Q17*100)</f>
-        <v/>
-      </c>
-      <c r="R19" s="167">
-        <f>IF(COUNT(R15,R17)&lt;2,"",R15/R17*100)</f>
-        <v/>
-      </c>
-      <c r="S19" s="167">
-        <f>IF(COUNT(S15,S17)&lt;2,"",S15/S17*100)</f>
-        <v/>
-      </c>
-      <c r="T19" s="155" t="inlineStr">
-        <is>
-          <t>Model setting in column D</t>
-        </is>
-      </c>
-      <c r="U19" s="155" t="inlineStr">
-        <is>
-          <t>assumptions/2026/vehicles.yaml: new_vehicle_segment_split</t>
-        </is>
-      </c>
-      <c r="V19" s="155" t="inlineStr"/>
+      <c r="A19" s="161" t="inlineStr">
+        <is>
+          <t>Light vehicles</t>
+        </is>
+      </c>
+      <c r="B19" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C19" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D19" s="164" t="n">
+        <v>26.9915704235799</v>
+      </c>
+      <c r="E19" s="161" t="inlineStr">
+        <is>
+          <t>Road diesel times the group's share in the study (column D, %). Driver: fleet and distance, electric share of new sales.</t>
+        </is>
+      </c>
+      <c r="F19" s="164">
+        <f>IF(ISNUMBER(F15),F15*$D$19/100,"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="164">
+        <f>IF(ISNUMBER(G15),G15*$D$19/100,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="164">
+        <f>IF(ISNUMBER(H15),H15*$D$19/100,"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="164">
+        <f>IF(ISNUMBER(I15),I15*$D$19/100,"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="164">
+        <f>IF(ISNUMBER(J15),J15*$D$19/100,"")</f>
+        <v/>
+      </c>
+      <c r="K19" s="164">
+        <f>IF(ISNUMBER(K15),K15*$D$19/100,"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="164">
+        <f>IF(ISNUMBER(L15),L15*$D$19/100,"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="164">
+        <f>IF(ISNUMBER(M15),M15*$D$19/100,"")</f>
+        <v/>
+      </c>
+      <c r="N19" s="164">
+        <f>IF(ISNUMBER(N15),N15*$D$19/100,"")</f>
+        <v/>
+      </c>
+      <c r="O19" s="164">
+        <f>IF(ISNUMBER(O15),O15*$D$19/100,"")</f>
+        <v/>
+      </c>
+      <c r="P19" s="164">
+        <f>IF(ISNUMBER(P15),P15*$D$19/100,"")</f>
+        <v/>
+      </c>
+      <c r="Q19" s="164">
+        <f>IF(ISNUMBER(Q15),Q15*$D$19/100,"")</f>
+        <v/>
+      </c>
+      <c r="R19" s="164">
+        <f>IF(ISNUMBER(R15),R15*$D$19/100,"")</f>
+        <v/>
+      </c>
+      <c r="S19" s="164">
+        <f>IF(ISNUMBER(S15),S15*$D$19/100,"")</f>
+        <v/>
+      </c>
+      <c r="T19" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; shares are for the 2010 fleet</t>
+        </is>
+      </c>
+      <c r="U19" s="161" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018), vehicles x distance x fuel use by class</t>
+        </is>
+      </c>
+      <c r="V19" s="161" t="inlineStr">
+        <is>
+          <t>Diesel vehicles have doubled since 2010 while trucks grew about a quarter, so today's heavy share is probably lower</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="155" t="inlineStr">
-        <is>
-          <t>Medium and heavy commercial share of new sales</t>
-        </is>
-      </c>
-      <c r="B20" s="156" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C20" s="156" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D20" s="167" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" s="155" t="inlineStr">
-        <is>
-          <t>Observed share. Column D is the model's fixed split of new vehicles.</t>
-        </is>
-      </c>
-      <c r="F20" s="167">
-        <f>IF(COUNT(F16,F17)&lt;2,"",F16/F17*100)</f>
-        <v/>
-      </c>
-      <c r="G20" s="167">
-        <f>IF(COUNT(G16,G17)&lt;2,"",G16/G17*100)</f>
-        <v/>
-      </c>
-      <c r="H20" s="167">
-        <f>IF(COUNT(H16,H17)&lt;2,"",H16/H17*100)</f>
-        <v/>
-      </c>
-      <c r="I20" s="167">
-        <f>IF(COUNT(I16,I17)&lt;2,"",I16/I17*100)</f>
-        <v/>
-      </c>
-      <c r="J20" s="167">
-        <f>IF(COUNT(J16,J17)&lt;2,"",J16/J17*100)</f>
-        <v/>
-      </c>
-      <c r="K20" s="167">
-        <f>IF(COUNT(K16,K17)&lt;2,"",K16/K17*100)</f>
-        <v/>
-      </c>
-      <c r="L20" s="167">
-        <f>IF(COUNT(L16,L17)&lt;2,"",L16/L17*100)</f>
-        <v/>
-      </c>
-      <c r="M20" s="167">
-        <f>IF(COUNT(M16,M17)&lt;2,"",M16/M17*100)</f>
-        <v/>
-      </c>
-      <c r="N20" s="167">
-        <f>IF(COUNT(N16,N17)&lt;2,"",N16/N17*100)</f>
-        <v/>
-      </c>
-      <c r="O20" s="167">
-        <f>IF(COUNT(O16,O17)&lt;2,"",O16/O17*100)</f>
-        <v/>
-      </c>
-      <c r="P20" s="167">
-        <f>IF(COUNT(P16,P17)&lt;2,"",P16/P17*100)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="167">
-        <f>IF(COUNT(Q16,Q17)&lt;2,"",Q16/Q17*100)</f>
-        <v/>
-      </c>
-      <c r="R20" s="167">
-        <f>IF(COUNT(R16,R17)&lt;2,"",R16/R17*100)</f>
-        <v/>
-      </c>
-      <c r="S20" s="167">
-        <f>IF(COUNT(S16,S17)&lt;2,"",S16/S17*100)</f>
-        <v/>
-      </c>
-      <c r="T20" s="155" t="inlineStr">
-        <is>
-          <t>Model setting in column D</t>
-        </is>
-      </c>
-      <c r="U20" s="155" t="inlineStr">
-        <is>
-          <t>assumptions/2026/vehicles.yaml: new_vehicle_segment_split</t>
-        </is>
-      </c>
-      <c r="V20" s="155" t="inlineStr"/>
+      <c r="A20" s="161" t="inlineStr">
+        <is>
+          <t>Passenger vehicles</t>
+        </is>
+      </c>
+      <c r="B20" s="162" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C20" s="162" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D20" s="164" t="n">
+        <v>12.47778938735136</v>
+      </c>
+      <c r="E20" s="161" t="inlineStr">
+        <is>
+          <t>Road diesel times the group's share in the study (column D, %). Driver: fleet and distance, electric share of new sales.</t>
+        </is>
+      </c>
+      <c r="F20" s="164">
+        <f>IF(ISNUMBER(F15),F15*$D$20/100,"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="164">
+        <f>IF(ISNUMBER(G15),G15*$D$20/100,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="164">
+        <f>IF(ISNUMBER(H15),H15*$D$20/100,"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="164">
+        <f>IF(ISNUMBER(I15),I15*$D$20/100,"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="164">
+        <f>IF(ISNUMBER(J15),J15*$D$20/100,"")</f>
+        <v/>
+      </c>
+      <c r="K20" s="164">
+        <f>IF(ISNUMBER(K15),K15*$D$20/100,"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="164">
+        <f>IF(ISNUMBER(L15),L15*$D$20/100,"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="164">
+        <f>IF(ISNUMBER(M15),M15*$D$20/100,"")</f>
+        <v/>
+      </c>
+      <c r="N20" s="164">
+        <f>IF(ISNUMBER(N15),N15*$D$20/100,"")</f>
+        <v/>
+      </c>
+      <c r="O20" s="164">
+        <f>IF(ISNUMBER(O15),O15*$D$20/100,"")</f>
+        <v/>
+      </c>
+      <c r="P20" s="164">
+        <f>IF(ISNUMBER(P15),P15*$D$20/100,"")</f>
+        <v/>
+      </c>
+      <c r="Q20" s="164">
+        <f>IF(ISNUMBER(Q15),Q15*$D$20/100,"")</f>
+        <v/>
+      </c>
+      <c r="R20" s="164">
+        <f>IF(ISNUMBER(R15),R15*$D$20/100,"")</f>
+        <v/>
+      </c>
+      <c r="S20" s="164">
+        <f>IF(ISNUMBER(S15),S15*$D$20/100,"")</f>
+        <v/>
+      </c>
+      <c r="T20" s="161" t="inlineStr">
+        <is>
+          <t>Estimate; shares are for the 2010 fleet</t>
+        </is>
+      </c>
+      <c r="U20" s="161" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018), vehicles x distance x fuel use by class</t>
+        </is>
+      </c>
+      <c r="V20" s="161" t="inlineStr">
+        <is>
+          <t>Diesel vehicles have doubled since 2010 while trucks grew about a quarter, so today's heavy share is probably lower</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="151" t="inlineStr">
         <is>
-          <t>3. Apparent retirements: last December's stock plus this year's sales less this December's stock</t>
+          <t>4. Checks</t>
         </is>
       </c>
       <c r="B22" s="151" t="n"/>
@@ -45831,12 +45882,12 @@
     <row r="23">
       <c r="A23" s="155" t="inlineStr">
         <is>
-          <t>Cars retired</t>
+          <t>Sum of the six branches</t>
         </is>
       </c>
       <c r="B23" s="156" t="inlineStr">
         <is>
-          <t>vehicles/year</t>
+          <t>million L/year</t>
         </is>
       </c>
       <c r="C23" s="156" t="inlineStr">
@@ -45844,63 +45895,66 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D23" s="168" t="n"/>
+      <c r="D23" s="157" t="n"/>
       <c r="E23" s="155" t="inlineStr">
         <is>
-          <t>Includes deregistration, export and write-off; used imports and re-registration would lower it.</t>
-        </is>
-      </c>
-      <c r="F23" s="168" t="n"/>
-      <c r="G23" s="168">
-        <f>IF(COUNT(F6,G6,G14)&lt;3,"",F6+G14-G6)</f>
-        <v/>
-      </c>
-      <c r="H23" s="168">
-        <f>IF(COUNT(G6,H6,H14)&lt;3,"",G6+H14-H6)</f>
-        <v/>
-      </c>
-      <c r="I23" s="168">
-        <f>IF(COUNT(H6,I6,I14)&lt;3,"",H6+I14-I6)</f>
-        <v/>
-      </c>
-      <c r="J23" s="168">
-        <f>IF(COUNT(I6,J6,J14)&lt;3,"",I6+J14-J6)</f>
-        <v/>
-      </c>
-      <c r="K23" s="168">
-        <f>IF(COUNT(J6,K6,K14)&lt;3,"",J6+K14-K6)</f>
-        <v/>
-      </c>
-      <c r="L23" s="168">
-        <f>IF(COUNT(K6,L6,L14)&lt;3,"",K6+L14-L6)</f>
-        <v/>
-      </c>
-      <c r="M23" s="168">
-        <f>IF(COUNT(L6,M6,M14)&lt;3,"",L6+M14-M6)</f>
-        <v/>
-      </c>
-      <c r="N23" s="168">
-        <f>IF(COUNT(M6,N6,N14)&lt;3,"",M6+N14-N6)</f>
-        <v/>
-      </c>
-      <c r="O23" s="168">
-        <f>IF(COUNT(N6,O6,O14)&lt;3,"",N6+O14-O6)</f>
-        <v/>
-      </c>
-      <c r="P23" s="168">
-        <f>IF(COUNT(O6,P6,P14)&lt;3,"",O6+P14-P6)</f>
-        <v/>
-      </c>
-      <c r="Q23" s="168">
-        <f>IF(COUNT(P6,Q6,Q14)&lt;3,"",P6+Q14-Q6)</f>
-        <v/>
-      </c>
-      <c r="R23" s="168">
-        <f>IF(COUNT(Q6,R6,R14)&lt;3,"",Q6+R14-R6)</f>
-        <v/>
-      </c>
-      <c r="S23" s="168">
-        <f>IF(COUNT(R6,S6,S14)&lt;3,"",R6+S14-S6)</f>
+          <t>Should equal diesel sales used.</t>
+        </is>
+      </c>
+      <c r="F23" s="157">
+        <f>IF(ISNUMBER(F15),F7+N(F8)+F9+N(F12)+F18+F19+F20,"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="157">
+        <f>IF(ISNUMBER(G15),G7+N(G8)+G9+N(G12)+G18+G19+G20,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="157">
+        <f>IF(ISNUMBER(H15),H7+N(H8)+H9+N(H12)+H18+H19+H20,"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="157">
+        <f>IF(ISNUMBER(I15),I7+N(I8)+I9+N(I12)+I18+I19+I20,"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="157">
+        <f>IF(ISNUMBER(J15),J7+N(J8)+J9+N(J12)+J18+J19+J20,"")</f>
+        <v/>
+      </c>
+      <c r="K23" s="157">
+        <f>IF(ISNUMBER(K15),K7+N(K8)+K9+N(K12)+K18+K19+K20,"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="157">
+        <f>IF(ISNUMBER(L15),L7+N(L8)+L9+N(L12)+L18+L19+L20,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="157">
+        <f>IF(ISNUMBER(M15),M7+N(M8)+M9+N(M12)+M18+M19+M20,"")</f>
+        <v/>
+      </c>
+      <c r="N23" s="157">
+        <f>IF(ISNUMBER(N15),N7+N(N8)+N9+N(N12)+N18+N19+N20,"")</f>
+        <v/>
+      </c>
+      <c r="O23" s="157">
+        <f>IF(ISNUMBER(O15),O7+N(O8)+O9+N(O12)+O18+O19+O20,"")</f>
+        <v/>
+      </c>
+      <c r="P23" s="157">
+        <f>IF(ISNUMBER(P15),P7+N(P8)+P9+N(P12)+P18+P19+P20,"")</f>
+        <v/>
+      </c>
+      <c r="Q23" s="157">
+        <f>IF(ISNUMBER(Q15),Q7+N(Q8)+Q9+N(Q12)+Q18+Q19+Q20,"")</f>
+        <v/>
+      </c>
+      <c r="R23" s="157">
+        <f>IF(ISNUMBER(R15),R7+N(R8)+R9+N(R12)+R18+R19+R20,"")</f>
+        <v/>
+      </c>
+      <c r="S23" s="157">
+        <f>IF(ISNUMBER(S15),S7+N(S8)+S9+N(S12)+S18+S19+S20,"")</f>
         <v/>
       </c>
       <c r="T23" s="155" t="inlineStr"/>
@@ -45908,103 +45962,66 @@
       <c r="V23" s="155" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="155" t="inlineStr">
-        <is>
-          <t>Cars retirement rate</t>
-        </is>
-      </c>
-      <c r="B24" s="156" t="inlineStr">
-        <is>
-          <t>% of last December's stock</t>
-        </is>
-      </c>
-      <c r="C24" s="156" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D24" s="167" t="n">
-        <v>4</v>
-      </c>
-      <c r="E24" s="155" t="inlineStr">
-        <is>
-          <t>Retired divided by last December's stock. Column D is the model's scrappage rate.</t>
-        </is>
-      </c>
-      <c r="F24" s="167" t="n"/>
-      <c r="G24" s="167">
-        <f>IF(ISNUMBER(G23),G23/F6*100,"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="167">
-        <f>IF(ISNUMBER(H23),H23/G6*100,"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="167">
-        <f>IF(ISNUMBER(I23),I23/H6*100,"")</f>
-        <v/>
-      </c>
-      <c r="J24" s="167">
-        <f>IF(ISNUMBER(J23),J23/I6*100,"")</f>
-        <v/>
-      </c>
-      <c r="K24" s="167">
-        <f>IF(ISNUMBER(K23),K23/J6*100,"")</f>
-        <v/>
-      </c>
-      <c r="L24" s="167">
-        <f>IF(ISNUMBER(L23),L23/K6*100,"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="167">
-        <f>IF(ISNUMBER(M23),M23/L6*100,"")</f>
-        <v/>
-      </c>
-      <c r="N24" s="167">
-        <f>IF(ISNUMBER(N23),N23/M6*100,"")</f>
-        <v/>
-      </c>
-      <c r="O24" s="167">
-        <f>IF(ISNUMBER(O23),O23/N6*100,"")</f>
-        <v/>
-      </c>
-      <c r="P24" s="167">
-        <f>IF(ISNUMBER(P23),P23/O6*100,"")</f>
-        <v/>
-      </c>
-      <c r="Q24" s="167">
-        <f>IF(ISNUMBER(Q23),Q23/P6*100,"")</f>
-        <v/>
-      </c>
-      <c r="R24" s="167">
-        <f>IF(ISNUMBER(R23),R23/Q6*100,"")</f>
-        <v/>
-      </c>
-      <c r="S24" s="167">
-        <f>IF(ISNUMBER(S23),S23/R6*100,"")</f>
-        <v/>
-      </c>
-      <c r="T24" s="155" t="inlineStr">
-        <is>
-          <t>Model setting in column D</t>
-        </is>
-      </c>
-      <c r="U24" s="155" t="inlineStr">
-        <is>
-          <t>assumptions/2026/vehicles.yaml: scrappage_rate</t>
-        </is>
-      </c>
-      <c r="V24" s="155" t="inlineStr"/>
+      <c r="A24" s="158" t="inlineStr">
+        <is>
+          <t>Fuel bought by road freight businesses</t>
+        </is>
+      </c>
+      <c r="B24" s="159" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C24" s="159" t="inlineStr">
+        <is>
+          <t>Source observation, converted</t>
+        </is>
+      </c>
+      <c r="D24" s="160" t="n"/>
+      <c r="E24" s="158" t="inlineStr">
+        <is>
+          <t>Stats SA rand figure divided by the average inland wholesale diesel price over the survey year (R14.58 and R22.66 a litre). Hire-and-reward operators only; may include some petrol and lubricants.</t>
+        </is>
+      </c>
+      <c r="F24" s="160" t="n"/>
+      <c r="G24" s="160" t="n"/>
+      <c r="H24" s="160" t="n"/>
+      <c r="I24" s="160" t="n"/>
+      <c r="J24" s="160" t="n"/>
+      <c r="K24" s="160" t="n"/>
+      <c r="L24" s="160" t="n"/>
+      <c r="M24" s="160" t="n">
+        <v>2855.120137544933</v>
+      </c>
+      <c r="N24" s="160" t="n"/>
+      <c r="O24" s="160" t="n"/>
+      <c r="P24" s="160" t="n"/>
+      <c r="Q24" s="160" t="n">
+        <v>3154.341754930314</v>
+      </c>
+      <c r="R24" s="160" t="n"/>
+      <c r="S24" s="160" t="n"/>
+      <c r="T24" s="158" t="inlineStr">
+        <is>
+          <t>2019 and 2023 only</t>
+        </is>
+      </c>
+      <c r="U24" s="158" t="inlineStr">
+        <is>
+          <t>Stats SA, Transport and storage industry 2023 (Report 71-02-01), Table 20</t>
+        </is>
+      </c>
+      <c r="V24" s="158" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="155" t="inlineStr">
         <is>
-          <t>Light commercial vehicles retired</t>
+          <t>Heavy vehicles less the road freight figure</t>
         </is>
       </c>
       <c r="B25" s="156" t="inlineStr">
         <is>
-          <t>vehicles/year</t>
+          <t>million L/year</t>
         </is>
       </c>
       <c r="C25" s="156" t="inlineStr">
@@ -46012,63 +46029,66 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D25" s="168" t="n"/>
+      <c r="D25" s="157" t="n"/>
       <c r="E25" s="155" t="inlineStr">
         <is>
-          <t>Includes deregistration, export and write-off; used imports and re-registration would lower it.</t>
-        </is>
-      </c>
-      <c r="F25" s="168" t="n"/>
-      <c r="G25" s="168">
-        <f>IF(COUNT(F7,G7,G15)&lt;3,"",F7+G15-G7)</f>
-        <v/>
-      </c>
-      <c r="H25" s="168">
-        <f>IF(COUNT(G7,H7,H15)&lt;3,"",G7+H15-H7)</f>
-        <v/>
-      </c>
-      <c r="I25" s="168">
-        <f>IF(COUNT(H7,I7,I15)&lt;3,"",H7+I15-I7)</f>
-        <v/>
-      </c>
-      <c r="J25" s="168">
-        <f>IF(COUNT(I7,J7,J15)&lt;3,"",I7+J15-J7)</f>
-        <v/>
-      </c>
-      <c r="K25" s="168">
-        <f>IF(COUNT(J7,K7,K15)&lt;3,"",J7+K15-K7)</f>
-        <v/>
-      </c>
-      <c r="L25" s="168">
-        <f>IF(COUNT(K7,L7,L15)&lt;3,"",K7+L15-L7)</f>
-        <v/>
-      </c>
-      <c r="M25" s="168">
-        <f>IF(COUNT(L7,M7,M15)&lt;3,"",L7+M15-M7)</f>
-        <v/>
-      </c>
-      <c r="N25" s="168">
-        <f>IF(COUNT(M7,N7,N15)&lt;3,"",M7+N15-N7)</f>
-        <v/>
-      </c>
-      <c r="O25" s="168">
-        <f>IF(COUNT(N7,O7,O15)&lt;3,"",N7+O15-O7)</f>
-        <v/>
-      </c>
-      <c r="P25" s="168">
-        <f>IF(COUNT(O7,P7,P15)&lt;3,"",O7+P15-P7)</f>
-        <v/>
-      </c>
-      <c r="Q25" s="168">
-        <f>IF(COUNT(P7,Q7,Q15)&lt;3,"",P7+Q15-Q7)</f>
-        <v/>
-      </c>
-      <c r="R25" s="168">
-        <f>IF(COUNT(Q7,R7,R15)&lt;3,"",Q7+R15-R7)</f>
-        <v/>
-      </c>
-      <c r="S25" s="168">
-        <f>IF(COUNT(R7,S7,S15)&lt;3,"",R7+S15-S7)</f>
+          <t>Should be positive: the survey leaves out trucks run by firms for their own goods.</t>
+        </is>
+      </c>
+      <c r="F25" s="157">
+        <f>IF(COUNT(F18,F24)&lt;2,"",F18-F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="157">
+        <f>IF(COUNT(G18,G24)&lt;2,"",G18-G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="157">
+        <f>IF(COUNT(H18,H24)&lt;2,"",H18-H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="157">
+        <f>IF(COUNT(I18,I24)&lt;2,"",I18-I24)</f>
+        <v/>
+      </c>
+      <c r="J25" s="157">
+        <f>IF(COUNT(J18,J24)&lt;2,"",J18-J24)</f>
+        <v/>
+      </c>
+      <c r="K25" s="157">
+        <f>IF(COUNT(K18,K24)&lt;2,"",K18-K24)</f>
+        <v/>
+      </c>
+      <c r="L25" s="157">
+        <f>IF(COUNT(L18,L24)&lt;2,"",L18-L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="157">
+        <f>IF(COUNT(M18,M24)&lt;2,"",M18-M24)</f>
+        <v/>
+      </c>
+      <c r="N25" s="157">
+        <f>IF(COUNT(N18,N24)&lt;2,"",N18-N24)</f>
+        <v/>
+      </c>
+      <c r="O25" s="157">
+        <f>IF(COUNT(O18,O24)&lt;2,"",O18-O24)</f>
+        <v/>
+      </c>
+      <c r="P25" s="157">
+        <f>IF(COUNT(P18,P24)&lt;2,"",P18-P24)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="157">
+        <f>IF(COUNT(Q18,Q24)&lt;2,"",Q18-Q24)</f>
+        <v/>
+      </c>
+      <c r="R25" s="157">
+        <f>IF(COUNT(R18,R24)&lt;2,"",R18-R24)</f>
+        <v/>
+      </c>
+      <c r="S25" s="157">
+        <f>IF(COUNT(S18,S24)&lt;2,"",S18-S24)</f>
         <v/>
       </c>
       <c r="T25" s="155" t="inlineStr"/>
@@ -46076,1849 +46096,252 @@
       <c r="V25" s="155" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="155" t="inlineStr">
-        <is>
-          <t>Light commercial vehicles retirement rate</t>
-        </is>
-      </c>
-      <c r="B26" s="156" t="inlineStr">
-        <is>
-          <t>% of last December's stock</t>
-        </is>
-      </c>
-      <c r="C26" s="156" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
+      <c r="A26" s="158" t="inlineStr">
+        <is>
+          <t>Land freight share of diesel in a second study</t>
+        </is>
+      </c>
+      <c r="B26" s="159" t="inlineStr">
+        <is>
+          <t>% of diesel demand</t>
+        </is>
+      </c>
+      <c r="C26" s="159" t="inlineStr">
+        <is>
+          <t>Comparison only</t>
         </is>
       </c>
       <c r="D26" s="167" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" s="155" t="inlineStr">
-        <is>
-          <t>Retired divided by last December's stock. Column D is the model's scrappage rate.</t>
+        <v>60.5</v>
+      </c>
+      <c r="E26" s="158" t="inlineStr">
+        <is>
+          <t>Merven, Hartley and Ahjum (2019): land freight took 60.5% of domestic diesel demand in 2012. Same research group as the vehicle study.</t>
         </is>
       </c>
       <c r="F26" s="167" t="n"/>
-      <c r="G26" s="167">
-        <f>IF(ISNUMBER(G25),G25/F7*100,"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="167">
-        <f>IF(ISNUMBER(H25),H25/G7*100,"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="167">
-        <f>IF(ISNUMBER(I25),I25/H7*100,"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="167">
-        <f>IF(ISNUMBER(J25),J25/I7*100,"")</f>
-        <v/>
-      </c>
-      <c r="K26" s="167">
-        <f>IF(ISNUMBER(K25),K25/J7*100,"")</f>
-        <v/>
-      </c>
-      <c r="L26" s="167">
-        <f>IF(ISNUMBER(L25),L25/K7*100,"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="167">
-        <f>IF(ISNUMBER(M25),M25/L7*100,"")</f>
-        <v/>
-      </c>
-      <c r="N26" s="167">
-        <f>IF(ISNUMBER(N25),N25/M7*100,"")</f>
-        <v/>
-      </c>
-      <c r="O26" s="167">
-        <f>IF(ISNUMBER(O25),O25/N7*100,"")</f>
-        <v/>
-      </c>
-      <c r="P26" s="167">
-        <f>IF(ISNUMBER(P25),P25/O7*100,"")</f>
-        <v/>
-      </c>
-      <c r="Q26" s="167">
-        <f>IF(ISNUMBER(Q25),Q25/P7*100,"")</f>
-        <v/>
-      </c>
-      <c r="R26" s="167">
-        <f>IF(ISNUMBER(R25),R25/Q7*100,"")</f>
-        <v/>
-      </c>
-      <c r="S26" s="167">
-        <f>IF(ISNUMBER(S25),S25/R7*100,"")</f>
-        <v/>
-      </c>
-      <c r="T26" s="155" t="inlineStr">
-        <is>
-          <t>Model setting in column D</t>
-        </is>
-      </c>
-      <c r="U26" s="155" t="inlineStr">
-        <is>
-          <t>assumptions/2026/vehicles.yaml: scrappage_rate</t>
-        </is>
-      </c>
-      <c r="V26" s="155" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="155" t="inlineStr">
-        <is>
-          <t>Trucks retired</t>
-        </is>
-      </c>
-      <c r="B27" s="156" t="inlineStr">
-        <is>
-          <t>vehicles/year</t>
-        </is>
-      </c>
-      <c r="C27" s="156" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D27" s="168" t="n"/>
-      <c r="E27" s="155" t="inlineStr">
-        <is>
-          <t>Includes deregistration, export and write-off; used imports and re-registration would lower it.</t>
-        </is>
-      </c>
-      <c r="F27" s="168" t="n"/>
-      <c r="G27" s="168">
-        <f>IF(COUNT(F8,G8,G16)&lt;3,"",F8+G16-G8)</f>
-        <v/>
-      </c>
-      <c r="H27" s="168">
-        <f>IF(COUNT(G8,H8,H16)&lt;3,"",G8+H16-H8)</f>
-        <v/>
-      </c>
-      <c r="I27" s="168">
-        <f>IF(COUNT(H8,I8,I16)&lt;3,"",H8+I16-I8)</f>
-        <v/>
-      </c>
-      <c r="J27" s="168">
-        <f>IF(COUNT(I8,J8,J16)&lt;3,"",I8+J16-J8)</f>
-        <v/>
-      </c>
-      <c r="K27" s="168">
-        <f>IF(COUNT(J8,K8,K16)&lt;3,"",J8+K16-K8)</f>
-        <v/>
-      </c>
-      <c r="L27" s="168">
-        <f>IF(COUNT(K8,L8,L16)&lt;3,"",K8+L16-L8)</f>
-        <v/>
-      </c>
-      <c r="M27" s="168">
-        <f>IF(COUNT(L8,M8,M16)&lt;3,"",L8+M16-M8)</f>
-        <v/>
-      </c>
-      <c r="N27" s="168">
-        <f>IF(COUNT(M8,N8,N16)&lt;3,"",M8+N16-N8)</f>
-        <v/>
-      </c>
-      <c r="O27" s="168">
-        <f>IF(COUNT(N8,O8,O16)&lt;3,"",N8+O16-O8)</f>
-        <v/>
-      </c>
-      <c r="P27" s="168">
-        <f>IF(COUNT(O8,P8,P16)&lt;3,"",O8+P16-P8)</f>
-        <v/>
-      </c>
-      <c r="Q27" s="168">
-        <f>IF(COUNT(P8,Q8,Q16)&lt;3,"",P8+Q16-Q8)</f>
-        <v/>
-      </c>
-      <c r="R27" s="168">
-        <f>IF(COUNT(Q8,R8,R16)&lt;3,"",Q8+R16-R8)</f>
-        <v/>
-      </c>
-      <c r="S27" s="168">
-        <f>IF(COUNT(R8,S8,S16)&lt;3,"",R8+S16-S8)</f>
-        <v/>
-      </c>
-      <c r="T27" s="155" t="inlineStr"/>
-      <c r="U27" s="155" t="inlineStr"/>
-      <c r="V27" s="155" t="inlineStr"/>
+      <c r="G26" s="167" t="n"/>
+      <c r="H26" s="167" t="n"/>
+      <c r="I26" s="167" t="n"/>
+      <c r="J26" s="167" t="n"/>
+      <c r="K26" s="167" t="n"/>
+      <c r="L26" s="167" t="n"/>
+      <c r="M26" s="167" t="n"/>
+      <c r="N26" s="167" t="n"/>
+      <c r="O26" s="167" t="n"/>
+      <c r="P26" s="167" t="n"/>
+      <c r="Q26" s="167" t="n"/>
+      <c r="R26" s="167" t="n"/>
+      <c r="S26" s="167" t="n"/>
+      <c r="T26" s="158" t="inlineStr"/>
+      <c r="U26" s="158" t="inlineStr">
+        <is>
+          <t>SA-TIED Working Paper 60, p.10</t>
+        </is>
+      </c>
+      <c r="V26" s="158" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="155" t="inlineStr">
-        <is>
-          <t>Trucks retirement rate</t>
-        </is>
-      </c>
-      <c r="B28" s="156" t="inlineStr">
-        <is>
-          <t>% of last December's stock</t>
-        </is>
-      </c>
-      <c r="C28" s="156" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D28" s="167" t="n">
-        <v>6</v>
-      </c>
-      <c r="E28" s="155" t="inlineStr">
-        <is>
-          <t>Retired divided by last December's stock. Column D is the model's scrappage rate.</t>
-        </is>
-      </c>
-      <c r="F28" s="167" t="n"/>
-      <c r="G28" s="167">
-        <f>IF(ISNUMBER(G27),G27/F8*100,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="167">
-        <f>IF(ISNUMBER(H27),H27/G8*100,"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="167">
-        <f>IF(ISNUMBER(I27),I27/H8*100,"")</f>
-        <v/>
-      </c>
-      <c r="J28" s="167">
-        <f>IF(ISNUMBER(J27),J27/I8*100,"")</f>
-        <v/>
-      </c>
-      <c r="K28" s="167">
-        <f>IF(ISNUMBER(K27),K27/J8*100,"")</f>
-        <v/>
-      </c>
-      <c r="L28" s="167">
-        <f>IF(ISNUMBER(L27),L27/K8*100,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="167">
-        <f>IF(ISNUMBER(M27),M27/L8*100,"")</f>
-        <v/>
-      </c>
-      <c r="N28" s="167">
-        <f>IF(ISNUMBER(N27),N27/M8*100,"")</f>
-        <v/>
-      </c>
-      <c r="O28" s="167">
-        <f>IF(ISNUMBER(O27),O27/N8*100,"")</f>
-        <v/>
-      </c>
-      <c r="P28" s="167">
-        <f>IF(ISNUMBER(P27),P27/O8*100,"")</f>
-        <v/>
-      </c>
-      <c r="Q28" s="167">
-        <f>IF(ISNUMBER(Q27),Q27/P8*100,"")</f>
-        <v/>
-      </c>
-      <c r="R28" s="167">
-        <f>IF(ISNUMBER(R27),R27/Q8*100,"")</f>
-        <v/>
-      </c>
-      <c r="S28" s="167">
-        <f>IF(ISNUMBER(S27),S27/R8*100,"")</f>
-        <v/>
-      </c>
-      <c r="T28" s="155" t="inlineStr">
-        <is>
-          <t>Model setting in column D</t>
-        </is>
-      </c>
-      <c r="U28" s="155" t="inlineStr">
-        <is>
-          <t>assumptions/2026/vehicles.yaml: scrappage_rate</t>
-        </is>
-      </c>
-      <c r="V28" s="155" t="inlineStr"/>
+      <c r="A28" s="151" t="inlineStr">
+        <is>
+          <t>5. Which classes of the study fall in each group</t>
+        </is>
+      </c>
+      <c r="B28" s="151" t="n"/>
+      <c r="C28" s="151" t="n"/>
+      <c r="D28" s="151" t="n"/>
+      <c r="E28" s="151" t="n"/>
+      <c r="F28" s="151" t="n"/>
+      <c r="G28" s="151" t="n"/>
+      <c r="H28" s="151" t="n"/>
+      <c r="I28" s="151" t="n"/>
+      <c r="J28" s="151" t="n"/>
+      <c r="K28" s="151" t="n"/>
+      <c r="L28" s="151" t="n"/>
+      <c r="M28" s="151" t="n"/>
+      <c r="N28" s="151" t="n"/>
+      <c r="O28" s="151" t="n"/>
+      <c r="P28" s="151" t="n"/>
+      <c r="Q28" s="151" t="n"/>
+      <c r="R28" s="151" t="n"/>
+      <c r="S28" s="151" t="n"/>
+      <c r="T28" s="151" t="n"/>
+      <c r="U28" s="151" t="n"/>
+      <c r="V28" s="151" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="158" t="inlineStr">
+        <is>
+          <t>Heavy vehicles: classes</t>
+        </is>
+      </c>
+      <c r="B29" s="159" t="inlineStr"/>
+      <c r="C29" s="159" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D29" s="168" t="n">
+        <v>4836.490501047</v>
+      </c>
+      <c r="E29" s="158" t="inlineStr">
+        <is>
+          <t>Diesel classes counted: HCV1Diesel, HCV2Diesel, HCV3Diesel, HCV4Diesel, HCV5Diesel, HCV6Diesel, HCV7Diesel, HCV8Diesel, HCV9Diesel. Other classes in the group, not diesel: HCV1Gasoline.</t>
+        </is>
+      </c>
+      <c r="F29" s="168" t="n"/>
+      <c r="G29" s="168" t="n"/>
+      <c r="H29" s="168" t="n"/>
+      <c r="I29" s="168" t="n"/>
+      <c r="J29" s="168" t="n"/>
+      <c r="K29" s="168" t="n"/>
+      <c r="L29" s="168" t="n"/>
+      <c r="M29" s="168" t="n"/>
+      <c r="N29" s="168" t="n"/>
+      <c r="O29" s="168" t="n"/>
+      <c r="P29" s="168" t="n"/>
+      <c r="Q29" s="168" t="n"/>
+      <c r="R29" s="168" t="n"/>
+      <c r="S29" s="168" t="n"/>
+      <c r="T29" s="158" t="inlineStr">
+        <is>
+          <t>Column D is the group's diesel in the study, million litres, 2010 fleet</t>
+        </is>
+      </c>
+      <c r="U29" s="158" t="inlineStr">
+        <is>
+          <t>assumptions/2026/reference/vehicle_parameters_stone2018.csv</t>
+        </is>
+      </c>
+      <c r="V29" s="158" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="151" t="inlineStr">
-        <is>
-          <t>4. Electrified new sales (all segments)</t>
-        </is>
-      </c>
-      <c r="B30" s="151" t="n"/>
-      <c r="C30" s="151" t="n"/>
-      <c r="D30" s="151" t="n"/>
-      <c r="E30" s="151" t="n"/>
-      <c r="F30" s="151" t="n"/>
-      <c r="G30" s="151" t="n"/>
-      <c r="H30" s="151" t="n"/>
-      <c r="I30" s="151" t="n"/>
-      <c r="J30" s="151" t="n"/>
-      <c r="K30" s="151" t="n"/>
-      <c r="L30" s="151" t="n"/>
-      <c r="M30" s="151" t="n"/>
-      <c r="N30" s="151" t="n"/>
-      <c r="O30" s="151" t="n"/>
-      <c r="P30" s="151" t="n"/>
-      <c r="Q30" s="151" t="n"/>
-      <c r="R30" s="151" t="n"/>
-      <c r="S30" s="151" t="n"/>
-      <c r="T30" s="151" t="n"/>
-      <c r="U30" s="151" t="n"/>
-      <c r="V30" s="151" t="n"/>
+      <c r="A30" s="158" t="inlineStr">
+        <is>
+          <t>Light vehicles: classes</t>
+        </is>
+      </c>
+      <c r="B30" s="159" t="inlineStr"/>
+      <c r="C30" s="159" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D30" s="168" t="n">
+        <v>2156.667657144</v>
+      </c>
+      <c r="E30" s="158" t="inlineStr">
+        <is>
+          <t>Diesel classes counted: LCVDiesel. Other classes in the group, not diesel: LCVGasoline.</t>
+        </is>
+      </c>
+      <c r="F30" s="168" t="n"/>
+      <c r="G30" s="168" t="n"/>
+      <c r="H30" s="168" t="n"/>
+      <c r="I30" s="168" t="n"/>
+      <c r="J30" s="168" t="n"/>
+      <c r="K30" s="168" t="n"/>
+      <c r="L30" s="168" t="n"/>
+      <c r="M30" s="168" t="n"/>
+      <c r="N30" s="168" t="n"/>
+      <c r="O30" s="168" t="n"/>
+      <c r="P30" s="168" t="n"/>
+      <c r="Q30" s="168" t="n"/>
+      <c r="R30" s="168" t="n"/>
+      <c r="S30" s="168" t="n"/>
+      <c r="T30" s="158" t="inlineStr">
+        <is>
+          <t>Column D is the group's diesel in the study, million litres, 2010 fleet</t>
+        </is>
+      </c>
+      <c r="U30" s="158" t="inlineStr">
+        <is>
+          <t>assumptions/2026/reference/vehicle_parameters_stone2018.csv</t>
+        </is>
+      </c>
+      <c r="V30" s="158" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="152" t="inlineStr">
-        <is>
-          <t>Battery electric, new sales</t>
-        </is>
-      </c>
-      <c r="B31" s="153" t="inlineStr">
-        <is>
-          <t>vehicles/year</t>
-        </is>
-      </c>
-      <c r="C31" s="153" t="inlineStr">
-        <is>
-          <t>Source observation</t>
-        </is>
-      </c>
-      <c r="D31" s="166" t="n"/>
-      <c r="E31" s="152" t="inlineStr">
-        <is>
-          <t>Total market, not passenger cars only.</t>
-        </is>
-      </c>
-      <c r="F31" s="166" t="n"/>
-      <c r="G31" s="166" t="n"/>
-      <c r="H31" s="166" t="n"/>
-      <c r="I31" s="166" t="n"/>
-      <c r="J31" s="166" t="n"/>
-      <c r="K31" s="166" t="n"/>
-      <c r="L31" s="166" t="n"/>
-      <c r="M31" s="166" t="n">
-        <v>154</v>
-      </c>
-      <c r="N31" s="166" t="n">
-        <v>92</v>
-      </c>
-      <c r="O31" s="166" t="n">
-        <v>218</v>
-      </c>
-      <c r="P31" s="166" t="n">
-        <v>502</v>
-      </c>
-      <c r="Q31" s="166" t="n">
-        <v>929</v>
-      </c>
-      <c r="R31" s="166" t="n">
-        <v>1257</v>
-      </c>
-      <c r="S31" s="166" t="n">
-        <v>1088</v>
-      </c>
-      <c r="T31" s="152" t="inlineStr">
-        <is>
-          <t>2019-2025</t>
-        </is>
-      </c>
-      <c r="U31" s="152" t="inlineStr">
-        <is>
-          <t>naamsa new-energy vehicle sales</t>
-        </is>
-      </c>
-      <c r="V31" s="152" t="inlineStr"/>
+      <c r="A31" s="158" t="inlineStr">
+        <is>
+          <t>Passenger vehicles: classes</t>
+        </is>
+      </c>
+      <c r="B31" s="159" t="inlineStr"/>
+      <c r="C31" s="159" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D31" s="168" t="n">
+        <v>996.994409071</v>
+      </c>
+      <c r="E31" s="158" t="inlineStr">
+        <is>
+          <t>Diesel classes counted: CarDiesel, CarHybridDiesel, BusDiesel, MBTDiesel, SUVDiesel. Other classes in the group, not diesel: CarElectric, CarGasoline, CarHybridGasoline, MBTGasoline, MotoGasoline, SUVGasoline, SUVHybridGasoline.</t>
+        </is>
+      </c>
+      <c r="F31" s="168" t="n"/>
+      <c r="G31" s="168" t="n"/>
+      <c r="H31" s="168" t="n"/>
+      <c r="I31" s="168" t="n"/>
+      <c r="J31" s="168" t="n"/>
+      <c r="K31" s="168" t="n"/>
+      <c r="L31" s="168" t="n"/>
+      <c r="M31" s="168" t="n"/>
+      <c r="N31" s="168" t="n"/>
+      <c r="O31" s="168" t="n"/>
+      <c r="P31" s="168" t="n"/>
+      <c r="Q31" s="168" t="n"/>
+      <c r="R31" s="168" t="n"/>
+      <c r="S31" s="168" t="n"/>
+      <c r="T31" s="158" t="inlineStr">
+        <is>
+          <t>Column D is the group's diesel in the study, million litres, 2010 fleet</t>
+        </is>
+      </c>
+      <c r="U31" s="158" t="inlineStr">
+        <is>
+          <t>assumptions/2026/reference/vehicle_parameters_stone2018.csv</t>
+        </is>
+      </c>
+      <c r="V31" s="158" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="155" t="inlineStr">
-        <is>
-          <t>Battery electric share of new sales</t>
-        </is>
-      </c>
-      <c r="B32" s="156" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C32" s="156" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D32" s="169" t="n"/>
-      <c r="E32" s="155" t="inlineStr">
-        <is>
-          <t>Share of all new vehicles sold in the year.</t>
-        </is>
-      </c>
-      <c r="F32" s="169">
-        <f>IF(COUNT(F31,F17)&lt;2,"",F31/F17*100)</f>
-        <v/>
-      </c>
-      <c r="G32" s="169">
-        <f>IF(COUNT(G31,G17)&lt;2,"",G31/G17*100)</f>
-        <v/>
-      </c>
-      <c r="H32" s="169">
-        <f>IF(COUNT(H31,H17)&lt;2,"",H31/H17*100)</f>
-        <v/>
-      </c>
-      <c r="I32" s="169">
-        <f>IF(COUNT(I31,I17)&lt;2,"",I31/I17*100)</f>
-        <v/>
-      </c>
-      <c r="J32" s="169">
-        <f>IF(COUNT(J31,J17)&lt;2,"",J31/J17*100)</f>
-        <v/>
-      </c>
-      <c r="K32" s="169">
-        <f>IF(COUNT(K31,K17)&lt;2,"",K31/K17*100)</f>
-        <v/>
-      </c>
-      <c r="L32" s="169">
-        <f>IF(COUNT(L31,L17)&lt;2,"",L31/L17*100)</f>
-        <v/>
-      </c>
-      <c r="M32" s="169">
-        <f>IF(COUNT(M31,M17)&lt;2,"",M31/M17*100)</f>
-        <v/>
-      </c>
-      <c r="N32" s="169">
-        <f>IF(COUNT(N31,N17)&lt;2,"",N31/N17*100)</f>
-        <v/>
-      </c>
-      <c r="O32" s="169">
-        <f>IF(COUNT(O31,O17)&lt;2,"",O31/O17*100)</f>
-        <v/>
-      </c>
-      <c r="P32" s="169">
-        <f>IF(COUNT(P31,P17)&lt;2,"",P31/P17*100)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="169">
-        <f>IF(COUNT(Q31,Q17)&lt;2,"",Q31/Q17*100)</f>
-        <v/>
-      </c>
-      <c r="R32" s="169">
-        <f>IF(COUNT(R31,R17)&lt;2,"",R31/R17*100)</f>
-        <v/>
-      </c>
-      <c r="S32" s="169">
-        <f>IF(COUNT(S31,S17)&lt;2,"",S31/S17*100)</f>
-        <v/>
-      </c>
-      <c r="T32" s="155" t="inlineStr"/>
-      <c r="U32" s="155" t="inlineStr"/>
-      <c r="V32" s="155" t="inlineStr">
-        <is>
-          <t>Share of the fleet is not observed after December 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="152" t="inlineStr">
-        <is>
-          <t>Plug-in hybrid, new sales</t>
-        </is>
-      </c>
-      <c r="B33" s="153" t="inlineStr">
-        <is>
-          <t>vehicles/year</t>
-        </is>
-      </c>
-      <c r="C33" s="153" t="inlineStr">
-        <is>
-          <t>Source observation</t>
-        </is>
-      </c>
-      <c r="D33" s="166" t="n"/>
-      <c r="E33" s="152" t="inlineStr">
-        <is>
-          <t>Total market, not passenger cars only.</t>
-        </is>
-      </c>
-      <c r="F33" s="166" t="n"/>
-      <c r="G33" s="166" t="n"/>
-      <c r="H33" s="166" t="n"/>
-      <c r="I33" s="166" t="n"/>
-      <c r="J33" s="166" t="n"/>
-      <c r="K33" s="166" t="n"/>
-      <c r="L33" s="166" t="n"/>
-      <c r="M33" s="166" t="n">
-        <v>72</v>
-      </c>
-      <c r="N33" s="166" t="n">
-        <v>77</v>
-      </c>
-      <c r="O33" s="166" t="n">
-        <v>51</v>
-      </c>
-      <c r="P33" s="166" t="n">
-        <v>122</v>
-      </c>
-      <c r="Q33" s="166" t="n">
-        <v>368</v>
-      </c>
-      <c r="R33" s="166" t="n">
-        <v>738</v>
-      </c>
-      <c r="S33" s="166" t="n">
-        <v>2810</v>
-      </c>
-      <c r="T33" s="152" t="inlineStr">
-        <is>
-          <t>2019-2025</t>
-        </is>
-      </c>
-      <c r="U33" s="152" t="inlineStr">
-        <is>
-          <t>naamsa new-energy vehicle sales</t>
-        </is>
-      </c>
-      <c r="V33" s="152" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="155" t="inlineStr">
-        <is>
-          <t>Plug-in hybrid share of new sales</t>
-        </is>
-      </c>
-      <c r="B34" s="156" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C34" s="156" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D34" s="169" t="n"/>
-      <c r="E34" s="155" t="inlineStr">
-        <is>
-          <t>Share of all new vehicles sold in the year.</t>
-        </is>
-      </c>
-      <c r="F34" s="169">
-        <f>IF(COUNT(F33,F17)&lt;2,"",F33/F17*100)</f>
-        <v/>
-      </c>
-      <c r="G34" s="169">
-        <f>IF(COUNT(G33,G17)&lt;2,"",G33/G17*100)</f>
-        <v/>
-      </c>
-      <c r="H34" s="169">
-        <f>IF(COUNT(H33,H17)&lt;2,"",H33/H17*100)</f>
-        <v/>
-      </c>
-      <c r="I34" s="169">
-        <f>IF(COUNT(I33,I17)&lt;2,"",I33/I17*100)</f>
-        <v/>
-      </c>
-      <c r="J34" s="169">
-        <f>IF(COUNT(J33,J17)&lt;2,"",J33/J17*100)</f>
-        <v/>
-      </c>
-      <c r="K34" s="169">
-        <f>IF(COUNT(K33,K17)&lt;2,"",K33/K17*100)</f>
-        <v/>
-      </c>
-      <c r="L34" s="169">
-        <f>IF(COUNT(L33,L17)&lt;2,"",L33/L17*100)</f>
-        <v/>
-      </c>
-      <c r="M34" s="169">
-        <f>IF(COUNT(M33,M17)&lt;2,"",M33/M17*100)</f>
-        <v/>
-      </c>
-      <c r="N34" s="169">
-        <f>IF(COUNT(N33,N17)&lt;2,"",N33/N17*100)</f>
-        <v/>
-      </c>
-      <c r="O34" s="169">
-        <f>IF(COUNT(O33,O17)&lt;2,"",O33/O17*100)</f>
-        <v/>
-      </c>
-      <c r="P34" s="169">
-        <f>IF(COUNT(P33,P17)&lt;2,"",P33/P17*100)</f>
-        <v/>
-      </c>
-      <c r="Q34" s="169">
-        <f>IF(COUNT(Q33,Q17)&lt;2,"",Q33/Q17*100)</f>
-        <v/>
-      </c>
-      <c r="R34" s="169">
-        <f>IF(COUNT(R33,R17)&lt;2,"",R33/R17*100)</f>
-        <v/>
-      </c>
-      <c r="S34" s="169">
-        <f>IF(COUNT(S33,S17)&lt;2,"",S33/S17*100)</f>
-        <v/>
-      </c>
-      <c r="T34" s="155" t="inlineStr"/>
-      <c r="U34" s="155" t="inlineStr"/>
-      <c r="V34" s="155" t="inlineStr">
-        <is>
-          <t>Share of the fleet is not observed after December 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="152" t="inlineStr">
-        <is>
-          <t>Conventional hybrid, new sales</t>
-        </is>
-      </c>
-      <c r="B35" s="153" t="inlineStr">
-        <is>
-          <t>vehicles/year</t>
-        </is>
-      </c>
-      <c r="C35" s="153" t="inlineStr">
-        <is>
-          <t>Source observation</t>
-        </is>
-      </c>
-      <c r="D35" s="166" t="n"/>
-      <c r="E35" s="152" t="inlineStr">
-        <is>
-          <t>Total market, not passenger cars only.</t>
-        </is>
-      </c>
-      <c r="F35" s="166" t="n"/>
-      <c r="G35" s="166" t="n"/>
-      <c r="H35" s="166" t="n"/>
-      <c r="I35" s="166" t="n"/>
-      <c r="J35" s="166" t="n"/>
-      <c r="K35" s="166" t="n"/>
-      <c r="L35" s="166" t="n"/>
-      <c r="M35" s="166" t="n">
-        <v>181</v>
-      </c>
-      <c r="N35" s="166" t="n">
-        <v>155</v>
-      </c>
-      <c r="O35" s="166" t="n">
-        <v>627</v>
-      </c>
-      <c r="P35" s="166" t="n">
-        <v>4070</v>
-      </c>
-      <c r="Q35" s="166" t="n">
-        <v>6485</v>
-      </c>
-      <c r="R35" s="166" t="n">
-        <v>13616</v>
-      </c>
-      <c r="S35" s="166" t="n">
-        <v>12818</v>
-      </c>
-      <c r="T35" s="152" t="inlineStr">
-        <is>
-          <t>2019-2025</t>
-        </is>
-      </c>
-      <c r="U35" s="152" t="inlineStr">
-        <is>
-          <t>naamsa new-energy vehicle sales</t>
-        </is>
-      </c>
-      <c r="V35" s="152" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="155" t="inlineStr">
-        <is>
-          <t>Conventional hybrid share of new sales</t>
-        </is>
-      </c>
-      <c r="B36" s="156" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C36" s="156" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D36" s="169" t="n"/>
-      <c r="E36" s="155" t="inlineStr">
-        <is>
-          <t>Share of all new vehicles sold in the year.</t>
-        </is>
-      </c>
-      <c r="F36" s="169">
-        <f>IF(COUNT(F35,F17)&lt;2,"",F35/F17*100)</f>
-        <v/>
-      </c>
-      <c r="G36" s="169">
-        <f>IF(COUNT(G35,G17)&lt;2,"",G35/G17*100)</f>
-        <v/>
-      </c>
-      <c r="H36" s="169">
-        <f>IF(COUNT(H35,H17)&lt;2,"",H35/H17*100)</f>
-        <v/>
-      </c>
-      <c r="I36" s="169">
-        <f>IF(COUNT(I35,I17)&lt;2,"",I35/I17*100)</f>
-        <v/>
-      </c>
-      <c r="J36" s="169">
-        <f>IF(COUNT(J35,J17)&lt;2,"",J35/J17*100)</f>
-        <v/>
-      </c>
-      <c r="K36" s="169">
-        <f>IF(COUNT(K35,K17)&lt;2,"",K35/K17*100)</f>
-        <v/>
-      </c>
-      <c r="L36" s="169">
-        <f>IF(COUNT(L35,L17)&lt;2,"",L35/L17*100)</f>
-        <v/>
-      </c>
-      <c r="M36" s="169">
-        <f>IF(COUNT(M35,M17)&lt;2,"",M35/M17*100)</f>
-        <v/>
-      </c>
-      <c r="N36" s="169">
-        <f>IF(COUNT(N35,N17)&lt;2,"",N35/N17*100)</f>
-        <v/>
-      </c>
-      <c r="O36" s="169">
-        <f>IF(COUNT(O35,O17)&lt;2,"",O35/O17*100)</f>
-        <v/>
-      </c>
-      <c r="P36" s="169">
-        <f>IF(COUNT(P35,P17)&lt;2,"",P35/P17*100)</f>
-        <v/>
-      </c>
-      <c r="Q36" s="169">
-        <f>IF(COUNT(Q35,Q17)&lt;2,"",Q35/Q17*100)</f>
-        <v/>
-      </c>
-      <c r="R36" s="169">
-        <f>IF(COUNT(R35,R17)&lt;2,"",R35/R17*100)</f>
-        <v/>
-      </c>
-      <c r="S36" s="169">
-        <f>IF(COUNT(S35,S17)&lt;2,"",S35/S17*100)</f>
-        <v/>
-      </c>
-      <c r="T36" s="155" t="inlineStr"/>
-      <c r="U36" s="155" t="inlineStr"/>
-      <c r="V36" s="155" t="inlineStr">
-        <is>
-          <t>Share of the fleet is not observed after December 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="151" t="inlineStr">
-        <is>
-          <t>5. Fuel split of the registered fleet</t>
-        </is>
-      </c>
-      <c r="B38" s="151" t="n"/>
-      <c r="C38" s="151" t="n"/>
-      <c r="D38" s="151" t="n"/>
-      <c r="E38" s="151" t="n"/>
-      <c r="F38" s="151" t="n"/>
-      <c r="G38" s="151" t="n"/>
-      <c r="H38" s="151" t="n"/>
-      <c r="I38" s="151" t="n"/>
-      <c r="J38" s="151" t="n"/>
-      <c r="K38" s="151" t="n"/>
-      <c r="L38" s="151" t="n"/>
-      <c r="M38" s="151" t="n"/>
-      <c r="N38" s="151" t="n"/>
-      <c r="O38" s="151" t="n"/>
-      <c r="P38" s="151" t="n"/>
-      <c r="Q38" s="151" t="n"/>
-      <c r="R38" s="151" t="n"/>
-      <c r="S38" s="151" t="n"/>
-      <c r="T38" s="151" t="n"/>
-      <c r="U38" s="151" t="n"/>
-      <c r="V38" s="151" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="152" t="inlineStr">
-        <is>
-          <t>Petrol vehicles registered</t>
-        </is>
-      </c>
-      <c r="B39" s="153" t="inlineStr">
-        <is>
-          <t>vehicles</t>
-        </is>
-      </c>
-      <c r="C39" s="153" t="inlineStr">
-        <is>
-          <t>Source observation</t>
-        </is>
-      </c>
-      <c r="D39" s="166" t="n"/>
-      <c r="E39" s="152" t="inlineStr">
-        <is>
-          <t>All classes, December 2023.</t>
-        </is>
-      </c>
-      <c r="F39" s="166" t="n"/>
-      <c r="G39" s="166" t="n"/>
-      <c r="H39" s="166" t="n"/>
-      <c r="I39" s="166" t="n"/>
-      <c r="J39" s="166" t="n"/>
-      <c r="K39" s="166" t="n"/>
-      <c r="L39" s="166" t="n"/>
-      <c r="M39" s="166" t="n"/>
-      <c r="N39" s="166" t="n"/>
-      <c r="O39" s="166" t="n"/>
-      <c r="P39" s="166" t="n"/>
-      <c r="Q39" s="166" t="n">
-        <v>8555772</v>
-      </c>
-      <c r="R39" s="166" t="n"/>
-      <c r="S39" s="166" t="n"/>
-      <c r="T39" s="152" t="inlineStr">
-        <is>
-          <t>One date only</t>
-        </is>
-      </c>
-      <c r="U39" s="152" t="inlineStr">
-        <is>
-          <t>Department of Transport, 2023</t>
-        </is>
-      </c>
-      <c r="V39" s="152" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="152" t="inlineStr">
-        <is>
-          <t>Diesel vehicles registered</t>
-        </is>
-      </c>
-      <c r="B40" s="153" t="inlineStr">
-        <is>
-          <t>vehicles</t>
-        </is>
-      </c>
-      <c r="C40" s="153" t="inlineStr">
-        <is>
-          <t>Source observation</t>
-        </is>
-      </c>
-      <c r="D40" s="166" t="n"/>
-      <c r="E40" s="152" t="inlineStr">
-        <is>
-          <t>All classes, December 2023.</t>
-        </is>
-      </c>
-      <c r="F40" s="166" t="n"/>
-      <c r="G40" s="166" t="n"/>
-      <c r="H40" s="166" t="n"/>
-      <c r="I40" s="166" t="n"/>
-      <c r="J40" s="166" t="n"/>
-      <c r="K40" s="166" t="n"/>
-      <c r="L40" s="166" t="n"/>
-      <c r="M40" s="166" t="n"/>
-      <c r="N40" s="166" t="n"/>
-      <c r="O40" s="166" t="n"/>
-      <c r="P40" s="166" t="n"/>
-      <c r="Q40" s="166" t="n">
-        <v>3335546</v>
-      </c>
-      <c r="R40" s="166" t="n"/>
-      <c r="S40" s="166" t="n"/>
-      <c r="T40" s="152" t="inlineStr">
-        <is>
-          <t>One date only</t>
-        </is>
-      </c>
-      <c r="U40" s="152" t="inlineStr">
-        <is>
-          <t>Department of Transport, 2023</t>
-        </is>
-      </c>
-      <c r="V40" s="152" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="152" t="inlineStr">
-        <is>
-          <t>Electric vehicles registered</t>
-        </is>
-      </c>
-      <c r="B41" s="153" t="inlineStr">
-        <is>
-          <t>vehicles</t>
-        </is>
-      </c>
-      <c r="C41" s="153" t="inlineStr">
-        <is>
-          <t>Source observation</t>
-        </is>
-      </c>
-      <c r="D41" s="166" t="n"/>
-      <c r="E41" s="152" t="inlineStr">
-        <is>
-          <t>All classes, December 2023.</t>
-        </is>
-      </c>
-      <c r="F41" s="166" t="n"/>
-      <c r="G41" s="166" t="n"/>
-      <c r="H41" s="166" t="n"/>
-      <c r="I41" s="166" t="n"/>
-      <c r="J41" s="166" t="n"/>
-      <c r="K41" s="166" t="n"/>
-      <c r="L41" s="166" t="n"/>
-      <c r="M41" s="166" t="n"/>
-      <c r="N41" s="166" t="n"/>
-      <c r="O41" s="166" t="n"/>
-      <c r="P41" s="166" t="n"/>
-      <c r="Q41" s="166" t="n">
-        <v>4090</v>
-      </c>
-      <c r="R41" s="166" t="n"/>
-      <c r="S41" s="166" t="n"/>
-      <c r="T41" s="152" t="inlineStr">
-        <is>
-          <t>One date only</t>
-        </is>
-      </c>
-      <c r="U41" s="152" t="inlineStr">
-        <is>
-          <t>Department of Transport, 2023</t>
-        </is>
-      </c>
-      <c r="V41" s="152" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="155" t="inlineStr">
-        <is>
-          <t>Diesel vehicles implied by the model's split</t>
-        </is>
-      </c>
-      <c r="B42" s="156" t="inlineStr">
-        <is>
-          <t>vehicles</t>
-        </is>
-      </c>
-      <c r="C42" s="156" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D42" s="168" t="n"/>
-      <c r="E42" s="155" t="inlineStr">
-        <is>
-          <t>Cars x 17% plus light commercial x 70% plus trucks and buses. The model's split is for new sales; applied here to stock as a test.</t>
-        </is>
-      </c>
-      <c r="F42" s="168">
-        <f>IF(COUNT(F6,F7)&lt;2,"",F6*0.17+F7*0.7+F8+F9)</f>
-        <v/>
-      </c>
-      <c r="G42" s="168">
-        <f>IF(COUNT(G6,G7)&lt;2,"",G6*0.17+G7*0.7+G8+G9)</f>
-        <v/>
-      </c>
-      <c r="H42" s="168">
-        <f>IF(COUNT(H6,H7)&lt;2,"",H6*0.17+H7*0.7+H8+H9)</f>
-        <v/>
-      </c>
-      <c r="I42" s="168">
-        <f>IF(COUNT(I6,I7)&lt;2,"",I6*0.17+I7*0.7+I8+I9)</f>
-        <v/>
-      </c>
-      <c r="J42" s="168">
-        <f>IF(COUNT(J6,J7)&lt;2,"",J6*0.17+J7*0.7+J8+J9)</f>
-        <v/>
-      </c>
-      <c r="K42" s="168">
-        <f>IF(COUNT(K6,K7)&lt;2,"",K6*0.17+K7*0.7+K8+K9)</f>
-        <v/>
-      </c>
-      <c r="L42" s="168">
-        <f>IF(COUNT(L6,L7)&lt;2,"",L6*0.17+L7*0.7+L8+L9)</f>
-        <v/>
-      </c>
-      <c r="M42" s="168">
-        <f>IF(COUNT(M6,M7)&lt;2,"",M6*0.17+M7*0.7+M8+M9)</f>
-        <v/>
-      </c>
-      <c r="N42" s="168">
-        <f>IF(COUNT(N6,N7)&lt;2,"",N6*0.17+N7*0.7+N8+N9)</f>
-        <v/>
-      </c>
-      <c r="O42" s="168">
-        <f>IF(COUNT(O6,O7)&lt;2,"",O6*0.17+O7*0.7+O8+O9)</f>
-        <v/>
-      </c>
-      <c r="P42" s="168">
-        <f>IF(COUNT(P6,P7)&lt;2,"",P6*0.17+P7*0.7+P8+P9)</f>
-        <v/>
-      </c>
-      <c r="Q42" s="168">
-        <f>IF(COUNT(Q6,Q7)&lt;2,"",Q6*0.17+Q7*0.7+Q8+Q9)</f>
-        <v/>
-      </c>
-      <c r="R42" s="168">
-        <f>IF(COUNT(R6,R7)&lt;2,"",R6*0.17+R7*0.7+R8+R9)</f>
-        <v/>
-      </c>
-      <c r="S42" s="168">
-        <f>IF(COUNT(S6,S7)&lt;2,"",S6*0.17+S7*0.7+S8+S9)</f>
-        <v/>
-      </c>
-      <c r="T42" s="155" t="inlineStr"/>
-      <c r="U42" s="155" t="inlineStr">
-        <is>
-          <t>assumptions/2026/vehicles.yaml: petrol_diesel_split</t>
-        </is>
-      </c>
-      <c r="V42" s="155" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="155" t="inlineStr">
-        <is>
-          <t>Implied less registered diesel vehicles</t>
-        </is>
-      </c>
-      <c r="B43" s="156" t="inlineStr">
-        <is>
-          <t>vehicles</t>
-        </is>
-      </c>
-      <c r="C43" s="156" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D43" s="168" t="n"/>
-      <c r="E43" s="155" t="inlineStr">
-        <is>
-          <t>Positive means the model's split puts more diesel vehicles on the road than are registered. Minibuses and motorcycles are left out of the implied figure.</t>
-        </is>
-      </c>
-      <c r="F43" s="168">
-        <f>IF(COUNT(F42,F40)&lt;2,"",F42-F40)</f>
-        <v/>
-      </c>
-      <c r="G43" s="168">
-        <f>IF(COUNT(G42,G40)&lt;2,"",G42-G40)</f>
-        <v/>
-      </c>
-      <c r="H43" s="168">
-        <f>IF(COUNT(H42,H40)&lt;2,"",H42-H40)</f>
-        <v/>
-      </c>
-      <c r="I43" s="168">
-        <f>IF(COUNT(I42,I40)&lt;2,"",I42-I40)</f>
-        <v/>
-      </c>
-      <c r="J43" s="168">
-        <f>IF(COUNT(J42,J40)&lt;2,"",J42-J40)</f>
-        <v/>
-      </c>
-      <c r="K43" s="168">
-        <f>IF(COUNT(K42,K40)&lt;2,"",K42-K40)</f>
-        <v/>
-      </c>
-      <c r="L43" s="168">
-        <f>IF(COUNT(L42,L40)&lt;2,"",L42-L40)</f>
-        <v/>
-      </c>
-      <c r="M43" s="168">
-        <f>IF(COUNT(M42,M40)&lt;2,"",M42-M40)</f>
-        <v/>
-      </c>
-      <c r="N43" s="168">
-        <f>IF(COUNT(N42,N40)&lt;2,"",N42-N40)</f>
-        <v/>
-      </c>
-      <c r="O43" s="168">
-        <f>IF(COUNT(O42,O40)&lt;2,"",O42-O40)</f>
-        <v/>
-      </c>
-      <c r="P43" s="168">
-        <f>IF(COUNT(P42,P40)&lt;2,"",P42-P40)</f>
-        <v/>
-      </c>
-      <c r="Q43" s="168">
-        <f>IF(COUNT(Q42,Q40)&lt;2,"",Q42-Q40)</f>
-        <v/>
-      </c>
-      <c r="R43" s="168">
-        <f>IF(COUNT(R42,R40)&lt;2,"",R42-R40)</f>
-        <v/>
-      </c>
-      <c r="S43" s="168">
-        <f>IF(COUNT(S42,S40)&lt;2,"",S42-S40)</f>
-        <v/>
-      </c>
-      <c r="T43" s="155" t="inlineStr"/>
-      <c r="U43" s="155" t="inlineStr"/>
-      <c r="V43" s="155" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="151" t="inlineStr">
-        <is>
-          <t>6. Distance and fuel use: model settings beside the published study</t>
-        </is>
-      </c>
-      <c r="B45" s="151" t="n"/>
-      <c r="C45" s="151" t="n"/>
-      <c r="D45" s="151" t="n"/>
-      <c r="E45" s="151" t="n"/>
-      <c r="F45" s="151" t="n"/>
-      <c r="G45" s="151" t="n"/>
-      <c r="H45" s="151" t="n"/>
-      <c r="I45" s="151" t="n"/>
-      <c r="J45" s="151" t="n"/>
-      <c r="K45" s="151" t="n"/>
-      <c r="L45" s="151" t="n"/>
-      <c r="M45" s="151" t="n"/>
-      <c r="N45" s="151" t="n"/>
-      <c r="O45" s="151" t="n"/>
-      <c r="P45" s="151" t="n"/>
-      <c r="Q45" s="151" t="n"/>
-      <c r="R45" s="151" t="n"/>
-      <c r="S45" s="151" t="n"/>
-      <c r="T45" s="151" t="n"/>
-      <c r="U45" s="151" t="n"/>
-      <c r="V45" s="151" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="158" t="inlineStr">
-        <is>
-          <t>Passenger cars, distance</t>
-        </is>
-      </c>
-      <c r="B46" s="159" t="inlineStr">
-        <is>
-          <t>km/vehicle/year</t>
-        </is>
-      </c>
-      <c r="C46" s="159" t="inlineStr">
-        <is>
-          <t>Model setting</t>
-        </is>
-      </c>
-      <c r="D46" s="160" t="n">
-        <v>17000</v>
-      </c>
-      <c r="E46" s="158" t="inlineStr">
-        <is>
-          <t>Column D is the model's value. The study gives 14,457.0 for CarGasoline (fleet average, 2014 base).</t>
-        </is>
-      </c>
-      <c r="F46" s="160" t="n"/>
-      <c r="G46" s="160" t="n"/>
-      <c r="H46" s="160" t="n"/>
-      <c r="I46" s="160" t="n"/>
-      <c r="J46" s="160" t="n"/>
-      <c r="K46" s="160" t="n"/>
-      <c r="L46" s="160" t="n"/>
-      <c r="M46" s="160" t="n"/>
-      <c r="N46" s="160" t="n"/>
-      <c r="O46" s="160" t="n"/>
-      <c r="P46" s="160" t="n"/>
-      <c r="Q46" s="160" t="n"/>
-      <c r="R46" s="160" t="n"/>
-      <c r="S46" s="160" t="n"/>
-      <c r="T46" s="158" t="inlineStr">
-        <is>
-          <t>Model value is a placeholder with no source</t>
-        </is>
-      </c>
-      <c r="U46" s="158" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
-        </is>
-      </c>
-      <c r="V46" s="158" t="inlineStr">
-        <is>
-          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="158" t="inlineStr">
-        <is>
-          <t>Light commercial, distance</t>
-        </is>
-      </c>
-      <c r="B47" s="159" t="inlineStr">
-        <is>
-          <t>km/vehicle/year</t>
-        </is>
-      </c>
-      <c r="C47" s="159" t="inlineStr">
-        <is>
-          <t>Model setting</t>
-        </is>
-      </c>
-      <c r="D47" s="160" t="n">
-        <v>28000</v>
-      </c>
-      <c r="E47" s="158" t="inlineStr">
-        <is>
-          <t>Column D is the model's value. The study gives 20,397.0 for LCVDiesel (fleet average, 2014 base).</t>
-        </is>
-      </c>
-      <c r="F47" s="160" t="n"/>
-      <c r="G47" s="160" t="n"/>
-      <c r="H47" s="160" t="n"/>
-      <c r="I47" s="160" t="n"/>
-      <c r="J47" s="160" t="n"/>
-      <c r="K47" s="160" t="n"/>
-      <c r="L47" s="160" t="n"/>
-      <c r="M47" s="160" t="n"/>
-      <c r="N47" s="160" t="n"/>
-      <c r="O47" s="160" t="n"/>
-      <c r="P47" s="160" t="n"/>
-      <c r="Q47" s="160" t="n"/>
-      <c r="R47" s="160" t="n"/>
-      <c r="S47" s="160" t="n"/>
-      <c r="T47" s="158" t="inlineStr">
-        <is>
-          <t>Model value is a placeholder with no source</t>
-        </is>
-      </c>
-      <c r="U47" s="158" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
-        </is>
-      </c>
-      <c r="V47" s="158" t="inlineStr">
-        <is>
-          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="158" t="inlineStr">
-        <is>
-          <t>Heavy commercial, distance</t>
-        </is>
-      </c>
-      <c r="B48" s="159" t="inlineStr">
-        <is>
-          <t>km/vehicle/year</t>
-        </is>
-      </c>
-      <c r="C48" s="159" t="inlineStr">
-        <is>
-          <t>Model setting</t>
-        </is>
-      </c>
-      <c r="D48" s="160" t="n">
-        <v>70000</v>
-      </c>
-      <c r="E48" s="158" t="inlineStr">
-        <is>
-          <t>Column D is the model's value. The study gives 62,461.0 for HCV5Diesel (fleet average, 2014 base).</t>
-        </is>
-      </c>
-      <c r="F48" s="160" t="n"/>
-      <c r="G48" s="160" t="n"/>
-      <c r="H48" s="160" t="n"/>
-      <c r="I48" s="160" t="n"/>
-      <c r="J48" s="160" t="n"/>
-      <c r="K48" s="160" t="n"/>
-      <c r="L48" s="160" t="n"/>
-      <c r="M48" s="160" t="n"/>
-      <c r="N48" s="160" t="n"/>
-      <c r="O48" s="160" t="n"/>
-      <c r="P48" s="160" t="n"/>
-      <c r="Q48" s="160" t="n"/>
-      <c r="R48" s="160" t="n"/>
-      <c r="S48" s="160" t="n"/>
-      <c r="T48" s="158" t="inlineStr">
-        <is>
-          <t>Model value is a placeholder with no source</t>
-        </is>
-      </c>
-      <c r="U48" s="158" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
-        </is>
-      </c>
-      <c r="V48" s="158" t="inlineStr">
-        <is>
-          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="158" t="inlineStr">
-        <is>
-          <t>Petrol cars, fuel use</t>
-        </is>
-      </c>
-      <c r="B49" s="159" t="inlineStr">
-        <is>
-          <t>L/100 km</t>
-        </is>
-      </c>
-      <c r="C49" s="159" t="inlineStr">
-        <is>
-          <t>Model setting</t>
-        </is>
-      </c>
-      <c r="D49" s="160" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E49" s="158" t="inlineStr">
-        <is>
-          <t>Column D is the model's value. The study gives 8.2 for CarGasoline (fleet average, 2014 base).</t>
-        </is>
-      </c>
-      <c r="F49" s="160" t="n"/>
-      <c r="G49" s="160" t="n"/>
-      <c r="H49" s="160" t="n"/>
-      <c r="I49" s="160" t="n"/>
-      <c r="J49" s="160" t="n"/>
-      <c r="K49" s="160" t="n"/>
-      <c r="L49" s="160" t="n"/>
-      <c r="M49" s="160" t="n"/>
-      <c r="N49" s="160" t="n"/>
-      <c r="O49" s="160" t="n"/>
-      <c r="P49" s="160" t="n"/>
-      <c r="Q49" s="160" t="n"/>
-      <c r="R49" s="160" t="n"/>
-      <c r="S49" s="160" t="n"/>
-      <c r="T49" s="158" t="inlineStr">
-        <is>
-          <t>Model value is a placeholder with no source</t>
-        </is>
-      </c>
-      <c r="U49" s="158" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
-        </is>
-      </c>
-      <c r="V49" s="158" t="inlineStr">
-        <is>
-          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="158" t="inlineStr">
-        <is>
-          <t>Diesel light commercial, fuel use</t>
-        </is>
-      </c>
-      <c r="B50" s="159" t="inlineStr">
-        <is>
-          <t>L/100 km</t>
-        </is>
-      </c>
-      <c r="C50" s="159" t="inlineStr">
-        <is>
-          <t>Model setting</t>
-        </is>
-      </c>
-      <c r="D50" s="160" t="n">
-        <v>9</v>
-      </c>
-      <c r="E50" s="158" t="inlineStr">
-        <is>
-          <t>Column D is the model's value. The study gives 12.4 for LCVDiesel (fleet average, 2014 base).</t>
-        </is>
-      </c>
-      <c r="F50" s="160" t="n"/>
-      <c r="G50" s="160" t="n"/>
-      <c r="H50" s="160" t="n"/>
-      <c r="I50" s="160" t="n"/>
-      <c r="J50" s="160" t="n"/>
-      <c r="K50" s="160" t="n"/>
-      <c r="L50" s="160" t="n"/>
-      <c r="M50" s="160" t="n"/>
-      <c r="N50" s="160" t="n"/>
-      <c r="O50" s="160" t="n"/>
-      <c r="P50" s="160" t="n"/>
-      <c r="Q50" s="160" t="n"/>
-      <c r="R50" s="160" t="n"/>
-      <c r="S50" s="160" t="n"/>
-      <c r="T50" s="158" t="inlineStr">
-        <is>
-          <t>Model value is a placeholder with no source</t>
-        </is>
-      </c>
-      <c r="U50" s="158" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
-        </is>
-      </c>
-      <c r="V50" s="158" t="inlineStr">
-        <is>
-          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="158" t="inlineStr">
-        <is>
-          <t>Heavy commercial, fuel use</t>
-        </is>
-      </c>
-      <c r="B51" s="159" t="inlineStr">
-        <is>
-          <t>L/100 km</t>
-        </is>
-      </c>
-      <c r="C51" s="159" t="inlineStr">
-        <is>
-          <t>Model setting</t>
-        </is>
-      </c>
-      <c r="D51" s="160" t="n">
-        <v>35</v>
-      </c>
-      <c r="E51" s="158" t="inlineStr">
-        <is>
-          <t>Column D is the model's value. The study gives 31.2 for HCV5Diesel (fleet average, 2014 base).</t>
-        </is>
-      </c>
-      <c r="F51" s="160" t="n"/>
-      <c r="G51" s="160" t="n"/>
-      <c r="H51" s="160" t="n"/>
-      <c r="I51" s="160" t="n"/>
-      <c r="J51" s="160" t="n"/>
-      <c r="K51" s="160" t="n"/>
-      <c r="L51" s="160" t="n"/>
-      <c r="M51" s="160" t="n"/>
-      <c r="N51" s="160" t="n"/>
-      <c r="O51" s="160" t="n"/>
-      <c r="P51" s="160" t="n"/>
-      <c r="Q51" s="160" t="n"/>
-      <c r="R51" s="160" t="n"/>
-      <c r="S51" s="160" t="n"/>
-      <c r="T51" s="158" t="inlineStr">
-        <is>
-          <t>Model value is a placeholder with no source</t>
-        </is>
-      </c>
-      <c r="U51" s="158" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
-        </is>
-      </c>
-      <c r="V51" s="158" t="inlineStr">
-        <is>
-          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="155" t="inlineStr">
-        <is>
-          <t>Petrol sold per registered petrol vehicle</t>
-        </is>
-      </c>
-      <c r="B52" s="156" t="inlineStr">
-        <is>
-          <t>litres/vehicle/year</t>
-        </is>
-      </c>
-      <c r="C52" s="156" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D52" s="168" t="n"/>
-      <c r="E52" s="155" t="inlineStr">
-        <is>
-          <t>National petrol sales used (History) divided by registered petrol vehicles.</t>
-        </is>
-      </c>
-      <c r="F52" s="168">
-        <f>IF(COUNT(History!F57,F39)&lt;2,"",History!F57*1000000/F39)</f>
-        <v/>
-      </c>
-      <c r="G52" s="168">
-        <f>IF(COUNT(History!G57,G39)&lt;2,"",History!G57*1000000/G39)</f>
-        <v/>
-      </c>
-      <c r="H52" s="168">
-        <f>IF(COUNT(History!H57,H39)&lt;2,"",History!H57*1000000/H39)</f>
-        <v/>
-      </c>
-      <c r="I52" s="168">
-        <f>IF(COUNT(History!I57,I39)&lt;2,"",History!I57*1000000/I39)</f>
-        <v/>
-      </c>
-      <c r="J52" s="168">
-        <f>IF(COUNT(History!J57,J39)&lt;2,"",History!J57*1000000/J39)</f>
-        <v/>
-      </c>
-      <c r="K52" s="168">
-        <f>IF(COUNT(History!K57,K39)&lt;2,"",History!K57*1000000/K39)</f>
-        <v/>
-      </c>
-      <c r="L52" s="168">
-        <f>IF(COUNT(History!L57,L39)&lt;2,"",History!L57*1000000/L39)</f>
-        <v/>
-      </c>
-      <c r="M52" s="168">
-        <f>IF(COUNT(History!M57,M39)&lt;2,"",History!M57*1000000/M39)</f>
-        <v/>
-      </c>
-      <c r="N52" s="168">
-        <f>IF(COUNT(History!N57,N39)&lt;2,"",History!N57*1000000/N39)</f>
-        <v/>
-      </c>
-      <c r="O52" s="168">
-        <f>IF(COUNT(History!O57,O39)&lt;2,"",History!O57*1000000/O39)</f>
-        <v/>
-      </c>
-      <c r="P52" s="168">
-        <f>IF(COUNT(History!P57,P39)&lt;2,"",History!P57*1000000/P39)</f>
-        <v/>
-      </c>
-      <c r="Q52" s="168">
-        <f>IF(COUNT(History!Q57,Q39)&lt;2,"",History!Q57*1000000/Q39)</f>
-        <v/>
-      </c>
-      <c r="R52" s="168">
-        <f>IF(COUNT(History!R57,R39)&lt;2,"",History!R57*1000000/R39)</f>
-        <v/>
-      </c>
-      <c r="S52" s="168">
-        <f>IF(COUNT(History!S57,S39)&lt;2,"",History!S57*1000000/S39)</f>
-        <v/>
-      </c>
-      <c r="T52" s="155" t="inlineStr"/>
-      <c r="U52" s="155" t="inlineStr"/>
-      <c r="V52" s="155" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="155" t="inlineStr">
-        <is>
-          <t>Distance implied by petrol sales</t>
-        </is>
-      </c>
-      <c r="B53" s="156" t="inlineStr">
-        <is>
-          <t>km/vehicle/year</t>
-        </is>
-      </c>
-      <c r="C53" s="156" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D53" s="168" t="n">
-        <v>17000</v>
-      </c>
-      <c r="E53" s="155" t="inlineStr">
-        <is>
-          <t>Litres per vehicle divided by 8.2 L/100 km (the study's petrol car average). Column D is the model's passenger distance.</t>
-        </is>
-      </c>
-      <c r="F53" s="168">
-        <f>IF(ISNUMBER(F52),F52/8.2*100,"")</f>
-        <v/>
-      </c>
-      <c r="G53" s="168">
-        <f>IF(ISNUMBER(G52),G52/8.2*100,"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="168">
-        <f>IF(ISNUMBER(H52),H52/8.2*100,"")</f>
-        <v/>
-      </c>
-      <c r="I53" s="168">
-        <f>IF(ISNUMBER(I52),I52/8.2*100,"")</f>
-        <v/>
-      </c>
-      <c r="J53" s="168">
-        <f>IF(ISNUMBER(J52),J52/8.2*100,"")</f>
-        <v/>
-      </c>
-      <c r="K53" s="168">
-        <f>IF(ISNUMBER(K52),K52/8.2*100,"")</f>
-        <v/>
-      </c>
-      <c r="L53" s="168">
-        <f>IF(ISNUMBER(L52),L52/8.2*100,"")</f>
-        <v/>
-      </c>
-      <c r="M53" s="168">
-        <f>IF(ISNUMBER(M52),M52/8.2*100,"")</f>
-        <v/>
-      </c>
-      <c r="N53" s="168">
-        <f>IF(ISNUMBER(N52),N52/8.2*100,"")</f>
-        <v/>
-      </c>
-      <c r="O53" s="168">
-        <f>IF(ISNUMBER(O52),O52/8.2*100,"")</f>
-        <v/>
-      </c>
-      <c r="P53" s="168">
-        <f>IF(ISNUMBER(P52),P52/8.2*100,"")</f>
-        <v/>
-      </c>
-      <c r="Q53" s="168">
-        <f>IF(ISNUMBER(Q52),Q52/8.2*100,"")</f>
-        <v/>
-      </c>
-      <c r="R53" s="168">
-        <f>IF(ISNUMBER(R52),R52/8.2*100,"")</f>
-        <v/>
-      </c>
-      <c r="S53" s="168">
-        <f>IF(ISNUMBER(S52),S52/8.2*100,"")</f>
-        <v/>
-      </c>
-      <c r="T53" s="155" t="inlineStr"/>
-      <c r="U53" s="155" t="inlineStr"/>
-      <c r="V53" s="155" t="inlineStr">
-        <is>
-          <t>If the model's distance and fuel use both held, petrol sales would be far above what is recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="151" t="inlineStr">
-        <is>
-          <t>7. Not available from any source held</t>
-        </is>
-      </c>
-      <c r="B55" s="151" t="n"/>
-      <c r="C55" s="151" t="n"/>
-      <c r="D55" s="151" t="n"/>
-      <c r="E55" s="151" t="n"/>
-      <c r="F55" s="151" t="n"/>
-      <c r="G55" s="151" t="n"/>
-      <c r="H55" s="151" t="n"/>
-      <c r="I55" s="151" t="n"/>
-      <c r="J55" s="151" t="n"/>
-      <c r="K55" s="151" t="n"/>
-      <c r="L55" s="151" t="n"/>
-      <c r="M55" s="151" t="n"/>
-      <c r="N55" s="151" t="n"/>
-      <c r="O55" s="151" t="n"/>
-      <c r="P55" s="151" t="n"/>
-      <c r="Q55" s="151" t="n"/>
-      <c r="R55" s="151" t="n"/>
-      <c r="S55" s="151" t="n"/>
-      <c r="T55" s="151" t="n"/>
-      <c r="U55" s="151" t="n"/>
-      <c r="V55" s="151" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="161" t="inlineStr">
-        <is>
-          <t>Stock by age (year of first registration)</t>
-        </is>
-      </c>
-      <c r="B56" s="162" t="inlineStr"/>
-      <c r="C56" s="162" t="inlineStr">
-        <is>
-          <t>Missing input</t>
-        </is>
-      </c>
-      <c r="D56" s="164" t="n"/>
-      <c r="E56" s="161" t="inlineStr">
-        <is>
-          <t>Needed for the cohort calculation; NaTIS publishes totals by class only.</t>
-        </is>
-      </c>
-      <c r="F56" s="164" t="n"/>
-      <c r="G56" s="164" t="n"/>
-      <c r="H56" s="164" t="n"/>
-      <c r="I56" s="164" t="n"/>
-      <c r="J56" s="164" t="n"/>
-      <c r="K56" s="164" t="n"/>
-      <c r="L56" s="164" t="n"/>
-      <c r="M56" s="164" t="n"/>
-      <c r="N56" s="164" t="n"/>
-      <c r="O56" s="164" t="n"/>
-      <c r="P56" s="164" t="n"/>
-      <c r="Q56" s="164" t="n"/>
-      <c r="R56" s="164" t="n"/>
-      <c r="S56" s="164" t="n"/>
-      <c r="T56" s="161" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="U56" s="161" t="inlineStr"/>
-      <c r="V56" s="161" t="inlineStr">
-        <is>
-          <t>Source to be found or assumption agreed</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="161" t="inlineStr">
-        <is>
-          <t>Stock by fuel within each class</t>
-        </is>
-      </c>
-      <c r="B57" s="162" t="inlineStr"/>
-      <c r="C57" s="162" t="inlineStr">
-        <is>
-          <t>Missing input</t>
-        </is>
-      </c>
-      <c r="D57" s="164" t="n"/>
-      <c r="E57" s="161" t="inlineStr">
-        <is>
-          <t>Only an all-class fuel count exists, for December 2023.</t>
-        </is>
-      </c>
-      <c r="F57" s="164" t="n"/>
-      <c r="G57" s="164" t="n"/>
-      <c r="H57" s="164" t="n"/>
-      <c r="I57" s="164" t="n"/>
-      <c r="J57" s="164" t="n"/>
-      <c r="K57" s="164" t="n"/>
-      <c r="L57" s="164" t="n"/>
-      <c r="M57" s="164" t="n"/>
-      <c r="N57" s="164" t="n"/>
-      <c r="O57" s="164" t="n"/>
-      <c r="P57" s="164" t="n"/>
-      <c r="Q57" s="164" t="n"/>
-      <c r="R57" s="164" t="n"/>
-      <c r="S57" s="164" t="n"/>
-      <c r="T57" s="161" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="U57" s="161" t="inlineStr"/>
-      <c r="V57" s="161" t="inlineStr">
-        <is>
-          <t>Source to be found or assumption agreed</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="161" t="inlineStr">
-        <is>
-          <t>Electric and hybrid vehicles in the fleet by year</t>
-        </is>
-      </c>
-      <c r="B58" s="162" t="inlineStr"/>
-      <c r="C58" s="162" t="inlineStr">
-        <is>
-          <t>Missing input</t>
-        </is>
-      </c>
-      <c r="D58" s="164" t="n"/>
-      <c r="E58" s="161" t="inlineStr">
-        <is>
-          <t>Sales are known from 2019; stock only for December 2023.</t>
-        </is>
-      </c>
-      <c r="F58" s="164" t="n"/>
-      <c r="G58" s="164" t="n"/>
-      <c r="H58" s="164" t="n"/>
-      <c r="I58" s="164" t="n"/>
-      <c r="J58" s="164" t="n"/>
-      <c r="K58" s="164" t="n"/>
-      <c r="L58" s="164" t="n"/>
-      <c r="M58" s="164" t="n"/>
-      <c r="N58" s="164" t="n"/>
-      <c r="O58" s="164" t="n"/>
-      <c r="P58" s="164" t="n"/>
-      <c r="Q58" s="164" t="n"/>
-      <c r="R58" s="164" t="n"/>
-      <c r="S58" s="164" t="n"/>
-      <c r="T58" s="161" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="U58" s="161" t="inlineStr"/>
-      <c r="V58" s="161" t="inlineStr">
-        <is>
-          <t>Source to be found or assumption agreed</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="161" t="inlineStr">
-        <is>
-          <t>Distance driven after 2014</t>
-        </is>
-      </c>
-      <c r="B59" s="162" t="inlineStr"/>
-      <c r="C59" s="162" t="inlineStr">
-        <is>
-          <t>Missing input</t>
-        </is>
-      </c>
-      <c r="D59" s="164" t="n"/>
-      <c r="E59" s="161" t="inlineStr">
-        <is>
-          <t>The study's figures are a 2014 base; no later survey is held.</t>
-        </is>
-      </c>
-      <c r="F59" s="164" t="n"/>
-      <c r="G59" s="164" t="n"/>
-      <c r="H59" s="164" t="n"/>
-      <c r="I59" s="164" t="n"/>
-      <c r="J59" s="164" t="n"/>
-      <c r="K59" s="164" t="n"/>
-      <c r="L59" s="164" t="n"/>
-      <c r="M59" s="164" t="n"/>
-      <c r="N59" s="164" t="n"/>
-      <c r="O59" s="164" t="n"/>
-      <c r="P59" s="164" t="n"/>
-      <c r="Q59" s="164" t="n"/>
-      <c r="R59" s="164" t="n"/>
-      <c r="S59" s="164" t="n"/>
-      <c r="T59" s="161" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="U59" s="161" t="inlineStr"/>
-      <c r="V59" s="161" t="inlineStr">
-        <is>
-          <t>Source to be found or assumption agreed</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="161" t="inlineStr">
-        <is>
-          <t>Petrol and diesel split of new sales by segment</t>
-        </is>
-      </c>
-      <c r="B60" s="162" t="inlineStr"/>
-      <c r="C60" s="162" t="inlineStr">
-        <is>
-          <t>Missing input</t>
-        </is>
-      </c>
-      <c r="D60" s="164" t="n"/>
-      <c r="E60" s="161" t="inlineStr">
-        <is>
-          <t>naamsa reports drivetrain for the total market only.</t>
-        </is>
-      </c>
-      <c r="F60" s="164" t="n"/>
-      <c r="G60" s="164" t="n"/>
-      <c r="H60" s="164" t="n"/>
-      <c r="I60" s="164" t="n"/>
-      <c r="J60" s="164" t="n"/>
-      <c r="K60" s="164" t="n"/>
-      <c r="L60" s="164" t="n"/>
-      <c r="M60" s="164" t="n"/>
-      <c r="N60" s="164" t="n"/>
-      <c r="O60" s="164" t="n"/>
-      <c r="P60" s="164" t="n"/>
-      <c r="Q60" s="164" t="n"/>
-      <c r="R60" s="164" t="n"/>
-      <c r="S60" s="164" t="n"/>
-      <c r="T60" s="161" t="inlineStr">
-        <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="U60" s="161" t="inlineStr"/>
-      <c r="V60" s="161" t="inlineStr">
-        <is>
-          <t>Source to be found or assumption agreed</t>
-        </is>
-      </c>
+      <c r="A32" s="158" t="inlineStr">
+        <is>
+          <t>Reading the class names</t>
+        </is>
+      </c>
+      <c r="B32" s="159" t="inlineStr"/>
+      <c r="C32" s="159" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D32" s="160" t="n"/>
+      <c r="E32" s="158" t="inlineStr">
+        <is>
+          <t>Car and SUV are private passenger vehicles; Bus is buses; MBT is minibus taxis; Moto is motorcycles; LCV is light commercial vehicles (bakkies and vans); HCV1 to HCV9 are trucks in nine weight classes, lightest to heaviest.</t>
+        </is>
+      </c>
+      <c r="F32" s="160" t="n"/>
+      <c r="G32" s="160" t="n"/>
+      <c r="H32" s="160" t="n"/>
+      <c r="I32" s="160" t="n"/>
+      <c r="J32" s="160" t="n"/>
+      <c r="K32" s="160" t="n"/>
+      <c r="L32" s="160" t="n"/>
+      <c r="M32" s="160" t="n"/>
+      <c r="N32" s="160" t="n"/>
+      <c r="O32" s="160" t="n"/>
+      <c r="P32" s="160" t="n"/>
+      <c r="Q32" s="160" t="n"/>
+      <c r="R32" s="160" t="n"/>
+      <c r="S32" s="160" t="n"/>
+      <c r="T32" s="158" t="inlineStr"/>
+      <c r="U32" s="158" t="inlineStr"/>
+      <c r="V32" s="158" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -50465,6 +48888,3246 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:V60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="11.5" customWidth="1" min="6" max="6"/>
+    <col width="11.5" customWidth="1" min="7" max="7"/>
+    <col width="11.5" customWidth="1" min="8" max="8"/>
+    <col width="11.5" customWidth="1" min="9" max="9"/>
+    <col width="11.5" customWidth="1" min="10" max="10"/>
+    <col width="11.5" customWidth="1" min="11" max="11"/>
+    <col width="11.5" customWidth="1" min="12" max="12"/>
+    <col width="11.5" customWidth="1" min="13" max="13"/>
+    <col width="11.5" customWidth="1" min="14" max="14"/>
+    <col width="11.5" customWidth="1" min="15" max="15"/>
+    <col width="11.5" customWidth="1" min="16" max="16"/>
+    <col width="11.5" customWidth="1" min="17" max="17"/>
+    <col width="11.5" customWidth="1" min="18" max="18"/>
+    <col width="11.5" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="44" customWidth="1" min="21" max="21"/>
+    <col width="44" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="149" t="inlineStr">
+        <is>
+          <t>Vehicle block: what is observed beside what the model assumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Stock, new sales, scrapping, drivetrain, fuel split and use. Observations are values from the registered inputs; the model's settings are in column D; shares, retirements and cross-checks are formulas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="150" t="inlineStr">
+        <is>
+          <t>Driver / output</t>
+        </is>
+      </c>
+      <c r="B4" s="150" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C4" s="150" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D4" s="150" t="inlineStr">
+        <is>
+          <t>Scalar / latest value</t>
+        </is>
+      </c>
+      <c r="E4" s="150" t="inlineStr">
+        <is>
+          <t>Definition / period</t>
+        </is>
+      </c>
+      <c r="F4" s="150" t="n">
+        <v>2012</v>
+      </c>
+      <c r="G4" s="150" t="n">
+        <v>2013</v>
+      </c>
+      <c r="H4" s="150" t="n">
+        <v>2014</v>
+      </c>
+      <c r="I4" s="150" t="n">
+        <v>2015</v>
+      </c>
+      <c r="J4" s="150" t="n">
+        <v>2016</v>
+      </c>
+      <c r="K4" s="150" t="n">
+        <v>2017</v>
+      </c>
+      <c r="L4" s="150" t="n">
+        <v>2018</v>
+      </c>
+      <c r="M4" s="150" t="n">
+        <v>2019</v>
+      </c>
+      <c r="N4" s="150" t="n">
+        <v>2020</v>
+      </c>
+      <c r="O4" s="150" t="n">
+        <v>2021</v>
+      </c>
+      <c r="P4" s="150" t="n">
+        <v>2022</v>
+      </c>
+      <c r="Q4" s="150" t="n">
+        <v>2023</v>
+      </c>
+      <c r="R4" s="150" t="n">
+        <v>2024</v>
+      </c>
+      <c r="S4" s="150" t="n">
+        <v>2025</v>
+      </c>
+      <c r="T4" s="150" t="inlineStr">
+        <is>
+          <t>Coverage / status</t>
+        </is>
+      </c>
+      <c r="U4" s="150" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="V4" s="150" t="inlineStr">
+        <is>
+          <t>Missing evidence / next action</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="151" t="inlineStr">
+        <is>
+          <t>1. Registered vehicles at December</t>
+        </is>
+      </c>
+      <c r="B5" s="151" t="n"/>
+      <c r="C5" s="151" t="n"/>
+      <c r="D5" s="151" t="n"/>
+      <c r="E5" s="151" t="n"/>
+      <c r="F5" s="151" t="n"/>
+      <c r="G5" s="151" t="n"/>
+      <c r="H5" s="151" t="n"/>
+      <c r="I5" s="151" t="n"/>
+      <c r="J5" s="151" t="n"/>
+      <c r="K5" s="151" t="n"/>
+      <c r="L5" s="151" t="n"/>
+      <c r="M5" s="151" t="n"/>
+      <c r="N5" s="151" t="n"/>
+      <c r="O5" s="151" t="n"/>
+      <c r="P5" s="151" t="n"/>
+      <c r="Q5" s="151" t="n"/>
+      <c r="R5" s="151" t="n"/>
+      <c r="S5" s="151" t="n"/>
+      <c r="T5" s="151" t="n"/>
+      <c r="U5" s="151" t="n"/>
+      <c r="V5" s="151" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="152" t="inlineStr">
+        <is>
+          <t>Cars</t>
+        </is>
+      </c>
+      <c r="B6" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C6" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D6" s="166" t="n"/>
+      <c r="E6" s="152" t="inlineStr">
+        <is>
+          <t>Live (licensed) vehicles, all fuels together.</t>
+        </is>
+      </c>
+      <c r="F6" s="166" t="n"/>
+      <c r="G6" s="166" t="n"/>
+      <c r="H6" s="166" t="n"/>
+      <c r="I6" s="166" t="n"/>
+      <c r="J6" s="166" t="n"/>
+      <c r="K6" s="166" t="n"/>
+      <c r="L6" s="166" t="n"/>
+      <c r="M6" s="166" t="n"/>
+      <c r="N6" s="166" t="n"/>
+      <c r="O6" s="166" t="n">
+        <v>7652077</v>
+      </c>
+      <c r="P6" s="166" t="n">
+        <v>7685153</v>
+      </c>
+      <c r="Q6" s="166" t="n">
+        <v>7794164</v>
+      </c>
+      <c r="R6" s="166" t="n">
+        <v>7949275</v>
+      </c>
+      <c r="S6" s="166" t="n">
+        <v>8184111</v>
+      </c>
+      <c r="T6" s="152" t="inlineStr">
+        <is>
+          <t>2021-2025</t>
+        </is>
+      </c>
+      <c r="U6" s="152" t="inlineStr">
+        <is>
+          <t>NaTIS live vehicle population, December</t>
+        </is>
+      </c>
+      <c r="V6" s="152" t="inlineStr">
+        <is>
+          <t>No split by fuel or by age in this source</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="152" t="inlineStr">
+        <is>
+          <t>Light commercial vehicles</t>
+        </is>
+      </c>
+      <c r="B7" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C7" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D7" s="166" t="n"/>
+      <c r="E7" s="152" t="inlineStr">
+        <is>
+          <t>Live (licensed) vehicles, all fuels together.</t>
+        </is>
+      </c>
+      <c r="F7" s="166" t="n"/>
+      <c r="G7" s="166" t="n"/>
+      <c r="H7" s="166" t="n"/>
+      <c r="I7" s="166" t="n"/>
+      <c r="J7" s="166" t="n"/>
+      <c r="K7" s="166" t="n"/>
+      <c r="L7" s="166" t="n"/>
+      <c r="M7" s="166" t="n"/>
+      <c r="N7" s="166" t="n"/>
+      <c r="O7" s="166" t="n">
+        <v>2671314</v>
+      </c>
+      <c r="P7" s="166" t="n">
+        <v>2658416</v>
+      </c>
+      <c r="Q7" s="166" t="n">
+        <v>2689310</v>
+      </c>
+      <c r="R7" s="166" t="n">
+        <v>2725606</v>
+      </c>
+      <c r="S7" s="166" t="n">
+        <v>2776258</v>
+      </c>
+      <c r="T7" s="152" t="inlineStr">
+        <is>
+          <t>2021-2025</t>
+        </is>
+      </c>
+      <c r="U7" s="152" t="inlineStr">
+        <is>
+          <t>NaTIS live vehicle population, December</t>
+        </is>
+      </c>
+      <c r="V7" s="152" t="inlineStr">
+        <is>
+          <t>No split by fuel or by age in this source</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="152" t="inlineStr">
+        <is>
+          <t>Trucks</t>
+        </is>
+      </c>
+      <c r="B8" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C8" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D8" s="166" t="n"/>
+      <c r="E8" s="152" t="inlineStr">
+        <is>
+          <t>Live (licensed) vehicles, all fuels together.</t>
+        </is>
+      </c>
+      <c r="F8" s="166" t="n"/>
+      <c r="G8" s="166" t="n"/>
+      <c r="H8" s="166" t="n"/>
+      <c r="I8" s="166" t="n"/>
+      <c r="J8" s="166" t="n"/>
+      <c r="K8" s="166" t="n"/>
+      <c r="L8" s="166" t="n"/>
+      <c r="M8" s="166" t="n"/>
+      <c r="N8" s="166" t="n"/>
+      <c r="O8" s="166" t="n">
+        <v>389112</v>
+      </c>
+      <c r="P8" s="166" t="n">
+        <v>385845</v>
+      </c>
+      <c r="Q8" s="166" t="n">
+        <v>392349</v>
+      </c>
+      <c r="R8" s="166" t="n">
+        <v>398542</v>
+      </c>
+      <c r="S8" s="166" t="n">
+        <v>404752</v>
+      </c>
+      <c r="T8" s="152" t="inlineStr">
+        <is>
+          <t>2021-2025</t>
+        </is>
+      </c>
+      <c r="U8" s="152" t="inlineStr">
+        <is>
+          <t>NaTIS live vehicle population, December</t>
+        </is>
+      </c>
+      <c r="V8" s="152" t="inlineStr">
+        <is>
+          <t>No split by fuel or by age in this source</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="152" t="inlineStr">
+        <is>
+          <t>Buses</t>
+        </is>
+      </c>
+      <c r="B9" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C9" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D9" s="166" t="n"/>
+      <c r="E9" s="152" t="inlineStr">
+        <is>
+          <t>Live (licensed) vehicles, all fuels together.</t>
+        </is>
+      </c>
+      <c r="F9" s="166" t="n"/>
+      <c r="G9" s="166" t="n"/>
+      <c r="H9" s="166" t="n"/>
+      <c r="I9" s="166" t="n"/>
+      <c r="J9" s="166" t="n"/>
+      <c r="K9" s="166" t="n"/>
+      <c r="L9" s="166" t="n"/>
+      <c r="M9" s="166" t="n"/>
+      <c r="N9" s="166" t="n"/>
+      <c r="O9" s="166" t="n">
+        <v>64340</v>
+      </c>
+      <c r="P9" s="166" t="n">
+        <v>64170</v>
+      </c>
+      <c r="Q9" s="166" t="n">
+        <v>64982</v>
+      </c>
+      <c r="R9" s="166" t="n">
+        <v>65792</v>
+      </c>
+      <c r="S9" s="166" t="n">
+        <v>66249</v>
+      </c>
+      <c r="T9" s="152" t="inlineStr">
+        <is>
+          <t>2021-2025</t>
+        </is>
+      </c>
+      <c r="U9" s="152" t="inlineStr">
+        <is>
+          <t>NaTIS live vehicle population, December</t>
+        </is>
+      </c>
+      <c r="V9" s="152" t="inlineStr">
+        <is>
+          <t>No split by fuel or by age in this source</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="152" t="inlineStr">
+        <is>
+          <t>Minibuses</t>
+        </is>
+      </c>
+      <c r="B10" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C10" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D10" s="166" t="n"/>
+      <c r="E10" s="152" t="inlineStr">
+        <is>
+          <t>Live (licensed) vehicles, all fuels together.</t>
+        </is>
+      </c>
+      <c r="F10" s="166" t="n"/>
+      <c r="G10" s="166" t="n"/>
+      <c r="H10" s="166" t="n"/>
+      <c r="I10" s="166" t="n"/>
+      <c r="J10" s="166" t="n"/>
+      <c r="K10" s="166" t="n"/>
+      <c r="L10" s="166" t="n"/>
+      <c r="M10" s="166" t="n"/>
+      <c r="N10" s="166" t="n"/>
+      <c r="O10" s="166" t="n">
+        <v>349671</v>
+      </c>
+      <c r="P10" s="166" t="n">
+        <v>349335</v>
+      </c>
+      <c r="Q10" s="166" t="n">
+        <v>355235</v>
+      </c>
+      <c r="R10" s="166" t="n">
+        <v>355139</v>
+      </c>
+      <c r="S10" s="166" t="n">
+        <v>355145</v>
+      </c>
+      <c r="T10" s="152" t="inlineStr">
+        <is>
+          <t>2021-2025</t>
+        </is>
+      </c>
+      <c r="U10" s="152" t="inlineStr">
+        <is>
+          <t>NaTIS live vehicle population, December</t>
+        </is>
+      </c>
+      <c r="V10" s="152" t="inlineStr">
+        <is>
+          <t>No split by fuel or by age in this source</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="152" t="inlineStr">
+        <is>
+          <t>Motorcycles</t>
+        </is>
+      </c>
+      <c r="B11" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C11" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D11" s="166" t="n"/>
+      <c r="E11" s="152" t="inlineStr">
+        <is>
+          <t>Live (licensed) vehicles, all fuels together.</t>
+        </is>
+      </c>
+      <c r="F11" s="166" t="n"/>
+      <c r="G11" s="166" t="n"/>
+      <c r="H11" s="166" t="n"/>
+      <c r="I11" s="166" t="n"/>
+      <c r="J11" s="166" t="n"/>
+      <c r="K11" s="166" t="n"/>
+      <c r="L11" s="166" t="n"/>
+      <c r="M11" s="166" t="n"/>
+      <c r="N11" s="166" t="n"/>
+      <c r="O11" s="166" t="n">
+        <v>347631</v>
+      </c>
+      <c r="P11" s="166" t="n">
+        <v>346153</v>
+      </c>
+      <c r="Q11" s="166" t="n">
+        <v>349215</v>
+      </c>
+      <c r="R11" s="166" t="n">
+        <v>358817</v>
+      </c>
+      <c r="S11" s="166" t="n">
+        <v>372137</v>
+      </c>
+      <c r="T11" s="152" t="inlineStr">
+        <is>
+          <t>2021-2025</t>
+        </is>
+      </c>
+      <c r="U11" s="152" t="inlineStr">
+        <is>
+          <t>NaTIS live vehicle population, December</t>
+        </is>
+      </c>
+      <c r="V11" s="152" t="inlineStr">
+        <is>
+          <t>No split by fuel or by age in this source</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="151" t="inlineStr">
+        <is>
+          <t>2. New vehicle sales</t>
+        </is>
+      </c>
+      <c r="B13" s="151" t="n"/>
+      <c r="C13" s="151" t="n"/>
+      <c r="D13" s="151" t="n"/>
+      <c r="E13" s="151" t="n"/>
+      <c r="F13" s="151" t="n"/>
+      <c r="G13" s="151" t="n"/>
+      <c r="H13" s="151" t="n"/>
+      <c r="I13" s="151" t="n"/>
+      <c r="J13" s="151" t="n"/>
+      <c r="K13" s="151" t="n"/>
+      <c r="L13" s="151" t="n"/>
+      <c r="M13" s="151" t="n"/>
+      <c r="N13" s="151" t="n"/>
+      <c r="O13" s="151" t="n"/>
+      <c r="P13" s="151" t="n"/>
+      <c r="Q13" s="151" t="n"/>
+      <c r="R13" s="151" t="n"/>
+      <c r="S13" s="151" t="n"/>
+      <c r="T13" s="151" t="n"/>
+      <c r="U13" s="151" t="n"/>
+      <c r="V13" s="151" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="152" t="inlineStr">
+        <is>
+          <t>Cars, new sales</t>
+        </is>
+      </c>
+      <c r="B14" s="153" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C14" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D14" s="166" t="n"/>
+      <c r="E14" s="152" t="inlineStr">
+        <is>
+          <t>Actual new sales, all drivetrains.</t>
+        </is>
+      </c>
+      <c r="F14" s="166" t="n"/>
+      <c r="G14" s="166" t="n"/>
+      <c r="H14" s="166" t="n"/>
+      <c r="I14" s="166" t="n">
+        <v>412397</v>
+      </c>
+      <c r="J14" s="166" t="n">
+        <v>361265</v>
+      </c>
+      <c r="K14" s="166" t="n">
+        <v>368114</v>
+      </c>
+      <c r="L14" s="166" t="n">
+        <v>365247</v>
+      </c>
+      <c r="M14" s="166" t="n">
+        <v>355379</v>
+      </c>
+      <c r="N14" s="166" t="n">
+        <v>246541</v>
+      </c>
+      <c r="O14" s="166" t="n">
+        <v>304338</v>
+      </c>
+      <c r="P14" s="166" t="n">
+        <v>363681</v>
+      </c>
+      <c r="Q14" s="166" t="n">
+        <v>347377</v>
+      </c>
+      <c r="R14" s="166" t="n">
+        <v>351553</v>
+      </c>
+      <c r="S14" s="166" t="n">
+        <v>422463</v>
+      </c>
+      <c r="T14" s="152" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+      <c r="U14" s="152" t="inlineStr">
+        <is>
+          <t>naamsa industry vehicle sales</t>
+        </is>
+      </c>
+      <c r="V14" s="152" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="152" t="inlineStr">
+        <is>
+          <t>Light commercial vehicles, new sales</t>
+        </is>
+      </c>
+      <c r="B15" s="153" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C15" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D15" s="166" t="n"/>
+      <c r="E15" s="152" t="inlineStr">
+        <is>
+          <t>Actual new sales, all drivetrains.</t>
+        </is>
+      </c>
+      <c r="F15" s="166" t="n"/>
+      <c r="G15" s="166" t="n"/>
+      <c r="H15" s="166" t="n"/>
+      <c r="I15" s="166" t="n">
+        <v>174812</v>
+      </c>
+      <c r="J15" s="166" t="n">
+        <v>159316</v>
+      </c>
+      <c r="K15" s="166" t="n">
+        <v>163317</v>
+      </c>
+      <c r="L15" s="166" t="n">
+        <v>159525</v>
+      </c>
+      <c r="M15" s="166" t="n">
+        <v>153221</v>
+      </c>
+      <c r="N15" s="166" t="n">
+        <v>110912</v>
+      </c>
+      <c r="O15" s="166" t="n">
+        <v>133078</v>
+      </c>
+      <c r="P15" s="166" t="n">
+        <v>135711</v>
+      </c>
+      <c r="Q15" s="166" t="n">
+        <v>151490</v>
+      </c>
+      <c r="R15" s="166" t="n">
+        <v>133375</v>
+      </c>
+      <c r="S15" s="166" t="n">
+        <v>143964</v>
+      </c>
+      <c r="T15" s="152" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+      <c r="U15" s="152" t="inlineStr">
+        <is>
+          <t>naamsa industry vehicle sales</t>
+        </is>
+      </c>
+      <c r="V15" s="152" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="152" t="inlineStr">
+        <is>
+          <t>Medium and heavy commercial vehicles, new sales</t>
+        </is>
+      </c>
+      <c r="B16" s="153" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C16" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D16" s="166" t="n"/>
+      <c r="E16" s="152" t="inlineStr">
+        <is>
+          <t>Actual new sales, all drivetrains.</t>
+        </is>
+      </c>
+      <c r="F16" s="166" t="n"/>
+      <c r="G16" s="166" t="n"/>
+      <c r="H16" s="166" t="n"/>
+      <c r="I16" s="166" t="n">
+        <v>30441</v>
+      </c>
+      <c r="J16" s="166" t="n">
+        <v>26972</v>
+      </c>
+      <c r="K16" s="166" t="n">
+        <v>26272</v>
+      </c>
+      <c r="L16" s="166" t="n">
+        <v>27449</v>
+      </c>
+      <c r="M16" s="166" t="n">
+        <v>27891</v>
+      </c>
+      <c r="N16" s="166" t="n">
+        <v>22614</v>
+      </c>
+      <c r="O16" s="166" t="n">
+        <v>26906</v>
+      </c>
+      <c r="P16" s="166" t="n">
+        <v>29942</v>
+      </c>
+      <c r="Q16" s="166" t="n">
+        <v>32690</v>
+      </c>
+      <c r="R16" s="166" t="n">
+        <v>31175</v>
+      </c>
+      <c r="S16" s="166" t="n">
+        <v>30911</v>
+      </c>
+      <c r="T16" s="152" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+      <c r="U16" s="152" t="inlineStr">
+        <is>
+          <t>naamsa industry vehicle sales</t>
+        </is>
+      </c>
+      <c r="V16" s="152" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="152" t="inlineStr">
+        <is>
+          <t>All segments, new sales</t>
+        </is>
+      </c>
+      <c r="B17" s="153" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C17" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D17" s="166" t="n"/>
+      <c r="E17" s="152" t="inlineStr">
+        <is>
+          <t>Total market as reported.</t>
+        </is>
+      </c>
+      <c r="F17" s="166" t="n"/>
+      <c r="G17" s="166" t="n"/>
+      <c r="H17" s="166" t="n"/>
+      <c r="I17" s="166" t="n">
+        <v>617650</v>
+      </c>
+      <c r="J17" s="166" t="n">
+        <v>547552</v>
+      </c>
+      <c r="K17" s="166" t="n">
+        <v>557719</v>
+      </c>
+      <c r="L17" s="166" t="n">
+        <v>552221</v>
+      </c>
+      <c r="M17" s="166" t="n">
+        <v>536486</v>
+      </c>
+      <c r="N17" s="166" t="n">
+        <v>380065</v>
+      </c>
+      <c r="O17" s="166" t="n">
+        <v>464322</v>
+      </c>
+      <c r="P17" s="166" t="n">
+        <v>529335</v>
+      </c>
+      <c r="Q17" s="166" t="n">
+        <v>531557</v>
+      </c>
+      <c r="R17" s="166" t="n">
+        <v>516103</v>
+      </c>
+      <c r="S17" s="166" t="n">
+        <v>597338</v>
+      </c>
+      <c r="T17" s="152" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+      <c r="U17" s="152" t="inlineStr">
+        <is>
+          <t>naamsa industry vehicle sales</t>
+        </is>
+      </c>
+      <c r="V17" s="152" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="155" t="inlineStr">
+        <is>
+          <t>Cars share of new sales</t>
+        </is>
+      </c>
+      <c r="B18" s="156" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C18" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D18" s="169" t="n">
+        <v>78</v>
+      </c>
+      <c r="E18" s="155" t="inlineStr">
+        <is>
+          <t>Observed share. Column D is the model's fixed split of new vehicles.</t>
+        </is>
+      </c>
+      <c r="F18" s="169">
+        <f>IF(COUNT(F14,F17)&lt;2,"",F14/F17*100)</f>
+        <v/>
+      </c>
+      <c r="G18" s="169">
+        <f>IF(COUNT(G14,G17)&lt;2,"",G14/G17*100)</f>
+        <v/>
+      </c>
+      <c r="H18" s="169">
+        <f>IF(COUNT(H14,H17)&lt;2,"",H14/H17*100)</f>
+        <v/>
+      </c>
+      <c r="I18" s="169">
+        <f>IF(COUNT(I14,I17)&lt;2,"",I14/I17*100)</f>
+        <v/>
+      </c>
+      <c r="J18" s="169">
+        <f>IF(COUNT(J14,J17)&lt;2,"",J14/J17*100)</f>
+        <v/>
+      </c>
+      <c r="K18" s="169">
+        <f>IF(COUNT(K14,K17)&lt;2,"",K14/K17*100)</f>
+        <v/>
+      </c>
+      <c r="L18" s="169">
+        <f>IF(COUNT(L14,L17)&lt;2,"",L14/L17*100)</f>
+        <v/>
+      </c>
+      <c r="M18" s="169">
+        <f>IF(COUNT(M14,M17)&lt;2,"",M14/M17*100)</f>
+        <v/>
+      </c>
+      <c r="N18" s="169">
+        <f>IF(COUNT(N14,N17)&lt;2,"",N14/N17*100)</f>
+        <v/>
+      </c>
+      <c r="O18" s="169">
+        <f>IF(COUNT(O14,O17)&lt;2,"",O14/O17*100)</f>
+        <v/>
+      </c>
+      <c r="P18" s="169">
+        <f>IF(COUNT(P14,P17)&lt;2,"",P14/P17*100)</f>
+        <v/>
+      </c>
+      <c r="Q18" s="169">
+        <f>IF(COUNT(Q14,Q17)&lt;2,"",Q14/Q17*100)</f>
+        <v/>
+      </c>
+      <c r="R18" s="169">
+        <f>IF(COUNT(R14,R17)&lt;2,"",R14/R17*100)</f>
+        <v/>
+      </c>
+      <c r="S18" s="169">
+        <f>IF(COUNT(S14,S17)&lt;2,"",S14/S17*100)</f>
+        <v/>
+      </c>
+      <c r="T18" s="155" t="inlineStr">
+        <is>
+          <t>Model setting in column D</t>
+        </is>
+      </c>
+      <c r="U18" s="155" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml: new_vehicle_segment_split</t>
+        </is>
+      </c>
+      <c r="V18" s="155" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="155" t="inlineStr">
+        <is>
+          <t>Light commercial share of new sales</t>
+        </is>
+      </c>
+      <c r="B19" s="156" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C19" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D19" s="169" t="n">
+        <v>18</v>
+      </c>
+      <c r="E19" s="155" t="inlineStr">
+        <is>
+          <t>Observed share. Column D is the model's fixed split of new vehicles.</t>
+        </is>
+      </c>
+      <c r="F19" s="169">
+        <f>IF(COUNT(F15,F17)&lt;2,"",F15/F17*100)</f>
+        <v/>
+      </c>
+      <c r="G19" s="169">
+        <f>IF(COUNT(G15,G17)&lt;2,"",G15/G17*100)</f>
+        <v/>
+      </c>
+      <c r="H19" s="169">
+        <f>IF(COUNT(H15,H17)&lt;2,"",H15/H17*100)</f>
+        <v/>
+      </c>
+      <c r="I19" s="169">
+        <f>IF(COUNT(I15,I17)&lt;2,"",I15/I17*100)</f>
+        <v/>
+      </c>
+      <c r="J19" s="169">
+        <f>IF(COUNT(J15,J17)&lt;2,"",J15/J17*100)</f>
+        <v/>
+      </c>
+      <c r="K19" s="169">
+        <f>IF(COUNT(K15,K17)&lt;2,"",K15/K17*100)</f>
+        <v/>
+      </c>
+      <c r="L19" s="169">
+        <f>IF(COUNT(L15,L17)&lt;2,"",L15/L17*100)</f>
+        <v/>
+      </c>
+      <c r="M19" s="169">
+        <f>IF(COUNT(M15,M17)&lt;2,"",M15/M17*100)</f>
+        <v/>
+      </c>
+      <c r="N19" s="169">
+        <f>IF(COUNT(N15,N17)&lt;2,"",N15/N17*100)</f>
+        <v/>
+      </c>
+      <c r="O19" s="169">
+        <f>IF(COUNT(O15,O17)&lt;2,"",O15/O17*100)</f>
+        <v/>
+      </c>
+      <c r="P19" s="169">
+        <f>IF(COUNT(P15,P17)&lt;2,"",P15/P17*100)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="169">
+        <f>IF(COUNT(Q15,Q17)&lt;2,"",Q15/Q17*100)</f>
+        <v/>
+      </c>
+      <c r="R19" s="169">
+        <f>IF(COUNT(R15,R17)&lt;2,"",R15/R17*100)</f>
+        <v/>
+      </c>
+      <c r="S19" s="169">
+        <f>IF(COUNT(S15,S17)&lt;2,"",S15/S17*100)</f>
+        <v/>
+      </c>
+      <c r="T19" s="155" t="inlineStr">
+        <is>
+          <t>Model setting in column D</t>
+        </is>
+      </c>
+      <c r="U19" s="155" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml: new_vehicle_segment_split</t>
+        </is>
+      </c>
+      <c r="V19" s="155" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="155" t="inlineStr">
+        <is>
+          <t>Medium and heavy commercial share of new sales</t>
+        </is>
+      </c>
+      <c r="B20" s="156" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C20" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D20" s="169" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="155" t="inlineStr">
+        <is>
+          <t>Observed share. Column D is the model's fixed split of new vehicles.</t>
+        </is>
+      </c>
+      <c r="F20" s="169">
+        <f>IF(COUNT(F16,F17)&lt;2,"",F16/F17*100)</f>
+        <v/>
+      </c>
+      <c r="G20" s="169">
+        <f>IF(COUNT(G16,G17)&lt;2,"",G16/G17*100)</f>
+        <v/>
+      </c>
+      <c r="H20" s="169">
+        <f>IF(COUNT(H16,H17)&lt;2,"",H16/H17*100)</f>
+        <v/>
+      </c>
+      <c r="I20" s="169">
+        <f>IF(COUNT(I16,I17)&lt;2,"",I16/I17*100)</f>
+        <v/>
+      </c>
+      <c r="J20" s="169">
+        <f>IF(COUNT(J16,J17)&lt;2,"",J16/J17*100)</f>
+        <v/>
+      </c>
+      <c r="K20" s="169">
+        <f>IF(COUNT(K16,K17)&lt;2,"",K16/K17*100)</f>
+        <v/>
+      </c>
+      <c r="L20" s="169">
+        <f>IF(COUNT(L16,L17)&lt;2,"",L16/L17*100)</f>
+        <v/>
+      </c>
+      <c r="M20" s="169">
+        <f>IF(COUNT(M16,M17)&lt;2,"",M16/M17*100)</f>
+        <v/>
+      </c>
+      <c r="N20" s="169">
+        <f>IF(COUNT(N16,N17)&lt;2,"",N16/N17*100)</f>
+        <v/>
+      </c>
+      <c r="O20" s="169">
+        <f>IF(COUNT(O16,O17)&lt;2,"",O16/O17*100)</f>
+        <v/>
+      </c>
+      <c r="P20" s="169">
+        <f>IF(COUNT(P16,P17)&lt;2,"",P16/P17*100)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="169">
+        <f>IF(COUNT(Q16,Q17)&lt;2,"",Q16/Q17*100)</f>
+        <v/>
+      </c>
+      <c r="R20" s="169">
+        <f>IF(COUNT(R16,R17)&lt;2,"",R16/R17*100)</f>
+        <v/>
+      </c>
+      <c r="S20" s="169">
+        <f>IF(COUNT(S16,S17)&lt;2,"",S16/S17*100)</f>
+        <v/>
+      </c>
+      <c r="T20" s="155" t="inlineStr">
+        <is>
+          <t>Model setting in column D</t>
+        </is>
+      </c>
+      <c r="U20" s="155" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml: new_vehicle_segment_split</t>
+        </is>
+      </c>
+      <c r="V20" s="155" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="151" t="inlineStr">
+        <is>
+          <t>3. Apparent retirements: last December's stock plus this year's sales less this December's stock</t>
+        </is>
+      </c>
+      <c r="B22" s="151" t="n"/>
+      <c r="C22" s="151" t="n"/>
+      <c r="D22" s="151" t="n"/>
+      <c r="E22" s="151" t="n"/>
+      <c r="F22" s="151" t="n"/>
+      <c r="G22" s="151" t="n"/>
+      <c r="H22" s="151" t="n"/>
+      <c r="I22" s="151" t="n"/>
+      <c r="J22" s="151" t="n"/>
+      <c r="K22" s="151" t="n"/>
+      <c r="L22" s="151" t="n"/>
+      <c r="M22" s="151" t="n"/>
+      <c r="N22" s="151" t="n"/>
+      <c r="O22" s="151" t="n"/>
+      <c r="P22" s="151" t="n"/>
+      <c r="Q22" s="151" t="n"/>
+      <c r="R22" s="151" t="n"/>
+      <c r="S22" s="151" t="n"/>
+      <c r="T22" s="151" t="n"/>
+      <c r="U22" s="151" t="n"/>
+      <c r="V22" s="151" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="155" t="inlineStr">
+        <is>
+          <t>Cars retired</t>
+        </is>
+      </c>
+      <c r="B23" s="156" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C23" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D23" s="170" t="n"/>
+      <c r="E23" s="155" t="inlineStr">
+        <is>
+          <t>Includes deregistration, export and write-off; used imports and re-registration would lower it.</t>
+        </is>
+      </c>
+      <c r="F23" s="170" t="n"/>
+      <c r="G23" s="170">
+        <f>IF(COUNT(F6,G6,G14)&lt;3,"",F6+G14-G6)</f>
+        <v/>
+      </c>
+      <c r="H23" s="170">
+        <f>IF(COUNT(G6,H6,H14)&lt;3,"",G6+H14-H6)</f>
+        <v/>
+      </c>
+      <c r="I23" s="170">
+        <f>IF(COUNT(H6,I6,I14)&lt;3,"",H6+I14-I6)</f>
+        <v/>
+      </c>
+      <c r="J23" s="170">
+        <f>IF(COUNT(I6,J6,J14)&lt;3,"",I6+J14-J6)</f>
+        <v/>
+      </c>
+      <c r="K23" s="170">
+        <f>IF(COUNT(J6,K6,K14)&lt;3,"",J6+K14-K6)</f>
+        <v/>
+      </c>
+      <c r="L23" s="170">
+        <f>IF(COUNT(K6,L6,L14)&lt;3,"",K6+L14-L6)</f>
+        <v/>
+      </c>
+      <c r="M23" s="170">
+        <f>IF(COUNT(L6,M6,M14)&lt;3,"",L6+M14-M6)</f>
+        <v/>
+      </c>
+      <c r="N23" s="170">
+        <f>IF(COUNT(M6,N6,N14)&lt;3,"",M6+N14-N6)</f>
+        <v/>
+      </c>
+      <c r="O23" s="170">
+        <f>IF(COUNT(N6,O6,O14)&lt;3,"",N6+O14-O6)</f>
+        <v/>
+      </c>
+      <c r="P23" s="170">
+        <f>IF(COUNT(O6,P6,P14)&lt;3,"",O6+P14-P6)</f>
+        <v/>
+      </c>
+      <c r="Q23" s="170">
+        <f>IF(COUNT(P6,Q6,Q14)&lt;3,"",P6+Q14-Q6)</f>
+        <v/>
+      </c>
+      <c r="R23" s="170">
+        <f>IF(COUNT(Q6,R6,R14)&lt;3,"",Q6+R14-R6)</f>
+        <v/>
+      </c>
+      <c r="S23" s="170">
+        <f>IF(COUNT(R6,S6,S14)&lt;3,"",R6+S14-S6)</f>
+        <v/>
+      </c>
+      <c r="T23" s="155" t="inlineStr"/>
+      <c r="U23" s="155" t="inlineStr"/>
+      <c r="V23" s="155" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="155" t="inlineStr">
+        <is>
+          <t>Cars retirement rate</t>
+        </is>
+      </c>
+      <c r="B24" s="156" t="inlineStr">
+        <is>
+          <t>% of last December's stock</t>
+        </is>
+      </c>
+      <c r="C24" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D24" s="169" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="155" t="inlineStr">
+        <is>
+          <t>Retired divided by last December's stock. Column D is the model's scrappage rate.</t>
+        </is>
+      </c>
+      <c r="F24" s="169" t="n"/>
+      <c r="G24" s="169">
+        <f>IF(ISNUMBER(G23),G23/F6*100,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="169">
+        <f>IF(ISNUMBER(H23),H23/G6*100,"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="169">
+        <f>IF(ISNUMBER(I23),I23/H6*100,"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="169">
+        <f>IF(ISNUMBER(J23),J23/I6*100,"")</f>
+        <v/>
+      </c>
+      <c r="K24" s="169">
+        <f>IF(ISNUMBER(K23),K23/J6*100,"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="169">
+        <f>IF(ISNUMBER(L23),L23/K6*100,"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="169">
+        <f>IF(ISNUMBER(M23),M23/L6*100,"")</f>
+        <v/>
+      </c>
+      <c r="N24" s="169">
+        <f>IF(ISNUMBER(N23),N23/M6*100,"")</f>
+        <v/>
+      </c>
+      <c r="O24" s="169">
+        <f>IF(ISNUMBER(O23),O23/N6*100,"")</f>
+        <v/>
+      </c>
+      <c r="P24" s="169">
+        <f>IF(ISNUMBER(P23),P23/O6*100,"")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="169">
+        <f>IF(ISNUMBER(Q23),Q23/P6*100,"")</f>
+        <v/>
+      </c>
+      <c r="R24" s="169">
+        <f>IF(ISNUMBER(R23),R23/Q6*100,"")</f>
+        <v/>
+      </c>
+      <c r="S24" s="169">
+        <f>IF(ISNUMBER(S23),S23/R6*100,"")</f>
+        <v/>
+      </c>
+      <c r="T24" s="155" t="inlineStr">
+        <is>
+          <t>Model setting in column D</t>
+        </is>
+      </c>
+      <c r="U24" s="155" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml: scrappage_rate</t>
+        </is>
+      </c>
+      <c r="V24" s="155" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="155" t="inlineStr">
+        <is>
+          <t>Light commercial vehicles retired</t>
+        </is>
+      </c>
+      <c r="B25" s="156" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C25" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D25" s="170" t="n"/>
+      <c r="E25" s="155" t="inlineStr">
+        <is>
+          <t>Includes deregistration, export and write-off; used imports and re-registration would lower it.</t>
+        </is>
+      </c>
+      <c r="F25" s="170" t="n"/>
+      <c r="G25" s="170">
+        <f>IF(COUNT(F7,G7,G15)&lt;3,"",F7+G15-G7)</f>
+        <v/>
+      </c>
+      <c r="H25" s="170">
+        <f>IF(COUNT(G7,H7,H15)&lt;3,"",G7+H15-H7)</f>
+        <v/>
+      </c>
+      <c r="I25" s="170">
+        <f>IF(COUNT(H7,I7,I15)&lt;3,"",H7+I15-I7)</f>
+        <v/>
+      </c>
+      <c r="J25" s="170">
+        <f>IF(COUNT(I7,J7,J15)&lt;3,"",I7+J15-J7)</f>
+        <v/>
+      </c>
+      <c r="K25" s="170">
+        <f>IF(COUNT(J7,K7,K15)&lt;3,"",J7+K15-K7)</f>
+        <v/>
+      </c>
+      <c r="L25" s="170">
+        <f>IF(COUNT(K7,L7,L15)&lt;3,"",K7+L15-L7)</f>
+        <v/>
+      </c>
+      <c r="M25" s="170">
+        <f>IF(COUNT(L7,M7,M15)&lt;3,"",L7+M15-M7)</f>
+        <v/>
+      </c>
+      <c r="N25" s="170">
+        <f>IF(COUNT(M7,N7,N15)&lt;3,"",M7+N15-N7)</f>
+        <v/>
+      </c>
+      <c r="O25" s="170">
+        <f>IF(COUNT(N7,O7,O15)&lt;3,"",N7+O15-O7)</f>
+        <v/>
+      </c>
+      <c r="P25" s="170">
+        <f>IF(COUNT(O7,P7,P15)&lt;3,"",O7+P15-P7)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="170">
+        <f>IF(COUNT(P7,Q7,Q15)&lt;3,"",P7+Q15-Q7)</f>
+        <v/>
+      </c>
+      <c r="R25" s="170">
+        <f>IF(COUNT(Q7,R7,R15)&lt;3,"",Q7+R15-R7)</f>
+        <v/>
+      </c>
+      <c r="S25" s="170">
+        <f>IF(COUNT(R7,S7,S15)&lt;3,"",R7+S15-S7)</f>
+        <v/>
+      </c>
+      <c r="T25" s="155" t="inlineStr"/>
+      <c r="U25" s="155" t="inlineStr"/>
+      <c r="V25" s="155" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="155" t="inlineStr">
+        <is>
+          <t>Light commercial vehicles retirement rate</t>
+        </is>
+      </c>
+      <c r="B26" s="156" t="inlineStr">
+        <is>
+          <t>% of last December's stock</t>
+        </is>
+      </c>
+      <c r="C26" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D26" s="169" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="155" t="inlineStr">
+        <is>
+          <t>Retired divided by last December's stock. Column D is the model's scrappage rate.</t>
+        </is>
+      </c>
+      <c r="F26" s="169" t="n"/>
+      <c r="G26" s="169">
+        <f>IF(ISNUMBER(G25),G25/F7*100,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="169">
+        <f>IF(ISNUMBER(H25),H25/G7*100,"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="169">
+        <f>IF(ISNUMBER(I25),I25/H7*100,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="169">
+        <f>IF(ISNUMBER(J25),J25/I7*100,"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="169">
+        <f>IF(ISNUMBER(K25),K25/J7*100,"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="169">
+        <f>IF(ISNUMBER(L25),L25/K7*100,"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="169">
+        <f>IF(ISNUMBER(M25),M25/L7*100,"")</f>
+        <v/>
+      </c>
+      <c r="N26" s="169">
+        <f>IF(ISNUMBER(N25),N25/M7*100,"")</f>
+        <v/>
+      </c>
+      <c r="O26" s="169">
+        <f>IF(ISNUMBER(O25),O25/N7*100,"")</f>
+        <v/>
+      </c>
+      <c r="P26" s="169">
+        <f>IF(ISNUMBER(P25),P25/O7*100,"")</f>
+        <v/>
+      </c>
+      <c r="Q26" s="169">
+        <f>IF(ISNUMBER(Q25),Q25/P7*100,"")</f>
+        <v/>
+      </c>
+      <c r="R26" s="169">
+        <f>IF(ISNUMBER(R25),R25/Q7*100,"")</f>
+        <v/>
+      </c>
+      <c r="S26" s="169">
+        <f>IF(ISNUMBER(S25),S25/R7*100,"")</f>
+        <v/>
+      </c>
+      <c r="T26" s="155" t="inlineStr">
+        <is>
+          <t>Model setting in column D</t>
+        </is>
+      </c>
+      <c r="U26" s="155" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml: scrappage_rate</t>
+        </is>
+      </c>
+      <c r="V26" s="155" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="155" t="inlineStr">
+        <is>
+          <t>Trucks retired</t>
+        </is>
+      </c>
+      <c r="B27" s="156" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C27" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D27" s="170" t="n"/>
+      <c r="E27" s="155" t="inlineStr">
+        <is>
+          <t>Includes deregistration, export and write-off; used imports and re-registration would lower it.</t>
+        </is>
+      </c>
+      <c r="F27" s="170" t="n"/>
+      <c r="G27" s="170">
+        <f>IF(COUNT(F8,G8,G16)&lt;3,"",F8+G16-G8)</f>
+        <v/>
+      </c>
+      <c r="H27" s="170">
+        <f>IF(COUNT(G8,H8,H16)&lt;3,"",G8+H16-H8)</f>
+        <v/>
+      </c>
+      <c r="I27" s="170">
+        <f>IF(COUNT(H8,I8,I16)&lt;3,"",H8+I16-I8)</f>
+        <v/>
+      </c>
+      <c r="J27" s="170">
+        <f>IF(COUNT(I8,J8,J16)&lt;3,"",I8+J16-J8)</f>
+        <v/>
+      </c>
+      <c r="K27" s="170">
+        <f>IF(COUNT(J8,K8,K16)&lt;3,"",J8+K16-K8)</f>
+        <v/>
+      </c>
+      <c r="L27" s="170">
+        <f>IF(COUNT(K8,L8,L16)&lt;3,"",K8+L16-L8)</f>
+        <v/>
+      </c>
+      <c r="M27" s="170">
+        <f>IF(COUNT(L8,M8,M16)&lt;3,"",L8+M16-M8)</f>
+        <v/>
+      </c>
+      <c r="N27" s="170">
+        <f>IF(COUNT(M8,N8,N16)&lt;3,"",M8+N16-N8)</f>
+        <v/>
+      </c>
+      <c r="O27" s="170">
+        <f>IF(COUNT(N8,O8,O16)&lt;3,"",N8+O16-O8)</f>
+        <v/>
+      </c>
+      <c r="P27" s="170">
+        <f>IF(COUNT(O8,P8,P16)&lt;3,"",O8+P16-P8)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="170">
+        <f>IF(COUNT(P8,Q8,Q16)&lt;3,"",P8+Q16-Q8)</f>
+        <v/>
+      </c>
+      <c r="R27" s="170">
+        <f>IF(COUNT(Q8,R8,R16)&lt;3,"",Q8+R16-R8)</f>
+        <v/>
+      </c>
+      <c r="S27" s="170">
+        <f>IF(COUNT(R8,S8,S16)&lt;3,"",R8+S16-S8)</f>
+        <v/>
+      </c>
+      <c r="T27" s="155" t="inlineStr"/>
+      <c r="U27" s="155" t="inlineStr"/>
+      <c r="V27" s="155" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="155" t="inlineStr">
+        <is>
+          <t>Trucks retirement rate</t>
+        </is>
+      </c>
+      <c r="B28" s="156" t="inlineStr">
+        <is>
+          <t>% of last December's stock</t>
+        </is>
+      </c>
+      <c r="C28" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D28" s="169" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="155" t="inlineStr">
+        <is>
+          <t>Retired divided by last December's stock. Column D is the model's scrappage rate.</t>
+        </is>
+      </c>
+      <c r="F28" s="169" t="n"/>
+      <c r="G28" s="169">
+        <f>IF(ISNUMBER(G27),G27/F8*100,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="169">
+        <f>IF(ISNUMBER(H27),H27/G8*100,"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="169">
+        <f>IF(ISNUMBER(I27),I27/H8*100,"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="169">
+        <f>IF(ISNUMBER(J27),J27/I8*100,"")</f>
+        <v/>
+      </c>
+      <c r="K28" s="169">
+        <f>IF(ISNUMBER(K27),K27/J8*100,"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="169">
+        <f>IF(ISNUMBER(L27),L27/K8*100,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="169">
+        <f>IF(ISNUMBER(M27),M27/L8*100,"")</f>
+        <v/>
+      </c>
+      <c r="N28" s="169">
+        <f>IF(ISNUMBER(N27),N27/M8*100,"")</f>
+        <v/>
+      </c>
+      <c r="O28" s="169">
+        <f>IF(ISNUMBER(O27),O27/N8*100,"")</f>
+        <v/>
+      </c>
+      <c r="P28" s="169">
+        <f>IF(ISNUMBER(P27),P27/O8*100,"")</f>
+        <v/>
+      </c>
+      <c r="Q28" s="169">
+        <f>IF(ISNUMBER(Q27),Q27/P8*100,"")</f>
+        <v/>
+      </c>
+      <c r="R28" s="169">
+        <f>IF(ISNUMBER(R27),R27/Q8*100,"")</f>
+        <v/>
+      </c>
+      <c r="S28" s="169">
+        <f>IF(ISNUMBER(S27),S27/R8*100,"")</f>
+        <v/>
+      </c>
+      <c r="T28" s="155" t="inlineStr">
+        <is>
+          <t>Model setting in column D</t>
+        </is>
+      </c>
+      <c r="U28" s="155" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml: scrappage_rate</t>
+        </is>
+      </c>
+      <c r="V28" s="155" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="151" t="inlineStr">
+        <is>
+          <t>4. Electrified new sales (all segments)</t>
+        </is>
+      </c>
+      <c r="B30" s="151" t="n"/>
+      <c r="C30" s="151" t="n"/>
+      <c r="D30" s="151" t="n"/>
+      <c r="E30" s="151" t="n"/>
+      <c r="F30" s="151" t="n"/>
+      <c r="G30" s="151" t="n"/>
+      <c r="H30" s="151" t="n"/>
+      <c r="I30" s="151" t="n"/>
+      <c r="J30" s="151" t="n"/>
+      <c r="K30" s="151" t="n"/>
+      <c r="L30" s="151" t="n"/>
+      <c r="M30" s="151" t="n"/>
+      <c r="N30" s="151" t="n"/>
+      <c r="O30" s="151" t="n"/>
+      <c r="P30" s="151" t="n"/>
+      <c r="Q30" s="151" t="n"/>
+      <c r="R30" s="151" t="n"/>
+      <c r="S30" s="151" t="n"/>
+      <c r="T30" s="151" t="n"/>
+      <c r="U30" s="151" t="n"/>
+      <c r="V30" s="151" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="152" t="inlineStr">
+        <is>
+          <t>Battery electric, new sales</t>
+        </is>
+      </c>
+      <c r="B31" s="153" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C31" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D31" s="166" t="n"/>
+      <c r="E31" s="152" t="inlineStr">
+        <is>
+          <t>Total market, not passenger cars only.</t>
+        </is>
+      </c>
+      <c r="F31" s="166" t="n"/>
+      <c r="G31" s="166" t="n"/>
+      <c r="H31" s="166" t="n"/>
+      <c r="I31" s="166" t="n"/>
+      <c r="J31" s="166" t="n"/>
+      <c r="K31" s="166" t="n"/>
+      <c r="L31" s="166" t="n"/>
+      <c r="M31" s="166" t="n">
+        <v>154</v>
+      </c>
+      <c r="N31" s="166" t="n">
+        <v>92</v>
+      </c>
+      <c r="O31" s="166" t="n">
+        <v>218</v>
+      </c>
+      <c r="P31" s="166" t="n">
+        <v>502</v>
+      </c>
+      <c r="Q31" s="166" t="n">
+        <v>929</v>
+      </c>
+      <c r="R31" s="166" t="n">
+        <v>1257</v>
+      </c>
+      <c r="S31" s="166" t="n">
+        <v>1088</v>
+      </c>
+      <c r="T31" s="152" t="inlineStr">
+        <is>
+          <t>2019-2025</t>
+        </is>
+      </c>
+      <c r="U31" s="152" t="inlineStr">
+        <is>
+          <t>naamsa new-energy vehicle sales</t>
+        </is>
+      </c>
+      <c r="V31" s="152" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="155" t="inlineStr">
+        <is>
+          <t>Battery electric share of new sales</t>
+        </is>
+      </c>
+      <c r="B32" s="156" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C32" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D32" s="171" t="n"/>
+      <c r="E32" s="155" t="inlineStr">
+        <is>
+          <t>Share of all new vehicles sold in the year.</t>
+        </is>
+      </c>
+      <c r="F32" s="171">
+        <f>IF(COUNT(F31,F17)&lt;2,"",F31/F17*100)</f>
+        <v/>
+      </c>
+      <c r="G32" s="171">
+        <f>IF(COUNT(G31,G17)&lt;2,"",G31/G17*100)</f>
+        <v/>
+      </c>
+      <c r="H32" s="171">
+        <f>IF(COUNT(H31,H17)&lt;2,"",H31/H17*100)</f>
+        <v/>
+      </c>
+      <c r="I32" s="171">
+        <f>IF(COUNT(I31,I17)&lt;2,"",I31/I17*100)</f>
+        <v/>
+      </c>
+      <c r="J32" s="171">
+        <f>IF(COUNT(J31,J17)&lt;2,"",J31/J17*100)</f>
+        <v/>
+      </c>
+      <c r="K32" s="171">
+        <f>IF(COUNT(K31,K17)&lt;2,"",K31/K17*100)</f>
+        <v/>
+      </c>
+      <c r="L32" s="171">
+        <f>IF(COUNT(L31,L17)&lt;2,"",L31/L17*100)</f>
+        <v/>
+      </c>
+      <c r="M32" s="171">
+        <f>IF(COUNT(M31,M17)&lt;2,"",M31/M17*100)</f>
+        <v/>
+      </c>
+      <c r="N32" s="171">
+        <f>IF(COUNT(N31,N17)&lt;2,"",N31/N17*100)</f>
+        <v/>
+      </c>
+      <c r="O32" s="171">
+        <f>IF(COUNT(O31,O17)&lt;2,"",O31/O17*100)</f>
+        <v/>
+      </c>
+      <c r="P32" s="171">
+        <f>IF(COUNT(P31,P17)&lt;2,"",P31/P17*100)</f>
+        <v/>
+      </c>
+      <c r="Q32" s="171">
+        <f>IF(COUNT(Q31,Q17)&lt;2,"",Q31/Q17*100)</f>
+        <v/>
+      </c>
+      <c r="R32" s="171">
+        <f>IF(COUNT(R31,R17)&lt;2,"",R31/R17*100)</f>
+        <v/>
+      </c>
+      <c r="S32" s="171">
+        <f>IF(COUNT(S31,S17)&lt;2,"",S31/S17*100)</f>
+        <v/>
+      </c>
+      <c r="T32" s="155" t="inlineStr"/>
+      <c r="U32" s="155" t="inlineStr"/>
+      <c r="V32" s="155" t="inlineStr">
+        <is>
+          <t>Share of the fleet is not observed after December 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="152" t="inlineStr">
+        <is>
+          <t>Plug-in hybrid, new sales</t>
+        </is>
+      </c>
+      <c r="B33" s="153" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C33" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D33" s="166" t="n"/>
+      <c r="E33" s="152" t="inlineStr">
+        <is>
+          <t>Total market, not passenger cars only.</t>
+        </is>
+      </c>
+      <c r="F33" s="166" t="n"/>
+      <c r="G33" s="166" t="n"/>
+      <c r="H33" s="166" t="n"/>
+      <c r="I33" s="166" t="n"/>
+      <c r="J33" s="166" t="n"/>
+      <c r="K33" s="166" t="n"/>
+      <c r="L33" s="166" t="n"/>
+      <c r="M33" s="166" t="n">
+        <v>72</v>
+      </c>
+      <c r="N33" s="166" t="n">
+        <v>77</v>
+      </c>
+      <c r="O33" s="166" t="n">
+        <v>51</v>
+      </c>
+      <c r="P33" s="166" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q33" s="166" t="n">
+        <v>368</v>
+      </c>
+      <c r="R33" s="166" t="n">
+        <v>738</v>
+      </c>
+      <c r="S33" s="166" t="n">
+        <v>2810</v>
+      </c>
+      <c r="T33" s="152" t="inlineStr">
+        <is>
+          <t>2019-2025</t>
+        </is>
+      </c>
+      <c r="U33" s="152" t="inlineStr">
+        <is>
+          <t>naamsa new-energy vehicle sales</t>
+        </is>
+      </c>
+      <c r="V33" s="152" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="155" t="inlineStr">
+        <is>
+          <t>Plug-in hybrid share of new sales</t>
+        </is>
+      </c>
+      <c r="B34" s="156" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C34" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D34" s="171" t="n"/>
+      <c r="E34" s="155" t="inlineStr">
+        <is>
+          <t>Share of all new vehicles sold in the year.</t>
+        </is>
+      </c>
+      <c r="F34" s="171">
+        <f>IF(COUNT(F33,F17)&lt;2,"",F33/F17*100)</f>
+        <v/>
+      </c>
+      <c r="G34" s="171">
+        <f>IF(COUNT(G33,G17)&lt;2,"",G33/G17*100)</f>
+        <v/>
+      </c>
+      <c r="H34" s="171">
+        <f>IF(COUNT(H33,H17)&lt;2,"",H33/H17*100)</f>
+        <v/>
+      </c>
+      <c r="I34" s="171">
+        <f>IF(COUNT(I33,I17)&lt;2,"",I33/I17*100)</f>
+        <v/>
+      </c>
+      <c r="J34" s="171">
+        <f>IF(COUNT(J33,J17)&lt;2,"",J33/J17*100)</f>
+        <v/>
+      </c>
+      <c r="K34" s="171">
+        <f>IF(COUNT(K33,K17)&lt;2,"",K33/K17*100)</f>
+        <v/>
+      </c>
+      <c r="L34" s="171">
+        <f>IF(COUNT(L33,L17)&lt;2,"",L33/L17*100)</f>
+        <v/>
+      </c>
+      <c r="M34" s="171">
+        <f>IF(COUNT(M33,M17)&lt;2,"",M33/M17*100)</f>
+        <v/>
+      </c>
+      <c r="N34" s="171">
+        <f>IF(COUNT(N33,N17)&lt;2,"",N33/N17*100)</f>
+        <v/>
+      </c>
+      <c r="O34" s="171">
+        <f>IF(COUNT(O33,O17)&lt;2,"",O33/O17*100)</f>
+        <v/>
+      </c>
+      <c r="P34" s="171">
+        <f>IF(COUNT(P33,P17)&lt;2,"",P33/P17*100)</f>
+        <v/>
+      </c>
+      <c r="Q34" s="171">
+        <f>IF(COUNT(Q33,Q17)&lt;2,"",Q33/Q17*100)</f>
+        <v/>
+      </c>
+      <c r="R34" s="171">
+        <f>IF(COUNT(R33,R17)&lt;2,"",R33/R17*100)</f>
+        <v/>
+      </c>
+      <c r="S34" s="171">
+        <f>IF(COUNT(S33,S17)&lt;2,"",S33/S17*100)</f>
+        <v/>
+      </c>
+      <c r="T34" s="155" t="inlineStr"/>
+      <c r="U34" s="155" t="inlineStr"/>
+      <c r="V34" s="155" t="inlineStr">
+        <is>
+          <t>Share of the fleet is not observed after December 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="152" t="inlineStr">
+        <is>
+          <t>Conventional hybrid, new sales</t>
+        </is>
+      </c>
+      <c r="B35" s="153" t="inlineStr">
+        <is>
+          <t>vehicles/year</t>
+        </is>
+      </c>
+      <c r="C35" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D35" s="166" t="n"/>
+      <c r="E35" s="152" t="inlineStr">
+        <is>
+          <t>Total market, not passenger cars only.</t>
+        </is>
+      </c>
+      <c r="F35" s="166" t="n"/>
+      <c r="G35" s="166" t="n"/>
+      <c r="H35" s="166" t="n"/>
+      <c r="I35" s="166" t="n"/>
+      <c r="J35" s="166" t="n"/>
+      <c r="K35" s="166" t="n"/>
+      <c r="L35" s="166" t="n"/>
+      <c r="M35" s="166" t="n">
+        <v>181</v>
+      </c>
+      <c r="N35" s="166" t="n">
+        <v>155</v>
+      </c>
+      <c r="O35" s="166" t="n">
+        <v>627</v>
+      </c>
+      <c r="P35" s="166" t="n">
+        <v>4070</v>
+      </c>
+      <c r="Q35" s="166" t="n">
+        <v>6485</v>
+      </c>
+      <c r="R35" s="166" t="n">
+        <v>13616</v>
+      </c>
+      <c r="S35" s="166" t="n">
+        <v>12818</v>
+      </c>
+      <c r="T35" s="152" t="inlineStr">
+        <is>
+          <t>2019-2025</t>
+        </is>
+      </c>
+      <c r="U35" s="152" t="inlineStr">
+        <is>
+          <t>naamsa new-energy vehicle sales</t>
+        </is>
+      </c>
+      <c r="V35" s="152" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="155" t="inlineStr">
+        <is>
+          <t>Conventional hybrid share of new sales</t>
+        </is>
+      </c>
+      <c r="B36" s="156" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C36" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D36" s="171" t="n"/>
+      <c r="E36" s="155" t="inlineStr">
+        <is>
+          <t>Share of all new vehicles sold in the year.</t>
+        </is>
+      </c>
+      <c r="F36" s="171">
+        <f>IF(COUNT(F35,F17)&lt;2,"",F35/F17*100)</f>
+        <v/>
+      </c>
+      <c r="G36" s="171">
+        <f>IF(COUNT(G35,G17)&lt;2,"",G35/G17*100)</f>
+        <v/>
+      </c>
+      <c r="H36" s="171">
+        <f>IF(COUNT(H35,H17)&lt;2,"",H35/H17*100)</f>
+        <v/>
+      </c>
+      <c r="I36" s="171">
+        <f>IF(COUNT(I35,I17)&lt;2,"",I35/I17*100)</f>
+        <v/>
+      </c>
+      <c r="J36" s="171">
+        <f>IF(COUNT(J35,J17)&lt;2,"",J35/J17*100)</f>
+        <v/>
+      </c>
+      <c r="K36" s="171">
+        <f>IF(COUNT(K35,K17)&lt;2,"",K35/K17*100)</f>
+        <v/>
+      </c>
+      <c r="L36" s="171">
+        <f>IF(COUNT(L35,L17)&lt;2,"",L35/L17*100)</f>
+        <v/>
+      </c>
+      <c r="M36" s="171">
+        <f>IF(COUNT(M35,M17)&lt;2,"",M35/M17*100)</f>
+        <v/>
+      </c>
+      <c r="N36" s="171">
+        <f>IF(COUNT(N35,N17)&lt;2,"",N35/N17*100)</f>
+        <v/>
+      </c>
+      <c r="O36" s="171">
+        <f>IF(COUNT(O35,O17)&lt;2,"",O35/O17*100)</f>
+        <v/>
+      </c>
+      <c r="P36" s="171">
+        <f>IF(COUNT(P35,P17)&lt;2,"",P35/P17*100)</f>
+        <v/>
+      </c>
+      <c r="Q36" s="171">
+        <f>IF(COUNT(Q35,Q17)&lt;2,"",Q35/Q17*100)</f>
+        <v/>
+      </c>
+      <c r="R36" s="171">
+        <f>IF(COUNT(R35,R17)&lt;2,"",R35/R17*100)</f>
+        <v/>
+      </c>
+      <c r="S36" s="171">
+        <f>IF(COUNT(S35,S17)&lt;2,"",S35/S17*100)</f>
+        <v/>
+      </c>
+      <c r="T36" s="155" t="inlineStr"/>
+      <c r="U36" s="155" t="inlineStr"/>
+      <c r="V36" s="155" t="inlineStr">
+        <is>
+          <t>Share of the fleet is not observed after December 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="151" t="inlineStr">
+        <is>
+          <t>5. Fuel split of the registered fleet</t>
+        </is>
+      </c>
+      <c r="B38" s="151" t="n"/>
+      <c r="C38" s="151" t="n"/>
+      <c r="D38" s="151" t="n"/>
+      <c r="E38" s="151" t="n"/>
+      <c r="F38" s="151" t="n"/>
+      <c r="G38" s="151" t="n"/>
+      <c r="H38" s="151" t="n"/>
+      <c r="I38" s="151" t="n"/>
+      <c r="J38" s="151" t="n"/>
+      <c r="K38" s="151" t="n"/>
+      <c r="L38" s="151" t="n"/>
+      <c r="M38" s="151" t="n"/>
+      <c r="N38" s="151" t="n"/>
+      <c r="O38" s="151" t="n"/>
+      <c r="P38" s="151" t="n"/>
+      <c r="Q38" s="151" t="n"/>
+      <c r="R38" s="151" t="n"/>
+      <c r="S38" s="151" t="n"/>
+      <c r="T38" s="151" t="n"/>
+      <c r="U38" s="151" t="n"/>
+      <c r="V38" s="151" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="152" t="inlineStr">
+        <is>
+          <t>Petrol vehicles registered</t>
+        </is>
+      </c>
+      <c r="B39" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C39" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D39" s="166" t="n"/>
+      <c r="E39" s="152" t="inlineStr">
+        <is>
+          <t>All classes, December 2023.</t>
+        </is>
+      </c>
+      <c r="F39" s="166" t="n"/>
+      <c r="G39" s="166" t="n"/>
+      <c r="H39" s="166" t="n"/>
+      <c r="I39" s="166" t="n"/>
+      <c r="J39" s="166" t="n"/>
+      <c r="K39" s="166" t="n"/>
+      <c r="L39" s="166" t="n"/>
+      <c r="M39" s="166" t="n"/>
+      <c r="N39" s="166" t="n"/>
+      <c r="O39" s="166" t="n"/>
+      <c r="P39" s="166" t="n"/>
+      <c r="Q39" s="166" t="n">
+        <v>8555772</v>
+      </c>
+      <c r="R39" s="166" t="n"/>
+      <c r="S39" s="166" t="n"/>
+      <c r="T39" s="152" t="inlineStr">
+        <is>
+          <t>One date only</t>
+        </is>
+      </c>
+      <c r="U39" s="152" t="inlineStr">
+        <is>
+          <t>Department of Transport, 2023</t>
+        </is>
+      </c>
+      <c r="V39" s="152" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="152" t="inlineStr">
+        <is>
+          <t>Diesel vehicles registered</t>
+        </is>
+      </c>
+      <c r="B40" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C40" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D40" s="166" t="n"/>
+      <c r="E40" s="152" t="inlineStr">
+        <is>
+          <t>All classes, December 2023.</t>
+        </is>
+      </c>
+      <c r="F40" s="166" t="n"/>
+      <c r="G40" s="166" t="n"/>
+      <c r="H40" s="166" t="n"/>
+      <c r="I40" s="166" t="n"/>
+      <c r="J40" s="166" t="n"/>
+      <c r="K40" s="166" t="n"/>
+      <c r="L40" s="166" t="n"/>
+      <c r="M40" s="166" t="n"/>
+      <c r="N40" s="166" t="n"/>
+      <c r="O40" s="166" t="n"/>
+      <c r="P40" s="166" t="n"/>
+      <c r="Q40" s="166" t="n">
+        <v>3335546</v>
+      </c>
+      <c r="R40" s="166" t="n"/>
+      <c r="S40" s="166" t="n"/>
+      <c r="T40" s="152" t="inlineStr">
+        <is>
+          <t>One date only</t>
+        </is>
+      </c>
+      <c r="U40" s="152" t="inlineStr">
+        <is>
+          <t>Department of Transport, 2023</t>
+        </is>
+      </c>
+      <c r="V40" s="152" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="152" t="inlineStr">
+        <is>
+          <t>Electric vehicles registered</t>
+        </is>
+      </c>
+      <c r="B41" s="153" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C41" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D41" s="166" t="n"/>
+      <c r="E41" s="152" t="inlineStr">
+        <is>
+          <t>All classes, December 2023.</t>
+        </is>
+      </c>
+      <c r="F41" s="166" t="n"/>
+      <c r="G41" s="166" t="n"/>
+      <c r="H41" s="166" t="n"/>
+      <c r="I41" s="166" t="n"/>
+      <c r="J41" s="166" t="n"/>
+      <c r="K41" s="166" t="n"/>
+      <c r="L41" s="166" t="n"/>
+      <c r="M41" s="166" t="n"/>
+      <c r="N41" s="166" t="n"/>
+      <c r="O41" s="166" t="n"/>
+      <c r="P41" s="166" t="n"/>
+      <c r="Q41" s="166" t="n">
+        <v>4090</v>
+      </c>
+      <c r="R41" s="166" t="n"/>
+      <c r="S41" s="166" t="n"/>
+      <c r="T41" s="152" t="inlineStr">
+        <is>
+          <t>One date only</t>
+        </is>
+      </c>
+      <c r="U41" s="152" t="inlineStr">
+        <is>
+          <t>Department of Transport, 2023</t>
+        </is>
+      </c>
+      <c r="V41" s="152" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="155" t="inlineStr">
+        <is>
+          <t>Diesel vehicles implied by the model's split</t>
+        </is>
+      </c>
+      <c r="B42" s="156" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C42" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D42" s="170" t="n"/>
+      <c r="E42" s="155" t="inlineStr">
+        <is>
+          <t>Cars x 17% plus light commercial x 70% plus trucks and buses. The model's split is for new sales; applied here to stock as a test.</t>
+        </is>
+      </c>
+      <c r="F42" s="170">
+        <f>IF(COUNT(F6,F7)&lt;2,"",F6*0.17+F7*0.7+F8+F9)</f>
+        <v/>
+      </c>
+      <c r="G42" s="170">
+        <f>IF(COUNT(G6,G7)&lt;2,"",G6*0.17+G7*0.7+G8+G9)</f>
+        <v/>
+      </c>
+      <c r="H42" s="170">
+        <f>IF(COUNT(H6,H7)&lt;2,"",H6*0.17+H7*0.7+H8+H9)</f>
+        <v/>
+      </c>
+      <c r="I42" s="170">
+        <f>IF(COUNT(I6,I7)&lt;2,"",I6*0.17+I7*0.7+I8+I9)</f>
+        <v/>
+      </c>
+      <c r="J42" s="170">
+        <f>IF(COUNT(J6,J7)&lt;2,"",J6*0.17+J7*0.7+J8+J9)</f>
+        <v/>
+      </c>
+      <c r="K42" s="170">
+        <f>IF(COUNT(K6,K7)&lt;2,"",K6*0.17+K7*0.7+K8+K9)</f>
+        <v/>
+      </c>
+      <c r="L42" s="170">
+        <f>IF(COUNT(L6,L7)&lt;2,"",L6*0.17+L7*0.7+L8+L9)</f>
+        <v/>
+      </c>
+      <c r="M42" s="170">
+        <f>IF(COUNT(M6,M7)&lt;2,"",M6*0.17+M7*0.7+M8+M9)</f>
+        <v/>
+      </c>
+      <c r="N42" s="170">
+        <f>IF(COUNT(N6,N7)&lt;2,"",N6*0.17+N7*0.7+N8+N9)</f>
+        <v/>
+      </c>
+      <c r="O42" s="170">
+        <f>IF(COUNT(O6,O7)&lt;2,"",O6*0.17+O7*0.7+O8+O9)</f>
+        <v/>
+      </c>
+      <c r="P42" s="170">
+        <f>IF(COUNT(P6,P7)&lt;2,"",P6*0.17+P7*0.7+P8+P9)</f>
+        <v/>
+      </c>
+      <c r="Q42" s="170">
+        <f>IF(COUNT(Q6,Q7)&lt;2,"",Q6*0.17+Q7*0.7+Q8+Q9)</f>
+        <v/>
+      </c>
+      <c r="R42" s="170">
+        <f>IF(COUNT(R6,R7)&lt;2,"",R6*0.17+R7*0.7+R8+R9)</f>
+        <v/>
+      </c>
+      <c r="S42" s="170">
+        <f>IF(COUNT(S6,S7)&lt;2,"",S6*0.17+S7*0.7+S8+S9)</f>
+        <v/>
+      </c>
+      <c r="T42" s="155" t="inlineStr"/>
+      <c r="U42" s="155" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml: petrol_diesel_split</t>
+        </is>
+      </c>
+      <c r="V42" s="155" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="155" t="inlineStr">
+        <is>
+          <t>Implied less registered diesel vehicles</t>
+        </is>
+      </c>
+      <c r="B43" s="156" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="C43" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D43" s="170" t="n"/>
+      <c r="E43" s="155" t="inlineStr">
+        <is>
+          <t>Positive means the model's split puts more diesel vehicles on the road than are registered. Minibuses and motorcycles are left out of the implied figure.</t>
+        </is>
+      </c>
+      <c r="F43" s="170">
+        <f>IF(COUNT(F42,F40)&lt;2,"",F42-F40)</f>
+        <v/>
+      </c>
+      <c r="G43" s="170">
+        <f>IF(COUNT(G42,G40)&lt;2,"",G42-G40)</f>
+        <v/>
+      </c>
+      <c r="H43" s="170">
+        <f>IF(COUNT(H42,H40)&lt;2,"",H42-H40)</f>
+        <v/>
+      </c>
+      <c r="I43" s="170">
+        <f>IF(COUNT(I42,I40)&lt;2,"",I42-I40)</f>
+        <v/>
+      </c>
+      <c r="J43" s="170">
+        <f>IF(COUNT(J42,J40)&lt;2,"",J42-J40)</f>
+        <v/>
+      </c>
+      <c r="K43" s="170">
+        <f>IF(COUNT(K42,K40)&lt;2,"",K42-K40)</f>
+        <v/>
+      </c>
+      <c r="L43" s="170">
+        <f>IF(COUNT(L42,L40)&lt;2,"",L42-L40)</f>
+        <v/>
+      </c>
+      <c r="M43" s="170">
+        <f>IF(COUNT(M42,M40)&lt;2,"",M42-M40)</f>
+        <v/>
+      </c>
+      <c r="N43" s="170">
+        <f>IF(COUNT(N42,N40)&lt;2,"",N42-N40)</f>
+        <v/>
+      </c>
+      <c r="O43" s="170">
+        <f>IF(COUNT(O42,O40)&lt;2,"",O42-O40)</f>
+        <v/>
+      </c>
+      <c r="P43" s="170">
+        <f>IF(COUNT(P42,P40)&lt;2,"",P42-P40)</f>
+        <v/>
+      </c>
+      <c r="Q43" s="170">
+        <f>IF(COUNT(Q42,Q40)&lt;2,"",Q42-Q40)</f>
+        <v/>
+      </c>
+      <c r="R43" s="170">
+        <f>IF(COUNT(R42,R40)&lt;2,"",R42-R40)</f>
+        <v/>
+      </c>
+      <c r="S43" s="170">
+        <f>IF(COUNT(S42,S40)&lt;2,"",S42-S40)</f>
+        <v/>
+      </c>
+      <c r="T43" s="155" t="inlineStr"/>
+      <c r="U43" s="155" t="inlineStr"/>
+      <c r="V43" s="155" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="151" t="inlineStr">
+        <is>
+          <t>6. Distance and fuel use: model settings beside the published study</t>
+        </is>
+      </c>
+      <c r="B45" s="151" t="n"/>
+      <c r="C45" s="151" t="n"/>
+      <c r="D45" s="151" t="n"/>
+      <c r="E45" s="151" t="n"/>
+      <c r="F45" s="151" t="n"/>
+      <c r="G45" s="151" t="n"/>
+      <c r="H45" s="151" t="n"/>
+      <c r="I45" s="151" t="n"/>
+      <c r="J45" s="151" t="n"/>
+      <c r="K45" s="151" t="n"/>
+      <c r="L45" s="151" t="n"/>
+      <c r="M45" s="151" t="n"/>
+      <c r="N45" s="151" t="n"/>
+      <c r="O45" s="151" t="n"/>
+      <c r="P45" s="151" t="n"/>
+      <c r="Q45" s="151" t="n"/>
+      <c r="R45" s="151" t="n"/>
+      <c r="S45" s="151" t="n"/>
+      <c r="T45" s="151" t="n"/>
+      <c r="U45" s="151" t="n"/>
+      <c r="V45" s="151" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="158" t="inlineStr">
+        <is>
+          <t>Passenger cars, distance</t>
+        </is>
+      </c>
+      <c r="B46" s="159" t="inlineStr">
+        <is>
+          <t>km/vehicle/year</t>
+        </is>
+      </c>
+      <c r="C46" s="159" t="inlineStr">
+        <is>
+          <t>Model setting</t>
+        </is>
+      </c>
+      <c r="D46" s="160" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E46" s="158" t="inlineStr">
+        <is>
+          <t>Column D is the model's value. The study gives 14,457.0 for CarGasoline (fleet average, 2014 base).</t>
+        </is>
+      </c>
+      <c r="F46" s="160" t="n"/>
+      <c r="G46" s="160" t="n"/>
+      <c r="H46" s="160" t="n"/>
+      <c r="I46" s="160" t="n"/>
+      <c r="J46" s="160" t="n"/>
+      <c r="K46" s="160" t="n"/>
+      <c r="L46" s="160" t="n"/>
+      <c r="M46" s="160" t="n"/>
+      <c r="N46" s="160" t="n"/>
+      <c r="O46" s="160" t="n"/>
+      <c r="P46" s="160" t="n"/>
+      <c r="Q46" s="160" t="n"/>
+      <c r="R46" s="160" t="n"/>
+      <c r="S46" s="160" t="n"/>
+      <c r="T46" s="158" t="inlineStr">
+        <is>
+          <t>Model value is a placeholder with no source</t>
+        </is>
+      </c>
+      <c r="U46" s="158" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
+        </is>
+      </c>
+      <c r="V46" s="158" t="inlineStr">
+        <is>
+          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="158" t="inlineStr">
+        <is>
+          <t>Light commercial, distance</t>
+        </is>
+      </c>
+      <c r="B47" s="159" t="inlineStr">
+        <is>
+          <t>km/vehicle/year</t>
+        </is>
+      </c>
+      <c r="C47" s="159" t="inlineStr">
+        <is>
+          <t>Model setting</t>
+        </is>
+      </c>
+      <c r="D47" s="160" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E47" s="158" t="inlineStr">
+        <is>
+          <t>Column D is the model's value. The study gives 20,397.0 for LCVDiesel (fleet average, 2014 base).</t>
+        </is>
+      </c>
+      <c r="F47" s="160" t="n"/>
+      <c r="G47" s="160" t="n"/>
+      <c r="H47" s="160" t="n"/>
+      <c r="I47" s="160" t="n"/>
+      <c r="J47" s="160" t="n"/>
+      <c r="K47" s="160" t="n"/>
+      <c r="L47" s="160" t="n"/>
+      <c r="M47" s="160" t="n"/>
+      <c r="N47" s="160" t="n"/>
+      <c r="O47" s="160" t="n"/>
+      <c r="P47" s="160" t="n"/>
+      <c r="Q47" s="160" t="n"/>
+      <c r="R47" s="160" t="n"/>
+      <c r="S47" s="160" t="n"/>
+      <c r="T47" s="158" t="inlineStr">
+        <is>
+          <t>Model value is a placeholder with no source</t>
+        </is>
+      </c>
+      <c r="U47" s="158" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
+        </is>
+      </c>
+      <c r="V47" s="158" t="inlineStr">
+        <is>
+          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="158" t="inlineStr">
+        <is>
+          <t>Heavy commercial, distance</t>
+        </is>
+      </c>
+      <c r="B48" s="159" t="inlineStr">
+        <is>
+          <t>km/vehicle/year</t>
+        </is>
+      </c>
+      <c r="C48" s="159" t="inlineStr">
+        <is>
+          <t>Model setting</t>
+        </is>
+      </c>
+      <c r="D48" s="160" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E48" s="158" t="inlineStr">
+        <is>
+          <t>Column D is the model's value. The study gives 62,461.0 for HCV5Diesel (fleet average, 2014 base).</t>
+        </is>
+      </c>
+      <c r="F48" s="160" t="n"/>
+      <c r="G48" s="160" t="n"/>
+      <c r="H48" s="160" t="n"/>
+      <c r="I48" s="160" t="n"/>
+      <c r="J48" s="160" t="n"/>
+      <c r="K48" s="160" t="n"/>
+      <c r="L48" s="160" t="n"/>
+      <c r="M48" s="160" t="n"/>
+      <c r="N48" s="160" t="n"/>
+      <c r="O48" s="160" t="n"/>
+      <c r="P48" s="160" t="n"/>
+      <c r="Q48" s="160" t="n"/>
+      <c r="R48" s="160" t="n"/>
+      <c r="S48" s="160" t="n"/>
+      <c r="T48" s="158" t="inlineStr">
+        <is>
+          <t>Model value is a placeholder with no source</t>
+        </is>
+      </c>
+      <c r="U48" s="158" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
+        </is>
+      </c>
+      <c r="V48" s="158" t="inlineStr">
+        <is>
+          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="158" t="inlineStr">
+        <is>
+          <t>Petrol cars, fuel use</t>
+        </is>
+      </c>
+      <c r="B49" s="159" t="inlineStr">
+        <is>
+          <t>L/100 km</t>
+        </is>
+      </c>
+      <c r="C49" s="159" t="inlineStr">
+        <is>
+          <t>Model setting</t>
+        </is>
+      </c>
+      <c r="D49" s="160" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E49" s="158" t="inlineStr">
+        <is>
+          <t>Column D is the model's value. The study gives 8.2 for CarGasoline (fleet average, 2014 base).</t>
+        </is>
+      </c>
+      <c r="F49" s="160" t="n"/>
+      <c r="G49" s="160" t="n"/>
+      <c r="H49" s="160" t="n"/>
+      <c r="I49" s="160" t="n"/>
+      <c r="J49" s="160" t="n"/>
+      <c r="K49" s="160" t="n"/>
+      <c r="L49" s="160" t="n"/>
+      <c r="M49" s="160" t="n"/>
+      <c r="N49" s="160" t="n"/>
+      <c r="O49" s="160" t="n"/>
+      <c r="P49" s="160" t="n"/>
+      <c r="Q49" s="160" t="n"/>
+      <c r="R49" s="160" t="n"/>
+      <c r="S49" s="160" t="n"/>
+      <c r="T49" s="158" t="inlineStr">
+        <is>
+          <t>Model value is a placeholder with no source</t>
+        </is>
+      </c>
+      <c r="U49" s="158" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
+        </is>
+      </c>
+      <c r="V49" s="158" t="inlineStr">
+        <is>
+          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="158" t="inlineStr">
+        <is>
+          <t>Diesel light commercial, fuel use</t>
+        </is>
+      </c>
+      <c r="B50" s="159" t="inlineStr">
+        <is>
+          <t>L/100 km</t>
+        </is>
+      </c>
+      <c r="C50" s="159" t="inlineStr">
+        <is>
+          <t>Model setting</t>
+        </is>
+      </c>
+      <c r="D50" s="160" t="n">
+        <v>9</v>
+      </c>
+      <c r="E50" s="158" t="inlineStr">
+        <is>
+          <t>Column D is the model's value. The study gives 12.4 for LCVDiesel (fleet average, 2014 base).</t>
+        </is>
+      </c>
+      <c r="F50" s="160" t="n"/>
+      <c r="G50" s="160" t="n"/>
+      <c r="H50" s="160" t="n"/>
+      <c r="I50" s="160" t="n"/>
+      <c r="J50" s="160" t="n"/>
+      <c r="K50" s="160" t="n"/>
+      <c r="L50" s="160" t="n"/>
+      <c r="M50" s="160" t="n"/>
+      <c r="N50" s="160" t="n"/>
+      <c r="O50" s="160" t="n"/>
+      <c r="P50" s="160" t="n"/>
+      <c r="Q50" s="160" t="n"/>
+      <c r="R50" s="160" t="n"/>
+      <c r="S50" s="160" t="n"/>
+      <c r="T50" s="158" t="inlineStr">
+        <is>
+          <t>Model value is a placeholder with no source</t>
+        </is>
+      </c>
+      <c r="U50" s="158" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
+        </is>
+      </c>
+      <c r="V50" s="158" t="inlineStr">
+        <is>
+          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="158" t="inlineStr">
+        <is>
+          <t>Heavy commercial, fuel use</t>
+        </is>
+      </c>
+      <c r="B51" s="159" t="inlineStr">
+        <is>
+          <t>L/100 km</t>
+        </is>
+      </c>
+      <c r="C51" s="159" t="inlineStr">
+        <is>
+          <t>Model setting</t>
+        </is>
+      </c>
+      <c r="D51" s="160" t="n">
+        <v>35</v>
+      </c>
+      <c r="E51" s="158" t="inlineStr">
+        <is>
+          <t>Column D is the model's value. The study gives 31.2 for HCV5Diesel (fleet average, 2014 base).</t>
+        </is>
+      </c>
+      <c r="F51" s="160" t="n"/>
+      <c r="G51" s="160" t="n"/>
+      <c r="H51" s="160" t="n"/>
+      <c r="I51" s="160" t="n"/>
+      <c r="J51" s="160" t="n"/>
+      <c r="K51" s="160" t="n"/>
+      <c r="L51" s="160" t="n"/>
+      <c r="M51" s="160" t="n"/>
+      <c r="N51" s="160" t="n"/>
+      <c r="O51" s="160" t="n"/>
+      <c r="P51" s="160" t="n"/>
+      <c r="Q51" s="160" t="n"/>
+      <c r="R51" s="160" t="n"/>
+      <c r="S51" s="160" t="n"/>
+      <c r="T51" s="158" t="inlineStr">
+        <is>
+          <t>Model value is a placeholder with no source</t>
+        </is>
+      </c>
+      <c r="U51" s="158" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018); assumptions/2026/vehicles.yaml</t>
+        </is>
+      </c>
+      <c r="V51" s="158" t="inlineStr">
+        <is>
+          <t>The heavy class in the study spans nine weight classes; HCV5 is shown as a mid-point</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="155" t="inlineStr">
+        <is>
+          <t>Petrol sold per registered petrol vehicle</t>
+        </is>
+      </c>
+      <c r="B52" s="156" t="inlineStr">
+        <is>
+          <t>litres/vehicle/year</t>
+        </is>
+      </c>
+      <c r="C52" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D52" s="170" t="n"/>
+      <c r="E52" s="155" t="inlineStr">
+        <is>
+          <t>National petrol sales used (History) divided by registered petrol vehicles.</t>
+        </is>
+      </c>
+      <c r="F52" s="170">
+        <f>IF(COUNT(History!F57,F39)&lt;2,"",History!F57*1000000/F39)</f>
+        <v/>
+      </c>
+      <c r="G52" s="170">
+        <f>IF(COUNT(History!G57,G39)&lt;2,"",History!G57*1000000/G39)</f>
+        <v/>
+      </c>
+      <c r="H52" s="170">
+        <f>IF(COUNT(History!H57,H39)&lt;2,"",History!H57*1000000/H39)</f>
+        <v/>
+      </c>
+      <c r="I52" s="170">
+        <f>IF(COUNT(History!I57,I39)&lt;2,"",History!I57*1000000/I39)</f>
+        <v/>
+      </c>
+      <c r="J52" s="170">
+        <f>IF(COUNT(History!J57,J39)&lt;2,"",History!J57*1000000/J39)</f>
+        <v/>
+      </c>
+      <c r="K52" s="170">
+        <f>IF(COUNT(History!K57,K39)&lt;2,"",History!K57*1000000/K39)</f>
+        <v/>
+      </c>
+      <c r="L52" s="170">
+        <f>IF(COUNT(History!L57,L39)&lt;2,"",History!L57*1000000/L39)</f>
+        <v/>
+      </c>
+      <c r="M52" s="170">
+        <f>IF(COUNT(History!M57,M39)&lt;2,"",History!M57*1000000/M39)</f>
+        <v/>
+      </c>
+      <c r="N52" s="170">
+        <f>IF(COUNT(History!N57,N39)&lt;2,"",History!N57*1000000/N39)</f>
+        <v/>
+      </c>
+      <c r="O52" s="170">
+        <f>IF(COUNT(History!O57,O39)&lt;2,"",History!O57*1000000/O39)</f>
+        <v/>
+      </c>
+      <c r="P52" s="170">
+        <f>IF(COUNT(History!P57,P39)&lt;2,"",History!P57*1000000/P39)</f>
+        <v/>
+      </c>
+      <c r="Q52" s="170">
+        <f>IF(COUNT(History!Q57,Q39)&lt;2,"",History!Q57*1000000/Q39)</f>
+        <v/>
+      </c>
+      <c r="R52" s="170">
+        <f>IF(COUNT(History!R57,R39)&lt;2,"",History!R57*1000000/R39)</f>
+        <v/>
+      </c>
+      <c r="S52" s="170">
+        <f>IF(COUNT(History!S57,S39)&lt;2,"",History!S57*1000000/S39)</f>
+        <v/>
+      </c>
+      <c r="T52" s="155" t="inlineStr"/>
+      <c r="U52" s="155" t="inlineStr"/>
+      <c r="V52" s="155" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="155" t="inlineStr">
+        <is>
+          <t>Distance implied by petrol sales</t>
+        </is>
+      </c>
+      <c r="B53" s="156" t="inlineStr">
+        <is>
+          <t>km/vehicle/year</t>
+        </is>
+      </c>
+      <c r="C53" s="156" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D53" s="170" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E53" s="155" t="inlineStr">
+        <is>
+          <t>Litres per vehicle divided by 8.2 L/100 km (the study's petrol car average). Column D is the model's passenger distance.</t>
+        </is>
+      </c>
+      <c r="F53" s="170">
+        <f>IF(ISNUMBER(F52),F52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="170">
+        <f>IF(ISNUMBER(G52),G52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="170">
+        <f>IF(ISNUMBER(H52),H52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="I53" s="170">
+        <f>IF(ISNUMBER(I52),I52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="J53" s="170">
+        <f>IF(ISNUMBER(J52),J52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="K53" s="170">
+        <f>IF(ISNUMBER(K52),K52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="L53" s="170">
+        <f>IF(ISNUMBER(L52),L52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="M53" s="170">
+        <f>IF(ISNUMBER(M52),M52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="N53" s="170">
+        <f>IF(ISNUMBER(N52),N52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="O53" s="170">
+        <f>IF(ISNUMBER(O52),O52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="P53" s="170">
+        <f>IF(ISNUMBER(P52),P52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="Q53" s="170">
+        <f>IF(ISNUMBER(Q52),Q52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="R53" s="170">
+        <f>IF(ISNUMBER(R52),R52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="S53" s="170">
+        <f>IF(ISNUMBER(S52),S52/8.2*100,"")</f>
+        <v/>
+      </c>
+      <c r="T53" s="155" t="inlineStr"/>
+      <c r="U53" s="155" t="inlineStr"/>
+      <c r="V53" s="155" t="inlineStr">
+        <is>
+          <t>If the model's distance and fuel use both held, petrol sales would be far above what is recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="151" t="inlineStr">
+        <is>
+          <t>7. Not available from any source held</t>
+        </is>
+      </c>
+      <c r="B55" s="151" t="n"/>
+      <c r="C55" s="151" t="n"/>
+      <c r="D55" s="151" t="n"/>
+      <c r="E55" s="151" t="n"/>
+      <c r="F55" s="151" t="n"/>
+      <c r="G55" s="151" t="n"/>
+      <c r="H55" s="151" t="n"/>
+      <c r="I55" s="151" t="n"/>
+      <c r="J55" s="151" t="n"/>
+      <c r="K55" s="151" t="n"/>
+      <c r="L55" s="151" t="n"/>
+      <c r="M55" s="151" t="n"/>
+      <c r="N55" s="151" t="n"/>
+      <c r="O55" s="151" t="n"/>
+      <c r="P55" s="151" t="n"/>
+      <c r="Q55" s="151" t="n"/>
+      <c r="R55" s="151" t="n"/>
+      <c r="S55" s="151" t="n"/>
+      <c r="T55" s="151" t="n"/>
+      <c r="U55" s="151" t="n"/>
+      <c r="V55" s="151" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="161" t="inlineStr">
+        <is>
+          <t>Stock by age (year of first registration)</t>
+        </is>
+      </c>
+      <c r="B56" s="162" t="inlineStr"/>
+      <c r="C56" s="162" t="inlineStr">
+        <is>
+          <t>Missing input</t>
+        </is>
+      </c>
+      <c r="D56" s="164" t="n"/>
+      <c r="E56" s="161" t="inlineStr">
+        <is>
+          <t>Needed for the cohort calculation; NaTIS publishes totals by class only.</t>
+        </is>
+      </c>
+      <c r="F56" s="164" t="n"/>
+      <c r="G56" s="164" t="n"/>
+      <c r="H56" s="164" t="n"/>
+      <c r="I56" s="164" t="n"/>
+      <c r="J56" s="164" t="n"/>
+      <c r="K56" s="164" t="n"/>
+      <c r="L56" s="164" t="n"/>
+      <c r="M56" s="164" t="n"/>
+      <c r="N56" s="164" t="n"/>
+      <c r="O56" s="164" t="n"/>
+      <c r="P56" s="164" t="n"/>
+      <c r="Q56" s="164" t="n"/>
+      <c r="R56" s="164" t="n"/>
+      <c r="S56" s="164" t="n"/>
+      <c r="T56" s="161" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="U56" s="161" t="inlineStr"/>
+      <c r="V56" s="161" t="inlineStr">
+        <is>
+          <t>Source to be found or assumption agreed</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="161" t="inlineStr">
+        <is>
+          <t>Stock by fuel within each class</t>
+        </is>
+      </c>
+      <c r="B57" s="162" t="inlineStr"/>
+      <c r="C57" s="162" t="inlineStr">
+        <is>
+          <t>Missing input</t>
+        </is>
+      </c>
+      <c r="D57" s="164" t="n"/>
+      <c r="E57" s="161" t="inlineStr">
+        <is>
+          <t>Only an all-class fuel count exists, for December 2023.</t>
+        </is>
+      </c>
+      <c r="F57" s="164" t="n"/>
+      <c r="G57" s="164" t="n"/>
+      <c r="H57" s="164" t="n"/>
+      <c r="I57" s="164" t="n"/>
+      <c r="J57" s="164" t="n"/>
+      <c r="K57" s="164" t="n"/>
+      <c r="L57" s="164" t="n"/>
+      <c r="M57" s="164" t="n"/>
+      <c r="N57" s="164" t="n"/>
+      <c r="O57" s="164" t="n"/>
+      <c r="P57" s="164" t="n"/>
+      <c r="Q57" s="164" t="n"/>
+      <c r="R57" s="164" t="n"/>
+      <c r="S57" s="164" t="n"/>
+      <c r="T57" s="161" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="U57" s="161" t="inlineStr"/>
+      <c r="V57" s="161" t="inlineStr">
+        <is>
+          <t>Source to be found or assumption agreed</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="161" t="inlineStr">
+        <is>
+          <t>Electric and hybrid vehicles in the fleet by year</t>
+        </is>
+      </c>
+      <c r="B58" s="162" t="inlineStr"/>
+      <c r="C58" s="162" t="inlineStr">
+        <is>
+          <t>Missing input</t>
+        </is>
+      </c>
+      <c r="D58" s="164" t="n"/>
+      <c r="E58" s="161" t="inlineStr">
+        <is>
+          <t>Sales are known from 2019; stock only for December 2023.</t>
+        </is>
+      </c>
+      <c r="F58" s="164" t="n"/>
+      <c r="G58" s="164" t="n"/>
+      <c r="H58" s="164" t="n"/>
+      <c r="I58" s="164" t="n"/>
+      <c r="J58" s="164" t="n"/>
+      <c r="K58" s="164" t="n"/>
+      <c r="L58" s="164" t="n"/>
+      <c r="M58" s="164" t="n"/>
+      <c r="N58" s="164" t="n"/>
+      <c r="O58" s="164" t="n"/>
+      <c r="P58" s="164" t="n"/>
+      <c r="Q58" s="164" t="n"/>
+      <c r="R58" s="164" t="n"/>
+      <c r="S58" s="164" t="n"/>
+      <c r="T58" s="161" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="U58" s="161" t="inlineStr"/>
+      <c r="V58" s="161" t="inlineStr">
+        <is>
+          <t>Source to be found or assumption agreed</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="161" t="inlineStr">
+        <is>
+          <t>Distance driven after 2014</t>
+        </is>
+      </c>
+      <c r="B59" s="162" t="inlineStr"/>
+      <c r="C59" s="162" t="inlineStr">
+        <is>
+          <t>Missing input</t>
+        </is>
+      </c>
+      <c r="D59" s="164" t="n"/>
+      <c r="E59" s="161" t="inlineStr">
+        <is>
+          <t>The study's figures are a 2014 base; no later survey is held.</t>
+        </is>
+      </c>
+      <c r="F59" s="164" t="n"/>
+      <c r="G59" s="164" t="n"/>
+      <c r="H59" s="164" t="n"/>
+      <c r="I59" s="164" t="n"/>
+      <c r="J59" s="164" t="n"/>
+      <c r="K59" s="164" t="n"/>
+      <c r="L59" s="164" t="n"/>
+      <c r="M59" s="164" t="n"/>
+      <c r="N59" s="164" t="n"/>
+      <c r="O59" s="164" t="n"/>
+      <c r="P59" s="164" t="n"/>
+      <c r="Q59" s="164" t="n"/>
+      <c r="R59" s="164" t="n"/>
+      <c r="S59" s="164" t="n"/>
+      <c r="T59" s="161" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="U59" s="161" t="inlineStr"/>
+      <c r="V59" s="161" t="inlineStr">
+        <is>
+          <t>Source to be found or assumption agreed</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="161" t="inlineStr">
+        <is>
+          <t>Petrol and diesel split of new sales by segment</t>
+        </is>
+      </c>
+      <c r="B60" s="162" t="inlineStr"/>
+      <c r="C60" s="162" t="inlineStr">
+        <is>
+          <t>Missing input</t>
+        </is>
+      </c>
+      <c r="D60" s="164" t="n"/>
+      <c r="E60" s="161" t="inlineStr">
+        <is>
+          <t>naamsa reports drivetrain for the total market only.</t>
+        </is>
+      </c>
+      <c r="F60" s="164" t="n"/>
+      <c r="G60" s="164" t="n"/>
+      <c r="H60" s="164" t="n"/>
+      <c r="I60" s="164" t="n"/>
+      <c r="J60" s="164" t="n"/>
+      <c r="K60" s="164" t="n"/>
+      <c r="L60" s="164" t="n"/>
+      <c r="M60" s="164" t="n"/>
+      <c r="N60" s="164" t="n"/>
+      <c r="O60" s="164" t="n"/>
+      <c r="P60" s="164" t="n"/>
+      <c r="Q60" s="164" t="n"/>
+      <c r="R60" s="164" t="n"/>
+      <c r="S60" s="164" t="n"/>
+      <c r="T60" s="161" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="U60" s="161" t="inlineStr"/>
+      <c r="V60" s="161" t="inlineStr">
+        <is>
+          <t>Source to be found or assumption agreed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -50492,37 +52155,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="170" t="inlineStr">
+      <c r="A4" s="172" t="inlineStr">
         <is>
           <t>Evidence row</t>
         </is>
       </c>
-      <c r="B4" s="170" t="inlineStr">
+      <c r="B4" s="172" t="inlineStr">
         <is>
           <t>Series</t>
         </is>
       </c>
-      <c r="C4" s="170" t="inlineStr">
+      <c r="C4" s="172" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D4" s="170" t="inlineStr">
+      <c r="D4" s="172" t="inlineStr">
         <is>
           <t>Workbook value</t>
         </is>
       </c>
-      <c r="E4" s="170" t="inlineStr">
+      <c r="E4" s="172" t="inlineStr">
         <is>
           <t>Recomputed from inputs</t>
         </is>
       </c>
-      <c r="F4" s="170" t="inlineStr">
+      <c r="F4" s="172" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="G4" s="170" t="inlineStr">
+      <c r="G4" s="172" t="inlineStr">
         <is>
           <t>Input file</t>
         </is>
@@ -50542,10 +52205,10 @@
       <c r="C5" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D5" s="171" t="n">
+      <c r="D5" s="173" t="n">
         <v>9185</v>
       </c>
-      <c r="E5" s="171" t="n">
+      <c r="E5" s="173" t="n">
         <v>9185</v>
       </c>
       <c r="F5" s="1" t="inlineStr">
@@ -50573,10 +52236,10 @@
       <c r="C6" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D6" s="171" t="n">
+      <c r="D6" s="173" t="n">
         <v>9037</v>
       </c>
-      <c r="E6" s="171" t="n">
+      <c r="E6" s="173" t="n">
         <v>9037</v>
       </c>
       <c r="F6" s="1" t="inlineStr">
@@ -50604,10 +52267,10 @@
       <c r="C7" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D7" s="171" t="n">
+      <c r="D7" s="173" t="n">
         <v>9029</v>
       </c>
-      <c r="E7" s="171" t="n">
+      <c r="E7" s="173" t="n">
         <v>9029</v>
       </c>
       <c r="F7" s="1" t="inlineStr">
@@ -50635,10 +52298,10 @@
       <c r="C8" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D8" s="171" t="n">
+      <c r="D8" s="173" t="n">
         <v>9184.869915572999</v>
       </c>
-      <c r="E8" s="171" t="n">
+      <c r="E8" s="173" t="n">
         <v>9184.869915572999</v>
       </c>
       <c r="F8" s="1" t="inlineStr">
@@ -50666,10 +52329,10 @@
       <c r="C9" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D9" s="171" t="n">
+      <c r="D9" s="173" t="n">
         <v>9036.950113492001</v>
       </c>
-      <c r="E9" s="171" t="n">
+      <c r="E9" s="173" t="n">
         <v>9036.950113492001</v>
       </c>
       <c r="F9" s="1" t="inlineStr">
@@ -50697,10 +52360,10 @@
       <c r="C10" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D10" s="171" t="n">
+      <c r="D10" s="173" t="n">
         <v>12717</v>
       </c>
-      <c r="E10" s="171" t="n">
+      <c r="E10" s="173" t="n">
         <v>12717</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
@@ -50728,10 +52391,10 @@
       <c r="C11" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D11" s="171" t="n">
+      <c r="D11" s="173" t="n">
         <v>12907</v>
       </c>
-      <c r="E11" s="171" t="n">
+      <c r="E11" s="173" t="n">
         <v>12907</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
@@ -50759,10 +52422,10 @@
       <c r="C12" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D12" s="171" t="n">
+      <c r="D12" s="173" t="n">
         <v>11734</v>
       </c>
-      <c r="E12" s="171" t="n">
+      <c r="E12" s="173" t="n">
         <v>11734</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
@@ -50790,10 +52453,10 @@
       <c r="C13" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D13" s="171" t="n">
+      <c r="D13" s="173" t="n">
         <v>12717.326319019</v>
       </c>
-      <c r="E13" s="171" t="n">
+      <c r="E13" s="173" t="n">
         <v>12717.326319019</v>
       </c>
       <c r="F13" s="1" t="inlineStr">
@@ -50821,10 +52484,10 @@
       <c r="C14" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D14" s="171" t="n">
+      <c r="D14" s="173" t="n">
         <v>12907.499965808</v>
       </c>
-      <c r="E14" s="171" t="n">
+      <c r="E14" s="173" t="n">
         <v>12907.499965808</v>
       </c>
       <c r="F14" s="1" t="inlineStr">
@@ -50852,10 +52515,10 @@
       <c r="C15" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D15" s="171" t="n">
+      <c r="D15" s="173" t="n">
         <v>1478</v>
       </c>
-      <c r="E15" s="171" t="n">
+      <c r="E15" s="173" t="n">
         <v>1478</v>
       </c>
       <c r="F15" s="1" t="inlineStr">
@@ -50883,10 +52546,10 @@
       <c r="C16" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D16" s="171" t="n">
+      <c r="D16" s="173" t="n">
         <v>1844</v>
       </c>
-      <c r="E16" s="171" t="n">
+      <c r="E16" s="173" t="n">
         <v>1844</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
@@ -50914,10 +52577,10 @@
       <c r="C17" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D17" s="171" t="n">
+      <c r="D17" s="173" t="n">
         <v>1955</v>
       </c>
-      <c r="E17" s="171" t="n">
+      <c r="E17" s="173" t="n">
         <v>1955</v>
       </c>
       <c r="F17" s="1" t="inlineStr">
@@ -50945,10 +52608,10 @@
       <c r="C18" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D18" s="171" t="n">
+      <c r="D18" s="173" t="n">
         <v>1478.149852603</v>
       </c>
-      <c r="E18" s="171" t="n">
+      <c r="E18" s="173" t="n">
         <v>1478.149852603</v>
       </c>
       <c r="F18" s="1" t="inlineStr">
@@ -50976,10 +52639,10 @@
       <c r="C19" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D19" s="171" t="n">
+      <c r="D19" s="173" t="n">
         <v>1843.971762465</v>
       </c>
-      <c r="E19" s="171" t="n">
+      <c r="E19" s="173" t="n">
         <v>1843.971762465</v>
       </c>
       <c r="F19" s="1" t="inlineStr">
@@ -51007,10 +52670,10 @@
       <c r="C20" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D20" s="171" t="n">
+      <c r="D20" s="173" t="n">
         <v>594</v>
       </c>
-      <c r="E20" s="171" t="n">
+      <c r="E20" s="173" t="n">
         <v>594</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
@@ -51038,10 +52701,10 @@
       <c r="C21" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D21" s="171" t="n">
+      <c r="D21" s="173" t="n">
         <v>658</v>
       </c>
-      <c r="E21" s="171" t="n">
+      <c r="E21" s="173" t="n">
         <v>658</v>
       </c>
       <c r="F21" s="1" t="inlineStr">
@@ -51069,10 +52732,10 @@
       <c r="C22" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D22" s="171" t="n">
+      <c r="D22" s="173" t="n">
         <v>441</v>
       </c>
-      <c r="E22" s="171" t="n">
+      <c r="E22" s="173" t="n">
         <v>441</v>
       </c>
       <c r="F22" s="1" t="inlineStr">
@@ -51100,10 +52763,10 @@
       <c r="C23" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D23" s="171" t="n">
+      <c r="D23" s="173" t="n">
         <v>594.0401649620001</v>
       </c>
-      <c r="E23" s="171" t="n">
+      <c r="E23" s="173" t="n">
         <v>594.0401649620001</v>
       </c>
       <c r="F23" s="1" t="inlineStr">
@@ -51131,10 +52794,10 @@
       <c r="C24" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D24" s="171" t="n">
+      <c r="D24" s="173" t="n">
         <v>658.0930416160001</v>
       </c>
-      <c r="E24" s="171" t="n">
+      <c r="E24" s="173" t="n">
         <v>658.0930416160001</v>
       </c>
       <c r="F24" s="1" t="inlineStr">
@@ -51162,10 +52825,10 @@
       <c r="C25" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D25" s="171" t="n">
+      <c r="D25" s="173" t="n">
         <v>76055.06748983047</v>
       </c>
-      <c r="E25" s="171" t="n">
+      <c r="E25" s="173" t="n">
         <v>76055.06748983047</v>
       </c>
       <c r="F25" s="1" t="inlineStr">
@@ -51193,10 +52856,10 @@
       <c r="C26" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D26" s="171" t="n">
+      <c r="D26" s="173" t="n">
         <v>75781.52071231291</v>
       </c>
-      <c r="E26" s="171" t="n">
+      <c r="E26" s="173" t="n">
         <v>75781.52071231291</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
@@ -51224,10 +52887,10 @@
       <c r="C27" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D27" s="171" t="n">
+      <c r="D27" s="173" t="n">
         <v>75255.62912098455</v>
       </c>
-      <c r="E27" s="171" t="n">
+      <c r="E27" s="173" t="n">
         <v>75255.62912098455</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
@@ -51255,10 +52918,10 @@
       <c r="C28" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D28" s="171" t="n">
+      <c r="D28" s="173" t="n">
         <v>75149.98563223911</v>
       </c>
-      <c r="E28" s="171" t="n">
+      <c r="E28" s="173" t="n">
         <v>75149.98563223911</v>
       </c>
       <c r="F28" s="1" t="inlineStr">
@@ -51286,10 +52949,10 @@
       <c r="C29" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D29" s="171" t="n">
+      <c r="D29" s="173" t="n">
         <v>131.7706421450265</v>
       </c>
-      <c r="E29" s="171" t="n">
+      <c r="E29" s="173" t="n">
         <v>131.7706421450265</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
@@ -51317,10 +52980,10 @@
       <c r="C30" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D30" s="171" t="n">
+      <c r="D30" s="173" t="n">
         <v>125.7466421450265</v>
       </c>
-      <c r="E30" s="171" t="n">
+      <c r="E30" s="173" t="n">
         <v>125.7466421450265</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
@@ -51348,10 +53011,10 @@
       <c r="C31" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D31" s="171" t="n">
+      <c r="D31" s="173" t="n">
         <v>114.7916421450265</v>
       </c>
-      <c r="E31" s="171" t="n">
+      <c r="E31" s="173" t="n">
         <v>114.7916421450265</v>
       </c>
       <c r="F31" s="1" t="inlineStr">
@@ -51379,10 +53042,10 @@
       <c r="C32" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D32" s="171" t="n">
+      <c r="D32" s="173" t="n">
         <v>134.7967469817132</v>
       </c>
-      <c r="E32" s="171" t="n">
+      <c r="E32" s="173" t="n">
         <v>134.7967469817132</v>
       </c>
       <c r="F32" s="1" t="inlineStr">
@@ -51410,10 +53073,10 @@
       <c r="C33" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D33" s="171" t="n">
+      <c r="D33" s="173" t="n">
         <v>523.0907540648606</v>
       </c>
-      <c r="E33" s="171" t="n">
+      <c r="E33" s="173" t="n">
         <v>523.0907540648606</v>
       </c>
       <c r="F33" s="1" t="inlineStr">
@@ -51441,10 +53104,10 @@
       <c r="C34" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D34" s="171" t="n">
+      <c r="D34" s="173" t="n">
         <v>524.9937540648609</v>
       </c>
-      <c r="E34" s="171" t="n">
+      <c r="E34" s="173" t="n">
         <v>524.9937540648609</v>
       </c>
       <c r="F34" s="1" t="inlineStr">
@@ -51472,10 +53135,10 @@
       <c r="C35" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D35" s="171" t="n">
+      <c r="D35" s="173" t="n">
         <v>523.150754064861</v>
       </c>
-      <c r="E35" s="171" t="n">
+      <c r="E35" s="173" t="n">
         <v>523.150754064861</v>
       </c>
       <c r="F35" s="1" t="inlineStr">
@@ -51503,10 +53166,10 @@
       <c r="C36" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D36" s="171" t="n">
+      <c r="D36" s="173" t="n">
         <v>516.9856529750193</v>
       </c>
-      <c r="E36" s="171" t="n">
+      <c r="E36" s="173" t="n">
         <v>516.9856529750193</v>
       </c>
       <c r="F36" s="1" t="inlineStr">
@@ -51534,10 +53197,10 @@
       <c r="C37" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D37" s="171" t="n">
+      <c r="D37" s="173" t="n">
         <v>204.4529227196744</v>
       </c>
-      <c r="E37" s="171" t="n">
+      <c r="E37" s="173" t="n">
         <v>204.4529227196744</v>
       </c>
       <c r="F37" s="1" t="inlineStr">
@@ -51565,10 +53228,10 @@
       <c r="C38" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D38" s="171" t="n">
+      <c r="D38" s="173" t="n">
         <v>204.2286999662737</v>
       </c>
-      <c r="E38" s="171" t="n">
+      <c r="E38" s="173" t="n">
         <v>204.2286999662738</v>
       </c>
       <c r="F38" s="1" t="inlineStr">
@@ -51596,10 +53259,10 @@
       <c r="C39" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D39" s="171" t="n">
+      <c r="D39" s="173" t="n">
         <v>205.1258295918731</v>
       </c>
-      <c r="E39" s="171" t="n">
+      <c r="E39" s="173" t="n">
         <v>205.1258295918731</v>
       </c>
       <c r="F39" s="1" t="inlineStr">
@@ -51627,10 +53290,10 @@
       <c r="C40" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D40" s="171" t="n">
+      <c r="D40" s="173" t="n">
         <v>205.4648860142573</v>
       </c>
-      <c r="E40" s="171" t="n">
+      <c r="E40" s="173" t="n">
         <v>205.4648860142574</v>
       </c>
       <c r="F40" s="1" t="inlineStr">
@@ -51658,10 +53321,10 @@
       <c r="C41" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D41" s="171" t="n">
+      <c r="D41" s="173" t="n">
         <v>110.0650907489087</v>
       </c>
-      <c r="E41" s="171" t="n">
+      <c r="E41" s="173" t="n">
         <v>110.0650907489087</v>
       </c>
       <c r="F41" s="1" t="inlineStr">
@@ -51689,10 +53352,10 @@
       <c r="C42" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D42" s="171" t="n">
+      <c r="D42" s="173" t="n">
         <v>109.5650907489087</v>
       </c>
-      <c r="E42" s="171" t="n">
+      <c r="E42" s="173" t="n">
         <v>109.5650907489087</v>
       </c>
       <c r="F42" s="1" t="inlineStr">
@@ -51720,10 +53383,10 @@
       <c r="C43" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D43" s="171" t="n">
+      <c r="D43" s="173" t="n">
         <v>103.6250907489087</v>
       </c>
-      <c r="E43" s="171" t="n">
+      <c r="E43" s="173" t="n">
         <v>103.6250907489087</v>
       </c>
       <c r="F43" s="1" t="inlineStr">
@@ -51751,10 +53414,10 @@
       <c r="C44" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D44" s="171" t="n">
+      <c r="D44" s="173" t="n">
         <v>99.09852067977131</v>
       </c>
-      <c r="E44" s="171" t="n">
+      <c r="E44" s="173" t="n">
         <v>99.09852067977131</v>
       </c>
       <c r="F44" s="1" t="inlineStr">
@@ -51782,10 +53445,10 @@
       <c r="C45" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D45" s="171" t="n">
+      <c r="D45" s="173" t="n">
         <v>93.14166666666667</v>
       </c>
-      <c r="E45" s="171" t="n">
+      <c r="E45" s="173" t="n">
         <v>93.14166666666667</v>
       </c>
       <c r="F45" s="1" t="inlineStr">
@@ -51813,10 +53476,10 @@
       <c r="C46" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D46" s="171" t="n">
+      <c r="D46" s="173" t="n">
         <v>93.71666666666665</v>
       </c>
-      <c r="E46" s="171" t="n">
+      <c r="E46" s="173" t="n">
         <v>93.71666666666665</v>
       </c>
       <c r="F46" s="1" t="inlineStr">
@@ -51844,10 +53507,10 @@
       <c r="C47" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D47" s="171" t="n">
+      <c r="D47" s="173" t="n">
         <v>93.33333333333333</v>
       </c>
-      <c r="E47" s="171" t="n">
+      <c r="E47" s="173" t="n">
         <v>93.33333333333333</v>
       </c>
       <c r="F47" s="1" t="inlineStr">
@@ -51875,10 +53538,10 @@
       <c r="C48" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D48" s="171" t="n">
+      <c r="D48" s="173" t="n">
         <v>92.14166666666665</v>
       </c>
-      <c r="E48" s="171" t="n">
+      <c r="E48" s="173" t="n">
         <v>92.14166666666667</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
@@ -51906,10 +53569,10 @@
       <c r="C49" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D49" s="171" t="n">
+      <c r="D49" s="173" t="n">
         <v>93.00833333333334</v>
       </c>
-      <c r="E49" s="171" t="n">
+      <c r="E49" s="173" t="n">
         <v>93.00833333333333</v>
       </c>
       <c r="F49" s="1" t="inlineStr">
@@ -51937,10 +53600,10 @@
       <c r="C50" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D50" s="171" t="n">
+      <c r="D50" s="173" t="n">
         <v>93.01666666666667</v>
       </c>
-      <c r="E50" s="171" t="n">
+      <c r="E50" s="173" t="n">
         <v>93.01666666666667</v>
       </c>
       <c r="F50" s="1" t="inlineStr">
@@ -51968,10 +53631,10 @@
       <c r="C51" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D51" s="171" t="n">
+      <c r="D51" s="173" t="n">
         <v>93.53333333333332</v>
       </c>
-      <c r="E51" s="171" t="n">
+      <c r="E51" s="173" t="n">
         <v>93.53333333333335</v>
       </c>
       <c r="F51" s="1" t="inlineStr">
@@ -51999,10 +53662,10 @@
       <c r="C52" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D52" s="171" t="n">
+      <c r="D52" s="173" t="n">
         <v>93.70833333333333</v>
       </c>
-      <c r="E52" s="171" t="n">
+      <c r="E52" s="173" t="n">
         <v>93.70833333333333</v>
       </c>
       <c r="F52" s="1" t="inlineStr">
@@ -52030,10 +53693,10 @@
       <c r="C53" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D53" s="171" t="n">
+      <c r="D53" s="173" t="n">
         <v>703.1324447169991</v>
       </c>
-      <c r="E53" s="171" t="n">
+      <c r="E53" s="173" t="n">
         <v>703.132444716999</v>
       </c>
       <c r="F53" s="1" t="inlineStr">
@@ -52061,10 +53724,10 @@
       <c r="C54" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D54" s="171" t="n">
+      <c r="D54" s="173" t="n">
         <v>587.4580081820001</v>
       </c>
-      <c r="E54" s="171" t="n">
+      <c r="E54" s="173" t="n">
         <v>587.4580081820001</v>
       </c>
       <c r="F54" s="1" t="inlineStr">
@@ -52092,10 +53755,10 @@
       <c r="C55" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D55" s="171" t="n">
+      <c r="D55" s="173" t="n">
         <v>3530.440256933996</v>
       </c>
-      <c r="E55" s="171" t="n">
+      <c r="E55" s="173" t="n">
         <v>3530.440256933996</v>
       </c>
       <c r="F55" s="1" t="inlineStr">
@@ -52123,10 +53786,10 @@
       <c r="C56" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D56" s="171" t="n">
+      <c r="D56" s="173" t="n">
         <v>1498.937893394999</v>
       </c>
-      <c r="E56" s="171" t="n">
+      <c r="E56" s="173" t="n">
         <v>1498.937893394999</v>
       </c>
       <c r="F56" s="1" t="inlineStr">
@@ -52154,10 +53817,10 @@
       <c r="C57" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D57" s="171" t="n">
+      <c r="D57" s="173" t="n">
         <v>273.644045045999</v>
       </c>
-      <c r="E57" s="171" t="n">
+      <c r="E57" s="173" t="n">
         <v>273.644045045999</v>
       </c>
       <c r="F57" s="1" t="inlineStr">
@@ -52185,10 +53848,10 @@
       <c r="C58" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D58" s="171" t="n">
+      <c r="D58" s="173" t="n">
         <v>612.2656460789989</v>
       </c>
-      <c r="E58" s="171" t="n">
+      <c r="E58" s="173" t="n">
         <v>612.2656460789989</v>
       </c>
       <c r="F58" s="1" t="inlineStr">
@@ -52216,10 +53879,10 @@
       <c r="C59" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D59" s="171" t="n">
+      <c r="D59" s="173" t="n">
         <v>99.82992901300001</v>
       </c>
-      <c r="E59" s="171" t="n">
+      <c r="E59" s="173" t="n">
         <v>99.829929013</v>
       </c>
       <c r="F59" s="1" t="inlineStr">
@@ -52247,10 +53910,10 @@
       <c r="C60" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D60" s="171" t="n">
+      <c r="D60" s="173" t="n">
         <v>448.1562321239999</v>
       </c>
-      <c r="E60" s="171" t="n">
+      <c r="E60" s="173" t="n">
         <v>448.1562321239999</v>
       </c>
       <c r="F60" s="1" t="inlineStr">
@@ -52278,10 +53941,10 @@
       <c r="C61" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D61" s="171" t="n">
+      <c r="D61" s="173" t="n">
         <v>1431.005460082997</v>
       </c>
-      <c r="E61" s="171" t="n">
+      <c r="E61" s="173" t="n">
         <v>1431.005460082997</v>
       </c>
       <c r="F61" s="1" t="inlineStr">
@@ -52309,10 +53972,10 @@
       <c r="C62" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D62" s="171" t="n">
+      <c r="D62" s="173" t="n">
         <v>1032.35218272</v>
       </c>
-      <c r="E62" s="171" t="n">
+      <c r="E62" s="173" t="n">
         <v>1032.35218272</v>
       </c>
       <c r="F62" s="1" t="inlineStr">
@@ -52340,10 +54003,10 @@
       <c r="C63" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D63" s="171" t="n">
+      <c r="D63" s="173" t="n">
         <v>781.8611598310002</v>
       </c>
-      <c r="E63" s="171" t="n">
+      <c r="E63" s="173" t="n">
         <v>781.8611598310002</v>
       </c>
       <c r="F63" s="1" t="inlineStr">
@@ -52371,10 +54034,10 @@
       <c r="C64" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D64" s="171" t="n">
+      <c r="D64" s="173" t="n">
         <v>3278.990501961999</v>
       </c>
-      <c r="E64" s="171" t="n">
+      <c r="E64" s="173" t="n">
         <v>3278.990501961999</v>
       </c>
       <c r="F64" s="1" t="inlineStr">
@@ -52402,10 +54065,10 @@
       <c r="C65" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D65" s="171" t="n">
+      <c r="D65" s="173" t="n">
         <v>2785.554802503</v>
       </c>
-      <c r="E65" s="171" t="n">
+      <c r="E65" s="173" t="n">
         <v>2785.554802503</v>
       </c>
       <c r="F65" s="1" t="inlineStr">
@@ -52433,10 +54096,10 @@
       <c r="C66" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D66" s="171" t="n">
+      <c r="D66" s="173" t="n">
         <v>221.987440248</v>
       </c>
-      <c r="E66" s="171" t="n">
+      <c r="E66" s="173" t="n">
         <v>221.987440248</v>
       </c>
       <c r="F66" s="1" t="inlineStr">
@@ -52464,10 +54127,10 @@
       <c r="C67" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D67" s="171" t="n">
+      <c r="D67" s="173" t="n">
         <v>1144.924075864997</v>
       </c>
-      <c r="E67" s="171" t="n">
+      <c r="E67" s="173" t="n">
         <v>1144.924075864997</v>
       </c>
       <c r="F67" s="1" t="inlineStr">
@@ -52495,10 +54158,10 @@
       <c r="C68" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D68" s="171" t="n">
+      <c r="D68" s="173" t="n">
         <v>351.9801199100001</v>
       </c>
-      <c r="E68" s="171" t="n">
+      <c r="E68" s="173" t="n">
         <v>351.9801199100001</v>
       </c>
       <c r="F68" s="1" t="inlineStr">
@@ -52526,10 +54189,10 @@
       <c r="C69" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D69" s="171" t="n">
+      <c r="D69" s="173" t="n">
         <v>619.906488913</v>
       </c>
-      <c r="E69" s="171" t="n">
+      <c r="E69" s="173" t="n">
         <v>619.906488913</v>
       </c>
       <c r="F69" s="1" t="inlineStr">
@@ -52557,10 +54220,10 @@
       <c r="C70" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D70" s="171" t="n">
+      <c r="D70" s="173" t="n">
         <v>2499.769547067</v>
       </c>
-      <c r="E70" s="171" t="n">
+      <c r="E70" s="173" t="n">
         <v>2499.769547067</v>
       </c>
       <c r="F70" s="1" t="inlineStr">
@@ -52668,7 +54331,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>Sheets added: History, Sector history, Vehicle history, Checks, History sources. No other cell changed.</t>
+          <t>Sheets added: History, Sector history, Diesel by use, Vehicle history, Checks, History sources. No other cell changed.</t>
         </is>
       </c>
     </row>
@@ -52677,7 +54340,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -52705,517 +54368,517 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="170" t="inlineStr">
+      <c r="A4" s="172" t="inlineStr">
         <is>
           <t>Used for</t>
         </is>
       </c>
-      <c r="B4" s="170" t="inlineStr">
+      <c r="B4" s="172" t="inlineStr">
         <is>
           <t>Publisher</t>
         </is>
       </c>
-      <c r="C4" s="170" t="inlineStr">
+      <c r="C4" s="172" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="D4" s="170" t="inlineStr">
+      <c r="D4" s="172" t="inlineStr">
         <is>
           <t>Original file</t>
         </is>
       </c>
-      <c r="E4" s="170" t="inlineStr">
+      <c r="E4" s="172" t="inlineStr">
         <is>
           <t>Where the original is kept</t>
         </is>
       </c>
-      <c r="F4" s="170" t="inlineStr">
+      <c r="F4" s="172" t="inlineStr">
         <is>
           <t>Extract in the repository</t>
         </is>
       </c>
-      <c r="G4" s="170" t="inlineStr">
+      <c r="G4" s="172" t="inlineStr">
         <is>
           <t>Refresh command</t>
         </is>
       </c>
-      <c r="H4" s="170" t="inlineStr">
+      <c r="H4" s="172" t="inlineStr">
         <is>
           <t>Periods</t>
         </is>
       </c>
-      <c r="I4" s="170" t="inlineStr">
+      <c r="I4" s="172" t="inlineStr">
         <is>
           <t>Limits</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="172" t="inlineStr">
+      <c r="A5" s="174" t="inlineStr">
         <is>
           <t>History sections 1 and 4: national sales</t>
         </is>
       </c>
-      <c r="B5" s="172" t="inlineStr">
+      <c r="B5" s="174" t="inlineStr">
         <is>
           <t>Department of Mineral and Petroleum Resources (energy department)</t>
         </is>
       </c>
-      <c r="C5" s="172" t="inlineStr">
+      <c r="C5" s="174" t="inlineStr">
         <is>
           <t>https://www.dmpr.gov.za/Portals/0/Energy_Website/files/media/SA FUEL SALES VOLUME/</t>
         </is>
       </c>
-      <c r="D5" s="172" t="inlineStr">
+      <c r="D5" s="174" t="inlineStr">
         <is>
           <t>&lt;year&gt;-...-FSV....xls(x), national annual workbooks 2005-2023</t>
         </is>
       </c>
-      <c r="E5" s="172" t="inlineStr">
+      <c r="E5" s="174" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main</t>
         </is>
       </c>
-      <c r="F5" s="172" t="inlineStr">
+      <c r="F5" s="174" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_sales_department.csv</t>
         </is>
       </c>
-      <c r="G5" s="172" t="inlineStr">
+      <c r="G5" s="174" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_energy_dept --vintage 2026</t>
         </is>
       </c>
-      <c r="H5" s="172" t="inlineStr">
+      <c r="H5" s="174" t="inlineStr">
         <is>
           <t>2005-2023</t>
         </is>
       </c>
-      <c r="I5" s="172" t="inlineStr">
+      <c r="I5" s="174" t="inlineStr">
         <is>
           <t>2013 corrected on manish-branch (published sheet). Series ends 2023.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="172" t="inlineStr">
+      <c r="A6" s="174" t="inlineStr">
         <is>
           <t>History section 1: sales by province</t>
         </is>
       </c>
-      <c r="B6" s="172" t="inlineStr">
+      <c r="B6" s="174" t="inlineStr">
         <is>
           <t>Department of Mineral and Petroleum Resources (energy department)</t>
         </is>
       </c>
-      <c r="C6" s="172" t="inlineStr">
+      <c r="C6" s="174" t="inlineStr">
         <is>
           <t>https://www.dmpr.gov.za/Portals/0/Energy_Website/files/media/SA FUEL SALES VOLUME/</t>
         </is>
       </c>
-      <c r="D6" s="172" t="inlineStr">
+      <c r="D6" s="174" t="inlineStr">
         <is>
           <t>&lt;year&gt;-...-Magisterial-Districts-data.xlsx, quarterly sheets</t>
         </is>
       </c>
-      <c r="E6" s="172" t="inlineStr">
+      <c r="E6" s="174" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main (2013 annual workbook on manish-branch)</t>
         </is>
       </c>
-      <c r="F6" s="172" t="inlineStr">
+      <c r="F6" s="174" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_sales_department_by_province.csv</t>
         </is>
       </c>
-      <c r="G6" s="172" t="inlineStr">
+      <c r="G6" s="174" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_energy_dept --vintage 2026</t>
         </is>
       </c>
-      <c r="H6" s="172" t="inlineStr">
+      <c r="H6" s="174" t="inlineStr">
         <is>
           <t>2013-2022</t>
         </is>
       </c>
-      <c r="I6" s="172" t="inlineStr">
+      <c r="I6" s="174" t="inlineStr">
         <is>
           <t>Ends 2022. 2018 understated about 1.8% (district Q1 sheet incomplete). 2014-Q3 differs from national file.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="172" t="inlineStr">
+      <c r="A7" s="174" t="inlineStr">
         <is>
           <t>History section 2: imports and exports</t>
         </is>
       </c>
-      <c r="B7" s="172" t="inlineStr">
+      <c r="B7" s="174" t="inlineStr">
         <is>
           <t>South African Revenue Service, trade statistics</t>
         </is>
       </c>
-      <c r="C7" s="172" t="inlineStr">
+      <c r="C7" s="174" t="inlineStr">
         <is>
           <t>https://tools.sars.gov.za/tradestatsportal/data_download.aspx</t>
         </is>
       </c>
-      <c r="D7" s="172" t="inlineStr">
+      <c r="D7" s="174" t="inlineStr">
         <is>
           <t>sars-&lt;imports|exports&gt;-chapter27-fuels-&lt;year&gt;.xlsx, 2010-2026</t>
         </is>
       </c>
-      <c r="E7" s="172" t="inlineStr">
+      <c r="E7" s="174" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/sars/)</t>
         </is>
       </c>
-      <c r="F7" s="172" t="inlineStr">
+      <c r="F7" s="174" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_trade_sars.csv</t>
         </is>
       </c>
-      <c r="G7" s="172" t="inlineStr">
+      <c r="G7" s="174" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_sars --vintage 2026</t>
         </is>
       </c>
-      <c r="H7" s="172" t="inlineStr">
+      <c r="H7" s="174" t="inlineStr">
         <is>
           <t>2010-2026</t>
         </is>
       </c>
-      <c r="I7" s="172" t="inlineStr">
+      <c r="I7" s="174" t="inlineStr">
         <is>
           <t>Primary record of imports and exports from 2014. Kilograms to 2012, litres from 2014, both in 2013.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="172" t="inlineStr">
+      <c r="A8" s="174" t="inlineStr">
         <is>
           <t>History section 2: FIASA comparison rows</t>
         </is>
       </c>
-      <c r="B8" s="172" t="inlineStr">
+      <c r="B8" s="174" t="inlineStr">
         <is>
           <t>Fuels Industry Association of South Africa (from customs data)</t>
         </is>
       </c>
-      <c r="C8" s="172" t="inlineStr">
+      <c r="C8" s="174" t="inlineStr">
         <is>
           <t>https://fuelsindustry.org.za/publications/annual-reports/</t>
         </is>
       </c>
-      <c r="D8" s="172" t="inlineStr">
+      <c r="D8" s="174" t="inlineStr">
         <is>
           <t>annual-report-&lt;year&gt;.pdf; 2025 edition pp.47-49</t>
         </is>
       </c>
-      <c r="E8" s="172" t="inlineStr">
+      <c r="E8" s="174" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main; 2025 edition on main</t>
         </is>
       </c>
-      <c r="F8" s="172" t="inlineStr">
+      <c r="F8" s="174" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_trade_fiasa.csv</t>
         </is>
       </c>
-      <c r="G8" s="172" t="inlineStr">
+      <c r="G8" s="174" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_fuel_sales --vintage 2026</t>
         </is>
       </c>
-      <c r="H8" s="172" t="inlineStr">
+      <c r="H8" s="174" t="inlineStr">
         <is>
           <t>2009-2025</t>
         </is>
       </c>
-      <c r="I8" s="172" t="inlineStr">
+      <c r="I8" s="174" t="inlineStr">
         <is>
           <t>Cross-check, and the record before 2014; SARS is primary from 2014. 'Kerosene' is jet plus paraffin. Its 2024 diesel import figure is 4.000 bn L above customs.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="172" t="inlineStr">
+      <c r="A9" s="174" t="inlineStr">
         <is>
           <t>History section 4: FIASA comparison row</t>
         </is>
       </c>
-      <c r="B9" s="172" t="inlineStr">
+      <c r="B9" s="174" t="inlineStr">
         <is>
           <t>Fuels Industry Association of South Africa</t>
         </is>
       </c>
-      <c r="C9" s="172" t="inlineStr">
+      <c r="C9" s="174" t="inlineStr">
         <is>
           <t>https://fuelsindustry.org.za/publications/annual-reports/</t>
         </is>
       </c>
-      <c r="D9" s="172" t="inlineStr">
+      <c r="D9" s="174" t="inlineStr">
         <is>
           <t>annual-report-&lt;year&gt;.pdf, 2021-2025 editions</t>
         </is>
       </c>
-      <c r="E9" s="172" t="inlineStr">
+      <c r="E9" s="174" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main; 2025 edition on main</t>
         </is>
       </c>
-      <c r="F9" s="172" t="inlineStr">
+      <c r="F9" s="174" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_sales_fiasa.csv</t>
         </is>
       </c>
-      <c r="G9" s="172" t="inlineStr">
+      <c r="G9" s="174" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_fuel_sales --vintage 2026</t>
         </is>
       </c>
-      <c r="H9" s="172" t="inlineStr">
+      <c r="H9" s="174" t="inlineStr">
         <is>
           <t>2009-2024</t>
         </is>
       </c>
-      <c r="I9" s="172" t="inlineStr">
+      <c r="I9" s="174" t="inlineStr">
         <is>
           <t>Used for 2024 only. Its 2013 figures equal the department's superseded sheet.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="172" t="inlineStr">
+      <c r="A10" s="174" t="inlineStr">
         <is>
           <t>History section 3 and Sector history: production and diesel by sector</t>
         </is>
       </c>
-      <c r="B10" s="172" t="inlineStr">
+      <c r="B10" s="174" t="inlineStr">
         <is>
           <t>Department of Mineral and Petroleum Resources (energy department)</t>
         </is>
       </c>
-      <c r="C10" s="172" t="inlineStr">
+      <c r="C10" s="174" t="inlineStr">
         <is>
           <t>https://www.dmpr.gov.za/Portals/0/Energy_Website/files/media/Energy_Balances.html</t>
         </is>
       </c>
-      <c r="D10" s="172" t="inlineStr">
+      <c r="D10" s="174" t="inlineStr">
         <is>
           <t>&lt;year&gt;-Commodity-Flow-and-Energy-Balance.xlsx, 2007-2021</t>
         </is>
       </c>
-      <c r="E10" s="172" t="inlineStr">
+      <c r="E10" s="174" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main</t>
         </is>
       </c>
-      <c r="F10" s="172" t="inlineStr">
+      <c r="F10" s="174" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/energy_balance_department.csv</t>
         </is>
       </c>
-      <c r="G10" s="172" t="inlineStr">
+      <c r="G10" s="174" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_energy_dept --vintage 2026</t>
         </is>
       </c>
-      <c r="H10" s="172" t="inlineStr">
+      <c r="H10" s="174" t="inlineStr">
         <is>
           <t>2007-2021</t>
         </is>
       </c>
-      <c r="I10" s="172" t="inlineStr">
+      <c r="I10" s="174" t="inlineStr">
         <is>
           <t>Ends 2021. Sector definitions shift in 2016. Fuel oil not extracted.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="172" t="inlineStr">
+      <c r="A11" s="174" t="inlineStr">
         <is>
           <t>History section 3: operators' reported output</t>
         </is>
       </c>
-      <c r="B11" s="172" t="inlineStr">
+      <c r="B11" s="174" t="inlineStr">
         <is>
           <t>Sasol (production and sales metrics); Glencore (annual reports)</t>
         </is>
       </c>
-      <c r="C11" s="172" t="inlineStr">
+      <c r="C11" s="174" t="inlineStr">
         <is>
           <t>https://www.sasol.com/</t>
         </is>
       </c>
-      <c r="D11" s="172" t="inlineStr">
+      <c r="D11" s="174" t="inlineStr">
         <is>
           <t>sasol-metrics-fy2022/2025/2026.pdf, p.4; GLEN-2023/2024/2025-Annual-Report.pdf</t>
         </is>
       </c>
-      <c r="E11" s="172" t="inlineStr">
+      <c r="E11" s="174" t="inlineStr">
         <is>
           <t>Sasol files on manish-branch (external/data/raw/sasol/); Glencore reports by link only</t>
         </is>
       </c>
-      <c r="F11" s="172" t="inlineStr">
+      <c r="F11" s="174" t="inlineStr">
         <is>
           <t>assumptions/2026/reference/refinery_output_operators.csv</t>
         </is>
       </c>
-      <c r="G11" s="172" t="inlineStr">
+      <c r="G11" s="174" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="H11" s="172" t="inlineStr">
+      <c r="H11" s="174" t="inlineStr">
         <is>
           <t>2020-2026</t>
         </is>
       </c>
-      <c r="I11" s="172" t="inlineStr">
+      <c r="I11" s="174" t="inlineStr">
         <is>
           <t>All refined products, no product split; fiscal and calendar years; Astron as energy content.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="172" t="inlineStr">
+      <c r="A12" s="174" t="inlineStr">
         <is>
           <t>History section 5: litres levied</t>
         </is>
       </c>
-      <c r="B12" s="172" t="inlineStr">
+      <c r="B12" s="174" t="inlineStr">
         <is>
           <t>Road Accident Fund</t>
         </is>
       </c>
-      <c r="C12" s="172" t="inlineStr">
+      <c r="C12" s="174" t="inlineStr">
         <is>
           <t>https://static.pmg.org.za/RAF_Annual_Report_2025.pdf</t>
         </is>
       </c>
-      <c r="D12" s="172" t="inlineStr">
+      <c r="D12" s="174" t="inlineStr">
         <is>
           <t>raf-annual-report-2024-25.pdf, note 16 (p.183)</t>
         </is>
       </c>
-      <c r="E12" s="172" t="inlineStr">
+      <c r="E12" s="174" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/raf/)</t>
         </is>
       </c>
-      <c r="F12" s="172" t="inlineStr">
+      <c r="F12" s="174" t="inlineStr">
         <is>
           <t>assumptions/2026/reference/fuel_levy_revenue_raf.csv</t>
         </is>
       </c>
-      <c r="G12" s="172" t="inlineStr">
+      <c r="G12" s="174" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="H12" s="172" t="inlineStr">
+      <c r="H12" s="174" t="inlineStr">
         <is>
           <t>2024-2025</t>
         </is>
       </c>
-      <c r="I12" s="172" t="inlineStr">
+      <c r="I12" s="174" t="inlineStr">
         <is>
           <t>Gross levies and diesel rebate in rand; litres derived in the balance note. Fiscal years; petrol and diesel together.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="172" t="inlineStr">
+      <c r="A13" s="174" t="inlineStr">
         <is>
           <t>Sector history: mining and manufacturing volume indices</t>
         </is>
       </c>
-      <c r="B13" s="172" t="inlineStr">
+      <c r="B13" s="174" t="inlineStr">
         <is>
           <t>Statistics South Africa (P2041 mining, P3041.2 manufacturing, P7162 land transport, P0141 CPI)</t>
         </is>
       </c>
-      <c r="C13" s="172" t="inlineStr">
+      <c r="C13" s="174" t="inlineStr">
         <is>
           <t>https://www.statssa.gov.za/?page_id=1847</t>
         </is>
       </c>
-      <c r="D13" s="172" t="inlineStr">
+      <c r="D13" s="174" t="inlineStr">
         <is>
           <t>release zips, July and August 2026</t>
         </is>
       </c>
-      <c r="E13" s="172" t="inlineStr">
+      <c r="E13" s="174" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/statssa/)</t>
         </is>
       </c>
-      <c r="F13" s="172" t="inlineStr">
+      <c r="F13" s="174" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/activity_statssa_monthly.csv</t>
         </is>
       </c>
-      <c r="G13" s="172" t="inlineStr">
+      <c r="G13" s="174" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_statssa_monthly --vintage 2026</t>
         </is>
       </c>
-      <c r="H13" s="172" t="inlineStr">
+      <c r="H13" s="174" t="inlineStr">
         <is>
           <t>1998-01-2026-08</t>
         </is>
       </c>
-      <c r="I13" s="172" t="inlineStr">
+      <c r="I13" s="174" t="inlineStr">
         <is>
           <t>Activity measures, not fuel volumes. Not seasonally adjusted. Tonnes, not tonne-kilometres.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="172" t="inlineStr">
+      <c r="A14" s="174" t="inlineStr">
         <is>
           <t>Sector history: agriculture real value added</t>
         </is>
       </c>
-      <c r="B14" s="172" t="inlineStr">
+      <c r="B14" s="174" t="inlineStr">
         <is>
           <t>Statistics South Africa (P0441 GDP; P0302 mid-year population)</t>
         </is>
       </c>
-      <c r="C14" s="172" t="inlineStr">
+      <c r="C14" s="174" t="inlineStr">
         <is>
           <t>https://www.statssa.gov.za/?page_id=1854&amp;PPN=P0441</t>
         </is>
       </c>
-      <c r="D14" s="172" t="inlineStr">
+      <c r="D14" s="174" t="inlineStr">
         <is>
           <t>GDP P0441 - GDP Time series Q2 2026.xlsx (Annual sheet); Country projection ... (2002-2026).xlsx</t>
         </is>
       </c>
-      <c r="E14" s="172" t="inlineStr">
+      <c r="E14" s="174" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/statssa/)</t>
         </is>
       </c>
-      <c r="F14" s="172" t="inlineStr">
+      <c r="F14" s="174" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/macro_statssa.csv</t>
         </is>
       </c>
-      <c r="G14" s="172" t="inlineStr">
+      <c r="G14" s="174" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_economy --vintage 2026</t>
         </is>
       </c>
-      <c r="H14" s="172" t="inlineStr">
+      <c r="H14" s="174" t="inlineStr">
         <is>
           <t>1993-2050</t>
         </is>
       </c>
-      <c r="I14" s="172" t="inlineStr">
+      <c r="I14" s="174" t="inlineStr">
         <is>
           <t>Manual placement each release. Years after 2026 are projections, not observations.</t>
         </is>

--- a/output/delivered/Demand_baseline_workshop_2026_10_08_history.xlsx
+++ b/output/delivered/Demand_baseline_workshop_2026_10_08_history.xlsx
@@ -36924,7 +36924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V110"/>
+  <dimension ref="A1:V112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -37131,15 +37131,15 @@
         <v>3530.440256933996</v>
       </c>
       <c r="Q6" s="155">
-        <f>IF(ISNUMBER(Q82),Q82,"")</f>
+        <f>IF(ISNUMBER(Q84),Q84,"")</f>
         <v/>
       </c>
       <c r="R6" s="155">
-        <f>IF(ISNUMBER(R82),R82,"")</f>
+        <f>IF(ISNUMBER(R84),R84,"")</f>
         <v/>
       </c>
       <c r="S6" s="155">
-        <f>IF(ISNUMBER(S82),S82,"")</f>
+        <f>IF(ISNUMBER(S84),S84,"")</f>
         <v/>
       </c>
       <c r="T6" s="152" t="inlineStr">
@@ -37212,15 +37212,15 @@
         <v>1498.937893394999</v>
       </c>
       <c r="Q7" s="155">
-        <f>IF(ISNUMBER(Q83),Q83,"")</f>
+        <f>IF(ISNUMBER(Q85),Q85,"")</f>
         <v/>
       </c>
       <c r="R7" s="155">
-        <f>IF(ISNUMBER(R83),R83,"")</f>
+        <f>IF(ISNUMBER(R85),R85,"")</f>
         <v/>
       </c>
       <c r="S7" s="155">
-        <f>IF(ISNUMBER(S83),S83,"")</f>
+        <f>IF(ISNUMBER(S85),S85,"")</f>
         <v/>
       </c>
       <c r="T7" s="152" t="inlineStr">
@@ -37293,15 +37293,15 @@
         <v>1431.005460082997</v>
       </c>
       <c r="Q8" s="155">
-        <f>IF(ISNUMBER(Q84),Q84,"")</f>
+        <f>IF(ISNUMBER(Q86),Q86,"")</f>
         <v/>
       </c>
       <c r="R8" s="155">
-        <f>IF(ISNUMBER(R84),R84,"")</f>
+        <f>IF(ISNUMBER(R86),R86,"")</f>
         <v/>
       </c>
       <c r="S8" s="155">
-        <f>IF(ISNUMBER(S84),S84,"")</f>
+        <f>IF(ISNUMBER(S86),S86,"")</f>
         <v/>
       </c>
       <c r="T8" s="152" t="inlineStr">
@@ -37374,15 +37374,15 @@
         <v>703.132444716999</v>
       </c>
       <c r="Q9" s="155">
-        <f>IF(ISNUMBER(Q85),Q85,"")</f>
+        <f>IF(ISNUMBER(Q87),Q87,"")</f>
         <v/>
       </c>
       <c r="R9" s="155">
-        <f>IF(ISNUMBER(R85),R85,"")</f>
+        <f>IF(ISNUMBER(R87),R87,"")</f>
         <v/>
       </c>
       <c r="S9" s="155">
-        <f>IF(ISNUMBER(S85),S85,"")</f>
+        <f>IF(ISNUMBER(S87),S87,"")</f>
         <v/>
       </c>
       <c r="T9" s="152" t="inlineStr">
@@ -37455,15 +37455,15 @@
         <v>612.2656460789989</v>
       </c>
       <c r="Q10" s="155">
-        <f>IF(ISNUMBER(Q86),Q86,"")</f>
+        <f>IF(ISNUMBER(Q88),Q88,"")</f>
         <v/>
       </c>
       <c r="R10" s="155">
-        <f>IF(ISNUMBER(R86),R86,"")</f>
+        <f>IF(ISNUMBER(R88),R88,"")</f>
         <v/>
       </c>
       <c r="S10" s="155">
-        <f>IF(ISNUMBER(S86),S86,"")</f>
+        <f>IF(ISNUMBER(S88),S88,"")</f>
         <v/>
       </c>
       <c r="T10" s="152" t="inlineStr">
@@ -37536,15 +37536,15 @@
         <v>587.4580081820001</v>
       </c>
       <c r="Q11" s="155">
-        <f>IF(ISNUMBER(Q87),Q87,"")</f>
+        <f>IF(ISNUMBER(Q89),Q89,"")</f>
         <v/>
       </c>
       <c r="R11" s="155">
-        <f>IF(ISNUMBER(R87),R87,"")</f>
+        <f>IF(ISNUMBER(R89),R89,"")</f>
         <v/>
       </c>
       <c r="S11" s="155">
-        <f>IF(ISNUMBER(S87),S87,"")</f>
+        <f>IF(ISNUMBER(S89),S89,"")</f>
         <v/>
       </c>
       <c r="T11" s="152" t="inlineStr">
@@ -37617,15 +37617,15 @@
         <v>448.1562321239999</v>
       </c>
       <c r="Q12" s="155">
-        <f>IF(ISNUMBER(Q88),Q88,"")</f>
+        <f>IF(ISNUMBER(Q90),Q90,"")</f>
         <v/>
       </c>
       <c r="R12" s="155">
-        <f>IF(ISNUMBER(R88),R88,"")</f>
+        <f>IF(ISNUMBER(R90),R90,"")</f>
         <v/>
       </c>
       <c r="S12" s="155">
-        <f>IF(ISNUMBER(S88),S88,"")</f>
+        <f>IF(ISNUMBER(S90),S90,"")</f>
         <v/>
       </c>
       <c r="T12" s="152" t="inlineStr">
@@ -37698,15 +37698,15 @@
         <v>273.644045045999</v>
       </c>
       <c r="Q13" s="155">
-        <f>IF(ISNUMBER(Q89),Q89,"")</f>
+        <f>IF(ISNUMBER(Q91),Q91,"")</f>
         <v/>
       </c>
       <c r="R13" s="155">
-        <f>IF(ISNUMBER(R89),R89,"")</f>
+        <f>IF(ISNUMBER(R91),R91,"")</f>
         <v/>
       </c>
       <c r="S13" s="155">
-        <f>IF(ISNUMBER(S89),S89,"")</f>
+        <f>IF(ISNUMBER(S91),S91,"")</f>
         <v/>
       </c>
       <c r="T13" s="152" t="inlineStr">
@@ -37779,15 +37779,15 @@
         <v>99.829929013</v>
       </c>
       <c r="Q14" s="155">
-        <f>IF(ISNUMBER(Q90),Q90,"")</f>
+        <f>IF(ISNUMBER(Q92),Q92,"")</f>
         <v/>
       </c>
       <c r="R14" s="155">
-        <f>IF(ISNUMBER(R90),R90,"")</f>
+        <f>IF(ISNUMBER(R92),R92,"")</f>
         <v/>
       </c>
       <c r="S14" s="155">
-        <f>IF(ISNUMBER(S90),S90,"")</f>
+        <f>IF(ISNUMBER(S92),S92,"")</f>
         <v/>
       </c>
       <c r="T14" s="152" t="inlineStr">
@@ -38050,119 +38050,82 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="151" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="159" t="inlineStr">
+        <is>
+          <t>Why 2025 is blank, petrol</t>
+        </is>
+      </c>
+      <c r="B18" s="160" t="inlineStr"/>
+      <c r="C18" s="160" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D18" s="161" t="n"/>
+      <c r="E18" s="159" t="inlineStr">
+        <is>
+          <t>No national petrol sales figure exists for 2025. The department's national series ends at 2023, and FIASA's 2025 report repeats its 2024 row for 2025, so that row was dropped. Without a national total there is nothing to apply the provincial shares to. The estimated 2025 shares are in section 6; the volumes fill in by formula once a 2025 figure is added to the department or FIASA sales row.</t>
+        </is>
+      </c>
+      <c r="F18" s="161" t="n"/>
+      <c r="G18" s="161" t="n"/>
+      <c r="H18" s="161" t="n"/>
+      <c r="I18" s="161" t="n"/>
+      <c r="J18" s="161" t="n"/>
+      <c r="K18" s="161" t="n"/>
+      <c r="L18" s="161" t="n"/>
+      <c r="M18" s="161" t="n"/>
+      <c r="N18" s="161" t="n"/>
+      <c r="O18" s="161" t="n"/>
+      <c r="P18" s="161" t="n"/>
+      <c r="Q18" s="161" t="n"/>
+      <c r="R18" s="161" t="n"/>
+      <c r="S18" s="161" t="n"/>
+      <c r="T18" s="159" t="inlineStr">
+        <is>
+          <t>2025 not estimated</t>
+        </is>
+      </c>
+      <c r="U18" s="159" t="inlineStr"/>
+      <c r="V18" s="159" t="inlineStr">
+        <is>
+          <t>Add the 2025 national figure when the department or FIASA publishes it</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="151" t="inlineStr">
         <is>
           <t>1. Department sales by province: diesel</t>
         </is>
       </c>
-      <c r="B19" s="151" t="n"/>
-      <c r="C19" s="151" t="n"/>
-      <c r="D19" s="151" t="n"/>
-      <c r="E19" s="151" t="n"/>
-      <c r="F19" s="151" t="n"/>
-      <c r="G19" s="151" t="n"/>
-      <c r="H19" s="151" t="n"/>
-      <c r="I19" s="151" t="n"/>
-      <c r="J19" s="151" t="n"/>
-      <c r="K19" s="151" t="n"/>
-      <c r="L19" s="151" t="n"/>
-      <c r="M19" s="151" t="n"/>
-      <c r="N19" s="151" t="n"/>
-      <c r="O19" s="151" t="n"/>
-      <c r="P19" s="151" t="n"/>
-      <c r="Q19" s="151" t="n"/>
-      <c r="R19" s="151" t="n"/>
-      <c r="S19" s="151" t="n"/>
-      <c r="T19" s="151" t="n"/>
-      <c r="U19" s="151" t="n"/>
-      <c r="V19" s="151" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="152" t="inlineStr">
-        <is>
-          <t>Gauteng diesel</t>
-        </is>
-      </c>
-      <c r="B20" s="153" t="inlineStr">
-        <is>
-          <t>million L/year</t>
-        </is>
-      </c>
-      <c r="C20" s="153" t="inlineStr">
-        <is>
-          <t>Observation to 2022; estimate after</t>
-        </is>
-      </c>
-      <c r="D20" s="154" t="n"/>
-      <c r="E20" s="152" t="inlineStr">
-        <is>
-          <t>District-level sales summed to province, 2013-2022. Shows where fuel was sold, not where it was used. 2023-2025 (yellow, italic) are ESTIMATES from section 6, not department data.</t>
-        </is>
-      </c>
-      <c r="F20" s="154" t="n"/>
-      <c r="G20" s="154" t="n">
-        <v>2785.429802</v>
-      </c>
-      <c r="H20" s="154" t="n">
-        <v>3118.078004</v>
-      </c>
-      <c r="I20" s="154" t="n">
-        <v>3160.426878</v>
-      </c>
-      <c r="J20" s="154" t="n">
-        <v>2953.325706855998</v>
-      </c>
-      <c r="K20" s="154" t="n">
-        <v>3125.523429546999</v>
-      </c>
-      <c r="L20" s="154" t="n">
-        <v>3320.043256458996</v>
-      </c>
-      <c r="M20" s="154" t="n">
-        <v>3565.209035882996</v>
-      </c>
-      <c r="N20" s="154" t="n">
-        <v>2950.670842131997</v>
-      </c>
-      <c r="O20" s="154" t="n">
-        <v>3205.191324365998</v>
-      </c>
-      <c r="P20" s="154" t="n">
-        <v>3278.990501961999</v>
-      </c>
-      <c r="Q20" s="155">
-        <f>IF(ISNUMBER(Q102),Q102,"")</f>
-        <v/>
-      </c>
-      <c r="R20" s="155">
-        <f>IF(ISNUMBER(R102),R102,"")</f>
-        <v/>
-      </c>
-      <c r="S20" s="155">
-        <f>IF(ISNUMBER(S102),S102,"")</f>
-        <v/>
-      </c>
-      <c r="T20" s="152" t="inlineStr">
-        <is>
-          <t>2013-2022 observed; 2023-2025 estimated</t>
-        </is>
-      </c>
-      <c r="U20" s="152" t="inlineStr">
-        <is>
-          <t>Department of Mineral and Petroleum Resources, sales volumes, district workbooks; estimates: see section 6</t>
-        </is>
-      </c>
-      <c r="V20" s="152" t="inlineStr">
-        <is>
-          <t>Replace the estimates when the department publishes district data after 2023 quarter 1</t>
-        </is>
-      </c>
+      <c r="B20" s="151" t="n"/>
+      <c r="C20" s="151" t="n"/>
+      <c r="D20" s="151" t="n"/>
+      <c r="E20" s="151" t="n"/>
+      <c r="F20" s="151" t="n"/>
+      <c r="G20" s="151" t="n"/>
+      <c r="H20" s="151" t="n"/>
+      <c r="I20" s="151" t="n"/>
+      <c r="J20" s="151" t="n"/>
+      <c r="K20" s="151" t="n"/>
+      <c r="L20" s="151" t="n"/>
+      <c r="M20" s="151" t="n"/>
+      <c r="N20" s="151" t="n"/>
+      <c r="O20" s="151" t="n"/>
+      <c r="P20" s="151" t="n"/>
+      <c r="Q20" s="151" t="n"/>
+      <c r="R20" s="151" t="n"/>
+      <c r="S20" s="151" t="n"/>
+      <c r="T20" s="151" t="n"/>
+      <c r="U20" s="151" t="n"/>
+      <c r="V20" s="151" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="152" t="inlineStr">
         <is>
-          <t>KwaZulu-Natal diesel</t>
+          <t>Gauteng diesel</t>
         </is>
       </c>
       <c r="B21" s="153" t="inlineStr">
@@ -38183,45 +38146,45 @@
       </c>
       <c r="F21" s="154" t="n"/>
       <c r="G21" s="154" t="n">
-        <v>2252.156455</v>
+        <v>2785.429802</v>
       </c>
       <c r="H21" s="154" t="n">
-        <v>2131.256221</v>
+        <v>3118.078004</v>
       </c>
       <c r="I21" s="154" t="n">
-        <v>2125.006744</v>
+        <v>3160.426878</v>
       </c>
       <c r="J21" s="154" t="n">
-        <v>2176.897259443</v>
+        <v>2953.325706855998</v>
       </c>
       <c r="K21" s="154" t="n">
-        <v>2459.701383962</v>
+        <v>3125.523429546999</v>
       </c>
       <c r="L21" s="154" t="n">
-        <v>2374.693964448</v>
+        <v>3320.043256458996</v>
       </c>
       <c r="M21" s="154" t="n">
-        <v>2576.035405942</v>
+        <v>3565.209035882996</v>
       </c>
       <c r="N21" s="154" t="n">
-        <v>2610.320287135</v>
+        <v>2950.670842131997</v>
       </c>
       <c r="O21" s="154" t="n">
-        <v>2724.422486838</v>
+        <v>3205.191324365998</v>
       </c>
       <c r="P21" s="154" t="n">
-        <v>2785.554802503</v>
+        <v>3278.990501961999</v>
       </c>
       <c r="Q21" s="155">
-        <f>IF(ISNUMBER(Q103),Q103,"")</f>
+        <f>IF(ISNUMBER(Q104),Q104,"")</f>
         <v/>
       </c>
       <c r="R21" s="155">
-        <f>IF(ISNUMBER(R103),R103,"")</f>
+        <f>IF(ISNUMBER(R104),R104,"")</f>
         <v/>
       </c>
       <c r="S21" s="155">
-        <f>IF(ISNUMBER(S103),S103,"")</f>
+        <f>IF(ISNUMBER(S104),S104,"")</f>
         <v/>
       </c>
       <c r="T21" s="152" t="inlineStr">
@@ -38243,7 +38206,7 @@
     <row r="22">
       <c r="A22" s="152" t="inlineStr">
         <is>
-          <t>Western Cape diesel</t>
+          <t>KwaZulu-Natal diesel</t>
         </is>
       </c>
       <c r="B22" s="153" t="inlineStr">
@@ -38264,45 +38227,45 @@
       </c>
       <c r="F22" s="154" t="n"/>
       <c r="G22" s="154" t="n">
-        <v>1987.532805</v>
+        <v>2252.156455</v>
       </c>
       <c r="H22" s="154" t="n">
-        <v>2371.62726</v>
+        <v>2131.256221</v>
       </c>
       <c r="I22" s="154" t="n">
-        <v>2951.017107</v>
+        <v>2125.006744</v>
       </c>
       <c r="J22" s="154" t="n">
-        <v>1896.010479563</v>
+        <v>2176.897259443</v>
       </c>
       <c r="K22" s="154" t="n">
-        <v>1854.222386571999</v>
+        <v>2459.701383962</v>
       </c>
       <c r="L22" s="154" t="n">
-        <v>1849.560718467999</v>
+        <v>2374.693964448</v>
       </c>
       <c r="M22" s="154" t="n">
-        <v>2061.836736</v>
+        <v>2576.035405942</v>
       </c>
       <c r="N22" s="154" t="n">
-        <v>1849.409077413</v>
+        <v>2610.320287135</v>
       </c>
       <c r="O22" s="154" t="n">
-        <v>2608.371193924998</v>
+        <v>2724.422486838</v>
       </c>
       <c r="P22" s="154" t="n">
-        <v>2499.769547067</v>
+        <v>2785.554802503</v>
       </c>
       <c r="Q22" s="155">
-        <f>IF(ISNUMBER(Q104),Q104,"")</f>
+        <f>IF(ISNUMBER(Q105),Q105,"")</f>
         <v/>
       </c>
       <c r="R22" s="155">
-        <f>IF(ISNUMBER(R104),R104,"")</f>
+        <f>IF(ISNUMBER(R105),R105,"")</f>
         <v/>
       </c>
       <c r="S22" s="155">
-        <f>IF(ISNUMBER(S104),S104,"")</f>
+        <f>IF(ISNUMBER(S105),S105,"")</f>
         <v/>
       </c>
       <c r="T22" s="152" t="inlineStr">
@@ -38324,7 +38287,7 @@
     <row r="23">
       <c r="A23" s="152" t="inlineStr">
         <is>
-          <t>Eastern Cape diesel</t>
+          <t>Western Cape diesel</t>
         </is>
       </c>
       <c r="B23" s="153" t="inlineStr">
@@ -38345,45 +38308,45 @@
       </c>
       <c r="F23" s="154" t="n"/>
       <c r="G23" s="154" t="n">
-        <v>782.1488440000001</v>
+        <v>1987.532805</v>
       </c>
       <c r="H23" s="154" t="n">
-        <v>807.224237</v>
+        <v>2371.62726</v>
       </c>
       <c r="I23" s="154" t="n">
-        <v>929.269033</v>
+        <v>2951.017107</v>
       </c>
       <c r="J23" s="154" t="n">
-        <v>928.1418288860002</v>
+        <v>1896.010479563</v>
       </c>
       <c r="K23" s="154" t="n">
-        <v>937.323412165999</v>
+        <v>1854.222386571999</v>
       </c>
       <c r="L23" s="154" t="n">
-        <v>960.6054126530001</v>
+        <v>1849.560718467999</v>
       </c>
       <c r="M23" s="154" t="n">
-        <v>999.0317762660002</v>
+        <v>2061.836736</v>
       </c>
       <c r="N23" s="154" t="n">
-        <v>936.8169864540001</v>
+        <v>1849.409077413</v>
       </c>
       <c r="O23" s="154" t="n">
-        <v>1036.454764805</v>
+        <v>2608.371193924998</v>
       </c>
       <c r="P23" s="154" t="n">
-        <v>1032.35218272</v>
+        <v>2499.769547067</v>
       </c>
       <c r="Q23" s="155">
-        <f>IF(ISNUMBER(Q105),Q105,"")</f>
+        <f>IF(ISNUMBER(Q106),Q106,"")</f>
         <v/>
       </c>
       <c r="R23" s="155">
-        <f>IF(ISNUMBER(R105),R105,"")</f>
+        <f>IF(ISNUMBER(R106),R106,"")</f>
         <v/>
       </c>
       <c r="S23" s="155">
-        <f>IF(ISNUMBER(S105),S105,"")</f>
+        <f>IF(ISNUMBER(S106),S106,"")</f>
         <v/>
       </c>
       <c r="T23" s="152" t="inlineStr">
@@ -38405,7 +38368,7 @@
     <row r="24">
       <c r="A24" s="152" t="inlineStr">
         <is>
-          <t>Mpumalanga diesel</t>
+          <t>Eastern Cape diesel</t>
         </is>
       </c>
       <c r="B24" s="153" t="inlineStr">
@@ -38426,45 +38389,45 @@
       </c>
       <c r="F24" s="154" t="n"/>
       <c r="G24" s="154" t="n">
-        <v>1488.831128</v>
+        <v>782.1488440000001</v>
       </c>
       <c r="H24" s="154" t="n">
-        <v>1513.316515</v>
+        <v>807.224237</v>
       </c>
       <c r="I24" s="154" t="n">
-        <v>1499.329399</v>
+        <v>929.269033</v>
       </c>
       <c r="J24" s="154" t="n">
-        <v>1631.206634515</v>
+        <v>928.1418288860002</v>
       </c>
       <c r="K24" s="154" t="n">
-        <v>1546.048578055</v>
+        <v>937.323412165999</v>
       </c>
       <c r="L24" s="154" t="n">
-        <v>1576.691392181</v>
+        <v>960.6054126530001</v>
       </c>
       <c r="M24" s="154" t="n">
-        <v>1435.128292351999</v>
+        <v>999.0317762660002</v>
       </c>
       <c r="N24" s="154" t="n">
-        <v>1307.424417362</v>
+        <v>936.8169864540001</v>
       </c>
       <c r="O24" s="154" t="n">
-        <v>1275.609358918997</v>
+        <v>1036.454764805</v>
       </c>
       <c r="P24" s="154" t="n">
-        <v>1144.924075864997</v>
+        <v>1032.35218272</v>
       </c>
       <c r="Q24" s="155">
-        <f>IF(ISNUMBER(Q106),Q106,"")</f>
+        <f>IF(ISNUMBER(Q107),Q107,"")</f>
         <v/>
       </c>
       <c r="R24" s="155">
-        <f>IF(ISNUMBER(R106),R106,"")</f>
+        <f>IF(ISNUMBER(R107),R107,"")</f>
         <v/>
       </c>
       <c r="S24" s="155">
-        <f>IF(ISNUMBER(S106),S106,"")</f>
+        <f>IF(ISNUMBER(S107),S107,"")</f>
         <v/>
       </c>
       <c r="T24" s="152" t="inlineStr">
@@ -38486,7 +38449,7 @@
     <row r="25">
       <c r="A25" s="152" t="inlineStr">
         <is>
-          <t>Free State diesel</t>
+          <t>Mpumalanga diesel</t>
         </is>
       </c>
       <c r="B25" s="153" t="inlineStr">
@@ -38507,45 +38470,45 @@
       </c>
       <c r="F25" s="154" t="n"/>
       <c r="G25" s="154" t="n">
-        <v>1292.525069</v>
+        <v>1488.831128</v>
       </c>
       <c r="H25" s="154" t="n">
-        <v>1249.179829</v>
+        <v>1513.316515</v>
       </c>
       <c r="I25" s="154" t="n">
-        <v>1259.015189</v>
+        <v>1499.329399</v>
       </c>
       <c r="J25" s="154" t="n">
-        <v>1124.907207231</v>
+        <v>1631.206634515</v>
       </c>
       <c r="K25" s="154" t="n">
-        <v>930.163930832</v>
+        <v>1546.048578055</v>
       </c>
       <c r="L25" s="154" t="n">
-        <v>1007.279195237</v>
+        <v>1576.691392181</v>
       </c>
       <c r="M25" s="154" t="n">
-        <v>1059.053904877</v>
+        <v>1435.128292351999</v>
       </c>
       <c r="N25" s="154" t="n">
-        <v>1030.588800552</v>
+        <v>1307.424417362</v>
       </c>
       <c r="O25" s="154" t="n">
-        <v>1025.652327622999</v>
+        <v>1275.609358918997</v>
       </c>
       <c r="P25" s="154" t="n">
-        <v>781.8611598310002</v>
+        <v>1144.924075864997</v>
       </c>
       <c r="Q25" s="155">
-        <f>IF(ISNUMBER(Q107),Q107,"")</f>
+        <f>IF(ISNUMBER(Q108),Q108,"")</f>
         <v/>
       </c>
       <c r="R25" s="155">
-        <f>IF(ISNUMBER(R107),R107,"")</f>
+        <f>IF(ISNUMBER(R108),R108,"")</f>
         <v/>
       </c>
       <c r="S25" s="155">
-        <f>IF(ISNUMBER(S107),S107,"")</f>
+        <f>IF(ISNUMBER(S108),S108,"")</f>
         <v/>
       </c>
       <c r="T25" s="152" t="inlineStr">
@@ -38567,7 +38530,7 @@
     <row r="26">
       <c r="A26" s="152" t="inlineStr">
         <is>
-          <t>North West diesel</t>
+          <t>Free State diesel</t>
         </is>
       </c>
       <c r="B26" s="153" t="inlineStr">
@@ -38588,45 +38551,45 @@
       </c>
       <c r="F26" s="154" t="n"/>
       <c r="G26" s="154" t="n">
-        <v>662.591762</v>
+        <v>1292.525069</v>
       </c>
       <c r="H26" s="154" t="n">
-        <v>637.2781210000001</v>
+        <v>1249.179829</v>
       </c>
       <c r="I26" s="154" t="n">
-        <v>659.0079469999999</v>
+        <v>1259.015189</v>
       </c>
       <c r="J26" s="154" t="n">
-        <v>650.4184553739999</v>
+        <v>1124.907207231</v>
       </c>
       <c r="K26" s="154" t="n">
-        <v>587.1623233729999</v>
+        <v>930.163930832</v>
       </c>
       <c r="L26" s="154" t="n">
-        <v>514.025031385</v>
+        <v>1007.279195237</v>
       </c>
       <c r="M26" s="154" t="n">
-        <v>518.359393999</v>
+        <v>1059.053904877</v>
       </c>
       <c r="N26" s="154" t="n">
-        <v>436.165795866</v>
+        <v>1030.588800552</v>
       </c>
       <c r="O26" s="154" t="n">
-        <v>500.4056482319999</v>
+        <v>1025.652327622999</v>
       </c>
       <c r="P26" s="154" t="n">
-        <v>619.906488913</v>
+        <v>781.8611598310002</v>
       </c>
       <c r="Q26" s="155">
-        <f>IF(ISNUMBER(Q108),Q108,"")</f>
+        <f>IF(ISNUMBER(Q109),Q109,"")</f>
         <v/>
       </c>
       <c r="R26" s="155">
-        <f>IF(ISNUMBER(R108),R108,"")</f>
+        <f>IF(ISNUMBER(R109),R109,"")</f>
         <v/>
       </c>
       <c r="S26" s="155">
-        <f>IF(ISNUMBER(S108),S108,"")</f>
+        <f>IF(ISNUMBER(S109),S109,"")</f>
         <v/>
       </c>
       <c r="T26" s="152" t="inlineStr">
@@ -38648,7 +38611,7 @@
     <row r="27">
       <c r="A27" s="152" t="inlineStr">
         <is>
-          <t>Limpopo diesel</t>
+          <t>North West diesel</t>
         </is>
       </c>
       <c r="B27" s="153" t="inlineStr">
@@ -38669,45 +38632,45 @@
       </c>
       <c r="F27" s="154" t="n"/>
       <c r="G27" s="154" t="n">
-        <v>424.483028</v>
+        <v>662.591762</v>
       </c>
       <c r="H27" s="154" t="n">
-        <v>408.41603</v>
+        <v>637.2781210000001</v>
       </c>
       <c r="I27" s="154" t="n">
-        <v>371.279601</v>
+        <v>659.0079469999999</v>
       </c>
       <c r="J27" s="154" t="n">
-        <v>309.226164304</v>
+        <v>650.4184553739999</v>
       </c>
       <c r="K27" s="154" t="n">
-        <v>274.713980268</v>
+        <v>587.1623233729999</v>
       </c>
       <c r="L27" s="154" t="n">
-        <v>295.60009792</v>
+        <v>514.025031385</v>
       </c>
       <c r="M27" s="154" t="n">
-        <v>269.697983735</v>
+        <v>518.359393999</v>
       </c>
       <c r="N27" s="154" t="n">
-        <v>216.1239956</v>
+        <v>436.165795866</v>
       </c>
       <c r="O27" s="154" t="n">
-        <v>210.257732307</v>
+        <v>500.4056482319999</v>
       </c>
       <c r="P27" s="154" t="n">
-        <v>221.987440248</v>
+        <v>619.906488913</v>
       </c>
       <c r="Q27" s="155">
-        <f>IF(ISNUMBER(Q109),Q109,"")</f>
+        <f>IF(ISNUMBER(Q110),Q110,"")</f>
         <v/>
       </c>
       <c r="R27" s="155">
-        <f>IF(ISNUMBER(R109),R109,"")</f>
+        <f>IF(ISNUMBER(R110),R110,"")</f>
         <v/>
       </c>
       <c r="S27" s="155">
-        <f>IF(ISNUMBER(S109),S109,"")</f>
+        <f>IF(ISNUMBER(S110),S110,"")</f>
         <v/>
       </c>
       <c r="T27" s="152" t="inlineStr">
@@ -38729,7 +38692,7 @@
     <row r="28">
       <c r="A28" s="152" t="inlineStr">
         <is>
-          <t>Northern Cape diesel</t>
+          <t>Limpopo diesel</t>
         </is>
       </c>
       <c r="B28" s="153" t="inlineStr">
@@ -38750,565 +38713,536 @@
       </c>
       <c r="F28" s="154" t="n"/>
       <c r="G28" s="154" t="n">
+        <v>424.483028</v>
+      </c>
+      <c r="H28" s="154" t="n">
+        <v>408.41603</v>
+      </c>
+      <c r="I28" s="154" t="n">
+        <v>371.279601</v>
+      </c>
+      <c r="J28" s="154" t="n">
+        <v>309.226164304</v>
+      </c>
+      <c r="K28" s="154" t="n">
+        <v>274.713980268</v>
+      </c>
+      <c r="L28" s="154" t="n">
+        <v>295.60009792</v>
+      </c>
+      <c r="M28" s="154" t="n">
+        <v>269.697983735</v>
+      </c>
+      <c r="N28" s="154" t="n">
+        <v>216.1239956</v>
+      </c>
+      <c r="O28" s="154" t="n">
+        <v>210.257732307</v>
+      </c>
+      <c r="P28" s="154" t="n">
+        <v>221.987440248</v>
+      </c>
+      <c r="Q28" s="155">
+        <f>IF(ISNUMBER(Q111),Q111,"")</f>
+        <v/>
+      </c>
+      <c r="R28" s="155">
+        <f>IF(ISNUMBER(R111),R111,"")</f>
+        <v/>
+      </c>
+      <c r="S28" s="155">
+        <f>IF(ISNUMBER(S111),S111,"")</f>
+        <v/>
+      </c>
+      <c r="T28" s="152" t="inlineStr">
+        <is>
+          <t>2013-2022 observed; 2023-2025 estimated</t>
+        </is>
+      </c>
+      <c r="U28" s="152" t="inlineStr">
+        <is>
+          <t>Department of Mineral and Petroleum Resources, sales volumes, district workbooks; estimates: see section 6</t>
+        </is>
+      </c>
+      <c r="V28" s="152" t="inlineStr">
+        <is>
+          <t>Replace the estimates when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="152" t="inlineStr">
+        <is>
+          <t>Northern Cape diesel</t>
+        </is>
+      </c>
+      <c r="B29" s="153" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C29" s="153" t="inlineStr">
+        <is>
+          <t>Observation to 2022; estimate after</t>
+        </is>
+      </c>
+      <c r="D29" s="154" t="n"/>
+      <c r="E29" s="152" t="inlineStr">
+        <is>
+          <t>District-level sales summed to province, 2013-2022. Shows where fuel was sold, not where it was used. 2023-2025 (yellow, italic) are ESTIMATES from section 6, not department data.</t>
+        </is>
+      </c>
+      <c r="F29" s="154" t="n"/>
+      <c r="G29" s="154" t="n">
         <v>465.348224</v>
       </c>
-      <c r="H28" s="154" t="n">
+      <c r="H29" s="154" t="n">
         <v>507.013669</v>
       </c>
-      <c r="I28" s="154" t="n">
+      <c r="I29" s="154" t="n">
         <v>537.799461</v>
       </c>
-      <c r="J28" s="154" t="n">
+      <c r="J29" s="154" t="n">
         <v>412.24030225</v>
       </c>
-      <c r="K28" s="154" t="n">
+      <c r="K29" s="154" t="n">
         <v>430.290764414</v>
       </c>
-      <c r="L28" s="154" t="n">
+      <c r="L29" s="154" t="n">
         <v>420.121363622</v>
       </c>
-      <c r="M28" s="154" t="n">
+      <c r="M29" s="154" t="n">
         <v>424.278703163</v>
       </c>
-      <c r="N28" s="154" t="n">
+      <c r="N29" s="154" t="n">
         <v>352.4375567820001</v>
       </c>
-      <c r="O28" s="154" t="n">
+      <c r="O29" s="154" t="n">
         <v>358.653178157</v>
       </c>
-      <c r="P28" s="154" t="n">
+      <c r="P29" s="154" t="n">
         <v>351.9801199100001</v>
       </c>
-      <c r="Q28" s="155">
-        <f>IF(ISNUMBER(Q110),Q110,"")</f>
-        <v/>
-      </c>
-      <c r="R28" s="155">
-        <f>IF(ISNUMBER(R110),R110,"")</f>
-        <v/>
-      </c>
-      <c r="S28" s="155">
-        <f>IF(ISNUMBER(S110),S110,"")</f>
-        <v/>
-      </c>
-      <c r="T28" s="152" t="inlineStr">
+      <c r="Q29" s="155">
+        <f>IF(ISNUMBER(Q112),Q112,"")</f>
+        <v/>
+      </c>
+      <c r="R29" s="155">
+        <f>IF(ISNUMBER(R112),R112,"")</f>
+        <v/>
+      </c>
+      <c r="S29" s="155">
+        <f>IF(ISNUMBER(S112),S112,"")</f>
+        <v/>
+      </c>
+      <c r="T29" s="152" t="inlineStr">
         <is>
           <t>2013-2022 observed; 2023-2025 estimated</t>
         </is>
       </c>
-      <c r="U28" s="152" t="inlineStr">
+      <c r="U29" s="152" t="inlineStr">
         <is>
           <t>Department of Mineral and Petroleum Resources, sales volumes, district workbooks; estimates: see section 6</t>
         </is>
       </c>
-      <c r="V28" s="152" t="inlineStr">
+      <c r="V29" s="152" t="inlineStr">
         <is>
           <t>Replace the estimates when the department publishes district data after 2023 quarter 1</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="156" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="156" t="inlineStr">
         <is>
           <t>Sum of nine provinces, diesel</t>
         </is>
       </c>
-      <c r="B29" s="157" t="inlineStr">
+      <c r="B30" s="157" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C29" s="157" t="inlineStr">
+      <c r="C30" s="157" t="inlineStr">
         <is>
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D29" s="158" t="n"/>
-      <c r="E29" s="156" t="inlineStr">
+      <c r="D30" s="158" t="n"/>
+      <c r="E30" s="156" t="inlineStr">
         <is>
           <t>Sum of the nine rows above. From 2023 it sums estimates, which add to the national figure by construction.</t>
         </is>
       </c>
-      <c r="F29" s="158">
-        <f>IF(COUNT(F20:F28)&lt;9,"",SUM(F20:F28))</f>
-        <v/>
-      </c>
-      <c r="G29" s="158">
-        <f>IF(COUNT(G20:G28)&lt;9,"",SUM(G20:G28))</f>
-        <v/>
-      </c>
-      <c r="H29" s="158">
-        <f>IF(COUNT(H20:H28)&lt;9,"",SUM(H20:H28))</f>
-        <v/>
-      </c>
-      <c r="I29" s="158">
-        <f>IF(COUNT(I20:I28)&lt;9,"",SUM(I20:I28))</f>
-        <v/>
-      </c>
-      <c r="J29" s="158">
-        <f>IF(COUNT(J20:J28)&lt;9,"",SUM(J20:J28))</f>
-        <v/>
-      </c>
-      <c r="K29" s="158">
-        <f>IF(COUNT(K20:K28)&lt;9,"",SUM(K20:K28))</f>
-        <v/>
-      </c>
-      <c r="L29" s="158">
-        <f>IF(COUNT(L20:L28)&lt;9,"",SUM(L20:L28))</f>
-        <v/>
-      </c>
-      <c r="M29" s="158">
-        <f>IF(COUNT(M20:M28)&lt;9,"",SUM(M20:M28))</f>
-        <v/>
-      </c>
-      <c r="N29" s="158">
-        <f>IF(COUNT(N20:N28)&lt;9,"",SUM(N20:N28))</f>
-        <v/>
-      </c>
-      <c r="O29" s="158">
-        <f>IF(COUNT(O20:O28)&lt;9,"",SUM(O20:O28))</f>
-        <v/>
-      </c>
-      <c r="P29" s="158">
-        <f>IF(COUNT(P20:P28)&lt;9,"",SUM(P20:P28))</f>
-        <v/>
-      </c>
-      <c r="Q29" s="158">
-        <f>IF(COUNT(Q20:Q28)&lt;9,"",SUM(Q20:Q28))</f>
-        <v/>
-      </c>
-      <c r="R29" s="158">
-        <f>IF(COUNT(R20:R28)&lt;9,"",SUM(R20:R28))</f>
-        <v/>
-      </c>
-      <c r="S29" s="158">
-        <f>IF(COUNT(S20:S28)&lt;9,"",SUM(S20:S28))</f>
-        <v/>
-      </c>
-      <c r="T29" s="156" t="inlineStr"/>
-      <c r="U29" s="156" t="inlineStr"/>
-      <c r="V29" s="156" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="152" t="inlineStr">
+      <c r="F30" s="158">
+        <f>IF(COUNT(F21:F29)&lt;9,"",SUM(F21:F29))</f>
+        <v/>
+      </c>
+      <c r="G30" s="158">
+        <f>IF(COUNT(G21:G29)&lt;9,"",SUM(G21:G29))</f>
+        <v/>
+      </c>
+      <c r="H30" s="158">
+        <f>IF(COUNT(H21:H29)&lt;9,"",SUM(H21:H29))</f>
+        <v/>
+      </c>
+      <c r="I30" s="158">
+        <f>IF(COUNT(I21:I29)&lt;9,"",SUM(I21:I29))</f>
+        <v/>
+      </c>
+      <c r="J30" s="158">
+        <f>IF(COUNT(J21:J29)&lt;9,"",SUM(J21:J29))</f>
+        <v/>
+      </c>
+      <c r="K30" s="158">
+        <f>IF(COUNT(K21:K29)&lt;9,"",SUM(K21:K29))</f>
+        <v/>
+      </c>
+      <c r="L30" s="158">
+        <f>IF(COUNT(L21:L29)&lt;9,"",SUM(L21:L29))</f>
+        <v/>
+      </c>
+      <c r="M30" s="158">
+        <f>IF(COUNT(M21:M29)&lt;9,"",SUM(M21:M29))</f>
+        <v/>
+      </c>
+      <c r="N30" s="158">
+        <f>IF(COUNT(N21:N29)&lt;9,"",SUM(N21:N29))</f>
+        <v/>
+      </c>
+      <c r="O30" s="158">
+        <f>IF(COUNT(O21:O29)&lt;9,"",SUM(O21:O29))</f>
+        <v/>
+      </c>
+      <c r="P30" s="158">
+        <f>IF(COUNT(P21:P29)&lt;9,"",SUM(P21:P29))</f>
+        <v/>
+      </c>
+      <c r="Q30" s="158">
+        <f>IF(COUNT(Q21:Q29)&lt;9,"",SUM(Q21:Q29))</f>
+        <v/>
+      </c>
+      <c r="R30" s="158">
+        <f>IF(COUNT(R21:R29)&lt;9,"",SUM(R21:R29))</f>
+        <v/>
+      </c>
+      <c r="S30" s="158">
+        <f>IF(COUNT(S21:S29)&lt;9,"",SUM(S21:S29))</f>
+        <v/>
+      </c>
+      <c r="T30" s="156" t="inlineStr"/>
+      <c r="U30" s="156" t="inlineStr"/>
+      <c r="V30" s="156" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="152" t="inlineStr">
         <is>
           <t>Department national file, diesel</t>
         </is>
       </c>
-      <c r="B30" s="153" t="inlineStr">
+      <c r="B31" s="153" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C30" s="153" t="inlineStr">
+      <c r="C31" s="153" t="inlineStr">
         <is>
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D30" s="154" t="n"/>
-      <c r="E30" s="152" t="inlineStr">
+      <c r="D31" s="154" t="n"/>
+      <c r="E31" s="152" t="inlineStr">
         <is>
           <t>National annual workbook, years with four quarters reported.</t>
         </is>
       </c>
-      <c r="F30" s="154" t="n">
+      <c r="F31" s="154" t="n">
         <v>11663.34068</v>
       </c>
-      <c r="G30" s="154" t="n">
+      <c r="G31" s="154" t="n">
         <v>12141.281548</v>
       </c>
-      <c r="H30" s="154" t="n">
+      <c r="H31" s="154" t="n">
         <v>12615.023359</v>
       </c>
-      <c r="I30" s="154" t="n">
+      <c r="I31" s="154" t="n">
         <v>13520.13925195</v>
       </c>
-      <c r="J30" s="154" t="n">
+      <c r="J31" s="154" t="n">
         <v>12082.374038422</v>
       </c>
-      <c r="K30" s="154" t="n">
+      <c r="K31" s="154" t="n">
         <v>12147.245167189</v>
       </c>
-      <c r="L30" s="154" t="n">
+      <c r="L31" s="154" t="n">
         <v>12538.744325998</v>
       </c>
-      <c r="M30" s="154" t="n">
+      <c r="M31" s="154" t="n">
         <v>12908.631232217</v>
       </c>
-      <c r="N30" s="154" t="n">
+      <c r="N31" s="154" t="n">
         <v>11689.957759296</v>
       </c>
-      <c r="O30" s="154" t="n">
+      <c r="O31" s="154" t="n">
         <v>12945.782750435</v>
       </c>
-      <c r="P30" s="154" t="n">
+      <c r="P31" s="154" t="n">
         <v>12717.326319019</v>
       </c>
-      <c r="Q30" s="154" t="n">
+      <c r="Q31" s="154" t="n">
         <v>12907.499965808</v>
       </c>
-      <c r="R30" s="154" t="n"/>
-      <c r="S30" s="154" t="n"/>
-      <c r="T30" s="152" t="inlineStr">
+      <c r="R31" s="154" t="n"/>
+      <c r="S31" s="154" t="n"/>
+      <c r="T31" s="152" t="inlineStr">
         <is>
           <t>2012-2023; nothing published for 2024 or 2025</t>
         </is>
       </c>
-      <c r="U30" s="152" t="inlineStr">
+      <c r="U31" s="152" t="inlineStr">
         <is>
           <t>Department of Mineral and Petroleum Resources, sales volumes, national workbooks</t>
         </is>
       </c>
-      <c r="V30" s="152" t="inlineStr">
+      <c r="V31" s="152" t="inlineStr">
         <is>
           <t>2024 national sales: source to be agreed (Nigel)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="156" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="156" t="inlineStr">
         <is>
           <t>Provinces less national, diesel</t>
         </is>
       </c>
-      <c r="B31" s="157" t="inlineStr">
+      <c r="B32" s="157" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C31" s="157" t="inlineStr">
+      <c r="C32" s="157" t="inlineStr">
         <is>
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D31" s="158" t="n"/>
-      <c r="E31" s="156" t="inlineStr">
+      <c r="D32" s="158" t="n"/>
+      <c r="E32" s="156" t="inlineStr">
         <is>
           <t>Difference between the department's two files. 2013 and 2015 traced; 2014 and 2018 for decision. Zero from 2023 only because the estimates are shares of the national figure.</t>
         </is>
       </c>
-      <c r="F31" s="158">
-        <f>IF(COUNT(F29,F30)&lt;2,"",F29-F30)</f>
-        <v/>
-      </c>
-      <c r="G31" s="158">
-        <f>IF(COUNT(G29,G30)&lt;2,"",G29-G30)</f>
-        <v/>
-      </c>
-      <c r="H31" s="158">
-        <f>IF(COUNT(H29,H30)&lt;2,"",H29-H30)</f>
-        <v/>
-      </c>
-      <c r="I31" s="158">
-        <f>IF(COUNT(I29,I30)&lt;2,"",I29-I30)</f>
-        <v/>
-      </c>
-      <c r="J31" s="158">
-        <f>IF(COUNT(J29,J30)&lt;2,"",J29-J30)</f>
-        <v/>
-      </c>
-      <c r="K31" s="158">
-        <f>IF(COUNT(K29,K30)&lt;2,"",K29-K30)</f>
-        <v/>
-      </c>
-      <c r="L31" s="158">
-        <f>IF(COUNT(L29,L30)&lt;2,"",L29-L30)</f>
-        <v/>
-      </c>
-      <c r="M31" s="158">
-        <f>IF(COUNT(M29,M30)&lt;2,"",M29-M30)</f>
-        <v/>
-      </c>
-      <c r="N31" s="158">
-        <f>IF(COUNT(N29,N30)&lt;2,"",N29-N30)</f>
-        <v/>
-      </c>
-      <c r="O31" s="158">
-        <f>IF(COUNT(O29,O30)&lt;2,"",O29-O30)</f>
-        <v/>
-      </c>
-      <c r="P31" s="158">
-        <f>IF(COUNT(P29,P30)&lt;2,"",P29-P30)</f>
-        <v/>
-      </c>
-      <c r="Q31" s="158">
-        <f>IF(COUNT(Q29,Q30)&lt;2,"",Q29-Q30)</f>
-        <v/>
-      </c>
-      <c r="R31" s="158">
-        <f>IF(COUNT(R29,R30)&lt;2,"",R29-R30)</f>
-        <v/>
-      </c>
-      <c r="S31" s="158">
-        <f>IF(COUNT(S29,S30)&lt;2,"",S29-S30)</f>
-        <v/>
-      </c>
-      <c r="T31" s="156" t="inlineStr"/>
-      <c r="U31" s="156" t="inlineStr"/>
-      <c r="V31" s="156" t="inlineStr">
+      <c r="F32" s="158">
+        <f>IF(COUNT(F30,F31)&lt;2,"",F30-F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="158">
+        <f>IF(COUNT(G30,G31)&lt;2,"",G30-G31)</f>
+        <v/>
+      </c>
+      <c r="H32" s="158">
+        <f>IF(COUNT(H30,H31)&lt;2,"",H30-H31)</f>
+        <v/>
+      </c>
+      <c r="I32" s="158">
+        <f>IF(COUNT(I30,I31)&lt;2,"",I30-I31)</f>
+        <v/>
+      </c>
+      <c r="J32" s="158">
+        <f>IF(COUNT(J30,J31)&lt;2,"",J30-J31)</f>
+        <v/>
+      </c>
+      <c r="K32" s="158">
+        <f>IF(COUNT(K30,K31)&lt;2,"",K30-K31)</f>
+        <v/>
+      </c>
+      <c r="L32" s="158">
+        <f>IF(COUNT(L30,L31)&lt;2,"",L30-L31)</f>
+        <v/>
+      </c>
+      <c r="M32" s="158">
+        <f>IF(COUNT(M30,M31)&lt;2,"",M30-M31)</f>
+        <v/>
+      </c>
+      <c r="N32" s="158">
+        <f>IF(COUNT(N30,N31)&lt;2,"",N30-N31)</f>
+        <v/>
+      </c>
+      <c r="O32" s="158">
+        <f>IF(COUNT(O30,O31)&lt;2,"",O30-O31)</f>
+        <v/>
+      </c>
+      <c r="P32" s="158">
+        <f>IF(COUNT(P30,P31)&lt;2,"",P30-P31)</f>
+        <v/>
+      </c>
+      <c r="Q32" s="158">
+        <f>IF(COUNT(Q30,Q31)&lt;2,"",Q30-Q31)</f>
+        <v/>
+      </c>
+      <c r="R32" s="158">
+        <f>IF(COUNT(R30,R31)&lt;2,"",R30-R31)</f>
+        <v/>
+      </c>
+      <c r="S32" s="158">
+        <f>IF(COUNT(S30,S31)&lt;2,"",S30-S31)</f>
+        <v/>
+      </c>
+      <c r="T32" s="156" t="inlineStr"/>
+      <c r="U32" s="156" t="inlineStr"/>
+      <c r="V32" s="156" t="inlineStr">
         <is>
           <t>See integrity_flag_log_2026-10-06.md</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="151" t="inlineStr">
+      <c r="A33" s="159" t="inlineStr">
+        <is>
+          <t>Why 2025 is blank, diesel</t>
+        </is>
+      </c>
+      <c r="B33" s="160" t="inlineStr"/>
+      <c r="C33" s="160" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D33" s="161" t="n"/>
+      <c r="E33" s="159" t="inlineStr">
+        <is>
+          <t>No national diesel sales figure exists for 2025. The department's national series ends at 2023, and FIASA's 2025 report repeats its 2024 row for 2025, so that row was dropped. Without a national total there is nothing to apply the provincial shares to. The estimated 2025 shares are in section 6; the volumes fill in by formula once a 2025 figure is added to the department or FIASA sales row.</t>
+        </is>
+      </c>
+      <c r="F33" s="161" t="n"/>
+      <c r="G33" s="161" t="n"/>
+      <c r="H33" s="161" t="n"/>
+      <c r="I33" s="161" t="n"/>
+      <c r="J33" s="161" t="n"/>
+      <c r="K33" s="161" t="n"/>
+      <c r="L33" s="161" t="n"/>
+      <c r="M33" s="161" t="n"/>
+      <c r="N33" s="161" t="n"/>
+      <c r="O33" s="161" t="n"/>
+      <c r="P33" s="161" t="n"/>
+      <c r="Q33" s="161" t="n"/>
+      <c r="R33" s="161" t="n"/>
+      <c r="S33" s="161" t="n"/>
+      <c r="T33" s="159" t="inlineStr">
+        <is>
+          <t>2025 not estimated</t>
+        </is>
+      </c>
+      <c r="U33" s="159" t="inlineStr"/>
+      <c r="V33" s="159" t="inlineStr">
+        <is>
+          <t>Add the 2025 national figure when the department or FIASA publishes it</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="151" t="inlineStr">
         <is>
           <t>2. Customs trade (SARS)</t>
         </is>
       </c>
-      <c r="B33" s="151" t="n"/>
-      <c r="C33" s="151" t="n"/>
-      <c r="D33" s="151" t="n"/>
-      <c r="E33" s="151" t="n"/>
-      <c r="F33" s="151" t="n"/>
-      <c r="G33" s="151" t="n"/>
-      <c r="H33" s="151" t="n"/>
-      <c r="I33" s="151" t="n"/>
-      <c r="J33" s="151" t="n"/>
-      <c r="K33" s="151" t="n"/>
-      <c r="L33" s="151" t="n"/>
-      <c r="M33" s="151" t="n"/>
-      <c r="N33" s="151" t="n"/>
-      <c r="O33" s="151" t="n"/>
-      <c r="P33" s="151" t="n"/>
-      <c r="Q33" s="151" t="n"/>
-      <c r="R33" s="151" t="n"/>
-      <c r="S33" s="151" t="n"/>
-      <c r="T33" s="151" t="n"/>
-      <c r="U33" s="151" t="n"/>
-      <c r="V33" s="151" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="152" t="inlineStr">
+      <c r="B35" s="151" t="n"/>
+      <c r="C35" s="151" t="n"/>
+      <c r="D35" s="151" t="n"/>
+      <c r="E35" s="151" t="n"/>
+      <c r="F35" s="151" t="n"/>
+      <c r="G35" s="151" t="n"/>
+      <c r="H35" s="151" t="n"/>
+      <c r="I35" s="151" t="n"/>
+      <c r="J35" s="151" t="n"/>
+      <c r="K35" s="151" t="n"/>
+      <c r="L35" s="151" t="n"/>
+      <c r="M35" s="151" t="n"/>
+      <c r="N35" s="151" t="n"/>
+      <c r="O35" s="151" t="n"/>
+      <c r="P35" s="151" t="n"/>
+      <c r="Q35" s="151" t="n"/>
+      <c r="R35" s="151" t="n"/>
+      <c r="S35" s="151" t="n"/>
+      <c r="T35" s="151" t="n"/>
+      <c r="U35" s="151" t="n"/>
+      <c r="V35" s="151" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="152" t="inlineStr">
         <is>
           <t>Imports, diesel</t>
         </is>
       </c>
-      <c r="B34" s="153" t="inlineStr">
+      <c r="B36" s="153" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C34" s="153" t="inlineStr">
+      <c r="C36" s="153" t="inlineStr">
         <is>
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D34" s="154" t="n"/>
-      <c r="E34" s="152" t="inlineStr">
+      <c r="D36" s="154" t="n"/>
+      <c r="E36" s="152" t="inlineStr">
         <is>
           <t>Complete years reported in litres. Before 2014 customs is in kilograms or mixed units and is not used.</t>
         </is>
       </c>
-      <c r="F34" s="154" t="n"/>
-      <c r="G34" s="154" t="n"/>
-      <c r="H34" s="154" t="n">
+      <c r="F36" s="154" t="n"/>
+      <c r="G36" s="154" t="n"/>
+      <c r="H36" s="154" t="n">
         <v>4991.712326600001</v>
       </c>
-      <c r="I34" s="154" t="n">
+      <c r="I36" s="154" t="n">
         <v>6450.779034560001</v>
       </c>
-      <c r="J34" s="154" t="n">
+      <c r="J36" s="154" t="n">
         <v>4424.29496489</v>
       </c>
-      <c r="K34" s="154" t="n">
+      <c r="K36" s="154" t="n">
         <v>6037.45991081</v>
       </c>
-      <c r="L34" s="154" t="n">
+      <c r="L36" s="154" t="n">
         <v>5122.95948654</v>
       </c>
-      <c r="M34" s="154" t="n">
+      <c r="M36" s="154" t="n">
         <v>5590.272108560001</v>
       </c>
-      <c r="N34" s="154" t="n">
+      <c r="N36" s="154" t="n">
         <v>6814.98544784</v>
       </c>
-      <c r="O34" s="154" t="n">
+      <c r="O36" s="154" t="n">
         <v>9761.395305739999</v>
       </c>
-      <c r="P34" s="154" t="n">
+      <c r="P36" s="154" t="n">
         <v>11954.2565479</v>
       </c>
-      <c r="Q34" s="154" t="n">
+      <c r="Q36" s="154" t="n">
         <v>12870.03210067</v>
       </c>
-      <c r="R34" s="154" t="n">
+      <c r="R36" s="154" t="n">
         <v>10792.54713405</v>
       </c>
-      <c r="S34" s="154" t="n">
+      <c r="S36" s="154" t="n">
         <v>12248.72026207</v>
       </c>
-      <c r="T34" s="152" t="inlineStr">
+      <c r="T36" s="152" t="inlineStr">
         <is>
           <t>2014-2025 (2026 to August, not shown)</t>
         </is>
       </c>
-      <c r="U34" s="152" t="inlineStr">
+      <c r="U36" s="152" t="inlineStr">
         <is>
           <t>South African Revenue Service, trade statistics by tariff line</t>
         </is>
       </c>
-      <c r="V34" s="152" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="152" t="inlineStr">
-        <is>
-          <t>Imports, petrol</t>
-        </is>
-      </c>
-      <c r="B35" s="153" t="inlineStr">
-        <is>
-          <t>million L/year</t>
-        </is>
-      </c>
-      <c r="C35" s="153" t="inlineStr">
-        <is>
-          <t>Source observation</t>
-        </is>
-      </c>
-      <c r="D35" s="154" t="n"/>
-      <c r="E35" s="152" t="inlineStr">
-        <is>
-          <t>Complete years reported in litres. Before 2014 customs is in kilograms or mixed units and is not used.</t>
-        </is>
-      </c>
-      <c r="F35" s="154" t="n"/>
-      <c r="G35" s="154" t="n"/>
-      <c r="H35" s="154" t="n">
-        <v>1150.19482187</v>
-      </c>
-      <c r="I35" s="154" t="n">
-        <v>1869.64520821</v>
-      </c>
-      <c r="J35" s="154" t="n">
-        <v>1395.6384761</v>
-      </c>
-      <c r="K35" s="154" t="n">
-        <v>2114.15648464</v>
-      </c>
-      <c r="L35" s="154" t="n">
-        <v>1829.7712635</v>
-      </c>
-      <c r="M35" s="154" t="n">
-        <v>1477.38584109</v>
-      </c>
-      <c r="N35" s="154" t="n">
-        <v>1719.67306448</v>
-      </c>
-      <c r="O35" s="154" t="n">
-        <v>4008.61276378</v>
-      </c>
-      <c r="P35" s="154" t="n">
-        <v>5455.26181472</v>
-      </c>
-      <c r="Q35" s="154" t="n">
-        <v>4482.77476038</v>
-      </c>
-      <c r="R35" s="154" t="n">
-        <v>4000.85443345</v>
-      </c>
-      <c r="S35" s="154" t="n">
-        <v>4453.47117815</v>
-      </c>
-      <c r="T35" s="152" t="inlineStr">
-        <is>
-          <t>2014-2025 (2026 to August, not shown)</t>
-        </is>
-      </c>
-      <c r="U35" s="152" t="inlineStr">
-        <is>
-          <t>South African Revenue Service, trade statistics by tariff line</t>
-        </is>
-      </c>
-      <c r="V35" s="152" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="156" t="inlineStr">
-        <is>
-          <t>Imports, diesel and petrol</t>
-        </is>
-      </c>
-      <c r="B36" s="157" t="inlineStr">
-        <is>
-          <t>million L/year</t>
-        </is>
-      </c>
-      <c r="C36" s="157" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D36" s="158" t="n"/>
-      <c r="E36" s="156" t="inlineStr">
-        <is>
-          <t>Sum of the two rows above.</t>
-        </is>
-      </c>
-      <c r="F36" s="158">
-        <f>IF(COUNT(F34,F35)&lt;2,"",F34+F35)</f>
-        <v/>
-      </c>
-      <c r="G36" s="158">
-        <f>IF(COUNT(G34,G35)&lt;2,"",G34+G35)</f>
-        <v/>
-      </c>
-      <c r="H36" s="158">
-        <f>IF(COUNT(H34,H35)&lt;2,"",H34+H35)</f>
-        <v/>
-      </c>
-      <c r="I36" s="158">
-        <f>IF(COUNT(I34,I35)&lt;2,"",I34+I35)</f>
-        <v/>
-      </c>
-      <c r="J36" s="158">
-        <f>IF(COUNT(J34,J35)&lt;2,"",J34+J35)</f>
-        <v/>
-      </c>
-      <c r="K36" s="158">
-        <f>IF(COUNT(K34,K35)&lt;2,"",K34+K35)</f>
-        <v/>
-      </c>
-      <c r="L36" s="158">
-        <f>IF(COUNT(L34,L35)&lt;2,"",L34+L35)</f>
-        <v/>
-      </c>
-      <c r="M36" s="158">
-        <f>IF(COUNT(M34,M35)&lt;2,"",M34+M35)</f>
-        <v/>
-      </c>
-      <c r="N36" s="158">
-        <f>IF(COUNT(N34,N35)&lt;2,"",N34+N35)</f>
-        <v/>
-      </c>
-      <c r="O36" s="158">
-        <f>IF(COUNT(O34,O35)&lt;2,"",O34+O35)</f>
-        <v/>
-      </c>
-      <c r="P36" s="158">
-        <f>IF(COUNT(P34,P35)&lt;2,"",P34+P35)</f>
-        <v/>
-      </c>
-      <c r="Q36" s="158">
-        <f>IF(COUNT(Q34,Q35)&lt;2,"",Q34+Q35)</f>
-        <v/>
-      </c>
-      <c r="R36" s="158">
-        <f>IF(COUNT(R34,R35)&lt;2,"",R34+R35)</f>
-        <v/>
-      </c>
-      <c r="S36" s="158">
-        <f>IF(COUNT(S34,S35)&lt;2,"",S34+S35)</f>
-        <v/>
-      </c>
-      <c r="T36" s="156" t="inlineStr"/>
-      <c r="U36" s="156" t="inlineStr"/>
-      <c r="V36" s="156" t="inlineStr"/>
+      <c r="V36" s="152" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="152" t="inlineStr">
         <is>
-          <t>Exports, diesel</t>
+          <t>Imports, petrol</t>
         </is>
       </c>
       <c r="B37" s="153" t="inlineStr">
@@ -39330,293 +39264,283 @@
       <c r="F37" s="154" t="n"/>
       <c r="G37" s="154" t="n"/>
       <c r="H37" s="154" t="n">
+        <v>1150.19482187</v>
+      </c>
+      <c r="I37" s="154" t="n">
+        <v>1869.64520821</v>
+      </c>
+      <c r="J37" s="154" t="n">
+        <v>1395.6384761</v>
+      </c>
+      <c r="K37" s="154" t="n">
+        <v>2114.15648464</v>
+      </c>
+      <c r="L37" s="154" t="n">
+        <v>1829.7712635</v>
+      </c>
+      <c r="M37" s="154" t="n">
+        <v>1477.38584109</v>
+      </c>
+      <c r="N37" s="154" t="n">
+        <v>1719.67306448</v>
+      </c>
+      <c r="O37" s="154" t="n">
+        <v>4008.61276378</v>
+      </c>
+      <c r="P37" s="154" t="n">
+        <v>5455.26181472</v>
+      </c>
+      <c r="Q37" s="154" t="n">
+        <v>4482.77476038</v>
+      </c>
+      <c r="R37" s="154" t="n">
+        <v>4000.85443345</v>
+      </c>
+      <c r="S37" s="154" t="n">
+        <v>4453.47117815</v>
+      </c>
+      <c r="T37" s="152" t="inlineStr">
+        <is>
+          <t>2014-2025 (2026 to August, not shown)</t>
+        </is>
+      </c>
+      <c r="U37" s="152" t="inlineStr">
+        <is>
+          <t>South African Revenue Service, trade statistics by tariff line</t>
+        </is>
+      </c>
+      <c r="V37" s="152" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="156" t="inlineStr">
+        <is>
+          <t>Imports, diesel and petrol</t>
+        </is>
+      </c>
+      <c r="B38" s="157" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C38" s="157" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D38" s="158" t="n"/>
+      <c r="E38" s="156" t="inlineStr">
+        <is>
+          <t>Sum of the two rows above.</t>
+        </is>
+      </c>
+      <c r="F38" s="158">
+        <f>IF(COUNT(F36,F37)&lt;2,"",F36+F37)</f>
+        <v/>
+      </c>
+      <c r="G38" s="158">
+        <f>IF(COUNT(G36,G37)&lt;2,"",G36+G37)</f>
+        <v/>
+      </c>
+      <c r="H38" s="158">
+        <f>IF(COUNT(H36,H37)&lt;2,"",H36+H37)</f>
+        <v/>
+      </c>
+      <c r="I38" s="158">
+        <f>IF(COUNT(I36,I37)&lt;2,"",I36+I37)</f>
+        <v/>
+      </c>
+      <c r="J38" s="158">
+        <f>IF(COUNT(J36,J37)&lt;2,"",J36+J37)</f>
+        <v/>
+      </c>
+      <c r="K38" s="158">
+        <f>IF(COUNT(K36,K37)&lt;2,"",K36+K37)</f>
+        <v/>
+      </c>
+      <c r="L38" s="158">
+        <f>IF(COUNT(L36,L37)&lt;2,"",L36+L37)</f>
+        <v/>
+      </c>
+      <c r="M38" s="158">
+        <f>IF(COUNT(M36,M37)&lt;2,"",M36+M37)</f>
+        <v/>
+      </c>
+      <c r="N38" s="158">
+        <f>IF(COUNT(N36,N37)&lt;2,"",N36+N37)</f>
+        <v/>
+      </c>
+      <c r="O38" s="158">
+        <f>IF(COUNT(O36,O37)&lt;2,"",O36+O37)</f>
+        <v/>
+      </c>
+      <c r="P38" s="158">
+        <f>IF(COUNT(P36,P37)&lt;2,"",P36+P37)</f>
+        <v/>
+      </c>
+      <c r="Q38" s="158">
+        <f>IF(COUNT(Q36,Q37)&lt;2,"",Q36+Q37)</f>
+        <v/>
+      </c>
+      <c r="R38" s="158">
+        <f>IF(COUNT(R36,R37)&lt;2,"",R36+R37)</f>
+        <v/>
+      </c>
+      <c r="S38" s="158">
+        <f>IF(COUNT(S36,S37)&lt;2,"",S36+S37)</f>
+        <v/>
+      </c>
+      <c r="T38" s="156" t="inlineStr"/>
+      <c r="U38" s="156" t="inlineStr"/>
+      <c r="V38" s="156" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="152" t="inlineStr">
+        <is>
+          <t>Exports, diesel</t>
+        </is>
+      </c>
+      <c r="B39" s="153" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C39" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D39" s="154" t="n"/>
+      <c r="E39" s="152" t="inlineStr">
+        <is>
+          <t>Complete years reported in litres. Before 2014 customs is in kilograms or mixed units and is not used.</t>
+        </is>
+      </c>
+      <c r="F39" s="154" t="n"/>
+      <c r="G39" s="154" t="n"/>
+      <c r="H39" s="154" t="n">
         <v>1493.76262809</v>
       </c>
-      <c r="I37" s="154" t="n">
+      <c r="I39" s="154" t="n">
         <v>1612.85503972</v>
       </c>
-      <c r="J37" s="154" t="n">
+      <c r="J39" s="154" t="n">
         <v>1885.60542996</v>
       </c>
-      <c r="K37" s="154" t="n">
+      <c r="K39" s="154" t="n">
         <v>1782.67408028</v>
       </c>
-      <c r="L37" s="154" t="n">
+      <c r="L39" s="154" t="n">
         <v>1582.07010837</v>
       </c>
-      <c r="M37" s="154" t="n">
+      <c r="M39" s="154" t="n">
         <v>1741.3773122</v>
       </c>
-      <c r="N37" s="154" t="n">
+      <c r="N39" s="154" t="n">
         <v>913.81452025</v>
       </c>
-      <c r="O37" s="154" t="n">
+      <c r="O39" s="154" t="n">
         <v>893.4881057699999</v>
       </c>
-      <c r="P37" s="154" t="n">
+      <c r="P39" s="154" t="n">
         <v>889.1990678200001</v>
       </c>
-      <c r="Q37" s="154" t="n">
+      <c r="Q39" s="154" t="n">
         <v>889.44590792</v>
       </c>
-      <c r="R37" s="154" t="n">
+      <c r="R39" s="154" t="n">
         <v>795.83467852</v>
       </c>
-      <c r="S37" s="154" t="n">
+      <c r="S39" s="154" t="n">
         <v>746.70021007</v>
       </c>
-      <c r="T37" s="152" t="inlineStr">
+      <c r="T39" s="152" t="inlineStr">
         <is>
           <t>2014-2025 (2026 to August, not shown)</t>
         </is>
       </c>
-      <c r="U37" s="152" t="inlineStr">
+      <c r="U39" s="152" t="inlineStr">
         <is>
           <t>South African Revenue Service, trade statistics by tariff line</t>
         </is>
       </c>
-      <c r="V37" s="152" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="152" t="inlineStr">
+      <c r="V39" s="152" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="152" t="inlineStr">
         <is>
           <t>Exports, petrol</t>
         </is>
       </c>
-      <c r="B38" s="153" t="inlineStr">
+      <c r="B40" s="153" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C38" s="153" t="inlineStr">
+      <c r="C40" s="153" t="inlineStr">
         <is>
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D38" s="154" t="n"/>
-      <c r="E38" s="152" t="inlineStr">
+      <c r="D40" s="154" t="n"/>
+      <c r="E40" s="152" t="inlineStr">
         <is>
           <t>Complete years reported in litres. Before 2014 customs is in kilograms or mixed units and is not used.</t>
         </is>
       </c>
-      <c r="F38" s="154" t="n"/>
-      <c r="G38" s="154" t="n"/>
-      <c r="H38" s="154" t="n">
+      <c r="F40" s="154" t="n"/>
+      <c r="G40" s="154" t="n"/>
+      <c r="H40" s="154" t="n">
         <v>989.515894</v>
       </c>
-      <c r="I38" s="154" t="n">
+      <c r="I40" s="154" t="n">
         <v>1085.67044231</v>
       </c>
-      <c r="J38" s="154" t="n">
+      <c r="J40" s="154" t="n">
         <v>1157.32879425</v>
       </c>
-      <c r="K38" s="154" t="n">
+      <c r="K40" s="154" t="n">
         <v>1075.88615968</v>
       </c>
-      <c r="L38" s="154" t="n">
+      <c r="L40" s="154" t="n">
         <v>1135.0502547</v>
       </c>
-      <c r="M38" s="154" t="n">
+      <c r="M40" s="154" t="n">
         <v>1174.70177789</v>
       </c>
-      <c r="N38" s="154" t="n">
+      <c r="N40" s="154" t="n">
         <v>1154.77907118</v>
       </c>
-      <c r="O38" s="154" t="n">
+      <c r="O40" s="154" t="n">
         <v>1052.49514457</v>
       </c>
-      <c r="P38" s="154" t="n">
+      <c r="P40" s="154" t="n">
         <v>854.61371378</v>
       </c>
-      <c r="Q38" s="154" t="n">
+      <c r="Q40" s="154" t="n">
         <v>994.01955902</v>
       </c>
-      <c r="R38" s="154" t="n">
+      <c r="R40" s="154" t="n">
         <v>919.74501589</v>
       </c>
-      <c r="S38" s="154" t="n">
+      <c r="S40" s="154" t="n">
         <v>801.762466</v>
       </c>
-      <c r="T38" s="152" t="inlineStr">
+      <c r="T40" s="152" t="inlineStr">
         <is>
           <t>2014-2025 (2026 to August, not shown)</t>
         </is>
       </c>
-      <c r="U38" s="152" t="inlineStr">
+      <c r="U40" s="152" t="inlineStr">
         <is>
           <t>South African Revenue Service, trade statistics by tariff line</t>
         </is>
       </c>
-      <c r="V38" s="152" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="156" t="inlineStr">
-        <is>
-          <t>Exports, diesel and petrol</t>
-        </is>
-      </c>
-      <c r="B39" s="157" t="inlineStr">
-        <is>
-          <t>million L/year</t>
-        </is>
-      </c>
-      <c r="C39" s="157" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D39" s="158" t="n"/>
-      <c r="E39" s="156" t="inlineStr">
-        <is>
-          <t>Sum of the two rows above.</t>
-        </is>
-      </c>
-      <c r="F39" s="158">
-        <f>IF(COUNT(F37,F38)&lt;2,"",F37+F38)</f>
-        <v/>
-      </c>
-      <c r="G39" s="158">
-        <f>IF(COUNT(G37,G38)&lt;2,"",G37+G38)</f>
-        <v/>
-      </c>
-      <c r="H39" s="158">
-        <f>IF(COUNT(H37,H38)&lt;2,"",H37+H38)</f>
-        <v/>
-      </c>
-      <c r="I39" s="158">
-        <f>IF(COUNT(I37,I38)&lt;2,"",I37+I38)</f>
-        <v/>
-      </c>
-      <c r="J39" s="158">
-        <f>IF(COUNT(J37,J38)&lt;2,"",J37+J38)</f>
-        <v/>
-      </c>
-      <c r="K39" s="158">
-        <f>IF(COUNT(K37,K38)&lt;2,"",K37+K38)</f>
-        <v/>
-      </c>
-      <c r="L39" s="158">
-        <f>IF(COUNT(L37,L38)&lt;2,"",L37+L38)</f>
-        <v/>
-      </c>
-      <c r="M39" s="158">
-        <f>IF(COUNT(M37,M38)&lt;2,"",M37+M38)</f>
-        <v/>
-      </c>
-      <c r="N39" s="158">
-        <f>IF(COUNT(N37,N38)&lt;2,"",N37+N38)</f>
-        <v/>
-      </c>
-      <c r="O39" s="158">
-        <f>IF(COUNT(O37,O38)&lt;2,"",O37+O38)</f>
-        <v/>
-      </c>
-      <c r="P39" s="158">
-        <f>IF(COUNT(P37,P38)&lt;2,"",P37+P38)</f>
-        <v/>
-      </c>
-      <c r="Q39" s="158">
-        <f>IF(COUNT(Q37,Q38)&lt;2,"",Q37+Q38)</f>
-        <v/>
-      </c>
-      <c r="R39" s="158">
-        <f>IF(COUNT(R37,R38)&lt;2,"",R37+R38)</f>
-        <v/>
-      </c>
-      <c r="S39" s="158">
-        <f>IF(COUNT(S37,S38)&lt;2,"",S37+S38)</f>
-        <v/>
-      </c>
-      <c r="T39" s="156" t="inlineStr"/>
-      <c r="U39" s="156" t="inlineStr"/>
-      <c r="V39" s="156" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="156" t="inlineStr">
-        <is>
-          <t>Net imports, diesel</t>
-        </is>
-      </c>
-      <c r="B40" s="157" t="inlineStr">
-        <is>
-          <t>million L/year</t>
-        </is>
-      </c>
-      <c r="C40" s="157" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D40" s="158" t="n"/>
-      <c r="E40" s="156" t="inlineStr">
-        <is>
-          <t>Imports less exports.</t>
-        </is>
-      </c>
-      <c r="F40" s="158">
-        <f>IF(COUNT(F34,F37)&lt;2,"",F34-F37)</f>
-        <v/>
-      </c>
-      <c r="G40" s="158">
-        <f>IF(COUNT(G34,G37)&lt;2,"",G34-G37)</f>
-        <v/>
-      </c>
-      <c r="H40" s="158">
-        <f>IF(COUNT(H34,H37)&lt;2,"",H34-H37)</f>
-        <v/>
-      </c>
-      <c r="I40" s="158">
-        <f>IF(COUNT(I34,I37)&lt;2,"",I34-I37)</f>
-        <v/>
-      </c>
-      <c r="J40" s="158">
-        <f>IF(COUNT(J34,J37)&lt;2,"",J34-J37)</f>
-        <v/>
-      </c>
-      <c r="K40" s="158">
-        <f>IF(COUNT(K34,K37)&lt;2,"",K34-K37)</f>
-        <v/>
-      </c>
-      <c r="L40" s="158">
-        <f>IF(COUNT(L34,L37)&lt;2,"",L34-L37)</f>
-        <v/>
-      </c>
-      <c r="M40" s="158">
-        <f>IF(COUNT(M34,M37)&lt;2,"",M34-M37)</f>
-        <v/>
-      </c>
-      <c r="N40" s="158">
-        <f>IF(COUNT(N34,N37)&lt;2,"",N34-N37)</f>
-        <v/>
-      </c>
-      <c r="O40" s="158">
-        <f>IF(COUNT(O34,O37)&lt;2,"",O34-O37)</f>
-        <v/>
-      </c>
-      <c r="P40" s="158">
-        <f>IF(COUNT(P34,P37)&lt;2,"",P34-P37)</f>
-        <v/>
-      </c>
-      <c r="Q40" s="158">
-        <f>IF(COUNT(Q34,Q37)&lt;2,"",Q34-Q37)</f>
-        <v/>
-      </c>
-      <c r="R40" s="158">
-        <f>IF(COUNT(R34,R37)&lt;2,"",R34-R37)</f>
-        <v/>
-      </c>
-      <c r="S40" s="158">
-        <f>IF(COUNT(S34,S37)&lt;2,"",S34-S37)</f>
-        <v/>
-      </c>
-      <c r="T40" s="156" t="inlineStr"/>
-      <c r="U40" s="156" t="inlineStr"/>
-      <c r="V40" s="156" t="inlineStr"/>
+      <c r="V40" s="152" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="156" t="inlineStr">
         <is>
-          <t>Net imports, petrol</t>
+          <t>Exports, diesel and petrol</t>
         </is>
       </c>
       <c r="B41" s="157" t="inlineStr">
@@ -39632,63 +39556,63 @@
       <c r="D41" s="158" t="n"/>
       <c r="E41" s="156" t="inlineStr">
         <is>
-          <t>Imports less exports.</t>
+          <t>Sum of the two rows above.</t>
         </is>
       </c>
       <c r="F41" s="158">
-        <f>IF(COUNT(F35,F38)&lt;2,"",F35-F38)</f>
+        <f>IF(COUNT(F39,F40)&lt;2,"",F39+F40)</f>
         <v/>
       </c>
       <c r="G41" s="158">
-        <f>IF(COUNT(G35,G38)&lt;2,"",G35-G38)</f>
+        <f>IF(COUNT(G39,G40)&lt;2,"",G39+G40)</f>
         <v/>
       </c>
       <c r="H41" s="158">
-        <f>IF(COUNT(H35,H38)&lt;2,"",H35-H38)</f>
+        <f>IF(COUNT(H39,H40)&lt;2,"",H39+H40)</f>
         <v/>
       </c>
       <c r="I41" s="158">
-        <f>IF(COUNT(I35,I38)&lt;2,"",I35-I38)</f>
+        <f>IF(COUNT(I39,I40)&lt;2,"",I39+I40)</f>
         <v/>
       </c>
       <c r="J41" s="158">
-        <f>IF(COUNT(J35,J38)&lt;2,"",J35-J38)</f>
+        <f>IF(COUNT(J39,J40)&lt;2,"",J39+J40)</f>
         <v/>
       </c>
       <c r="K41" s="158">
-        <f>IF(COUNT(K35,K38)&lt;2,"",K35-K38)</f>
+        <f>IF(COUNT(K39,K40)&lt;2,"",K39+K40)</f>
         <v/>
       </c>
       <c r="L41" s="158">
-        <f>IF(COUNT(L35,L38)&lt;2,"",L35-L38)</f>
+        <f>IF(COUNT(L39,L40)&lt;2,"",L39+L40)</f>
         <v/>
       </c>
       <c r="M41" s="158">
-        <f>IF(COUNT(M35,M38)&lt;2,"",M35-M38)</f>
+        <f>IF(COUNT(M39,M40)&lt;2,"",M39+M40)</f>
         <v/>
       </c>
       <c r="N41" s="158">
-        <f>IF(COUNT(N35,N38)&lt;2,"",N35-N38)</f>
+        <f>IF(COUNT(N39,N40)&lt;2,"",N39+N40)</f>
         <v/>
       </c>
       <c r="O41" s="158">
-        <f>IF(COUNT(O35,O38)&lt;2,"",O35-O38)</f>
+        <f>IF(COUNT(O39,O40)&lt;2,"",O39+O40)</f>
         <v/>
       </c>
       <c r="P41" s="158">
-        <f>IF(COUNT(P35,P38)&lt;2,"",P35-P38)</f>
+        <f>IF(COUNT(P39,P40)&lt;2,"",P39+P40)</f>
         <v/>
       </c>
       <c r="Q41" s="158">
-        <f>IF(COUNT(Q35,Q38)&lt;2,"",Q35-Q38)</f>
+        <f>IF(COUNT(Q39,Q40)&lt;2,"",Q39+Q40)</f>
         <v/>
       </c>
       <c r="R41" s="158">
-        <f>IF(COUNT(R35,R38)&lt;2,"",R35-R38)</f>
+        <f>IF(COUNT(R39,R40)&lt;2,"",R39+R40)</f>
         <v/>
       </c>
       <c r="S41" s="158">
-        <f>IF(COUNT(S35,S38)&lt;2,"",S35-S38)</f>
+        <f>IF(COUNT(S39,S40)&lt;2,"",S39+S40)</f>
         <v/>
       </c>
       <c r="T41" s="156" t="inlineStr"/>
@@ -39698,7 +39622,7 @@
     <row r="42">
       <c r="A42" s="156" t="inlineStr">
         <is>
-          <t>Net imports, diesel and petrol</t>
+          <t>Net imports, diesel</t>
         </is>
       </c>
       <c r="B42" s="157" t="inlineStr">
@@ -39778,157 +39702,173 @@
       <c r="V42" s="156" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="159" t="inlineStr">
-        <is>
-          <t>FIASA imports, diesel</t>
-        </is>
-      </c>
-      <c r="B43" s="160" t="inlineStr">
+      <c r="A43" s="156" t="inlineStr">
+        <is>
+          <t>Net imports, petrol</t>
+        </is>
+      </c>
+      <c r="B43" s="157" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C43" s="160" t="inlineStr">
-        <is>
-          <t>Comparison only</t>
-        </is>
-      </c>
-      <c r="D43" s="161" t="n"/>
-      <c r="E43" s="159" t="inlineStr">
-        <is>
-          <t>FIASA annual report, latest edition for each year. Not used in the balance.</t>
-        </is>
-      </c>
-      <c r="F43" s="161" t="n">
-        <v>3247</v>
-      </c>
-      <c r="G43" s="161" t="n">
-        <v>4254</v>
-      </c>
-      <c r="H43" s="161" t="n">
-        <v>4997</v>
-      </c>
-      <c r="I43" s="161" t="n">
-        <v>6451</v>
-      </c>
-      <c r="J43" s="161" t="n">
-        <v>4424</v>
-      </c>
-      <c r="K43" s="161" t="n">
-        <v>6036</v>
-      </c>
-      <c r="L43" s="161" t="n">
-        <v>6105</v>
-      </c>
-      <c r="M43" s="161" t="n">
-        <v>5858</v>
-      </c>
-      <c r="N43" s="161" t="n">
-        <v>6815</v>
-      </c>
-      <c r="O43" s="161" t="n">
-        <v>9567</v>
-      </c>
-      <c r="P43" s="161" t="n">
-        <v>11914</v>
-      </c>
-      <c r="Q43" s="161" t="n">
-        <v>12794</v>
-      </c>
-      <c r="R43" s="161" t="n">
-        <v>14793</v>
-      </c>
-      <c r="S43" s="161" t="n">
-        <v>12249</v>
-      </c>
-      <c r="T43" s="159" t="inlineStr">
-        <is>
-          <t>2024 diesel imports is a suspected misprint (14,793 for 10,793)</t>
-        </is>
-      </c>
-      <c r="U43" s="159" t="inlineStr">
-        <is>
-          <t>Fuels Industry Association of South Africa, annual reports</t>
-        </is>
-      </c>
-      <c r="V43" s="159" t="inlineStr"/>
+      <c r="C43" s="157" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D43" s="158" t="n"/>
+      <c r="E43" s="156" t="inlineStr">
+        <is>
+          <t>Imports less exports.</t>
+        </is>
+      </c>
+      <c r="F43" s="158">
+        <f>IF(COUNT(F37,F40)&lt;2,"",F37-F40)</f>
+        <v/>
+      </c>
+      <c r="G43" s="158">
+        <f>IF(COUNT(G37,G40)&lt;2,"",G37-G40)</f>
+        <v/>
+      </c>
+      <c r="H43" s="158">
+        <f>IF(COUNT(H37,H40)&lt;2,"",H37-H40)</f>
+        <v/>
+      </c>
+      <c r="I43" s="158">
+        <f>IF(COUNT(I37,I40)&lt;2,"",I37-I40)</f>
+        <v/>
+      </c>
+      <c r="J43" s="158">
+        <f>IF(COUNT(J37,J40)&lt;2,"",J37-J40)</f>
+        <v/>
+      </c>
+      <c r="K43" s="158">
+        <f>IF(COUNT(K37,K40)&lt;2,"",K37-K40)</f>
+        <v/>
+      </c>
+      <c r="L43" s="158">
+        <f>IF(COUNT(L37,L40)&lt;2,"",L37-L40)</f>
+        <v/>
+      </c>
+      <c r="M43" s="158">
+        <f>IF(COUNT(M37,M40)&lt;2,"",M37-M40)</f>
+        <v/>
+      </c>
+      <c r="N43" s="158">
+        <f>IF(COUNT(N37,N40)&lt;2,"",N37-N40)</f>
+        <v/>
+      </c>
+      <c r="O43" s="158">
+        <f>IF(COUNT(O37,O40)&lt;2,"",O37-O40)</f>
+        <v/>
+      </c>
+      <c r="P43" s="158">
+        <f>IF(COUNT(P37,P40)&lt;2,"",P37-P40)</f>
+        <v/>
+      </c>
+      <c r="Q43" s="158">
+        <f>IF(COUNT(Q37,Q40)&lt;2,"",Q37-Q40)</f>
+        <v/>
+      </c>
+      <c r="R43" s="158">
+        <f>IF(COUNT(R37,R40)&lt;2,"",R37-R40)</f>
+        <v/>
+      </c>
+      <c r="S43" s="158">
+        <f>IF(COUNT(S37,S40)&lt;2,"",S37-S40)</f>
+        <v/>
+      </c>
+      <c r="T43" s="156" t="inlineStr"/>
+      <c r="U43" s="156" t="inlineStr"/>
+      <c r="V43" s="156" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="159" t="inlineStr">
-        <is>
-          <t>FIASA imports, petrol</t>
-        </is>
-      </c>
-      <c r="B44" s="160" t="inlineStr">
+      <c r="A44" s="156" t="inlineStr">
+        <is>
+          <t>Net imports, diesel and petrol</t>
+        </is>
+      </c>
+      <c r="B44" s="157" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C44" s="160" t="inlineStr">
-        <is>
-          <t>Comparison only</t>
-        </is>
-      </c>
-      <c r="D44" s="161" t="n"/>
-      <c r="E44" s="159" t="inlineStr">
-        <is>
-          <t>FIASA annual report, latest edition for each year. Not used in the balance.</t>
-        </is>
-      </c>
-      <c r="F44" s="161" t="n">
-        <v>1827</v>
-      </c>
-      <c r="G44" s="161" t="n">
-        <v>1509</v>
-      </c>
-      <c r="H44" s="161" t="n">
-        <v>1150</v>
-      </c>
-      <c r="I44" s="161" t="n">
-        <v>1870</v>
-      </c>
-      <c r="J44" s="161" t="n">
-        <v>1396</v>
-      </c>
-      <c r="K44" s="161" t="n">
-        <v>2114</v>
-      </c>
-      <c r="L44" s="161" t="n">
-        <v>2195</v>
-      </c>
-      <c r="M44" s="161" t="n">
-        <v>1477</v>
-      </c>
-      <c r="N44" s="161" t="n">
-        <v>1720</v>
-      </c>
-      <c r="O44" s="161" t="n">
-        <v>4009</v>
-      </c>
-      <c r="P44" s="161" t="n">
-        <v>5455</v>
-      </c>
-      <c r="Q44" s="161" t="n">
-        <v>4483</v>
-      </c>
-      <c r="R44" s="161" t="n">
-        <v>4000</v>
-      </c>
-      <c r="S44" s="161" t="n">
-        <v>4453</v>
-      </c>
-      <c r="T44" s="159" t="inlineStr"/>
-      <c r="U44" s="159" t="inlineStr">
-        <is>
-          <t>Fuels Industry Association of South Africa, annual reports</t>
-        </is>
-      </c>
-      <c r="V44" s="159" t="inlineStr"/>
+      <c r="C44" s="157" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D44" s="158" t="n"/>
+      <c r="E44" s="156" t="inlineStr">
+        <is>
+          <t>Imports less exports.</t>
+        </is>
+      </c>
+      <c r="F44" s="158">
+        <f>IF(COUNT(F38,F41)&lt;2,"",F38-F41)</f>
+        <v/>
+      </c>
+      <c r="G44" s="158">
+        <f>IF(COUNT(G38,G41)&lt;2,"",G38-G41)</f>
+        <v/>
+      </c>
+      <c r="H44" s="158">
+        <f>IF(COUNT(H38,H41)&lt;2,"",H38-H41)</f>
+        <v/>
+      </c>
+      <c r="I44" s="158">
+        <f>IF(COUNT(I38,I41)&lt;2,"",I38-I41)</f>
+        <v/>
+      </c>
+      <c r="J44" s="158">
+        <f>IF(COUNT(J38,J41)&lt;2,"",J38-J41)</f>
+        <v/>
+      </c>
+      <c r="K44" s="158">
+        <f>IF(COUNT(K38,K41)&lt;2,"",K38-K41)</f>
+        <v/>
+      </c>
+      <c r="L44" s="158">
+        <f>IF(COUNT(L38,L41)&lt;2,"",L38-L41)</f>
+        <v/>
+      </c>
+      <c r="M44" s="158">
+        <f>IF(COUNT(M38,M41)&lt;2,"",M38-M41)</f>
+        <v/>
+      </c>
+      <c r="N44" s="158">
+        <f>IF(COUNT(N38,N41)&lt;2,"",N38-N41)</f>
+        <v/>
+      </c>
+      <c r="O44" s="158">
+        <f>IF(COUNT(O38,O41)&lt;2,"",O38-O41)</f>
+        <v/>
+      </c>
+      <c r="P44" s="158">
+        <f>IF(COUNT(P38,P41)&lt;2,"",P38-P41)</f>
+        <v/>
+      </c>
+      <c r="Q44" s="158">
+        <f>IF(COUNT(Q38,Q41)&lt;2,"",Q38-Q41)</f>
+        <v/>
+      </c>
+      <c r="R44" s="158">
+        <f>IF(COUNT(R38,R41)&lt;2,"",R38-R41)</f>
+        <v/>
+      </c>
+      <c r="S44" s="158">
+        <f>IF(COUNT(S38,S41)&lt;2,"",S38-S41)</f>
+        <v/>
+      </c>
+      <c r="T44" s="156" t="inlineStr"/>
+      <c r="U44" s="156" t="inlineStr"/>
+      <c r="V44" s="156" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="159" t="inlineStr">
         <is>
-          <t>FIASA exports, diesel</t>
+          <t>FIASA imports, diesel</t>
         </is>
       </c>
       <c r="B45" s="160" t="inlineStr">
@@ -39948,48 +39888,52 @@
         </is>
       </c>
       <c r="F45" s="161" t="n">
-        <v>929</v>
+        <v>3247</v>
       </c>
       <c r="G45" s="161" t="n">
-        <v>1620</v>
+        <v>4254</v>
       </c>
       <c r="H45" s="161" t="n">
-        <v>1493</v>
+        <v>4997</v>
       </c>
       <c r="I45" s="161" t="n">
-        <v>1625</v>
+        <v>6451</v>
       </c>
       <c r="J45" s="161" t="n">
-        <v>1887</v>
+        <v>4424</v>
       </c>
       <c r="K45" s="161" t="n">
-        <v>1784</v>
+        <v>6036</v>
       </c>
       <c r="L45" s="161" t="n">
-        <v>1838</v>
+        <v>6105</v>
       </c>
       <c r="M45" s="161" t="n">
-        <v>1786</v>
+        <v>5858</v>
       </c>
       <c r="N45" s="161" t="n">
-        <v>914</v>
+        <v>6815</v>
       </c>
       <c r="O45" s="161" t="n">
-        <v>895</v>
+        <v>9567</v>
       </c>
       <c r="P45" s="161" t="n">
-        <v>698</v>
+        <v>11914</v>
       </c>
       <c r="Q45" s="161" t="n">
-        <v>935</v>
+        <v>12794</v>
       </c>
       <c r="R45" s="161" t="n">
-        <v>821</v>
+        <v>14793</v>
       </c>
       <c r="S45" s="161" t="n">
-        <v>748</v>
-      </c>
-      <c r="T45" s="159" t="inlineStr"/>
+        <v>12249</v>
+      </c>
+      <c r="T45" s="159" t="inlineStr">
+        <is>
+          <t>2024 diesel imports is a suspected misprint (14,793 for 10,793)</t>
+        </is>
+      </c>
       <c r="U45" s="159" t="inlineStr">
         <is>
           <t>Fuels Industry Association of South Africa, annual reports</t>
@@ -40000,7 +39944,7 @@
     <row r="46">
       <c r="A46" s="159" t="inlineStr">
         <is>
-          <t>FIASA exports, petrol</t>
+          <t>FIASA imports, petrol</t>
         </is>
       </c>
       <c r="B46" s="160" t="inlineStr">
@@ -40020,46 +39964,46 @@
         </is>
       </c>
       <c r="F46" s="161" t="n">
-        <v>444</v>
+        <v>1827</v>
       </c>
       <c r="G46" s="161" t="n">
-        <v>956</v>
+        <v>1509</v>
       </c>
       <c r="H46" s="161" t="n">
-        <v>989</v>
+        <v>1150</v>
       </c>
       <c r="I46" s="161" t="n">
-        <v>1086</v>
+        <v>1870</v>
       </c>
       <c r="J46" s="161" t="n">
-        <v>1159</v>
+        <v>1396</v>
       </c>
       <c r="K46" s="161" t="n">
-        <v>1082</v>
+        <v>2114</v>
       </c>
       <c r="L46" s="161" t="n">
-        <v>1321</v>
+        <v>2195</v>
       </c>
       <c r="M46" s="161" t="n">
-        <v>1179</v>
+        <v>1477</v>
       </c>
       <c r="N46" s="161" t="n">
-        <v>1155</v>
+        <v>1720</v>
       </c>
       <c r="O46" s="161" t="n">
-        <v>1054</v>
+        <v>4009</v>
       </c>
       <c r="P46" s="161" t="n">
-        <v>793</v>
+        <v>5455</v>
       </c>
       <c r="Q46" s="161" t="n">
-        <v>1018</v>
+        <v>4483</v>
       </c>
       <c r="R46" s="161" t="n">
-        <v>939</v>
+        <v>4000</v>
       </c>
       <c r="S46" s="161" t="n">
-        <v>802</v>
+        <v>4453</v>
       </c>
       <c r="T46" s="159" t="inlineStr"/>
       <c r="U46" s="159" t="inlineStr">
@@ -40069,307 +40013,331 @@
       </c>
       <c r="V46" s="159" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" s="159" t="inlineStr">
+        <is>
+          <t>FIASA exports, diesel</t>
+        </is>
+      </c>
+      <c r="B47" s="160" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C47" s="160" t="inlineStr">
+        <is>
+          <t>Comparison only</t>
+        </is>
+      </c>
+      <c r="D47" s="161" t="n"/>
+      <c r="E47" s="159" t="inlineStr">
+        <is>
+          <t>FIASA annual report, latest edition for each year. Not used in the balance.</t>
+        </is>
+      </c>
+      <c r="F47" s="161" t="n">
+        <v>929</v>
+      </c>
+      <c r="G47" s="161" t="n">
+        <v>1620</v>
+      </c>
+      <c r="H47" s="161" t="n">
+        <v>1493</v>
+      </c>
+      <c r="I47" s="161" t="n">
+        <v>1625</v>
+      </c>
+      <c r="J47" s="161" t="n">
+        <v>1887</v>
+      </c>
+      <c r="K47" s="161" t="n">
+        <v>1784</v>
+      </c>
+      <c r="L47" s="161" t="n">
+        <v>1838</v>
+      </c>
+      <c r="M47" s="161" t="n">
+        <v>1786</v>
+      </c>
+      <c r="N47" s="161" t="n">
+        <v>914</v>
+      </c>
+      <c r="O47" s="161" t="n">
+        <v>895</v>
+      </c>
+      <c r="P47" s="161" t="n">
+        <v>698</v>
+      </c>
+      <c r="Q47" s="161" t="n">
+        <v>935</v>
+      </c>
+      <c r="R47" s="161" t="n">
+        <v>821</v>
+      </c>
+      <c r="S47" s="161" t="n">
+        <v>748</v>
+      </c>
+      <c r="T47" s="159" t="inlineStr"/>
+      <c r="U47" s="159" t="inlineStr">
+        <is>
+          <t>Fuels Industry Association of South Africa, annual reports</t>
+        </is>
+      </c>
+      <c r="V47" s="159" t="inlineStr"/>
+    </row>
     <row r="48">
-      <c r="A48" s="151" t="inlineStr">
+      <c r="A48" s="159" t="inlineStr">
+        <is>
+          <t>FIASA exports, petrol</t>
+        </is>
+      </c>
+      <c r="B48" s="160" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C48" s="160" t="inlineStr">
+        <is>
+          <t>Comparison only</t>
+        </is>
+      </c>
+      <c r="D48" s="161" t="n"/>
+      <c r="E48" s="159" t="inlineStr">
+        <is>
+          <t>FIASA annual report, latest edition for each year. Not used in the balance.</t>
+        </is>
+      </c>
+      <c r="F48" s="161" t="n">
+        <v>444</v>
+      </c>
+      <c r="G48" s="161" t="n">
+        <v>956</v>
+      </c>
+      <c r="H48" s="161" t="n">
+        <v>989</v>
+      </c>
+      <c r="I48" s="161" t="n">
+        <v>1086</v>
+      </c>
+      <c r="J48" s="161" t="n">
+        <v>1159</v>
+      </c>
+      <c r="K48" s="161" t="n">
+        <v>1082</v>
+      </c>
+      <c r="L48" s="161" t="n">
+        <v>1321</v>
+      </c>
+      <c r="M48" s="161" t="n">
+        <v>1179</v>
+      </c>
+      <c r="N48" s="161" t="n">
+        <v>1155</v>
+      </c>
+      <c r="O48" s="161" t="n">
+        <v>1054</v>
+      </c>
+      <c r="P48" s="161" t="n">
+        <v>793</v>
+      </c>
+      <c r="Q48" s="161" t="n">
+        <v>1018</v>
+      </c>
+      <c r="R48" s="161" t="n">
+        <v>939</v>
+      </c>
+      <c r="S48" s="161" t="n">
+        <v>802</v>
+      </c>
+      <c r="T48" s="159" t="inlineStr"/>
+      <c r="U48" s="159" t="inlineStr">
+        <is>
+          <t>Fuels Industry Association of South Africa, annual reports</t>
+        </is>
+      </c>
+      <c r="V48" s="159" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="151" t="inlineStr">
         <is>
           <t>3. Refinery production</t>
         </is>
       </c>
-      <c r="B48" s="151" t="n"/>
-      <c r="C48" s="151" t="n"/>
-      <c r="D48" s="151" t="n"/>
-      <c r="E48" s="151" t="n"/>
-      <c r="F48" s="151" t="n"/>
-      <c r="G48" s="151" t="n"/>
-      <c r="H48" s="151" t="n"/>
-      <c r="I48" s="151" t="n"/>
-      <c r="J48" s="151" t="n"/>
-      <c r="K48" s="151" t="n"/>
-      <c r="L48" s="151" t="n"/>
-      <c r="M48" s="151" t="n"/>
-      <c r="N48" s="151" t="n"/>
-      <c r="O48" s="151" t="n"/>
-      <c r="P48" s="151" t="n"/>
-      <c r="Q48" s="151" t="n"/>
-      <c r="R48" s="151" t="n"/>
-      <c r="S48" s="151" t="n"/>
-      <c r="T48" s="151" t="n"/>
-      <c r="U48" s="151" t="n"/>
-      <c r="V48" s="151" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="152" t="inlineStr">
+      <c r="B50" s="151" t="n"/>
+      <c r="C50" s="151" t="n"/>
+      <c r="D50" s="151" t="n"/>
+      <c r="E50" s="151" t="n"/>
+      <c r="F50" s="151" t="n"/>
+      <c r="G50" s="151" t="n"/>
+      <c r="H50" s="151" t="n"/>
+      <c r="I50" s="151" t="n"/>
+      <c r="J50" s="151" t="n"/>
+      <c r="K50" s="151" t="n"/>
+      <c r="L50" s="151" t="n"/>
+      <c r="M50" s="151" t="n"/>
+      <c r="N50" s="151" t="n"/>
+      <c r="O50" s="151" t="n"/>
+      <c r="P50" s="151" t="n"/>
+      <c r="Q50" s="151" t="n"/>
+      <c r="R50" s="151" t="n"/>
+      <c r="S50" s="151" t="n"/>
+      <c r="T50" s="151" t="n"/>
+      <c r="U50" s="151" t="n"/>
+      <c r="V50" s="151" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="152" t="inlineStr">
         <is>
           <t>Production reported, petrol</t>
         </is>
       </c>
-      <c r="B49" s="153" t="inlineStr">
+      <c r="B51" s="153" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C49" s="153" t="inlineStr">
+      <c r="C51" s="153" t="inlineStr">
         <is>
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D49" s="154" t="n"/>
-      <c r="E49" s="152" t="inlineStr">
+      <c r="D51" s="154" t="n"/>
+      <c r="E51" s="152" t="inlineStr">
         <is>
           <t>National production line of the department's energy balance. The only production by product.</t>
         </is>
       </c>
-      <c r="F49" s="154" t="n">
+      <c r="F51" s="154" t="n">
         <v>9637.8138</v>
       </c>
-      <c r="G49" s="154" t="n">
+      <c r="G51" s="154" t="n">
         <v>10480.187</v>
       </c>
-      <c r="H49" s="154" t="n">
+      <c r="H51" s="154" t="n">
         <v>10828.16</v>
       </c>
-      <c r="I49" s="154" t="n">
+      <c r="I51" s="154" t="n">
         <v>10457.813</v>
       </c>
-      <c r="J49" s="154" t="n">
+      <c r="J51" s="154" t="n">
         <v>10393.066</v>
       </c>
-      <c r="K49" s="154" t="n">
+      <c r="K51" s="154" t="n">
         <v>9434.440000000001</v>
       </c>
-      <c r="L49" s="154" t="n">
+      <c r="L51" s="154" t="n">
         <v>9974.559999999999</v>
       </c>
-      <c r="M49" s="154" t="n">
+      <c r="M51" s="154" t="n">
         <v>10424.467</v>
       </c>
-      <c r="N49" s="154" t="n">
+      <c r="N51" s="154" t="n">
         <v>7895</v>
       </c>
-      <c r="O49" s="154" t="n">
+      <c r="O51" s="154" t="n">
         <v>6351.306666663</v>
       </c>
-      <c r="P49" s="154" t="n"/>
-      <c r="Q49" s="154" t="n"/>
-      <c r="R49" s="154" t="n"/>
-      <c r="S49" s="154" t="n"/>
-      <c r="T49" s="152" t="inlineStr">
+      <c r="P51" s="154" t="n"/>
+      <c r="Q51" s="154" t="n"/>
+      <c r="R51" s="154" t="n"/>
+      <c r="S51" s="154" t="n"/>
+      <c r="T51" s="152" t="inlineStr">
         <is>
           <t>2012-2021; no balance published after 2021</t>
         </is>
       </c>
-      <c r="U49" s="152" t="inlineStr">
+      <c r="U51" s="152" t="inlineStr">
         <is>
           <t>Department energy balances</t>
         </is>
       </c>
-      <c r="V49" s="152" t="inlineStr">
+      <c r="V51" s="152" t="inlineStr">
         <is>
           <t>Production by product after 2021 is not published by any source found</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="152" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="152" t="inlineStr">
         <is>
           <t>Production reported, diesel</t>
         </is>
       </c>
-      <c r="B50" s="153" t="inlineStr">
+      <c r="B52" s="153" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C50" s="153" t="inlineStr">
+      <c r="C52" s="153" t="inlineStr">
         <is>
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D50" s="154" t="n"/>
-      <c r="E50" s="152" t="inlineStr">
+      <c r="D52" s="154" t="n"/>
+      <c r="E52" s="152" t="inlineStr">
         <is>
           <t>National production line of the department's energy balance. The only production by product.</t>
         </is>
       </c>
-      <c r="F50" s="154" t="n">
+      <c r="F52" s="154" t="n">
         <v>9661.628000000001</v>
       </c>
-      <c r="G50" s="154" t="n">
+      <c r="G52" s="154" t="n">
         <v>9380.035</v>
       </c>
-      <c r="H50" s="154" t="n">
+      <c r="H52" s="154" t="n">
         <v>9587.74</v>
       </c>
-      <c r="I50" s="154" t="n">
+      <c r="I52" s="154" t="n">
         <v>9368.482</v>
       </c>
-      <c r="J50" s="154" t="n">
+      <c r="J52" s="154" t="n">
         <v>9014.190000000001</v>
       </c>
-      <c r="K50" s="154" t="n">
+      <c r="K52" s="154" t="n">
         <v>7921.726</v>
       </c>
-      <c r="L50" s="154" t="n">
+      <c r="L52" s="154" t="n">
         <v>8425.262000000001</v>
       </c>
-      <c r="M50" s="154" t="n">
+      <c r="M52" s="154" t="n">
         <v>9080.357</v>
       </c>
-      <c r="N50" s="154" t="n">
+      <c r="N52" s="154" t="n">
         <v>6447.8095</v>
       </c>
-      <c r="O50" s="154" t="n">
+      <c r="O52" s="154" t="n">
         <v>5314.964285718001</v>
       </c>
-      <c r="P50" s="154" t="n"/>
-      <c r="Q50" s="154" t="n"/>
-      <c r="R50" s="154" t="n"/>
-      <c r="S50" s="154" t="n"/>
-      <c r="T50" s="152" t="inlineStr">
+      <c r="P52" s="154" t="n"/>
+      <c r="Q52" s="154" t="n"/>
+      <c r="R52" s="154" t="n"/>
+      <c r="S52" s="154" t="n"/>
+      <c r="T52" s="152" t="inlineStr">
         <is>
           <t>2012-2021; no balance published after 2021</t>
         </is>
       </c>
-      <c r="U50" s="152" t="inlineStr">
+      <c r="U52" s="152" t="inlineStr">
         <is>
           <t>Department energy balances</t>
         </is>
       </c>
-      <c r="V50" s="152" t="inlineStr">
+      <c r="V52" s="152" t="inlineStr">
         <is>
           <t>Production by product after 2021 is not published by any source found</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="159" t="inlineStr">
-        <is>
-          <t>Secunda, all refined products</t>
-        </is>
-      </c>
-      <c r="B51" s="160" t="inlineStr">
-        <is>
-          <t>million barrels</t>
-        </is>
-      </c>
-      <c r="C51" s="160" t="inlineStr">
-        <is>
-          <t>Reported units; not converted</t>
-        </is>
-      </c>
-      <c r="D51" s="161" t="n"/>
-      <c r="E51" s="159" t="inlineStr">
-        <is>
-          <t>As reported by the operator; year to 30 June. All products together, so not comparable with the rows above without assumptions.</t>
-        </is>
-      </c>
-      <c r="F51" s="161" t="n"/>
-      <c r="G51" s="161" t="n"/>
-      <c r="H51" s="161" t="n"/>
-      <c r="I51" s="161" t="n"/>
-      <c r="J51" s="161" t="n"/>
-      <c r="K51" s="161" t="n"/>
-      <c r="L51" s="161" t="n"/>
-      <c r="M51" s="161" t="n"/>
-      <c r="N51" s="161" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="O51" s="161" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="P51" s="161" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="Q51" s="161" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="R51" s="161" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="S51" s="161" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="T51" s="159" t="inlineStr">
-        <is>
-          <t>Operator reports; no split by product</t>
-        </is>
-      </c>
-      <c r="U51" s="159" t="inlineStr">
-        <is>
-          <t>Sasol production metrics; Glencore annual reports</t>
-        </is>
-      </c>
-      <c r="V51" s="159" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="159" t="inlineStr">
-        <is>
-          <t>Natref, Sasol's 63.64% share</t>
-        </is>
-      </c>
-      <c r="B52" s="160" t="inlineStr">
-        <is>
-          <t>million barrels</t>
-        </is>
-      </c>
-      <c r="C52" s="160" t="inlineStr">
-        <is>
-          <t>Reported units; not converted</t>
-        </is>
-      </c>
-      <c r="D52" s="161" t="n"/>
-      <c r="E52" s="159" t="inlineStr">
-        <is>
-          <t>As reported by the operator; year to 30 June. All products together, so not comparable with the rows above without assumptions.</t>
-        </is>
-      </c>
-      <c r="F52" s="161" t="n"/>
-      <c r="G52" s="161" t="n"/>
-      <c r="H52" s="161" t="n"/>
-      <c r="I52" s="161" t="n"/>
-      <c r="J52" s="161" t="n"/>
-      <c r="K52" s="161" t="n"/>
-      <c r="L52" s="161" t="n"/>
-      <c r="M52" s="161" t="n"/>
-      <c r="N52" s="161" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="O52" s="161" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="P52" s="161" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q52" s="161" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="R52" s="161" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S52" s="161" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="T52" s="159" t="inlineStr">
-        <is>
-          <t>Operator reports; no split by product</t>
-        </is>
-      </c>
-      <c r="U52" s="159" t="inlineStr">
-        <is>
-          <t>Sasol production metrics; Glencore annual reports</t>
-        </is>
-      </c>
-      <c r="V52" s="159" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="159" t="inlineStr">
         <is>
-          <t>Astron (Cape Town), all refined products</t>
+          <t>Secunda, all refined products</t>
         </is>
       </c>
       <c r="B53" s="160" t="inlineStr">
         <is>
-          <t>billion Btu</t>
+          <t>million barrels</t>
         </is>
       </c>
       <c r="C53" s="160" t="inlineStr">
@@ -40380,7 +40348,7 @@
       <c r="D53" s="161" t="n"/>
       <c r="E53" s="159" t="inlineStr">
         <is>
-          <t>As reported by the operator; calendar year. All products together, so not comparable with the rows above without assumptions.</t>
+          <t>As reported by the operator; year to 30 June. All products together, so not comparable with the rows above without assumptions.</t>
         </is>
       </c>
       <c r="F53" s="161" t="n"/>
@@ -40391,308 +40359,256 @@
       <c r="K53" s="161" t="n"/>
       <c r="L53" s="161" t="n"/>
       <c r="M53" s="161" t="n"/>
-      <c r="N53" s="161" t="n"/>
-      <c r="O53" s="161" t="n"/>
-      <c r="P53" s="161" t="n"/>
+      <c r="N53" s="161" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="O53" s="161" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="P53" s="161" t="n">
+        <v>29.2</v>
+      </c>
       <c r="Q53" s="161" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="R53" s="161" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="S53" s="161" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T53" s="159" t="inlineStr">
+        <is>
+          <t>Operator reports; no split by product</t>
+        </is>
+      </c>
+      <c r="U53" s="159" t="inlineStr">
+        <is>
+          <t>Sasol production metrics; Glencore annual reports</t>
+        </is>
+      </c>
+      <c r="V53" s="159" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="159" t="inlineStr">
+        <is>
+          <t>Natref, Sasol's 63.64% share</t>
+        </is>
+      </c>
+      <c r="B54" s="160" t="inlineStr">
+        <is>
+          <t>million barrels</t>
+        </is>
+      </c>
+      <c r="C54" s="160" t="inlineStr">
+        <is>
+          <t>Reported units; not converted</t>
+        </is>
+      </c>
+      <c r="D54" s="161" t="n"/>
+      <c r="E54" s="159" t="inlineStr">
+        <is>
+          <t>As reported by the operator; year to 30 June. All products together, so not comparable with the rows above without assumptions.</t>
+        </is>
+      </c>
+      <c r="F54" s="161" t="n"/>
+      <c r="G54" s="161" t="n"/>
+      <c r="H54" s="161" t="n"/>
+      <c r="I54" s="161" t="n"/>
+      <c r="J54" s="161" t="n"/>
+      <c r="K54" s="161" t="n"/>
+      <c r="L54" s="161" t="n"/>
+      <c r="M54" s="161" t="n"/>
+      <c r="N54" s="161" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="O54" s="161" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="P54" s="161" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Q54" s="161" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="R54" s="161" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="S54" s="161" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="T54" s="159" t="inlineStr">
+        <is>
+          <t>Operator reports; no split by product</t>
+        </is>
+      </c>
+      <c r="U54" s="159" t="inlineStr">
+        <is>
+          <t>Sasol production metrics; Glencore annual reports</t>
+        </is>
+      </c>
+      <c r="V54" s="159" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="159" t="inlineStr">
+        <is>
+          <t>Astron (Cape Town), all refined products</t>
+        </is>
+      </c>
+      <c r="B55" s="160" t="inlineStr">
+        <is>
+          <t>billion Btu</t>
+        </is>
+      </c>
+      <c r="C55" s="160" t="inlineStr">
+        <is>
+          <t>Reported units; not converted</t>
+        </is>
+      </c>
+      <c r="D55" s="161" t="n"/>
+      <c r="E55" s="159" t="inlineStr">
+        <is>
+          <t>As reported by the operator; calendar year. All products together, so not comparable with the rows above without assumptions.</t>
+        </is>
+      </c>
+      <c r="F55" s="161" t="n"/>
+      <c r="G55" s="161" t="n"/>
+      <c r="H55" s="161" t="n"/>
+      <c r="I55" s="161" t="n"/>
+      <c r="J55" s="161" t="n"/>
+      <c r="K55" s="161" t="n"/>
+      <c r="L55" s="161" t="n"/>
+      <c r="M55" s="161" t="n"/>
+      <c r="N55" s="161" t="n"/>
+      <c r="O55" s="161" t="n"/>
+      <c r="P55" s="161" t="n"/>
+      <c r="Q55" s="161" t="n">
         <v>136665</v>
       </c>
-      <c r="R53" s="161" t="n">
+      <c r="R55" s="161" t="n">
         <v>166204</v>
       </c>
-      <c r="S53" s="161" t="n">
+      <c r="S55" s="161" t="n">
         <v>164365</v>
       </c>
-      <c r="T53" s="159" t="inlineStr">
+      <c r="T55" s="159" t="inlineStr">
         <is>
           <t>Operator reports; no split by product</t>
         </is>
       </c>
-      <c r="U53" s="159" t="inlineStr">
+      <c r="U55" s="159" t="inlineStr">
         <is>
           <t>Sasol production metrics; Glencore annual reports</t>
         </is>
       </c>
-      <c r="V53" s="159" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="151" t="inlineStr">
+      <c r="V55" s="159" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="151" t="inlineStr">
         <is>
           <t>4. Balance: consumption = imports - exports + production + stock change</t>
         </is>
       </c>
-      <c r="B55" s="151" t="n"/>
-      <c r="C55" s="151" t="n"/>
-      <c r="D55" s="151" t="n"/>
-      <c r="E55" s="151" t="n"/>
-      <c r="F55" s="151" t="n"/>
-      <c r="G55" s="151" t="n"/>
-      <c r="H55" s="151" t="n"/>
-      <c r="I55" s="151" t="n"/>
-      <c r="J55" s="151" t="n"/>
-      <c r="K55" s="151" t="n"/>
-      <c r="L55" s="151" t="n"/>
-      <c r="M55" s="151" t="n"/>
-      <c r="N55" s="151" t="n"/>
-      <c r="O55" s="151" t="n"/>
-      <c r="P55" s="151" t="n"/>
-      <c r="Q55" s="151" t="n"/>
-      <c r="R55" s="151" t="n"/>
-      <c r="S55" s="151" t="n"/>
-      <c r="T55" s="151" t="n"/>
-      <c r="U55" s="151" t="n"/>
-      <c r="V55" s="151" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="159" t="inlineStr">
+      <c r="B57" s="151" t="n"/>
+      <c r="C57" s="151" t="n"/>
+      <c r="D57" s="151" t="n"/>
+      <c r="E57" s="151" t="n"/>
+      <c r="F57" s="151" t="n"/>
+      <c r="G57" s="151" t="n"/>
+      <c r="H57" s="151" t="n"/>
+      <c r="I57" s="151" t="n"/>
+      <c r="J57" s="151" t="n"/>
+      <c r="K57" s="151" t="n"/>
+      <c r="L57" s="151" t="n"/>
+      <c r="M57" s="151" t="n"/>
+      <c r="N57" s="151" t="n"/>
+      <c r="O57" s="151" t="n"/>
+      <c r="P57" s="151" t="n"/>
+      <c r="Q57" s="151" t="n"/>
+      <c r="R57" s="151" t="n"/>
+      <c r="S57" s="151" t="n"/>
+      <c r="T57" s="151" t="n"/>
+      <c r="U57" s="151" t="n"/>
+      <c r="V57" s="151" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="159" t="inlineStr">
         <is>
           <t>FIASA sales, petrol</t>
         </is>
       </c>
-      <c r="B56" s="160" t="inlineStr">
+      <c r="B58" s="160" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C56" s="160" t="inlineStr">
+      <c r="C58" s="160" t="inlineStr">
         <is>
           <t>Comparison only</t>
         </is>
       </c>
-      <c r="D56" s="161" t="n"/>
-      <c r="E56" s="159" t="inlineStr">
+      <c r="D58" s="161" t="n"/>
+      <c r="E58" s="159" t="inlineStr">
         <is>
           <t>FIASA annual report, latest edition. Attributed by FIASA to the department.</t>
         </is>
       </c>
-      <c r="F56" s="161" t="n">
+      <c r="F58" s="161" t="n">
         <v>11714</v>
       </c>
-      <c r="G56" s="161" t="n">
+      <c r="G58" s="161" t="n">
         <v>11153</v>
       </c>
-      <c r="H56" s="161" t="n">
+      <c r="H58" s="161" t="n">
         <v>11344</v>
       </c>
-      <c r="I56" s="161" t="n">
+      <c r="I58" s="161" t="n">
         <v>12072</v>
       </c>
-      <c r="J56" s="161" t="n">
+      <c r="J58" s="161" t="n">
         <v>10160</v>
       </c>
-      <c r="K56" s="161" t="n">
+      <c r="K58" s="161" t="n">
         <v>11174</v>
       </c>
-      <c r="L56" s="161" t="n">
+      <c r="L58" s="161" t="n">
         <v>11142</v>
       </c>
-      <c r="M56" s="161" t="n">
+      <c r="M58" s="161" t="n">
         <v>10773</v>
       </c>
-      <c r="N56" s="161" t="n">
+      <c r="N58" s="161" t="n">
         <v>8761</v>
       </c>
-      <c r="O56" s="161" t="n">
+      <c r="O58" s="161" t="n">
         <v>9302</v>
       </c>
-      <c r="P56" s="161" t="n">
+      <c r="P58" s="161" t="n">
         <v>9185</v>
       </c>
-      <c r="Q56" s="161" t="n">
+      <c r="Q58" s="161" t="n">
         <v>9037</v>
       </c>
-      <c r="R56" s="161" t="n">
+      <c r="R58" s="161" t="n">
         <v>9029</v>
       </c>
-      <c r="S56" s="161" t="n"/>
-      <c r="T56" s="159" t="inlineStr">
+      <c r="S58" s="161" t="n"/>
+      <c r="T58" s="159" t="inlineStr">
         <is>
           <t>2024 differs between FIASA's 2024 and 2025 editions</t>
         </is>
       </c>
-      <c r="U56" s="159" t="inlineStr">
+      <c r="U58" s="159" t="inlineStr">
         <is>
           <t>Fuels Industry Association of South Africa, annual reports</t>
         </is>
       </c>
-      <c r="V56" s="159" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="156" t="inlineStr">
-        <is>
-          <t>Sales used, petrol</t>
-        </is>
-      </c>
-      <c r="B57" s="157" t="inlineStr">
-        <is>
-          <t>million L/year</t>
-        </is>
-      </c>
-      <c r="C57" s="157" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D57" s="158" t="n"/>
-      <c r="E57" s="156" t="inlineStr">
-        <is>
-          <t>Department national file where published; otherwise FIASA, which is unverified.</t>
-        </is>
-      </c>
-      <c r="F57" s="158">
-        <f>IF(ISNUMBER(F16),F16,IF(ISNUMBER(F56),F56,""))</f>
-        <v/>
-      </c>
-      <c r="G57" s="158">
-        <f>IF(ISNUMBER(G16),G16,IF(ISNUMBER(G56),G56,""))</f>
-        <v/>
-      </c>
-      <c r="H57" s="158">
-        <f>IF(ISNUMBER(H16),H16,IF(ISNUMBER(H56),H56,""))</f>
-        <v/>
-      </c>
-      <c r="I57" s="158">
-        <f>IF(ISNUMBER(I16),I16,IF(ISNUMBER(I56),I56,""))</f>
-        <v/>
-      </c>
-      <c r="J57" s="158">
-        <f>IF(ISNUMBER(J16),J16,IF(ISNUMBER(J56),J56,""))</f>
-        <v/>
-      </c>
-      <c r="K57" s="158">
-        <f>IF(ISNUMBER(K16),K16,IF(ISNUMBER(K56),K56,""))</f>
-        <v/>
-      </c>
-      <c r="L57" s="158">
-        <f>IF(ISNUMBER(L16),L16,IF(ISNUMBER(L56),L56,""))</f>
-        <v/>
-      </c>
-      <c r="M57" s="158">
-        <f>IF(ISNUMBER(M16),M16,IF(ISNUMBER(M56),M56,""))</f>
-        <v/>
-      </c>
-      <c r="N57" s="158">
-        <f>IF(ISNUMBER(N16),N16,IF(ISNUMBER(N56),N56,""))</f>
-        <v/>
-      </c>
-      <c r="O57" s="158">
-        <f>IF(ISNUMBER(O16),O16,IF(ISNUMBER(O56),O56,""))</f>
-        <v/>
-      </c>
-      <c r="P57" s="158">
-        <f>IF(ISNUMBER(P16),P16,IF(ISNUMBER(P56),P56,""))</f>
-        <v/>
-      </c>
-      <c r="Q57" s="158">
-        <f>IF(ISNUMBER(Q16),Q16,IF(ISNUMBER(Q56),Q56,""))</f>
-        <v/>
-      </c>
-      <c r="R57" s="158">
-        <f>IF(ISNUMBER(R16),R16,IF(ISNUMBER(R56),R56,""))</f>
-        <v/>
-      </c>
-      <c r="S57" s="158">
-        <f>IF(ISNUMBER(S16),S16,IF(ISNUMBER(S56),S56,""))</f>
-        <v/>
-      </c>
-      <c r="T57" s="156" t="inlineStr">
-        <is>
-          <t>Department to 2023; FIASA for 2024</t>
-        </is>
-      </c>
-      <c r="U57" s="156" t="inlineStr"/>
-      <c r="V57" s="156" t="inlineStr">
-        <is>
-          <t>Agree the 2024 source (Nigel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="156" t="inlineStr">
-        <is>
-          <t>Net imports used, petrol</t>
-        </is>
-      </c>
-      <c r="B58" s="157" t="inlineStr">
-        <is>
-          <t>million L/year</t>
-        </is>
-      </c>
-      <c r="C58" s="157" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D58" s="158" t="n"/>
-      <c r="E58" s="156" t="inlineStr">
-        <is>
-          <t>SARS customs from 2014 (section 2).</t>
-        </is>
-      </c>
-      <c r="F58" s="158">
-        <f>IF(ISNUMBER(F41),F41,"")</f>
-        <v/>
-      </c>
-      <c r="G58" s="158">
-        <f>IF(ISNUMBER(G41),G41,"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="158">
-        <f>IF(ISNUMBER(H41),H41,"")</f>
-        <v/>
-      </c>
-      <c r="I58" s="158">
-        <f>IF(ISNUMBER(I41),I41,"")</f>
-        <v/>
-      </c>
-      <c r="J58" s="158">
-        <f>IF(ISNUMBER(J41),J41,"")</f>
-        <v/>
-      </c>
-      <c r="K58" s="158">
-        <f>IF(ISNUMBER(K41),K41,"")</f>
-        <v/>
-      </c>
-      <c r="L58" s="158">
-        <f>IF(ISNUMBER(L41),L41,"")</f>
-        <v/>
-      </c>
-      <c r="M58" s="158">
-        <f>IF(ISNUMBER(M41),M41,"")</f>
-        <v/>
-      </c>
-      <c r="N58" s="158">
-        <f>IF(ISNUMBER(N41),N41,"")</f>
-        <v/>
-      </c>
-      <c r="O58" s="158">
-        <f>IF(ISNUMBER(O41),O41,"")</f>
-        <v/>
-      </c>
-      <c r="P58" s="158">
-        <f>IF(ISNUMBER(P41),P41,"")</f>
-        <v/>
-      </c>
-      <c r="Q58" s="158">
-        <f>IF(ISNUMBER(Q41),Q41,"")</f>
-        <v/>
-      </c>
-      <c r="R58" s="158">
-        <f>IF(ISNUMBER(R41),R41,"")</f>
-        <v/>
-      </c>
-      <c r="S58" s="158">
-        <f>IF(ISNUMBER(S41),S41,"")</f>
-        <v/>
-      </c>
-      <c r="T58" s="156" t="inlineStr"/>
-      <c r="U58" s="156" t="inlineStr"/>
-      <c r="V58" s="156" t="inlineStr"/>
+      <c r="V58" s="159" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="156" t="inlineStr">
         <is>
-          <t>Sales less net imports, petrol</t>
+          <t>Sales used, petrol</t>
         </is>
       </c>
       <c r="B59" s="157" t="inlineStr">
@@ -40708,73 +40624,81 @@
       <c r="D59" s="158" t="n"/>
       <c r="E59" s="156" t="inlineStr">
         <is>
-          <t>What production, stock changes and gaps in sales coverage must together supply. Not a measurement of production.</t>
+          <t>Department national file where published; otherwise FIASA, which is unverified.</t>
         </is>
       </c>
       <c r="F59" s="158">
-        <f>IF(COUNT(F57,F58)&lt;2,"",F57-F58)</f>
+        <f>IF(ISNUMBER(F16),F16,IF(ISNUMBER(F58),F58,""))</f>
         <v/>
       </c>
       <c r="G59" s="158">
-        <f>IF(COUNT(G57,G58)&lt;2,"",G57-G58)</f>
+        <f>IF(ISNUMBER(G16),G16,IF(ISNUMBER(G58),G58,""))</f>
         <v/>
       </c>
       <c r="H59" s="158">
-        <f>IF(COUNT(H57,H58)&lt;2,"",H57-H58)</f>
+        <f>IF(ISNUMBER(H16),H16,IF(ISNUMBER(H58),H58,""))</f>
         <v/>
       </c>
       <c r="I59" s="158">
-        <f>IF(COUNT(I57,I58)&lt;2,"",I57-I58)</f>
+        <f>IF(ISNUMBER(I16),I16,IF(ISNUMBER(I58),I58,""))</f>
         <v/>
       </c>
       <c r="J59" s="158">
-        <f>IF(COUNT(J57,J58)&lt;2,"",J57-J58)</f>
+        <f>IF(ISNUMBER(J16),J16,IF(ISNUMBER(J58),J58,""))</f>
         <v/>
       </c>
       <c r="K59" s="158">
-        <f>IF(COUNT(K57,K58)&lt;2,"",K57-K58)</f>
+        <f>IF(ISNUMBER(K16),K16,IF(ISNUMBER(K58),K58,""))</f>
         <v/>
       </c>
       <c r="L59" s="158">
-        <f>IF(COUNT(L57,L58)&lt;2,"",L57-L58)</f>
+        <f>IF(ISNUMBER(L16),L16,IF(ISNUMBER(L58),L58,""))</f>
         <v/>
       </c>
       <c r="M59" s="158">
-        <f>IF(COUNT(M57,M58)&lt;2,"",M57-M58)</f>
+        <f>IF(ISNUMBER(M16),M16,IF(ISNUMBER(M58),M58,""))</f>
         <v/>
       </c>
       <c r="N59" s="158">
-        <f>IF(COUNT(N57,N58)&lt;2,"",N57-N58)</f>
+        <f>IF(ISNUMBER(N16),N16,IF(ISNUMBER(N58),N58,""))</f>
         <v/>
       </c>
       <c r="O59" s="158">
-        <f>IF(COUNT(O57,O58)&lt;2,"",O57-O58)</f>
+        <f>IF(ISNUMBER(O16),O16,IF(ISNUMBER(O58),O58,""))</f>
         <v/>
       </c>
       <c r="P59" s="158">
-        <f>IF(COUNT(P57,P58)&lt;2,"",P57-P58)</f>
+        <f>IF(ISNUMBER(P16),P16,IF(ISNUMBER(P58),P58,""))</f>
         <v/>
       </c>
       <c r="Q59" s="158">
-        <f>IF(COUNT(Q57,Q58)&lt;2,"",Q57-Q58)</f>
+        <f>IF(ISNUMBER(Q16),Q16,IF(ISNUMBER(Q58),Q58,""))</f>
         <v/>
       </c>
       <c r="R59" s="158">
-        <f>IF(COUNT(R57,R58)&lt;2,"",R57-R58)</f>
+        <f>IF(ISNUMBER(R16),R16,IF(ISNUMBER(R58),R58,""))</f>
         <v/>
       </c>
       <c r="S59" s="158">
-        <f>IF(COUNT(S57,S58)&lt;2,"",S57-S58)</f>
-        <v/>
-      </c>
-      <c r="T59" s="156" t="inlineStr"/>
+        <f>IF(ISNUMBER(S16),S16,IF(ISNUMBER(S58),S58,""))</f>
+        <v/>
+      </c>
+      <c r="T59" s="156" t="inlineStr">
+        <is>
+          <t>Department to 2023; FIASA for 2024</t>
+        </is>
+      </c>
       <c r="U59" s="156" t="inlineStr"/>
-      <c r="V59" s="156" t="inlineStr"/>
+      <c r="V59" s="156" t="inlineStr">
+        <is>
+          <t>Agree the 2024 source (Nigel)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="156" t="inlineStr">
         <is>
-          <t>Unexplained after reported production, petrol</t>
+          <t>Net imports used, petrol</t>
         </is>
       </c>
       <c r="B60" s="157" t="inlineStr">
@@ -40790,155 +40714,155 @@
       <c r="D60" s="158" t="n"/>
       <c r="E60" s="156" t="inlineStr">
         <is>
-          <t>Sales less net imports less reported production: stock change plus anything the sources do not cover.</t>
+          <t>SARS customs from 2014 (section 2).</t>
         </is>
       </c>
       <c r="F60" s="158">
-        <f>IF(COUNT(F59,F49)&lt;2,"",F59-F49)</f>
+        <f>IF(ISNUMBER(F43),F43,"")</f>
         <v/>
       </c>
       <c r="G60" s="158">
-        <f>IF(COUNT(G59,G49)&lt;2,"",G59-G49)</f>
+        <f>IF(ISNUMBER(G43),G43,"")</f>
         <v/>
       </c>
       <c r="H60" s="158">
-        <f>IF(COUNT(H59,H49)&lt;2,"",H59-H49)</f>
+        <f>IF(ISNUMBER(H43),H43,"")</f>
         <v/>
       </c>
       <c r="I60" s="158">
-        <f>IF(COUNT(I59,I49)&lt;2,"",I59-I49)</f>
+        <f>IF(ISNUMBER(I43),I43,"")</f>
         <v/>
       </c>
       <c r="J60" s="158">
-        <f>IF(COUNT(J59,J49)&lt;2,"",J59-J49)</f>
+        <f>IF(ISNUMBER(J43),J43,"")</f>
         <v/>
       </c>
       <c r="K60" s="158">
-        <f>IF(COUNT(K59,K49)&lt;2,"",K59-K49)</f>
+        <f>IF(ISNUMBER(K43),K43,"")</f>
         <v/>
       </c>
       <c r="L60" s="158">
-        <f>IF(COUNT(L59,L49)&lt;2,"",L59-L49)</f>
+        <f>IF(ISNUMBER(L43),L43,"")</f>
         <v/>
       </c>
       <c r="M60" s="158">
-        <f>IF(COUNT(M59,M49)&lt;2,"",M59-M49)</f>
+        <f>IF(ISNUMBER(M43),M43,"")</f>
         <v/>
       </c>
       <c r="N60" s="158">
-        <f>IF(COUNT(N59,N49)&lt;2,"",N59-N49)</f>
+        <f>IF(ISNUMBER(N43),N43,"")</f>
         <v/>
       </c>
       <c r="O60" s="158">
-        <f>IF(COUNT(O59,O49)&lt;2,"",O59-O49)</f>
+        <f>IF(ISNUMBER(O43),O43,"")</f>
         <v/>
       </c>
       <c r="P60" s="158">
-        <f>IF(COUNT(P59,P49)&lt;2,"",P59-P49)</f>
+        <f>IF(ISNUMBER(P43),P43,"")</f>
         <v/>
       </c>
       <c r="Q60" s="158">
-        <f>IF(COUNT(Q59,Q49)&lt;2,"",Q59-Q49)</f>
+        <f>IF(ISNUMBER(Q43),Q43,"")</f>
         <v/>
       </c>
       <c r="R60" s="158">
-        <f>IF(COUNT(R59,R49)&lt;2,"",R59-R49)</f>
+        <f>IF(ISNUMBER(R43),R43,"")</f>
         <v/>
       </c>
       <c r="S60" s="158">
-        <f>IF(COUNT(S59,S49)&lt;2,"",S59-S49)</f>
-        <v/>
-      </c>
-      <c r="T60" s="156" t="inlineStr">
-        <is>
-          <t>Only where production is reported (to 2021)</t>
-        </is>
-      </c>
+        <f>IF(ISNUMBER(S43),S43,"")</f>
+        <v/>
+      </c>
+      <c r="T60" s="156" t="inlineStr"/>
       <c r="U60" s="156" t="inlineStr"/>
-      <c r="V60" s="156" t="inlineStr">
-        <is>
-          <t>No usable stock series exists; JODI's carries its lowest reliability code</t>
-        </is>
-      </c>
+      <c r="V60" s="156" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="159" t="inlineStr">
-        <is>
-          <t>FIASA sales, diesel</t>
-        </is>
-      </c>
-      <c r="B61" s="160" t="inlineStr">
+      <c r="A61" s="156" t="inlineStr">
+        <is>
+          <t>Sales less net imports, petrol</t>
+        </is>
+      </c>
+      <c r="B61" s="157" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C61" s="160" t="inlineStr">
-        <is>
-          <t>Comparison only</t>
-        </is>
-      </c>
-      <c r="D61" s="161" t="n"/>
-      <c r="E61" s="159" t="inlineStr">
-        <is>
-          <t>FIASA annual report, latest edition. Attributed by FIASA to the department.</t>
-        </is>
-      </c>
-      <c r="F61" s="161" t="n">
-        <v>11262</v>
-      </c>
-      <c r="G61" s="161" t="n">
-        <v>11890</v>
-      </c>
-      <c r="H61" s="161" t="n">
-        <v>13169</v>
-      </c>
-      <c r="I61" s="161" t="n">
-        <v>14178</v>
-      </c>
-      <c r="J61" s="161" t="n">
-        <v>10846</v>
-      </c>
-      <c r="K61" s="161" t="n">
-        <v>12147</v>
-      </c>
-      <c r="L61" s="161" t="n">
-        <v>12539</v>
-      </c>
-      <c r="M61" s="161" t="n">
-        <v>12909</v>
-      </c>
-      <c r="N61" s="161" t="n">
-        <v>11690</v>
-      </c>
-      <c r="O61" s="161" t="n">
-        <v>12946</v>
-      </c>
-      <c r="P61" s="161" t="n">
-        <v>12717</v>
-      </c>
-      <c r="Q61" s="161" t="n">
-        <v>12907</v>
-      </c>
-      <c r="R61" s="161" t="n">
-        <v>11734</v>
-      </c>
-      <c r="S61" s="161" t="n"/>
-      <c r="T61" s="159" t="inlineStr">
-        <is>
-          <t>2024 differs between FIASA's 2024 and 2025 editions</t>
-        </is>
-      </c>
-      <c r="U61" s="159" t="inlineStr">
-        <is>
-          <t>Fuels Industry Association of South Africa, annual reports</t>
-        </is>
-      </c>
-      <c r="V61" s="159" t="inlineStr"/>
+      <c r="C61" s="157" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D61" s="158" t="n"/>
+      <c r="E61" s="156" t="inlineStr">
+        <is>
+          <t>What production, stock changes and gaps in sales coverage must together supply. Not a measurement of production.</t>
+        </is>
+      </c>
+      <c r="F61" s="158">
+        <f>IF(COUNT(F59,F60)&lt;2,"",F59-F60)</f>
+        <v/>
+      </c>
+      <c r="G61" s="158">
+        <f>IF(COUNT(G59,G60)&lt;2,"",G59-G60)</f>
+        <v/>
+      </c>
+      <c r="H61" s="158">
+        <f>IF(COUNT(H59,H60)&lt;2,"",H59-H60)</f>
+        <v/>
+      </c>
+      <c r="I61" s="158">
+        <f>IF(COUNT(I59,I60)&lt;2,"",I59-I60)</f>
+        <v/>
+      </c>
+      <c r="J61" s="158">
+        <f>IF(COUNT(J59,J60)&lt;2,"",J59-J60)</f>
+        <v/>
+      </c>
+      <c r="K61" s="158">
+        <f>IF(COUNT(K59,K60)&lt;2,"",K59-K60)</f>
+        <v/>
+      </c>
+      <c r="L61" s="158">
+        <f>IF(COUNT(L59,L60)&lt;2,"",L59-L60)</f>
+        <v/>
+      </c>
+      <c r="M61" s="158">
+        <f>IF(COUNT(M59,M60)&lt;2,"",M59-M60)</f>
+        <v/>
+      </c>
+      <c r="N61" s="158">
+        <f>IF(COUNT(N59,N60)&lt;2,"",N59-N60)</f>
+        <v/>
+      </c>
+      <c r="O61" s="158">
+        <f>IF(COUNT(O59,O60)&lt;2,"",O59-O60)</f>
+        <v/>
+      </c>
+      <c r="P61" s="158">
+        <f>IF(COUNT(P59,P60)&lt;2,"",P59-P60)</f>
+        <v/>
+      </c>
+      <c r="Q61" s="158">
+        <f>IF(COUNT(Q59,Q60)&lt;2,"",Q59-Q60)</f>
+        <v/>
+      </c>
+      <c r="R61" s="158">
+        <f>IF(COUNT(R59,R60)&lt;2,"",R59-R60)</f>
+        <v/>
+      </c>
+      <c r="S61" s="158">
+        <f>IF(COUNT(S59,S60)&lt;2,"",S59-S60)</f>
+        <v/>
+      </c>
+      <c r="T61" s="156" t="inlineStr"/>
+      <c r="U61" s="156" t="inlineStr"/>
+      <c r="V61" s="156" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="156" t="inlineStr">
         <is>
-          <t>Sales used, diesel</t>
+          <t>Unexplained after reported production, petrol</t>
         </is>
       </c>
       <c r="B62" s="157" t="inlineStr">
@@ -40954,163 +40878,155 @@
       <c r="D62" s="158" t="n"/>
       <c r="E62" s="156" t="inlineStr">
         <is>
-          <t>Department national file where published; otherwise FIASA, which is unverified.</t>
+          <t>Sales less net imports less reported production: stock change plus anything the sources do not cover.</t>
         </is>
       </c>
       <c r="F62" s="158">
-        <f>IF(ISNUMBER(F30),F30,IF(ISNUMBER(F61),F61,""))</f>
+        <f>IF(COUNT(F61,F51)&lt;2,"",F61-F51)</f>
         <v/>
       </c>
       <c r="G62" s="158">
-        <f>IF(ISNUMBER(G30),G30,IF(ISNUMBER(G61),G61,""))</f>
+        <f>IF(COUNT(G61,G51)&lt;2,"",G61-G51)</f>
         <v/>
       </c>
       <c r="H62" s="158">
-        <f>IF(ISNUMBER(H30),H30,IF(ISNUMBER(H61),H61,""))</f>
+        <f>IF(COUNT(H61,H51)&lt;2,"",H61-H51)</f>
         <v/>
       </c>
       <c r="I62" s="158">
-        <f>IF(ISNUMBER(I30),I30,IF(ISNUMBER(I61),I61,""))</f>
+        <f>IF(COUNT(I61,I51)&lt;2,"",I61-I51)</f>
         <v/>
       </c>
       <c r="J62" s="158">
-        <f>IF(ISNUMBER(J30),J30,IF(ISNUMBER(J61),J61,""))</f>
+        <f>IF(COUNT(J61,J51)&lt;2,"",J61-J51)</f>
         <v/>
       </c>
       <c r="K62" s="158">
-        <f>IF(ISNUMBER(K30),K30,IF(ISNUMBER(K61),K61,""))</f>
+        <f>IF(COUNT(K61,K51)&lt;2,"",K61-K51)</f>
         <v/>
       </c>
       <c r="L62" s="158">
-        <f>IF(ISNUMBER(L30),L30,IF(ISNUMBER(L61),L61,""))</f>
+        <f>IF(COUNT(L61,L51)&lt;2,"",L61-L51)</f>
         <v/>
       </c>
       <c r="M62" s="158">
-        <f>IF(ISNUMBER(M30),M30,IF(ISNUMBER(M61),M61,""))</f>
+        <f>IF(COUNT(M61,M51)&lt;2,"",M61-M51)</f>
         <v/>
       </c>
       <c r="N62" s="158">
-        <f>IF(ISNUMBER(N30),N30,IF(ISNUMBER(N61),N61,""))</f>
+        <f>IF(COUNT(N61,N51)&lt;2,"",N61-N51)</f>
         <v/>
       </c>
       <c r="O62" s="158">
-        <f>IF(ISNUMBER(O30),O30,IF(ISNUMBER(O61),O61,""))</f>
+        <f>IF(COUNT(O61,O51)&lt;2,"",O61-O51)</f>
         <v/>
       </c>
       <c r="P62" s="158">
-        <f>IF(ISNUMBER(P30),P30,IF(ISNUMBER(P61),P61,""))</f>
+        <f>IF(COUNT(P61,P51)&lt;2,"",P61-P51)</f>
         <v/>
       </c>
       <c r="Q62" s="158">
-        <f>IF(ISNUMBER(Q30),Q30,IF(ISNUMBER(Q61),Q61,""))</f>
+        <f>IF(COUNT(Q61,Q51)&lt;2,"",Q61-Q51)</f>
         <v/>
       </c>
       <c r="R62" s="158">
-        <f>IF(ISNUMBER(R30),R30,IF(ISNUMBER(R61),R61,""))</f>
+        <f>IF(COUNT(R61,R51)&lt;2,"",R61-R51)</f>
         <v/>
       </c>
       <c r="S62" s="158">
-        <f>IF(ISNUMBER(S30),S30,IF(ISNUMBER(S61),S61,""))</f>
+        <f>IF(COUNT(S61,S51)&lt;2,"",S61-S51)</f>
         <v/>
       </c>
       <c r="T62" s="156" t="inlineStr">
         <is>
-          <t>Department to 2023; FIASA for 2024</t>
+          <t>Only where production is reported (to 2021)</t>
         </is>
       </c>
       <c r="U62" s="156" t="inlineStr"/>
       <c r="V62" s="156" t="inlineStr">
         <is>
-          <t>Agree the 2024 source (Nigel)</t>
+          <t>No usable stock series exists; JODI's carries its lowest reliability code</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="156" t="inlineStr">
-        <is>
-          <t>Net imports used, diesel</t>
-        </is>
-      </c>
-      <c r="B63" s="157" t="inlineStr">
+      <c r="A63" s="159" t="inlineStr">
+        <is>
+          <t>FIASA sales, diesel</t>
+        </is>
+      </c>
+      <c r="B63" s="160" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C63" s="157" t="inlineStr">
-        <is>
-          <t>Reporting formula</t>
-        </is>
-      </c>
-      <c r="D63" s="158" t="n"/>
-      <c r="E63" s="156" t="inlineStr">
-        <is>
-          <t>SARS customs from 2014 (section 2).</t>
-        </is>
-      </c>
-      <c r="F63" s="158">
-        <f>IF(ISNUMBER(F40),F40,"")</f>
-        <v/>
-      </c>
-      <c r="G63" s="158">
-        <f>IF(ISNUMBER(G40),G40,"")</f>
-        <v/>
-      </c>
-      <c r="H63" s="158">
-        <f>IF(ISNUMBER(H40),H40,"")</f>
-        <v/>
-      </c>
-      <c r="I63" s="158">
-        <f>IF(ISNUMBER(I40),I40,"")</f>
-        <v/>
-      </c>
-      <c r="J63" s="158">
-        <f>IF(ISNUMBER(J40),J40,"")</f>
-        <v/>
-      </c>
-      <c r="K63" s="158">
-        <f>IF(ISNUMBER(K40),K40,"")</f>
-        <v/>
-      </c>
-      <c r="L63" s="158">
-        <f>IF(ISNUMBER(L40),L40,"")</f>
-        <v/>
-      </c>
-      <c r="M63" s="158">
-        <f>IF(ISNUMBER(M40),M40,"")</f>
-        <v/>
-      </c>
-      <c r="N63" s="158">
-        <f>IF(ISNUMBER(N40),N40,"")</f>
-        <v/>
-      </c>
-      <c r="O63" s="158">
-        <f>IF(ISNUMBER(O40),O40,"")</f>
-        <v/>
-      </c>
-      <c r="P63" s="158">
-        <f>IF(ISNUMBER(P40),P40,"")</f>
-        <v/>
-      </c>
-      <c r="Q63" s="158">
-        <f>IF(ISNUMBER(Q40),Q40,"")</f>
-        <v/>
-      </c>
-      <c r="R63" s="158">
-        <f>IF(ISNUMBER(R40),R40,"")</f>
-        <v/>
-      </c>
-      <c r="S63" s="158">
-        <f>IF(ISNUMBER(S40),S40,"")</f>
-        <v/>
-      </c>
-      <c r="T63" s="156" t="inlineStr"/>
-      <c r="U63" s="156" t="inlineStr"/>
-      <c r="V63" s="156" t="inlineStr"/>
+      <c r="C63" s="160" t="inlineStr">
+        <is>
+          <t>Comparison only</t>
+        </is>
+      </c>
+      <c r="D63" s="161" t="n"/>
+      <c r="E63" s="159" t="inlineStr">
+        <is>
+          <t>FIASA annual report, latest edition. Attributed by FIASA to the department.</t>
+        </is>
+      </c>
+      <c r="F63" s="161" t="n">
+        <v>11262</v>
+      </c>
+      <c r="G63" s="161" t="n">
+        <v>11890</v>
+      </c>
+      <c r="H63" s="161" t="n">
+        <v>13169</v>
+      </c>
+      <c r="I63" s="161" t="n">
+        <v>14178</v>
+      </c>
+      <c r="J63" s="161" t="n">
+        <v>10846</v>
+      </c>
+      <c r="K63" s="161" t="n">
+        <v>12147</v>
+      </c>
+      <c r="L63" s="161" t="n">
+        <v>12539</v>
+      </c>
+      <c r="M63" s="161" t="n">
+        <v>12909</v>
+      </c>
+      <c r="N63" s="161" t="n">
+        <v>11690</v>
+      </c>
+      <c r="O63" s="161" t="n">
+        <v>12946</v>
+      </c>
+      <c r="P63" s="161" t="n">
+        <v>12717</v>
+      </c>
+      <c r="Q63" s="161" t="n">
+        <v>12907</v>
+      </c>
+      <c r="R63" s="161" t="n">
+        <v>11734</v>
+      </c>
+      <c r="S63" s="161" t="n"/>
+      <c r="T63" s="159" t="inlineStr">
+        <is>
+          <t>2024 differs between FIASA's 2024 and 2025 editions</t>
+        </is>
+      </c>
+      <c r="U63" s="159" t="inlineStr">
+        <is>
+          <t>Fuels Industry Association of South Africa, annual reports</t>
+        </is>
+      </c>
+      <c r="V63" s="159" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="156" t="inlineStr">
         <is>
-          <t>Sales less net imports, diesel</t>
+          <t>Sales used, diesel</t>
         </is>
       </c>
       <c r="B64" s="157" t="inlineStr">
@@ -41126,73 +41042,81 @@
       <c r="D64" s="158" t="n"/>
       <c r="E64" s="156" t="inlineStr">
         <is>
-          <t>What production, stock changes and gaps in sales coverage must together supply. Not a measurement of production.</t>
+          <t>Department national file where published; otherwise FIASA, which is unverified.</t>
         </is>
       </c>
       <c r="F64" s="158">
-        <f>IF(COUNT(F62,F63)&lt;2,"",F62-F63)</f>
+        <f>IF(ISNUMBER(F31),F31,IF(ISNUMBER(F63),F63,""))</f>
         <v/>
       </c>
       <c r="G64" s="158">
-        <f>IF(COUNT(G62,G63)&lt;2,"",G62-G63)</f>
+        <f>IF(ISNUMBER(G31),G31,IF(ISNUMBER(G63),G63,""))</f>
         <v/>
       </c>
       <c r="H64" s="158">
-        <f>IF(COUNT(H62,H63)&lt;2,"",H62-H63)</f>
+        <f>IF(ISNUMBER(H31),H31,IF(ISNUMBER(H63),H63,""))</f>
         <v/>
       </c>
       <c r="I64" s="158">
-        <f>IF(COUNT(I62,I63)&lt;2,"",I62-I63)</f>
+        <f>IF(ISNUMBER(I31),I31,IF(ISNUMBER(I63),I63,""))</f>
         <v/>
       </c>
       <c r="J64" s="158">
-        <f>IF(COUNT(J62,J63)&lt;2,"",J62-J63)</f>
+        <f>IF(ISNUMBER(J31),J31,IF(ISNUMBER(J63),J63,""))</f>
         <v/>
       </c>
       <c r="K64" s="158">
-        <f>IF(COUNT(K62,K63)&lt;2,"",K62-K63)</f>
+        <f>IF(ISNUMBER(K31),K31,IF(ISNUMBER(K63),K63,""))</f>
         <v/>
       </c>
       <c r="L64" s="158">
-        <f>IF(COUNT(L62,L63)&lt;2,"",L62-L63)</f>
+        <f>IF(ISNUMBER(L31),L31,IF(ISNUMBER(L63),L63,""))</f>
         <v/>
       </c>
       <c r="M64" s="158">
-        <f>IF(COUNT(M62,M63)&lt;2,"",M62-M63)</f>
+        <f>IF(ISNUMBER(M31),M31,IF(ISNUMBER(M63),M63,""))</f>
         <v/>
       </c>
       <c r="N64" s="158">
-        <f>IF(COUNT(N62,N63)&lt;2,"",N62-N63)</f>
+        <f>IF(ISNUMBER(N31),N31,IF(ISNUMBER(N63),N63,""))</f>
         <v/>
       </c>
       <c r="O64" s="158">
-        <f>IF(COUNT(O62,O63)&lt;2,"",O62-O63)</f>
+        <f>IF(ISNUMBER(O31),O31,IF(ISNUMBER(O63),O63,""))</f>
         <v/>
       </c>
       <c r="P64" s="158">
-        <f>IF(COUNT(P62,P63)&lt;2,"",P62-P63)</f>
+        <f>IF(ISNUMBER(P31),P31,IF(ISNUMBER(P63),P63,""))</f>
         <v/>
       </c>
       <c r="Q64" s="158">
-        <f>IF(COUNT(Q62,Q63)&lt;2,"",Q62-Q63)</f>
+        <f>IF(ISNUMBER(Q31),Q31,IF(ISNUMBER(Q63),Q63,""))</f>
         <v/>
       </c>
       <c r="R64" s="158">
-        <f>IF(COUNT(R62,R63)&lt;2,"",R62-R63)</f>
+        <f>IF(ISNUMBER(R31),R31,IF(ISNUMBER(R63),R63,""))</f>
         <v/>
       </c>
       <c r="S64" s="158">
-        <f>IF(COUNT(S62,S63)&lt;2,"",S62-S63)</f>
-        <v/>
-      </c>
-      <c r="T64" s="156" t="inlineStr"/>
+        <f>IF(ISNUMBER(S31),S31,IF(ISNUMBER(S63),S63,""))</f>
+        <v/>
+      </c>
+      <c r="T64" s="156" t="inlineStr">
+        <is>
+          <t>Department to 2023; FIASA for 2024</t>
+        </is>
+      </c>
       <c r="U64" s="156" t="inlineStr"/>
-      <c r="V64" s="156" t="inlineStr"/>
+      <c r="V64" s="156" t="inlineStr">
+        <is>
+          <t>Agree the 2024 source (Nigel)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="156" t="inlineStr">
         <is>
-          <t>Unexplained after reported production, diesel</t>
+          <t>Net imports used, diesel</t>
         </is>
       </c>
       <c r="B65" s="157" t="inlineStr">
@@ -41208,461 +41132,517 @@
       <c r="D65" s="158" t="n"/>
       <c r="E65" s="156" t="inlineStr">
         <is>
+          <t>SARS customs from 2014 (section 2).</t>
+        </is>
+      </c>
+      <c r="F65" s="158">
+        <f>IF(ISNUMBER(F42),F42,"")</f>
+        <v/>
+      </c>
+      <c r="G65" s="158">
+        <f>IF(ISNUMBER(G42),G42,"")</f>
+        <v/>
+      </c>
+      <c r="H65" s="158">
+        <f>IF(ISNUMBER(H42),H42,"")</f>
+        <v/>
+      </c>
+      <c r="I65" s="158">
+        <f>IF(ISNUMBER(I42),I42,"")</f>
+        <v/>
+      </c>
+      <c r="J65" s="158">
+        <f>IF(ISNUMBER(J42),J42,"")</f>
+        <v/>
+      </c>
+      <c r="K65" s="158">
+        <f>IF(ISNUMBER(K42),K42,"")</f>
+        <v/>
+      </c>
+      <c r="L65" s="158">
+        <f>IF(ISNUMBER(L42),L42,"")</f>
+        <v/>
+      </c>
+      <c r="M65" s="158">
+        <f>IF(ISNUMBER(M42),M42,"")</f>
+        <v/>
+      </c>
+      <c r="N65" s="158">
+        <f>IF(ISNUMBER(N42),N42,"")</f>
+        <v/>
+      </c>
+      <c r="O65" s="158">
+        <f>IF(ISNUMBER(O42),O42,"")</f>
+        <v/>
+      </c>
+      <c r="P65" s="158">
+        <f>IF(ISNUMBER(P42),P42,"")</f>
+        <v/>
+      </c>
+      <c r="Q65" s="158">
+        <f>IF(ISNUMBER(Q42),Q42,"")</f>
+        <v/>
+      </c>
+      <c r="R65" s="158">
+        <f>IF(ISNUMBER(R42),R42,"")</f>
+        <v/>
+      </c>
+      <c r="S65" s="158">
+        <f>IF(ISNUMBER(S42),S42,"")</f>
+        <v/>
+      </c>
+      <c r="T65" s="156" t="inlineStr"/>
+      <c r="U65" s="156" t="inlineStr"/>
+      <c r="V65" s="156" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="156" t="inlineStr">
+        <is>
+          <t>Sales less net imports, diesel</t>
+        </is>
+      </c>
+      <c r="B66" s="157" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C66" s="157" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D66" s="158" t="n"/>
+      <c r="E66" s="156" t="inlineStr">
+        <is>
+          <t>What production, stock changes and gaps in sales coverage must together supply. Not a measurement of production.</t>
+        </is>
+      </c>
+      <c r="F66" s="158">
+        <f>IF(COUNT(F64,F65)&lt;2,"",F64-F65)</f>
+        <v/>
+      </c>
+      <c r="G66" s="158">
+        <f>IF(COUNT(G64,G65)&lt;2,"",G64-G65)</f>
+        <v/>
+      </c>
+      <c r="H66" s="158">
+        <f>IF(COUNT(H64,H65)&lt;2,"",H64-H65)</f>
+        <v/>
+      </c>
+      <c r="I66" s="158">
+        <f>IF(COUNT(I64,I65)&lt;2,"",I64-I65)</f>
+        <v/>
+      </c>
+      <c r="J66" s="158">
+        <f>IF(COUNT(J64,J65)&lt;2,"",J64-J65)</f>
+        <v/>
+      </c>
+      <c r="K66" s="158">
+        <f>IF(COUNT(K64,K65)&lt;2,"",K64-K65)</f>
+        <v/>
+      </c>
+      <c r="L66" s="158">
+        <f>IF(COUNT(L64,L65)&lt;2,"",L64-L65)</f>
+        <v/>
+      </c>
+      <c r="M66" s="158">
+        <f>IF(COUNT(M64,M65)&lt;2,"",M64-M65)</f>
+        <v/>
+      </c>
+      <c r="N66" s="158">
+        <f>IF(COUNT(N64,N65)&lt;2,"",N64-N65)</f>
+        <v/>
+      </c>
+      <c r="O66" s="158">
+        <f>IF(COUNT(O64,O65)&lt;2,"",O64-O65)</f>
+        <v/>
+      </c>
+      <c r="P66" s="158">
+        <f>IF(COUNT(P64,P65)&lt;2,"",P64-P65)</f>
+        <v/>
+      </c>
+      <c r="Q66" s="158">
+        <f>IF(COUNT(Q64,Q65)&lt;2,"",Q64-Q65)</f>
+        <v/>
+      </c>
+      <c r="R66" s="158">
+        <f>IF(COUNT(R64,R65)&lt;2,"",R64-R65)</f>
+        <v/>
+      </c>
+      <c r="S66" s="158">
+        <f>IF(COUNT(S64,S65)&lt;2,"",S64-S65)</f>
+        <v/>
+      </c>
+      <c r="T66" s="156" t="inlineStr"/>
+      <c r="U66" s="156" t="inlineStr"/>
+      <c r="V66" s="156" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="156" t="inlineStr">
+        <is>
+          <t>Unexplained after reported production, diesel</t>
+        </is>
+      </c>
+      <c r="B67" s="157" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C67" s="157" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D67" s="158" t="n"/>
+      <c r="E67" s="156" t="inlineStr">
+        <is>
           <t>Sales less net imports less reported production: stock change plus anything the sources do not cover.</t>
         </is>
       </c>
-      <c r="F65" s="158">
-        <f>IF(COUNT(F64,F50)&lt;2,"",F64-F50)</f>
-        <v/>
-      </c>
-      <c r="G65" s="158">
-        <f>IF(COUNT(G64,G50)&lt;2,"",G64-G50)</f>
-        <v/>
-      </c>
-      <c r="H65" s="158">
-        <f>IF(COUNT(H64,H50)&lt;2,"",H64-H50)</f>
-        <v/>
-      </c>
-      <c r="I65" s="158">
-        <f>IF(COUNT(I64,I50)&lt;2,"",I64-I50)</f>
-        <v/>
-      </c>
-      <c r="J65" s="158">
-        <f>IF(COUNT(J64,J50)&lt;2,"",J64-J50)</f>
-        <v/>
-      </c>
-      <c r="K65" s="158">
-        <f>IF(COUNT(K64,K50)&lt;2,"",K64-K50)</f>
-        <v/>
-      </c>
-      <c r="L65" s="158">
-        <f>IF(COUNT(L64,L50)&lt;2,"",L64-L50)</f>
-        <v/>
-      </c>
-      <c r="M65" s="158">
-        <f>IF(COUNT(M64,M50)&lt;2,"",M64-M50)</f>
-        <v/>
-      </c>
-      <c r="N65" s="158">
-        <f>IF(COUNT(N64,N50)&lt;2,"",N64-N50)</f>
-        <v/>
-      </c>
-      <c r="O65" s="158">
-        <f>IF(COUNT(O64,O50)&lt;2,"",O64-O50)</f>
-        <v/>
-      </c>
-      <c r="P65" s="158">
-        <f>IF(COUNT(P64,P50)&lt;2,"",P64-P50)</f>
-        <v/>
-      </c>
-      <c r="Q65" s="158">
-        <f>IF(COUNT(Q64,Q50)&lt;2,"",Q64-Q50)</f>
-        <v/>
-      </c>
-      <c r="R65" s="158">
-        <f>IF(COUNT(R64,R50)&lt;2,"",R64-R50)</f>
-        <v/>
-      </c>
-      <c r="S65" s="158">
-        <f>IF(COUNT(S64,S50)&lt;2,"",S64-S50)</f>
-        <v/>
-      </c>
-      <c r="T65" s="156" t="inlineStr">
+      <c r="F67" s="158">
+        <f>IF(COUNT(F66,F52)&lt;2,"",F66-F52)</f>
+        <v/>
+      </c>
+      <c r="G67" s="158">
+        <f>IF(COUNT(G66,G52)&lt;2,"",G66-G52)</f>
+        <v/>
+      </c>
+      <c r="H67" s="158">
+        <f>IF(COUNT(H66,H52)&lt;2,"",H66-H52)</f>
+        <v/>
+      </c>
+      <c r="I67" s="158">
+        <f>IF(COUNT(I66,I52)&lt;2,"",I66-I52)</f>
+        <v/>
+      </c>
+      <c r="J67" s="158">
+        <f>IF(COUNT(J66,J52)&lt;2,"",J66-J52)</f>
+        <v/>
+      </c>
+      <c r="K67" s="158">
+        <f>IF(COUNT(K66,K52)&lt;2,"",K66-K52)</f>
+        <v/>
+      </c>
+      <c r="L67" s="158">
+        <f>IF(COUNT(L66,L52)&lt;2,"",L66-L52)</f>
+        <v/>
+      </c>
+      <c r="M67" s="158">
+        <f>IF(COUNT(M66,M52)&lt;2,"",M66-M52)</f>
+        <v/>
+      </c>
+      <c r="N67" s="158">
+        <f>IF(COUNT(N66,N52)&lt;2,"",N66-N52)</f>
+        <v/>
+      </c>
+      <c r="O67" s="158">
+        <f>IF(COUNT(O66,O52)&lt;2,"",O66-O52)</f>
+        <v/>
+      </c>
+      <c r="P67" s="158">
+        <f>IF(COUNT(P66,P52)&lt;2,"",P66-P52)</f>
+        <v/>
+      </c>
+      <c r="Q67" s="158">
+        <f>IF(COUNT(Q66,Q52)&lt;2,"",Q66-Q52)</f>
+        <v/>
+      </c>
+      <c r="R67" s="158">
+        <f>IF(COUNT(R66,R52)&lt;2,"",R66-R52)</f>
+        <v/>
+      </c>
+      <c r="S67" s="158">
+        <f>IF(COUNT(S66,S52)&lt;2,"",S66-S52)</f>
+        <v/>
+      </c>
+      <c r="T67" s="156" t="inlineStr">
         <is>
           <t>Only where production is reported (to 2021)</t>
         </is>
       </c>
-      <c r="U65" s="156" t="inlineStr"/>
-      <c r="V65" s="156" t="inlineStr">
+      <c r="U67" s="156" t="inlineStr"/>
+      <c r="V67" s="156" t="inlineStr">
         <is>
           <t>No usable stock series exists; JODI's carries its lowest reliability code</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="151" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="151" t="inlineStr">
         <is>
           <t>5. Independent count of litres: Road Accident Fund levy (new evidence, 7 October)</t>
         </is>
       </c>
-      <c r="B67" s="151" t="n"/>
-      <c r="C67" s="151" t="n"/>
-      <c r="D67" s="151" t="n"/>
-      <c r="E67" s="151" t="n"/>
-      <c r="F67" s="151" t="n"/>
-      <c r="G67" s="151" t="n"/>
-      <c r="H67" s="151" t="n"/>
-      <c r="I67" s="151" t="n"/>
-      <c r="J67" s="151" t="n"/>
-      <c r="K67" s="151" t="n"/>
-      <c r="L67" s="151" t="n"/>
-      <c r="M67" s="151" t="n"/>
-      <c r="N67" s="151" t="n"/>
-      <c r="O67" s="151" t="n"/>
-      <c r="P67" s="151" t="n"/>
-      <c r="Q67" s="151" t="n"/>
-      <c r="R67" s="151" t="n"/>
-      <c r="S67" s="151" t="n"/>
-      <c r="T67" s="151" t="n"/>
-      <c r="U67" s="151" t="n"/>
-      <c r="V67" s="151" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="159" t="inlineStr">
+      <c r="B69" s="151" t="n"/>
+      <c r="C69" s="151" t="n"/>
+      <c r="D69" s="151" t="n"/>
+      <c r="E69" s="151" t="n"/>
+      <c r="F69" s="151" t="n"/>
+      <c r="G69" s="151" t="n"/>
+      <c r="H69" s="151" t="n"/>
+      <c r="I69" s="151" t="n"/>
+      <c r="J69" s="151" t="n"/>
+      <c r="K69" s="151" t="n"/>
+      <c r="L69" s="151" t="n"/>
+      <c r="M69" s="151" t="n"/>
+      <c r="N69" s="151" t="n"/>
+      <c r="O69" s="151" t="n"/>
+      <c r="P69" s="151" t="n"/>
+      <c r="Q69" s="151" t="n"/>
+      <c r="R69" s="151" t="n"/>
+      <c r="S69" s="151" t="n"/>
+      <c r="T69" s="151" t="n"/>
+      <c r="U69" s="151" t="n"/>
+      <c r="V69" s="151" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="159" t="inlineStr">
         <is>
           <t>Litres levied, petrol and diesel</t>
         </is>
       </c>
-      <c r="B68" s="160" t="inlineStr">
+      <c r="B70" s="160" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C68" s="160" t="inlineStr">
+      <c r="C70" s="160" t="inlineStr">
         <is>
           <t>Comparison only</t>
         </is>
       </c>
-      <c r="D68" s="161" t="n"/>
-      <c r="E68" s="159" t="inlineStr">
+      <c r="D70" s="161" t="n"/>
+      <c r="E70" s="159" t="inlineStr">
         <is>
           <t>Gross levies divided by 218 cents a litre. Fiscal year to 31 March of the following year, shown under the calendar year it mostly covers.</t>
         </is>
       </c>
-      <c r="F68" s="161" t="n"/>
-      <c r="G68" s="161" t="n"/>
-      <c r="H68" s="161" t="n"/>
-      <c r="I68" s="161" t="n"/>
-      <c r="J68" s="161" t="n"/>
-      <c r="K68" s="161" t="n"/>
-      <c r="L68" s="161" t="n"/>
-      <c r="M68" s="161" t="n"/>
-      <c r="N68" s="161" t="n"/>
-      <c r="O68" s="161" t="n"/>
-      <c r="P68" s="161" t="n"/>
-      <c r="Q68" s="161" t="n">
+      <c r="F70" s="161" t="n"/>
+      <c r="G70" s="161" t="n"/>
+      <c r="H70" s="161" t="n"/>
+      <c r="I70" s="161" t="n"/>
+      <c r="J70" s="161" t="n"/>
+      <c r="K70" s="161" t="n"/>
+      <c r="L70" s="161" t="n"/>
+      <c r="M70" s="161" t="n"/>
+      <c r="N70" s="161" t="n"/>
+      <c r="O70" s="161" t="n"/>
+      <c r="P70" s="161" t="n"/>
+      <c r="Q70" s="161" t="n">
         <v>24246.16513761468</v>
       </c>
-      <c r="R68" s="161" t="n">
+      <c r="R70" s="161" t="n">
         <v>24424.24541284404</v>
       </c>
-      <c r="S68" s="161" t="n"/>
-      <c r="T68" s="159" t="inlineStr">
+      <c r="S70" s="161" t="n"/>
+      <c r="T70" s="159" t="inlineStr">
         <is>
           <t>Both fuels together; accrual basis; not reconciled with SARS's statement</t>
         </is>
       </c>
-      <c r="U68" s="159" t="inlineStr">
+      <c r="U70" s="159" t="inlineStr">
         <is>
           <t>Road Accident Fund Annual Report 2024/25, note 16 (p.183)</t>
         </is>
       </c>
-      <c r="V68" s="159" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="156" t="inlineStr">
+      <c r="V70" s="159" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="156" t="inlineStr">
         <is>
           <t>Recorded sales used, petrol and diesel</t>
         </is>
       </c>
-      <c r="B69" s="157" t="inlineStr">
+      <c r="B71" s="157" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C69" s="157" t="inlineStr">
+      <c r="C71" s="157" t="inlineStr">
         <is>
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D69" s="158" t="n"/>
-      <c r="E69" s="156" t="inlineStr">
+      <c r="D71" s="158" t="n"/>
+      <c r="E71" s="156" t="inlineStr">
         <is>
           <t>Sum of the two 'sales used' rows.</t>
         </is>
       </c>
-      <c r="F69" s="158">
-        <f>IF(COUNT(F57,F62)&lt;2,"",F57+F62)</f>
-        <v/>
-      </c>
-      <c r="G69" s="158">
-        <f>IF(COUNT(G57,G62)&lt;2,"",G57+G62)</f>
-        <v/>
-      </c>
-      <c r="H69" s="158">
-        <f>IF(COUNT(H57,H62)&lt;2,"",H57+H62)</f>
-        <v/>
-      </c>
-      <c r="I69" s="158">
-        <f>IF(COUNT(I57,I62)&lt;2,"",I57+I62)</f>
-        <v/>
-      </c>
-      <c r="J69" s="158">
-        <f>IF(COUNT(J57,J62)&lt;2,"",J57+J62)</f>
-        <v/>
-      </c>
-      <c r="K69" s="158">
-        <f>IF(COUNT(K57,K62)&lt;2,"",K57+K62)</f>
-        <v/>
-      </c>
-      <c r="L69" s="158">
-        <f>IF(COUNT(L57,L62)&lt;2,"",L57+L62)</f>
-        <v/>
-      </c>
-      <c r="M69" s="158">
-        <f>IF(COUNT(M57,M62)&lt;2,"",M57+M62)</f>
-        <v/>
-      </c>
-      <c r="N69" s="158">
-        <f>IF(COUNT(N57,N62)&lt;2,"",N57+N62)</f>
-        <v/>
-      </c>
-      <c r="O69" s="158">
-        <f>IF(COUNT(O57,O62)&lt;2,"",O57+O62)</f>
-        <v/>
-      </c>
-      <c r="P69" s="158">
-        <f>IF(COUNT(P57,P62)&lt;2,"",P57+P62)</f>
-        <v/>
-      </c>
-      <c r="Q69" s="158">
-        <f>IF(COUNT(Q57,Q62)&lt;2,"",Q57+Q62)</f>
-        <v/>
-      </c>
-      <c r="R69" s="158">
-        <f>IF(COUNT(R57,R62)&lt;2,"",R57+R62)</f>
-        <v/>
-      </c>
-      <c r="S69" s="158">
-        <f>IF(COUNT(S57,S62)&lt;2,"",S57+S62)</f>
-        <v/>
-      </c>
-      <c r="T69" s="156" t="inlineStr"/>
-      <c r="U69" s="156" t="inlineStr"/>
-      <c r="V69" s="156" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="156" t="inlineStr">
+      <c r="F71" s="158">
+        <f>IF(COUNT(F59,F64)&lt;2,"",F59+F64)</f>
+        <v/>
+      </c>
+      <c r="G71" s="158">
+        <f>IF(COUNT(G59,G64)&lt;2,"",G59+G64)</f>
+        <v/>
+      </c>
+      <c r="H71" s="158">
+        <f>IF(COUNT(H59,H64)&lt;2,"",H59+H64)</f>
+        <v/>
+      </c>
+      <c r="I71" s="158">
+        <f>IF(COUNT(I59,I64)&lt;2,"",I59+I64)</f>
+        <v/>
+      </c>
+      <c r="J71" s="158">
+        <f>IF(COUNT(J59,J64)&lt;2,"",J59+J64)</f>
+        <v/>
+      </c>
+      <c r="K71" s="158">
+        <f>IF(COUNT(K59,K64)&lt;2,"",K59+K64)</f>
+        <v/>
+      </c>
+      <c r="L71" s="158">
+        <f>IF(COUNT(L59,L64)&lt;2,"",L59+L64)</f>
+        <v/>
+      </c>
+      <c r="M71" s="158">
+        <f>IF(COUNT(M59,M64)&lt;2,"",M59+M64)</f>
+        <v/>
+      </c>
+      <c r="N71" s="158">
+        <f>IF(COUNT(N59,N64)&lt;2,"",N59+N64)</f>
+        <v/>
+      </c>
+      <c r="O71" s="158">
+        <f>IF(COUNT(O59,O64)&lt;2,"",O59+O64)</f>
+        <v/>
+      </c>
+      <c r="P71" s="158">
+        <f>IF(COUNT(P59,P64)&lt;2,"",P59+P64)</f>
+        <v/>
+      </c>
+      <c r="Q71" s="158">
+        <f>IF(COUNT(Q59,Q64)&lt;2,"",Q59+Q64)</f>
+        <v/>
+      </c>
+      <c r="R71" s="158">
+        <f>IF(COUNT(R59,R64)&lt;2,"",R59+R64)</f>
+        <v/>
+      </c>
+      <c r="S71" s="158">
+        <f>IF(COUNT(S59,S64)&lt;2,"",S59+S64)</f>
+        <v/>
+      </c>
+      <c r="T71" s="156" t="inlineStr"/>
+      <c r="U71" s="156" t="inlineStr"/>
+      <c r="V71" s="156" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="156" t="inlineStr">
         <is>
           <t>Litres levied less recorded sales</t>
         </is>
       </c>
-      <c r="B70" s="157" t="inlineStr">
+      <c r="B72" s="157" t="inlineStr">
         <is>
           <t>million L/year</t>
         </is>
       </c>
-      <c r="C70" s="157" t="inlineStr">
+      <c r="C72" s="157" t="inlineStr">
         <is>
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D70" s="158" t="n"/>
-      <c r="E70" s="156" t="inlineStr">
+      <c r="D72" s="158" t="n"/>
+      <c r="E72" s="156" t="inlineStr">
         <is>
           <t>An indication that recorded sales may undercount. A hypothesis to test; not added to demand.</t>
         </is>
       </c>
-      <c r="F70" s="158">
-        <f>IF(COUNT(F68,F69)&lt;2,"",F68-F69)</f>
-        <v/>
-      </c>
-      <c r="G70" s="158">
-        <f>IF(COUNT(G68,G69)&lt;2,"",G68-G69)</f>
-        <v/>
-      </c>
-      <c r="H70" s="158">
-        <f>IF(COUNT(H68,H69)&lt;2,"",H68-H69)</f>
-        <v/>
-      </c>
-      <c r="I70" s="158">
-        <f>IF(COUNT(I68,I69)&lt;2,"",I68-I69)</f>
-        <v/>
-      </c>
-      <c r="J70" s="158">
-        <f>IF(COUNT(J68,J69)&lt;2,"",J68-J69)</f>
-        <v/>
-      </c>
-      <c r="K70" s="158">
-        <f>IF(COUNT(K68,K69)&lt;2,"",K68-K69)</f>
-        <v/>
-      </c>
-      <c r="L70" s="158">
-        <f>IF(COUNT(L68,L69)&lt;2,"",L68-L69)</f>
-        <v/>
-      </c>
-      <c r="M70" s="158">
-        <f>IF(COUNT(M68,M69)&lt;2,"",M68-M69)</f>
-        <v/>
-      </c>
-      <c r="N70" s="158">
-        <f>IF(COUNT(N68,N69)&lt;2,"",N68-N69)</f>
-        <v/>
-      </c>
-      <c r="O70" s="158">
-        <f>IF(COUNT(O68,O69)&lt;2,"",O68-O69)</f>
-        <v/>
-      </c>
-      <c r="P70" s="158">
-        <f>IF(COUNT(P68,P69)&lt;2,"",P68-P69)</f>
-        <v/>
-      </c>
-      <c r="Q70" s="158">
-        <f>IF(COUNT(Q68,Q69)&lt;2,"",Q68-Q69)</f>
-        <v/>
-      </c>
-      <c r="R70" s="158">
-        <f>IF(COUNT(R68,R69)&lt;2,"",R68-R69)</f>
-        <v/>
-      </c>
-      <c r="S70" s="158">
-        <f>IF(COUNT(S68,S69)&lt;2,"",S68-S69)</f>
-        <v/>
-      </c>
-      <c r="T70" s="156" t="inlineStr"/>
-      <c r="U70" s="156" t="inlineStr"/>
-      <c r="V70" s="156" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="151" t="inlineStr">
+      <c r="F72" s="158">
+        <f>IF(COUNT(F70,F71)&lt;2,"",F70-F71)</f>
+        <v/>
+      </c>
+      <c r="G72" s="158">
+        <f>IF(COUNT(G70,G71)&lt;2,"",G70-G71)</f>
+        <v/>
+      </c>
+      <c r="H72" s="158">
+        <f>IF(COUNT(H70,H71)&lt;2,"",H70-H71)</f>
+        <v/>
+      </c>
+      <c r="I72" s="158">
+        <f>IF(COUNT(I70,I71)&lt;2,"",I70-I71)</f>
+        <v/>
+      </c>
+      <c r="J72" s="158">
+        <f>IF(COUNT(J70,J71)&lt;2,"",J70-J71)</f>
+        <v/>
+      </c>
+      <c r="K72" s="158">
+        <f>IF(COUNT(K70,K71)&lt;2,"",K70-K71)</f>
+        <v/>
+      </c>
+      <c r="L72" s="158">
+        <f>IF(COUNT(L70,L71)&lt;2,"",L70-L71)</f>
+        <v/>
+      </c>
+      <c r="M72" s="158">
+        <f>IF(COUNT(M70,M71)&lt;2,"",M70-M71)</f>
+        <v/>
+      </c>
+      <c r="N72" s="158">
+        <f>IF(COUNT(N70,N71)&lt;2,"",N70-N71)</f>
+        <v/>
+      </c>
+      <c r="O72" s="158">
+        <f>IF(COUNT(O70,O71)&lt;2,"",O70-O71)</f>
+        <v/>
+      </c>
+      <c r="P72" s="158">
+        <f>IF(COUNT(P70,P71)&lt;2,"",P70-P71)</f>
+        <v/>
+      </c>
+      <c r="Q72" s="158">
+        <f>IF(COUNT(Q70,Q71)&lt;2,"",Q70-Q71)</f>
+        <v/>
+      </c>
+      <c r="R72" s="158">
+        <f>IF(COUNT(R70,R71)&lt;2,"",R70-R71)</f>
+        <v/>
+      </c>
+      <c r="S72" s="158">
+        <f>IF(COUNT(S70,S71)&lt;2,"",S70-S71)</f>
+        <v/>
+      </c>
+      <c r="T72" s="156" t="inlineStr"/>
+      <c r="U72" s="156" t="inlineStr"/>
+      <c r="V72" s="156" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="151" t="inlineStr">
         <is>
           <t>6. Estimated sales by province, 2023-2025: petrol (estimates, not observations)</t>
         </is>
       </c>
-      <c r="B72" s="151" t="n"/>
-      <c r="C72" s="151" t="n"/>
-      <c r="D72" s="151" t="n"/>
-      <c r="E72" s="151" t="n"/>
-      <c r="F72" s="151" t="n"/>
-      <c r="G72" s="151" t="n"/>
-      <c r="H72" s="151" t="n"/>
-      <c r="I72" s="151" t="n"/>
-      <c r="J72" s="151" t="n"/>
-      <c r="K72" s="151" t="n"/>
-      <c r="L72" s="151" t="n"/>
-      <c r="M72" s="151" t="n"/>
-      <c r="N72" s="151" t="n"/>
-      <c r="O72" s="151" t="n"/>
-      <c r="P72" s="151" t="n"/>
-      <c r="Q72" s="151" t="n"/>
-      <c r="R72" s="151" t="n"/>
-      <c r="S72" s="151" t="n"/>
-      <c r="T72" s="151" t="n"/>
-      <c r="U72" s="151" t="n"/>
-      <c r="V72" s="151" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="162" t="inlineStr">
-        <is>
-          <t>Gauteng share of petrol</t>
-        </is>
-      </c>
-      <c r="B73" s="163" t="inlineStr">
-        <is>
-          <t>% of national</t>
-        </is>
-      </c>
-      <c r="C73" s="163" t="inlineStr">
-        <is>
-          <t>Proposed estimate</t>
-        </is>
-      </c>
-      <c r="D73" s="164" t="n"/>
-      <c r="E73" s="162" t="inlineStr">
-        <is>
-          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
-        </is>
-      </c>
-      <c r="F73" s="164" t="n"/>
-      <c r="G73" s="164" t="n"/>
-      <c r="H73" s="164" t="n"/>
-      <c r="I73" s="164" t="n"/>
-      <c r="J73" s="164" t="n"/>
-      <c r="K73" s="164" t="n"/>
-      <c r="L73" s="164" t="n"/>
-      <c r="M73" s="164" t="n"/>
-      <c r="N73" s="164" t="n"/>
-      <c r="O73" s="164" t="n"/>
-      <c r="P73" s="164" t="n"/>
-      <c r="Q73" s="164" t="n">
-        <v>38.29082808102595</v>
-      </c>
-      <c r="R73" s="164" t="n">
-        <v>38.377262681276</v>
-      </c>
-      <c r="S73" s="164" t="n">
-        <v>38.377262681276</v>
-      </c>
-      <c r="T73" s="162" t="inlineStr">
-        <is>
-          <t>Estimate</t>
-        </is>
-      </c>
-      <c r="U73" s="162" t="inlineStr">
-        <is>
-          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
-        </is>
-      </c>
-      <c r="V73" s="162" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="162" t="inlineStr">
-        <is>
-          <t>KwaZulu-Natal share of petrol</t>
-        </is>
-      </c>
-      <c r="B74" s="163" t="inlineStr">
-        <is>
-          <t>% of national</t>
-        </is>
-      </c>
-      <c r="C74" s="163" t="inlineStr">
-        <is>
-          <t>Proposed estimate</t>
-        </is>
-      </c>
-      <c r="D74" s="164" t="n"/>
-      <c r="E74" s="162" t="inlineStr">
-        <is>
-          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
-        </is>
-      </c>
-      <c r="F74" s="164" t="n"/>
-      <c r="G74" s="164" t="n"/>
-      <c r="H74" s="164" t="n"/>
-      <c r="I74" s="164" t="n"/>
-      <c r="J74" s="164" t="n"/>
-      <c r="K74" s="164" t="n"/>
-      <c r="L74" s="164" t="n"/>
-      <c r="M74" s="164" t="n"/>
-      <c r="N74" s="164" t="n"/>
-      <c r="O74" s="164" t="n"/>
-      <c r="P74" s="164" t="n"/>
-      <c r="Q74" s="164" t="n">
-        <v>16.13082894316334</v>
-      </c>
-      <c r="R74" s="164" t="n">
-        <v>16.11326672611471</v>
-      </c>
-      <c r="S74" s="164" t="n">
-        <v>16.11326672611471</v>
-      </c>
-      <c r="T74" s="162" t="inlineStr">
-        <is>
-          <t>Estimate</t>
-        </is>
-      </c>
-      <c r="U74" s="162" t="inlineStr">
-        <is>
-          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
-        </is>
-      </c>
-      <c r="V74" s="162" t="inlineStr"/>
+      <c r="B74" s="151" t="n"/>
+      <c r="C74" s="151" t="n"/>
+      <c r="D74" s="151" t="n"/>
+      <c r="E74" s="151" t="n"/>
+      <c r="F74" s="151" t="n"/>
+      <c r="G74" s="151" t="n"/>
+      <c r="H74" s="151" t="n"/>
+      <c r="I74" s="151" t="n"/>
+      <c r="J74" s="151" t="n"/>
+      <c r="K74" s="151" t="n"/>
+      <c r="L74" s="151" t="n"/>
+      <c r="M74" s="151" t="n"/>
+      <c r="N74" s="151" t="n"/>
+      <c r="O74" s="151" t="n"/>
+      <c r="P74" s="151" t="n"/>
+      <c r="Q74" s="151" t="n"/>
+      <c r="R74" s="151" t="n"/>
+      <c r="S74" s="151" t="n"/>
+      <c r="T74" s="151" t="n"/>
+      <c r="U74" s="151" t="n"/>
+      <c r="V74" s="151" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="162" t="inlineStr">
         <is>
-          <t>Western Cape share of petrol</t>
+          <t>Gauteng share of petrol</t>
         </is>
       </c>
       <c r="B75" s="163" t="inlineStr">
@@ -41693,13 +41673,13 @@
       <c r="O75" s="164" t="n"/>
       <c r="P75" s="164" t="n"/>
       <c r="Q75" s="164" t="n">
-        <v>16.21627470314407</v>
+        <v>38.29082808102595</v>
       </c>
       <c r="R75" s="164" t="n">
-        <v>16.24783009372781</v>
+        <v>38.377262681276</v>
       </c>
       <c r="S75" s="164" t="n">
-        <v>16.24783009372781</v>
+        <v>38.377262681276</v>
       </c>
       <c r="T75" s="162" t="inlineStr">
         <is>
@@ -41716,7 +41696,7 @@
     <row r="76">
       <c r="A76" s="162" t="inlineStr">
         <is>
-          <t>Eastern Cape share of petrol</t>
+          <t>KwaZulu-Natal share of petrol</t>
         </is>
       </c>
       <c r="B76" s="163" t="inlineStr">
@@ -41747,13 +41727,13 @@
       <c r="O76" s="164" t="n"/>
       <c r="P76" s="164" t="n"/>
       <c r="Q76" s="164" t="n">
-        <v>7.511233012378306</v>
+        <v>16.13082894316334</v>
       </c>
       <c r="R76" s="164" t="n">
-        <v>7.458565493679201</v>
+        <v>16.11326672611471</v>
       </c>
       <c r="S76" s="164" t="n">
-        <v>7.458565493679201</v>
+        <v>16.11326672611471</v>
       </c>
       <c r="T76" s="162" t="inlineStr">
         <is>
@@ -41770,7 +41750,7 @@
     <row r="77">
       <c r="A77" s="162" t="inlineStr">
         <is>
-          <t>Mpumalanga share of petrol</t>
+          <t>Western Cape share of petrol</t>
         </is>
       </c>
       <c r="B77" s="163" t="inlineStr">
@@ -41801,13 +41781,13 @@
       <c r="O77" s="164" t="n"/>
       <c r="P77" s="164" t="n"/>
       <c r="Q77" s="164" t="n">
-        <v>7.055371979667532</v>
+        <v>16.21627470314407</v>
       </c>
       <c r="R77" s="164" t="n">
-        <v>7.040255181823918</v>
+        <v>16.24783009372781</v>
       </c>
       <c r="S77" s="164" t="n">
-        <v>7.040255181823918</v>
+        <v>16.24783009372781</v>
       </c>
       <c r="T77" s="162" t="inlineStr">
         <is>
@@ -41824,7 +41804,7 @@
     <row r="78">
       <c r="A78" s="162" t="inlineStr">
         <is>
-          <t>Free State share of petrol</t>
+          <t>Eastern Cape share of petrol</t>
         </is>
       </c>
       <c r="B78" s="163" t="inlineStr">
@@ -41855,13 +41835,13 @@
       <c r="O78" s="164" t="n"/>
       <c r="P78" s="164" t="n"/>
       <c r="Q78" s="164" t="n">
-        <v>5.932159079461925</v>
+        <v>7.511233012378306</v>
       </c>
       <c r="R78" s="164" t="n">
-        <v>5.927995171497546</v>
+        <v>7.458565493679201</v>
       </c>
       <c r="S78" s="164" t="n">
-        <v>5.927995171497546</v>
+        <v>7.458565493679201</v>
       </c>
       <c r="T78" s="162" t="inlineStr">
         <is>
@@ -41878,7 +41858,7 @@
     <row r="79">
       <c r="A79" s="162" t="inlineStr">
         <is>
-          <t>North West share of petrol</t>
+          <t>Mpumalanga share of petrol</t>
         </is>
       </c>
       <c r="B79" s="163" t="inlineStr">
@@ -41909,13 +41889,13 @@
       <c r="O79" s="164" t="n"/>
       <c r="P79" s="164" t="n"/>
       <c r="Q79" s="164" t="n">
-        <v>4.766687274392559</v>
+        <v>7.055371979667532</v>
       </c>
       <c r="R79" s="164" t="n">
-        <v>4.734315144837777</v>
+        <v>7.040255181823918</v>
       </c>
       <c r="S79" s="164" t="n">
-        <v>4.734315144837777</v>
+        <v>7.040255181823918</v>
       </c>
       <c r="T79" s="162" t="inlineStr">
         <is>
@@ -41932,7 +41912,7 @@
     <row r="80">
       <c r="A80" s="162" t="inlineStr">
         <is>
-          <t>Limpopo share of petrol</t>
+          <t>Free State share of petrol</t>
         </is>
       </c>
       <c r="B80" s="163" t="inlineStr">
@@ -41963,13 +41943,13 @@
       <c r="O80" s="164" t="n"/>
       <c r="P80" s="164" t="n"/>
       <c r="Q80" s="164" t="n">
-        <v>3.008852500759491</v>
+        <v>5.932159079461925</v>
       </c>
       <c r="R80" s="164" t="n">
-        <v>3.01928993993442</v>
+        <v>5.927995171497546</v>
       </c>
       <c r="S80" s="164" t="n">
-        <v>3.01928993993442</v>
+        <v>5.927995171497546</v>
       </c>
       <c r="T80" s="162" t="inlineStr">
         <is>
@@ -41986,7 +41966,7 @@
     <row r="81">
       <c r="A81" s="162" t="inlineStr">
         <is>
-          <t>Northern Cape share of petrol</t>
+          <t>North West share of petrol</t>
         </is>
       </c>
       <c r="B81" s="163" t="inlineStr">
@@ -42017,13 +41997,13 @@
       <c r="O81" s="164" t="n"/>
       <c r="P81" s="164" t="n"/>
       <c r="Q81" s="164" t="n">
-        <v>1.087764426006824</v>
+        <v>4.766687274392559</v>
       </c>
       <c r="R81" s="164" t="n">
-        <v>1.081219567108614</v>
+        <v>4.734315144837777</v>
       </c>
       <c r="S81" s="164" t="n">
-        <v>1.081219567108614</v>
+        <v>4.734315144837777</v>
       </c>
       <c r="T81" s="162" t="inlineStr">
         <is>
@@ -42040,12 +42020,12 @@
     <row r="82">
       <c r="A82" s="162" t="inlineStr">
         <is>
-          <t>Gauteng petrol, estimated</t>
+          <t>Limpopo share of petrol</t>
         </is>
       </c>
       <c r="B82" s="163" t="inlineStr">
         <is>
-          <t>million L/year</t>
+          <t>% of national</t>
         </is>
       </c>
       <c r="C82" s="163" t="inlineStr">
@@ -42053,56 +42033,53 @@
           <t>Proposed estimate</t>
         </is>
       </c>
-      <c r="D82" s="165" t="n"/>
+      <c r="D82" s="164" t="n"/>
       <c r="E82" s="162" t="inlineStr">
         <is>
-          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
-        </is>
-      </c>
-      <c r="F82" s="165" t="n"/>
-      <c r="G82" s="165" t="n"/>
-      <c r="H82" s="165" t="n"/>
-      <c r="I82" s="165" t="n"/>
-      <c r="J82" s="165" t="n"/>
-      <c r="K82" s="165" t="n"/>
-      <c r="L82" s="165" t="n"/>
-      <c r="M82" s="165" t="n"/>
-      <c r="N82" s="165" t="n"/>
-      <c r="O82" s="165" t="n"/>
-      <c r="P82" s="165" t="n"/>
-      <c r="Q82" s="165">
-        <f>IF(COUNT(Q73,Q57)&lt;2,"",Q73/100*Q57)</f>
-        <v/>
-      </c>
-      <c r="R82" s="165">
-        <f>IF(COUNT(R73,R57)&lt;2,"",R73/100*R57)</f>
-        <v/>
-      </c>
-      <c r="S82" s="165">
-        <f>IF(COUNT(S73,S57)&lt;2,"",S73/100*S57)</f>
-        <v/>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F82" s="164" t="n"/>
+      <c r="G82" s="164" t="n"/>
+      <c r="H82" s="164" t="n"/>
+      <c r="I82" s="164" t="n"/>
+      <c r="J82" s="164" t="n"/>
+      <c r="K82" s="164" t="n"/>
+      <c r="L82" s="164" t="n"/>
+      <c r="M82" s="164" t="n"/>
+      <c r="N82" s="164" t="n"/>
+      <c r="O82" s="164" t="n"/>
+      <c r="P82" s="164" t="n"/>
+      <c r="Q82" s="164" t="n">
+        <v>3.008852500759491</v>
+      </c>
+      <c r="R82" s="164" t="n">
+        <v>3.01928993993442</v>
+      </c>
+      <c r="S82" s="164" t="n">
+        <v>3.01928993993442</v>
       </c>
       <c r="T82" s="162" t="inlineStr">
         <is>
-          <t>Estimate; 2024 also carries the unverified national total</t>
-        </is>
-      </c>
-      <c r="U82" s="162" t="inlineStr"/>
-      <c r="V82" s="162" t="inlineStr">
-        <is>
-          <t>Replace when the department publishes district data after 2023 quarter 1</t>
-        </is>
-      </c>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U82" s="162" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V82" s="162" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="162" t="inlineStr">
         <is>
-          <t>KwaZulu-Natal petrol, estimated</t>
+          <t>Northern Cape share of petrol</t>
         </is>
       </c>
       <c r="B83" s="163" t="inlineStr">
         <is>
-          <t>million L/year</t>
+          <t>% of national</t>
         </is>
       </c>
       <c r="C83" s="163" t="inlineStr">
@@ -42110,51 +42087,48 @@
           <t>Proposed estimate</t>
         </is>
       </c>
-      <c r="D83" s="165" t="n"/>
+      <c r="D83" s="164" t="n"/>
       <c r="E83" s="162" t="inlineStr">
         <is>
-          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
-        </is>
-      </c>
-      <c r="F83" s="165" t="n"/>
-      <c r="G83" s="165" t="n"/>
-      <c r="H83" s="165" t="n"/>
-      <c r="I83" s="165" t="n"/>
-      <c r="J83" s="165" t="n"/>
-      <c r="K83" s="165" t="n"/>
-      <c r="L83" s="165" t="n"/>
-      <c r="M83" s="165" t="n"/>
-      <c r="N83" s="165" t="n"/>
-      <c r="O83" s="165" t="n"/>
-      <c r="P83" s="165" t="n"/>
-      <c r="Q83" s="165">
-        <f>IF(COUNT(Q74,Q57)&lt;2,"",Q74/100*Q57)</f>
-        <v/>
-      </c>
-      <c r="R83" s="165">
-        <f>IF(COUNT(R74,R57)&lt;2,"",R74/100*R57)</f>
-        <v/>
-      </c>
-      <c r="S83" s="165">
-        <f>IF(COUNT(S74,S57)&lt;2,"",S74/100*S57)</f>
-        <v/>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F83" s="164" t="n"/>
+      <c r="G83" s="164" t="n"/>
+      <c r="H83" s="164" t="n"/>
+      <c r="I83" s="164" t="n"/>
+      <c r="J83" s="164" t="n"/>
+      <c r="K83" s="164" t="n"/>
+      <c r="L83" s="164" t="n"/>
+      <c r="M83" s="164" t="n"/>
+      <c r="N83" s="164" t="n"/>
+      <c r="O83" s="164" t="n"/>
+      <c r="P83" s="164" t="n"/>
+      <c r="Q83" s="164" t="n">
+        <v>1.087764426006824</v>
+      </c>
+      <c r="R83" s="164" t="n">
+        <v>1.081219567108614</v>
+      </c>
+      <c r="S83" s="164" t="n">
+        <v>1.081219567108614</v>
       </c>
       <c r="T83" s="162" t="inlineStr">
         <is>
-          <t>Estimate; 2024 also carries the unverified national total</t>
-        </is>
-      </c>
-      <c r="U83" s="162" t="inlineStr"/>
-      <c r="V83" s="162" t="inlineStr">
-        <is>
-          <t>Replace when the department publishes district data after 2023 quarter 1</t>
-        </is>
-      </c>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U83" s="162" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V83" s="162" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="162" t="inlineStr">
         <is>
-          <t>Western Cape petrol, estimated</t>
+          <t>Gauteng petrol, estimated</t>
         </is>
       </c>
       <c r="B84" s="163" t="inlineStr">
@@ -42185,15 +42159,15 @@
       <c r="O84" s="165" t="n"/>
       <c r="P84" s="165" t="n"/>
       <c r="Q84" s="165">
-        <f>IF(COUNT(Q75,Q57)&lt;2,"",Q75/100*Q57)</f>
+        <f>IF(COUNT(Q75,Q59)&lt;2,"",Q75/100*Q59)</f>
         <v/>
       </c>
       <c r="R84" s="165">
-        <f>IF(COUNT(R75,R57)&lt;2,"",R75/100*R57)</f>
+        <f>IF(COUNT(R75,R59)&lt;2,"",R75/100*R59)</f>
         <v/>
       </c>
       <c r="S84" s="165">
-        <f>IF(COUNT(S75,S57)&lt;2,"",S75/100*S57)</f>
+        <f>IF(COUNT(S75,S59)&lt;2,"",S75/100*S59)</f>
         <v/>
       </c>
       <c r="T84" s="162" t="inlineStr">
@@ -42211,7 +42185,7 @@
     <row r="85">
       <c r="A85" s="162" t="inlineStr">
         <is>
-          <t>Eastern Cape petrol, estimated</t>
+          <t>KwaZulu-Natal petrol, estimated</t>
         </is>
       </c>
       <c r="B85" s="163" t="inlineStr">
@@ -42242,15 +42216,15 @@
       <c r="O85" s="165" t="n"/>
       <c r="P85" s="165" t="n"/>
       <c r="Q85" s="165">
-        <f>IF(COUNT(Q76,Q57)&lt;2,"",Q76/100*Q57)</f>
+        <f>IF(COUNT(Q76,Q59)&lt;2,"",Q76/100*Q59)</f>
         <v/>
       </c>
       <c r="R85" s="165">
-        <f>IF(COUNT(R76,R57)&lt;2,"",R76/100*R57)</f>
+        <f>IF(COUNT(R76,R59)&lt;2,"",R76/100*R59)</f>
         <v/>
       </c>
       <c r="S85" s="165">
-        <f>IF(COUNT(S76,S57)&lt;2,"",S76/100*S57)</f>
+        <f>IF(COUNT(S76,S59)&lt;2,"",S76/100*S59)</f>
         <v/>
       </c>
       <c r="T85" s="162" t="inlineStr">
@@ -42268,7 +42242,7 @@
     <row r="86">
       <c r="A86" s="162" t="inlineStr">
         <is>
-          <t>Mpumalanga petrol, estimated</t>
+          <t>Western Cape petrol, estimated</t>
         </is>
       </c>
       <c r="B86" s="163" t="inlineStr">
@@ -42299,15 +42273,15 @@
       <c r="O86" s="165" t="n"/>
       <c r="P86" s="165" t="n"/>
       <c r="Q86" s="165">
-        <f>IF(COUNT(Q77,Q57)&lt;2,"",Q77/100*Q57)</f>
+        <f>IF(COUNT(Q77,Q59)&lt;2,"",Q77/100*Q59)</f>
         <v/>
       </c>
       <c r="R86" s="165">
-        <f>IF(COUNT(R77,R57)&lt;2,"",R77/100*R57)</f>
+        <f>IF(COUNT(R77,R59)&lt;2,"",R77/100*R59)</f>
         <v/>
       </c>
       <c r="S86" s="165">
-        <f>IF(COUNT(S77,S57)&lt;2,"",S77/100*S57)</f>
+        <f>IF(COUNT(S77,S59)&lt;2,"",S77/100*S59)</f>
         <v/>
       </c>
       <c r="T86" s="162" t="inlineStr">
@@ -42325,7 +42299,7 @@
     <row r="87">
       <c r="A87" s="162" t="inlineStr">
         <is>
-          <t>Free State petrol, estimated</t>
+          <t>Eastern Cape petrol, estimated</t>
         </is>
       </c>
       <c r="B87" s="163" t="inlineStr">
@@ -42356,15 +42330,15 @@
       <c r="O87" s="165" t="n"/>
       <c r="P87" s="165" t="n"/>
       <c r="Q87" s="165">
-        <f>IF(COUNT(Q78,Q57)&lt;2,"",Q78/100*Q57)</f>
+        <f>IF(COUNT(Q78,Q59)&lt;2,"",Q78/100*Q59)</f>
         <v/>
       </c>
       <c r="R87" s="165">
-        <f>IF(COUNT(R78,R57)&lt;2,"",R78/100*R57)</f>
+        <f>IF(COUNT(R78,R59)&lt;2,"",R78/100*R59)</f>
         <v/>
       </c>
       <c r="S87" s="165">
-        <f>IF(COUNT(S78,S57)&lt;2,"",S78/100*S57)</f>
+        <f>IF(COUNT(S78,S59)&lt;2,"",S78/100*S59)</f>
         <v/>
       </c>
       <c r="T87" s="162" t="inlineStr">
@@ -42382,7 +42356,7 @@
     <row r="88">
       <c r="A88" s="162" t="inlineStr">
         <is>
-          <t>North West petrol, estimated</t>
+          <t>Mpumalanga petrol, estimated</t>
         </is>
       </c>
       <c r="B88" s="163" t="inlineStr">
@@ -42413,15 +42387,15 @@
       <c r="O88" s="165" t="n"/>
       <c r="P88" s="165" t="n"/>
       <c r="Q88" s="165">
-        <f>IF(COUNT(Q79,Q57)&lt;2,"",Q79/100*Q57)</f>
+        <f>IF(COUNT(Q79,Q59)&lt;2,"",Q79/100*Q59)</f>
         <v/>
       </c>
       <c r="R88" s="165">
-        <f>IF(COUNT(R79,R57)&lt;2,"",R79/100*R57)</f>
+        <f>IF(COUNT(R79,R59)&lt;2,"",R79/100*R59)</f>
         <v/>
       </c>
       <c r="S88" s="165">
-        <f>IF(COUNT(S79,S57)&lt;2,"",S79/100*S57)</f>
+        <f>IF(COUNT(S79,S59)&lt;2,"",S79/100*S59)</f>
         <v/>
       </c>
       <c r="T88" s="162" t="inlineStr">
@@ -42439,7 +42413,7 @@
     <row r="89">
       <c r="A89" s="162" t="inlineStr">
         <is>
-          <t>Limpopo petrol, estimated</t>
+          <t>Free State petrol, estimated</t>
         </is>
       </c>
       <c r="B89" s="163" t="inlineStr">
@@ -42470,15 +42444,15 @@
       <c r="O89" s="165" t="n"/>
       <c r="P89" s="165" t="n"/>
       <c r="Q89" s="165">
-        <f>IF(COUNT(Q80,Q57)&lt;2,"",Q80/100*Q57)</f>
+        <f>IF(COUNT(Q80,Q59)&lt;2,"",Q80/100*Q59)</f>
         <v/>
       </c>
       <c r="R89" s="165">
-        <f>IF(COUNT(R80,R57)&lt;2,"",R80/100*R57)</f>
+        <f>IF(COUNT(R80,R59)&lt;2,"",R80/100*R59)</f>
         <v/>
       </c>
       <c r="S89" s="165">
-        <f>IF(COUNT(S80,S57)&lt;2,"",S80/100*S57)</f>
+        <f>IF(COUNT(S80,S59)&lt;2,"",S80/100*S59)</f>
         <v/>
       </c>
       <c r="T89" s="162" t="inlineStr">
@@ -42496,7 +42470,7 @@
     <row r="90">
       <c r="A90" s="162" t="inlineStr">
         <is>
-          <t>Northern Cape petrol, estimated</t>
+          <t>North West petrol, estimated</t>
         </is>
       </c>
       <c r="B90" s="163" t="inlineStr">
@@ -42527,15 +42501,15 @@
       <c r="O90" s="165" t="n"/>
       <c r="P90" s="165" t="n"/>
       <c r="Q90" s="165">
-        <f>IF(COUNT(Q81,Q57)&lt;2,"",Q81/100*Q57)</f>
+        <f>IF(COUNT(Q81,Q59)&lt;2,"",Q81/100*Q59)</f>
         <v/>
       </c>
       <c r="R90" s="165">
-        <f>IF(COUNT(R81,R57)&lt;2,"",R81/100*R57)</f>
+        <f>IF(COUNT(R81,R59)&lt;2,"",R81/100*R59)</f>
         <v/>
       </c>
       <c r="S90" s="165">
-        <f>IF(COUNT(S81,S57)&lt;2,"",S81/100*S57)</f>
+        <f>IF(COUNT(S81,S59)&lt;2,"",S81/100*S59)</f>
         <v/>
       </c>
       <c r="T90" s="162" t="inlineStr">
@@ -42550,146 +42524,152 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="162" t="inlineStr">
+        <is>
+          <t>Limpopo petrol, estimated</t>
+        </is>
+      </c>
+      <c r="B91" s="163" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C91" s="163" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D91" s="165" t="n"/>
+      <c r="E91" s="162" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F91" s="165" t="n"/>
+      <c r="G91" s="165" t="n"/>
+      <c r="H91" s="165" t="n"/>
+      <c r="I91" s="165" t="n"/>
+      <c r="J91" s="165" t="n"/>
+      <c r="K91" s="165" t="n"/>
+      <c r="L91" s="165" t="n"/>
+      <c r="M91" s="165" t="n"/>
+      <c r="N91" s="165" t="n"/>
+      <c r="O91" s="165" t="n"/>
+      <c r="P91" s="165" t="n"/>
+      <c r="Q91" s="165">
+        <f>IF(COUNT(Q82,Q59)&lt;2,"",Q82/100*Q59)</f>
+        <v/>
+      </c>
+      <c r="R91" s="165">
+        <f>IF(COUNT(R82,R59)&lt;2,"",R82/100*R59)</f>
+        <v/>
+      </c>
+      <c r="S91" s="165">
+        <f>IF(COUNT(S82,S59)&lt;2,"",S82/100*S59)</f>
+        <v/>
+      </c>
+      <c r="T91" s="162" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U91" s="162" t="inlineStr"/>
+      <c r="V91" s="162" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
     <row r="92">
-      <c r="A92" s="151" t="inlineStr">
+      <c r="A92" s="162" t="inlineStr">
+        <is>
+          <t>Northern Cape petrol, estimated</t>
+        </is>
+      </c>
+      <c r="B92" s="163" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C92" s="163" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D92" s="165" t="n"/>
+      <c r="E92" s="162" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F92" s="165" t="n"/>
+      <c r="G92" s="165" t="n"/>
+      <c r="H92" s="165" t="n"/>
+      <c r="I92" s="165" t="n"/>
+      <c r="J92" s="165" t="n"/>
+      <c r="K92" s="165" t="n"/>
+      <c r="L92" s="165" t="n"/>
+      <c r="M92" s="165" t="n"/>
+      <c r="N92" s="165" t="n"/>
+      <c r="O92" s="165" t="n"/>
+      <c r="P92" s="165" t="n"/>
+      <c r="Q92" s="165">
+        <f>IF(COUNT(Q83,Q59)&lt;2,"",Q83/100*Q59)</f>
+        <v/>
+      </c>
+      <c r="R92" s="165">
+        <f>IF(COUNT(R83,R59)&lt;2,"",R83/100*R59)</f>
+        <v/>
+      </c>
+      <c r="S92" s="165">
+        <f>IF(COUNT(S83,S59)&lt;2,"",S83/100*S59)</f>
+        <v/>
+      </c>
+      <c r="T92" s="162" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U92" s="162" t="inlineStr"/>
+      <c r="V92" s="162" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="151" t="inlineStr">
         <is>
           <t>6. Estimated sales by province, 2023-2025: diesel (estimates, not observations)</t>
         </is>
       </c>
-      <c r="B92" s="151" t="n"/>
-      <c r="C92" s="151" t="n"/>
-      <c r="D92" s="151" t="n"/>
-      <c r="E92" s="151" t="n"/>
-      <c r="F92" s="151" t="n"/>
-      <c r="G92" s="151" t="n"/>
-      <c r="H92" s="151" t="n"/>
-      <c r="I92" s="151" t="n"/>
-      <c r="J92" s="151" t="n"/>
-      <c r="K92" s="151" t="n"/>
-      <c r="L92" s="151" t="n"/>
-      <c r="M92" s="151" t="n"/>
-      <c r="N92" s="151" t="n"/>
-      <c r="O92" s="151" t="n"/>
-      <c r="P92" s="151" t="n"/>
-      <c r="Q92" s="151" t="n"/>
-      <c r="R92" s="151" t="n"/>
-      <c r="S92" s="151" t="n"/>
-      <c r="T92" s="151" t="n"/>
-      <c r="U92" s="151" t="n"/>
-      <c r="V92" s="151" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="162" t="inlineStr">
-        <is>
-          <t>Gauteng share of diesel</t>
-        </is>
-      </c>
-      <c r="B93" s="163" t="inlineStr">
-        <is>
-          <t>% of national</t>
-        </is>
-      </c>
-      <c r="C93" s="163" t="inlineStr">
-        <is>
-          <t>Proposed estimate</t>
-        </is>
-      </c>
-      <c r="D93" s="164" t="n"/>
-      <c r="E93" s="162" t="inlineStr">
-        <is>
-          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
-        </is>
-      </c>
-      <c r="F93" s="164" t="n"/>
-      <c r="G93" s="164" t="n"/>
-      <c r="H93" s="164" t="n"/>
-      <c r="I93" s="164" t="n"/>
-      <c r="J93" s="164" t="n"/>
-      <c r="K93" s="164" t="n"/>
-      <c r="L93" s="164" t="n"/>
-      <c r="M93" s="164" t="n"/>
-      <c r="N93" s="164" t="n"/>
-      <c r="O93" s="164" t="n"/>
-      <c r="P93" s="164" t="n"/>
-      <c r="Q93" s="164" t="n">
-        <v>25.95571268012436</v>
-      </c>
-      <c r="R93" s="164" t="n">
-        <v>26.02351192632266</v>
-      </c>
-      <c r="S93" s="164" t="n">
-        <v>26.02351192632266</v>
-      </c>
-      <c r="T93" s="162" t="inlineStr">
-        <is>
-          <t>Estimate</t>
-        </is>
-      </c>
-      <c r="U93" s="162" t="inlineStr">
-        <is>
-          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
-        </is>
-      </c>
-      <c r="V93" s="162" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="162" t="inlineStr">
-        <is>
-          <t>KwaZulu-Natal share of diesel</t>
-        </is>
-      </c>
-      <c r="B94" s="163" t="inlineStr">
-        <is>
-          <t>% of national</t>
-        </is>
-      </c>
-      <c r="C94" s="163" t="inlineStr">
-        <is>
-          <t>Proposed estimate</t>
-        </is>
-      </c>
-      <c r="D94" s="164" t="n"/>
-      <c r="E94" s="162" t="inlineStr">
-        <is>
-          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
-        </is>
-      </c>
-      <c r="F94" s="164" t="n"/>
-      <c r="G94" s="164" t="n"/>
-      <c r="H94" s="164" t="n"/>
-      <c r="I94" s="164" t="n"/>
-      <c r="J94" s="164" t="n"/>
-      <c r="K94" s="164" t="n"/>
-      <c r="L94" s="164" t="n"/>
-      <c r="M94" s="164" t="n"/>
-      <c r="N94" s="164" t="n"/>
-      <c r="O94" s="164" t="n"/>
-      <c r="P94" s="164" t="n"/>
-      <c r="Q94" s="164" t="n">
-        <v>18.98574601235529</v>
-      </c>
-      <c r="R94" s="164" t="n">
-        <v>18.97178908483028</v>
-      </c>
-      <c r="S94" s="164" t="n">
-        <v>18.97178908483028</v>
-      </c>
-      <c r="T94" s="162" t="inlineStr">
-        <is>
-          <t>Estimate</t>
-        </is>
-      </c>
-      <c r="U94" s="162" t="inlineStr">
-        <is>
-          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
-        </is>
-      </c>
-      <c r="V94" s="162" t="inlineStr"/>
+      <c r="B94" s="151" t="n"/>
+      <c r="C94" s="151" t="n"/>
+      <c r="D94" s="151" t="n"/>
+      <c r="E94" s="151" t="n"/>
+      <c r="F94" s="151" t="n"/>
+      <c r="G94" s="151" t="n"/>
+      <c r="H94" s="151" t="n"/>
+      <c r="I94" s="151" t="n"/>
+      <c r="J94" s="151" t="n"/>
+      <c r="K94" s="151" t="n"/>
+      <c r="L94" s="151" t="n"/>
+      <c r="M94" s="151" t="n"/>
+      <c r="N94" s="151" t="n"/>
+      <c r="O94" s="151" t="n"/>
+      <c r="P94" s="151" t="n"/>
+      <c r="Q94" s="151" t="n"/>
+      <c r="R94" s="151" t="n"/>
+      <c r="S94" s="151" t="n"/>
+      <c r="T94" s="151" t="n"/>
+      <c r="U94" s="151" t="n"/>
+      <c r="V94" s="151" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="162" t="inlineStr">
         <is>
-          <t>Western Cape share of diesel</t>
+          <t>Gauteng share of diesel</t>
         </is>
       </c>
       <c r="B95" s="163" t="inlineStr">
@@ -42720,13 +42700,13 @@
       <c r="O95" s="164" t="n"/>
       <c r="P95" s="164" t="n"/>
       <c r="Q95" s="164" t="n">
-        <v>23.48567896125875</v>
+        <v>25.95571268012436</v>
       </c>
       <c r="R95" s="164" t="n">
-        <v>23.53970993881584</v>
+        <v>26.02351192632266</v>
       </c>
       <c r="S95" s="164" t="n">
-        <v>23.53970993881584</v>
+        <v>26.02351192632266</v>
       </c>
       <c r="T95" s="162" t="inlineStr">
         <is>
@@ -42743,7 +42723,7 @@
     <row r="96">
       <c r="A96" s="162" t="inlineStr">
         <is>
-          <t>Eastern Cape share of diesel</t>
+          <t>KwaZulu-Natal share of diesel</t>
         </is>
       </c>
       <c r="B96" s="163" t="inlineStr">
@@ -42774,13 +42754,13 @@
       <c r="O96" s="164" t="n"/>
       <c r="P96" s="164" t="n"/>
       <c r="Q96" s="164" t="n">
-        <v>7.89067723132441</v>
+        <v>18.98574601235529</v>
       </c>
       <c r="R96" s="164" t="n">
-        <v>7.83812278680507</v>
+        <v>18.97178908483028</v>
       </c>
       <c r="S96" s="164" t="n">
-        <v>7.83812278680507</v>
+        <v>18.97178908483028</v>
       </c>
       <c r="T96" s="162" t="inlineStr">
         <is>
@@ -42797,7 +42777,7 @@
     <row r="97">
       <c r="A97" s="162" t="inlineStr">
         <is>
-          <t>Mpumalanga share of diesel</t>
+          <t>Western Cape share of diesel</t>
         </is>
       </c>
       <c r="B97" s="163" t="inlineStr">
@@ -42828,13 +42808,13 @@
       <c r="O97" s="164" t="n"/>
       <c r="P97" s="164" t="n"/>
       <c r="Q97" s="164" t="n">
-        <v>9.154016030764375</v>
+        <v>23.48567896125875</v>
       </c>
       <c r="R97" s="164" t="n">
-        <v>9.137636223166661</v>
+        <v>23.53970993881584</v>
       </c>
       <c r="S97" s="164" t="n">
-        <v>9.137636223166661</v>
+        <v>23.53970993881584</v>
       </c>
       <c r="T97" s="162" t="inlineStr">
         <is>
@@ -42851,7 +42831,7 @@
     <row r="98">
       <c r="A98" s="162" t="inlineStr">
         <is>
-          <t>Free State share of diesel</t>
+          <t>Eastern Cape share of diesel</t>
         </is>
       </c>
       <c r="B98" s="163" t="inlineStr">
@@ -42882,13 +42862,13 @@
       <c r="O98" s="164" t="n"/>
       <c r="P98" s="164" t="n"/>
       <c r="Q98" s="164" t="n">
-        <v>5.426397730797064</v>
+        <v>7.89067723132441</v>
       </c>
       <c r="R98" s="164" t="n">
-        <v>5.42450839649958</v>
+        <v>7.83812278680507</v>
       </c>
       <c r="S98" s="164" t="n">
-        <v>5.42450839649958</v>
+        <v>7.83812278680507</v>
       </c>
       <c r="T98" s="162" t="inlineStr">
         <is>
@@ -42905,7 +42885,7 @@
     <row r="99">
       <c r="A99" s="162" t="inlineStr">
         <is>
-          <t>North West share of diesel</t>
+          <t>Mpumalanga share of diesel</t>
         </is>
       </c>
       <c r="B99" s="163" t="inlineStr">
@@ -42936,13 +42916,13 @@
       <c r="O99" s="164" t="n"/>
       <c r="P99" s="164" t="n"/>
       <c r="Q99" s="164" t="n">
-        <v>4.4050379640929</v>
+        <v>9.154016030764375</v>
       </c>
       <c r="R99" s="164" t="n">
-        <v>4.376670684154155</v>
+        <v>9.137636223166661</v>
       </c>
       <c r="S99" s="164" t="n">
-        <v>4.376670684154155</v>
+        <v>9.137636223166661</v>
       </c>
       <c r="T99" s="162" t="inlineStr">
         <is>
@@ -42959,7 +42939,7 @@
     <row r="100">
       <c r="A100" s="162" t="inlineStr">
         <is>
-          <t>Limpopo share of diesel</t>
+          <t>Free State share of diesel</t>
         </is>
       </c>
       <c r="B100" s="163" t="inlineStr">
@@ -42990,13 +42970,13 @@
       <c r="O100" s="164" t="n"/>
       <c r="P100" s="164" t="n"/>
       <c r="Q100" s="164" t="n">
-        <v>1.888937215844854</v>
+        <v>5.426397730797064</v>
       </c>
       <c r="R100" s="164" t="n">
-        <v>1.896160763259574</v>
+        <v>5.42450839649958</v>
       </c>
       <c r="S100" s="164" t="n">
-        <v>1.896160763259574</v>
+        <v>5.42450839649958</v>
       </c>
       <c r="T100" s="162" t="inlineStr">
         <is>
@@ -43013,7 +42993,7 @@
     <row r="101">
       <c r="A101" s="162" t="inlineStr">
         <is>
-          <t>Northern Cape share of diesel</t>
+          <t>North West share of diesel</t>
         </is>
       </c>
       <c r="B101" s="163" t="inlineStr">
@@ -43044,13 +43024,13 @@
       <c r="O101" s="164" t="n"/>
       <c r="P101" s="164" t="n"/>
       <c r="Q101" s="164" t="n">
-        <v>2.807796173437997</v>
+        <v>4.4050379640929</v>
       </c>
       <c r="R101" s="164" t="n">
-        <v>2.791890196146183</v>
+        <v>4.376670684154155</v>
       </c>
       <c r="S101" s="164" t="n">
-        <v>2.791890196146183</v>
+        <v>4.376670684154155</v>
       </c>
       <c r="T101" s="162" t="inlineStr">
         <is>
@@ -43067,12 +43047,12 @@
     <row r="102">
       <c r="A102" s="162" t="inlineStr">
         <is>
-          <t>Gauteng diesel, estimated</t>
+          <t>Limpopo share of diesel</t>
         </is>
       </c>
       <c r="B102" s="163" t="inlineStr">
         <is>
-          <t>million L/year</t>
+          <t>% of national</t>
         </is>
       </c>
       <c r="C102" s="163" t="inlineStr">
@@ -43080,56 +43060,53 @@
           <t>Proposed estimate</t>
         </is>
       </c>
-      <c r="D102" s="165" t="n"/>
+      <c r="D102" s="164" t="n"/>
       <c r="E102" s="162" t="inlineStr">
         <is>
-          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
-        </is>
-      </c>
-      <c r="F102" s="165" t="n"/>
-      <c r="G102" s="165" t="n"/>
-      <c r="H102" s="165" t="n"/>
-      <c r="I102" s="165" t="n"/>
-      <c r="J102" s="165" t="n"/>
-      <c r="K102" s="165" t="n"/>
-      <c r="L102" s="165" t="n"/>
-      <c r="M102" s="165" t="n"/>
-      <c r="N102" s="165" t="n"/>
-      <c r="O102" s="165" t="n"/>
-      <c r="P102" s="165" t="n"/>
-      <c r="Q102" s="165">
-        <f>IF(COUNT(Q93,Q62)&lt;2,"",Q93/100*Q62)</f>
-        <v/>
-      </c>
-      <c r="R102" s="165">
-        <f>IF(COUNT(R93,R62)&lt;2,"",R93/100*R62)</f>
-        <v/>
-      </c>
-      <c r="S102" s="165">
-        <f>IF(COUNT(S93,S62)&lt;2,"",S93/100*S62)</f>
-        <v/>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F102" s="164" t="n"/>
+      <c r="G102" s="164" t="n"/>
+      <c r="H102" s="164" t="n"/>
+      <c r="I102" s="164" t="n"/>
+      <c r="J102" s="164" t="n"/>
+      <c r="K102" s="164" t="n"/>
+      <c r="L102" s="164" t="n"/>
+      <c r="M102" s="164" t="n"/>
+      <c r="N102" s="164" t="n"/>
+      <c r="O102" s="164" t="n"/>
+      <c r="P102" s="164" t="n"/>
+      <c r="Q102" s="164" t="n">
+        <v>1.888937215844854</v>
+      </c>
+      <c r="R102" s="164" t="n">
+        <v>1.896160763259574</v>
+      </c>
+      <c r="S102" s="164" t="n">
+        <v>1.896160763259574</v>
       </c>
       <c r="T102" s="162" t="inlineStr">
         <is>
-          <t>Estimate; 2024 also carries the unverified national total</t>
-        </is>
-      </c>
-      <c r="U102" s="162" t="inlineStr"/>
-      <c r="V102" s="162" t="inlineStr">
-        <is>
-          <t>Replace when the department publishes district data after 2023 quarter 1</t>
-        </is>
-      </c>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U102" s="162" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V102" s="162" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="162" t="inlineStr">
         <is>
-          <t>KwaZulu-Natal diesel, estimated</t>
+          <t>Northern Cape share of diesel</t>
         </is>
       </c>
       <c r="B103" s="163" t="inlineStr">
         <is>
-          <t>million L/year</t>
+          <t>% of national</t>
         </is>
       </c>
       <c r="C103" s="163" t="inlineStr">
@@ -43137,51 +43114,48 @@
           <t>Proposed estimate</t>
         </is>
       </c>
-      <c r="D103" s="165" t="n"/>
+      <c r="D103" s="164" t="n"/>
       <c r="E103" s="162" t="inlineStr">
         <is>
-          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
-        </is>
-      </c>
-      <c r="F103" s="165" t="n"/>
-      <c r="G103" s="165" t="n"/>
-      <c r="H103" s="165" t="n"/>
-      <c r="I103" s="165" t="n"/>
-      <c r="J103" s="165" t="n"/>
-      <c r="K103" s="165" t="n"/>
-      <c r="L103" s="165" t="n"/>
-      <c r="M103" s="165" t="n"/>
-      <c r="N103" s="165" t="n"/>
-      <c r="O103" s="165" t="n"/>
-      <c r="P103" s="165" t="n"/>
-      <c r="Q103" s="165">
-        <f>IF(COUNT(Q94,Q62)&lt;2,"",Q94/100*Q62)</f>
-        <v/>
-      </c>
-      <c r="R103" s="165">
-        <f>IF(COUNT(R94,R62)&lt;2,"",R94/100*R62)</f>
-        <v/>
-      </c>
-      <c r="S103" s="165">
-        <f>IF(COUNT(S94,S62)&lt;2,"",S94/100*S62)</f>
-        <v/>
+          <t>2023: the province's share of quarter 1 2023 sales, as observed. 2024: the 2023 share moved with the province's share of real GDP. 2025: 2024 held.</t>
+        </is>
+      </c>
+      <c r="F103" s="164" t="n"/>
+      <c r="G103" s="164" t="n"/>
+      <c r="H103" s="164" t="n"/>
+      <c r="I103" s="164" t="n"/>
+      <c r="J103" s="164" t="n"/>
+      <c r="K103" s="164" t="n"/>
+      <c r="L103" s="164" t="n"/>
+      <c r="M103" s="164" t="n"/>
+      <c r="N103" s="164" t="n"/>
+      <c r="O103" s="164" t="n"/>
+      <c r="P103" s="164" t="n"/>
+      <c r="Q103" s="164" t="n">
+        <v>2.807796173437997</v>
+      </c>
+      <c r="R103" s="164" t="n">
+        <v>2.791890196146183</v>
+      </c>
+      <c r="S103" s="164" t="n">
+        <v>2.791890196146183</v>
       </c>
       <c r="T103" s="162" t="inlineStr">
         <is>
-          <t>Estimate; 2024 also carries the unverified national total</t>
-        </is>
-      </c>
-      <c r="U103" s="162" t="inlineStr"/>
-      <c r="V103" s="162" t="inlineStr">
-        <is>
-          <t>Replace when the department publishes district data after 2023 quarter 1</t>
-        </is>
-      </c>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="U103" s="162" t="inlineStr">
+        <is>
+          <t>Department district data, quarter 1 2023; Stats SA P0441.2</t>
+        </is>
+      </c>
+      <c r="V103" s="162" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="162" t="inlineStr">
         <is>
-          <t>Western Cape diesel, estimated</t>
+          <t>Gauteng diesel, estimated</t>
         </is>
       </c>
       <c r="B104" s="163" t="inlineStr">
@@ -43212,15 +43186,15 @@
       <c r="O104" s="165" t="n"/>
       <c r="P104" s="165" t="n"/>
       <c r="Q104" s="165">
-        <f>IF(COUNT(Q95,Q62)&lt;2,"",Q95/100*Q62)</f>
+        <f>IF(COUNT(Q95,Q64)&lt;2,"",Q95/100*Q64)</f>
         <v/>
       </c>
       <c r="R104" s="165">
-        <f>IF(COUNT(R95,R62)&lt;2,"",R95/100*R62)</f>
+        <f>IF(COUNT(R95,R64)&lt;2,"",R95/100*R64)</f>
         <v/>
       </c>
       <c r="S104" s="165">
-        <f>IF(COUNT(S95,S62)&lt;2,"",S95/100*S62)</f>
+        <f>IF(COUNT(S95,S64)&lt;2,"",S95/100*S64)</f>
         <v/>
       </c>
       <c r="T104" s="162" t="inlineStr">
@@ -43238,7 +43212,7 @@
     <row r="105">
       <c r="A105" s="162" t="inlineStr">
         <is>
-          <t>Eastern Cape diesel, estimated</t>
+          <t>KwaZulu-Natal diesel, estimated</t>
         </is>
       </c>
       <c r="B105" s="163" t="inlineStr">
@@ -43269,15 +43243,15 @@
       <c r="O105" s="165" t="n"/>
       <c r="P105" s="165" t="n"/>
       <c r="Q105" s="165">
-        <f>IF(COUNT(Q96,Q62)&lt;2,"",Q96/100*Q62)</f>
+        <f>IF(COUNT(Q96,Q64)&lt;2,"",Q96/100*Q64)</f>
         <v/>
       </c>
       <c r="R105" s="165">
-        <f>IF(COUNT(R96,R62)&lt;2,"",R96/100*R62)</f>
+        <f>IF(COUNT(R96,R64)&lt;2,"",R96/100*R64)</f>
         <v/>
       </c>
       <c r="S105" s="165">
-        <f>IF(COUNT(S96,S62)&lt;2,"",S96/100*S62)</f>
+        <f>IF(COUNT(S96,S64)&lt;2,"",S96/100*S64)</f>
         <v/>
       </c>
       <c r="T105" s="162" t="inlineStr">
@@ -43295,7 +43269,7 @@
     <row r="106">
       <c r="A106" s="162" t="inlineStr">
         <is>
-          <t>Mpumalanga diesel, estimated</t>
+          <t>Western Cape diesel, estimated</t>
         </is>
       </c>
       <c r="B106" s="163" t="inlineStr">
@@ -43326,15 +43300,15 @@
       <c r="O106" s="165" t="n"/>
       <c r="P106" s="165" t="n"/>
       <c r="Q106" s="165">
-        <f>IF(COUNT(Q97,Q62)&lt;2,"",Q97/100*Q62)</f>
+        <f>IF(COUNT(Q97,Q64)&lt;2,"",Q97/100*Q64)</f>
         <v/>
       </c>
       <c r="R106" s="165">
-        <f>IF(COUNT(R97,R62)&lt;2,"",R97/100*R62)</f>
+        <f>IF(COUNT(R97,R64)&lt;2,"",R97/100*R64)</f>
         <v/>
       </c>
       <c r="S106" s="165">
-        <f>IF(COUNT(S97,S62)&lt;2,"",S97/100*S62)</f>
+        <f>IF(COUNT(S97,S64)&lt;2,"",S97/100*S64)</f>
         <v/>
       </c>
       <c r="T106" s="162" t="inlineStr">
@@ -43352,7 +43326,7 @@
     <row r="107">
       <c r="A107" s="162" t="inlineStr">
         <is>
-          <t>Free State diesel, estimated</t>
+          <t>Eastern Cape diesel, estimated</t>
         </is>
       </c>
       <c r="B107" s="163" t="inlineStr">
@@ -43383,15 +43357,15 @@
       <c r="O107" s="165" t="n"/>
       <c r="P107" s="165" t="n"/>
       <c r="Q107" s="165">
-        <f>IF(COUNT(Q98,Q62)&lt;2,"",Q98/100*Q62)</f>
+        <f>IF(COUNT(Q98,Q64)&lt;2,"",Q98/100*Q64)</f>
         <v/>
       </c>
       <c r="R107" s="165">
-        <f>IF(COUNT(R98,R62)&lt;2,"",R98/100*R62)</f>
+        <f>IF(COUNT(R98,R64)&lt;2,"",R98/100*R64)</f>
         <v/>
       </c>
       <c r="S107" s="165">
-        <f>IF(COUNT(S98,S62)&lt;2,"",S98/100*S62)</f>
+        <f>IF(COUNT(S98,S64)&lt;2,"",S98/100*S64)</f>
         <v/>
       </c>
       <c r="T107" s="162" t="inlineStr">
@@ -43409,7 +43383,7 @@
     <row r="108">
       <c r="A108" s="162" t="inlineStr">
         <is>
-          <t>North West diesel, estimated</t>
+          <t>Mpumalanga diesel, estimated</t>
         </is>
       </c>
       <c r="B108" s="163" t="inlineStr">
@@ -43440,15 +43414,15 @@
       <c r="O108" s="165" t="n"/>
       <c r="P108" s="165" t="n"/>
       <c r="Q108" s="165">
-        <f>IF(COUNT(Q99,Q62)&lt;2,"",Q99/100*Q62)</f>
+        <f>IF(COUNT(Q99,Q64)&lt;2,"",Q99/100*Q64)</f>
         <v/>
       </c>
       <c r="R108" s="165">
-        <f>IF(COUNT(R99,R62)&lt;2,"",R99/100*R62)</f>
+        <f>IF(COUNT(R99,R64)&lt;2,"",R99/100*R64)</f>
         <v/>
       </c>
       <c r="S108" s="165">
-        <f>IF(COUNT(S99,S62)&lt;2,"",S99/100*S62)</f>
+        <f>IF(COUNT(S99,S64)&lt;2,"",S99/100*S64)</f>
         <v/>
       </c>
       <c r="T108" s="162" t="inlineStr">
@@ -43466,7 +43440,7 @@
     <row r="109">
       <c r="A109" s="162" t="inlineStr">
         <is>
-          <t>Limpopo diesel, estimated</t>
+          <t>Free State diesel, estimated</t>
         </is>
       </c>
       <c r="B109" s="163" t="inlineStr">
@@ -43497,15 +43471,15 @@
       <c r="O109" s="165" t="n"/>
       <c r="P109" s="165" t="n"/>
       <c r="Q109" s="165">
-        <f>IF(COUNT(Q100,Q62)&lt;2,"",Q100/100*Q62)</f>
+        <f>IF(COUNT(Q100,Q64)&lt;2,"",Q100/100*Q64)</f>
         <v/>
       </c>
       <c r="R109" s="165">
-        <f>IF(COUNT(R100,R62)&lt;2,"",R100/100*R62)</f>
+        <f>IF(COUNT(R100,R64)&lt;2,"",R100/100*R64)</f>
         <v/>
       </c>
       <c r="S109" s="165">
-        <f>IF(COUNT(S100,S62)&lt;2,"",S100/100*S62)</f>
+        <f>IF(COUNT(S100,S64)&lt;2,"",S100/100*S64)</f>
         <v/>
       </c>
       <c r="T109" s="162" t="inlineStr">
@@ -43523,7 +43497,7 @@
     <row r="110">
       <c r="A110" s="162" t="inlineStr">
         <is>
-          <t>Northern Cape diesel, estimated</t>
+          <t>North West diesel, estimated</t>
         </is>
       </c>
       <c r="B110" s="163" t="inlineStr">
@@ -43554,15 +43528,15 @@
       <c r="O110" s="165" t="n"/>
       <c r="P110" s="165" t="n"/>
       <c r="Q110" s="165">
-        <f>IF(COUNT(Q101,Q62)&lt;2,"",Q101/100*Q62)</f>
+        <f>IF(COUNT(Q101,Q64)&lt;2,"",Q101/100*Q64)</f>
         <v/>
       </c>
       <c r="R110" s="165">
-        <f>IF(COUNT(R101,R62)&lt;2,"",R101/100*R62)</f>
+        <f>IF(COUNT(R101,R64)&lt;2,"",R101/100*R64)</f>
         <v/>
       </c>
       <c r="S110" s="165">
-        <f>IF(COUNT(S101,S62)&lt;2,"",S101/100*S62)</f>
+        <f>IF(COUNT(S101,S64)&lt;2,"",S101/100*S64)</f>
         <v/>
       </c>
       <c r="T110" s="162" t="inlineStr">
@@ -43572,6 +43546,120 @@
       </c>
       <c r="U110" s="162" t="inlineStr"/>
       <c r="V110" s="162" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="162" t="inlineStr">
+        <is>
+          <t>Limpopo diesel, estimated</t>
+        </is>
+      </c>
+      <c r="B111" s="163" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C111" s="163" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D111" s="165" t="n"/>
+      <c r="E111" s="162" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F111" s="165" t="n"/>
+      <c r="G111" s="165" t="n"/>
+      <c r="H111" s="165" t="n"/>
+      <c r="I111" s="165" t="n"/>
+      <c r="J111" s="165" t="n"/>
+      <c r="K111" s="165" t="n"/>
+      <c r="L111" s="165" t="n"/>
+      <c r="M111" s="165" t="n"/>
+      <c r="N111" s="165" t="n"/>
+      <c r="O111" s="165" t="n"/>
+      <c r="P111" s="165" t="n"/>
+      <c r="Q111" s="165">
+        <f>IF(COUNT(Q102,Q64)&lt;2,"",Q102/100*Q64)</f>
+        <v/>
+      </c>
+      <c r="R111" s="165">
+        <f>IF(COUNT(R102,R64)&lt;2,"",R102/100*R64)</f>
+        <v/>
+      </c>
+      <c r="S111" s="165">
+        <f>IF(COUNT(S102,S64)&lt;2,"",S102/100*S64)</f>
+        <v/>
+      </c>
+      <c r="T111" s="162" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U111" s="162" t="inlineStr"/>
+      <c r="V111" s="162" t="inlineStr">
+        <is>
+          <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="162" t="inlineStr">
+        <is>
+          <t>Northern Cape diesel, estimated</t>
+        </is>
+      </c>
+      <c r="B112" s="163" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C112" s="163" t="inlineStr">
+        <is>
+          <t>Proposed estimate</t>
+        </is>
+      </c>
+      <c r="D112" s="165" t="n"/>
+      <c r="E112" s="162" t="inlineStr">
+        <is>
+          <t>Estimated share times national sales used (section 4). Blank where no national figure exists.</t>
+        </is>
+      </c>
+      <c r="F112" s="165" t="n"/>
+      <c r="G112" s="165" t="n"/>
+      <c r="H112" s="165" t="n"/>
+      <c r="I112" s="165" t="n"/>
+      <c r="J112" s="165" t="n"/>
+      <c r="K112" s="165" t="n"/>
+      <c r="L112" s="165" t="n"/>
+      <c r="M112" s="165" t="n"/>
+      <c r="N112" s="165" t="n"/>
+      <c r="O112" s="165" t="n"/>
+      <c r="P112" s="165" t="n"/>
+      <c r="Q112" s="165">
+        <f>IF(COUNT(Q103,Q64)&lt;2,"",Q103/100*Q64)</f>
+        <v/>
+      </c>
+      <c r="R112" s="165">
+        <f>IF(COUNT(R103,R64)&lt;2,"",R103/100*R64)</f>
+        <v/>
+      </c>
+      <c r="S112" s="165">
+        <f>IF(COUNT(S103,S64)&lt;2,"",S103/100*S64)</f>
+        <v/>
+      </c>
+      <c r="T112" s="162" t="inlineStr">
+        <is>
+          <t>Estimate; 2024 also carries the unverified national total</t>
+        </is>
+      </c>
+      <c r="U112" s="162" t="inlineStr"/>
+      <c r="V112" s="162" t="inlineStr">
         <is>
           <t>Replace when the department publishes district data after 2023 quarter 1</t>
         </is>
@@ -45117,59 +45205,59 @@
         </is>
       </c>
       <c r="F6" s="158">
-        <f>IF(ISNUMBER(History!F62),History!F62,"")</f>
+        <f>IF(ISNUMBER(History!F64),History!F64,"")</f>
         <v/>
       </c>
       <c r="G6" s="158">
-        <f>IF(ISNUMBER(History!G62),History!G62,"")</f>
+        <f>IF(ISNUMBER(History!G64),History!G64,"")</f>
         <v/>
       </c>
       <c r="H6" s="158">
-        <f>IF(ISNUMBER(History!H62),History!H62,"")</f>
+        <f>IF(ISNUMBER(History!H64),History!H64,"")</f>
         <v/>
       </c>
       <c r="I6" s="158">
-        <f>IF(ISNUMBER(History!I62),History!I62,"")</f>
+        <f>IF(ISNUMBER(History!I64),History!I64,"")</f>
         <v/>
       </c>
       <c r="J6" s="158">
-        <f>IF(ISNUMBER(History!J62),History!J62,"")</f>
+        <f>IF(ISNUMBER(History!J64),History!J64,"")</f>
         <v/>
       </c>
       <c r="K6" s="158">
-        <f>IF(ISNUMBER(History!K62),History!K62,"")</f>
+        <f>IF(ISNUMBER(History!K64),History!K64,"")</f>
         <v/>
       </c>
       <c r="L6" s="158">
-        <f>IF(ISNUMBER(History!L62),History!L62,"")</f>
+        <f>IF(ISNUMBER(History!L64),History!L64,"")</f>
         <v/>
       </c>
       <c r="M6" s="158">
-        <f>IF(ISNUMBER(History!M62),History!M62,"")</f>
+        <f>IF(ISNUMBER(History!M64),History!M64,"")</f>
         <v/>
       </c>
       <c r="N6" s="158">
-        <f>IF(ISNUMBER(History!N62),History!N62,"")</f>
+        <f>IF(ISNUMBER(History!N64),History!N64,"")</f>
         <v/>
       </c>
       <c r="O6" s="158">
-        <f>IF(ISNUMBER(History!O62),History!O62,"")</f>
+        <f>IF(ISNUMBER(History!O64),History!O64,"")</f>
         <v/>
       </c>
       <c r="P6" s="158">
-        <f>IF(ISNUMBER(History!P62),History!P62,"")</f>
+        <f>IF(ISNUMBER(History!P64),History!P64,"")</f>
         <v/>
       </c>
       <c r="Q6" s="158">
-        <f>IF(ISNUMBER(History!Q62),History!Q62,"")</f>
+        <f>IF(ISNUMBER(History!Q64),History!Q64,"")</f>
         <v/>
       </c>
       <c r="R6" s="158">
-        <f>IF(ISNUMBER(History!R62),History!R62,"")</f>
+        <f>IF(ISNUMBER(History!R64),History!R64,"")</f>
         <v/>
       </c>
       <c r="S6" s="158">
-        <f>IF(ISNUMBER(History!S62),History!S62,"")</f>
+        <f>IF(ISNUMBER(History!S64),History!S64,"")</f>
         <v/>
       </c>
       <c r="T6" s="156" t="inlineStr">
@@ -51965,59 +52053,59 @@
         </is>
       </c>
       <c r="F52" s="171">
-        <f>IF(COUNT(History!F57,F39)&lt;2,"",History!F57*1000000/F39)</f>
+        <f>IF(COUNT(History!F59,F39)&lt;2,"",History!F59*1000000/F39)</f>
         <v/>
       </c>
       <c r="G52" s="171">
-        <f>IF(COUNT(History!G57,G39)&lt;2,"",History!G57*1000000/G39)</f>
+        <f>IF(COUNT(History!G59,G39)&lt;2,"",History!G59*1000000/G39)</f>
         <v/>
       </c>
       <c r="H52" s="171">
-        <f>IF(COUNT(History!H57,H39)&lt;2,"",History!H57*1000000/H39)</f>
+        <f>IF(COUNT(History!H59,H39)&lt;2,"",History!H59*1000000/H39)</f>
         <v/>
       </c>
       <c r="I52" s="171">
-        <f>IF(COUNT(History!I57,I39)&lt;2,"",History!I57*1000000/I39)</f>
+        <f>IF(COUNT(History!I59,I39)&lt;2,"",History!I59*1000000/I39)</f>
         <v/>
       </c>
       <c r="J52" s="171">
-        <f>IF(COUNT(History!J57,J39)&lt;2,"",History!J57*1000000/J39)</f>
+        <f>IF(COUNT(History!J59,J39)&lt;2,"",History!J59*1000000/J39)</f>
         <v/>
       </c>
       <c r="K52" s="171">
-        <f>IF(COUNT(History!K57,K39)&lt;2,"",History!K57*1000000/K39)</f>
+        <f>IF(COUNT(History!K59,K39)&lt;2,"",History!K59*1000000/K39)</f>
         <v/>
       </c>
       <c r="L52" s="171">
-        <f>IF(COUNT(History!L57,L39)&lt;2,"",History!L57*1000000/L39)</f>
+        <f>IF(COUNT(History!L59,L39)&lt;2,"",History!L59*1000000/L39)</f>
         <v/>
       </c>
       <c r="M52" s="171">
-        <f>IF(COUNT(History!M57,M39)&lt;2,"",History!M57*1000000/M39)</f>
+        <f>IF(COUNT(History!M59,M39)&lt;2,"",History!M59*1000000/M39)</f>
         <v/>
       </c>
       <c r="N52" s="171">
-        <f>IF(COUNT(History!N57,N39)&lt;2,"",History!N57*1000000/N39)</f>
+        <f>IF(COUNT(History!N59,N39)&lt;2,"",History!N59*1000000/N39)</f>
         <v/>
       </c>
       <c r="O52" s="171">
-        <f>IF(COUNT(History!O57,O39)&lt;2,"",History!O57*1000000/O39)</f>
+        <f>IF(COUNT(History!O59,O39)&lt;2,"",History!O59*1000000/O39)</f>
         <v/>
       </c>
       <c r="P52" s="171">
-        <f>IF(COUNT(History!P57,P39)&lt;2,"",History!P57*1000000/P39)</f>
+        <f>IF(COUNT(History!P59,P39)&lt;2,"",History!P59*1000000/P39)</f>
         <v/>
       </c>
       <c r="Q52" s="171">
-        <f>IF(COUNT(History!Q57,Q39)&lt;2,"",History!Q57*1000000/Q39)</f>
+        <f>IF(COUNT(History!Q59,Q39)&lt;2,"",History!Q59*1000000/Q39)</f>
         <v/>
       </c>
       <c r="R52" s="171">
-        <f>IF(COUNT(History!R57,R39)&lt;2,"",History!R57*1000000/R39)</f>
+        <f>IF(COUNT(History!R59,R39)&lt;2,"",History!R59*1000000/R39)</f>
         <v/>
       </c>
       <c r="S52" s="171">
-        <f>IF(COUNT(History!S57,S39)&lt;2,"",History!S57*1000000/S39)</f>
+        <f>IF(COUNT(History!S59,S39)&lt;2,"",History!S59*1000000/S39)</f>
         <v/>
       </c>
       <c r="T52" s="156" t="inlineStr"/>

--- a/output/delivered/Demand_baseline_workshop_2026_10_08_history.xlsx
+++ b/output/delivered/Demand_baseline_workshop_2026_10_08_history.xlsx
@@ -23,8 +23,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector history" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diesel by use" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vehicle history" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History sources" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HML response" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap status" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History sources" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -678,10 +680,13 @@
     <xf numFmtId="164" fontId="1" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="1" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="168" fontId="1" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -693,17 +698,14 @@
     <xf numFmtId="168" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -36924,7 +36926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V112"/>
+  <dimension ref="A1:V125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -43662,6 +43664,872 @@
       <c r="V112" s="162" t="inlineStr">
         <is>
           <t>Replace when the department publishes district data after 2023 quarter 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="151" t="inlineStr">
+        <is>
+          <t>7. Jet fuel: sales, trade, production and aircraft movements</t>
+        </is>
+      </c>
+      <c r="B114" s="151" t="n"/>
+      <c r="C114" s="151" t="n"/>
+      <c r="D114" s="151" t="n"/>
+      <c r="E114" s="151" t="n"/>
+      <c r="F114" s="151" t="n"/>
+      <c r="G114" s="151" t="n"/>
+      <c r="H114" s="151" t="n"/>
+      <c r="I114" s="151" t="n"/>
+      <c r="J114" s="151" t="n"/>
+      <c r="K114" s="151" t="n"/>
+      <c r="L114" s="151" t="n"/>
+      <c r="M114" s="151" t="n"/>
+      <c r="N114" s="151" t="n"/>
+      <c r="O114" s="151" t="n"/>
+      <c r="P114" s="151" t="n"/>
+      <c r="Q114" s="151" t="n"/>
+      <c r="R114" s="151" t="n"/>
+      <c r="S114" s="151" t="n"/>
+      <c r="T114" s="151" t="n"/>
+      <c r="U114" s="151" t="n"/>
+      <c r="V114" s="151" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="152" t="inlineStr">
+        <is>
+          <t>Department national file, jet</t>
+        </is>
+      </c>
+      <c r="B115" s="153" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C115" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D115" s="154" t="n"/>
+      <c r="E115" s="152" t="inlineStr">
+        <is>
+          <t>National annual workbook, years with four quarters reported.</t>
+        </is>
+      </c>
+      <c r="F115" s="154" t="n">
+        <v>2431.08548</v>
+      </c>
+      <c r="G115" s="154" t="n">
+        <v>2305.651372</v>
+      </c>
+      <c r="H115" s="154" t="n">
+        <v>2293.018714</v>
+      </c>
+      <c r="I115" s="154" t="n">
+        <v>2457.95129655</v>
+      </c>
+      <c r="J115" s="154" t="n">
+        <v>2598.760123418</v>
+      </c>
+      <c r="K115" s="154" t="n">
+        <v>2712.662668234242</v>
+      </c>
+      <c r="L115" s="154" t="n">
+        <v>2346.059526818</v>
+      </c>
+      <c r="M115" s="154" t="n">
+        <v>2438.852598017</v>
+      </c>
+      <c r="N115" s="154" t="n">
+        <v>1090.817659253</v>
+      </c>
+      <c r="O115" s="154" t="n">
+        <v>1047.881004178</v>
+      </c>
+      <c r="P115" s="154" t="n">
+        <v>1478.149852603</v>
+      </c>
+      <c r="Q115" s="154" t="n">
+        <v>1843.971762465</v>
+      </c>
+      <c r="R115" s="154" t="n"/>
+      <c r="S115" s="154" t="n"/>
+      <c r="T115" s="152" t="inlineStr">
+        <is>
+          <t>2012-2023</t>
+        </is>
+      </c>
+      <c r="U115" s="152" t="inlineStr">
+        <is>
+          <t>Department of Mineral and Petroleum Resources, sales volumes, national workbooks</t>
+        </is>
+      </c>
+      <c r="V115" s="152" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="159" t="inlineStr">
+        <is>
+          <t>FIASA sales, jet</t>
+        </is>
+      </c>
+      <c r="B116" s="160" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C116" s="160" t="inlineStr">
+        <is>
+          <t>Comparison only</t>
+        </is>
+      </c>
+      <c r="D116" s="161" t="n"/>
+      <c r="E116" s="159" t="inlineStr">
+        <is>
+          <t>FIASA annual report, latest edition.</t>
+        </is>
+      </c>
+      <c r="F116" s="161" t="n">
+        <v>2367</v>
+      </c>
+      <c r="G116" s="161" t="n">
+        <v>2223</v>
+      </c>
+      <c r="H116" s="161" t="n">
+        <v>2197</v>
+      </c>
+      <c r="I116" s="161" t="n">
+        <v>2441</v>
+      </c>
+      <c r="J116" s="161" t="n">
+        <v>2121</v>
+      </c>
+      <c r="K116" s="161" t="n">
+        <v>2713</v>
+      </c>
+      <c r="L116" s="161" t="n">
+        <v>2346</v>
+      </c>
+      <c r="M116" s="161" t="n">
+        <v>2439</v>
+      </c>
+      <c r="N116" s="161" t="n">
+        <v>1091</v>
+      </c>
+      <c r="O116" s="161" t="n">
+        <v>1048</v>
+      </c>
+      <c r="P116" s="161" t="n">
+        <v>1478</v>
+      </c>
+      <c r="Q116" s="161" t="n">
+        <v>1844</v>
+      </c>
+      <c r="R116" s="161" t="n">
+        <v>1955</v>
+      </c>
+      <c r="S116" s="161" t="n"/>
+      <c r="T116" s="159" t="inlineStr">
+        <is>
+          <t>2024: 1,754 in FIASA's 2024 edition, 1,955 in its 2025 edition</t>
+        </is>
+      </c>
+      <c r="U116" s="159" t="inlineStr">
+        <is>
+          <t>Fuels Industry Association of South Africa, annual reports</t>
+        </is>
+      </c>
+      <c r="V116" s="159" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="156" t="inlineStr">
+        <is>
+          <t>Sales used, jet</t>
+        </is>
+      </c>
+      <c r="B117" s="157" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C117" s="157" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D117" s="158" t="n"/>
+      <c r="E117" s="156" t="inlineStr">
+        <is>
+          <t>Department where published; otherwise FIASA, unverified.</t>
+        </is>
+      </c>
+      <c r="F117" s="158">
+        <f>IF(ISNUMBER(F115),F115,IF(ISNUMBER(F116),F116,""))</f>
+        <v/>
+      </c>
+      <c r="G117" s="158">
+        <f>IF(ISNUMBER(G115),G115,IF(ISNUMBER(G116),G116,""))</f>
+        <v/>
+      </c>
+      <c r="H117" s="158">
+        <f>IF(ISNUMBER(H115),H115,IF(ISNUMBER(H116),H116,""))</f>
+        <v/>
+      </c>
+      <c r="I117" s="158">
+        <f>IF(ISNUMBER(I115),I115,IF(ISNUMBER(I116),I116,""))</f>
+        <v/>
+      </c>
+      <c r="J117" s="158">
+        <f>IF(ISNUMBER(J115),J115,IF(ISNUMBER(J116),J116,""))</f>
+        <v/>
+      </c>
+      <c r="K117" s="158">
+        <f>IF(ISNUMBER(K115),K115,IF(ISNUMBER(K116),K116,""))</f>
+        <v/>
+      </c>
+      <c r="L117" s="158">
+        <f>IF(ISNUMBER(L115),L115,IF(ISNUMBER(L116),L116,""))</f>
+        <v/>
+      </c>
+      <c r="M117" s="158">
+        <f>IF(ISNUMBER(M115),M115,IF(ISNUMBER(M116),M116,""))</f>
+        <v/>
+      </c>
+      <c r="N117" s="158">
+        <f>IF(ISNUMBER(N115),N115,IF(ISNUMBER(N116),N116,""))</f>
+        <v/>
+      </c>
+      <c r="O117" s="158">
+        <f>IF(ISNUMBER(O115),O115,IF(ISNUMBER(O116),O116,""))</f>
+        <v/>
+      </c>
+      <c r="P117" s="158">
+        <f>IF(ISNUMBER(P115),P115,IF(ISNUMBER(P116),P116,""))</f>
+        <v/>
+      </c>
+      <c r="Q117" s="158">
+        <f>IF(ISNUMBER(Q115),Q115,IF(ISNUMBER(Q116),Q116,""))</f>
+        <v/>
+      </c>
+      <c r="R117" s="158">
+        <f>IF(ISNUMBER(R115),R115,IF(ISNUMBER(R116),R116,""))</f>
+        <v/>
+      </c>
+      <c r="S117" s="158">
+        <f>IF(ISNUMBER(S115),S115,IF(ISNUMBER(S116),S116,""))</f>
+        <v/>
+      </c>
+      <c r="T117" s="156" t="inlineStr"/>
+      <c r="U117" s="156" t="inlineStr"/>
+      <c r="V117" s="156" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="152" t="inlineStr">
+        <is>
+          <t>Imports, jet</t>
+        </is>
+      </c>
+      <c r="B118" s="153" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C118" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D118" s="154" t="n"/>
+      <c r="E118" s="152" t="inlineStr">
+        <is>
+          <t>Complete years reported in litres.</t>
+        </is>
+      </c>
+      <c r="F118" s="154" t="n"/>
+      <c r="G118" s="154" t="n"/>
+      <c r="H118" s="154" t="n"/>
+      <c r="I118" s="154" t="n"/>
+      <c r="J118" s="154" t="n"/>
+      <c r="K118" s="154" t="n">
+        <v>418.603994</v>
+      </c>
+      <c r="L118" s="154" t="n">
+        <v>341.60306375</v>
+      </c>
+      <c r="M118" s="154" t="n"/>
+      <c r="N118" s="154" t="n">
+        <v>587.4314575</v>
+      </c>
+      <c r="O118" s="154" t="n">
+        <v>446.819487</v>
+      </c>
+      <c r="P118" s="154" t="n">
+        <v>810.3529865</v>
+      </c>
+      <c r="Q118" s="154" t="n">
+        <v>673.86142982</v>
+      </c>
+      <c r="R118" s="154" t="n">
+        <v>718.0868890700001</v>
+      </c>
+      <c r="S118" s="154" t="n">
+        <v>884.9844383200001</v>
+      </c>
+      <c r="T118" s="152" t="inlineStr">
+        <is>
+          <t>From 2014; 2019 blank because one month is missing</t>
+        </is>
+      </c>
+      <c r="U118" s="152" t="inlineStr">
+        <is>
+          <t>South African Revenue Service, trade statistics by tariff line</t>
+        </is>
+      </c>
+      <c r="V118" s="152" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="152" t="inlineStr">
+        <is>
+          <t>Exports, jet</t>
+        </is>
+      </c>
+      <c r="B119" s="153" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C119" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D119" s="154" t="n"/>
+      <c r="E119" s="152" t="inlineStr">
+        <is>
+          <t>Complete years reported in litres. Whether fuel loaded onto international flights is recorded as an export is not established.</t>
+        </is>
+      </c>
+      <c r="F119" s="154" t="n"/>
+      <c r="G119" s="154" t="n"/>
+      <c r="H119" s="154" t="n">
+        <v>114.794276</v>
+      </c>
+      <c r="I119" s="154" t="n">
+        <v>821.0071333</v>
+      </c>
+      <c r="J119" s="154" t="n">
+        <v>334.5899605</v>
+      </c>
+      <c r="K119" s="154" t="n">
+        <v>348.7657881</v>
+      </c>
+      <c r="L119" s="154" t="n">
+        <v>327.817396</v>
+      </c>
+      <c r="M119" s="154" t="n">
+        <v>293.094467</v>
+      </c>
+      <c r="N119" s="154" t="n">
+        <v>620.3165292</v>
+      </c>
+      <c r="O119" s="154" t="n">
+        <v>98.7798698</v>
+      </c>
+      <c r="P119" s="154" t="n">
+        <v>384.881163</v>
+      </c>
+      <c r="Q119" s="154" t="n">
+        <v>451.76833507</v>
+      </c>
+      <c r="R119" s="154" t="n">
+        <v>478.4344717</v>
+      </c>
+      <c r="S119" s="154" t="n">
+        <v>471.98413936</v>
+      </c>
+      <c r="T119" s="152" t="inlineStr">
+        <is>
+          <t>From 2014</t>
+        </is>
+      </c>
+      <c r="U119" s="152" t="inlineStr">
+        <is>
+          <t>South African Revenue Service, trade statistics by tariff line</t>
+        </is>
+      </c>
+      <c r="V119" s="152" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="156" t="inlineStr">
+        <is>
+          <t>Net imports, jet</t>
+        </is>
+      </c>
+      <c r="B120" s="157" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C120" s="157" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D120" s="158" t="n"/>
+      <c r="E120" s="156" t="inlineStr">
+        <is>
+          <t>Imports less exports.</t>
+        </is>
+      </c>
+      <c r="F120" s="158">
+        <f>IF(COUNT(F118,F119)&lt;2,"",F118-F119)</f>
+        <v/>
+      </c>
+      <c r="G120" s="158">
+        <f>IF(COUNT(G118,G119)&lt;2,"",G118-G119)</f>
+        <v/>
+      </c>
+      <c r="H120" s="158">
+        <f>IF(COUNT(H118,H119)&lt;2,"",H118-H119)</f>
+        <v/>
+      </c>
+      <c r="I120" s="158">
+        <f>IF(COUNT(I118,I119)&lt;2,"",I118-I119)</f>
+        <v/>
+      </c>
+      <c r="J120" s="158">
+        <f>IF(COUNT(J118,J119)&lt;2,"",J118-J119)</f>
+        <v/>
+      </c>
+      <c r="K120" s="158">
+        <f>IF(COUNT(K118,K119)&lt;2,"",K118-K119)</f>
+        <v/>
+      </c>
+      <c r="L120" s="158">
+        <f>IF(COUNT(L118,L119)&lt;2,"",L118-L119)</f>
+        <v/>
+      </c>
+      <c r="M120" s="158">
+        <f>IF(COUNT(M118,M119)&lt;2,"",M118-M119)</f>
+        <v/>
+      </c>
+      <c r="N120" s="158">
+        <f>IF(COUNT(N118,N119)&lt;2,"",N118-N119)</f>
+        <v/>
+      </c>
+      <c r="O120" s="158">
+        <f>IF(COUNT(O118,O119)&lt;2,"",O118-O119)</f>
+        <v/>
+      </c>
+      <c r="P120" s="158">
+        <f>IF(COUNT(P118,P119)&lt;2,"",P118-P119)</f>
+        <v/>
+      </c>
+      <c r="Q120" s="158">
+        <f>IF(COUNT(Q118,Q119)&lt;2,"",Q118-Q119)</f>
+        <v/>
+      </c>
+      <c r="R120" s="158">
+        <f>IF(COUNT(R118,R119)&lt;2,"",R118-R119)</f>
+        <v/>
+      </c>
+      <c r="S120" s="158">
+        <f>IF(COUNT(S118,S119)&lt;2,"",S118-S119)</f>
+        <v/>
+      </c>
+      <c r="T120" s="156" t="inlineStr"/>
+      <c r="U120" s="156" t="inlineStr"/>
+      <c r="V120" s="156" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="152" t="inlineStr">
+        <is>
+          <t>Production reported, jet</t>
+        </is>
+      </c>
+      <c r="B121" s="153" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C121" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D121" s="154" t="n"/>
+      <c r="E121" s="152" t="inlineStr">
+        <is>
+          <t>National production line of the energy balance.</t>
+        </is>
+      </c>
+      <c r="F121" s="154" t="n">
+        <v>1100.507375</v>
+      </c>
+      <c r="G121" s="154" t="n">
+        <v>1762.443875</v>
+      </c>
+      <c r="H121" s="154" t="n">
+        <v>1715.08725</v>
+      </c>
+      <c r="I121" s="154" t="n">
+        <v>2967.27825</v>
+      </c>
+      <c r="J121" s="154" t="n">
+        <v>3047.4005</v>
+      </c>
+      <c r="K121" s="154" t="n">
+        <v>1518.965125</v>
+      </c>
+      <c r="L121" s="154" t="n">
+        <v>1543.192125</v>
+      </c>
+      <c r="M121" s="154" t="n">
+        <v>1089.709875</v>
+      </c>
+      <c r="N121" s="154" t="n">
+        <v>962.755625</v>
+      </c>
+      <c r="O121" s="154" t="n">
+        <v>861.3591022420001</v>
+      </c>
+      <c r="P121" s="154" t="n"/>
+      <c r="Q121" s="154" t="n"/>
+      <c r="R121" s="154" t="n"/>
+      <c r="S121" s="154" t="n"/>
+      <c r="T121" s="152" t="inlineStr">
+        <is>
+          <t>2012-2021</t>
+        </is>
+      </c>
+      <c r="U121" s="152" t="inlineStr">
+        <is>
+          <t>Department energy balances</t>
+        </is>
+      </c>
+      <c r="V121" s="152" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="156" t="inlineStr">
+        <is>
+          <t>Sales less net imports, jet</t>
+        </is>
+      </c>
+      <c r="B122" s="157" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C122" s="157" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D122" s="158" t="n"/>
+      <c r="E122" s="156" t="inlineStr">
+        <is>
+          <t>What production and stock changes must supply. Not a measurement of production.</t>
+        </is>
+      </c>
+      <c r="F122" s="158">
+        <f>IF(COUNT(F117,F120)&lt;2,"",F117-F120)</f>
+        <v/>
+      </c>
+      <c r="G122" s="158">
+        <f>IF(COUNT(G117,G120)&lt;2,"",G117-G120)</f>
+        <v/>
+      </c>
+      <c r="H122" s="158">
+        <f>IF(COUNT(H117,H120)&lt;2,"",H117-H120)</f>
+        <v/>
+      </c>
+      <c r="I122" s="158">
+        <f>IF(COUNT(I117,I120)&lt;2,"",I117-I120)</f>
+        <v/>
+      </c>
+      <c r="J122" s="158">
+        <f>IF(COUNT(J117,J120)&lt;2,"",J117-J120)</f>
+        <v/>
+      </c>
+      <c r="K122" s="158">
+        <f>IF(COUNT(K117,K120)&lt;2,"",K117-K120)</f>
+        <v/>
+      </c>
+      <c r="L122" s="158">
+        <f>IF(COUNT(L117,L120)&lt;2,"",L117-L120)</f>
+        <v/>
+      </c>
+      <c r="M122" s="158">
+        <f>IF(COUNT(M117,M120)&lt;2,"",M117-M120)</f>
+        <v/>
+      </c>
+      <c r="N122" s="158">
+        <f>IF(COUNT(N117,N120)&lt;2,"",N117-N120)</f>
+        <v/>
+      </c>
+      <c r="O122" s="158">
+        <f>IF(COUNT(O117,O120)&lt;2,"",O117-O120)</f>
+        <v/>
+      </c>
+      <c r="P122" s="158">
+        <f>IF(COUNT(P117,P120)&lt;2,"",P117-P120)</f>
+        <v/>
+      </c>
+      <c r="Q122" s="158">
+        <f>IF(COUNT(Q117,Q120)&lt;2,"",Q117-Q120)</f>
+        <v/>
+      </c>
+      <c r="R122" s="158">
+        <f>IF(COUNT(R117,R120)&lt;2,"",R117-R120)</f>
+        <v/>
+      </c>
+      <c r="S122" s="158">
+        <f>IF(COUNT(S117,S120)&lt;2,"",S117-S120)</f>
+        <v/>
+      </c>
+      <c r="T122" s="156" t="inlineStr"/>
+      <c r="U122" s="156" t="inlineStr"/>
+      <c r="V122" s="156" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="156" t="inlineStr">
+        <is>
+          <t>Unexplained after reported production, jet</t>
+        </is>
+      </c>
+      <c r="B123" s="157" t="inlineStr">
+        <is>
+          <t>million L/year</t>
+        </is>
+      </c>
+      <c r="C123" s="157" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D123" s="158" t="n"/>
+      <c r="E123" s="156" t="inlineStr">
+        <is>
+          <t>Sales less net imports less reported production.</t>
+        </is>
+      </c>
+      <c r="F123" s="158">
+        <f>IF(COUNT(F122,F121)&lt;2,"",F122-F121)</f>
+        <v/>
+      </c>
+      <c r="G123" s="158">
+        <f>IF(COUNT(G122,G121)&lt;2,"",G122-G121)</f>
+        <v/>
+      </c>
+      <c r="H123" s="158">
+        <f>IF(COUNT(H122,H121)&lt;2,"",H122-H121)</f>
+        <v/>
+      </c>
+      <c r="I123" s="158">
+        <f>IF(COUNT(I122,I121)&lt;2,"",I122-I121)</f>
+        <v/>
+      </c>
+      <c r="J123" s="158">
+        <f>IF(COUNT(J122,J121)&lt;2,"",J122-J121)</f>
+        <v/>
+      </c>
+      <c r="K123" s="158">
+        <f>IF(COUNT(K122,K121)&lt;2,"",K122-K121)</f>
+        <v/>
+      </c>
+      <c r="L123" s="158">
+        <f>IF(COUNT(L122,L121)&lt;2,"",L122-L121)</f>
+        <v/>
+      </c>
+      <c r="M123" s="158">
+        <f>IF(COUNT(M122,M121)&lt;2,"",M122-M121)</f>
+        <v/>
+      </c>
+      <c r="N123" s="158">
+        <f>IF(COUNT(N122,N121)&lt;2,"",N122-N121)</f>
+        <v/>
+      </c>
+      <c r="O123" s="158">
+        <f>IF(COUNT(O122,O121)&lt;2,"",O122-O121)</f>
+        <v/>
+      </c>
+      <c r="P123" s="158">
+        <f>IF(COUNT(P122,P121)&lt;2,"",P122-P121)</f>
+        <v/>
+      </c>
+      <c r="Q123" s="158">
+        <f>IF(COUNT(Q122,Q121)&lt;2,"",Q122-Q121)</f>
+        <v/>
+      </c>
+      <c r="R123" s="158">
+        <f>IF(COUNT(R122,R121)&lt;2,"",R122-R121)</f>
+        <v/>
+      </c>
+      <c r="S123" s="158">
+        <f>IF(COUNT(S122,S121)&lt;2,"",S122-S121)</f>
+        <v/>
+      </c>
+      <c r="T123" s="156" t="inlineStr"/>
+      <c r="U123" s="156" t="inlineStr"/>
+      <c r="V123" s="156" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="152" t="inlineStr">
+        <is>
+          <t>Aircraft movements at ACSA airports</t>
+        </is>
+      </c>
+      <c r="B124" s="153" t="inlineStr">
+        <is>
+          <t>movements/year</t>
+        </is>
+      </c>
+      <c r="C124" s="153" t="inlineStr">
+        <is>
+          <t>Source observation</t>
+        </is>
+      </c>
+      <c r="D124" s="166" t="n"/>
+      <c r="E124" s="152" t="inlineStr">
+        <is>
+          <t>Arrivals and departures, all flight types, nine ACSA airports. Non-ACSA airports (Lanseria and others) are not covered.</t>
+        </is>
+      </c>
+      <c r="F124" s="166" t="n"/>
+      <c r="G124" s="166" t="n">
+        <v>514106</v>
+      </c>
+      <c r="H124" s="166" t="n">
+        <v>541048</v>
+      </c>
+      <c r="I124" s="166" t="n">
+        <v>565516</v>
+      </c>
+      <c r="J124" s="166" t="n">
+        <v>568527</v>
+      </c>
+      <c r="K124" s="166" t="n">
+        <v>530912</v>
+      </c>
+      <c r="L124" s="166" t="n">
+        <v>519847</v>
+      </c>
+      <c r="M124" s="166" t="n">
+        <v>512467</v>
+      </c>
+      <c r="N124" s="166" t="n">
+        <v>236675</v>
+      </c>
+      <c r="O124" s="166" t="n">
+        <v>316436</v>
+      </c>
+      <c r="P124" s="166" t="n">
+        <v>416058</v>
+      </c>
+      <c r="Q124" s="166" t="n">
+        <v>451317</v>
+      </c>
+      <c r="R124" s="166" t="n">
+        <v>456214</v>
+      </c>
+      <c r="S124" s="166" t="n">
+        <v>462123</v>
+      </c>
+      <c r="T124" s="152" t="inlineStr">
+        <is>
+          <t>2013-2025</t>
+        </is>
+      </c>
+      <c r="U124" s="152" t="inlineStr">
+        <is>
+          <t>Airports Company South Africa, traffic statistics</t>
+        </is>
+      </c>
+      <c r="V124" s="152" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="156" t="inlineStr">
+        <is>
+          <t>Jet sold per aircraft movement</t>
+        </is>
+      </c>
+      <c r="B125" s="157" t="inlineStr">
+        <is>
+          <t>litres/movement</t>
+        </is>
+      </c>
+      <c r="C125" s="157" t="inlineStr">
+        <is>
+          <t>Reporting formula</t>
+        </is>
+      </c>
+      <c r="D125" s="167" t="n"/>
+      <c r="E125" s="156" t="inlineStr">
+        <is>
+          <t>Sales used divided by movements. 4,086 litres in 2023 against 4,759 in 2019; the reason for the fall is not established. Driver proposed for jet: movements times this intensity.</t>
+        </is>
+      </c>
+      <c r="F125" s="167">
+        <f>IF(COUNT(F117,F124)&lt;2,"",F117*1000000/F124)</f>
+        <v/>
+      </c>
+      <c r="G125" s="167">
+        <f>IF(COUNT(G117,G124)&lt;2,"",G117*1000000/G124)</f>
+        <v/>
+      </c>
+      <c r="H125" s="167">
+        <f>IF(COUNT(H117,H124)&lt;2,"",H117*1000000/H124)</f>
+        <v/>
+      </c>
+      <c r="I125" s="167">
+        <f>IF(COUNT(I117,I124)&lt;2,"",I117*1000000/I124)</f>
+        <v/>
+      </c>
+      <c r="J125" s="167">
+        <f>IF(COUNT(J117,J124)&lt;2,"",J117*1000000/J124)</f>
+        <v/>
+      </c>
+      <c r="K125" s="167">
+        <f>IF(COUNT(K117,K124)&lt;2,"",K117*1000000/K124)</f>
+        <v/>
+      </c>
+      <c r="L125" s="167">
+        <f>IF(COUNT(L117,L124)&lt;2,"",L117*1000000/L124)</f>
+        <v/>
+      </c>
+      <c r="M125" s="167">
+        <f>IF(COUNT(M117,M124)&lt;2,"",M117*1000000/M124)</f>
+        <v/>
+      </c>
+      <c r="N125" s="167">
+        <f>IF(COUNT(N117,N124)&lt;2,"",N117*1000000/N124)</f>
+        <v/>
+      </c>
+      <c r="O125" s="167">
+        <f>IF(COUNT(O117,O124)&lt;2,"",O117*1000000/O124)</f>
+        <v/>
+      </c>
+      <c r="P125" s="167">
+        <f>IF(COUNT(P117,P124)&lt;2,"",P117*1000000/P124)</f>
+        <v/>
+      </c>
+      <c r="Q125" s="167">
+        <f>IF(COUNT(Q117,Q124)&lt;2,"",Q117*1000000/Q124)</f>
+        <v/>
+      </c>
+      <c r="R125" s="167">
+        <f>IF(COUNT(R117,R124)&lt;2,"",R117*1000000/R124)</f>
+        <v/>
+      </c>
+      <c r="S125" s="167">
+        <f>IF(COUNT(S117,S124)&lt;2,"",S117*1000000/S124)</f>
+        <v/>
+      </c>
+      <c r="T125" s="156" t="inlineStr"/>
+      <c r="U125" s="156" t="inlineStr"/>
+      <c r="V125" s="156" t="inlineStr">
+        <is>
+          <t>Cargo, aircraft mix and route length are not separated; no source held gives jet by airport</t>
         </is>
       </c>
     </row>
@@ -43989,65 +44857,65 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D8" s="166" t="n"/>
+      <c r="D8" s="168" t="n"/>
       <c r="E8" s="156" t="inlineStr">
         <is>
           <t>Diesel divided by the activity measure, each year both exist.</t>
         </is>
       </c>
-      <c r="F8" s="166">
+      <c r="F8" s="168">
         <f>IF(COUNT(F6,F7)&lt;2,"",F6/F7)</f>
         <v/>
       </c>
-      <c r="G8" s="166">
+      <c r="G8" s="168">
         <f>IF(COUNT(G6,G7)&lt;2,"",G6/G7)</f>
         <v/>
       </c>
-      <c r="H8" s="166">
+      <c r="H8" s="168">
         <f>IF(COUNT(H6,H7)&lt;2,"",H6/H7)</f>
         <v/>
       </c>
-      <c r="I8" s="166">
+      <c r="I8" s="168">
         <f>IF(COUNT(I6,I7)&lt;2,"",I6/I7)</f>
         <v/>
       </c>
-      <c r="J8" s="166">
+      <c r="J8" s="168">
         <f>IF(COUNT(J6,J7)&lt;2,"",J6/J7)</f>
         <v/>
       </c>
-      <c r="K8" s="166">
+      <c r="K8" s="168">
         <f>IF(COUNT(K6,K7)&lt;2,"",K6/K7)</f>
         <v/>
       </c>
-      <c r="L8" s="166">
+      <c r="L8" s="168">
         <f>IF(COUNT(L6,L7)&lt;2,"",L6/L7)</f>
         <v/>
       </c>
-      <c r="M8" s="166">
+      <c r="M8" s="168">
         <f>IF(COUNT(M6,M7)&lt;2,"",M6/M7)</f>
         <v/>
       </c>
-      <c r="N8" s="166">
+      <c r="N8" s="168">
         <f>IF(COUNT(N6,N7)&lt;2,"",N6/N7)</f>
         <v/>
       </c>
-      <c r="O8" s="166">
+      <c r="O8" s="168">
         <f>IF(COUNT(O6,O7)&lt;2,"",O6/O7)</f>
         <v/>
       </c>
-      <c r="P8" s="166">
+      <c r="P8" s="168">
         <f>IF(COUNT(P6,P7)&lt;2,"",P6/P7)</f>
         <v/>
       </c>
-      <c r="Q8" s="166">
+      <c r="Q8" s="168">
         <f>IF(COUNT(Q6,Q7)&lt;2,"",Q6/Q7)</f>
         <v/>
       </c>
-      <c r="R8" s="166">
+      <c r="R8" s="168">
         <f>IF(COUNT(R6,R7)&lt;2,"",R6/R7)</f>
         <v/>
       </c>
-      <c r="S8" s="166">
+      <c r="S8" s="168">
         <f>IF(COUNT(S6,S7)&lt;2,"",S6/S7)</f>
         <v/>
       </c>
@@ -44512,65 +45380,65 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D18" s="166" t="n"/>
+      <c r="D18" s="168" t="n"/>
       <c r="E18" s="156" t="inlineStr">
         <is>
           <t>Diesel divided by the activity measure, each year both exist.</t>
         </is>
       </c>
-      <c r="F18" s="166">
+      <c r="F18" s="168">
         <f>IF(COUNT(F16,F17)&lt;2,"",F16/F17)</f>
         <v/>
       </c>
-      <c r="G18" s="166">
+      <c r="G18" s="168">
         <f>IF(COUNT(G16,G17)&lt;2,"",G16/G17)</f>
         <v/>
       </c>
-      <c r="H18" s="166">
+      <c r="H18" s="168">
         <f>IF(COUNT(H16,H17)&lt;2,"",H16/H17)</f>
         <v/>
       </c>
-      <c r="I18" s="166">
+      <c r="I18" s="168">
         <f>IF(COUNT(I16,I17)&lt;2,"",I16/I17)</f>
         <v/>
       </c>
-      <c r="J18" s="166">
+      <c r="J18" s="168">
         <f>IF(COUNT(J16,J17)&lt;2,"",J16/J17)</f>
         <v/>
       </c>
-      <c r="K18" s="166">
+      <c r="K18" s="168">
         <f>IF(COUNT(K16,K17)&lt;2,"",K16/K17)</f>
         <v/>
       </c>
-      <c r="L18" s="166">
+      <c r="L18" s="168">
         <f>IF(COUNT(L16,L17)&lt;2,"",L16/L17)</f>
         <v/>
       </c>
-      <c r="M18" s="166">
+      <c r="M18" s="168">
         <f>IF(COUNT(M16,M17)&lt;2,"",M16/M17)</f>
         <v/>
       </c>
-      <c r="N18" s="166">
+      <c r="N18" s="168">
         <f>IF(COUNT(N16,N17)&lt;2,"",N16/N17)</f>
         <v/>
       </c>
-      <c r="O18" s="166">
+      <c r="O18" s="168">
         <f>IF(COUNT(O16,O17)&lt;2,"",O16/O17)</f>
         <v/>
       </c>
-      <c r="P18" s="166">
+      <c r="P18" s="168">
         <f>IF(COUNT(P16,P17)&lt;2,"",P16/P17)</f>
         <v/>
       </c>
-      <c r="Q18" s="166">
+      <c r="Q18" s="168">
         <f>IF(COUNT(Q16,Q17)&lt;2,"",Q16/Q17)</f>
         <v/>
       </c>
-      <c r="R18" s="166">
+      <c r="R18" s="168">
         <f>IF(COUNT(R16,R17)&lt;2,"",R16/R17)</f>
         <v/>
       </c>
-      <c r="S18" s="166">
+      <c r="S18" s="168">
         <f>IF(COUNT(S16,S17)&lt;2,"",S16/S17)</f>
         <v/>
       </c>
@@ -44859,65 +45727,65 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D24" s="166" t="n"/>
+      <c r="D24" s="168" t="n"/>
       <c r="E24" s="156" t="inlineStr">
         <is>
           <t>Diesel divided by the activity measure, each year both exist.</t>
         </is>
       </c>
-      <c r="F24" s="166">
+      <c r="F24" s="168">
         <f>IF(COUNT(F22,F23)&lt;2,"",F22/F23)</f>
         <v/>
       </c>
-      <c r="G24" s="166">
+      <c r="G24" s="168">
         <f>IF(COUNT(G22,G23)&lt;2,"",G22/G23)</f>
         <v/>
       </c>
-      <c r="H24" s="166">
+      <c r="H24" s="168">
         <f>IF(COUNT(H22,H23)&lt;2,"",H22/H23)</f>
         <v/>
       </c>
-      <c r="I24" s="166">
+      <c r="I24" s="168">
         <f>IF(COUNT(I22,I23)&lt;2,"",I22/I23)</f>
         <v/>
       </c>
-      <c r="J24" s="166">
+      <c r="J24" s="168">
         <f>IF(COUNT(J22,J23)&lt;2,"",J22/J23)</f>
         <v/>
       </c>
-      <c r="K24" s="166">
+      <c r="K24" s="168">
         <f>IF(COUNT(K22,K23)&lt;2,"",K22/K23)</f>
         <v/>
       </c>
-      <c r="L24" s="166">
+      <c r="L24" s="168">
         <f>IF(COUNT(L22,L23)&lt;2,"",L22/L23)</f>
         <v/>
       </c>
-      <c r="M24" s="166">
+      <c r="M24" s="168">
         <f>IF(COUNT(M22,M23)&lt;2,"",M22/M23)</f>
         <v/>
       </c>
-      <c r="N24" s="166">
+      <c r="N24" s="168">
         <f>IF(COUNT(N22,N23)&lt;2,"",N22/N23)</f>
         <v/>
       </c>
-      <c r="O24" s="166">
+      <c r="O24" s="168">
         <f>IF(COUNT(O22,O23)&lt;2,"",O22/O23)</f>
         <v/>
       </c>
-      <c r="P24" s="166">
+      <c r="P24" s="168">
         <f>IF(COUNT(P22,P23)&lt;2,"",P22/P23)</f>
         <v/>
       </c>
-      <c r="Q24" s="166">
+      <c r="Q24" s="168">
         <f>IF(COUNT(Q22,Q23)&lt;2,"",Q22/Q23)</f>
         <v/>
       </c>
-      <c r="R24" s="166">
+      <c r="R24" s="168">
         <f>IF(COUNT(R22,R23)&lt;2,"",R22/R23)</f>
         <v/>
       </c>
-      <c r="S24" s="166">
+      <c r="S24" s="168">
         <f>IF(COUNT(S22,S23)&lt;2,"",S22/S23)</f>
         <v/>
       </c>
@@ -45554,32 +46422,32 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D10" s="167" t="n"/>
+      <c r="D10" s="166" t="n"/>
       <c r="E10" s="152" t="inlineStr">
         <is>
           <t>Year to 31 March of the following year, shown under the calendar year it mostly covers.</t>
         </is>
       </c>
-      <c r="F10" s="167" t="n"/>
-      <c r="G10" s="167" t="n"/>
-      <c r="H10" s="167" t="n"/>
-      <c r="I10" s="167" t="n"/>
-      <c r="J10" s="167" t="n"/>
-      <c r="K10" s="167" t="n"/>
-      <c r="L10" s="167" t="n"/>
-      <c r="M10" s="167" t="n"/>
-      <c r="N10" s="167" t="n"/>
-      <c r="O10" s="167" t="n"/>
-      <c r="P10" s="167" t="n">
+      <c r="F10" s="166" t="n"/>
+      <c r="G10" s="166" t="n"/>
+      <c r="H10" s="166" t="n"/>
+      <c r="I10" s="166" t="n"/>
+      <c r="J10" s="166" t="n"/>
+      <c r="K10" s="166" t="n"/>
+      <c r="L10" s="166" t="n"/>
+      <c r="M10" s="166" t="n"/>
+      <c r="N10" s="166" t="n"/>
+      <c r="O10" s="166" t="n"/>
+      <c r="P10" s="166" t="n">
         <v>4116</v>
       </c>
-      <c r="Q10" s="167" t="n">
+      <c r="Q10" s="166" t="n">
         <v>5143</v>
       </c>
-      <c r="R10" s="167" t="n">
+      <c r="R10" s="166" t="n">
         <v>2838</v>
       </c>
-      <c r="S10" s="167" t="n">
+      <c r="S10" s="166" t="n">
         <v>1079</v>
       </c>
       <c r="T10" s="152" t="inlineStr">
@@ -45672,7 +46540,7 @@
           <t>Observation, then estimate</t>
         </is>
       </c>
-      <c r="D12" s="166" t="n">
+      <c r="D12" s="168" t="n">
         <v>0.31</v>
       </c>
       <c r="E12" s="156" t="inlineStr">
@@ -45680,59 +46548,59 @@
           <t>Energy balance to 2021; from 2022 generation times litres per kWh (column D). Driver: turbine output.</t>
         </is>
       </c>
-      <c r="F12" s="166">
+      <c r="F12" s="168">
         <f>IF(ISNUMBER(F10),F10*$D$12,IF(ISNUMBER(F11),F11,""))</f>
         <v/>
       </c>
-      <c r="G12" s="166">
+      <c r="G12" s="168">
         <f>IF(ISNUMBER(G10),G10*$D$12,IF(ISNUMBER(G11),G11,""))</f>
         <v/>
       </c>
-      <c r="H12" s="166">
+      <c r="H12" s="168">
         <f>IF(ISNUMBER(H10),H10*$D$12,IF(ISNUMBER(H11),H11,""))</f>
         <v/>
       </c>
-      <c r="I12" s="166">
+      <c r="I12" s="168">
         <f>IF(ISNUMBER(I10),I10*$D$12,IF(ISNUMBER(I11),I11,""))</f>
         <v/>
       </c>
-      <c r="J12" s="166">
+      <c r="J12" s="168">
         <f>IF(ISNUMBER(J10),J10*$D$12,IF(ISNUMBER(J11),J11,""))</f>
         <v/>
       </c>
-      <c r="K12" s="166">
+      <c r="K12" s="168">
         <f>IF(ISNUMBER(K10),K10*$D$12,IF(ISNUMBER(K11),K11,""))</f>
         <v/>
       </c>
-      <c r="L12" s="166">
+      <c r="L12" s="168">
         <f>IF(ISNUMBER(L10),L10*$D$12,IF(ISNUMBER(L11),L11,""))</f>
         <v/>
       </c>
-      <c r="M12" s="166">
+      <c r="M12" s="168">
         <f>IF(ISNUMBER(M10),M10*$D$12,IF(ISNUMBER(M11),M11,""))</f>
         <v/>
       </c>
-      <c r="N12" s="166">
+      <c r="N12" s="168">
         <f>IF(ISNUMBER(N10),N10*$D$12,IF(ISNUMBER(N11),N11,""))</f>
         <v/>
       </c>
-      <c r="O12" s="166">
+      <c r="O12" s="168">
         <f>IF(ISNUMBER(O10),O10*$D$12,IF(ISNUMBER(O11),O11,""))</f>
         <v/>
       </c>
-      <c r="P12" s="166">
+      <c r="P12" s="168">
         <f>IF(ISNUMBER(P10),P10*$D$12,IF(ISNUMBER(P11),P11,""))</f>
         <v/>
       </c>
-      <c r="Q12" s="166">
+      <c r="Q12" s="168">
         <f>IF(ISNUMBER(Q10),Q10*$D$12,IF(ISNUMBER(Q11),Q11,""))</f>
         <v/>
       </c>
-      <c r="R12" s="166">
+      <c r="R12" s="168">
         <f>IF(ISNUMBER(R10),R10*$D$12,IF(ISNUMBER(R11),R11,""))</f>
         <v/>
       </c>
-      <c r="S12" s="166">
+      <c r="S12" s="168">
         <f>IF(ISNUMBER(S10),S10*$D$12,IF(ISNUMBER(S11),S11,""))</f>
         <v/>
       </c>
@@ -46442,7 +47310,7 @@
           <t>Comparison only</t>
         </is>
       </c>
-      <c r="D26" s="168" t="n">
+      <c r="D26" s="169" t="n">
         <v>60.5</v>
       </c>
       <c r="E26" s="159" t="inlineStr">
@@ -46450,20 +47318,20 @@
           <t>Merven, Hartley and Ahjum (2019): land freight took 60.5% of domestic diesel demand in 2012. Same research group as the vehicle study.</t>
         </is>
       </c>
-      <c r="F26" s="168" t="n"/>
-      <c r="G26" s="168" t="n"/>
-      <c r="H26" s="168" t="n"/>
-      <c r="I26" s="168" t="n"/>
-      <c r="J26" s="168" t="n"/>
-      <c r="K26" s="168" t="n"/>
-      <c r="L26" s="168" t="n"/>
-      <c r="M26" s="168" t="n"/>
-      <c r="N26" s="168" t="n"/>
-      <c r="O26" s="168" t="n"/>
-      <c r="P26" s="168" t="n"/>
-      <c r="Q26" s="168" t="n"/>
-      <c r="R26" s="168" t="n"/>
-      <c r="S26" s="168" t="n"/>
+      <c r="F26" s="169" t="n"/>
+      <c r="G26" s="169" t="n"/>
+      <c r="H26" s="169" t="n"/>
+      <c r="I26" s="169" t="n"/>
+      <c r="J26" s="169" t="n"/>
+      <c r="K26" s="169" t="n"/>
+      <c r="L26" s="169" t="n"/>
+      <c r="M26" s="169" t="n"/>
+      <c r="N26" s="169" t="n"/>
+      <c r="O26" s="169" t="n"/>
+      <c r="P26" s="169" t="n"/>
+      <c r="Q26" s="169" t="n"/>
+      <c r="R26" s="169" t="n"/>
+      <c r="S26" s="169" t="n"/>
       <c r="T26" s="159" t="inlineStr"/>
       <c r="U26" s="159" t="inlineStr">
         <is>
@@ -46512,7 +47380,7 @@
           <t>Note</t>
         </is>
       </c>
-      <c r="D29" s="169" t="n">
+      <c r="D29" s="170" t="n">
         <v>4836.490501047</v>
       </c>
       <c r="E29" s="159" t="inlineStr">
@@ -46520,20 +47388,20 @@
           <t>Diesel classes counted: HCV1Diesel, HCV2Diesel, HCV3Diesel, HCV4Diesel, HCV5Diesel, HCV6Diesel, HCV7Diesel, HCV8Diesel, HCV9Diesel. Other classes in the group, not diesel: HCV1Gasoline.</t>
         </is>
       </c>
-      <c r="F29" s="169" t="n"/>
-      <c r="G29" s="169" t="n"/>
-      <c r="H29" s="169" t="n"/>
-      <c r="I29" s="169" t="n"/>
-      <c r="J29" s="169" t="n"/>
-      <c r="K29" s="169" t="n"/>
-      <c r="L29" s="169" t="n"/>
-      <c r="M29" s="169" t="n"/>
-      <c r="N29" s="169" t="n"/>
-      <c r="O29" s="169" t="n"/>
-      <c r="P29" s="169" t="n"/>
-      <c r="Q29" s="169" t="n"/>
-      <c r="R29" s="169" t="n"/>
-      <c r="S29" s="169" t="n"/>
+      <c r="F29" s="170" t="n"/>
+      <c r="G29" s="170" t="n"/>
+      <c r="H29" s="170" t="n"/>
+      <c r="I29" s="170" t="n"/>
+      <c r="J29" s="170" t="n"/>
+      <c r="K29" s="170" t="n"/>
+      <c r="L29" s="170" t="n"/>
+      <c r="M29" s="170" t="n"/>
+      <c r="N29" s="170" t="n"/>
+      <c r="O29" s="170" t="n"/>
+      <c r="P29" s="170" t="n"/>
+      <c r="Q29" s="170" t="n"/>
+      <c r="R29" s="170" t="n"/>
+      <c r="S29" s="170" t="n"/>
       <c r="T29" s="159" t="inlineStr">
         <is>
           <t>Column D is the group's diesel in the study, million litres, 2010 fleet</t>
@@ -46558,7 +47426,7 @@
           <t>Note</t>
         </is>
       </c>
-      <c r="D30" s="169" t="n">
+      <c r="D30" s="170" t="n">
         <v>2156.667657144</v>
       </c>
       <c r="E30" s="159" t="inlineStr">
@@ -46566,20 +47434,20 @@
           <t>Diesel classes counted: LCVDiesel. Other classes in the group, not diesel: LCVGasoline.</t>
         </is>
       </c>
-      <c r="F30" s="169" t="n"/>
-      <c r="G30" s="169" t="n"/>
-      <c r="H30" s="169" t="n"/>
-      <c r="I30" s="169" t="n"/>
-      <c r="J30" s="169" t="n"/>
-      <c r="K30" s="169" t="n"/>
-      <c r="L30" s="169" t="n"/>
-      <c r="M30" s="169" t="n"/>
-      <c r="N30" s="169" t="n"/>
-      <c r="O30" s="169" t="n"/>
-      <c r="P30" s="169" t="n"/>
-      <c r="Q30" s="169" t="n"/>
-      <c r="R30" s="169" t="n"/>
-      <c r="S30" s="169" t="n"/>
+      <c r="F30" s="170" t="n"/>
+      <c r="G30" s="170" t="n"/>
+      <c r="H30" s="170" t="n"/>
+      <c r="I30" s="170" t="n"/>
+      <c r="J30" s="170" t="n"/>
+      <c r="K30" s="170" t="n"/>
+      <c r="L30" s="170" t="n"/>
+      <c r="M30" s="170" t="n"/>
+      <c r="N30" s="170" t="n"/>
+      <c r="O30" s="170" t="n"/>
+      <c r="P30" s="170" t="n"/>
+      <c r="Q30" s="170" t="n"/>
+      <c r="R30" s="170" t="n"/>
+      <c r="S30" s="170" t="n"/>
       <c r="T30" s="159" t="inlineStr">
         <is>
           <t>Column D is the group's diesel in the study, million litres, 2010 fleet</t>
@@ -46604,7 +47472,7 @@
           <t>Note</t>
         </is>
       </c>
-      <c r="D31" s="169" t="n">
+      <c r="D31" s="170" t="n">
         <v>996.994409071</v>
       </c>
       <c r="E31" s="159" t="inlineStr">
@@ -46612,20 +47480,20 @@
           <t>Diesel classes counted: CarDiesel, CarHybridDiesel, BusDiesel, MBTDiesel, SUVDiesel. Other classes in the group, not diesel: CarElectric, CarGasoline, CarHybridGasoline, MBTGasoline, MotoGasoline, SUVGasoline, SUVHybridGasoline.</t>
         </is>
       </c>
-      <c r="F31" s="169" t="n"/>
-      <c r="G31" s="169" t="n"/>
-      <c r="H31" s="169" t="n"/>
-      <c r="I31" s="169" t="n"/>
-      <c r="J31" s="169" t="n"/>
-      <c r="K31" s="169" t="n"/>
-      <c r="L31" s="169" t="n"/>
-      <c r="M31" s="169" t="n"/>
-      <c r="N31" s="169" t="n"/>
-      <c r="O31" s="169" t="n"/>
-      <c r="P31" s="169" t="n"/>
-      <c r="Q31" s="169" t="n"/>
-      <c r="R31" s="169" t="n"/>
-      <c r="S31" s="169" t="n"/>
+      <c r="F31" s="170" t="n"/>
+      <c r="G31" s="170" t="n"/>
+      <c r="H31" s="170" t="n"/>
+      <c r="I31" s="170" t="n"/>
+      <c r="J31" s="170" t="n"/>
+      <c r="K31" s="170" t="n"/>
+      <c r="L31" s="170" t="n"/>
+      <c r="M31" s="170" t="n"/>
+      <c r="N31" s="170" t="n"/>
+      <c r="O31" s="170" t="n"/>
+      <c r="P31" s="170" t="n"/>
+      <c r="Q31" s="170" t="n"/>
+      <c r="R31" s="170" t="n"/>
+      <c r="S31" s="170" t="n"/>
       <c r="T31" s="159" t="inlineStr">
         <is>
           <t>Column D is the group's diesel in the study, million litres, 2010 fleet</t>
@@ -49388,34 +50256,34 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D6" s="167" t="n"/>
+      <c r="D6" s="166" t="n"/>
       <c r="E6" s="152" t="inlineStr">
         <is>
           <t>Live (licensed) vehicles, all fuels together.</t>
         </is>
       </c>
-      <c r="F6" s="167" t="n"/>
-      <c r="G6" s="167" t="n"/>
-      <c r="H6" s="167" t="n"/>
-      <c r="I6" s="167" t="n"/>
-      <c r="J6" s="167" t="n"/>
-      <c r="K6" s="167" t="n"/>
-      <c r="L6" s="167" t="n"/>
-      <c r="M6" s="167" t="n"/>
-      <c r="N6" s="167" t="n"/>
-      <c r="O6" s="167" t="n">
+      <c r="F6" s="166" t="n"/>
+      <c r="G6" s="166" t="n"/>
+      <c r="H6" s="166" t="n"/>
+      <c r="I6" s="166" t="n"/>
+      <c r="J6" s="166" t="n"/>
+      <c r="K6" s="166" t="n"/>
+      <c r="L6" s="166" t="n"/>
+      <c r="M6" s="166" t="n"/>
+      <c r="N6" s="166" t="n"/>
+      <c r="O6" s="166" t="n">
         <v>7652077</v>
       </c>
-      <c r="P6" s="167" t="n">
+      <c r="P6" s="166" t="n">
         <v>7685153</v>
       </c>
-      <c r="Q6" s="167" t="n">
+      <c r="Q6" s="166" t="n">
         <v>7794164</v>
       </c>
-      <c r="R6" s="167" t="n">
+      <c r="R6" s="166" t="n">
         <v>7949275</v>
       </c>
-      <c r="S6" s="167" t="n">
+      <c r="S6" s="166" t="n">
         <v>8184111</v>
       </c>
       <c r="T6" s="152" t="inlineStr">
@@ -49450,34 +50318,34 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D7" s="167" t="n"/>
+      <c r="D7" s="166" t="n"/>
       <c r="E7" s="152" t="inlineStr">
         <is>
           <t>Live (licensed) vehicles, all fuels together.</t>
         </is>
       </c>
-      <c r="F7" s="167" t="n"/>
-      <c r="G7" s="167" t="n"/>
-      <c r="H7" s="167" t="n"/>
-      <c r="I7" s="167" t="n"/>
-      <c r="J7" s="167" t="n"/>
-      <c r="K7" s="167" t="n"/>
-      <c r="L7" s="167" t="n"/>
-      <c r="M7" s="167" t="n"/>
-      <c r="N7" s="167" t="n"/>
-      <c r="O7" s="167" t="n">
+      <c r="F7" s="166" t="n"/>
+      <c r="G7" s="166" t="n"/>
+      <c r="H7" s="166" t="n"/>
+      <c r="I7" s="166" t="n"/>
+      <c r="J7" s="166" t="n"/>
+      <c r="K7" s="166" t="n"/>
+      <c r="L7" s="166" t="n"/>
+      <c r="M7" s="166" t="n"/>
+      <c r="N7" s="166" t="n"/>
+      <c r="O7" s="166" t="n">
         <v>2671314</v>
       </c>
-      <c r="P7" s="167" t="n">
+      <c r="P7" s="166" t="n">
         <v>2658416</v>
       </c>
-      <c r="Q7" s="167" t="n">
+      <c r="Q7" s="166" t="n">
         <v>2689310</v>
       </c>
-      <c r="R7" s="167" t="n">
+      <c r="R7" s="166" t="n">
         <v>2725606</v>
       </c>
-      <c r="S7" s="167" t="n">
+      <c r="S7" s="166" t="n">
         <v>2776258</v>
       </c>
       <c r="T7" s="152" t="inlineStr">
@@ -49512,34 +50380,34 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D8" s="167" t="n"/>
+      <c r="D8" s="166" t="n"/>
       <c r="E8" s="152" t="inlineStr">
         <is>
           <t>Live (licensed) vehicles, all fuels together.</t>
         </is>
       </c>
-      <c r="F8" s="167" t="n"/>
-      <c r="G8" s="167" t="n"/>
-      <c r="H8" s="167" t="n"/>
-      <c r="I8" s="167" t="n"/>
-      <c r="J8" s="167" t="n"/>
-      <c r="K8" s="167" t="n"/>
-      <c r="L8" s="167" t="n"/>
-      <c r="M8" s="167" t="n"/>
-      <c r="N8" s="167" t="n"/>
-      <c r="O8" s="167" t="n">
+      <c r="F8" s="166" t="n"/>
+      <c r="G8" s="166" t="n"/>
+      <c r="H8" s="166" t="n"/>
+      <c r="I8" s="166" t="n"/>
+      <c r="J8" s="166" t="n"/>
+      <c r="K8" s="166" t="n"/>
+      <c r="L8" s="166" t="n"/>
+      <c r="M8" s="166" t="n"/>
+      <c r="N8" s="166" t="n"/>
+      <c r="O8" s="166" t="n">
         <v>389112</v>
       </c>
-      <c r="P8" s="167" t="n">
+      <c r="P8" s="166" t="n">
         <v>385845</v>
       </c>
-      <c r="Q8" s="167" t="n">
+      <c r="Q8" s="166" t="n">
         <v>392349</v>
       </c>
-      <c r="R8" s="167" t="n">
+      <c r="R8" s="166" t="n">
         <v>398542</v>
       </c>
-      <c r="S8" s="167" t="n">
+      <c r="S8" s="166" t="n">
         <v>404752</v>
       </c>
       <c r="T8" s="152" t="inlineStr">
@@ -49574,34 +50442,34 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D9" s="167" t="n"/>
+      <c r="D9" s="166" t="n"/>
       <c r="E9" s="152" t="inlineStr">
         <is>
           <t>Live (licensed) vehicles, all fuels together.</t>
         </is>
       </c>
-      <c r="F9" s="167" t="n"/>
-      <c r="G9" s="167" t="n"/>
-      <c r="H9" s="167" t="n"/>
-      <c r="I9" s="167" t="n"/>
-      <c r="J9" s="167" t="n"/>
-      <c r="K9" s="167" t="n"/>
-      <c r="L9" s="167" t="n"/>
-      <c r="M9" s="167" t="n"/>
-      <c r="N9" s="167" t="n"/>
-      <c r="O9" s="167" t="n">
+      <c r="F9" s="166" t="n"/>
+      <c r="G9" s="166" t="n"/>
+      <c r="H9" s="166" t="n"/>
+      <c r="I9" s="166" t="n"/>
+      <c r="J9" s="166" t="n"/>
+      <c r="K9" s="166" t="n"/>
+      <c r="L9" s="166" t="n"/>
+      <c r="M9" s="166" t="n"/>
+      <c r="N9" s="166" t="n"/>
+      <c r="O9" s="166" t="n">
         <v>64340</v>
       </c>
-      <c r="P9" s="167" t="n">
+      <c r="P9" s="166" t="n">
         <v>64170</v>
       </c>
-      <c r="Q9" s="167" t="n">
+      <c r="Q9" s="166" t="n">
         <v>64982</v>
       </c>
-      <c r="R9" s="167" t="n">
+      <c r="R9" s="166" t="n">
         <v>65792</v>
       </c>
-      <c r="S9" s="167" t="n">
+      <c r="S9" s="166" t="n">
         <v>66249</v>
       </c>
       <c r="T9" s="152" t="inlineStr">
@@ -49636,34 +50504,34 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D10" s="167" t="n"/>
+      <c r="D10" s="166" t="n"/>
       <c r="E10" s="152" t="inlineStr">
         <is>
           <t>Live (licensed) vehicles, all fuels together.</t>
         </is>
       </c>
-      <c r="F10" s="167" t="n"/>
-      <c r="G10" s="167" t="n"/>
-      <c r="H10" s="167" t="n"/>
-      <c r="I10" s="167" t="n"/>
-      <c r="J10" s="167" t="n"/>
-      <c r="K10" s="167" t="n"/>
-      <c r="L10" s="167" t="n"/>
-      <c r="M10" s="167" t="n"/>
-      <c r="N10" s="167" t="n"/>
-      <c r="O10" s="167" t="n">
+      <c r="F10" s="166" t="n"/>
+      <c r="G10" s="166" t="n"/>
+      <c r="H10" s="166" t="n"/>
+      <c r="I10" s="166" t="n"/>
+      <c r="J10" s="166" t="n"/>
+      <c r="K10" s="166" t="n"/>
+      <c r="L10" s="166" t="n"/>
+      <c r="M10" s="166" t="n"/>
+      <c r="N10" s="166" t="n"/>
+      <c r="O10" s="166" t="n">
         <v>349671</v>
       </c>
-      <c r="P10" s="167" t="n">
+      <c r="P10" s="166" t="n">
         <v>349335</v>
       </c>
-      <c r="Q10" s="167" t="n">
+      <c r="Q10" s="166" t="n">
         <v>355235</v>
       </c>
-      <c r="R10" s="167" t="n">
+      <c r="R10" s="166" t="n">
         <v>355139</v>
       </c>
-      <c r="S10" s="167" t="n">
+      <c r="S10" s="166" t="n">
         <v>355145</v>
       </c>
       <c r="T10" s="152" t="inlineStr">
@@ -49698,34 +50566,34 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D11" s="167" t="n"/>
+      <c r="D11" s="166" t="n"/>
       <c r="E11" s="152" t="inlineStr">
         <is>
           <t>Live (licensed) vehicles, all fuels together.</t>
         </is>
       </c>
-      <c r="F11" s="167" t="n"/>
-      <c r="G11" s="167" t="n"/>
-      <c r="H11" s="167" t="n"/>
-      <c r="I11" s="167" t="n"/>
-      <c r="J11" s="167" t="n"/>
-      <c r="K11" s="167" t="n"/>
-      <c r="L11" s="167" t="n"/>
-      <c r="M11" s="167" t="n"/>
-      <c r="N11" s="167" t="n"/>
-      <c r="O11" s="167" t="n">
+      <c r="F11" s="166" t="n"/>
+      <c r="G11" s="166" t="n"/>
+      <c r="H11" s="166" t="n"/>
+      <c r="I11" s="166" t="n"/>
+      <c r="J11" s="166" t="n"/>
+      <c r="K11" s="166" t="n"/>
+      <c r="L11" s="166" t="n"/>
+      <c r="M11" s="166" t="n"/>
+      <c r="N11" s="166" t="n"/>
+      <c r="O11" s="166" t="n">
         <v>347631</v>
       </c>
-      <c r="P11" s="167" t="n">
+      <c r="P11" s="166" t="n">
         <v>346153</v>
       </c>
-      <c r="Q11" s="167" t="n">
+      <c r="Q11" s="166" t="n">
         <v>349215</v>
       </c>
-      <c r="R11" s="167" t="n">
+      <c r="R11" s="166" t="n">
         <v>358817</v>
       </c>
-      <c r="S11" s="167" t="n">
+      <c r="S11" s="166" t="n">
         <v>372137</v>
       </c>
       <c r="T11" s="152" t="inlineStr">
@@ -49788,46 +50656,46 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D14" s="167" t="n"/>
+      <c r="D14" s="166" t="n"/>
       <c r="E14" s="152" t="inlineStr">
         <is>
           <t>Actual new sales, all drivetrains.</t>
         </is>
       </c>
-      <c r="F14" s="167" t="n"/>
-      <c r="G14" s="167" t="n"/>
-      <c r="H14" s="167" t="n"/>
-      <c r="I14" s="167" t="n">
+      <c r="F14" s="166" t="n"/>
+      <c r="G14" s="166" t="n"/>
+      <c r="H14" s="166" t="n"/>
+      <c r="I14" s="166" t="n">
         <v>412397</v>
       </c>
-      <c r="J14" s="167" t="n">
+      <c r="J14" s="166" t="n">
         <v>361265</v>
       </c>
-      <c r="K14" s="167" t="n">
+      <c r="K14" s="166" t="n">
         <v>368114</v>
       </c>
-      <c r="L14" s="167" t="n">
+      <c r="L14" s="166" t="n">
         <v>365247</v>
       </c>
-      <c r="M14" s="167" t="n">
+      <c r="M14" s="166" t="n">
         <v>355379</v>
       </c>
-      <c r="N14" s="167" t="n">
+      <c r="N14" s="166" t="n">
         <v>246541</v>
       </c>
-      <c r="O14" s="167" t="n">
+      <c r="O14" s="166" t="n">
         <v>304338</v>
       </c>
-      <c r="P14" s="167" t="n">
+      <c r="P14" s="166" t="n">
         <v>363681</v>
       </c>
-      <c r="Q14" s="167" t="n">
+      <c r="Q14" s="166" t="n">
         <v>347377</v>
       </c>
-      <c r="R14" s="167" t="n">
+      <c r="R14" s="166" t="n">
         <v>351553</v>
       </c>
-      <c r="S14" s="167" t="n">
+      <c r="S14" s="166" t="n">
         <v>422463</v>
       </c>
       <c r="T14" s="152" t="inlineStr">
@@ -49858,46 +50726,46 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D15" s="167" t="n"/>
+      <c r="D15" s="166" t="n"/>
       <c r="E15" s="152" t="inlineStr">
         <is>
           <t>Actual new sales, all drivetrains.</t>
         </is>
       </c>
-      <c r="F15" s="167" t="n"/>
-      <c r="G15" s="167" t="n"/>
-      <c r="H15" s="167" t="n"/>
-      <c r="I15" s="167" t="n">
+      <c r="F15" s="166" t="n"/>
+      <c r="G15" s="166" t="n"/>
+      <c r="H15" s="166" t="n"/>
+      <c r="I15" s="166" t="n">
         <v>174812</v>
       </c>
-      <c r="J15" s="167" t="n">
+      <c r="J15" s="166" t="n">
         <v>159316</v>
       </c>
-      <c r="K15" s="167" t="n">
+      <c r="K15" s="166" t="n">
         <v>163317</v>
       </c>
-      <c r="L15" s="167" t="n">
+      <c r="L15" s="166" t="n">
         <v>159525</v>
       </c>
-      <c r="M15" s="167" t="n">
+      <c r="M15" s="166" t="n">
         <v>153221</v>
       </c>
-      <c r="N15" s="167" t="n">
+      <c r="N15" s="166" t="n">
         <v>110912</v>
       </c>
-      <c r="O15" s="167" t="n">
+      <c r="O15" s="166" t="n">
         <v>133078</v>
       </c>
-      <c r="P15" s="167" t="n">
+      <c r="P15" s="166" t="n">
         <v>135711</v>
       </c>
-      <c r="Q15" s="167" t="n">
+      <c r="Q15" s="166" t="n">
         <v>151490</v>
       </c>
-      <c r="R15" s="167" t="n">
+      <c r="R15" s="166" t="n">
         <v>133375</v>
       </c>
-      <c r="S15" s="167" t="n">
+      <c r="S15" s="166" t="n">
         <v>143964</v>
       </c>
       <c r="T15" s="152" t="inlineStr">
@@ -49928,46 +50796,46 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D16" s="167" t="n"/>
+      <c r="D16" s="166" t="n"/>
       <c r="E16" s="152" t="inlineStr">
         <is>
           <t>Actual new sales, all drivetrains.</t>
         </is>
       </c>
-      <c r="F16" s="167" t="n"/>
-      <c r="G16" s="167" t="n"/>
-      <c r="H16" s="167" t="n"/>
-      <c r="I16" s="167" t="n">
+      <c r="F16" s="166" t="n"/>
+      <c r="G16" s="166" t="n"/>
+      <c r="H16" s="166" t="n"/>
+      <c r="I16" s="166" t="n">
         <v>30441</v>
       </c>
-      <c r="J16" s="167" t="n">
+      <c r="J16" s="166" t="n">
         <v>26972</v>
       </c>
-      <c r="K16" s="167" t="n">
+      <c r="K16" s="166" t="n">
         <v>26272</v>
       </c>
-      <c r="L16" s="167" t="n">
+      <c r="L16" s="166" t="n">
         <v>27449</v>
       </c>
-      <c r="M16" s="167" t="n">
+      <c r="M16" s="166" t="n">
         <v>27891</v>
       </c>
-      <c r="N16" s="167" t="n">
+      <c r="N16" s="166" t="n">
         <v>22614</v>
       </c>
-      <c r="O16" s="167" t="n">
+      <c r="O16" s="166" t="n">
         <v>26906</v>
       </c>
-      <c r="P16" s="167" t="n">
+      <c r="P16" s="166" t="n">
         <v>29942</v>
       </c>
-      <c r="Q16" s="167" t="n">
+      <c r="Q16" s="166" t="n">
         <v>32690</v>
       </c>
-      <c r="R16" s="167" t="n">
+      <c r="R16" s="166" t="n">
         <v>31175</v>
       </c>
-      <c r="S16" s="167" t="n">
+      <c r="S16" s="166" t="n">
         <v>30911</v>
       </c>
       <c r="T16" s="152" t="inlineStr">
@@ -49998,46 +50866,46 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D17" s="167" t="n"/>
+      <c r="D17" s="166" t="n"/>
       <c r="E17" s="152" t="inlineStr">
         <is>
           <t>Total market as reported.</t>
         </is>
       </c>
-      <c r="F17" s="167" t="n"/>
-      <c r="G17" s="167" t="n"/>
-      <c r="H17" s="167" t="n"/>
-      <c r="I17" s="167" t="n">
+      <c r="F17" s="166" t="n"/>
+      <c r="G17" s="166" t="n"/>
+      <c r="H17" s="166" t="n"/>
+      <c r="I17" s="166" t="n">
         <v>617650</v>
       </c>
-      <c r="J17" s="167" t="n">
+      <c r="J17" s="166" t="n">
         <v>547552</v>
       </c>
-      <c r="K17" s="167" t="n">
+      <c r="K17" s="166" t="n">
         <v>557719</v>
       </c>
-      <c r="L17" s="167" t="n">
+      <c r="L17" s="166" t="n">
         <v>552221</v>
       </c>
-      <c r="M17" s="167" t="n">
+      <c r="M17" s="166" t="n">
         <v>536486</v>
       </c>
-      <c r="N17" s="167" t="n">
+      <c r="N17" s="166" t="n">
         <v>380065</v>
       </c>
-      <c r="O17" s="167" t="n">
+      <c r="O17" s="166" t="n">
         <v>464322</v>
       </c>
-      <c r="P17" s="167" t="n">
+      <c r="P17" s="166" t="n">
         <v>529335</v>
       </c>
-      <c r="Q17" s="167" t="n">
+      <c r="Q17" s="166" t="n">
         <v>531557</v>
       </c>
-      <c r="R17" s="167" t="n">
+      <c r="R17" s="166" t="n">
         <v>516103</v>
       </c>
-      <c r="S17" s="167" t="n">
+      <c r="S17" s="166" t="n">
         <v>597338</v>
       </c>
       <c r="T17" s="152" t="inlineStr">
@@ -50068,7 +50936,7 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D18" s="170" t="n">
+      <c r="D18" s="171" t="n">
         <v>78</v>
       </c>
       <c r="E18" s="156" t="inlineStr">
@@ -50076,59 +50944,59 @@
           <t>Observed share. Column D is the model's fixed split of new vehicles.</t>
         </is>
       </c>
-      <c r="F18" s="170">
+      <c r="F18" s="171">
         <f>IF(COUNT(F14,F17)&lt;2,"",F14/F17*100)</f>
         <v/>
       </c>
-      <c r="G18" s="170">
+      <c r="G18" s="171">
         <f>IF(COUNT(G14,G17)&lt;2,"",G14/G17*100)</f>
         <v/>
       </c>
-      <c r="H18" s="170">
+      <c r="H18" s="171">
         <f>IF(COUNT(H14,H17)&lt;2,"",H14/H17*100)</f>
         <v/>
       </c>
-      <c r="I18" s="170">
+      <c r="I18" s="171">
         <f>IF(COUNT(I14,I17)&lt;2,"",I14/I17*100)</f>
         <v/>
       </c>
-      <c r="J18" s="170">
+      <c r="J18" s="171">
         <f>IF(COUNT(J14,J17)&lt;2,"",J14/J17*100)</f>
         <v/>
       </c>
-      <c r="K18" s="170">
+      <c r="K18" s="171">
         <f>IF(COUNT(K14,K17)&lt;2,"",K14/K17*100)</f>
         <v/>
       </c>
-      <c r="L18" s="170">
+      <c r="L18" s="171">
         <f>IF(COUNT(L14,L17)&lt;2,"",L14/L17*100)</f>
         <v/>
       </c>
-      <c r="M18" s="170">
+      <c r="M18" s="171">
         <f>IF(COUNT(M14,M17)&lt;2,"",M14/M17*100)</f>
         <v/>
       </c>
-      <c r="N18" s="170">
+      <c r="N18" s="171">
         <f>IF(COUNT(N14,N17)&lt;2,"",N14/N17*100)</f>
         <v/>
       </c>
-      <c r="O18" s="170">
+      <c r="O18" s="171">
         <f>IF(COUNT(O14,O17)&lt;2,"",O14/O17*100)</f>
         <v/>
       </c>
-      <c r="P18" s="170">
+      <c r="P18" s="171">
         <f>IF(COUNT(P14,P17)&lt;2,"",P14/P17*100)</f>
         <v/>
       </c>
-      <c r="Q18" s="170">
+      <c r="Q18" s="171">
         <f>IF(COUNT(Q14,Q17)&lt;2,"",Q14/Q17*100)</f>
         <v/>
       </c>
-      <c r="R18" s="170">
+      <c r="R18" s="171">
         <f>IF(COUNT(R14,R17)&lt;2,"",R14/R17*100)</f>
         <v/>
       </c>
-      <c r="S18" s="170">
+      <c r="S18" s="171">
         <f>IF(COUNT(S14,S17)&lt;2,"",S14/S17*100)</f>
         <v/>
       </c>
@@ -50160,7 +51028,7 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D19" s="170" t="n">
+      <c r="D19" s="171" t="n">
         <v>18</v>
       </c>
       <c r="E19" s="156" t="inlineStr">
@@ -50168,59 +51036,59 @@
           <t>Observed share. Column D is the model's fixed split of new vehicles.</t>
         </is>
       </c>
-      <c r="F19" s="170">
+      <c r="F19" s="171">
         <f>IF(COUNT(F15,F17)&lt;2,"",F15/F17*100)</f>
         <v/>
       </c>
-      <c r="G19" s="170">
+      <c r="G19" s="171">
         <f>IF(COUNT(G15,G17)&lt;2,"",G15/G17*100)</f>
         <v/>
       </c>
-      <c r="H19" s="170">
+      <c r="H19" s="171">
         <f>IF(COUNT(H15,H17)&lt;2,"",H15/H17*100)</f>
         <v/>
       </c>
-      <c r="I19" s="170">
+      <c r="I19" s="171">
         <f>IF(COUNT(I15,I17)&lt;2,"",I15/I17*100)</f>
         <v/>
       </c>
-      <c r="J19" s="170">
+      <c r="J19" s="171">
         <f>IF(COUNT(J15,J17)&lt;2,"",J15/J17*100)</f>
         <v/>
       </c>
-      <c r="K19" s="170">
+      <c r="K19" s="171">
         <f>IF(COUNT(K15,K17)&lt;2,"",K15/K17*100)</f>
         <v/>
       </c>
-      <c r="L19" s="170">
+      <c r="L19" s="171">
         <f>IF(COUNT(L15,L17)&lt;2,"",L15/L17*100)</f>
         <v/>
       </c>
-      <c r="M19" s="170">
+      <c r="M19" s="171">
         <f>IF(COUNT(M15,M17)&lt;2,"",M15/M17*100)</f>
         <v/>
       </c>
-      <c r="N19" s="170">
+      <c r="N19" s="171">
         <f>IF(COUNT(N15,N17)&lt;2,"",N15/N17*100)</f>
         <v/>
       </c>
-      <c r="O19" s="170">
+      <c r="O19" s="171">
         <f>IF(COUNT(O15,O17)&lt;2,"",O15/O17*100)</f>
         <v/>
       </c>
-      <c r="P19" s="170">
+      <c r="P19" s="171">
         <f>IF(COUNT(P15,P17)&lt;2,"",P15/P17*100)</f>
         <v/>
       </c>
-      <c r="Q19" s="170">
+      <c r="Q19" s="171">
         <f>IF(COUNT(Q15,Q17)&lt;2,"",Q15/Q17*100)</f>
         <v/>
       </c>
-      <c r="R19" s="170">
+      <c r="R19" s="171">
         <f>IF(COUNT(R15,R17)&lt;2,"",R15/R17*100)</f>
         <v/>
       </c>
-      <c r="S19" s="170">
+      <c r="S19" s="171">
         <f>IF(COUNT(S15,S17)&lt;2,"",S15/S17*100)</f>
         <v/>
       </c>
@@ -50252,7 +51120,7 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D20" s="170" t="n">
+      <c r="D20" s="171" t="n">
         <v>4</v>
       </c>
       <c r="E20" s="156" t="inlineStr">
@@ -50260,59 +51128,59 @@
           <t>Observed share. Column D is the model's fixed split of new vehicles.</t>
         </is>
       </c>
-      <c r="F20" s="170">
+      <c r="F20" s="171">
         <f>IF(COUNT(F16,F17)&lt;2,"",F16/F17*100)</f>
         <v/>
       </c>
-      <c r="G20" s="170">
+      <c r="G20" s="171">
         <f>IF(COUNT(G16,G17)&lt;2,"",G16/G17*100)</f>
         <v/>
       </c>
-      <c r="H20" s="170">
+      <c r="H20" s="171">
         <f>IF(COUNT(H16,H17)&lt;2,"",H16/H17*100)</f>
         <v/>
       </c>
-      <c r="I20" s="170">
+      <c r="I20" s="171">
         <f>IF(COUNT(I16,I17)&lt;2,"",I16/I17*100)</f>
         <v/>
       </c>
-      <c r="J20" s="170">
+      <c r="J20" s="171">
         <f>IF(COUNT(J16,J17)&lt;2,"",J16/J17*100)</f>
         <v/>
       </c>
-      <c r="K20" s="170">
+      <c r="K20" s="171">
         <f>IF(COUNT(K16,K17)&lt;2,"",K16/K17*100)</f>
         <v/>
       </c>
-      <c r="L20" s="170">
+      <c r="L20" s="171">
         <f>IF(COUNT(L16,L17)&lt;2,"",L16/L17*100)</f>
         <v/>
       </c>
-      <c r="M20" s="170">
+      <c r="M20" s="171">
         <f>IF(COUNT(M16,M17)&lt;2,"",M16/M17*100)</f>
         <v/>
       </c>
-      <c r="N20" s="170">
+      <c r="N20" s="171">
         <f>IF(COUNT(N16,N17)&lt;2,"",N16/N17*100)</f>
         <v/>
       </c>
-      <c r="O20" s="170">
+      <c r="O20" s="171">
         <f>IF(COUNT(O16,O17)&lt;2,"",O16/O17*100)</f>
         <v/>
       </c>
-      <c r="P20" s="170">
+      <c r="P20" s="171">
         <f>IF(COUNT(P16,P17)&lt;2,"",P16/P17*100)</f>
         <v/>
       </c>
-      <c r="Q20" s="170">
+      <c r="Q20" s="171">
         <f>IF(COUNT(Q16,Q17)&lt;2,"",Q16/Q17*100)</f>
         <v/>
       </c>
-      <c r="R20" s="170">
+      <c r="R20" s="171">
         <f>IF(COUNT(R16,R17)&lt;2,"",R16/R17*100)</f>
         <v/>
       </c>
-      <c r="S20" s="170">
+      <c r="S20" s="171">
         <f>IF(COUNT(S16,S17)&lt;2,"",S16/S17*100)</f>
         <v/>
       </c>
@@ -50372,62 +51240,62 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D23" s="171" t="n"/>
+      <c r="D23" s="167" t="n"/>
       <c r="E23" s="156" t="inlineStr">
         <is>
           <t>Includes deregistration, export and write-off; used imports and re-registration would lower it.</t>
         </is>
       </c>
-      <c r="F23" s="171" t="n"/>
-      <c r="G23" s="171">
+      <c r="F23" s="167" t="n"/>
+      <c r="G23" s="167">
         <f>IF(COUNT(F6,G6,G14)&lt;3,"",F6+G14-G6)</f>
         <v/>
       </c>
-      <c r="H23" s="171">
+      <c r="H23" s="167">
         <f>IF(COUNT(G6,H6,H14)&lt;3,"",G6+H14-H6)</f>
         <v/>
       </c>
-      <c r="I23" s="171">
+      <c r="I23" s="167">
         <f>IF(COUNT(H6,I6,I14)&lt;3,"",H6+I14-I6)</f>
         <v/>
       </c>
-      <c r="J23" s="171">
+      <c r="J23" s="167">
         <f>IF(COUNT(I6,J6,J14)&lt;3,"",I6+J14-J6)</f>
         <v/>
       </c>
-      <c r="K23" s="171">
+      <c r="K23" s="167">
         <f>IF(COUNT(J6,K6,K14)&lt;3,"",J6+K14-K6)</f>
         <v/>
       </c>
-      <c r="L23" s="171">
+      <c r="L23" s="167">
         <f>IF(COUNT(K6,L6,L14)&lt;3,"",K6+L14-L6)</f>
         <v/>
       </c>
-      <c r="M23" s="171">
+      <c r="M23" s="167">
         <f>IF(COUNT(L6,M6,M14)&lt;3,"",L6+M14-M6)</f>
         <v/>
       </c>
-      <c r="N23" s="171">
+      <c r="N23" s="167">
         <f>IF(COUNT(M6,N6,N14)&lt;3,"",M6+N14-N6)</f>
         <v/>
       </c>
-      <c r="O23" s="171">
+      <c r="O23" s="167">
         <f>IF(COUNT(N6,O6,O14)&lt;3,"",N6+O14-O6)</f>
         <v/>
       </c>
-      <c r="P23" s="171">
+      <c r="P23" s="167">
         <f>IF(COUNT(O6,P6,P14)&lt;3,"",O6+P14-P6)</f>
         <v/>
       </c>
-      <c r="Q23" s="171">
+      <c r="Q23" s="167">
         <f>IF(COUNT(P6,Q6,Q14)&lt;3,"",P6+Q14-Q6)</f>
         <v/>
       </c>
-      <c r="R23" s="171">
+      <c r="R23" s="167">
         <f>IF(COUNT(Q6,R6,R14)&lt;3,"",Q6+R14-R6)</f>
         <v/>
       </c>
-      <c r="S23" s="171">
+      <c r="S23" s="167">
         <f>IF(COUNT(R6,S6,S14)&lt;3,"",R6+S14-S6)</f>
         <v/>
       </c>
@@ -50451,7 +51319,7 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D24" s="170" t="n">
+      <c r="D24" s="171" t="n">
         <v>4</v>
       </c>
       <c r="E24" s="156" t="inlineStr">
@@ -50459,56 +51327,56 @@
           <t>Retired divided by last December's stock. Column D is the model's scrappage rate.</t>
         </is>
       </c>
-      <c r="F24" s="170" t="n"/>
-      <c r="G24" s="170">
+      <c r="F24" s="171" t="n"/>
+      <c r="G24" s="171">
         <f>IF(ISNUMBER(G23),G23/F6*100,"")</f>
         <v/>
       </c>
-      <c r="H24" s="170">
+      <c r="H24" s="171">
         <f>IF(ISNUMBER(H23),H23/G6*100,"")</f>
         <v/>
       </c>
-      <c r="I24" s="170">
+      <c r="I24" s="171">
         <f>IF(ISNUMBER(I23),I23/H6*100,"")</f>
         <v/>
       </c>
-      <c r="J24" s="170">
+      <c r="J24" s="171">
         <f>IF(ISNUMBER(J23),J23/I6*100,"")</f>
         <v/>
       </c>
-      <c r="K24" s="170">
+      <c r="K24" s="171">
         <f>IF(ISNUMBER(K23),K23/J6*100,"")</f>
         <v/>
       </c>
-      <c r="L24" s="170">
+      <c r="L24" s="171">
         <f>IF(ISNUMBER(L23),L23/K6*100,"")</f>
         <v/>
       </c>
-      <c r="M24" s="170">
+      <c r="M24" s="171">
         <f>IF(ISNUMBER(M23),M23/L6*100,"")</f>
         <v/>
       </c>
-      <c r="N24" s="170">
+      <c r="N24" s="171">
         <f>IF(ISNUMBER(N23),N23/M6*100,"")</f>
         <v/>
       </c>
-      <c r="O24" s="170">
+      <c r="O24" s="171">
         <f>IF(ISNUMBER(O23),O23/N6*100,"")</f>
         <v/>
       </c>
-      <c r="P24" s="170">
+      <c r="P24" s="171">
         <f>IF(ISNUMBER(P23),P23/O6*100,"")</f>
         <v/>
       </c>
-      <c r="Q24" s="170">
+      <c r="Q24" s="171">
         <f>IF(ISNUMBER(Q23),Q23/P6*100,"")</f>
         <v/>
       </c>
-      <c r="R24" s="170">
+      <c r="R24" s="171">
         <f>IF(ISNUMBER(R23),R23/Q6*100,"")</f>
         <v/>
       </c>
-      <c r="S24" s="170">
+      <c r="S24" s="171">
         <f>IF(ISNUMBER(S23),S23/R6*100,"")</f>
         <v/>
       </c>
@@ -50540,62 +51408,62 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D25" s="171" t="n"/>
+      <c r="D25" s="167" t="n"/>
       <c r="E25" s="156" t="inlineStr">
         <is>
           <t>Includes deregistration, export and write-off; used imports and re-registration would lower it.</t>
         </is>
       </c>
-      <c r="F25" s="171" t="n"/>
-      <c r="G25" s="171">
+      <c r="F25" s="167" t="n"/>
+      <c r="G25" s="167">
         <f>IF(COUNT(F7,G7,G15)&lt;3,"",F7+G15-G7)</f>
         <v/>
       </c>
-      <c r="H25" s="171">
+      <c r="H25" s="167">
         <f>IF(COUNT(G7,H7,H15)&lt;3,"",G7+H15-H7)</f>
         <v/>
       </c>
-      <c r="I25" s="171">
+      <c r="I25" s="167">
         <f>IF(COUNT(H7,I7,I15)&lt;3,"",H7+I15-I7)</f>
         <v/>
       </c>
-      <c r="J25" s="171">
+      <c r="J25" s="167">
         <f>IF(COUNT(I7,J7,J15)&lt;3,"",I7+J15-J7)</f>
         <v/>
       </c>
-      <c r="K25" s="171">
+      <c r="K25" s="167">
         <f>IF(COUNT(J7,K7,K15)&lt;3,"",J7+K15-K7)</f>
         <v/>
       </c>
-      <c r="L25" s="171">
+      <c r="L25" s="167">
         <f>IF(COUNT(K7,L7,L15)&lt;3,"",K7+L15-L7)</f>
         <v/>
       </c>
-      <c r="M25" s="171">
+      <c r="M25" s="167">
         <f>IF(COUNT(L7,M7,M15)&lt;3,"",L7+M15-M7)</f>
         <v/>
       </c>
-      <c r="N25" s="171">
+      <c r="N25" s="167">
         <f>IF(COUNT(M7,N7,N15)&lt;3,"",M7+N15-N7)</f>
         <v/>
       </c>
-      <c r="O25" s="171">
+      <c r="O25" s="167">
         <f>IF(COUNT(N7,O7,O15)&lt;3,"",N7+O15-O7)</f>
         <v/>
       </c>
-      <c r="P25" s="171">
+      <c r="P25" s="167">
         <f>IF(COUNT(O7,P7,P15)&lt;3,"",O7+P15-P7)</f>
         <v/>
       </c>
-      <c r="Q25" s="171">
+      <c r="Q25" s="167">
         <f>IF(COUNT(P7,Q7,Q15)&lt;3,"",P7+Q15-Q7)</f>
         <v/>
       </c>
-      <c r="R25" s="171">
+      <c r="R25" s="167">
         <f>IF(COUNT(Q7,R7,R15)&lt;3,"",Q7+R15-R7)</f>
         <v/>
       </c>
-      <c r="S25" s="171">
+      <c r="S25" s="167">
         <f>IF(COUNT(R7,S7,S15)&lt;3,"",R7+S15-S7)</f>
         <v/>
       </c>
@@ -50619,7 +51487,7 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D26" s="170" t="n">
+      <c r="D26" s="171" t="n">
         <v>5</v>
       </c>
       <c r="E26" s="156" t="inlineStr">
@@ -50627,56 +51495,56 @@
           <t>Retired divided by last December's stock. Column D is the model's scrappage rate.</t>
         </is>
       </c>
-      <c r="F26" s="170" t="n"/>
-      <c r="G26" s="170">
+      <c r="F26" s="171" t="n"/>
+      <c r="G26" s="171">
         <f>IF(ISNUMBER(G25),G25/F7*100,"")</f>
         <v/>
       </c>
-      <c r="H26" s="170">
+      <c r="H26" s="171">
         <f>IF(ISNUMBER(H25),H25/G7*100,"")</f>
         <v/>
       </c>
-      <c r="I26" s="170">
+      <c r="I26" s="171">
         <f>IF(ISNUMBER(I25),I25/H7*100,"")</f>
         <v/>
       </c>
-      <c r="J26" s="170">
+      <c r="J26" s="171">
         <f>IF(ISNUMBER(J25),J25/I7*100,"")</f>
         <v/>
       </c>
-      <c r="K26" s="170">
+      <c r="K26" s="171">
         <f>IF(ISNUMBER(K25),K25/J7*100,"")</f>
         <v/>
       </c>
-      <c r="L26" s="170">
+      <c r="L26" s="171">
         <f>IF(ISNUMBER(L25),L25/K7*100,"")</f>
         <v/>
       </c>
-      <c r="M26" s="170">
+      <c r="M26" s="171">
         <f>IF(ISNUMBER(M25),M25/L7*100,"")</f>
         <v/>
       </c>
-      <c r="N26" s="170">
+      <c r="N26" s="171">
         <f>IF(ISNUMBER(N25),N25/M7*100,"")</f>
         <v/>
       </c>
-      <c r="O26" s="170">
+      <c r="O26" s="171">
         <f>IF(ISNUMBER(O25),O25/N7*100,"")</f>
         <v/>
       </c>
-      <c r="P26" s="170">
+      <c r="P26" s="171">
         <f>IF(ISNUMBER(P25),P25/O7*100,"")</f>
         <v/>
       </c>
-      <c r="Q26" s="170">
+      <c r="Q26" s="171">
         <f>IF(ISNUMBER(Q25),Q25/P7*100,"")</f>
         <v/>
       </c>
-      <c r="R26" s="170">
+      <c r="R26" s="171">
         <f>IF(ISNUMBER(R25),R25/Q7*100,"")</f>
         <v/>
       </c>
-      <c r="S26" s="170">
+      <c r="S26" s="171">
         <f>IF(ISNUMBER(S25),S25/R7*100,"")</f>
         <v/>
       </c>
@@ -50708,62 +51576,62 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D27" s="171" t="n"/>
+      <c r="D27" s="167" t="n"/>
       <c r="E27" s="156" t="inlineStr">
         <is>
           <t>Includes deregistration, export and write-off; used imports and re-registration would lower it.</t>
         </is>
       </c>
-      <c r="F27" s="171" t="n"/>
-      <c r="G27" s="171">
+      <c r="F27" s="167" t="n"/>
+      <c r="G27" s="167">
         <f>IF(COUNT(F8,G8,G16)&lt;3,"",F8+G16-G8)</f>
         <v/>
       </c>
-      <c r="H27" s="171">
+      <c r="H27" s="167">
         <f>IF(COUNT(G8,H8,H16)&lt;3,"",G8+H16-H8)</f>
         <v/>
       </c>
-      <c r="I27" s="171">
+      <c r="I27" s="167">
         <f>IF(COUNT(H8,I8,I16)&lt;3,"",H8+I16-I8)</f>
         <v/>
       </c>
-      <c r="J27" s="171">
+      <c r="J27" s="167">
         <f>IF(COUNT(I8,J8,J16)&lt;3,"",I8+J16-J8)</f>
         <v/>
       </c>
-      <c r="K27" s="171">
+      <c r="K27" s="167">
         <f>IF(COUNT(J8,K8,K16)&lt;3,"",J8+K16-K8)</f>
         <v/>
       </c>
-      <c r="L27" s="171">
+      <c r="L27" s="167">
         <f>IF(COUNT(K8,L8,L16)&lt;3,"",K8+L16-L8)</f>
         <v/>
       </c>
-      <c r="M27" s="171">
+      <c r="M27" s="167">
         <f>IF(COUNT(L8,M8,M16)&lt;3,"",L8+M16-M8)</f>
         <v/>
       </c>
-      <c r="N27" s="171">
+      <c r="N27" s="167">
         <f>IF(COUNT(M8,N8,N16)&lt;3,"",M8+N16-N8)</f>
         <v/>
       </c>
-      <c r="O27" s="171">
+      <c r="O27" s="167">
         <f>IF(COUNT(N8,O8,O16)&lt;3,"",N8+O16-O8)</f>
         <v/>
       </c>
-      <c r="P27" s="171">
+      <c r="P27" s="167">
         <f>IF(COUNT(O8,P8,P16)&lt;3,"",O8+P16-P8)</f>
         <v/>
       </c>
-      <c r="Q27" s="171">
+      <c r="Q27" s="167">
         <f>IF(COUNT(P8,Q8,Q16)&lt;3,"",P8+Q16-Q8)</f>
         <v/>
       </c>
-      <c r="R27" s="171">
+      <c r="R27" s="167">
         <f>IF(COUNT(Q8,R8,R16)&lt;3,"",Q8+R16-R8)</f>
         <v/>
       </c>
-      <c r="S27" s="171">
+      <c r="S27" s="167">
         <f>IF(COUNT(R8,S8,S16)&lt;3,"",R8+S16-S8)</f>
         <v/>
       </c>
@@ -50787,7 +51655,7 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D28" s="170" t="n">
+      <c r="D28" s="171" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="156" t="inlineStr">
@@ -50795,56 +51663,56 @@
           <t>Retired divided by last December's stock. Column D is the model's scrappage rate.</t>
         </is>
       </c>
-      <c r="F28" s="170" t="n"/>
-      <c r="G28" s="170">
+      <c r="F28" s="171" t="n"/>
+      <c r="G28" s="171">
         <f>IF(ISNUMBER(G27),G27/F8*100,"")</f>
         <v/>
       </c>
-      <c r="H28" s="170">
+      <c r="H28" s="171">
         <f>IF(ISNUMBER(H27),H27/G8*100,"")</f>
         <v/>
       </c>
-      <c r="I28" s="170">
+      <c r="I28" s="171">
         <f>IF(ISNUMBER(I27),I27/H8*100,"")</f>
         <v/>
       </c>
-      <c r="J28" s="170">
+      <c r="J28" s="171">
         <f>IF(ISNUMBER(J27),J27/I8*100,"")</f>
         <v/>
       </c>
-      <c r="K28" s="170">
+      <c r="K28" s="171">
         <f>IF(ISNUMBER(K27),K27/J8*100,"")</f>
         <v/>
       </c>
-      <c r="L28" s="170">
+      <c r="L28" s="171">
         <f>IF(ISNUMBER(L27),L27/K8*100,"")</f>
         <v/>
       </c>
-      <c r="M28" s="170">
+      <c r="M28" s="171">
         <f>IF(ISNUMBER(M27),M27/L8*100,"")</f>
         <v/>
       </c>
-      <c r="N28" s="170">
+      <c r="N28" s="171">
         <f>IF(ISNUMBER(N27),N27/M8*100,"")</f>
         <v/>
       </c>
-      <c r="O28" s="170">
+      <c r="O28" s="171">
         <f>IF(ISNUMBER(O27),O27/N8*100,"")</f>
         <v/>
       </c>
-      <c r="P28" s="170">
+      <c r="P28" s="171">
         <f>IF(ISNUMBER(P27),P27/O8*100,"")</f>
         <v/>
       </c>
-      <c r="Q28" s="170">
+      <c r="Q28" s="171">
         <f>IF(ISNUMBER(Q27),Q27/P8*100,"")</f>
         <v/>
       </c>
-      <c r="R28" s="170">
+      <c r="R28" s="171">
         <f>IF(ISNUMBER(R27),R27/Q8*100,"")</f>
         <v/>
       </c>
-      <c r="S28" s="170">
+      <c r="S28" s="171">
         <f>IF(ISNUMBER(S27),S27/R8*100,"")</f>
         <v/>
       </c>
@@ -50904,38 +51772,38 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D31" s="167" t="n"/>
+      <c r="D31" s="166" t="n"/>
       <c r="E31" s="152" t="inlineStr">
         <is>
           <t>Total market, not passenger cars only.</t>
         </is>
       </c>
-      <c r="F31" s="167" t="n"/>
-      <c r="G31" s="167" t="n"/>
-      <c r="H31" s="167" t="n"/>
-      <c r="I31" s="167" t="n"/>
-      <c r="J31" s="167" t="n"/>
-      <c r="K31" s="167" t="n"/>
-      <c r="L31" s="167" t="n"/>
-      <c r="M31" s="167" t="n">
+      <c r="F31" s="166" t="n"/>
+      <c r="G31" s="166" t="n"/>
+      <c r="H31" s="166" t="n"/>
+      <c r="I31" s="166" t="n"/>
+      <c r="J31" s="166" t="n"/>
+      <c r="K31" s="166" t="n"/>
+      <c r="L31" s="166" t="n"/>
+      <c r="M31" s="166" t="n">
         <v>154</v>
       </c>
-      <c r="N31" s="167" t="n">
+      <c r="N31" s="166" t="n">
         <v>92</v>
       </c>
-      <c r="O31" s="167" t="n">
+      <c r="O31" s="166" t="n">
         <v>218</v>
       </c>
-      <c r="P31" s="167" t="n">
+      <c r="P31" s="166" t="n">
         <v>502</v>
       </c>
-      <c r="Q31" s="167" t="n">
+      <c r="Q31" s="166" t="n">
         <v>929</v>
       </c>
-      <c r="R31" s="167" t="n">
+      <c r="R31" s="166" t="n">
         <v>1257</v>
       </c>
-      <c r="S31" s="167" t="n">
+      <c r="S31" s="166" t="n">
         <v>1088</v>
       </c>
       <c r="T31" s="152" t="inlineStr">
@@ -51052,38 +51920,38 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D33" s="167" t="n"/>
+      <c r="D33" s="166" t="n"/>
       <c r="E33" s="152" t="inlineStr">
         <is>
           <t>Total market, not passenger cars only.</t>
         </is>
       </c>
-      <c r="F33" s="167" t="n"/>
-      <c r="G33" s="167" t="n"/>
-      <c r="H33" s="167" t="n"/>
-      <c r="I33" s="167" t="n"/>
-      <c r="J33" s="167" t="n"/>
-      <c r="K33" s="167" t="n"/>
-      <c r="L33" s="167" t="n"/>
-      <c r="M33" s="167" t="n">
+      <c r="F33" s="166" t="n"/>
+      <c r="G33" s="166" t="n"/>
+      <c r="H33" s="166" t="n"/>
+      <c r="I33" s="166" t="n"/>
+      <c r="J33" s="166" t="n"/>
+      <c r="K33" s="166" t="n"/>
+      <c r="L33" s="166" t="n"/>
+      <c r="M33" s="166" t="n">
         <v>72</v>
       </c>
-      <c r="N33" s="167" t="n">
+      <c r="N33" s="166" t="n">
         <v>77</v>
       </c>
-      <c r="O33" s="167" t="n">
+      <c r="O33" s="166" t="n">
         <v>51</v>
       </c>
-      <c r="P33" s="167" t="n">
+      <c r="P33" s="166" t="n">
         <v>122</v>
       </c>
-      <c r="Q33" s="167" t="n">
+      <c r="Q33" s="166" t="n">
         <v>368</v>
       </c>
-      <c r="R33" s="167" t="n">
+      <c r="R33" s="166" t="n">
         <v>738</v>
       </c>
-      <c r="S33" s="167" t="n">
+      <c r="S33" s="166" t="n">
         <v>2810</v>
       </c>
       <c r="T33" s="152" t="inlineStr">
@@ -51200,38 +52068,38 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D35" s="167" t="n"/>
+      <c r="D35" s="166" t="n"/>
       <c r="E35" s="152" t="inlineStr">
         <is>
           <t>Total market, not passenger cars only.</t>
         </is>
       </c>
-      <c r="F35" s="167" t="n"/>
-      <c r="G35" s="167" t="n"/>
-      <c r="H35" s="167" t="n"/>
-      <c r="I35" s="167" t="n"/>
-      <c r="J35" s="167" t="n"/>
-      <c r="K35" s="167" t="n"/>
-      <c r="L35" s="167" t="n"/>
-      <c r="M35" s="167" t="n">
+      <c r="F35" s="166" t="n"/>
+      <c r="G35" s="166" t="n"/>
+      <c r="H35" s="166" t="n"/>
+      <c r="I35" s="166" t="n"/>
+      <c r="J35" s="166" t="n"/>
+      <c r="K35" s="166" t="n"/>
+      <c r="L35" s="166" t="n"/>
+      <c r="M35" s="166" t="n">
         <v>181</v>
       </c>
-      <c r="N35" s="167" t="n">
+      <c r="N35" s="166" t="n">
         <v>155</v>
       </c>
-      <c r="O35" s="167" t="n">
+      <c r="O35" s="166" t="n">
         <v>627</v>
       </c>
-      <c r="P35" s="167" t="n">
+      <c r="P35" s="166" t="n">
         <v>4070</v>
       </c>
-      <c r="Q35" s="167" t="n">
+      <c r="Q35" s="166" t="n">
         <v>6485</v>
       </c>
-      <c r="R35" s="167" t="n">
+      <c r="R35" s="166" t="n">
         <v>13616</v>
       </c>
-      <c r="S35" s="167" t="n">
+      <c r="S35" s="166" t="n">
         <v>12818</v>
       </c>
       <c r="T35" s="152" t="inlineStr">
@@ -51376,28 +52244,28 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D39" s="167" t="n"/>
+      <c r="D39" s="166" t="n"/>
       <c r="E39" s="152" t="inlineStr">
         <is>
           <t>All classes, December 2023.</t>
         </is>
       </c>
-      <c r="F39" s="167" t="n"/>
-      <c r="G39" s="167" t="n"/>
-      <c r="H39" s="167" t="n"/>
-      <c r="I39" s="167" t="n"/>
-      <c r="J39" s="167" t="n"/>
-      <c r="K39" s="167" t="n"/>
-      <c r="L39" s="167" t="n"/>
-      <c r="M39" s="167" t="n"/>
-      <c r="N39" s="167" t="n"/>
-      <c r="O39" s="167" t="n"/>
-      <c r="P39" s="167" t="n"/>
-      <c r="Q39" s="167" t="n">
+      <c r="F39" s="166" t="n"/>
+      <c r="G39" s="166" t="n"/>
+      <c r="H39" s="166" t="n"/>
+      <c r="I39" s="166" t="n"/>
+      <c r="J39" s="166" t="n"/>
+      <c r="K39" s="166" t="n"/>
+      <c r="L39" s="166" t="n"/>
+      <c r="M39" s="166" t="n"/>
+      <c r="N39" s="166" t="n"/>
+      <c r="O39" s="166" t="n"/>
+      <c r="P39" s="166" t="n"/>
+      <c r="Q39" s="166" t="n">
         <v>8555772</v>
       </c>
-      <c r="R39" s="167" t="n"/>
-      <c r="S39" s="167" t="n"/>
+      <c r="R39" s="166" t="n"/>
+      <c r="S39" s="166" t="n"/>
       <c r="T39" s="152" t="inlineStr">
         <is>
           <t>One date only</t>
@@ -51426,28 +52294,28 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D40" s="167" t="n"/>
+      <c r="D40" s="166" t="n"/>
       <c r="E40" s="152" t="inlineStr">
         <is>
           <t>All classes, December 2023.</t>
         </is>
       </c>
-      <c r="F40" s="167" t="n"/>
-      <c r="G40" s="167" t="n"/>
-      <c r="H40" s="167" t="n"/>
-      <c r="I40" s="167" t="n"/>
-      <c r="J40" s="167" t="n"/>
-      <c r="K40" s="167" t="n"/>
-      <c r="L40" s="167" t="n"/>
-      <c r="M40" s="167" t="n"/>
-      <c r="N40" s="167" t="n"/>
-      <c r="O40" s="167" t="n"/>
-      <c r="P40" s="167" t="n"/>
-      <c r="Q40" s="167" t="n">
+      <c r="F40" s="166" t="n"/>
+      <c r="G40" s="166" t="n"/>
+      <c r="H40" s="166" t="n"/>
+      <c r="I40" s="166" t="n"/>
+      <c r="J40" s="166" t="n"/>
+      <c r="K40" s="166" t="n"/>
+      <c r="L40" s="166" t="n"/>
+      <c r="M40" s="166" t="n"/>
+      <c r="N40" s="166" t="n"/>
+      <c r="O40" s="166" t="n"/>
+      <c r="P40" s="166" t="n"/>
+      <c r="Q40" s="166" t="n">
         <v>3335546</v>
       </c>
-      <c r="R40" s="167" t="n"/>
-      <c r="S40" s="167" t="n"/>
+      <c r="R40" s="166" t="n"/>
+      <c r="S40" s="166" t="n"/>
       <c r="T40" s="152" t="inlineStr">
         <is>
           <t>One date only</t>
@@ -51476,28 +52344,28 @@
           <t>Source observation</t>
         </is>
       </c>
-      <c r="D41" s="167" t="n"/>
+      <c r="D41" s="166" t="n"/>
       <c r="E41" s="152" t="inlineStr">
         <is>
           <t>All classes, December 2023.</t>
         </is>
       </c>
-      <c r="F41" s="167" t="n"/>
-      <c r="G41" s="167" t="n"/>
-      <c r="H41" s="167" t="n"/>
-      <c r="I41" s="167" t="n"/>
-      <c r="J41" s="167" t="n"/>
-      <c r="K41" s="167" t="n"/>
-      <c r="L41" s="167" t="n"/>
-      <c r="M41" s="167" t="n"/>
-      <c r="N41" s="167" t="n"/>
-      <c r="O41" s="167" t="n"/>
-      <c r="P41" s="167" t="n"/>
-      <c r="Q41" s="167" t="n">
+      <c r="F41" s="166" t="n"/>
+      <c r="G41" s="166" t="n"/>
+      <c r="H41" s="166" t="n"/>
+      <c r="I41" s="166" t="n"/>
+      <c r="J41" s="166" t="n"/>
+      <c r="K41" s="166" t="n"/>
+      <c r="L41" s="166" t="n"/>
+      <c r="M41" s="166" t="n"/>
+      <c r="N41" s="166" t="n"/>
+      <c r="O41" s="166" t="n"/>
+      <c r="P41" s="166" t="n"/>
+      <c r="Q41" s="166" t="n">
         <v>4090</v>
       </c>
-      <c r="R41" s="167" t="n"/>
-      <c r="S41" s="167" t="n"/>
+      <c r="R41" s="166" t="n"/>
+      <c r="S41" s="166" t="n"/>
       <c r="T41" s="152" t="inlineStr">
         <is>
           <t>One date only</t>
@@ -51526,65 +52394,65 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D42" s="171" t="n"/>
+      <c r="D42" s="167" t="n"/>
       <c r="E42" s="156" t="inlineStr">
         <is>
           <t>Cars x 17% plus light commercial x 70% plus trucks and buses. The model's split is for new sales; applied here to stock as a test.</t>
         </is>
       </c>
-      <c r="F42" s="171">
+      <c r="F42" s="167">
         <f>IF(COUNT(F6,F7)&lt;2,"",F6*0.17+F7*0.7+F8+F9)</f>
         <v/>
       </c>
-      <c r="G42" s="171">
+      <c r="G42" s="167">
         <f>IF(COUNT(G6,G7)&lt;2,"",G6*0.17+G7*0.7+G8+G9)</f>
         <v/>
       </c>
-      <c r="H42" s="171">
+      <c r="H42" s="167">
         <f>IF(COUNT(H6,H7)&lt;2,"",H6*0.17+H7*0.7+H8+H9)</f>
         <v/>
       </c>
-      <c r="I42" s="171">
+      <c r="I42" s="167">
         <f>IF(COUNT(I6,I7)&lt;2,"",I6*0.17+I7*0.7+I8+I9)</f>
         <v/>
       </c>
-      <c r="J42" s="171">
+      <c r="J42" s="167">
         <f>IF(COUNT(J6,J7)&lt;2,"",J6*0.17+J7*0.7+J8+J9)</f>
         <v/>
       </c>
-      <c r="K42" s="171">
+      <c r="K42" s="167">
         <f>IF(COUNT(K6,K7)&lt;2,"",K6*0.17+K7*0.7+K8+K9)</f>
         <v/>
       </c>
-      <c r="L42" s="171">
+      <c r="L42" s="167">
         <f>IF(COUNT(L6,L7)&lt;2,"",L6*0.17+L7*0.7+L8+L9)</f>
         <v/>
       </c>
-      <c r="M42" s="171">
+      <c r="M42" s="167">
         <f>IF(COUNT(M6,M7)&lt;2,"",M6*0.17+M7*0.7+M8+M9)</f>
         <v/>
       </c>
-      <c r="N42" s="171">
+      <c r="N42" s="167">
         <f>IF(COUNT(N6,N7)&lt;2,"",N6*0.17+N7*0.7+N8+N9)</f>
         <v/>
       </c>
-      <c r="O42" s="171">
+      <c r="O42" s="167">
         <f>IF(COUNT(O6,O7)&lt;2,"",O6*0.17+O7*0.7+O8+O9)</f>
         <v/>
       </c>
-      <c r="P42" s="171">
+      <c r="P42" s="167">
         <f>IF(COUNT(P6,P7)&lt;2,"",P6*0.17+P7*0.7+P8+P9)</f>
         <v/>
       </c>
-      <c r="Q42" s="171">
+      <c r="Q42" s="167">
         <f>IF(COUNT(Q6,Q7)&lt;2,"",Q6*0.17+Q7*0.7+Q8+Q9)</f>
         <v/>
       </c>
-      <c r="R42" s="171">
+      <c r="R42" s="167">
         <f>IF(COUNT(R6,R7)&lt;2,"",R6*0.17+R7*0.7+R8+R9)</f>
         <v/>
       </c>
-      <c r="S42" s="171">
+      <c r="S42" s="167">
         <f>IF(COUNT(S6,S7)&lt;2,"",S6*0.17+S7*0.7+S8+S9)</f>
         <v/>
       </c>
@@ -51612,65 +52480,65 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D43" s="171" t="n"/>
+      <c r="D43" s="167" t="n"/>
       <c r="E43" s="156" t="inlineStr">
         <is>
           <t>Positive means the model's split puts more diesel vehicles on the road than are registered. Minibuses and motorcycles are left out of the implied figure.</t>
         </is>
       </c>
-      <c r="F43" s="171">
+      <c r="F43" s="167">
         <f>IF(COUNT(F42,F40)&lt;2,"",F42-F40)</f>
         <v/>
       </c>
-      <c r="G43" s="171">
+      <c r="G43" s="167">
         <f>IF(COUNT(G42,G40)&lt;2,"",G42-G40)</f>
         <v/>
       </c>
-      <c r="H43" s="171">
+      <c r="H43" s="167">
         <f>IF(COUNT(H42,H40)&lt;2,"",H42-H40)</f>
         <v/>
       </c>
-      <c r="I43" s="171">
+      <c r="I43" s="167">
         <f>IF(COUNT(I42,I40)&lt;2,"",I42-I40)</f>
         <v/>
       </c>
-      <c r="J43" s="171">
+      <c r="J43" s="167">
         <f>IF(COUNT(J42,J40)&lt;2,"",J42-J40)</f>
         <v/>
       </c>
-      <c r="K43" s="171">
+      <c r="K43" s="167">
         <f>IF(COUNT(K42,K40)&lt;2,"",K42-K40)</f>
         <v/>
       </c>
-      <c r="L43" s="171">
+      <c r="L43" s="167">
         <f>IF(COUNT(L42,L40)&lt;2,"",L42-L40)</f>
         <v/>
       </c>
-      <c r="M43" s="171">
+      <c r="M43" s="167">
         <f>IF(COUNT(M42,M40)&lt;2,"",M42-M40)</f>
         <v/>
       </c>
-      <c r="N43" s="171">
+      <c r="N43" s="167">
         <f>IF(COUNT(N42,N40)&lt;2,"",N42-N40)</f>
         <v/>
       </c>
-      <c r="O43" s="171">
+      <c r="O43" s="167">
         <f>IF(COUNT(O42,O40)&lt;2,"",O42-O40)</f>
         <v/>
       </c>
-      <c r="P43" s="171">
+      <c r="P43" s="167">
         <f>IF(COUNT(P42,P40)&lt;2,"",P42-P40)</f>
         <v/>
       </c>
-      <c r="Q43" s="171">
+      <c r="Q43" s="167">
         <f>IF(COUNT(Q42,Q40)&lt;2,"",Q42-Q40)</f>
         <v/>
       </c>
-      <c r="R43" s="171">
+      <c r="R43" s="167">
         <f>IF(COUNT(R42,R40)&lt;2,"",R42-R40)</f>
         <v/>
       </c>
-      <c r="S43" s="171">
+      <c r="S43" s="167">
         <f>IF(COUNT(S42,S40)&lt;2,"",S42-S40)</f>
         <v/>
       </c>
@@ -52046,65 +52914,65 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D52" s="171" t="n"/>
+      <c r="D52" s="167" t="n"/>
       <c r="E52" s="156" t="inlineStr">
         <is>
           <t>National petrol sales used (History) divided by registered petrol vehicles.</t>
         </is>
       </c>
-      <c r="F52" s="171">
+      <c r="F52" s="167">
         <f>IF(COUNT(History!F59,F39)&lt;2,"",History!F59*1000000/F39)</f>
         <v/>
       </c>
-      <c r="G52" s="171">
+      <c r="G52" s="167">
         <f>IF(COUNT(History!G59,G39)&lt;2,"",History!G59*1000000/G39)</f>
         <v/>
       </c>
-      <c r="H52" s="171">
+      <c r="H52" s="167">
         <f>IF(COUNT(History!H59,H39)&lt;2,"",History!H59*1000000/H39)</f>
         <v/>
       </c>
-      <c r="I52" s="171">
+      <c r="I52" s="167">
         <f>IF(COUNT(History!I59,I39)&lt;2,"",History!I59*1000000/I39)</f>
         <v/>
       </c>
-      <c r="J52" s="171">
+      <c r="J52" s="167">
         <f>IF(COUNT(History!J59,J39)&lt;2,"",History!J59*1000000/J39)</f>
         <v/>
       </c>
-      <c r="K52" s="171">
+      <c r="K52" s="167">
         <f>IF(COUNT(History!K59,K39)&lt;2,"",History!K59*1000000/K39)</f>
         <v/>
       </c>
-      <c r="L52" s="171">
+      <c r="L52" s="167">
         <f>IF(COUNT(History!L59,L39)&lt;2,"",History!L59*1000000/L39)</f>
         <v/>
       </c>
-      <c r="M52" s="171">
+      <c r="M52" s="167">
         <f>IF(COUNT(History!M59,M39)&lt;2,"",History!M59*1000000/M39)</f>
         <v/>
       </c>
-      <c r="N52" s="171">
+      <c r="N52" s="167">
         <f>IF(COUNT(History!N59,N39)&lt;2,"",History!N59*1000000/N39)</f>
         <v/>
       </c>
-      <c r="O52" s="171">
+      <c r="O52" s="167">
         <f>IF(COUNT(History!O59,O39)&lt;2,"",History!O59*1000000/O39)</f>
         <v/>
       </c>
-      <c r="P52" s="171">
+      <c r="P52" s="167">
         <f>IF(COUNT(History!P59,P39)&lt;2,"",History!P59*1000000/P39)</f>
         <v/>
       </c>
-      <c r="Q52" s="171">
+      <c r="Q52" s="167">
         <f>IF(COUNT(History!Q59,Q39)&lt;2,"",History!Q59*1000000/Q39)</f>
         <v/>
       </c>
-      <c r="R52" s="171">
+      <c r="R52" s="167">
         <f>IF(COUNT(History!R59,R39)&lt;2,"",History!R59*1000000/R39)</f>
         <v/>
       </c>
-      <c r="S52" s="171">
+      <c r="S52" s="167">
         <f>IF(COUNT(History!S59,S39)&lt;2,"",History!S59*1000000/S39)</f>
         <v/>
       </c>
@@ -52128,7 +52996,7 @@
           <t>Reporting formula</t>
         </is>
       </c>
-      <c r="D53" s="171" t="n">
+      <c r="D53" s="167" t="n">
         <v>17000</v>
       </c>
       <c r="E53" s="156" t="inlineStr">
@@ -52136,59 +53004,59 @@
           <t>Litres per vehicle divided by 8.2 L/100 km (the study's petrol car average). Column D is the model's passenger distance.</t>
         </is>
       </c>
-      <c r="F53" s="171">
+      <c r="F53" s="167">
         <f>IF(ISNUMBER(F52),F52/8.2*100,"")</f>
         <v/>
       </c>
-      <c r="G53" s="171">
+      <c r="G53" s="167">
         <f>IF(ISNUMBER(G52),G52/8.2*100,"")</f>
         <v/>
       </c>
-      <c r="H53" s="171">
+      <c r="H53" s="167">
         <f>IF(ISNUMBER(H52),H52/8.2*100,"")</f>
         <v/>
       </c>
-      <c r="I53" s="171">
+      <c r="I53" s="167">
         <f>IF(ISNUMBER(I52),I52/8.2*100,"")</f>
         <v/>
       </c>
-      <c r="J53" s="171">
+      <c r="J53" s="167">
         <f>IF(ISNUMBER(J52),J52/8.2*100,"")</f>
         <v/>
       </c>
-      <c r="K53" s="171">
+      <c r="K53" s="167">
         <f>IF(ISNUMBER(K52),K52/8.2*100,"")</f>
         <v/>
       </c>
-      <c r="L53" s="171">
+      <c r="L53" s="167">
         <f>IF(ISNUMBER(L52),L52/8.2*100,"")</f>
         <v/>
       </c>
-      <c r="M53" s="171">
+      <c r="M53" s="167">
         <f>IF(ISNUMBER(M52),M52/8.2*100,"")</f>
         <v/>
       </c>
-      <c r="N53" s="171">
+      <c r="N53" s="167">
         <f>IF(ISNUMBER(N52),N52/8.2*100,"")</f>
         <v/>
       </c>
-      <c r="O53" s="171">
+      <c r="O53" s="167">
         <f>IF(ISNUMBER(O52),O52/8.2*100,"")</f>
         <v/>
       </c>
-      <c r="P53" s="171">
+      <c r="P53" s="167">
         <f>IF(ISNUMBER(P52),P52/8.2*100,"")</f>
         <v/>
       </c>
-      <c r="Q53" s="171">
+      <c r="Q53" s="167">
         <f>IF(ISNUMBER(Q52),Q52/8.2*100,"")</f>
         <v/>
       </c>
-      <c r="R53" s="171">
+      <c r="R53" s="167">
         <f>IF(ISNUMBER(R52),R52/8.2*100,"")</f>
         <v/>
       </c>
-      <c r="S53" s="171">
+      <c r="S53" s="167">
         <f>IF(ISNUMBER(S52),S52/8.2*100,"")</f>
         <v/>
       </c>
@@ -52459,6 +53327,2119 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="110" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="149" t="inlineStr">
+        <is>
+          <t>Analyst response to the proposed low / medium / high inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>The HML sheet is unchanged. Values are low / medium / high. Replacements and added levers are proposals for review; source: fuel_lever_response_2026-10-07.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="150" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="B4" s="150" t="inlineStr">
+        <is>
+          <t>Lever</t>
+        </is>
+      </c>
+      <c r="C4" s="150" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D4" s="150" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="E4" s="150" t="inlineStr">
+        <is>
+          <t>Baseline basis</t>
+        </is>
+      </c>
+      <c r="F4" s="150" t="inlineStr">
+        <is>
+          <t>2030 proposed (Nigel)</t>
+        </is>
+      </c>
+      <c r="G4" s="150" t="inlineStr">
+        <is>
+          <t>2030 analyst</t>
+        </is>
+      </c>
+      <c r="H4" s="150" t="inlineStr">
+        <is>
+          <t>2035 proposed (Nigel)</t>
+        </is>
+      </c>
+      <c r="I4" s="150" t="inlineStr">
+        <is>
+          <t>2035 analyst</t>
+        </is>
+      </c>
+      <c r="J4" s="150" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="K4" s="150" t="inlineStr">
+        <is>
+          <t>Evidence and rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="173" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="B5" s="173" t="inlineStr">
+        <is>
+          <t>road_activity</t>
+        </is>
+      </c>
+      <c r="C5" s="173" t="inlineStr">
+        <is>
+          <t>index_2024_100</t>
+        </is>
+      </c>
+      <c r="D5" s="173" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E5" s="173" t="inlineStr">
+        <is>
+          <t>road freight payload 980 Mt in 2024 (Stats SA P7162)</t>
+        </is>
+      </c>
+      <c r="F5" s="173" t="inlineStr">
+        <is>
+          <t>95 / 115 / 135</t>
+        </is>
+      </c>
+      <c r="G5" s="173" t="inlineStr">
+        <is>
+          <t>95 / 115 / 135</t>
+        </is>
+      </c>
+      <c r="H5" s="173" t="inlineStr">
+        <is>
+          <t>95 / 135 / 175</t>
+        </is>
+      </c>
+      <c r="I5" s="173" t="inlineStr">
+        <is>
+          <t>95 / 135 / 150</t>
+        </is>
+      </c>
+      <c r="J5" s="173" t="inlineStr">
+        <is>
+          <t>replacement proposed</t>
+        </is>
+      </c>
+      <c r="K5" s="173" t="inlineStr">
+        <is>
+          <t>2014-2024 growth 2.4% a year; fastest eleven years (2012-2023) 3.7%; 2025 is 99.5. The 2035 high of 175 needs 5.2% a year for eleven years, without precedent; 150 matches the fastest observed. In tonne-kilometres the only published road figure found is 221 bn for 2013 (Havenga et al. 2016, Logistics Barometer), an average haul of about 307 km against Stats SA's tonnes. No annual tonne-kilometre series exists, so the index stays on tonnes. Part of past growth was freight leaving rail, so this overlaps the rail lever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="173" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="B6" s="173" t="inlineStr">
+        <is>
+          <t>rail_diversion</t>
+        </is>
+      </c>
+      <c r="C6" s="173" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D6" s="173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" s="173" t="inlineStr">
+        <is>
+          <t>rail 161 Mt and road 980 Mt in 2024 (Stats SA P7162)</t>
+        </is>
+      </c>
+      <c r="F6" s="173" t="inlineStr">
+        <is>
+          <t>0 / 10 / 20</t>
+        </is>
+      </c>
+      <c r="G6" s="173" t="inlineStr">
+        <is>
+          <t>0 / 3 / 9</t>
+        </is>
+      </c>
+      <c r="H6" s="173" t="inlineStr">
+        <is>
+          <t>0 / 20 / 35</t>
+        </is>
+      </c>
+      <c r="I6" s="173" t="inlineStr">
+        <is>
+          <t>0 / 7 / 13</t>
+        </is>
+      </c>
+      <c r="J6" s="173" t="inlineStr">
+        <is>
+          <t>replacement proposed</t>
+        </is>
+      </c>
+      <c r="K6" s="173" t="inlineStr">
+        <is>
+          <t>In tonnes, as a share of 2024 road tonnes: rail back to its 2020 level (190 Mt) is 3%; back to its 2017 peak (225 Mt) is 7%; the 250 Mt target for 2029/30 (Draft National Rail Master Plan, April 2026) is 9%; the market appetite of about 280 Mt reported with that plan is 12%. In tonne-kilometres: rail-friendly general freight was 47 bn in 2019 and rail carried 18 bn (Freight Logistics Roadmap, 2023, p.38); the 29 bn left on road is 13% of road tonne-kilometres (2013 base). Both routes put the ceiling at 12-13%, so the 2035 high is 13 and the proposed 20 and 35 exceed all rail-friendly freight. The 2030 medium of 10 is the full official target, not a middle case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="173" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="B7" s="173" t="inlineStr">
+        <is>
+          <t>ocgt_generation</t>
+        </is>
+      </c>
+      <c r="C7" s="173" t="inlineStr">
+        <is>
+          <t>index_FY2024_100</t>
+        </is>
+      </c>
+      <c r="D7" s="173" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E7" s="173" t="inlineStr">
+        <is>
+          <t>Eskom and independent OCGT output 5,143 GWh, year to March 2024</t>
+        </is>
+      </c>
+      <c r="F7" s="173" t="inlineStr">
+        <is>
+          <t>10 / 25 / 60</t>
+        </is>
+      </c>
+      <c r="G7" s="173" t="inlineStr">
+        <is>
+          <t>10 / 25 / 60</t>
+        </is>
+      </c>
+      <c r="H7" s="173" t="inlineStr">
+        <is>
+          <t>5 / 15 / 50</t>
+        </is>
+      </c>
+      <c r="I7" s="173" t="inlineStr">
+        <is>
+          <t>5 / 15 / 50</t>
+        </is>
+      </c>
+      <c r="J7" s="173" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="K7" s="173" t="inlineStr">
+        <is>
+          <t>Year to March 2025 is 55 and year to March 2026 is 21 on this index, so the medium of 25 in 2030 holds today's level. Reported burn is 0.31 litres per kWh in three years. No change proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="173" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="B8" s="173" t="inlineStr">
+        <is>
+          <t>new_cohort_efficiency</t>
+        </is>
+      </c>
+      <c r="C8" s="173" t="inlineStr">
+        <is>
+          <t>percent_per_year</t>
+        </is>
+      </c>
+      <c r="D8" s="173" t="inlineStr">
+        <is>
+          <t>0.5 to 1.0</t>
+        </is>
+      </c>
+      <c r="E8" s="173" t="inlineStr">
+        <is>
+          <t>registered diesel efficiency paths (low and high demand cases)</t>
+        </is>
+      </c>
+      <c r="F8" s="173" t="inlineStr">
+        <is>
+          <t>0.5 / 0.75 / 1</t>
+        </is>
+      </c>
+      <c r="G8" s="173" t="inlineStr">
+        <is>
+          <t>0.5 / 0.75 / 1</t>
+        </is>
+      </c>
+      <c r="H8" s="173" t="inlineStr">
+        <is>
+          <t>0.5 / 0.75 / 1</t>
+        </is>
+      </c>
+      <c r="I8" s="173" t="inlineStr">
+        <is>
+          <t>0.5 / 0.75 / 1</t>
+        </is>
+      </c>
+      <c r="J8" s="173" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="K8" s="173" t="inlineStr">
+        <is>
+          <t>Low and high equal the registered endpoints. Neither has a source. No change proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="173" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="B9" s="173" t="inlineStr">
+        <is>
+          <t>plant_utilisation</t>
+        </is>
+      </c>
+      <c r="C9" s="173" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D9" s="173" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E9" s="173" t="inlineStr">
+        <is>
+          <t>reported 2024 output over reported capacity, three plants; indicative</t>
+        </is>
+      </c>
+      <c r="F9" s="173" t="inlineStr">
+        <is>
+          <t>60 / 75 / 90</t>
+        </is>
+      </c>
+      <c r="G9" s="173" t="inlineStr">
+        <is>
+          <t>60 / 75 / 90</t>
+        </is>
+      </c>
+      <c r="H9" s="173" t="inlineStr">
+        <is>
+          <t>60 / 75 / 90</t>
+        </is>
+      </c>
+      <c r="I9" s="173" t="inlineStr">
+        <is>
+          <t>60 / 75 / 90</t>
+        </is>
+      </c>
+      <c r="J9" s="173" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="K9" s="173" t="inlineStr">
+        <is>
+          <t>Secunda 53%, Natref 71%, Astron 84%. Output is all refined products against crude-equivalent capacity; Sasol's year ends June; Astron converted at an assumed 36 MJ a litre. The model's Secunda capacity was 75 thousand barrels a day and is now FIASA's 150, with utilisation re-based so output is unchanged; the model then gives 62 thousand barrels a day for 2024 against 80 reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="173" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="B10" s="173" t="inlineStr">
+        <is>
+          <t>product_yield</t>
+        </is>
+      </c>
+      <c r="C10" s="173" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D10" s="173" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E10" s="173" t="inlineStr">
+        <is>
+          <t>diesel share of refinery output in 2024 (JODI; lowest reliability)</t>
+        </is>
+      </c>
+      <c r="F10" s="173" t="inlineStr">
+        <is>
+          <t>20 / 25 / 30</t>
+        </is>
+      </c>
+      <c r="G10" s="173" t="inlineStr">
+        <is>
+          <t>25 / 30 / 40</t>
+        </is>
+      </c>
+      <c r="H10" s="173" t="inlineStr">
+        <is>
+          <t>20 / 25 / 30</t>
+        </is>
+      </c>
+      <c r="I10" s="173" t="inlineStr">
+        <is>
+          <t>25 / 30 / 40</t>
+        </is>
+      </c>
+      <c r="J10" s="173" t="inlineStr">
+        <is>
+          <t>replacement proposed</t>
+        </is>
+      </c>
+      <c r="K10" s="173" t="inlineStr">
+        <is>
+          <t>Share of all refinery output: 31% in 2023 and 29% in 2024 (JODI). Before the Durban refineries closed, diesel was 40 to 42% of the five fuels in the 2017-2021 energy balances, which overstates its share of all output. The registered legacy yield is 25%. Replacement: legacy as the low, the recent observed share as the medium, the pre-closure share as the high. No plant-level slate is published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="173" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="B11" s="173" t="inlineStr">
+        <is>
+          <t>restart_capacity</t>
+        </is>
+      </c>
+      <c r="C11" s="173" t="inlineStr">
+        <is>
+          <t>thousand_bbl_per_day</t>
+        </is>
+      </c>
+      <c r="D11" s="173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="173" t="inlineStr">
+        <is>
+          <t>no committed addition</t>
+        </is>
+      </c>
+      <c r="F11" s="173" t="inlineStr">
+        <is>
+          <t>0 / 0 / 0</t>
+        </is>
+      </c>
+      <c r="G11" s="173" t="inlineStr">
+        <is>
+          <t>0 / 0 / 0</t>
+        </is>
+      </c>
+      <c r="H11" s="173" t="inlineStr">
+        <is>
+          <t>0 / 0 / 400</t>
+        </is>
+      </c>
+      <c r="I11" s="173" t="inlineStr">
+        <is>
+          <t>0 / 0 / 400</t>
+        </is>
+      </c>
+      <c r="J11" s="173" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="K11" s="173" t="inlineStr">
+        <is>
+          <t>Existing conditional illustration; no investment decision, timing or product slate is sourced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="173" t="inlineStr">
+        <is>
+          <t>jet</t>
+        </is>
+      </c>
+      <c r="B12" s="173" t="inlineStr">
+        <is>
+          <t>aircraft_movements</t>
+        </is>
+      </c>
+      <c r="C12" s="173" t="inlineStr">
+        <is>
+          <t>index_2024_100</t>
+        </is>
+      </c>
+      <c r="D12" s="173" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E12" s="173" t="inlineStr">
+        <is>
+          <t>456,214 movements at ACSA airports in 2024</t>
+        </is>
+      </c>
+      <c r="F12" s="173" t="inlineStr">
+        <is>
+          <t>100 / 120 / 140</t>
+        </is>
+      </c>
+      <c r="G12" s="173" t="inlineStr">
+        <is>
+          <t>100 / 110 / 125</t>
+        </is>
+      </c>
+      <c r="H12" s="173" t="inlineStr">
+        <is>
+          <t>100 / 145 / 190</t>
+        </is>
+      </c>
+      <c r="I12" s="173" t="inlineStr">
+        <is>
+          <t>100 / 120 / 140</t>
+        </is>
+      </c>
+      <c r="J12" s="173" t="inlineStr">
+        <is>
+          <t>replacement proposed</t>
+        </is>
+      </c>
+      <c r="K12" s="173" t="inlineStr">
+        <is>
+          <t>2019 was 112 and the peak, 2016, was 125 on this index; 2025 is 101.3. Movements fell 0.1% a year over 2013-2019. The proposed highs (140 and 190) are above every year on record. Replacement: medium returns to the 2019 level by 2030, high to the 2016 peak; 2035 extends each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="173" t="inlineStr">
+        <is>
+          <t>jet</t>
+        </is>
+      </c>
+      <c r="B13" s="173" t="inlineStr">
+        <is>
+          <t>fuel_burn_per_movement</t>
+        </is>
+      </c>
+      <c r="C13" s="173" t="inlineStr">
+        <is>
+          <t>index_2024_100</t>
+        </is>
+      </c>
+      <c r="D13" s="173" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E13" s="173" t="inlineStr">
+        <is>
+          <t>4,090 litres of jet sold per movement in 2024</t>
+        </is>
+      </c>
+      <c r="F13" s="173" t="inlineStr">
+        <is>
+          <t>80 / 90 / 100</t>
+        </is>
+      </c>
+      <c r="G13" s="173" t="inlineStr">
+        <is>
+          <t>80 / 90 / 113</t>
+        </is>
+      </c>
+      <c r="H13" s="173" t="inlineStr">
+        <is>
+          <t>65 / 80 / 100</t>
+        </is>
+      </c>
+      <c r="I13" s="173" t="inlineStr">
+        <is>
+          <t>65 / 80 / 113</t>
+        </is>
+      </c>
+      <c r="J13" s="173" t="inlineStr">
+        <is>
+          <t>replacement proposed</t>
+        </is>
+      </c>
+      <c r="K13" s="173" t="inlineStr">
+        <is>
+          <t>The 2013-2019 average was 4,608 litres, 113 on this index. Jet sales have recovered less than movements since 2020, for reasons not yet established (aircraft mix, fuel loaded abroad, or sales coverage). The proposed range only falls; the high case should allow a return to the earlier intensity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="173" t="inlineStr">
+        <is>
+          <t>jet</t>
+        </is>
+      </c>
+      <c r="B14" s="173" t="inlineStr">
+        <is>
+          <t>saf_volume_share</t>
+        </is>
+      </c>
+      <c r="C14" s="173" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D14" s="173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="173" t="inlineStr">
+        <is>
+          <t>no sustainable aviation fuel supply recorded in the sources held; unsourced</t>
+        </is>
+      </c>
+      <c r="F14" s="173" t="inlineStr">
+        <is>
+          <t>0 / 2 / 5</t>
+        </is>
+      </c>
+      <c r="G14" s="173" t="inlineStr">
+        <is>
+          <t>0 / 2 / 5</t>
+        </is>
+      </c>
+      <c r="H14" s="173" t="inlineStr">
+        <is>
+          <t>0 / 5 / 10</t>
+        </is>
+      </c>
+      <c r="I14" s="173" t="inlineStr">
+        <is>
+          <t>0 / 5 / 10</t>
+        </is>
+      </c>
+      <c r="J14" s="173" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="K14" s="173" t="inlineStr">
+        <is>
+          <t>No South African blend requirement is sourced. No change proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="173" t="inlineStr">
+        <is>
+          <t>jet</t>
+        </is>
+      </c>
+      <c r="B15" s="173" t="inlineStr">
+        <is>
+          <t>plant_utilisation</t>
+        </is>
+      </c>
+      <c r="C15" s="173" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D15" s="173" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E15" s="173" t="inlineStr">
+        <is>
+          <t>reported 2024 output over reported capacity, three plants; indicative</t>
+        </is>
+      </c>
+      <c r="F15" s="173" t="inlineStr">
+        <is>
+          <t>60 / 75 / 90</t>
+        </is>
+      </c>
+      <c r="G15" s="173" t="inlineStr">
+        <is>
+          <t>60 / 75 / 90</t>
+        </is>
+      </c>
+      <c r="H15" s="173" t="inlineStr">
+        <is>
+          <t>60 / 75 / 90</t>
+        </is>
+      </c>
+      <c r="I15" s="173" t="inlineStr">
+        <is>
+          <t>60 / 75 / 90</t>
+        </is>
+      </c>
+      <c r="J15" s="173" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="K15" s="173" t="inlineStr">
+        <is>
+          <t>Secunda 53%, Natref 71%, Astron 84%. Output is all refined products against crude-equivalent capacity; Sasol's year ends June; Astron converted at an assumed 36 MJ a litre. The model's Secunda capacity was 75 thousand barrels a day and is now FIASA's 150, with utilisation re-based so output is unchanged; the model then gives 62 thousand barrels a day for 2024 against 80 reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="173" t="inlineStr">
+        <is>
+          <t>jet</t>
+        </is>
+      </c>
+      <c r="B16" s="173" t="inlineStr">
+        <is>
+          <t>product_yield</t>
+        </is>
+      </c>
+      <c r="C16" s="173" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D16" s="173" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E16" s="173" t="inlineStr">
+        <is>
+          <t>registered legacy yield for capable plants</t>
+        </is>
+      </c>
+      <c r="F16" s="173" t="inlineStr">
+        <is>
+          <t>5 / 10 / 15</t>
+        </is>
+      </c>
+      <c r="G16" s="173" t="inlineStr">
+        <is>
+          <t>5 / 10 / 15</t>
+        </is>
+      </c>
+      <c r="H16" s="173" t="inlineStr">
+        <is>
+          <t>5 / 10 / 15</t>
+        </is>
+      </c>
+      <c r="I16" s="173" t="inlineStr">
+        <is>
+          <t>5 / 10 / 15</t>
+        </is>
+      </c>
+      <c r="J16" s="173" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="K16" s="173" t="inlineStr">
+        <is>
+          <t>Jet was 5 to 8% of the five fuels produced in the 2017-2021 energy balances, consistent with the range. No change proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="173" t="inlineStr">
+        <is>
+          <t>jet</t>
+        </is>
+      </c>
+      <c r="B17" s="173" t="inlineStr">
+        <is>
+          <t>restart_capacity</t>
+        </is>
+      </c>
+      <c r="C17" s="173" t="inlineStr">
+        <is>
+          <t>thousand_bbl_per_day</t>
+        </is>
+      </c>
+      <c r="D17" s="173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="173" t="inlineStr">
+        <is>
+          <t>no committed addition</t>
+        </is>
+      </c>
+      <c r="F17" s="173" t="inlineStr">
+        <is>
+          <t>0 / 0 / 0</t>
+        </is>
+      </c>
+      <c r="G17" s="173" t="inlineStr">
+        <is>
+          <t>0 / 0 / 0</t>
+        </is>
+      </c>
+      <c r="H17" s="173" t="inlineStr">
+        <is>
+          <t>0 / 0 / 400</t>
+        </is>
+      </c>
+      <c r="I17" s="173" t="inlineStr">
+        <is>
+          <t>0 / 0 / 400</t>
+        </is>
+      </c>
+      <c r="J17" s="173" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="K17" s="173" t="inlineStr">
+        <is>
+          <t>Existing conditional illustration; no investment decision, timing or product slate is sourced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="173" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="B18" s="173" t="inlineStr">
+        <is>
+          <t>passenger_mileage</t>
+        </is>
+      </c>
+      <c r="C18" s="173" t="inlineStr">
+        <is>
+          <t>km_per_vehicle_year</t>
+        </is>
+      </c>
+      <c r="D18" s="173" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="E18" s="173" t="inlineStr">
+        <is>
+          <t>registered placeholder; not an observation</t>
+        </is>
+      </c>
+      <c r="F18" s="173" t="inlineStr">
+        <is>
+          <t>13600 / 17000 / 20400</t>
+        </is>
+      </c>
+      <c r="G18" s="173" t="inlineStr">
+        <is>
+          <t>12900 / 14500 / 17000</t>
+        </is>
+      </c>
+      <c r="H18" s="173" t="inlineStr">
+        <is>
+          <t>13600 / 17000 / 20400</t>
+        </is>
+      </c>
+      <c r="I18" s="173" t="inlineStr">
+        <is>
+          <t>12900 / 14500 / 17000</t>
+        </is>
+      </c>
+      <c r="J18" s="173" t="inlineStr">
+        <is>
+          <t>replacement proposed</t>
+        </is>
+      </c>
+      <c r="K18" s="173" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018) give 14,457 km a year for the petrol car fleet. 2023 petrol sales over 8.56 million registered petrol vehicles is 1,056 litres each, about 12,881 km at 8.2 litres per 100 km. The placeholder sits above both, so it is better treated as the high case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="173" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="B19" s="173" t="inlineStr">
+        <is>
+          <t>gdp_growth</t>
+        </is>
+      </c>
+      <c r="C19" s="173" t="inlineStr">
+        <is>
+          <t>percent_per_year</t>
+        </is>
+      </c>
+      <c r="D19" s="173" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="E19" s="173" t="inlineStr">
+        <is>
+          <t>real GDP growth in 2024 (Stats SA P0441)</t>
+        </is>
+      </c>
+      <c r="F19" s="173" t="inlineStr">
+        <is>
+          <t>1 / 2 / 3</t>
+        </is>
+      </c>
+      <c r="G19" s="173" t="inlineStr">
+        <is>
+          <t>0.7 / 1.6 / 2</t>
+        </is>
+      </c>
+      <c r="H19" s="173" t="inlineStr">
+        <is>
+          <t>1 / 2 / 3</t>
+        </is>
+      </c>
+      <c r="I19" s="173" t="inlineStr">
+        <is>
+          <t>0.7 / 1.6 / 2</t>
+        </is>
+      </c>
+      <c r="J19" s="173" t="inlineStr">
+        <is>
+          <t>replacement proposed</t>
+        </is>
+      </c>
+      <c r="K19" s="173" t="inlineStr">
+        <is>
+          <t>Average growth was 0.7% a year over 2014-2024 and 1.6% over 2010-2019. National Treasury forecasts 1.6% for 2026 rising to 2.0% in 2028. The model's registered cases are 1.0% and 1.6%. A medium of 2% equals the top of the official forecast; 3% has no recent precedent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="173" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="B20" s="173" t="inlineStr">
+        <is>
+          <t>bev_new_sales_share</t>
+        </is>
+      </c>
+      <c r="C20" s="173" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D20" s="173" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="E20" s="173" t="inlineStr">
+        <is>
+          <t>1,088 battery electric vehicles sold in 2025, share of all new vehicles (naamsa)</t>
+        </is>
+      </c>
+      <c r="F20" s="173" t="inlineStr">
+        <is>
+          <t>5 / 15 / 30</t>
+        </is>
+      </c>
+      <c r="G20" s="173" t="inlineStr">
+        <is>
+          <t>0.5 / 4 / 20</t>
+        </is>
+      </c>
+      <c r="H20" s="173" t="inlineStr">
+        <is>
+          <t>15 / 35 / 60</t>
+        </is>
+      </c>
+      <c r="I20" s="173" t="inlineStr">
+        <is>
+          <t>2 / 15 / 40</t>
+        </is>
+      </c>
+      <c r="J20" s="173" t="inlineStr">
+        <is>
+          <t>replacement proposed</t>
+        </is>
+      </c>
+      <c r="K20" s="173" t="inlineStr">
+        <is>
+          <t>Battery electric sales fell from 1,257 in 2024 to 1,088 in 2025. No South African forecast was found; each case is tied to a market's observed 2025 share of new car sales (IEA, Global EV Outlook 2026). Low: South Africa stays under 1%, as in 2022-2025. Medium: India's share (nearly 4%) by 2030 and Indonesia's (15%) by 2035. High: Turkiye's path, from just over 1% in 2022 to over 20% in 2025, by 2030, and Vietnam's share (nearly 40%) by 2035. The IEA shares include plug-in hybrids, so they overstate battery electric alone. The proposed 2035 high of 60 is above every market cited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="173" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="B21" s="173" t="inlineStr">
+        <is>
+          <t>new_cohort_efficiency</t>
+        </is>
+      </c>
+      <c r="C21" s="173" t="inlineStr">
+        <is>
+          <t>percent_per_year</t>
+        </is>
+      </c>
+      <c r="D21" s="173" t="inlineStr">
+        <is>
+          <t>1.0 to 1.5</t>
+        </is>
+      </c>
+      <c r="E21" s="173" t="inlineStr">
+        <is>
+          <t>registered petrol efficiency paths (low and high demand cases)</t>
+        </is>
+      </c>
+      <c r="F21" s="173" t="inlineStr">
+        <is>
+          <t>1 / 1.25 / 1.5</t>
+        </is>
+      </c>
+      <c r="G21" s="173" t="inlineStr">
+        <is>
+          <t>1 / 1.25 / 1.5</t>
+        </is>
+      </c>
+      <c r="H21" s="173" t="inlineStr">
+        <is>
+          <t>1 / 1.25 / 1.5</t>
+        </is>
+      </c>
+      <c r="I21" s="173" t="inlineStr">
+        <is>
+          <t>1 / 1.25 / 1.5</t>
+        </is>
+      </c>
+      <c r="J21" s="173" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="K21" s="173" t="inlineStr">
+        <is>
+          <t>Low and high equal the registered endpoints. Neither has a source. No change proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="173" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="B22" s="173" t="inlineStr">
+        <is>
+          <t>plant_utilisation</t>
+        </is>
+      </c>
+      <c r="C22" s="173" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D22" s="173" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E22" s="173" t="inlineStr">
+        <is>
+          <t>reported 2024 output over reported capacity, three plants; indicative</t>
+        </is>
+      </c>
+      <c r="F22" s="173" t="inlineStr">
+        <is>
+          <t>60 / 75 / 90</t>
+        </is>
+      </c>
+      <c r="G22" s="173" t="inlineStr">
+        <is>
+          <t>60 / 75 / 90</t>
+        </is>
+      </c>
+      <c r="H22" s="173" t="inlineStr">
+        <is>
+          <t>60 / 75 / 90</t>
+        </is>
+      </c>
+      <c r="I22" s="173" t="inlineStr">
+        <is>
+          <t>60 / 75 / 90</t>
+        </is>
+      </c>
+      <c r="J22" s="173" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="K22" s="173" t="inlineStr">
+        <is>
+          <t>Secunda 53%, Natref 71%, Astron 84%. Output is all refined products against crude-equivalent capacity; Sasol's year ends June; Astron converted at an assumed 36 MJ a litre. The model's Secunda capacity was 75 thousand barrels a day and is now FIASA's 150, with utilisation re-based so output is unchanged; the model then gives 62 thousand barrels a day for 2024 against 80 reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="173" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="B23" s="173" t="inlineStr">
+        <is>
+          <t>product_yield</t>
+        </is>
+      </c>
+      <c r="C23" s="173" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D23" s="173" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E23" s="173" t="inlineStr">
+        <is>
+          <t>petrol share of refinery output in 2024 (JODI; lowest reliability)</t>
+        </is>
+      </c>
+      <c r="F23" s="173" t="inlineStr">
+        <is>
+          <t>35 / 45 / 55</t>
+        </is>
+      </c>
+      <c r="G23" s="173" t="inlineStr">
+        <is>
+          <t>45 / 50 / 55</t>
+        </is>
+      </c>
+      <c r="H23" s="173" t="inlineStr">
+        <is>
+          <t>35 / 45 / 55</t>
+        </is>
+      </c>
+      <c r="I23" s="173" t="inlineStr">
+        <is>
+          <t>45 / 50 / 55</t>
+        </is>
+      </c>
+      <c r="J23" s="173" t="inlineStr">
+        <is>
+          <t>replacement proposed</t>
+        </is>
+      </c>
+      <c r="K23" s="173" t="inlineStr">
+        <is>
+          <t>Share of all refinery output: 51% in 2023 and 54% in 2024 (JODI). Petrol was 47 to 50% of the five fuels in the 2017-2021 energy balances. The registered legacy yield is 45%. Replacement: legacy as the low, 50 as the medium, the recent observed share as the high. Petrol and diesel yields must be chosen together; their highs cannot both hold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="173" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="B24" s="173" t="inlineStr">
+        <is>
+          <t>restart_capacity</t>
+        </is>
+      </c>
+      <c r="C24" s="173" t="inlineStr">
+        <is>
+          <t>thousand_bbl_per_day</t>
+        </is>
+      </c>
+      <c r="D24" s="173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" s="173" t="inlineStr">
+        <is>
+          <t>no committed addition</t>
+        </is>
+      </c>
+      <c r="F24" s="173" t="inlineStr">
+        <is>
+          <t>0 / 0 / 0</t>
+        </is>
+      </c>
+      <c r="G24" s="173" t="inlineStr">
+        <is>
+          <t>0 / 0 / 0</t>
+        </is>
+      </c>
+      <c r="H24" s="173" t="inlineStr">
+        <is>
+          <t>0 / 0 / 400</t>
+        </is>
+      </c>
+      <c r="I24" s="173" t="inlineStr">
+        <is>
+          <t>0 / 0 / 400</t>
+        </is>
+      </c>
+      <c r="J24" s="173" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="K24" s="173" t="inlineStr">
+        <is>
+          <t>Existing conditional illustration; no investment decision, timing or product slate is sourced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="173" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="B25" s="173" t="inlineStr">
+        <is>
+          <t>real_fuel_price</t>
+        </is>
+      </c>
+      <c r="C25" s="173" t="inlineStr">
+        <is>
+          <t>index_2024_100</t>
+        </is>
+      </c>
+      <c r="D25" s="173" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E25" s="173" t="inlineStr">
+        <is>
+          <t>regulated inland price deflated by headline CPI, 2024 average</t>
+        </is>
+      </c>
+      <c r="F25" s="173" t="inlineStr">
+        <is>
+          <t>- / - / -</t>
+        </is>
+      </c>
+      <c r="G25" s="173" t="inlineStr">
+        <is>
+          <t>80 / 100 / 140</t>
+        </is>
+      </c>
+      <c r="H25" s="173" t="inlineStr">
+        <is>
+          <t>- / - / -</t>
+        </is>
+      </c>
+      <c r="I25" s="173" t="inlineStr">
+        <is>
+          <t>80 / 100 / 140</t>
+        </is>
+      </c>
+      <c r="J25" s="173" t="inlineStr">
+        <is>
+          <t>added lever</t>
+        </is>
+      </c>
+      <c r="K25" s="173" t="inlineStr">
+        <is>
+          <t>Annual range 2011-2025 is 76 to 120; October 2026 is 143. Low is the bottom of that range, medium a return to 2024, high October 2026 held. Boshoff (2012) puts the long-run response at -0.13, so the high case lowers demand by about 5%. One study; the model has no price response today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="173" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="B26" s="173" t="inlineStr">
+        <is>
+          <t>private_backup_generation</t>
+        </is>
+      </c>
+      <c r="C26" s="173" t="inlineStr">
+        <is>
+          <t>bn_litres_per_year</t>
+        </is>
+      </c>
+      <c r="D26" s="173" t="inlineStr">
+        <is>
+          <t>not measured</t>
+        </is>
+      </c>
+      <c r="E26" s="173" t="inlineStr">
+        <is>
+          <t>no measured volume exists</t>
+        </is>
+      </c>
+      <c r="F26" s="173" t="inlineStr">
+        <is>
+          <t>- / - / -</t>
+        </is>
+      </c>
+      <c r="G26" s="173" t="inlineStr">
+        <is>
+          <t>0 / 0 / 0.5</t>
+        </is>
+      </c>
+      <c r="H26" s="173" t="inlineStr">
+        <is>
+          <t>- / - / -</t>
+        </is>
+      </c>
+      <c r="I26" s="173" t="inlineStr">
+        <is>
+          <t>0 / 0 / 0.5</t>
+        </is>
+      </c>
+      <c r="J26" s="173" t="inlineStr">
+        <is>
+          <t>added lever</t>
+        </is>
+      </c>
+      <c r="K26" s="173" t="inlineStr">
+        <is>
+          <t>Recorded diesel sales fell by 1.2 bn litres between 2023 and 2024 as load-shedding ended; grid turbines account for about 0.7 of that at 0.31 litres per kWh, leaving about 0.5 that may be private generators. Indicative only: other causes are not excluded. High is load-shedding returning at 2023 intensity. Move together with diesel power generation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="173" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="B27" s="173" t="inlineStr">
+        <is>
+          <t>real_fuel_price</t>
+        </is>
+      </c>
+      <c r="C27" s="173" t="inlineStr">
+        <is>
+          <t>index_2024_100</t>
+        </is>
+      </c>
+      <c r="D27" s="173" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E27" s="173" t="inlineStr">
+        <is>
+          <t>regulated inland price deflated by headline CPI, 2024 average</t>
+        </is>
+      </c>
+      <c r="F27" s="173" t="inlineStr">
+        <is>
+          <t>- / - / -</t>
+        </is>
+      </c>
+      <c r="G27" s="173" t="inlineStr">
+        <is>
+          <t>80 / 100 / 120</t>
+        </is>
+      </c>
+      <c r="H27" s="173" t="inlineStr">
+        <is>
+          <t>- / - / -</t>
+        </is>
+      </c>
+      <c r="I27" s="173" t="inlineStr">
+        <is>
+          <t>80 / 100 / 120</t>
+        </is>
+      </c>
+      <c r="J27" s="173" t="inlineStr">
+        <is>
+          <t>added lever</t>
+        </is>
+      </c>
+      <c r="K27" s="173" t="inlineStr">
+        <is>
+          <t>Annual range 2011-2025 is 79 to 109; October 2026 is 121. Low is the bottom of that range, medium a return to 2024, high October 2026 held. Boshoff (2012) puts the long-run response at -0.5, so the high case lowers demand by about 10%. One study; the model has no price response today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="173" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="B28" s="173" t="inlineStr">
+        <is>
+          <t>plug_in_hybrid_new_sales_share</t>
+        </is>
+      </c>
+      <c r="C28" s="173" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D28" s="173" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="E28" s="173" t="inlineStr">
+        <is>
+          <t>share of all new vehicles in 2025 (naamsa)</t>
+        </is>
+      </c>
+      <c r="F28" s="173" t="inlineStr">
+        <is>
+          <t>- / - / -</t>
+        </is>
+      </c>
+      <c r="G28" s="173" t="inlineStr">
+        <is>
+          <t>0.5 / 1.2 / 2.1</t>
+        </is>
+      </c>
+      <c r="H28" s="173" t="inlineStr">
+        <is>
+          <t>- / - / -</t>
+        </is>
+      </c>
+      <c r="I28" s="173" t="inlineStr">
+        <is>
+          <t>0.5 / 2 / 3.7</t>
+        </is>
+      </c>
+      <c r="J28" s="173" t="inlineStr">
+        <is>
+          <t>added lever</t>
+        </is>
+      </c>
+      <c r="K28" s="173" t="inlineStr">
+        <is>
+          <t>Share rose from 0.02% in 2022 to 0.47% in 2025. Low holds 2025; medium adds the 2022-2025 average of 0.15 points a year; high adds the 2025 increase of 0.33 points a year. An extrapolation of South Africa's own sales, not a forecast. Enters through fuel use per kilometre; the share of distance on the battery is unsourced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="173" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="B29" s="173" t="inlineStr">
+        <is>
+          <t>conventional_hybrid_new_sales_share</t>
+        </is>
+      </c>
+      <c r="C29" s="173" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D29" s="173" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="E29" s="173" t="inlineStr">
+        <is>
+          <t>share of all new vehicles in 2025 (naamsa)</t>
+        </is>
+      </c>
+      <c r="F29" s="173" t="inlineStr">
+        <is>
+          <t>- / - / -</t>
+        </is>
+      </c>
+      <c r="G29" s="173" t="inlineStr">
+        <is>
+          <t>2.1 / 4.4 / 6.7</t>
+        </is>
+      </c>
+      <c r="H29" s="173" t="inlineStr">
+        <is>
+          <t>- / - / -</t>
+        </is>
+      </c>
+      <c r="I29" s="173" t="inlineStr">
+        <is>
+          <t>2.1 / 6.7 / 11.3</t>
+        </is>
+      </c>
+      <c r="J29" s="173" t="inlineStr">
+        <is>
+          <t>added lever</t>
+        </is>
+      </c>
+      <c r="K29" s="173" t="inlineStr">
+        <is>
+          <t>Share rose from 0.77% in 2022 to 2.64% in 2024 and was 2.15% in 2025. Low holds 2025; medium adds the 2022-2025 average of 0.46 points a year; high adds twice that. An extrapolation of South Africa's own sales, not a forecast. Enters through fuel use per kilometre; the saving per vehicle is unsourced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="173" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="B30" s="173" t="inlineStr">
+        <is>
+          <t>rail_passenger_journeys</t>
+        </is>
+      </c>
+      <c r="C30" s="173" t="inlineStr">
+        <is>
+          <t>million_per_year</t>
+        </is>
+      </c>
+      <c r="D30" s="173" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E30" s="173" t="inlineStr">
+        <is>
+          <t>rail passenger journeys in 2024 (Stats SA P7162)</t>
+        </is>
+      </c>
+      <c r="F30" s="173" t="inlineStr">
+        <is>
+          <t>- / - / -</t>
+        </is>
+      </c>
+      <c r="G30" s="173" t="inlineStr">
+        <is>
+          <t>100 / 180 / 320</t>
+        </is>
+      </c>
+      <c r="H30" s="173" t="inlineStr">
+        <is>
+          <t>- / - / -</t>
+        </is>
+      </c>
+      <c r="I30" s="173" t="inlineStr">
+        <is>
+          <t>100 / 250 / 320</t>
+        </is>
+      </c>
+      <c r="J30" s="173" t="inlineStr">
+        <is>
+          <t>added lever</t>
+        </is>
+      </c>
+      <c r="K30" s="173" t="inlineStr">
+        <is>
+          <t>Journeys were 317 million in 2017 and 175 in 2019, fell to 19 in 2022 and recovered to 103 in 2025. Low holds 2025; medium returns to 2019 by 2030 and to 2018 by 2035; high returns to 2017 by 2030 and holds. More rail journeys lower petrol use, but no survey covers the minibus taxi and car trips displaced, so the effect in litres cannot yet be stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="173" t="inlineStr">
+        <is>
+          <t>throughput</t>
+        </is>
+      </c>
+      <c r="B31" s="173" t="inlineStr">
+        <is>
+          <t>exports_to_neighbours</t>
+        </is>
+      </c>
+      <c r="C31" s="173" t="inlineStr">
+        <is>
+          <t>bn_litres_per_year</t>
+        </is>
+      </c>
+      <c r="D31" s="173" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="E31" s="173" t="inlineStr">
+        <is>
+          <t>petrol and diesel exported to nine neighbouring countries in 2024 (SARS customs)</t>
+        </is>
+      </c>
+      <c r="F31" s="173" t="inlineStr">
+        <is>
+          <t>- / - / -</t>
+        </is>
+      </c>
+      <c r="G31" s="173" t="inlineStr">
+        <is>
+          <t>0.7 / 1.4 / 1.7</t>
+        </is>
+      </c>
+      <c r="H31" s="173" t="inlineStr">
+        <is>
+          <t>- / - / -</t>
+        </is>
+      </c>
+      <c r="I31" s="173" t="inlineStr">
+        <is>
+          <t>0.7 / 1.4 / 1.7</t>
+        </is>
+      </c>
+      <c r="J31" s="173" t="inlineStr">
+        <is>
+          <t>added lever</t>
+        </is>
+      </c>
+      <c r="K31" s="173" t="inlineStr">
+        <is>
+          <t>2.66 bn litres in 2019, 1.73 in 2023 and 1.37 in 2025. Botswana took 1.05 in 2023 and 0.68 in 2025 and has said it is moving to Walvis Bay and Maputo. Low is 2025 with Botswana gone; medium holds 2025; high returns to 2023. This is throughput for South African terminals, not South African demand, and must not be added to it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="149" t="inlineStr">
+        <is>
+          <t>Status against the 13 data gaps on the Data gaps sheet, 8 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>The Data gaps sheet is unchanged. Statuses are the analyst's reading; closure is for the owner named there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="150" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="150" t="inlineStr">
+        <is>
+          <t>Demand component</t>
+        </is>
+      </c>
+      <c r="C4" s="150" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D4" s="150" t="inlineStr">
+        <is>
+          <t>What has been added</t>
+        </is>
+      </c>
+      <c r="E4" s="150" t="inlineStr">
+        <is>
+          <t>What is still missing</t>
+        </is>
+      </c>
+      <c r="F4" s="150" t="inlineStr">
+        <is>
+          <t>Where to look</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="173" t="inlineStr">
+        <is>
+          <t>G01</t>
+        </is>
+      </c>
+      <c r="B5" s="173" t="inlineStr">
+        <is>
+          <t>National fuel balance</t>
+        </is>
+      </c>
+      <c r="C5" s="173" t="inlineStr">
+        <is>
+          <t>Narrowed</t>
+        </is>
+      </c>
+      <c r="D5" s="173" t="inlineStr">
+        <is>
+          <t>Balance rebuilt on customs trade for 2014-2025; Road Accident Fund levy found as an independent count.</t>
+        </is>
+      </c>
+      <c r="E5" s="173" t="inlineStr">
+        <is>
+          <t>2024 sales source; no 2025 sales figure; production by product after 2021; stocks.</t>
+        </is>
+      </c>
+      <c r="F5" s="173" t="inlineStr">
+        <is>
+          <t>History, sections 2-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="173" t="inlineStr">
+        <is>
+          <t>G02</t>
+        </is>
+      </c>
+      <c r="B6" s="173" t="inlineStr">
+        <is>
+          <t>Fleet and new sales</t>
+        </is>
+      </c>
+      <c r="C6" s="173" t="inlineStr">
+        <is>
+          <t>Narrowed</t>
+        </is>
+      </c>
+      <c r="D6" s="173" t="inlineStr">
+        <is>
+          <t>Registered vehicles by class 2021-2025, new sales 2017-2025 and apparent retirements lined up against the model.</t>
+        </is>
+      </c>
+      <c r="E6" s="173" t="inlineStr">
+        <is>
+          <t>Stock by age and by fuel within each class is in no source held.</t>
+        </is>
+      </c>
+      <c r="F6" s="173" t="inlineStr">
+        <is>
+          <t>Vehicle history</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="173" t="inlineStr">
+        <is>
+          <t>G03</t>
+        </is>
+      </c>
+      <c r="B7" s="173" t="inlineStr">
+        <is>
+          <t>Passenger electrification</t>
+        </is>
+      </c>
+      <c r="C7" s="173" t="inlineStr">
+        <is>
+          <t>Narrowed</t>
+        </is>
+      </c>
+      <c r="D7" s="173" t="inlineStr">
+        <is>
+          <t>Battery electric, plug-in and conventional hybrid sales and shares, 2019-2025.</t>
+        </is>
+      </c>
+      <c r="E7" s="173" t="inlineStr">
+        <is>
+          <t>Passenger-only denominators; electric vehicles in the fleet after 2023; fuel saved by hybrids.</t>
+        </is>
+      </c>
+      <c r="F7" s="173" t="inlineStr">
+        <is>
+          <t>Vehicle history, section 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="173" t="inlineStr">
+        <is>
+          <t>G04</t>
+        </is>
+      </c>
+      <c r="B8" s="173" t="inlineStr">
+        <is>
+          <t>Road freight activity</t>
+        </is>
+      </c>
+      <c r="C8" s="173" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D8" s="173" t="inlineStr">
+        <is>
+          <t>Tonnes only. One tonne-kilometre figure (221 bn, 2013). Stats SA fuel purchases by road freight firms give a floor of about 2.9 bn litres (2019) and 3.2 bn (2023).</t>
+        </is>
+      </c>
+      <c r="E8" s="173" t="inlineStr">
+        <is>
+          <t>An annual tonne-kilometre series; distance and payload; light commercial freight scope.</t>
+        </is>
+      </c>
+      <c r="F8" s="173" t="inlineStr">
+        <is>
+          <t>Diesel by use, section 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="173" t="inlineStr">
+        <is>
+          <t>G05</t>
+        </is>
+      </c>
+      <c r="B9" s="173" t="inlineStr">
+        <is>
+          <t>Freight electrification</t>
+        </is>
+      </c>
+      <c r="C9" s="173" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D9" s="173" t="inlineStr">
+        <is>
+          <t>No truck electric or hybrid sales or stock data found.</t>
+        </is>
+      </c>
+      <c r="E9" s="173" t="inlineStr">
+        <is>
+          <t>Everything listed.</t>
+        </is>
+      </c>
+      <c r="F9" s="173" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="173" t="inlineStr">
+        <is>
+          <t>G06</t>
+        </is>
+      </c>
+      <c r="B10" s="173" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="C10" s="173" t="inlineStr">
+        <is>
+          <t>Narrowed</t>
+        </is>
+      </c>
+      <c r="D10" s="173" t="inlineStr">
+        <is>
+          <t>Manufacturing and other industry diesel by difference, 2016-2021 (0.16-0.23 bn litres), with litres per index point.</t>
+        </is>
+      </c>
+      <c r="E10" s="173" t="inlineStr">
+        <is>
+          <t>Sub-sector detail; the balance has no manufacturing lines before 2016.</t>
+        </is>
+      </c>
+      <c r="F10" s="173" t="inlineStr">
+        <is>
+          <t>Sector history</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="173" t="inlineStr">
+        <is>
+          <t>G07</t>
+        </is>
+      </c>
+      <c r="B11" s="173" t="inlineStr">
+        <is>
+          <t>Mining and construction</t>
+        </is>
+      </c>
+      <c r="C11" s="173" t="inlineStr">
+        <is>
+          <t>Narrowed</t>
+        </is>
+      </c>
+      <c r="D11" s="173" t="inlineStr">
+        <is>
+          <t>Mining diesel 2012-2021 with litres per index point (11-17 million); indicative 2022-2025.</t>
+        </is>
+      </c>
+      <c r="E11" s="173" t="inlineStr">
+        <is>
+          <t>Observed fuel after 2021; site and commodity split; on-road boundary.</t>
+        </is>
+      </c>
+      <c r="F11" s="173" t="inlineStr">
+        <is>
+          <t>Sector history</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="173" t="inlineStr">
+        <is>
+          <t>G08</t>
+        </is>
+      </c>
+      <c r="B12" s="173" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="C12" s="173" t="inlineStr">
+        <is>
+          <t>Narrowed</t>
+        </is>
+      </c>
+      <c r="D12" s="173" t="inlineStr">
+        <is>
+          <t>Agriculture diesel 2012-2021 with litres per rand of value added; indicative 2022-2025. Rebated diesel across all rebate sectors is 1.46 bn litres (year to March 2025).</t>
+        </is>
+      </c>
+      <c r="E12" s="173" t="inlineStr">
+        <is>
+          <t>A fuel baseline after 2021; crop and irrigation activity.</t>
+        </is>
+      </c>
+      <c r="F12" s="173" t="inlineStr">
+        <is>
+          <t>Sector history</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="173" t="inlineStr">
+        <is>
+          <t>G09</t>
+        </is>
+      </c>
+      <c r="B13" s="173" t="inlineStr">
+        <is>
+          <t>Generation</t>
+        </is>
+      </c>
+      <c r="C13" s="173" t="inlineStr">
+        <is>
+          <t>Narrowed</t>
+        </is>
+      </c>
+      <c r="D13" s="173" t="inlineStr">
+        <is>
+          <t>Generation to the year ending March 2026; 0.31 litres per kWh in three reported years. The model's 2024 figure (3.58 bn litres) is at least 2 bn above reported burn.</t>
+        </is>
+      </c>
+      <c r="E13" s="173" t="inlineStr">
+        <is>
+          <t>Matched fuel burn by calendar year; private backup generation has no measured volume.</t>
+        </is>
+      </c>
+      <c r="F13" s="173" t="inlineStr">
+        <is>
+          <t>Diesel by use, section 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="173" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="B14" s="173" t="inlineStr">
+        <is>
+          <t>Aviation</t>
+        </is>
+      </c>
+      <c r="C14" s="173" t="inlineStr">
+        <is>
+          <t>Narrowed</t>
+        </is>
+      </c>
+      <c r="D14" s="173" t="inlineStr">
+        <is>
+          <t>Jet sales, trade, production and aircraft movements lined up; jet sold per movement computed.</t>
+        </is>
+      </c>
+      <c r="E14" s="173" t="inlineStr">
+        <is>
+          <t>Cargo, aircraft and route mix; airports outside ACSA; jet by airport.</t>
+        </is>
+      </c>
+      <c r="F14" s="173" t="inlineStr">
+        <is>
+          <t>History, section 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="173" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="B15" s="173" t="inlineStr">
+        <is>
+          <t>Provincial demand</t>
+        </is>
+      </c>
+      <c r="C15" s="173" t="inlineStr">
+        <is>
+          <t>Narrowed</t>
+        </is>
+      </c>
+      <c r="D15" s="173" t="inlineStr">
+        <is>
+          <t>2013-2022 observed; 2023 and 2024 estimated with the best of six methods back-tested.</t>
+        </is>
+      </c>
+      <c r="E15" s="173" t="inlineStr">
+        <is>
+          <t>District data after 2023 quarter 1, which the department has not published; 2025 national total.</t>
+        </is>
+      </c>
+      <c r="F15" s="173" t="inlineStr">
+        <is>
+          <t>History, sections 1 and 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="173" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="B16" s="173" t="inlineStr">
+        <is>
+          <t>Marine and other coverage</t>
+        </is>
+      </c>
+      <c r="C16" s="173" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D16" s="173" t="inlineStr">
+        <is>
+          <t>Nothing new. The model's marine placeholder equals the 2007 balance figure.</t>
+        </is>
+      </c>
+      <c r="E16" s="173" t="inlineStr">
+        <is>
+          <t>Everything listed.</t>
+        </is>
+      </c>
+      <c r="F16" s="173" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="173" t="inlineStr">
+        <is>
+          <t>G13</t>
+        </is>
+      </c>
+      <c r="B17" s="173" t="inlineStr">
+        <is>
+          <t>Ranges and annual forecast paths</t>
+        </is>
+      </c>
+      <c r="C17" s="173" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="D17" s="173" t="inlineStr">
+        <is>
+          <t>Baseline, rationale and source for all 20 levers; 39 of 120 values with a proposed replacement; seven levers added.</t>
+        </is>
+      </c>
+      <c r="E17" s="173" t="inlineStr">
+        <is>
+          <t>Agreement on the reference case and annual paths.</t>
+        </is>
+      </c>
+      <c r="F17" s="173" t="inlineStr">
+        <is>
+          <t>HML response</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -52486,37 +55467,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="173" t="inlineStr">
+      <c r="A4" s="174" t="inlineStr">
         <is>
           <t>Evidence row</t>
         </is>
       </c>
-      <c r="B4" s="173" t="inlineStr">
+      <c r="B4" s="174" t="inlineStr">
         <is>
           <t>Series</t>
         </is>
       </c>
-      <c r="C4" s="173" t="inlineStr">
+      <c r="C4" s="174" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D4" s="173" t="inlineStr">
+      <c r="D4" s="174" t="inlineStr">
         <is>
           <t>Workbook value</t>
         </is>
       </c>
-      <c r="E4" s="173" t="inlineStr">
+      <c r="E4" s="174" t="inlineStr">
         <is>
           <t>Recomputed from inputs</t>
         </is>
       </c>
-      <c r="F4" s="173" t="inlineStr">
+      <c r="F4" s="174" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="G4" s="173" t="inlineStr">
+      <c r="G4" s="174" t="inlineStr">
         <is>
           <t>Input file</t>
         </is>
@@ -52536,10 +55517,10 @@
       <c r="C5" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D5" s="174" t="n">
+      <c r="D5" s="175" t="n">
         <v>9185</v>
       </c>
-      <c r="E5" s="174" t="n">
+      <c r="E5" s="175" t="n">
         <v>9185</v>
       </c>
       <c r="F5" s="1" t="inlineStr">
@@ -52567,10 +55548,10 @@
       <c r="C6" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D6" s="174" t="n">
+      <c r="D6" s="175" t="n">
         <v>9037</v>
       </c>
-      <c r="E6" s="174" t="n">
+      <c r="E6" s="175" t="n">
         <v>9037</v>
       </c>
       <c r="F6" s="1" t="inlineStr">
@@ -52598,10 +55579,10 @@
       <c r="C7" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D7" s="174" t="n">
+      <c r="D7" s="175" t="n">
         <v>9029</v>
       </c>
-      <c r="E7" s="174" t="n">
+      <c r="E7" s="175" t="n">
         <v>9029</v>
       </c>
       <c r="F7" s="1" t="inlineStr">
@@ -52629,10 +55610,10 @@
       <c r="C8" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D8" s="174" t="n">
+      <c r="D8" s="175" t="n">
         <v>9184.869915572999</v>
       </c>
-      <c r="E8" s="174" t="n">
+      <c r="E8" s="175" t="n">
         <v>9184.869915572999</v>
       </c>
       <c r="F8" s="1" t="inlineStr">
@@ -52660,10 +55641,10 @@
       <c r="C9" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D9" s="174" t="n">
+      <c r="D9" s="175" t="n">
         <v>9036.950113492001</v>
       </c>
-      <c r="E9" s="174" t="n">
+      <c r="E9" s="175" t="n">
         <v>9036.950113492001</v>
       </c>
       <c r="F9" s="1" t="inlineStr">
@@ -52691,10 +55672,10 @@
       <c r="C10" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D10" s="174" t="n">
+      <c r="D10" s="175" t="n">
         <v>12717</v>
       </c>
-      <c r="E10" s="174" t="n">
+      <c r="E10" s="175" t="n">
         <v>12717</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
@@ -52722,10 +55703,10 @@
       <c r="C11" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D11" s="174" t="n">
+      <c r="D11" s="175" t="n">
         <v>12907</v>
       </c>
-      <c r="E11" s="174" t="n">
+      <c r="E11" s="175" t="n">
         <v>12907</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
@@ -52753,10 +55734,10 @@
       <c r="C12" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D12" s="174" t="n">
+      <c r="D12" s="175" t="n">
         <v>11734</v>
       </c>
-      <c r="E12" s="174" t="n">
+      <c r="E12" s="175" t="n">
         <v>11734</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
@@ -52784,10 +55765,10 @@
       <c r="C13" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D13" s="174" t="n">
+      <c r="D13" s="175" t="n">
         <v>12717.326319019</v>
       </c>
-      <c r="E13" s="174" t="n">
+      <c r="E13" s="175" t="n">
         <v>12717.326319019</v>
       </c>
       <c r="F13" s="1" t="inlineStr">
@@ -52815,10 +55796,10 @@
       <c r="C14" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D14" s="174" t="n">
+      <c r="D14" s="175" t="n">
         <v>12907.499965808</v>
       </c>
-      <c r="E14" s="174" t="n">
+      <c r="E14" s="175" t="n">
         <v>12907.499965808</v>
       </c>
       <c r="F14" s="1" t="inlineStr">
@@ -52846,10 +55827,10 @@
       <c r="C15" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D15" s="174" t="n">
+      <c r="D15" s="175" t="n">
         <v>1478</v>
       </c>
-      <c r="E15" s="174" t="n">
+      <c r="E15" s="175" t="n">
         <v>1478</v>
       </c>
       <c r="F15" s="1" t="inlineStr">
@@ -52877,10 +55858,10 @@
       <c r="C16" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D16" s="174" t="n">
+      <c r="D16" s="175" t="n">
         <v>1844</v>
       </c>
-      <c r="E16" s="174" t="n">
+      <c r="E16" s="175" t="n">
         <v>1844</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
@@ -52908,10 +55889,10 @@
       <c r="C17" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D17" s="174" t="n">
+      <c r="D17" s="175" t="n">
         <v>1955</v>
       </c>
-      <c r="E17" s="174" t="n">
+      <c r="E17" s="175" t="n">
         <v>1955</v>
       </c>
       <c r="F17" s="1" t="inlineStr">
@@ -52939,10 +55920,10 @@
       <c r="C18" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D18" s="174" t="n">
+      <c r="D18" s="175" t="n">
         <v>1478.149852603</v>
       </c>
-      <c r="E18" s="174" t="n">
+      <c r="E18" s="175" t="n">
         <v>1478.149852603</v>
       </c>
       <c r="F18" s="1" t="inlineStr">
@@ -52970,10 +55951,10 @@
       <c r="C19" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D19" s="174" t="n">
+      <c r="D19" s="175" t="n">
         <v>1843.971762465</v>
       </c>
-      <c r="E19" s="174" t="n">
+      <c r="E19" s="175" t="n">
         <v>1843.971762465</v>
       </c>
       <c r="F19" s="1" t="inlineStr">
@@ -53001,10 +55982,10 @@
       <c r="C20" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D20" s="174" t="n">
+      <c r="D20" s="175" t="n">
         <v>594</v>
       </c>
-      <c r="E20" s="174" t="n">
+      <c r="E20" s="175" t="n">
         <v>594</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
@@ -53032,10 +56013,10 @@
       <c r="C21" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D21" s="174" t="n">
+      <c r="D21" s="175" t="n">
         <v>658</v>
       </c>
-      <c r="E21" s="174" t="n">
+      <c r="E21" s="175" t="n">
         <v>658</v>
       </c>
       <c r="F21" s="1" t="inlineStr">
@@ -53063,10 +56044,10 @@
       <c r="C22" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D22" s="174" t="n">
+      <c r="D22" s="175" t="n">
         <v>441</v>
       </c>
-      <c r="E22" s="174" t="n">
+      <c r="E22" s="175" t="n">
         <v>441</v>
       </c>
       <c r="F22" s="1" t="inlineStr">
@@ -53094,10 +56075,10 @@
       <c r="C23" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D23" s="174" t="n">
+      <c r="D23" s="175" t="n">
         <v>594.0401649620001</v>
       </c>
-      <c r="E23" s="174" t="n">
+      <c r="E23" s="175" t="n">
         <v>594.0401649620001</v>
       </c>
       <c r="F23" s="1" t="inlineStr">
@@ -53125,10 +56106,10 @@
       <c r="C24" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D24" s="174" t="n">
+      <c r="D24" s="175" t="n">
         <v>658.0930416160001</v>
       </c>
-      <c r="E24" s="174" t="n">
+      <c r="E24" s="175" t="n">
         <v>658.0930416160001</v>
       </c>
       <c r="F24" s="1" t="inlineStr">
@@ -53156,10 +56137,10 @@
       <c r="C25" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D25" s="174" t="n">
+      <c r="D25" s="175" t="n">
         <v>76055.06748983047</v>
       </c>
-      <c r="E25" s="174" t="n">
+      <c r="E25" s="175" t="n">
         <v>76055.06748983047</v>
       </c>
       <c r="F25" s="1" t="inlineStr">
@@ -53187,10 +56168,10 @@
       <c r="C26" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D26" s="174" t="n">
+      <c r="D26" s="175" t="n">
         <v>75781.52071231291</v>
       </c>
-      <c r="E26" s="174" t="n">
+      <c r="E26" s="175" t="n">
         <v>75781.52071231291</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
@@ -53218,10 +56199,10 @@
       <c r="C27" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D27" s="174" t="n">
+      <c r="D27" s="175" t="n">
         <v>75255.62912098455</v>
       </c>
-      <c r="E27" s="174" t="n">
+      <c r="E27" s="175" t="n">
         <v>75255.62912098455</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
@@ -53249,10 +56230,10 @@
       <c r="C28" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D28" s="174" t="n">
+      <c r="D28" s="175" t="n">
         <v>75149.98563223911</v>
       </c>
-      <c r="E28" s="174" t="n">
+      <c r="E28" s="175" t="n">
         <v>75149.98563223911</v>
       </c>
       <c r="F28" s="1" t="inlineStr">
@@ -53280,10 +56261,10 @@
       <c r="C29" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D29" s="174" t="n">
+      <c r="D29" s="175" t="n">
         <v>131.7706421450265</v>
       </c>
-      <c r="E29" s="174" t="n">
+      <c r="E29" s="175" t="n">
         <v>131.7706421450265</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
@@ -53311,10 +56292,10 @@
       <c r="C30" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D30" s="174" t="n">
+      <c r="D30" s="175" t="n">
         <v>125.7466421450265</v>
       </c>
-      <c r="E30" s="174" t="n">
+      <c r="E30" s="175" t="n">
         <v>125.7466421450265</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
@@ -53342,10 +56323,10 @@
       <c r="C31" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D31" s="174" t="n">
+      <c r="D31" s="175" t="n">
         <v>114.7916421450265</v>
       </c>
-      <c r="E31" s="174" t="n">
+      <c r="E31" s="175" t="n">
         <v>114.7916421450265</v>
       </c>
       <c r="F31" s="1" t="inlineStr">
@@ -53373,10 +56354,10 @@
       <c r="C32" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D32" s="174" t="n">
+      <c r="D32" s="175" t="n">
         <v>134.7967469817132</v>
       </c>
-      <c r="E32" s="174" t="n">
+      <c r="E32" s="175" t="n">
         <v>134.7967469817132</v>
       </c>
       <c r="F32" s="1" t="inlineStr">
@@ -53404,10 +56385,10 @@
       <c r="C33" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D33" s="174" t="n">
+      <c r="D33" s="175" t="n">
         <v>523.0907540648606</v>
       </c>
-      <c r="E33" s="174" t="n">
+      <c r="E33" s="175" t="n">
         <v>523.0907540648606</v>
       </c>
       <c r="F33" s="1" t="inlineStr">
@@ -53435,10 +56416,10 @@
       <c r="C34" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D34" s="174" t="n">
+      <c r="D34" s="175" t="n">
         <v>524.9937540648609</v>
       </c>
-      <c r="E34" s="174" t="n">
+      <c r="E34" s="175" t="n">
         <v>524.9937540648609</v>
       </c>
       <c r="F34" s="1" t="inlineStr">
@@ -53466,10 +56447,10 @@
       <c r="C35" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D35" s="174" t="n">
+      <c r="D35" s="175" t="n">
         <v>523.150754064861</v>
       </c>
-      <c r="E35" s="174" t="n">
+      <c r="E35" s="175" t="n">
         <v>523.150754064861</v>
       </c>
       <c r="F35" s="1" t="inlineStr">
@@ -53497,10 +56478,10 @@
       <c r="C36" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D36" s="174" t="n">
+      <c r="D36" s="175" t="n">
         <v>516.9856529750193</v>
       </c>
-      <c r="E36" s="174" t="n">
+      <c r="E36" s="175" t="n">
         <v>516.9856529750193</v>
       </c>
       <c r="F36" s="1" t="inlineStr">
@@ -53528,10 +56509,10 @@
       <c r="C37" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D37" s="174" t="n">
+      <c r="D37" s="175" t="n">
         <v>204.4529227196744</v>
       </c>
-      <c r="E37" s="174" t="n">
+      <c r="E37" s="175" t="n">
         <v>204.4529227196744</v>
       </c>
       <c r="F37" s="1" t="inlineStr">
@@ -53559,10 +56540,10 @@
       <c r="C38" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D38" s="174" t="n">
+      <c r="D38" s="175" t="n">
         <v>204.2286999662737</v>
       </c>
-      <c r="E38" s="174" t="n">
+      <c r="E38" s="175" t="n">
         <v>204.2286999662738</v>
       </c>
       <c r="F38" s="1" t="inlineStr">
@@ -53590,10 +56571,10 @@
       <c r="C39" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D39" s="174" t="n">
+      <c r="D39" s="175" t="n">
         <v>205.1258295918731</v>
       </c>
-      <c r="E39" s="174" t="n">
+      <c r="E39" s="175" t="n">
         <v>205.1258295918731</v>
       </c>
       <c r="F39" s="1" t="inlineStr">
@@ -53621,10 +56602,10 @@
       <c r="C40" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D40" s="174" t="n">
+      <c r="D40" s="175" t="n">
         <v>205.4648860142573</v>
       </c>
-      <c r="E40" s="174" t="n">
+      <c r="E40" s="175" t="n">
         <v>205.4648860142574</v>
       </c>
       <c r="F40" s="1" t="inlineStr">
@@ -53652,10 +56633,10 @@
       <c r="C41" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D41" s="174" t="n">
+      <c r="D41" s="175" t="n">
         <v>110.0650907489087</v>
       </c>
-      <c r="E41" s="174" t="n">
+      <c r="E41" s="175" t="n">
         <v>110.0650907489087</v>
       </c>
       <c r="F41" s="1" t="inlineStr">
@@ -53683,10 +56664,10 @@
       <c r="C42" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D42" s="174" t="n">
+      <c r="D42" s="175" t="n">
         <v>109.5650907489087</v>
       </c>
-      <c r="E42" s="174" t="n">
+      <c r="E42" s="175" t="n">
         <v>109.5650907489087</v>
       </c>
       <c r="F42" s="1" t="inlineStr">
@@ -53714,10 +56695,10 @@
       <c r="C43" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D43" s="174" t="n">
+      <c r="D43" s="175" t="n">
         <v>103.6250907489087</v>
       </c>
-      <c r="E43" s="174" t="n">
+      <c r="E43" s="175" t="n">
         <v>103.6250907489087</v>
       </c>
       <c r="F43" s="1" t="inlineStr">
@@ -53745,10 +56726,10 @@
       <c r="C44" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D44" s="174" t="n">
+      <c r="D44" s="175" t="n">
         <v>99.09852067977131</v>
       </c>
-      <c r="E44" s="174" t="n">
+      <c r="E44" s="175" t="n">
         <v>99.09852067977131</v>
       </c>
       <c r="F44" s="1" t="inlineStr">
@@ -53776,10 +56757,10 @@
       <c r="C45" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D45" s="174" t="n">
+      <c r="D45" s="175" t="n">
         <v>93.14166666666667</v>
       </c>
-      <c r="E45" s="174" t="n">
+      <c r="E45" s="175" t="n">
         <v>93.14166666666667</v>
       </c>
       <c r="F45" s="1" t="inlineStr">
@@ -53807,10 +56788,10 @@
       <c r="C46" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D46" s="174" t="n">
+      <c r="D46" s="175" t="n">
         <v>93.71666666666665</v>
       </c>
-      <c r="E46" s="174" t="n">
+      <c r="E46" s="175" t="n">
         <v>93.71666666666665</v>
       </c>
       <c r="F46" s="1" t="inlineStr">
@@ -53838,10 +56819,10 @@
       <c r="C47" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D47" s="174" t="n">
+      <c r="D47" s="175" t="n">
         <v>93.33333333333333</v>
       </c>
-      <c r="E47" s="174" t="n">
+      <c r="E47" s="175" t="n">
         <v>93.33333333333333</v>
       </c>
       <c r="F47" s="1" t="inlineStr">
@@ -53869,10 +56850,10 @@
       <c r="C48" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D48" s="174" t="n">
+      <c r="D48" s="175" t="n">
         <v>92.14166666666665</v>
       </c>
-      <c r="E48" s="174" t="n">
+      <c r="E48" s="175" t="n">
         <v>92.14166666666667</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
@@ -53900,10 +56881,10 @@
       <c r="C49" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D49" s="174" t="n">
+      <c r="D49" s="175" t="n">
         <v>93.00833333333334</v>
       </c>
-      <c r="E49" s="174" t="n">
+      <c r="E49" s="175" t="n">
         <v>93.00833333333333</v>
       </c>
       <c r="F49" s="1" t="inlineStr">
@@ -53931,10 +56912,10 @@
       <c r="C50" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="D50" s="174" t="n">
+      <c r="D50" s="175" t="n">
         <v>93.01666666666667</v>
       </c>
-      <c r="E50" s="174" t="n">
+      <c r="E50" s="175" t="n">
         <v>93.01666666666667</v>
       </c>
       <c r="F50" s="1" t="inlineStr">
@@ -53962,10 +56943,10 @@
       <c r="C51" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D51" s="174" t="n">
+      <c r="D51" s="175" t="n">
         <v>93.53333333333332</v>
       </c>
-      <c r="E51" s="174" t="n">
+      <c r="E51" s="175" t="n">
         <v>93.53333333333335</v>
       </c>
       <c r="F51" s="1" t="inlineStr">
@@ -53993,10 +56974,10 @@
       <c r="C52" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="D52" s="174" t="n">
+      <c r="D52" s="175" t="n">
         <v>93.70833333333333</v>
       </c>
-      <c r="E52" s="174" t="n">
+      <c r="E52" s="175" t="n">
         <v>93.70833333333333</v>
       </c>
       <c r="F52" s="1" t="inlineStr">
@@ -54024,10 +57005,10 @@
       <c r="C53" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D53" s="174" t="n">
+      <c r="D53" s="175" t="n">
         <v>703.1324447169991</v>
       </c>
-      <c r="E53" s="174" t="n">
+      <c r="E53" s="175" t="n">
         <v>703.132444716999</v>
       </c>
       <c r="F53" s="1" t="inlineStr">
@@ -54055,10 +57036,10 @@
       <c r="C54" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D54" s="174" t="n">
+      <c r="D54" s="175" t="n">
         <v>587.4580081820001</v>
       </c>
-      <c r="E54" s="174" t="n">
+      <c r="E54" s="175" t="n">
         <v>587.4580081820001</v>
       </c>
       <c r="F54" s="1" t="inlineStr">
@@ -54086,10 +57067,10 @@
       <c r="C55" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D55" s="174" t="n">
+      <c r="D55" s="175" t="n">
         <v>3530.440256933996</v>
       </c>
-      <c r="E55" s="174" t="n">
+      <c r="E55" s="175" t="n">
         <v>3530.440256933996</v>
       </c>
       <c r="F55" s="1" t="inlineStr">
@@ -54117,10 +57098,10 @@
       <c r="C56" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D56" s="174" t="n">
+      <c r="D56" s="175" t="n">
         <v>1498.937893394999</v>
       </c>
-      <c r="E56" s="174" t="n">
+      <c r="E56" s="175" t="n">
         <v>1498.937893394999</v>
       </c>
       <c r="F56" s="1" t="inlineStr">
@@ -54148,10 +57129,10 @@
       <c r="C57" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D57" s="174" t="n">
+      <c r="D57" s="175" t="n">
         <v>273.644045045999</v>
       </c>
-      <c r="E57" s="174" t="n">
+      <c r="E57" s="175" t="n">
         <v>273.644045045999</v>
       </c>
       <c r="F57" s="1" t="inlineStr">
@@ -54179,10 +57160,10 @@
       <c r="C58" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D58" s="174" t="n">
+      <c r="D58" s="175" t="n">
         <v>612.2656460789989</v>
       </c>
-      <c r="E58" s="174" t="n">
+      <c r="E58" s="175" t="n">
         <v>612.2656460789989</v>
       </c>
       <c r="F58" s="1" t="inlineStr">
@@ -54210,10 +57191,10 @@
       <c r="C59" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D59" s="174" t="n">
+      <c r="D59" s="175" t="n">
         <v>99.82992901300001</v>
       </c>
-      <c r="E59" s="174" t="n">
+      <c r="E59" s="175" t="n">
         <v>99.829929013</v>
       </c>
       <c r="F59" s="1" t="inlineStr">
@@ -54241,10 +57222,10 @@
       <c r="C60" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D60" s="174" t="n">
+      <c r="D60" s="175" t="n">
         <v>448.1562321239999</v>
       </c>
-      <c r="E60" s="174" t="n">
+      <c r="E60" s="175" t="n">
         <v>448.1562321239999</v>
       </c>
       <c r="F60" s="1" t="inlineStr">
@@ -54272,10 +57253,10 @@
       <c r="C61" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D61" s="174" t="n">
+      <c r="D61" s="175" t="n">
         <v>1431.005460082997</v>
       </c>
-      <c r="E61" s="174" t="n">
+      <c r="E61" s="175" t="n">
         <v>1431.005460082997</v>
       </c>
       <c r="F61" s="1" t="inlineStr">
@@ -54303,10 +57284,10 @@
       <c r="C62" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D62" s="174" t="n">
+      <c r="D62" s="175" t="n">
         <v>1032.35218272</v>
       </c>
-      <c r="E62" s="174" t="n">
+      <c r="E62" s="175" t="n">
         <v>1032.35218272</v>
       </c>
       <c r="F62" s="1" t="inlineStr">
@@ -54334,10 +57315,10 @@
       <c r="C63" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D63" s="174" t="n">
+      <c r="D63" s="175" t="n">
         <v>781.8611598310002</v>
       </c>
-      <c r="E63" s="174" t="n">
+      <c r="E63" s="175" t="n">
         <v>781.8611598310002</v>
       </c>
       <c r="F63" s="1" t="inlineStr">
@@ -54365,10 +57346,10 @@
       <c r="C64" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D64" s="174" t="n">
+      <c r="D64" s="175" t="n">
         <v>3278.990501961999</v>
       </c>
-      <c r="E64" s="174" t="n">
+      <c r="E64" s="175" t="n">
         <v>3278.990501961999</v>
       </c>
       <c r="F64" s="1" t="inlineStr">
@@ -54396,10 +57377,10 @@
       <c r="C65" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D65" s="174" t="n">
+      <c r="D65" s="175" t="n">
         <v>2785.554802503</v>
       </c>
-      <c r="E65" s="174" t="n">
+      <c r="E65" s="175" t="n">
         <v>2785.554802503</v>
       </c>
       <c r="F65" s="1" t="inlineStr">
@@ -54427,10 +57408,10 @@
       <c r="C66" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D66" s="174" t="n">
+      <c r="D66" s="175" t="n">
         <v>221.987440248</v>
       </c>
-      <c r="E66" s="174" t="n">
+      <c r="E66" s="175" t="n">
         <v>221.987440248</v>
       </c>
       <c r="F66" s="1" t="inlineStr">
@@ -54458,10 +57439,10 @@
       <c r="C67" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D67" s="174" t="n">
+      <c r="D67" s="175" t="n">
         <v>1144.924075864997</v>
       </c>
-      <c r="E67" s="174" t="n">
+      <c r="E67" s="175" t="n">
         <v>1144.924075864997</v>
       </c>
       <c r="F67" s="1" t="inlineStr">
@@ -54489,10 +57470,10 @@
       <c r="C68" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D68" s="174" t="n">
+      <c r="D68" s="175" t="n">
         <v>351.9801199100001</v>
       </c>
-      <c r="E68" s="174" t="n">
+      <c r="E68" s="175" t="n">
         <v>351.9801199100001</v>
       </c>
       <c r="F68" s="1" t="inlineStr">
@@ -54520,10 +57501,10 @@
       <c r="C69" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D69" s="174" t="n">
+      <c r="D69" s="175" t="n">
         <v>619.906488913</v>
       </c>
-      <c r="E69" s="174" t="n">
+      <c r="E69" s="175" t="n">
         <v>619.906488913</v>
       </c>
       <c r="F69" s="1" t="inlineStr">
@@ -54551,10 +57532,10 @@
       <c r="C70" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="D70" s="174" t="n">
+      <c r="D70" s="175" t="n">
         <v>2499.769547067</v>
       </c>
-      <c r="E70" s="174" t="n">
+      <c r="E70" s="175" t="n">
         <v>2499.769547067</v>
       </c>
       <c r="F70" s="1" t="inlineStr">
@@ -54662,7 +57643,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>Sheets added: History, Sector history, Diesel by use, Vehicle history, Checks, History sources. No other cell changed.</t>
+          <t>Sheets added: History, Sector history, Diesel by use, Vehicle history, HML response, Gap status, Checks, History sources. No other cell changed.</t>
         </is>
       </c>
     </row>
@@ -54671,13 +57652,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -54694,524 +57675,1213 @@
     <row r="1">
       <c r="A1" s="149" t="inlineStr">
         <is>
-          <t>Sources for the History and Sector history sheets</t>
+          <t>Sources for the sheets added to the workshop workbook</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="173" t="inlineStr">
+      <c r="A4" s="174" t="inlineStr">
         <is>
           <t>Used for</t>
         </is>
       </c>
-      <c r="B4" s="173" t="inlineStr">
+      <c r="B4" s="174" t="inlineStr">
         <is>
           <t>Publisher</t>
         </is>
       </c>
-      <c r="C4" s="173" t="inlineStr">
+      <c r="C4" s="174" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="D4" s="173" t="inlineStr">
+      <c r="D4" s="174" t="inlineStr">
         <is>
           <t>Original file</t>
         </is>
       </c>
-      <c r="E4" s="173" t="inlineStr">
+      <c r="E4" s="174" t="inlineStr">
         <is>
           <t>Where the original is kept</t>
         </is>
       </c>
-      <c r="F4" s="173" t="inlineStr">
+      <c r="F4" s="174" t="inlineStr">
         <is>
           <t>Extract in the repository</t>
         </is>
       </c>
-      <c r="G4" s="173" t="inlineStr">
+      <c r="G4" s="174" t="inlineStr">
         <is>
           <t>Refresh command</t>
         </is>
       </c>
-      <c r="H4" s="173" t="inlineStr">
+      <c r="H4" s="174" t="inlineStr">
         <is>
           <t>Periods</t>
         </is>
       </c>
-      <c r="I4" s="173" t="inlineStr">
+      <c r="I4" s="174" t="inlineStr">
         <is>
           <t>Limits</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="175" t="inlineStr">
+      <c r="A5" s="173" t="inlineStr">
         <is>
           <t>History sections 1 and 4: national sales</t>
         </is>
       </c>
-      <c r="B5" s="175" t="inlineStr">
+      <c r="B5" s="173" t="inlineStr">
         <is>
           <t>Department of Mineral and Petroleum Resources (energy department)</t>
         </is>
       </c>
-      <c r="C5" s="175" t="inlineStr">
+      <c r="C5" s="173" t="inlineStr">
         <is>
           <t>https://www.dmpr.gov.za/Portals/0/Energy_Website/files/media/SA FUEL SALES VOLUME/</t>
         </is>
       </c>
-      <c r="D5" s="175" t="inlineStr">
+      <c r="D5" s="173" t="inlineStr">
         <is>
           <t>&lt;year&gt;-...-FSV....xls(x), national annual workbooks 2005-2023</t>
         </is>
       </c>
-      <c r="E5" s="175" t="inlineStr">
+      <c r="E5" s="173" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main</t>
         </is>
       </c>
-      <c r="F5" s="175" t="inlineStr">
+      <c r="F5" s="173" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_sales_department.csv</t>
         </is>
       </c>
-      <c r="G5" s="175" t="inlineStr">
+      <c r="G5" s="173" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_energy_dept --vintage 2026</t>
         </is>
       </c>
-      <c r="H5" s="175" t="inlineStr">
+      <c r="H5" s="173" t="inlineStr">
         <is>
           <t>2005-2023</t>
         </is>
       </c>
-      <c r="I5" s="175" t="inlineStr">
+      <c r="I5" s="173" t="inlineStr">
         <is>
           <t>2013 corrected on manish-branch (published sheet). Series ends 2023.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="175" t="inlineStr">
+      <c r="A6" s="173" t="inlineStr">
         <is>
           <t>History section 1: sales by province</t>
         </is>
       </c>
-      <c r="B6" s="175" t="inlineStr">
+      <c r="B6" s="173" t="inlineStr">
         <is>
           <t>Department of Mineral and Petroleum Resources (energy department)</t>
         </is>
       </c>
-      <c r="C6" s="175" t="inlineStr">
+      <c r="C6" s="173" t="inlineStr">
         <is>
           <t>https://www.dmpr.gov.za/Portals/0/Energy_Website/files/media/SA FUEL SALES VOLUME/</t>
         </is>
       </c>
-      <c r="D6" s="175" t="inlineStr">
+      <c r="D6" s="173" t="inlineStr">
         <is>
           <t>&lt;year&gt;-...-Magisterial-Districts-data.xlsx, quarterly sheets</t>
         </is>
       </c>
-      <c r="E6" s="175" t="inlineStr">
+      <c r="E6" s="173" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main (2013 annual workbook on manish-branch)</t>
         </is>
       </c>
-      <c r="F6" s="175" t="inlineStr">
+      <c r="F6" s="173" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_sales_department_by_province.csv</t>
         </is>
       </c>
-      <c r="G6" s="175" t="inlineStr">
+      <c r="G6" s="173" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_energy_dept --vintage 2026</t>
         </is>
       </c>
-      <c r="H6" s="175" t="inlineStr">
+      <c r="H6" s="173" t="inlineStr">
         <is>
           <t>2013-2022</t>
         </is>
       </c>
-      <c r="I6" s="175" t="inlineStr">
+      <c r="I6" s="173" t="inlineStr">
         <is>
           <t>Ends 2022. 2018 understated about 1.8% (district Q1 sheet incomplete). 2014-Q3 differs from national file.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="175" t="inlineStr">
+      <c r="A7" s="173" t="inlineStr">
         <is>
           <t>History section 2: imports and exports</t>
         </is>
       </c>
-      <c r="B7" s="175" t="inlineStr">
+      <c r="B7" s="173" t="inlineStr">
         <is>
           <t>South African Revenue Service, trade statistics</t>
         </is>
       </c>
-      <c r="C7" s="175" t="inlineStr">
+      <c r="C7" s="173" t="inlineStr">
         <is>
           <t>https://tools.sars.gov.za/tradestatsportal/data_download.aspx</t>
         </is>
       </c>
-      <c r="D7" s="175" t="inlineStr">
+      <c r="D7" s="173" t="inlineStr">
         <is>
           <t>sars-&lt;imports|exports&gt;-chapter27-fuels-&lt;year&gt;.xlsx, 2010-2026</t>
         </is>
       </c>
-      <c r="E7" s="175" t="inlineStr">
+      <c r="E7" s="173" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/sars/)</t>
         </is>
       </c>
-      <c r="F7" s="175" t="inlineStr">
+      <c r="F7" s="173" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_trade_sars.csv</t>
         </is>
       </c>
-      <c r="G7" s="175" t="inlineStr">
+      <c r="G7" s="173" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_sars --vintage 2026</t>
         </is>
       </c>
-      <c r="H7" s="175" t="inlineStr">
+      <c r="H7" s="173" t="inlineStr">
         <is>
           <t>2010-2026</t>
         </is>
       </c>
-      <c r="I7" s="175" t="inlineStr">
+      <c r="I7" s="173" t="inlineStr">
         <is>
           <t>Primary record of imports and exports from 2014. Kilograms to 2012, litres from 2014, both in 2013.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="175" t="inlineStr">
+      <c r="A8" s="173" t="inlineStr">
         <is>
           <t>History section 2: FIASA comparison rows</t>
         </is>
       </c>
-      <c r="B8" s="175" t="inlineStr">
+      <c r="B8" s="173" t="inlineStr">
         <is>
           <t>Fuels Industry Association of South Africa (from customs data)</t>
         </is>
       </c>
-      <c r="C8" s="175" t="inlineStr">
+      <c r="C8" s="173" t="inlineStr">
         <is>
           <t>https://fuelsindustry.org.za/publications/annual-reports/</t>
         </is>
       </c>
-      <c r="D8" s="175" t="inlineStr">
+      <c r="D8" s="173" t="inlineStr">
         <is>
           <t>annual-report-&lt;year&gt;.pdf; 2025 edition pp.47-49</t>
         </is>
       </c>
-      <c r="E8" s="175" t="inlineStr">
+      <c r="E8" s="173" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main; 2025 edition on main</t>
         </is>
       </c>
-      <c r="F8" s="175" t="inlineStr">
+      <c r="F8" s="173" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_trade_fiasa.csv</t>
         </is>
       </c>
-      <c r="G8" s="175" t="inlineStr">
+      <c r="G8" s="173" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_fuel_sales --vintage 2026</t>
         </is>
       </c>
-      <c r="H8" s="175" t="inlineStr">
+      <c r="H8" s="173" t="inlineStr">
         <is>
           <t>2009-2025</t>
         </is>
       </c>
-      <c r="I8" s="175" t="inlineStr">
+      <c r="I8" s="173" t="inlineStr">
         <is>
           <t>Cross-check, and the record before 2014; SARS is primary from 2014. 'Kerosene' is jet plus paraffin. Its 2024 diesel import figure is 4.000 bn L above customs.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="175" t="inlineStr">
+      <c r="A9" s="173" t="inlineStr">
         <is>
           <t>History section 4: FIASA comparison row</t>
         </is>
       </c>
-      <c r="B9" s="175" t="inlineStr">
+      <c r="B9" s="173" t="inlineStr">
         <is>
           <t>Fuels Industry Association of South Africa</t>
         </is>
       </c>
-      <c r="C9" s="175" t="inlineStr">
+      <c r="C9" s="173" t="inlineStr">
         <is>
           <t>https://fuelsindustry.org.za/publications/annual-reports/</t>
         </is>
       </c>
-      <c r="D9" s="175" t="inlineStr">
+      <c r="D9" s="173" t="inlineStr">
         <is>
           <t>annual-report-&lt;year&gt;.pdf, 2021-2025 editions</t>
         </is>
       </c>
-      <c r="E9" s="175" t="inlineStr">
+      <c r="E9" s="173" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main; 2025 edition on main</t>
         </is>
       </c>
-      <c r="F9" s="175" t="inlineStr">
+      <c r="F9" s="173" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/fuel_sales_fiasa.csv</t>
         </is>
       </c>
-      <c r="G9" s="175" t="inlineStr">
+      <c r="G9" s="173" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_fuel_sales --vintage 2026</t>
         </is>
       </c>
-      <c r="H9" s="175" t="inlineStr">
+      <c r="H9" s="173" t="inlineStr">
         <is>
           <t>2009-2024</t>
         </is>
       </c>
-      <c r="I9" s="175" t="inlineStr">
+      <c r="I9" s="173" t="inlineStr">
         <is>
           <t>Used for 2024 only. Its 2013 figures equal the department's superseded sheet.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="175" t="inlineStr">
+      <c r="A10" s="173" t="inlineStr">
         <is>
           <t>History section 3 and Sector history: production and diesel by sector</t>
         </is>
       </c>
-      <c r="B10" s="175" t="inlineStr">
+      <c r="B10" s="173" t="inlineStr">
         <is>
           <t>Department of Mineral and Petroleum Resources (energy department)</t>
         </is>
       </c>
-      <c r="C10" s="175" t="inlineStr">
+      <c r="C10" s="173" t="inlineStr">
         <is>
           <t>https://www.dmpr.gov.za/Portals/0/Energy_Website/files/media/Energy_Balances.html</t>
         </is>
       </c>
-      <c r="D10" s="175" t="inlineStr">
+      <c r="D10" s="173" t="inlineStr">
         <is>
           <t>&lt;year&gt;-Commodity-Flow-and-Energy-Balance.xlsx, 2007-2021</t>
         </is>
       </c>
-      <c r="E10" s="175" t="inlineStr">
+      <c r="E10" s="173" t="inlineStr">
         <is>
           <t>local to Manish and Nigel; not on main</t>
         </is>
       </c>
-      <c r="F10" s="175" t="inlineStr">
+      <c r="F10" s="173" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/energy_balance_department.csv</t>
         </is>
       </c>
-      <c r="G10" s="175" t="inlineStr">
+      <c r="G10" s="173" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_energy_dept --vintage 2026</t>
         </is>
       </c>
-      <c r="H10" s="175" t="inlineStr">
+      <c r="H10" s="173" t="inlineStr">
         <is>
           <t>2007-2021</t>
         </is>
       </c>
-      <c r="I10" s="175" t="inlineStr">
+      <c r="I10" s="173" t="inlineStr">
         <is>
           <t>Ends 2021. Sector definitions shift in 2016. Fuel oil not extracted.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="175" t="inlineStr">
+      <c r="A11" s="173" t="inlineStr">
         <is>
           <t>History section 3: operators' reported output</t>
         </is>
       </c>
-      <c r="B11" s="175" t="inlineStr">
+      <c r="B11" s="173" t="inlineStr">
         <is>
           <t>Sasol (production and sales metrics); Glencore (annual reports)</t>
         </is>
       </c>
-      <c r="C11" s="175" t="inlineStr">
+      <c r="C11" s="173" t="inlineStr">
         <is>
           <t>https://www.sasol.com/</t>
         </is>
       </c>
-      <c r="D11" s="175" t="inlineStr">
+      <c r="D11" s="173" t="inlineStr">
         <is>
           <t>sasol-metrics-fy2022/2025/2026.pdf, p.4; GLEN-2023/2024/2025-Annual-Report.pdf</t>
         </is>
       </c>
-      <c r="E11" s="175" t="inlineStr">
+      <c r="E11" s="173" t="inlineStr">
         <is>
           <t>Sasol files on manish-branch (external/data/raw/sasol/); Glencore reports by link only</t>
         </is>
       </c>
-      <c r="F11" s="175" t="inlineStr">
+      <c r="F11" s="173" t="inlineStr">
         <is>
           <t>assumptions/2026/reference/refinery_output_operators.csv</t>
         </is>
       </c>
-      <c r="G11" s="175" t="inlineStr">
+      <c r="G11" s="173" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="H11" s="175" t="inlineStr">
+      <c r="H11" s="173" t="inlineStr">
         <is>
           <t>2020-2026</t>
         </is>
       </c>
-      <c r="I11" s="175" t="inlineStr">
+      <c r="I11" s="173" t="inlineStr">
         <is>
           <t>All refined products, no product split; fiscal and calendar years; Astron as energy content.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="175" t="inlineStr">
+      <c r="A12" s="173" t="inlineStr">
         <is>
           <t>History section 5: litres levied</t>
         </is>
       </c>
-      <c r="B12" s="175" t="inlineStr">
+      <c r="B12" s="173" t="inlineStr">
         <is>
           <t>Road Accident Fund</t>
         </is>
       </c>
-      <c r="C12" s="175" t="inlineStr">
+      <c r="C12" s="173" t="inlineStr">
         <is>
           <t>https://static.pmg.org.za/RAF_Annual_Report_2025.pdf</t>
         </is>
       </c>
-      <c r="D12" s="175" t="inlineStr">
+      <c r="D12" s="173" t="inlineStr">
         <is>
           <t>raf-annual-report-2024-25.pdf, note 16 (p.183)</t>
         </is>
       </c>
-      <c r="E12" s="175" t="inlineStr">
+      <c r="E12" s="173" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/raf/)</t>
         </is>
       </c>
-      <c r="F12" s="175" t="inlineStr">
+      <c r="F12" s="173" t="inlineStr">
         <is>
           <t>assumptions/2026/reference/fuel_levy_revenue_raf.csv</t>
         </is>
       </c>
-      <c r="G12" s="175" t="inlineStr">
+      <c r="G12" s="173" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="H12" s="175" t="inlineStr">
+      <c r="H12" s="173" t="inlineStr">
         <is>
           <t>2024-2025</t>
         </is>
       </c>
-      <c r="I12" s="175" t="inlineStr">
+      <c r="I12" s="173" t="inlineStr">
         <is>
           <t>Gross levies and diesel rebate in rand; litres derived in the balance note. Fiscal years; petrol and diesel together.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="175" t="inlineStr">
+      <c r="A13" s="173" t="inlineStr">
         <is>
           <t>Sector history: mining and manufacturing volume indices</t>
         </is>
       </c>
-      <c r="B13" s="175" t="inlineStr">
+      <c r="B13" s="173" t="inlineStr">
         <is>
           <t>Statistics South Africa (P2041 mining, P3041.2 manufacturing, P7162 land transport, P0141 CPI)</t>
         </is>
       </c>
-      <c r="C13" s="175" t="inlineStr">
+      <c r="C13" s="173" t="inlineStr">
         <is>
           <t>https://www.statssa.gov.za/?page_id=1847</t>
         </is>
       </c>
-      <c r="D13" s="175" t="inlineStr">
+      <c r="D13" s="173" t="inlineStr">
         <is>
           <t>release zips, July and August 2026</t>
         </is>
       </c>
-      <c r="E13" s="175" t="inlineStr">
+      <c r="E13" s="173" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/statssa/)</t>
         </is>
       </c>
-      <c r="F13" s="175" t="inlineStr">
+      <c r="F13" s="173" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/activity_statssa_monthly.csv</t>
         </is>
       </c>
-      <c r="G13" s="175" t="inlineStr">
+      <c r="G13" s="173" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_statssa_monthly --vintage 2026</t>
         </is>
       </c>
-      <c r="H13" s="175" t="inlineStr">
+      <c r="H13" s="173" t="inlineStr">
         <is>
           <t>1998-01-2026-08</t>
         </is>
       </c>
-      <c r="I13" s="175" t="inlineStr">
+      <c r="I13" s="173" t="inlineStr">
         <is>
           <t>Activity measures, not fuel volumes. Not seasonally adjusted. Tonnes, not tonne-kilometres.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="175" t="inlineStr">
+      <c r="A14" s="173" t="inlineStr">
         <is>
           <t>Sector history: agriculture real value added</t>
         </is>
       </c>
-      <c r="B14" s="175" t="inlineStr">
+      <c r="B14" s="173" t="inlineStr">
         <is>
           <t>Statistics South Africa (P0441 GDP; P0302 mid-year population)</t>
         </is>
       </c>
-      <c r="C14" s="175" t="inlineStr">
+      <c r="C14" s="173" t="inlineStr">
         <is>
           <t>https://www.statssa.gov.za/?page_id=1854&amp;PPN=P0441</t>
         </is>
       </c>
-      <c r="D14" s="175" t="inlineStr">
+      <c r="D14" s="173" t="inlineStr">
         <is>
           <t>GDP P0441 - GDP Time series Q2 2026.xlsx (Annual sheet); Country projection ... (2002-2026).xlsx</t>
         </is>
       </c>
-      <c r="E14" s="175" t="inlineStr">
+      <c r="E14" s="173" t="inlineStr">
         <is>
           <t>on manish-branch (external/data/raw/statssa/)</t>
         </is>
       </c>
-      <c r="F14" s="175" t="inlineStr">
+      <c r="F14" s="173" t="inlineStr">
         <is>
           <t>assumptions/2026/timeseries/macro_statssa.csv</t>
         </is>
       </c>
-      <c r="G14" s="175" t="inlineStr">
+      <c r="G14" s="173" t="inlineStr">
         <is>
           <t>python -m lfm.scripts.fetch_economy --vintage 2026</t>
         </is>
       </c>
-      <c r="H14" s="175" t="inlineStr">
+      <c r="H14" s="173" t="inlineStr">
         <is>
           <t>1993-2050</t>
         </is>
       </c>
-      <c r="I14" s="175" t="inlineStr">
+      <c r="I14" s="173" t="inlineStr">
         <is>
           <t>Manual placement each release. Years after 2026 are projections, not observations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="173" t="inlineStr">
+        <is>
+          <t>History section 7: aircraft movements</t>
+        </is>
+      </c>
+      <c r="B15" s="173" t="inlineStr">
+        <is>
+          <t>Airports Company South Africa</t>
+        </is>
+      </c>
+      <c r="C15" s="173" t="inlineStr">
+        <is>
+          <t>https://www.airports.co.za/StatisticsLib/</t>
+        </is>
+      </c>
+      <c r="D15" s="173" t="inlineStr">
+        <is>
+          <t>derived from the monthly file</t>
+        </is>
+      </c>
+      <c r="E15" s="173" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F15" s="173" t="inlineStr">
+        <is>
+          <t>assumptions/2026/timeseries/air_traffic_acsa_annual.csv</t>
+        </is>
+      </c>
+      <c r="G15" s="173" t="inlineStr">
+        <is>
+          <t>python -m lfm.scripts.fetch_acsa --vintage 2026</t>
+        </is>
+      </c>
+      <c r="H15" s="173" t="inlineStr">
+        <is>
+          <t>2013-2025</t>
+        </is>
+      </c>
+      <c r="I15" s="173" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="173" t="inlineStr">
+        <is>
+          <t>History section 6: quarter 1 2023 provincial shares</t>
+        </is>
+      </c>
+      <c r="B16" s="173" t="inlineStr">
+        <is>
+          <t>Department of Mineral and Petroleum Resources (energy department)</t>
+        </is>
+      </c>
+      <c r="C16" s="173" t="inlineStr">
+        <is>
+          <t>https://www.dmpr.gov.za/Portals/0/Energy_Website/files/media/SA FUEL SALES VOLUME/</t>
+        </is>
+      </c>
+      <c r="D16" s="173" t="inlineStr">
+        <is>
+          <t>same workbooks; source_file column names each one</t>
+        </is>
+      </c>
+      <c r="E16" s="173" t="inlineStr">
+        <is>
+          <t>local to Manish and Nigel; not on main</t>
+        </is>
+      </c>
+      <c r="F16" s="173" t="inlineStr">
+        <is>
+          <t>assumptions/2026/timeseries/fuel_sales_department_by_province_quarterly.csv</t>
+        </is>
+      </c>
+      <c r="G16" s="173" t="inlineStr">
+        <is>
+          <t>python -m lfm.scripts.fetch_energy_dept --vintage 2026</t>
+        </is>
+      </c>
+      <c r="H16" s="173" t="inlineStr">
+        <is>
+          <t>2013-Q1-2023-Q1</t>
+        </is>
+      </c>
+      <c r="I16" s="173" t="inlineStr">
+        <is>
+          <t>26 province/product years have blank quarters in the source (none petrol or diesel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="173" t="inlineStr">
+        <is>
+          <t>History section 6: provincial GDP used to move the 2024 shares</t>
+        </is>
+      </c>
+      <c r="B17" s="173" t="inlineStr">
+        <is>
+          <t>Statistics South Africa (P0441.2 Provincial GDP)</t>
+        </is>
+      </c>
+      <c r="C17" s="173" t="inlineStr">
+        <is>
+          <t>https://www.statssa.gov.za/?page_id=1847</t>
+        </is>
+      </c>
+      <c r="D17" s="173" t="inlineStr">
+        <is>
+          <t>P0441.2  Provincial Gross Domestic Product(2024).zip, Tables 2-10, block c</t>
+        </is>
+      </c>
+      <c r="E17" s="173" t="inlineStr">
+        <is>
+          <t>on manish-branch (external/data/raw/statssa/)</t>
+        </is>
+      </c>
+      <c r="F17" s="173" t="inlineStr">
+        <is>
+          <t>assumptions/2026/timeseries/gdp_by_province_statssa.csv</t>
+        </is>
+      </c>
+      <c r="G17" s="173" t="inlineStr">
+        <is>
+          <t>python -m lfm.scripts.fetch_economy --vintage 2026</t>
+        </is>
+      </c>
+      <c r="H17" s="173" t="inlineStr">
+        <is>
+          <t>2013-2024</t>
+        </is>
+      </c>
+      <c r="I17" s="173" t="inlineStr">
+        <is>
+          <t>Annual, 2013-2024. Economic activity by province, not fuel litres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="173" t="inlineStr">
+        <is>
+          <t>Diesel by use: power generation</t>
+        </is>
+      </c>
+      <c r="B18" s="173" t="inlineStr">
+        <is>
+          <t>Eskom integrated reports</t>
+        </is>
+      </c>
+      <c r="C18" s="173" t="inlineStr">
+        <is>
+          <t>https://www.eskom.co.za/investors/integrated-results/</t>
+        </is>
+      </c>
+      <c r="D18" s="173" t="inlineStr">
+        <is>
+          <t>integrated report PDFs, years to March 2022-2026</t>
+        </is>
+      </c>
+      <c r="E18" s="173" t="inlineStr">
+        <is>
+          <t>local to Manish and Nigel; not on main</t>
+        </is>
+      </c>
+      <c r="F18" s="173" t="inlineStr">
+        <is>
+          <t>assumptions/2026/timeseries/ocgt_generation_eskom.csv</t>
+        </is>
+      </c>
+      <c r="G18" s="173" t="inlineStr">
+        <is>
+          <t>python -m lfm.scripts.fetch_eskom --vintage 2026</t>
+        </is>
+      </c>
+      <c r="H18" s="173" t="inlineStr">
+        <is>
+          <t>2022-2026</t>
+        </is>
+      </c>
+      <c r="I18" s="173" t="inlineStr">
+        <is>
+          <t>GWh for financial years; diesel litres not reported in the extract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="173" t="inlineStr">
+        <is>
+          <t>Diesel by use: the 0.31 litres per kWh factor</t>
+        </is>
+      </c>
+      <c r="B19" s="173" t="inlineStr">
+        <is>
+          <t>Parliament (replies by the Ministers of Public Enterprises and of Electricity and Energy)</t>
+        </is>
+      </c>
+      <c r="C19" s="173" t="inlineStr">
+        <is>
+          <t>https://pmg.org.za/committee-question/30686/</t>
+        </is>
+      </c>
+      <c r="D19" s="173" t="inlineStr">
+        <is>
+          <t>reply NW1980 (2025); press reports for 2022 and 2023</t>
+        </is>
+      </c>
+      <c r="E19" s="173" t="inlineStr">
+        <is>
+          <t>by link only</t>
+        </is>
+      </c>
+      <c r="F19" s="173" t="inlineStr">
+        <is>
+          <t>assumptions/2026/reference/ocgt_diesel_burn_reported.csv</t>
+        </is>
+      </c>
+      <c r="G19" s="173" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H19" s="173" t="inlineStr">
+        <is>
+          <t>2022-2025</t>
+        </is>
+      </c>
+      <c r="I19" s="173" t="inlineStr">
+        <is>
+          <t>Three years; none for the year to March 2024. Implies 0.31 litres per kWh; not adopted in the model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="173" t="inlineStr">
+        <is>
+          <t>Diesel by use: price used to convert road freight fuel spending to litres</t>
+        </is>
+      </c>
+      <c r="B20" s="173" t="inlineStr">
+        <is>
+          <t>Department of Mineral and Petroleum Resources (energy department)</t>
+        </is>
+      </c>
+      <c r="C20" s="173" t="inlineStr">
+        <is>
+          <t>https://www.dmpr.gov.za/Portals/0/Energy_Website/files/media/</t>
+        </is>
+      </c>
+      <c r="D20" s="173" t="inlineStr">
+        <is>
+          <t>fuel-price-history-&lt;year&gt;.pdf, 2011-2025; price-breakdown-&lt;year&gt;-&lt;month&gt;.pdf to February 2026; cef-daily-&lt;date&gt;.pdf from February 2026 (Central Energy Fund)</t>
+        </is>
+      </c>
+      <c r="E20" s="173" t="inlineStr">
+        <is>
+          <t>local to Manish and Nigel; not on main</t>
+        </is>
+      </c>
+      <c r="F20" s="173" t="inlineStr">
+        <is>
+          <t>assumptions/2026/timeseries/fuel_prices_department.csv</t>
+        </is>
+      </c>
+      <c r="G20" s="173" t="inlineStr">
+        <is>
+          <t>python -m lfm.scripts.fetch_energy_dept --vintage 2026</t>
+        </is>
+      </c>
+      <c r="H20" s="173" t="inlineStr">
+        <is>
+          <t>2011-01-2026-10</t>
+        </is>
+      </c>
+      <c r="I20" s="173" t="inlineStr">
+        <is>
+          <t>Runs to October 2026. Department to February 2026, then CEF daily sheets, which give inland prices only: coastal diesel has no value from December 2025, coastal petrol and paraffin none from March 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="173" t="inlineStr">
+        <is>
+          <t>Diesel by use and Vehicle history: vehicle classes, distance and fuel use</t>
+        </is>
+      </c>
+      <c r="B21" s="173" t="inlineStr">
+        <is>
+          <t>Stone, Merven, Maseela and Moonsamy (2018), J. Energy in Southern Africa 29(2), and supplement</t>
+        </is>
+      </c>
+      <c r="C21" s="173" t="inlineStr">
+        <is>
+          <t>https://www.scielo.org.za/pdf/jesa/v29n2/06.pdf</t>
+        </is>
+      </c>
+      <c r="D21" s="173" t="inlineStr">
+        <is>
+          <t>stone-2018-vehicle-parc-model-jesa-29-2.pdf; stone-2018-supplementary.pdf</t>
+        </is>
+      </c>
+      <c r="E21" s="173" t="inlineStr">
+        <is>
+          <t>on manish-branch (external/data/raw/literature/)</t>
+        </is>
+      </c>
+      <c r="F21" s="173" t="inlineStr">
+        <is>
+          <t>assumptions/2026/reference/vehicle_parameters_stone2018.csv</t>
+        </is>
+      </c>
+      <c r="G21" s="173" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H21" s="173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="173" t="inlineStr">
+        <is>
+          <t>Values are for 2014. Transcription not independently re-checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="173" t="inlineStr">
+        <is>
+          <t>Vehicle history: registered vehicles by class</t>
+        </is>
+      </c>
+      <c r="B22" s="173" t="inlineStr">
+        <is>
+          <t>NaTIS (Road Traffic Management Corporation)</t>
+        </is>
+      </c>
+      <c r="C22" s="173" t="inlineStr">
+        <is>
+          <t>https://www.natis.gov.za/</t>
+        </is>
+      </c>
+      <c r="D22" s="173" t="inlineStr">
+        <is>
+          <t>monthly live vehicle population PDFs</t>
+        </is>
+      </c>
+      <c r="E22" s="173" t="inlineStr">
+        <is>
+          <t>local to Manish and Nigel; not on main</t>
+        </is>
+      </c>
+      <c r="F22" s="173" t="inlineStr">
+        <is>
+          <t>assumptions/2026/timeseries/vehicle_population_natis.csv</t>
+        </is>
+      </c>
+      <c r="G22" s="173" t="inlineStr">
+        <is>
+          <t>python -m lfm.scripts.fetch_natis --vintage 2026</t>
+        </is>
+      </c>
+      <c r="H22" s="173" t="inlineStr">
+        <is>
+          <t>2021-02-2026-06</t>
+        </is>
+      </c>
+      <c r="I22" s="173" t="inlineStr">
+        <is>
+          <t>All fuels together; no petrol/diesel split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="173" t="inlineStr">
+        <is>
+          <t>Vehicle history: new sales by segment</t>
+        </is>
+      </c>
+      <c r="B23" s="173" t="inlineStr">
+        <is>
+          <t>naamsa, quarterly review of business conditions</t>
+        </is>
+      </c>
+      <c r="C23" s="173" t="inlineStr">
+        <is>
+          <t>https://naamsa.net/quarterly-reviews/</t>
+        </is>
+      </c>
+      <c r="D23" s="173" t="inlineStr">
+        <is>
+          <t>quarterly review PDFs</t>
+        </is>
+      </c>
+      <c r="E23" s="173" t="inlineStr">
+        <is>
+          <t>local to Manish and Nigel; not on main</t>
+        </is>
+      </c>
+      <c r="F23" s="173" t="inlineStr">
+        <is>
+          <t>assumptions/2026/timeseries/new_vehicle_market_naamsa.csv</t>
+        </is>
+      </c>
+      <c r="G23" s="173" t="inlineStr">
+        <is>
+          <t>python -m lfm.scripts.fetch_naamsa --vintage 2026</t>
+        </is>
+      </c>
+      <c r="H23" s="173" t="inlineStr">
+        <is>
+          <t>2015-2027</t>
+        </is>
+      </c>
+      <c r="I23" s="173" t="inlineStr">
+        <is>
+          <t>2026-2027 are naamsa's own outlook, not observations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="173" t="inlineStr">
+        <is>
+          <t>Vehicle history: electrified new sales</t>
+        </is>
+      </c>
+      <c r="B24" s="173" t="inlineStr">
+        <is>
+          <t>naamsa, quarterly review of business conditions</t>
+        </is>
+      </c>
+      <c r="C24" s="173" t="inlineStr">
+        <is>
+          <t>https://naamsa.net/quarterly-reviews/</t>
+        </is>
+      </c>
+      <c r="D24" s="173" t="inlineStr">
+        <is>
+          <t>quarterly review PDFs</t>
+        </is>
+      </c>
+      <c r="E24" s="173" t="inlineStr">
+        <is>
+          <t>local to Manish and Nigel; not on main</t>
+        </is>
+      </c>
+      <c r="F24" s="173" t="inlineStr">
+        <is>
+          <t>assumptions/2026/timeseries/nev_sales_naamsa.csv</t>
+        </is>
+      </c>
+      <c r="G24" s="173" t="inlineStr">
+        <is>
+          <t>python -m lfm.scripts.fetch_naamsa --vintage 2026</t>
+        </is>
+      </c>
+      <c r="H24" s="173" t="inlineStr">
+        <is>
+          <t>2019-2025</t>
+        </is>
+      </c>
+      <c r="I24" s="173" t="inlineStr">
+        <is>
+          <t>New sales, not fleet. Audit logged parser warnings on the 5 October refresh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="173" t="inlineStr">
+        <is>
+          <t>Vehicle history: fuel split of the registered fleet</t>
+        </is>
+      </c>
+      <c r="B25" s="173" t="inlineStr">
+        <is>
+          <t>Department of Transport, Transport Statistics Bulletin 2023, Table 2.8 (source: RTMC)</t>
+        </is>
+      </c>
+      <c r="C25" s="173" t="inlineStr">
+        <is>
+          <t>https://www.transport.gov.za/wp-content/uploads/2023/02/Transport-Statistics-Bulletin-2023.pdf</t>
+        </is>
+      </c>
+      <c r="D25" s="173" t="inlineStr">
+        <is>
+          <t>dot-transport-statistics-bulletin-2023.pdf, p.40</t>
+        </is>
+      </c>
+      <c r="E25" s="173" t="inlineStr">
+        <is>
+          <t>on manish-branch (external/data/raw/literature/)</t>
+        </is>
+      </c>
+      <c r="F25" s="173" t="inlineStr">
+        <is>
+          <t>assumptions/2026/reference/vehicle_population_by_fuel_dot2023.csv</t>
+        </is>
+      </c>
+      <c r="G25" s="173" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H25" s="173" t="inlineStr">
+        <is>
+          <t>2023-12-2023-12</t>
+        </is>
+      </c>
+      <c r="I25" s="173" t="inlineStr">
+        <is>
+          <t>One date only (December 2023). No later edition found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="173" t="inlineStr">
+        <is>
+          <t>Diesel by use: fuel bought by road freight businesses</t>
+        </is>
+      </c>
+      <c r="B26" s="173" t="inlineStr">
+        <is>
+          <t>Statistics South Africa</t>
+        </is>
+      </c>
+      <c r="C26" s="173" t="inlineStr">
+        <is>
+          <t>https://www.statssa.gov.za/?page_id=1854&amp;PPN=Report-71-02-01</t>
+        </is>
+      </c>
+      <c r="D26" s="173" t="inlineStr">
+        <is>
+          <t>Report-71-02-012023.pdf, Table 20 (p.33)</t>
+        </is>
+      </c>
+      <c r="E26" s="173" t="inlineStr">
+        <is>
+          <t>on manish-branch (external/data/raw/statssa/statssa-transport-and-storage-industry-2023.pdf)</t>
+        </is>
+      </c>
+      <c r="F26" s="173" t="inlineStr">
+        <is>
+          <t>typed into build_demand_baseline_workbook.py (ROAD_FREIGHT_FUEL_RAND)</t>
+        </is>
+      </c>
+      <c r="G26" s="173" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H26" s="173" t="inlineStr">
+        <is>
+          <t>2019, 2023</t>
+        </is>
+      </c>
+      <c r="I26" s="173" t="inlineStr">
+        <is>
+          <t>Hire-and-reward operators only; 2023 preliminary</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="173" t="inlineStr">
+        <is>
+          <t>Diesel by use: land freight share of diesel</t>
+        </is>
+      </c>
+      <c r="B27" s="173" t="inlineStr">
+        <is>
+          <t>Merven, Hartley and Ahjum (2019), SA-TIED Working Paper 60</t>
+        </is>
+      </c>
+      <c r="C27" s="173" t="inlineStr">
+        <is>
+          <t>https://sa-tied.wider.unu.edu/sites/default/files/pdf/SATIED_WP60_Merven_Hartley_Ahjum_April_2019.pdf</t>
+        </is>
+      </c>
+      <c r="D27" s="173" t="inlineStr">
+        <is>
+          <t>p.10</t>
+        </is>
+      </c>
+      <c r="E27" s="173" t="inlineStr">
+        <is>
+          <t>on manish-branch (external/data/raw/literature/)</t>
+        </is>
+      </c>
+      <c r="F27" s="173" t="inlineStr">
+        <is>
+          <t>quoted on the sheet</t>
+        </is>
+      </c>
+      <c r="G27" s="173" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H27" s="173" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I27" s="173" t="inlineStr">
+        <is>
+          <t>Modelled; same research group as the vehicle study</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="173" t="inlineStr">
+        <is>
+          <t>Vehicle history and Diesel by use: the model's settings</t>
+        </is>
+      </c>
+      <c r="B28" s="173" t="inlineStr">
+        <is>
+          <t>AIA (Reatile workbook, March 2025)</t>
+        </is>
+      </c>
+      <c r="C28" s="173" t="inlineStr"/>
+      <c r="D28" s="173" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml</t>
+        </is>
+      </c>
+      <c r="E28" s="173" t="inlineStr">
+        <is>
+          <t>in the repository</t>
+        </is>
+      </c>
+      <c r="F28" s="173" t="inlineStr">
+        <is>
+          <t>assumptions/2026/vehicles.yaml</t>
+        </is>
+      </c>
+      <c r="G28" s="173" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H28" s="173" t="inlineStr"/>
+      <c r="I28" s="173" t="inlineStr">
+        <is>
+          <t>Placeholders without a published source</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="173" t="inlineStr">
+        <is>
+          <t>HML response</t>
+        </is>
+      </c>
+      <c r="B29" s="173" t="inlineStr">
+        <is>
+          <t>AIA (analyst), from the sources named in each row</t>
+        </is>
+      </c>
+      <c r="C29" s="173" t="inlineStr"/>
+      <c r="D29" s="173" t="inlineStr">
+        <is>
+          <t>workstreams/WS2_model_development/fuel_lever_response_2026-10-07.csv</t>
+        </is>
+      </c>
+      <c r="E29" s="173" t="inlineStr">
+        <is>
+          <t>in the repository</t>
+        </is>
+      </c>
+      <c r="F29" s="173" t="inlineStr">
+        <is>
+          <t>same file</t>
+        </is>
+      </c>
+      <c r="G29" s="173" t="inlineStr">
+        <is>
+          <t>python -m lfm.scripts.build_fuel_lever_response --vintage 2026</t>
+        </is>
+      </c>
+      <c r="H29" s="173" t="inlineStr">
+        <is>
+          <t>2030, 2035</t>
+        </is>
+      </c>
+      <c r="I29" s="173" t="inlineStr">
+        <is>
+          <t>Proposals</t>
         </is>
       </c>
     </row>
